--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="115">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -218,12 +218,156 @@
   </si>
   <si>
     <t>Nº</t>
+  </si>
+  <si>
+    <t>USA MLS</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>Los Angeles FC</t>
+  </si>
+  <si>
+    <t>Inter Miami</t>
+  </si>
+  <si>
+    <t>Atlanta United FC</t>
+  </si>
+  <si>
+    <t>FC Cincinnati</t>
+  </si>
+  <si>
+    <t>Columbus Crew</t>
+  </si>
+  <si>
+    <t>DC United</t>
+  </si>
+  <si>
+    <t>Orlando City</t>
+  </si>
+  <si>
+    <t>Austin</t>
+  </si>
+  <si>
+    <t>Houston Dynamo</t>
+  </si>
+  <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
+    <t>St. Louis City</t>
+  </si>
+  <si>
+    <t>SJ Earthquakes</t>
+  </si>
+  <si>
+    <t>Seattle Sounders</t>
+  </si>
+  <si>
+    <t>Minnesota United</t>
+  </si>
+  <si>
+    <t>New York City</t>
+  </si>
+  <si>
+    <t>Montreal Impact</t>
+  </si>
+  <si>
+    <t>New York RB</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>Toronto</t>
+  </si>
+  <si>
+    <t>Philadelphia Union</t>
+  </si>
+  <si>
+    <t>Sporting KC</t>
+  </si>
+  <si>
+    <t>FC Dallas</t>
+  </si>
+  <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
+    <t>Colorado Rapids</t>
+  </si>
+  <si>
+    <t>Real Salt Lake</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>['78']</t>
+  </si>
+  <si>
+    <t>['5', '90+10']</t>
+  </si>
+  <si>
+    <t>['41', '63', '85']</t>
+  </si>
+  <si>
+    <t>['70']</t>
+  </si>
+  <si>
+    <t>['19', '37', '45+1', '50']</t>
+  </si>
+  <si>
+    <t>['8', '35']</t>
+  </si>
+  <si>
+    <t>['8', '79']</t>
+  </si>
+  <si>
+    <t>['76']</t>
+  </si>
+  <si>
+    <t>['18']</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>['28', '70', '74', '83']</t>
+  </si>
+  <si>
+    <t>['19', '49']</t>
+  </si>
+  <si>
+    <t>['26', '55']</t>
+  </si>
+  <si>
+    <t>['47', '71']</t>
+  </si>
+  <si>
+    <t>['13', '22']</t>
+  </si>
+  <si>
+    <t>['27', '70']</t>
+  </si>
+  <si>
+    <t>['23', '48', '51', '64']</t>
+  </si>
+  <si>
+    <t>['55', '76']</t>
+  </si>
+  <si>
+    <t>['35', '90+2']</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -276,11 +420,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -784,6 +929,2684 @@
         <v>66</v>
       </c>
     </row>
+    <row r="2" spans="1:68">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>7781076</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45710.78125</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2" t="s">
+        <v>96</v>
+      </c>
+      <c r="P2" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q2">
+        <v>2.3</v>
+      </c>
+      <c r="R2">
+        <v>2.38</v>
+      </c>
+      <c r="S2">
+        <v>4.5</v>
+      </c>
+      <c r="T2">
+        <v>1.3</v>
+      </c>
+      <c r="U2">
+        <v>3.4</v>
+      </c>
+      <c r="V2">
+        <v>2.5</v>
+      </c>
+      <c r="W2">
+        <v>1.5</v>
+      </c>
+      <c r="X2">
+        <v>6</v>
+      </c>
+      <c r="Y2">
+        <v>1.13</v>
+      </c>
+      <c r="Z2">
+        <v>1.71</v>
+      </c>
+      <c r="AA2">
+        <v>3.89</v>
+      </c>
+      <c r="AB2">
+        <v>4.4</v>
+      </c>
+      <c r="AC2">
+        <v>1.03</v>
+      </c>
+      <c r="AD2">
+        <v>15</v>
+      </c>
+      <c r="AE2">
+        <v>1.22</v>
+      </c>
+      <c r="AF2">
+        <v>4.33</v>
+      </c>
+      <c r="AG2">
+        <v>1.6</v>
+      </c>
+      <c r="AH2">
+        <v>2.2</v>
+      </c>
+      <c r="AI2">
+        <v>1.62</v>
+      </c>
+      <c r="AJ2">
+        <v>2.2</v>
+      </c>
+      <c r="AK2">
+        <v>1.21</v>
+      </c>
+      <c r="AL2">
+        <v>1.24</v>
+      </c>
+      <c r="AM2">
+        <v>2.05</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>3</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>6</v>
+      </c>
+      <c r="AV2">
+        <v>2</v>
+      </c>
+      <c r="AW2">
+        <v>6</v>
+      </c>
+      <c r="AX2">
+        <v>11</v>
+      </c>
+      <c r="AY2">
+        <v>14</v>
+      </c>
+      <c r="AZ2">
+        <v>16</v>
+      </c>
+      <c r="BA2">
+        <v>4</v>
+      </c>
+      <c r="BB2">
+        <v>4</v>
+      </c>
+      <c r="BC2">
+        <v>8</v>
+      </c>
+      <c r="BD2">
+        <v>1.44</v>
+      </c>
+      <c r="BE2">
+        <v>7</v>
+      </c>
+      <c r="BF2">
+        <v>3.05</v>
+      </c>
+      <c r="BG2">
+        <v>1.19</v>
+      </c>
+      <c r="BH2">
+        <v>4</v>
+      </c>
+      <c r="BI2">
+        <v>1.34</v>
+      </c>
+      <c r="BJ2">
+        <v>2.9</v>
+      </c>
+      <c r="BK2">
+        <v>1.57</v>
+      </c>
+      <c r="BL2">
+        <v>2.23</v>
+      </c>
+      <c r="BM2">
+        <v>1.9</v>
+      </c>
+      <c r="BN2">
+        <v>1.79</v>
+      </c>
+      <c r="BO2">
+        <v>2.33</v>
+      </c>
+      <c r="BP2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:68">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>7781075</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45710.89583333334</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+      <c r="N3">
+        <v>4</v>
+      </c>
+      <c r="O3" t="s">
+        <v>97</v>
+      </c>
+      <c r="P3" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q3">
+        <v>2.25</v>
+      </c>
+      <c r="R3">
+        <v>2.4</v>
+      </c>
+      <c r="S3">
+        <v>4.33</v>
+      </c>
+      <c r="T3">
+        <v>1.29</v>
+      </c>
+      <c r="U3">
+        <v>3.5</v>
+      </c>
+      <c r="V3">
+        <v>2.25</v>
+      </c>
+      <c r="W3">
+        <v>1.57</v>
+      </c>
+      <c r="X3">
+        <v>5.5</v>
+      </c>
+      <c r="Y3">
+        <v>1.14</v>
+      </c>
+      <c r="Z3">
+        <v>1.71</v>
+      </c>
+      <c r="AA3">
+        <v>3.77</v>
+      </c>
+      <c r="AB3">
+        <v>4.6</v>
+      </c>
+      <c r="AC3">
+        <v>1.03</v>
+      </c>
+      <c r="AD3">
+        <v>17</v>
+      </c>
+      <c r="AE3">
+        <v>1.18</v>
+      </c>
+      <c r="AF3">
+        <v>5</v>
+      </c>
+      <c r="AG3">
+        <v>1.55</v>
+      </c>
+      <c r="AH3">
+        <v>2.36</v>
+      </c>
+      <c r="AI3">
+        <v>1.57</v>
+      </c>
+      <c r="AJ3">
+        <v>2.25</v>
+      </c>
+      <c r="AK3">
+        <v>1.19</v>
+      </c>
+      <c r="AL3">
+        <v>1.23</v>
+      </c>
+      <c r="AM3">
+        <v>2.1</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>1</v>
+      </c>
+      <c r="AQ3">
+        <v>1</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>7</v>
+      </c>
+      <c r="AV3">
+        <v>6</v>
+      </c>
+      <c r="AW3">
+        <v>6</v>
+      </c>
+      <c r="AX3">
+        <v>3</v>
+      </c>
+      <c r="AY3">
+        <v>18</v>
+      </c>
+      <c r="AZ3">
+        <v>10</v>
+      </c>
+      <c r="BA3">
+        <v>7</v>
+      </c>
+      <c r="BB3">
+        <v>2</v>
+      </c>
+      <c r="BC3">
+        <v>9</v>
+      </c>
+      <c r="BD3">
+        <v>1.72</v>
+      </c>
+      <c r="BE3">
+        <v>6.5</v>
+      </c>
+      <c r="BF3">
+        <v>2.4</v>
+      </c>
+      <c r="BG3">
+        <v>1.36</v>
+      </c>
+      <c r="BH3">
+        <v>2.85</v>
+      </c>
+      <c r="BI3">
+        <v>1.61</v>
+      </c>
+      <c r="BJ3">
+        <v>2.15</v>
+      </c>
+      <c r="BK3">
+        <v>1.98</v>
+      </c>
+      <c r="BL3">
+        <v>1.72</v>
+      </c>
+      <c r="BM3">
+        <v>2.55</v>
+      </c>
+      <c r="BN3">
+        <v>1.44</v>
+      </c>
+      <c r="BO3">
+        <v>3.3</v>
+      </c>
+      <c r="BP3">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7781077</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45710.89583333334</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+      <c r="N4">
+        <v>5</v>
+      </c>
+      <c r="O4" t="s">
+        <v>98</v>
+      </c>
+      <c r="P4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q4">
+        <v>2.2</v>
+      </c>
+      <c r="R4">
+        <v>2.4</v>
+      </c>
+      <c r="S4">
+        <v>5</v>
+      </c>
+      <c r="T4">
+        <v>1.3</v>
+      </c>
+      <c r="U4">
+        <v>3.4</v>
+      </c>
+      <c r="V4">
+        <v>2.5</v>
+      </c>
+      <c r="W4">
+        <v>1.5</v>
+      </c>
+      <c r="X4">
+        <v>6</v>
+      </c>
+      <c r="Y4">
+        <v>1.13</v>
+      </c>
+      <c r="Z4">
+        <v>1.66</v>
+      </c>
+      <c r="AA4">
+        <v>3.79</v>
+      </c>
+      <c r="AB4">
+        <v>4.9</v>
+      </c>
+      <c r="AC4">
+        <v>1.03</v>
+      </c>
+      <c r="AD4">
+        <v>15</v>
+      </c>
+      <c r="AE4">
+        <v>1.2</v>
+      </c>
+      <c r="AF4">
+        <v>4.5</v>
+      </c>
+      <c r="AG4">
+        <v>1.61</v>
+      </c>
+      <c r="AH4">
+        <v>2.15</v>
+      </c>
+      <c r="AI4">
+        <v>1.67</v>
+      </c>
+      <c r="AJ4">
+        <v>2.1</v>
+      </c>
+      <c r="AK4">
+        <v>1.18</v>
+      </c>
+      <c r="AL4">
+        <v>1.24</v>
+      </c>
+      <c r="AM4">
+        <v>2.15</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>3</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>8</v>
+      </c>
+      <c r="AV4">
+        <v>7</v>
+      </c>
+      <c r="AW4">
+        <v>8</v>
+      </c>
+      <c r="AX4">
+        <v>6</v>
+      </c>
+      <c r="AY4">
+        <v>19</v>
+      </c>
+      <c r="AZ4">
+        <v>14</v>
+      </c>
+      <c r="BA4">
+        <v>7</v>
+      </c>
+      <c r="BB4">
+        <v>5</v>
+      </c>
+      <c r="BC4">
+        <v>12</v>
+      </c>
+      <c r="BD4">
+        <v>1.43</v>
+      </c>
+      <c r="BE4">
+        <v>7</v>
+      </c>
+      <c r="BF4">
+        <v>3.15</v>
+      </c>
+      <c r="BG4">
+        <v>1.28</v>
+      </c>
+      <c r="BH4">
+        <v>3.2</v>
+      </c>
+      <c r="BI4">
+        <v>1.48</v>
+      </c>
+      <c r="BJ4">
+        <v>2.43</v>
+      </c>
+      <c r="BK4">
+        <v>1.78</v>
+      </c>
+      <c r="BL4">
+        <v>1.9</v>
+      </c>
+      <c r="BM4">
+        <v>2.23</v>
+      </c>
+      <c r="BN4">
+        <v>1.57</v>
+      </c>
+      <c r="BO4">
+        <v>2.8</v>
+      </c>
+      <c r="BP4">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:68">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7781078</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45710.89583333334</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5" t="s">
+        <v>99</v>
+      </c>
+      <c r="P5" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q5">
+        <v>2.75</v>
+      </c>
+      <c r="R5">
+        <v>2.25</v>
+      </c>
+      <c r="S5">
+        <v>3.75</v>
+      </c>
+      <c r="T5">
+        <v>1.33</v>
+      </c>
+      <c r="U5">
+        <v>3.25</v>
+      </c>
+      <c r="V5">
+        <v>2.63</v>
+      </c>
+      <c r="W5">
+        <v>1.44</v>
+      </c>
+      <c r="X5">
+        <v>7</v>
+      </c>
+      <c r="Y5">
+        <v>1.1</v>
+      </c>
+      <c r="Z5">
+        <v>1.96</v>
+      </c>
+      <c r="AA5">
+        <v>3.52</v>
+      </c>
+      <c r="AB5">
+        <v>3.63</v>
+      </c>
+      <c r="AC5">
+        <v>1.04</v>
+      </c>
+      <c r="AD5">
+        <v>13</v>
+      </c>
+      <c r="AE5">
+        <v>1.26</v>
+      </c>
+      <c r="AF5">
+        <v>4</v>
+      </c>
+      <c r="AG5">
+        <v>1.73</v>
+      </c>
+      <c r="AH5">
+        <v>2</v>
+      </c>
+      <c r="AI5">
+        <v>1.62</v>
+      </c>
+      <c r="AJ5">
+        <v>2.2</v>
+      </c>
+      <c r="AK5">
+        <v>1.3</v>
+      </c>
+      <c r="AL5">
+        <v>1.28</v>
+      </c>
+      <c r="AM5">
+        <v>1.75</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>3</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>3</v>
+      </c>
+      <c r="AV5">
+        <v>4</v>
+      </c>
+      <c r="AW5">
+        <v>8</v>
+      </c>
+      <c r="AX5">
+        <v>13</v>
+      </c>
+      <c r="AY5">
+        <v>13</v>
+      </c>
+      <c r="AZ5">
+        <v>20</v>
+      </c>
+      <c r="BA5">
+        <v>4</v>
+      </c>
+      <c r="BB5">
+        <v>2</v>
+      </c>
+      <c r="BC5">
+        <v>6</v>
+      </c>
+      <c r="BD5">
+        <v>1.57</v>
+      </c>
+      <c r="BE5">
+        <v>6.75</v>
+      </c>
+      <c r="BF5">
+        <v>2.65</v>
+      </c>
+      <c r="BG5">
+        <v>1.24</v>
+      </c>
+      <c r="BH5">
+        <v>3.55</v>
+      </c>
+      <c r="BI5">
+        <v>1.41</v>
+      </c>
+      <c r="BJ5">
+        <v>2.63</v>
+      </c>
+      <c r="BK5">
+        <v>1.68</v>
+      </c>
+      <c r="BL5">
+        <v>2.02</v>
+      </c>
+      <c r="BM5">
+        <v>2.07</v>
+      </c>
+      <c r="BN5">
+        <v>1.66</v>
+      </c>
+      <c r="BO5">
+        <v>2.65</v>
+      </c>
+      <c r="BP5">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>7781079</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45710.89583333334</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="N6">
+        <v>6</v>
+      </c>
+      <c r="O6" t="s">
+        <v>100</v>
+      </c>
+      <c r="P6" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q6">
+        <v>1.95</v>
+      </c>
+      <c r="R6">
+        <v>2.5</v>
+      </c>
+      <c r="S6">
+        <v>5.5</v>
+      </c>
+      <c r="T6">
+        <v>1.29</v>
+      </c>
+      <c r="U6">
+        <v>3.5</v>
+      </c>
+      <c r="V6">
+        <v>2.25</v>
+      </c>
+      <c r="W6">
+        <v>1.57</v>
+      </c>
+      <c r="X6">
+        <v>5.5</v>
+      </c>
+      <c r="Y6">
+        <v>1.14</v>
+      </c>
+      <c r="Z6">
+        <v>1.45</v>
+      </c>
+      <c r="AA6">
+        <v>4.4</v>
+      </c>
+      <c r="AB6">
+        <v>6.4</v>
+      </c>
+      <c r="AC6">
+        <v>1.02</v>
+      </c>
+      <c r="AD6">
+        <v>19</v>
+      </c>
+      <c r="AE6">
+        <v>1.18</v>
+      </c>
+      <c r="AF6">
+        <v>5</v>
+      </c>
+      <c r="AG6">
+        <v>1.58</v>
+      </c>
+      <c r="AH6">
+        <v>2.29</v>
+      </c>
+      <c r="AI6">
+        <v>1.7</v>
+      </c>
+      <c r="AJ6">
+        <v>2.05</v>
+      </c>
+      <c r="AK6">
+        <v>1.13</v>
+      </c>
+      <c r="AL6">
+        <v>1.18</v>
+      </c>
+      <c r="AM6">
+        <v>2.6</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>3</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>8</v>
+      </c>
+      <c r="AV6">
+        <v>6</v>
+      </c>
+      <c r="AW6">
+        <v>8</v>
+      </c>
+      <c r="AX6">
+        <v>8</v>
+      </c>
+      <c r="AY6">
+        <v>17</v>
+      </c>
+      <c r="AZ6">
+        <v>16</v>
+      </c>
+      <c r="BA6">
+        <v>5</v>
+      </c>
+      <c r="BB6">
+        <v>2</v>
+      </c>
+      <c r="BC6">
+        <v>7</v>
+      </c>
+      <c r="BD6">
+        <v>1.35</v>
+      </c>
+      <c r="BE6">
+        <v>7</v>
+      </c>
+      <c r="BF6">
+        <v>3.55</v>
+      </c>
+      <c r="BG6">
+        <v>1.4</v>
+      </c>
+      <c r="BH6">
+        <v>2.7</v>
+      </c>
+      <c r="BI6">
+        <v>1.66</v>
+      </c>
+      <c r="BJ6">
+        <v>2.07</v>
+      </c>
+      <c r="BK6">
+        <v>2.05</v>
+      </c>
+      <c r="BL6">
+        <v>1.67</v>
+      </c>
+      <c r="BM6">
+        <v>2.63</v>
+      </c>
+      <c r="BN6">
+        <v>1.42</v>
+      </c>
+      <c r="BO6">
+        <v>3.45</v>
+      </c>
+      <c r="BP6">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7781080</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45710.89583333334</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>88</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+      <c r="N7">
+        <v>4</v>
+      </c>
+      <c r="O7" t="s">
+        <v>101</v>
+      </c>
+      <c r="P7" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q7">
+        <v>2.38</v>
+      </c>
+      <c r="R7">
+        <v>2.4</v>
+      </c>
+      <c r="S7">
+        <v>4</v>
+      </c>
+      <c r="T7">
+        <v>1.29</v>
+      </c>
+      <c r="U7">
+        <v>3.5</v>
+      </c>
+      <c r="V7">
+        <v>2.38</v>
+      </c>
+      <c r="W7">
+        <v>1.53</v>
+      </c>
+      <c r="X7">
+        <v>5.5</v>
+      </c>
+      <c r="Y7">
+        <v>1.14</v>
+      </c>
+      <c r="Z7">
+        <v>1.81</v>
+      </c>
+      <c r="AA7">
+        <v>3.65</v>
+      </c>
+      <c r="AB7">
+        <v>4.1</v>
+      </c>
+      <c r="AC7">
+        <v>1.03</v>
+      </c>
+      <c r="AD7">
+        <v>15</v>
+      </c>
+      <c r="AE7">
+        <v>1.2</v>
+      </c>
+      <c r="AF7">
+        <v>4.5</v>
+      </c>
+      <c r="AG7">
+        <v>1.63</v>
+      </c>
+      <c r="AH7">
+        <v>2.19</v>
+      </c>
+      <c r="AI7">
+        <v>1.53</v>
+      </c>
+      <c r="AJ7">
+        <v>2.38</v>
+      </c>
+      <c r="AK7">
+        <v>1.25</v>
+      </c>
+      <c r="AL7">
+        <v>1.25</v>
+      </c>
+      <c r="AM7">
+        <v>1.93</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>1</v>
+      </c>
+      <c r="AQ7">
+        <v>1</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>5</v>
+      </c>
+      <c r="AV7">
+        <v>8</v>
+      </c>
+      <c r="AW7">
+        <v>5</v>
+      </c>
+      <c r="AX7">
+        <v>6</v>
+      </c>
+      <c r="AY7">
+        <v>11</v>
+      </c>
+      <c r="AZ7">
+        <v>15</v>
+      </c>
+      <c r="BA7">
+        <v>2</v>
+      </c>
+      <c r="BB7">
+        <v>7</v>
+      </c>
+      <c r="BC7">
+        <v>9</v>
+      </c>
+      <c r="BD7">
+        <v>1.5</v>
+      </c>
+      <c r="BE7">
+        <v>6.75</v>
+      </c>
+      <c r="BF7">
+        <v>2.9</v>
+      </c>
+      <c r="BG7">
+        <v>1.3</v>
+      </c>
+      <c r="BH7">
+        <v>3.15</v>
+      </c>
+      <c r="BI7">
+        <v>1.52</v>
+      </c>
+      <c r="BJ7">
+        <v>2.33</v>
+      </c>
+      <c r="BK7">
+        <v>1.84</v>
+      </c>
+      <c r="BL7">
+        <v>1.84</v>
+      </c>
+      <c r="BM7">
+        <v>2.32</v>
+      </c>
+      <c r="BN7">
+        <v>1.52</v>
+      </c>
+      <c r="BO7">
+        <v>2.95</v>
+      </c>
+      <c r="BP7">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7781081</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45710.89583333334</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>4</v>
+      </c>
+      <c r="N8">
+        <v>6</v>
+      </c>
+      <c r="O8" t="s">
+        <v>102</v>
+      </c>
+      <c r="P8" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q8">
+        <v>2.25</v>
+      </c>
+      <c r="R8">
+        <v>2.4</v>
+      </c>
+      <c r="S8">
+        <v>4.5</v>
+      </c>
+      <c r="T8">
+        <v>1.29</v>
+      </c>
+      <c r="U8">
+        <v>3.5</v>
+      </c>
+      <c r="V8">
+        <v>2.38</v>
+      </c>
+      <c r="W8">
+        <v>1.53</v>
+      </c>
+      <c r="X8">
+        <v>5.5</v>
+      </c>
+      <c r="Y8">
+        <v>1.14</v>
+      </c>
+      <c r="Z8">
+        <v>1.67</v>
+      </c>
+      <c r="AA8">
+        <v>4.2</v>
+      </c>
+      <c r="AB8">
+        <v>4.33</v>
+      </c>
+      <c r="AC8">
+        <v>1.02</v>
+      </c>
+      <c r="AD8">
+        <v>19</v>
+      </c>
+      <c r="AE8">
+        <v>1.18</v>
+      </c>
+      <c r="AF8">
+        <v>5</v>
+      </c>
+      <c r="AG8">
+        <v>1.55</v>
+      </c>
+      <c r="AH8">
+        <v>2.36</v>
+      </c>
+      <c r="AI8">
+        <v>1.57</v>
+      </c>
+      <c r="AJ8">
+        <v>2.25</v>
+      </c>
+      <c r="AK8">
+        <v>1.22</v>
+      </c>
+      <c r="AL8">
+        <v>1.24</v>
+      </c>
+      <c r="AM8">
+        <v>2.05</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>3</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>8</v>
+      </c>
+      <c r="AV8">
+        <v>5</v>
+      </c>
+      <c r="AW8">
+        <v>11</v>
+      </c>
+      <c r="AX8">
+        <v>3</v>
+      </c>
+      <c r="AY8">
+        <v>24</v>
+      </c>
+      <c r="AZ8">
+        <v>9</v>
+      </c>
+      <c r="BA8">
+        <v>7</v>
+      </c>
+      <c r="BB8">
+        <v>8</v>
+      </c>
+      <c r="BC8">
+        <v>15</v>
+      </c>
+      <c r="BD8">
+        <v>1.47</v>
+      </c>
+      <c r="BE8">
+        <v>6.75</v>
+      </c>
+      <c r="BF8">
+        <v>3.05</v>
+      </c>
+      <c r="BG8">
+        <v>1.28</v>
+      </c>
+      <c r="BH8">
+        <v>3.3</v>
+      </c>
+      <c r="BI8">
+        <v>1.47</v>
+      </c>
+      <c r="BJ8">
+        <v>2.43</v>
+      </c>
+      <c r="BK8">
+        <v>1.77</v>
+      </c>
+      <c r="BL8">
+        <v>1.92</v>
+      </c>
+      <c r="BM8">
+        <v>2.2</v>
+      </c>
+      <c r="BN8">
+        <v>1.58</v>
+      </c>
+      <c r="BO8">
+        <v>2.8</v>
+      </c>
+      <c r="BP8">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:68">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>7781082</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2">
+        <v>45710.9375</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" t="s">
+        <v>103</v>
+      </c>
+      <c r="P9" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q9">
+        <v>2.3</v>
+      </c>
+      <c r="R9">
+        <v>2.4</v>
+      </c>
+      <c r="S9">
+        <v>4.33</v>
+      </c>
+      <c r="T9">
+        <v>1.29</v>
+      </c>
+      <c r="U9">
+        <v>3.5</v>
+      </c>
+      <c r="V9">
+        <v>2.25</v>
+      </c>
+      <c r="W9">
+        <v>1.57</v>
+      </c>
+      <c r="X9">
+        <v>5.5</v>
+      </c>
+      <c r="Y9">
+        <v>1.14</v>
+      </c>
+      <c r="Z9">
+        <v>1.87</v>
+      </c>
+      <c r="AA9">
+        <v>3.78</v>
+      </c>
+      <c r="AB9">
+        <v>3.7</v>
+      </c>
+      <c r="AC9">
+        <v>1.02</v>
+      </c>
+      <c r="AD9">
+        <v>19</v>
+      </c>
+      <c r="AE9">
+        <v>1.18</v>
+      </c>
+      <c r="AF9">
+        <v>5</v>
+      </c>
+      <c r="AG9">
+        <v>1.59</v>
+      </c>
+      <c r="AH9">
+        <v>2.35</v>
+      </c>
+      <c r="AI9">
+        <v>1.53</v>
+      </c>
+      <c r="AJ9">
+        <v>2.38</v>
+      </c>
+      <c r="AK9">
+        <v>1.25</v>
+      </c>
+      <c r="AL9">
+        <v>1.24</v>
+      </c>
+      <c r="AM9">
+        <v>1.95</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>3</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>3</v>
+      </c>
+      <c r="AV9">
+        <v>3</v>
+      </c>
+      <c r="AW9">
+        <v>10</v>
+      </c>
+      <c r="AX9">
+        <v>5</v>
+      </c>
+      <c r="AY9">
+        <v>16</v>
+      </c>
+      <c r="AZ9">
+        <v>11</v>
+      </c>
+      <c r="BA9">
+        <v>4</v>
+      </c>
+      <c r="BB9">
+        <v>1</v>
+      </c>
+      <c r="BC9">
+        <v>5</v>
+      </c>
+      <c r="BD9">
+        <v>1.71</v>
+      </c>
+      <c r="BE9">
+        <v>6.5</v>
+      </c>
+      <c r="BF9">
+        <v>2.4</v>
+      </c>
+      <c r="BG9">
+        <v>1.23</v>
+      </c>
+      <c r="BH9">
+        <v>3.65</v>
+      </c>
+      <c r="BI9">
+        <v>1.41</v>
+      </c>
+      <c r="BJ9">
+        <v>2.65</v>
+      </c>
+      <c r="BK9">
+        <v>1.66</v>
+      </c>
+      <c r="BL9">
+        <v>2.07</v>
+      </c>
+      <c r="BM9">
+        <v>2.04</v>
+      </c>
+      <c r="BN9">
+        <v>1.67</v>
+      </c>
+      <c r="BO9">
+        <v>2.55</v>
+      </c>
+      <c r="BP9">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:68">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>7781083</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="2">
+        <v>45710.9375</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s">
+        <v>91</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>2</v>
+      </c>
+      <c r="N10">
+        <v>3</v>
+      </c>
+      <c r="O10" t="s">
+        <v>104</v>
+      </c>
+      <c r="P10" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q10">
+        <v>2.5</v>
+      </c>
+      <c r="R10">
+        <v>2.25</v>
+      </c>
+      <c r="S10">
+        <v>4.33</v>
+      </c>
+      <c r="T10">
+        <v>1.36</v>
+      </c>
+      <c r="U10">
+        <v>3</v>
+      </c>
+      <c r="V10">
+        <v>2.63</v>
+      </c>
+      <c r="W10">
+        <v>1.44</v>
+      </c>
+      <c r="X10">
+        <v>7</v>
+      </c>
+      <c r="Y10">
+        <v>1.1</v>
+      </c>
+      <c r="Z10">
+        <v>1.83</v>
+      </c>
+      <c r="AA10">
+        <v>3.47</v>
+      </c>
+      <c r="AB10">
+        <v>4.2</v>
+      </c>
+      <c r="AC10">
+        <v>1.03</v>
+      </c>
+      <c r="AD10">
+        <v>13</v>
+      </c>
+      <c r="AE10">
+        <v>1.25</v>
+      </c>
+      <c r="AF10">
+        <v>4</v>
+      </c>
+      <c r="AG10">
+        <v>1.79</v>
+      </c>
+      <c r="AH10">
+        <v>1.95</v>
+      </c>
+      <c r="AI10">
+        <v>1.7</v>
+      </c>
+      <c r="AJ10">
+        <v>2.05</v>
+      </c>
+      <c r="AK10">
+        <v>1.22</v>
+      </c>
+      <c r="AL10">
+        <v>1.27</v>
+      </c>
+      <c r="AM10">
+        <v>1.95</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>3</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>4</v>
+      </c>
+      <c r="AV10">
+        <v>5</v>
+      </c>
+      <c r="AW10">
+        <v>7</v>
+      </c>
+      <c r="AX10">
+        <v>3</v>
+      </c>
+      <c r="AY10">
+        <v>13</v>
+      </c>
+      <c r="AZ10">
+        <v>9</v>
+      </c>
+      <c r="BA10">
+        <v>5</v>
+      </c>
+      <c r="BB10">
+        <v>3</v>
+      </c>
+      <c r="BC10">
+        <v>8</v>
+      </c>
+      <c r="BD10">
+        <v>1.4</v>
+      </c>
+      <c r="BE10">
+        <v>7</v>
+      </c>
+      <c r="BF10">
+        <v>3.3</v>
+      </c>
+      <c r="BG10">
+        <v>1.35</v>
+      </c>
+      <c r="BH10">
+        <v>2.88</v>
+      </c>
+      <c r="BI10">
+        <v>1.6</v>
+      </c>
+      <c r="BJ10">
+        <v>2.17</v>
+      </c>
+      <c r="BK10">
+        <v>1.96</v>
+      </c>
+      <c r="BL10">
+        <v>1.73</v>
+      </c>
+      <c r="BM10">
+        <v>2.48</v>
+      </c>
+      <c r="BN10">
+        <v>1.47</v>
+      </c>
+      <c r="BO10">
+        <v>3.25</v>
+      </c>
+      <c r="BP10">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:68">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>7781084</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45710.9375</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" t="s">
+        <v>92</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>105</v>
+      </c>
+      <c r="P11" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q11">
+        <v>2.38</v>
+      </c>
+      <c r="R11">
+        <v>2.4</v>
+      </c>
+      <c r="S11">
+        <v>4</v>
+      </c>
+      <c r="T11">
+        <v>1.29</v>
+      </c>
+      <c r="U11">
+        <v>3.5</v>
+      </c>
+      <c r="V11">
+        <v>2.38</v>
+      </c>
+      <c r="W11">
+        <v>1.53</v>
+      </c>
+      <c r="X11">
+        <v>5.5</v>
+      </c>
+      <c r="Y11">
+        <v>1.14</v>
+      </c>
+      <c r="Z11">
+        <v>1.75</v>
+      </c>
+      <c r="AA11">
+        <v>3.76</v>
+      </c>
+      <c r="AB11">
+        <v>4.3</v>
+      </c>
+      <c r="AC11">
+        <v>1.03</v>
+      </c>
+      <c r="AD11">
+        <v>17</v>
+      </c>
+      <c r="AE11">
+        <v>1.18</v>
+      </c>
+      <c r="AF11">
+        <v>5</v>
+      </c>
+      <c r="AG11">
+        <v>1.62</v>
+      </c>
+      <c r="AH11">
+        <v>2.3</v>
+      </c>
+      <c r="AI11">
+        <v>1.53</v>
+      </c>
+      <c r="AJ11">
+        <v>2.38</v>
+      </c>
+      <c r="AK11">
+        <v>1.22</v>
+      </c>
+      <c r="AL11">
+        <v>1.25</v>
+      </c>
+      <c r="AM11">
+        <v>2</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>1</v>
+      </c>
+      <c r="AQ11">
+        <v>1</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>4</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>11</v>
+      </c>
+      <c r="AX11">
+        <v>10</v>
+      </c>
+      <c r="AY11">
+        <v>18</v>
+      </c>
+      <c r="AZ11">
+        <v>14</v>
+      </c>
+      <c r="BA11">
+        <v>8</v>
+      </c>
+      <c r="BB11">
+        <v>4</v>
+      </c>
+      <c r="BC11">
+        <v>12</v>
+      </c>
+      <c r="BD11">
+        <v>1.5</v>
+      </c>
+      <c r="BE11">
+        <v>6.75</v>
+      </c>
+      <c r="BF11">
+        <v>2.9</v>
+      </c>
+      <c r="BG11">
+        <v>1.27</v>
+      </c>
+      <c r="BH11">
+        <v>3.3</v>
+      </c>
+      <c r="BI11">
+        <v>1.46</v>
+      </c>
+      <c r="BJ11">
+        <v>2.48</v>
+      </c>
+      <c r="BK11">
+        <v>1.75</v>
+      </c>
+      <c r="BL11">
+        <v>1.95</v>
+      </c>
+      <c r="BM11">
+        <v>2.17</v>
+      </c>
+      <c r="BN11">
+        <v>1.58</v>
+      </c>
+      <c r="BO11">
+        <v>2.75</v>
+      </c>
+      <c r="BP11">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:68">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>7781085</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="2">
+        <v>45710.9375</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" t="s">
+        <v>93</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>105</v>
+      </c>
+      <c r="P12" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q12">
+        <v>2.4</v>
+      </c>
+      <c r="R12">
+        <v>2.5</v>
+      </c>
+      <c r="S12">
+        <v>3.6</v>
+      </c>
+      <c r="T12">
+        <v>1.25</v>
+      </c>
+      <c r="U12">
+        <v>3.75</v>
+      </c>
+      <c r="V12">
+        <v>2.1</v>
+      </c>
+      <c r="W12">
+        <v>1.67</v>
+      </c>
+      <c r="X12">
+        <v>4.5</v>
+      </c>
+      <c r="Y12">
+        <v>1.18</v>
+      </c>
+      <c r="Z12">
+        <v>1.92</v>
+      </c>
+      <c r="AA12">
+        <v>3.94</v>
+      </c>
+      <c r="AB12">
+        <v>3.37</v>
+      </c>
+      <c r="AC12">
+        <v>1.01</v>
+      </c>
+      <c r="AD12">
+        <v>23</v>
+      </c>
+      <c r="AE12">
+        <v>1.13</v>
+      </c>
+      <c r="AF12">
+        <v>6</v>
+      </c>
+      <c r="AG12">
+        <v>1.43</v>
+      </c>
+      <c r="AH12">
+        <v>2.7</v>
+      </c>
+      <c r="AI12">
+        <v>1.4</v>
+      </c>
+      <c r="AJ12">
+        <v>2.75</v>
+      </c>
+      <c r="AK12">
+        <v>1.32</v>
+      </c>
+      <c r="AL12">
+        <v>1.24</v>
+      </c>
+      <c r="AM12">
+        <v>1.78</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>1</v>
+      </c>
+      <c r="AQ12">
+        <v>1</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>7</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>13</v>
+      </c>
+      <c r="AX12">
+        <v>3</v>
+      </c>
+      <c r="AY12">
+        <v>23</v>
+      </c>
+      <c r="AZ12">
+        <v>4</v>
+      </c>
+      <c r="BA12">
+        <v>6</v>
+      </c>
+      <c r="BB12">
+        <v>1</v>
+      </c>
+      <c r="BC12">
+        <v>7</v>
+      </c>
+      <c r="BD12">
+        <v>1.63</v>
+      </c>
+      <c r="BE12">
+        <v>6.5</v>
+      </c>
+      <c r="BF12">
+        <v>2.55</v>
+      </c>
+      <c r="BG12">
+        <v>1.26</v>
+      </c>
+      <c r="BH12">
+        <v>3.4</v>
+      </c>
+      <c r="BI12">
+        <v>1.47</v>
+      </c>
+      <c r="BJ12">
+        <v>2.48</v>
+      </c>
+      <c r="BK12">
+        <v>1.75</v>
+      </c>
+      <c r="BL12">
+        <v>1.95</v>
+      </c>
+      <c r="BM12">
+        <v>2.17</v>
+      </c>
+      <c r="BN12">
+        <v>1.6</v>
+      </c>
+      <c r="BO12">
+        <v>2.7</v>
+      </c>
+      <c r="BP12">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:68">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7781086</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="2">
+        <v>45711.02083333334</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" t="s">
+        <v>94</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>4</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>4</v>
+      </c>
+      <c r="O13" t="s">
+        <v>106</v>
+      </c>
+      <c r="P13" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q13">
+        <v>2.88</v>
+      </c>
+      <c r="R13">
+        <v>2.38</v>
+      </c>
+      <c r="S13">
+        <v>3.4</v>
+      </c>
+      <c r="T13">
+        <v>1.3</v>
+      </c>
+      <c r="U13">
+        <v>3.4</v>
+      </c>
+      <c r="V13">
+        <v>2.38</v>
+      </c>
+      <c r="W13">
+        <v>1.53</v>
+      </c>
+      <c r="X13">
+        <v>6</v>
+      </c>
+      <c r="Y13">
+        <v>1.13</v>
+      </c>
+      <c r="Z13">
+        <v>2.25</v>
+      </c>
+      <c r="AA13">
+        <v>3.69</v>
+      </c>
+      <c r="AB13">
+        <v>2.82</v>
+      </c>
+      <c r="AC13">
+        <v>1.02</v>
+      </c>
+      <c r="AD13">
+        <v>17</v>
+      </c>
+      <c r="AE13">
+        <v>1.19</v>
+      </c>
+      <c r="AF13">
+        <v>4.75</v>
+      </c>
+      <c r="AG13">
+        <v>1.6</v>
+      </c>
+      <c r="AH13">
+        <v>2.2</v>
+      </c>
+      <c r="AI13">
+        <v>1.5</v>
+      </c>
+      <c r="AJ13">
+        <v>2.5</v>
+      </c>
+      <c r="AK13">
+        <v>1.42</v>
+      </c>
+      <c r="AL13">
+        <v>1.28</v>
+      </c>
+      <c r="AM13">
+        <v>1.57</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>3</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>10</v>
+      </c>
+      <c r="AV13">
+        <v>7</v>
+      </c>
+      <c r="AW13">
+        <v>6</v>
+      </c>
+      <c r="AX13">
+        <v>13</v>
+      </c>
+      <c r="AY13">
+        <v>17</v>
+      </c>
+      <c r="AZ13">
+        <v>23</v>
+      </c>
+      <c r="BA13">
+        <v>6</v>
+      </c>
+      <c r="BB13">
+        <v>5</v>
+      </c>
+      <c r="BC13">
+        <v>11</v>
+      </c>
+      <c r="BD13">
+        <v>1.74</v>
+      </c>
+      <c r="BE13">
+        <v>6.75</v>
+      </c>
+      <c r="BF13">
+        <v>2.3</v>
+      </c>
+      <c r="BG13">
+        <v>1.2</v>
+      </c>
+      <c r="BH13">
+        <v>3.9</v>
+      </c>
+      <c r="BI13">
+        <v>1.37</v>
+      </c>
+      <c r="BJ13">
+        <v>2.8</v>
+      </c>
+      <c r="BK13">
+        <v>1.61</v>
+      </c>
+      <c r="BL13">
+        <v>2.15</v>
+      </c>
+      <c r="BM13">
+        <v>1.96</v>
+      </c>
+      <c r="BN13">
+        <v>1.73</v>
+      </c>
+      <c r="BO13">
+        <v>2.48</v>
+      </c>
+      <c r="BP13">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:68">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>7781087</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45711.02083333334</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" t="s">
+        <v>95</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>2</v>
+      </c>
+      <c r="L14">
+        <v>2</v>
+      </c>
+      <c r="M14">
+        <v>2</v>
+      </c>
+      <c r="N14">
+        <v>4</v>
+      </c>
+      <c r="O14" t="s">
+        <v>107</v>
+      </c>
+      <c r="P14" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q14">
+        <v>2.38</v>
+      </c>
+      <c r="R14">
+        <v>2.2</v>
+      </c>
+      <c r="S14">
+        <v>5</v>
+      </c>
+      <c r="T14">
+        <v>1.4</v>
+      </c>
+      <c r="U14">
+        <v>2.75</v>
+      </c>
+      <c r="V14">
+        <v>2.75</v>
+      </c>
+      <c r="W14">
+        <v>1.4</v>
+      </c>
+      <c r="X14">
+        <v>8</v>
+      </c>
+      <c r="Y14">
+        <v>1.08</v>
+      </c>
+      <c r="Z14">
+        <v>1.74</v>
+      </c>
+      <c r="AA14">
+        <v>3.63</v>
+      </c>
+      <c r="AB14">
+        <v>4.6</v>
+      </c>
+      <c r="AC14">
+        <v>1.05</v>
+      </c>
+      <c r="AD14">
+        <v>12</v>
+      </c>
+      <c r="AE14">
+        <v>1.3</v>
+      </c>
+      <c r="AF14">
+        <v>3.6</v>
+      </c>
+      <c r="AG14">
+        <v>1.87</v>
+      </c>
+      <c r="AH14">
+        <v>1.87</v>
+      </c>
+      <c r="AI14">
+        <v>1.8</v>
+      </c>
+      <c r="AJ14">
+        <v>1.95</v>
+      </c>
+      <c r="AK14">
+        <v>1.2</v>
+      </c>
+      <c r="AL14">
+        <v>1.26</v>
+      </c>
+      <c r="AM14">
+        <v>2.05</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>1</v>
+      </c>
+      <c r="AQ14">
+        <v>1</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>9</v>
+      </c>
+      <c r="AV14">
+        <v>3</v>
+      </c>
+      <c r="AW14">
+        <v>11</v>
+      </c>
+      <c r="AX14">
+        <v>7</v>
+      </c>
+      <c r="AY14">
+        <v>28</v>
+      </c>
+      <c r="AZ14">
+        <v>12</v>
+      </c>
+      <c r="BA14">
+        <v>7</v>
+      </c>
+      <c r="BB14">
+        <v>4</v>
+      </c>
+      <c r="BC14">
+        <v>11</v>
+      </c>
+      <c r="BD14">
+        <v>1.43</v>
+      </c>
+      <c r="BE14">
+        <v>7</v>
+      </c>
+      <c r="BF14">
+        <v>3.15</v>
+      </c>
+      <c r="BG14">
+        <v>1.24</v>
+      </c>
+      <c r="BH14">
+        <v>3.55</v>
+      </c>
+      <c r="BI14">
+        <v>1.43</v>
+      </c>
+      <c r="BJ14">
+        <v>2.6</v>
+      </c>
+      <c r="BK14">
+        <v>1.68</v>
+      </c>
+      <c r="BL14">
+        <v>2.02</v>
+      </c>
+      <c r="BM14">
+        <v>2.07</v>
+      </c>
+      <c r="BN14">
+        <v>1.66</v>
+      </c>
+      <c r="BO14">
+        <v>2.63</v>
+      </c>
+      <c r="BP14">
+        <v>1.41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="122">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -265,6 +265,12 @@
     <t>Seattle Sounders</t>
   </si>
   <si>
+    <t>Portland Timbers</t>
+  </si>
+  <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
     <t>Minnesota United</t>
   </si>
   <si>
@@ -304,6 +310,12 @@
     <t>Charlotte</t>
   </si>
   <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
+    <t>San Diego</t>
+  </si>
+  <si>
     <t>['78']</t>
   </si>
   <si>
@@ -340,6 +352,9 @@
     <t>['19', '49']</t>
   </si>
   <si>
+    <t>['73']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -359,6 +374,12 @@
   </si>
   <si>
     <t>['35', '90+2']</t>
+  </si>
+  <si>
+    <t>['24', '32', '53', '61']</t>
+  </si>
+  <si>
+    <t>['52', '90+3']</t>
   </si>
 </sst>
 </file>
@@ -720,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP14"/>
+  <dimension ref="A1:BP16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -952,7 +973,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -973,10 +994,10 @@
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="P2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="Q2">
         <v>2.3</v>
@@ -1158,7 +1179,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1179,10 +1200,10 @@
         <v>4</v>
       </c>
       <c r="O3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -1364,7 +1385,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1385,10 +1406,10 @@
         <v>5</v>
       </c>
       <c r="O4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1570,7 +1591,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1591,10 +1612,10 @@
         <v>1</v>
       </c>
       <c r="O5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="P5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1776,7 +1797,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I6">
         <v>3</v>
@@ -1797,10 +1818,10 @@
         <v>6</v>
       </c>
       <c r="O6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -1982,7 +2003,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I7">
         <v>2</v>
@@ -2003,10 +2024,10 @@
         <v>4</v>
       </c>
       <c r="O7" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2188,7 +2209,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -2209,10 +2230,10 @@
         <v>6</v>
       </c>
       <c r="O8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2394,7 +2415,7 @@
         <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2415,10 +2436,10 @@
         <v>1</v>
       </c>
       <c r="O9" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="P9" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="Q9">
         <v>2.3</v>
@@ -2600,7 +2621,7 @@
         <v>78</v>
       </c>
       <c r="H10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -2621,10 +2642,10 @@
         <v>3</v>
       </c>
       <c r="O10" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -2806,7 +2827,7 @@
         <v>79</v>
       </c>
       <c r="H11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2827,10 +2848,10 @@
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="P11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3012,7 +3033,7 @@
         <v>80</v>
       </c>
       <c r="H12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -3033,10 +3054,10 @@
         <v>0</v>
       </c>
       <c r="O12" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="P12" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="Q12">
         <v>2.4</v>
@@ -3218,7 +3239,7 @@
         <v>81</v>
       </c>
       <c r="H13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -3239,10 +3260,10 @@
         <v>4</v>
       </c>
       <c r="O13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="P13" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="Q13">
         <v>2.88</v>
@@ -3424,7 +3445,7 @@
         <v>82</v>
       </c>
       <c r="H14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I14">
         <v>1</v>
@@ -3445,10 +3466,10 @@
         <v>4</v>
       </c>
       <c r="O14" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -3605,6 +3626,418 @@
       </c>
       <c r="BP14">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:68">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>7781088</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2">
+        <v>45711.75</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" t="s">
+        <v>98</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>4</v>
+      </c>
+      <c r="N15">
+        <v>5</v>
+      </c>
+      <c r="O15" t="s">
+        <v>112</v>
+      </c>
+      <c r="P15" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q15">
+        <v>2.4</v>
+      </c>
+      <c r="R15">
+        <v>2.5</v>
+      </c>
+      <c r="S15">
+        <v>3.75</v>
+      </c>
+      <c r="T15">
+        <v>1.25</v>
+      </c>
+      <c r="U15">
+        <v>3.75</v>
+      </c>
+      <c r="V15">
+        <v>2.2</v>
+      </c>
+      <c r="W15">
+        <v>1.62</v>
+      </c>
+      <c r="X15">
+        <v>5</v>
+      </c>
+      <c r="Y15">
+        <v>1.17</v>
+      </c>
+      <c r="Z15">
+        <v>1.9</v>
+      </c>
+      <c r="AA15">
+        <v>3.81</v>
+      </c>
+      <c r="AB15">
+        <v>3.56</v>
+      </c>
+      <c r="AC15">
+        <v>1.02</v>
+      </c>
+      <c r="AD15">
+        <v>21</v>
+      </c>
+      <c r="AE15">
+        <v>1.15</v>
+      </c>
+      <c r="AF15">
+        <v>5.5</v>
+      </c>
+      <c r="AG15">
+        <v>1.5</v>
+      </c>
+      <c r="AH15">
+        <v>2.48</v>
+      </c>
+      <c r="AI15">
+        <v>1.44</v>
+      </c>
+      <c r="AJ15">
+        <v>2.63</v>
+      </c>
+      <c r="AK15">
+        <v>1.29</v>
+      </c>
+      <c r="AL15">
+        <v>1.25</v>
+      </c>
+      <c r="AM15">
+        <v>1.83</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>3</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>3</v>
+      </c>
+      <c r="AV15">
+        <v>11</v>
+      </c>
+      <c r="AW15">
+        <v>3</v>
+      </c>
+      <c r="AX15">
+        <v>11</v>
+      </c>
+      <c r="AY15">
+        <v>8</v>
+      </c>
+      <c r="AZ15">
+        <v>26</v>
+      </c>
+      <c r="BA15">
+        <v>3</v>
+      </c>
+      <c r="BB15">
+        <v>10</v>
+      </c>
+      <c r="BC15">
+        <v>13</v>
+      </c>
+      <c r="BD15">
+        <v>1.71</v>
+      </c>
+      <c r="BE15">
+        <v>6.4</v>
+      </c>
+      <c r="BF15">
+        <v>2.4</v>
+      </c>
+      <c r="BG15">
+        <v>1.3</v>
+      </c>
+      <c r="BH15">
+        <v>3.1</v>
+      </c>
+      <c r="BI15">
+        <v>1.53</v>
+      </c>
+      <c r="BJ15">
+        <v>2.32</v>
+      </c>
+      <c r="BK15">
+        <v>1.86</v>
+      </c>
+      <c r="BL15">
+        <v>1.82</v>
+      </c>
+      <c r="BM15">
+        <v>2.33</v>
+      </c>
+      <c r="BN15">
+        <v>1.52</v>
+      </c>
+      <c r="BO15">
+        <v>2.95</v>
+      </c>
+      <c r="BP15">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:68">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>7781089</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45711.875</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
+        <v>84</v>
+      </c>
+      <c r="H16" t="s">
+        <v>99</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>2</v>
+      </c>
+      <c r="N16">
+        <v>2</v>
+      </c>
+      <c r="O16" t="s">
+        <v>109</v>
+      </c>
+      <c r="P16" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>1.43</v>
+      </c>
+      <c r="AA16">
+        <v>5</v>
+      </c>
+      <c r="AB16">
+        <v>5.8</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>1.41</v>
+      </c>
+      <c r="AH16">
+        <v>2.78</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>3</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>-1</v>
+      </c>
+      <c r="AV16">
+        <v>-1</v>
+      </c>
+      <c r="AW16">
+        <v>-1</v>
+      </c>
+      <c r="AX16">
+        <v>-1</v>
+      </c>
+      <c r="AY16">
+        <v>-1</v>
+      </c>
+      <c r="AZ16">
+        <v>-1</v>
+      </c>
+      <c r="BA16">
+        <v>-1</v>
+      </c>
+      <c r="BB16">
+        <v>-1</v>
+      </c>
+      <c r="BC16">
+        <v>-1</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -3974,31 +3974,31 @@
         <v>0</v>
       </c>
       <c r="AU16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AV16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AW16">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AX16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AY16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AZ16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BA16">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BB16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BD16">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="123">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -271,6 +271,12 @@
     <t>LA Galaxy</t>
   </si>
   <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>Real Salt Lake</t>
+  </si>
+  <si>
     <t>Minnesota United</t>
   </si>
   <si>
@@ -304,12 +310,6 @@
     <t>Colorado Rapids</t>
   </si>
   <si>
-    <t>Real Salt Lake</t>
-  </si>
-  <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
     <t>Vancouver Whitecaps</t>
   </si>
   <si>
@@ -353,6 +353,9 @@
   </si>
   <si>
     <t>['73']</t>
+  </si>
+  <si>
+    <t>['49', '54']</t>
   </si>
   <si>
     <t>['26', '55']</t>
@@ -741,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP16"/>
+  <dimension ref="A1:BP18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -973,7 +976,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1179,7 +1182,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1203,7 +1206,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -1385,7 +1388,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1409,7 +1412,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1591,7 +1594,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1797,7 +1800,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I6">
         <v>3</v>
@@ -1821,7 +1824,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2003,7 +2006,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I7">
         <v>2</v>
@@ -2027,7 +2030,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2209,7 +2212,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -2233,7 +2236,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2415,7 +2418,7 @@
         <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2621,7 +2624,7 @@
         <v>78</v>
       </c>
       <c r="H10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -2645,7 +2648,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -2827,7 +2830,7 @@
         <v>79</v>
       </c>
       <c r="H11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -3033,7 +3036,7 @@
         <v>80</v>
       </c>
       <c r="H12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -3239,7 +3242,7 @@
         <v>81</v>
       </c>
       <c r="H13" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -3445,7 +3448,7 @@
         <v>82</v>
       </c>
       <c r="H14" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I14">
         <v>1</v>
@@ -3469,7 +3472,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -3675,7 +3678,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -3881,7 +3884,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4038,6 +4041,418 @@
       </c>
       <c r="BP16">
         <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:68">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>7781090</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45717.67708333334</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" t="s">
+        <v>72</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>2</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>2</v>
+      </c>
+      <c r="O17" t="s">
+        <v>113</v>
+      </c>
+      <c r="P17" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q17">
+        <v>2.75</v>
+      </c>
+      <c r="R17">
+        <v>2.25</v>
+      </c>
+      <c r="S17">
+        <v>3.6</v>
+      </c>
+      <c r="T17">
+        <v>1.33</v>
+      </c>
+      <c r="U17">
+        <v>3.25</v>
+      </c>
+      <c r="V17">
+        <v>2.63</v>
+      </c>
+      <c r="W17">
+        <v>1.44</v>
+      </c>
+      <c r="X17">
+        <v>7</v>
+      </c>
+      <c r="Y17">
+        <v>1.1</v>
+      </c>
+      <c r="Z17">
+        <v>2.11</v>
+      </c>
+      <c r="AA17">
+        <v>3.25</v>
+      </c>
+      <c r="AB17">
+        <v>3.47</v>
+      </c>
+      <c r="AC17">
+        <v>1.05</v>
+      </c>
+      <c r="AD17">
+        <v>9.5</v>
+      </c>
+      <c r="AE17">
+        <v>1.25</v>
+      </c>
+      <c r="AF17">
+        <v>3.8</v>
+      </c>
+      <c r="AG17">
+        <v>1.75</v>
+      </c>
+      <c r="AH17">
+        <v>2</v>
+      </c>
+      <c r="AI17">
+        <v>1.57</v>
+      </c>
+      <c r="AJ17">
+        <v>2.25</v>
+      </c>
+      <c r="AK17">
+        <v>1.34</v>
+      </c>
+      <c r="AL17">
+        <v>1.28</v>
+      </c>
+      <c r="AM17">
+        <v>1.68</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>3</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>6</v>
+      </c>
+      <c r="AV17">
+        <v>4</v>
+      </c>
+      <c r="AW17">
+        <v>4</v>
+      </c>
+      <c r="AX17">
+        <v>13</v>
+      </c>
+      <c r="AY17">
+        <v>10</v>
+      </c>
+      <c r="AZ17">
+        <v>21</v>
+      </c>
+      <c r="BA17">
+        <v>1</v>
+      </c>
+      <c r="BB17">
+        <v>5</v>
+      </c>
+      <c r="BC17">
+        <v>6</v>
+      </c>
+      <c r="BD17">
+        <v>1.66</v>
+      </c>
+      <c r="BE17">
+        <v>6.75</v>
+      </c>
+      <c r="BF17">
+        <v>2.48</v>
+      </c>
+      <c r="BG17">
+        <v>1.28</v>
+      </c>
+      <c r="BH17">
+        <v>3.3</v>
+      </c>
+      <c r="BI17">
+        <v>1.48</v>
+      </c>
+      <c r="BJ17">
+        <v>2.43</v>
+      </c>
+      <c r="BK17">
+        <v>1.79</v>
+      </c>
+      <c r="BL17">
+        <v>1.9</v>
+      </c>
+      <c r="BM17">
+        <v>2.23</v>
+      </c>
+      <c r="BN17">
+        <v>1.56</v>
+      </c>
+      <c r="BO17">
+        <v>2.9</v>
+      </c>
+      <c r="BP17">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:68">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>7781091</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="2">
+        <v>45717.77083333334</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" t="s">
+        <v>82</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>2</v>
+      </c>
+      <c r="O18" t="s">
+        <v>106</v>
+      </c>
+      <c r="P18" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q18">
+        <v>3.1</v>
+      </c>
+      <c r="R18">
+        <v>2.2</v>
+      </c>
+      <c r="S18">
+        <v>3.5</v>
+      </c>
+      <c r="T18">
+        <v>1.4</v>
+      </c>
+      <c r="U18">
+        <v>2.75</v>
+      </c>
+      <c r="V18">
+        <v>2.75</v>
+      </c>
+      <c r="W18">
+        <v>1.4</v>
+      </c>
+      <c r="X18">
+        <v>8</v>
+      </c>
+      <c r="Y18">
+        <v>1.08</v>
+      </c>
+      <c r="Z18">
+        <v>2.38</v>
+      </c>
+      <c r="AA18">
+        <v>3.3</v>
+      </c>
+      <c r="AB18">
+        <v>2.88</v>
+      </c>
+      <c r="AC18">
+        <v>1.05</v>
+      </c>
+      <c r="AD18">
+        <v>11</v>
+      </c>
+      <c r="AE18">
+        <v>1.3</v>
+      </c>
+      <c r="AF18">
+        <v>3.6</v>
+      </c>
+      <c r="AG18">
+        <v>1.83</v>
+      </c>
+      <c r="AH18">
+        <v>1.91</v>
+      </c>
+      <c r="AI18">
+        <v>1.67</v>
+      </c>
+      <c r="AJ18">
+        <v>2.1</v>
+      </c>
+      <c r="AK18">
+        <v>1.4</v>
+      </c>
+      <c r="AL18">
+        <v>1.31</v>
+      </c>
+      <c r="AM18">
+        <v>1.53</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>3</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>5</v>
+      </c>
+      <c r="AV18">
+        <v>4</v>
+      </c>
+      <c r="AW18">
+        <v>7</v>
+      </c>
+      <c r="AX18">
+        <v>8</v>
+      </c>
+      <c r="AY18">
+        <v>13</v>
+      </c>
+      <c r="AZ18">
+        <v>12</v>
+      </c>
+      <c r="BA18">
+        <v>3</v>
+      </c>
+      <c r="BB18">
+        <v>4</v>
+      </c>
+      <c r="BC18">
+        <v>7</v>
+      </c>
+      <c r="BD18">
+        <v>1.85</v>
+      </c>
+      <c r="BE18">
+        <v>6.5</v>
+      </c>
+      <c r="BF18">
+        <v>2.15</v>
+      </c>
+      <c r="BG18">
+        <v>1.26</v>
+      </c>
+      <c r="BH18">
+        <v>3.4</v>
+      </c>
+      <c r="BI18">
+        <v>1.44</v>
+      </c>
+      <c r="BJ18">
+        <v>2.55</v>
+      </c>
+      <c r="BK18">
+        <v>1.72</v>
+      </c>
+      <c r="BL18">
+        <v>1.98</v>
+      </c>
+      <c r="BM18">
+        <v>2.14</v>
+      </c>
+      <c r="BN18">
+        <v>1.61</v>
+      </c>
+      <c r="BO18">
+        <v>2.65</v>
+      </c>
+      <c r="BP18">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="138">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -277,45 +277,45 @@
     <t>Real Salt Lake</t>
   </si>
   <si>
+    <t>New England Revolution</t>
+  </si>
+  <si>
+    <t>New York RB</t>
+  </si>
+  <si>
+    <t>Philadelphia Union</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>Sporting KC</t>
+  </si>
+  <si>
     <t>Minnesota United</t>
   </si>
   <si>
+    <t>Colorado Rapids</t>
+  </si>
+  <si>
+    <t>San Diego</t>
+  </si>
+  <si>
     <t>New York City</t>
   </si>
   <si>
     <t>Montreal Impact</t>
   </si>
   <si>
-    <t>New York RB</t>
-  </si>
-  <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
     <t>Toronto</t>
   </si>
   <si>
-    <t>Philadelphia Union</t>
-  </si>
-  <si>
-    <t>Sporting KC</t>
-  </si>
-  <si>
     <t>FC Dallas</t>
   </si>
   <si>
-    <t>New England Revolution</t>
-  </si>
-  <si>
-    <t>Colorado Rapids</t>
-  </si>
-  <si>
     <t>Vancouver Whitecaps</t>
   </si>
   <si>
-    <t>San Diego</t>
-  </si>
-  <si>
     <t>['78']</t>
   </si>
   <si>
@@ -358,6 +358,33 @@
     <t>['49', '54']</t>
   </si>
   <si>
+    <t>['7', '30']</t>
+  </si>
+  <si>
+    <t>['32', '35', '63', '81']</t>
+  </si>
+  <si>
+    <t>['6', '30', '52', '90+3']</t>
+  </si>
+  <si>
+    <t>['30', '70']</t>
+  </si>
+  <si>
+    <t>['27']</t>
+  </si>
+  <si>
+    <t>['69']</t>
+  </si>
+  <si>
+    <t>['6', '39', '72']</t>
+  </si>
+  <si>
+    <t>['86']</t>
+  </si>
+  <si>
+    <t>['89']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -383,6 +410,24 @@
   </si>
   <si>
     <t>['52', '90+3']</t>
+  </si>
+  <si>
+    <t>['51']</t>
+  </si>
+  <si>
+    <t>['72', '86']</t>
+  </si>
+  <si>
+    <t>['58']</t>
+  </si>
+  <si>
+    <t>['4', '90+6']</t>
+  </si>
+  <si>
+    <t>['3', '19']</t>
+  </si>
+  <si>
+    <t>['43', '45', '68']</t>
   </si>
 </sst>
 </file>
@@ -744,7 +789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP18"/>
+  <dimension ref="A1:BP29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -976,7 +1021,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1182,7 +1227,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1206,7 +1251,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -1287,7 +1332,7 @@
         <v>1</v>
       </c>
       <c r="AQ3">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1388,7 +1433,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1412,7 +1457,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1594,7 +1639,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1800,7 +1845,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I6">
         <v>3</v>
@@ -1824,7 +1869,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2006,7 +2051,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="I7">
         <v>2</v>
@@ -2030,7 +2075,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2111,7 +2156,7 @@
         <v>1</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2212,7 +2257,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -2236,7 +2281,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2314,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ8">
         <v>3</v>
@@ -2418,7 +2463,7 @@
         <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2624,7 +2669,7 @@
         <v>78</v>
       </c>
       <c r="H10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -2648,7 +2693,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -2729,7 +2774,7 @@
         <v>0</v>
       </c>
       <c r="AQ10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -2830,7 +2875,7 @@
         <v>79</v>
       </c>
       <c r="H11" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -3036,7 +3081,7 @@
         <v>80</v>
       </c>
       <c r="H12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -3472,7 +3517,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -3654,7 +3699,7 @@
         <v>83</v>
       </c>
       <c r="H15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -3678,7 +3723,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -3756,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ15">
         <v>3</v>
@@ -3860,7 +3905,7 @@
         <v>84</v>
       </c>
       <c r="H16" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -3884,7 +3929,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4453,6 +4498,2272 @@
       </c>
       <c r="BP18">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:68">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>7781092</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="2">
+        <v>45717.89583333334</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" t="s">
+        <v>74</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19" t="s">
+        <v>109</v>
+      </c>
+      <c r="P19" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q19">
+        <v>3.4</v>
+      </c>
+      <c r="R19">
+        <v>2.38</v>
+      </c>
+      <c r="S19">
+        <v>2.75</v>
+      </c>
+      <c r="T19">
+        <v>1.29</v>
+      </c>
+      <c r="U19">
+        <v>3.5</v>
+      </c>
+      <c r="V19">
+        <v>2.38</v>
+      </c>
+      <c r="W19">
+        <v>1.53</v>
+      </c>
+      <c r="X19">
+        <v>5.5</v>
+      </c>
+      <c r="Y19">
+        <v>1.14</v>
+      </c>
+      <c r="Z19">
+        <v>2.83</v>
+      </c>
+      <c r="AA19">
+        <v>3.71</v>
+      </c>
+      <c r="AB19">
+        <v>2.24</v>
+      </c>
+      <c r="AC19">
+        <v>1.02</v>
+      </c>
+      <c r="AD19">
+        <v>19</v>
+      </c>
+      <c r="AE19">
+        <v>1.18</v>
+      </c>
+      <c r="AF19">
+        <v>5</v>
+      </c>
+      <c r="AG19">
+        <v>1.59</v>
+      </c>
+      <c r="AH19">
+        <v>2.27</v>
+      </c>
+      <c r="AI19">
+        <v>1.5</v>
+      </c>
+      <c r="AJ19">
+        <v>2.5</v>
+      </c>
+      <c r="AK19">
+        <v>1.7</v>
+      </c>
+      <c r="AL19">
+        <v>1.22</v>
+      </c>
+      <c r="AM19">
+        <v>1.4</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>3</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>3</v>
+      </c>
+      <c r="AV19">
+        <v>5</v>
+      </c>
+      <c r="AW19">
+        <v>4</v>
+      </c>
+      <c r="AX19">
+        <v>2</v>
+      </c>
+      <c r="AY19">
+        <v>8</v>
+      </c>
+      <c r="AZ19">
+        <v>7</v>
+      </c>
+      <c r="BA19">
+        <v>1</v>
+      </c>
+      <c r="BB19">
+        <v>4</v>
+      </c>
+      <c r="BC19">
+        <v>5</v>
+      </c>
+      <c r="BD19">
+        <v>2.15</v>
+      </c>
+      <c r="BE19">
+        <v>6.1</v>
+      </c>
+      <c r="BF19">
+        <v>1.88</v>
+      </c>
+      <c r="BG19">
+        <v>1.43</v>
+      </c>
+      <c r="BH19">
+        <v>2.55</v>
+      </c>
+      <c r="BI19">
+        <v>1.72</v>
+      </c>
+      <c r="BJ19">
+        <v>1.98</v>
+      </c>
+      <c r="BK19">
+        <v>2.15</v>
+      </c>
+      <c r="BL19">
+        <v>1.61</v>
+      </c>
+      <c r="BM19">
+        <v>2.8</v>
+      </c>
+      <c r="BN19">
+        <v>1.37</v>
+      </c>
+      <c r="BO19">
+        <v>3.7</v>
+      </c>
+      <c r="BP19">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:68">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>7781093</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="2">
+        <v>45717.89583333334</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20" t="s">
+        <v>88</v>
+      </c>
+      <c r="H20" t="s">
+        <v>79</v>
+      </c>
+      <c r="I20">
+        <v>2</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>2</v>
+      </c>
+      <c r="L20">
+        <v>2</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>2</v>
+      </c>
+      <c r="O20" t="s">
+        <v>114</v>
+      </c>
+      <c r="P20" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q20">
+        <v>2.25</v>
+      </c>
+      <c r="R20">
+        <v>2.25</v>
+      </c>
+      <c r="S20">
+        <v>5.5</v>
+      </c>
+      <c r="T20">
+        <v>1.36</v>
+      </c>
+      <c r="U20">
+        <v>3</v>
+      </c>
+      <c r="V20">
+        <v>2.75</v>
+      </c>
+      <c r="W20">
+        <v>1.4</v>
+      </c>
+      <c r="X20">
+        <v>7</v>
+      </c>
+      <c r="Y20">
+        <v>1.1</v>
+      </c>
+      <c r="Z20">
+        <v>1.63</v>
+      </c>
+      <c r="AA20">
+        <v>4</v>
+      </c>
+      <c r="AB20">
+        <v>4.8</v>
+      </c>
+      <c r="AC20">
+        <v>1.04</v>
+      </c>
+      <c r="AD20">
+        <v>13</v>
+      </c>
+      <c r="AE20">
+        <v>1.28</v>
+      </c>
+      <c r="AF20">
+        <v>3.75</v>
+      </c>
+      <c r="AG20">
+        <v>1.83</v>
+      </c>
+      <c r="AH20">
+        <v>1.85</v>
+      </c>
+      <c r="AI20">
+        <v>1.91</v>
+      </c>
+      <c r="AJ20">
+        <v>1.91</v>
+      </c>
+      <c r="AK20">
+        <v>1.17</v>
+      </c>
+      <c r="AL20">
+        <v>1.24</v>
+      </c>
+      <c r="AM20">
+        <v>2.2</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>3</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>6</v>
+      </c>
+      <c r="AV20">
+        <v>2</v>
+      </c>
+      <c r="AW20">
+        <v>8</v>
+      </c>
+      <c r="AX20">
+        <v>10</v>
+      </c>
+      <c r="AY20">
+        <v>15</v>
+      </c>
+      <c r="AZ20">
+        <v>17</v>
+      </c>
+      <c r="BA20">
+        <v>1</v>
+      </c>
+      <c r="BB20">
+        <v>5</v>
+      </c>
+      <c r="BC20">
+        <v>6</v>
+      </c>
+      <c r="BD20">
+        <v>1.55</v>
+      </c>
+      <c r="BE20">
+        <v>7</v>
+      </c>
+      <c r="BF20">
+        <v>2.65</v>
+      </c>
+      <c r="BG20">
+        <v>1.3</v>
+      </c>
+      <c r="BH20">
+        <v>3.05</v>
+      </c>
+      <c r="BI20">
+        <v>1.53</v>
+      </c>
+      <c r="BJ20">
+        <v>2.32</v>
+      </c>
+      <c r="BK20">
+        <v>1.86</v>
+      </c>
+      <c r="BL20">
+        <v>1.82</v>
+      </c>
+      <c r="BM20">
+        <v>2.33</v>
+      </c>
+      <c r="BN20">
+        <v>1.52</v>
+      </c>
+      <c r="BO20">
+        <v>2.95</v>
+      </c>
+      <c r="BP20">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:68">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>7781094</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="2">
+        <v>45717.89583333334</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" t="s">
+        <v>97</v>
+      </c>
+      <c r="I21">
+        <v>2</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>2</v>
+      </c>
+      <c r="L21">
+        <v>4</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21">
+        <v>6</v>
+      </c>
+      <c r="O21" t="s">
+        <v>115</v>
+      </c>
+      <c r="P21" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q21">
+        <v>2.1</v>
+      </c>
+      <c r="R21">
+        <v>2.38</v>
+      </c>
+      <c r="S21">
+        <v>5.5</v>
+      </c>
+      <c r="T21">
+        <v>1.33</v>
+      </c>
+      <c r="U21">
+        <v>3.25</v>
+      </c>
+      <c r="V21">
+        <v>2.63</v>
+      </c>
+      <c r="W21">
+        <v>1.44</v>
+      </c>
+      <c r="X21">
+        <v>6.5</v>
+      </c>
+      <c r="Y21">
+        <v>1.11</v>
+      </c>
+      <c r="Z21">
+        <v>1.56</v>
+      </c>
+      <c r="AA21">
+        <v>3.83</v>
+      </c>
+      <c r="AB21">
+        <v>5.9</v>
+      </c>
+      <c r="AC21">
+        <v>1.04</v>
+      </c>
+      <c r="AD21">
+        <v>13</v>
+      </c>
+      <c r="AE21">
+        <v>1.24</v>
+      </c>
+      <c r="AF21">
+        <v>4.2</v>
+      </c>
+      <c r="AG21">
+        <v>1.67</v>
+      </c>
+      <c r="AH21">
+        <v>2.1</v>
+      </c>
+      <c r="AI21">
+        <v>1.75</v>
+      </c>
+      <c r="AJ21">
+        <v>2</v>
+      </c>
+      <c r="AK21">
+        <v>1.15</v>
+      </c>
+      <c r="AL21">
+        <v>1.23</v>
+      </c>
+      <c r="AM21">
+        <v>2.3</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>1</v>
+      </c>
+      <c r="AP21">
+        <v>1.5</v>
+      </c>
+      <c r="AQ21">
+        <v>0.5</v>
+      </c>
+      <c r="AR21">
+        <v>2.07</v>
+      </c>
+      <c r="AS21">
+        <v>1.74</v>
+      </c>
+      <c r="AT21">
+        <v>3.81</v>
+      </c>
+      <c r="AU21">
+        <v>6</v>
+      </c>
+      <c r="AV21">
+        <v>4</v>
+      </c>
+      <c r="AW21">
+        <v>3</v>
+      </c>
+      <c r="AX21">
+        <v>5</v>
+      </c>
+      <c r="AY21">
+        <v>10</v>
+      </c>
+      <c r="AZ21">
+        <v>10</v>
+      </c>
+      <c r="BA21">
+        <v>2</v>
+      </c>
+      <c r="BB21">
+        <v>2</v>
+      </c>
+      <c r="BC21">
+        <v>4</v>
+      </c>
+      <c r="BD21">
+        <v>1.38</v>
+      </c>
+      <c r="BE21">
+        <v>7</v>
+      </c>
+      <c r="BF21">
+        <v>3.4</v>
+      </c>
+      <c r="BG21">
+        <v>1.38</v>
+      </c>
+      <c r="BH21">
+        <v>2.7</v>
+      </c>
+      <c r="BI21">
+        <v>1.65</v>
+      </c>
+      <c r="BJ21">
+        <v>2.08</v>
+      </c>
+      <c r="BK21">
+        <v>2.04</v>
+      </c>
+      <c r="BL21">
+        <v>1.67</v>
+      </c>
+      <c r="BM21">
+        <v>2.65</v>
+      </c>
+      <c r="BN21">
+        <v>1.41</v>
+      </c>
+      <c r="BO21">
+        <v>3.4</v>
+      </c>
+      <c r="BP21">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:68">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>7781095</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="2">
+        <v>45717.89583333334</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22" t="s">
+        <v>89</v>
+      </c>
+      <c r="H22" t="s">
+        <v>73</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>2</v>
+      </c>
+      <c r="L22">
+        <v>4</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>5</v>
+      </c>
+      <c r="O22" t="s">
+        <v>116</v>
+      </c>
+      <c r="P22" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q22">
+        <v>2.88</v>
+      </c>
+      <c r="R22">
+        <v>2.38</v>
+      </c>
+      <c r="S22">
+        <v>3.25</v>
+      </c>
+      <c r="T22">
+        <v>1.3</v>
+      </c>
+      <c r="U22">
+        <v>3.4</v>
+      </c>
+      <c r="V22">
+        <v>2.38</v>
+      </c>
+      <c r="W22">
+        <v>1.53</v>
+      </c>
+      <c r="X22">
+        <v>6</v>
+      </c>
+      <c r="Y22">
+        <v>1.13</v>
+      </c>
+      <c r="Z22">
+        <v>2.25</v>
+      </c>
+      <c r="AA22">
+        <v>3.61</v>
+      </c>
+      <c r="AB22">
+        <v>2.86</v>
+      </c>
+      <c r="AC22">
+        <v>1.02</v>
+      </c>
+      <c r="AD22">
+        <v>17</v>
+      </c>
+      <c r="AE22">
+        <v>1.18</v>
+      </c>
+      <c r="AF22">
+        <v>5</v>
+      </c>
+      <c r="AG22">
+        <v>1.61</v>
+      </c>
+      <c r="AH22">
+        <v>2.15</v>
+      </c>
+      <c r="AI22">
+        <v>1.5</v>
+      </c>
+      <c r="AJ22">
+        <v>2.5</v>
+      </c>
+      <c r="AK22">
+        <v>1.41</v>
+      </c>
+      <c r="AL22">
+        <v>1.27</v>
+      </c>
+      <c r="AM22">
+        <v>1.6</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>3</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>8</v>
+      </c>
+      <c r="AV22">
+        <v>3</v>
+      </c>
+      <c r="AW22">
+        <v>5</v>
+      </c>
+      <c r="AX22">
+        <v>3</v>
+      </c>
+      <c r="AY22">
+        <v>16</v>
+      </c>
+      <c r="AZ22">
+        <v>8</v>
+      </c>
+      <c r="BA22">
+        <v>7</v>
+      </c>
+      <c r="BB22">
+        <v>2</v>
+      </c>
+      <c r="BC22">
+        <v>9</v>
+      </c>
+      <c r="BD22">
+        <v>1.65</v>
+      </c>
+      <c r="BE22">
+        <v>6.75</v>
+      </c>
+      <c r="BF22">
+        <v>2.48</v>
+      </c>
+      <c r="BG22">
+        <v>1.22</v>
+      </c>
+      <c r="BH22">
+        <v>3.7</v>
+      </c>
+      <c r="BI22">
+        <v>1.4</v>
+      </c>
+      <c r="BJ22">
+        <v>2.65</v>
+      </c>
+      <c r="BK22">
+        <v>1.65</v>
+      </c>
+      <c r="BL22">
+        <v>2.08</v>
+      </c>
+      <c r="BM22">
+        <v>2</v>
+      </c>
+      <c r="BN22">
+        <v>1.71</v>
+      </c>
+      <c r="BO22">
+        <v>2.5</v>
+      </c>
+      <c r="BP22">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:68">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>7781096</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="2">
+        <v>45717.9375</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23" t="s">
+        <v>90</v>
+      </c>
+      <c r="H23" t="s">
+        <v>75</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>2</v>
+      </c>
+      <c r="L23">
+        <v>2</v>
+      </c>
+      <c r="M23">
+        <v>2</v>
+      </c>
+      <c r="N23">
+        <v>4</v>
+      </c>
+      <c r="O23" t="s">
+        <v>117</v>
+      </c>
+      <c r="P23" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q23">
+        <v>2.75</v>
+      </c>
+      <c r="R23">
+        <v>2.3</v>
+      </c>
+      <c r="S23">
+        <v>3.5</v>
+      </c>
+      <c r="T23">
+        <v>1.3</v>
+      </c>
+      <c r="U23">
+        <v>3.4</v>
+      </c>
+      <c r="V23">
+        <v>2.5</v>
+      </c>
+      <c r="W23">
+        <v>1.5</v>
+      </c>
+      <c r="X23">
+        <v>6</v>
+      </c>
+      <c r="Y23">
+        <v>1.13</v>
+      </c>
+      <c r="Z23">
+        <v>2.17</v>
+      </c>
+      <c r="AA23">
+        <v>3.5</v>
+      </c>
+      <c r="AB23">
+        <v>3.09</v>
+      </c>
+      <c r="AC23">
+        <v>1.03</v>
+      </c>
+      <c r="AD23">
+        <v>17</v>
+      </c>
+      <c r="AE23">
+        <v>1.19</v>
+      </c>
+      <c r="AF23">
+        <v>4.75</v>
+      </c>
+      <c r="AG23">
+        <v>1.6</v>
+      </c>
+      <c r="AH23">
+        <v>2.2</v>
+      </c>
+      <c r="AI23">
+        <v>1.53</v>
+      </c>
+      <c r="AJ23">
+        <v>2.38</v>
+      </c>
+      <c r="AK23">
+        <v>1.37</v>
+      </c>
+      <c r="AL23">
+        <v>1.27</v>
+      </c>
+      <c r="AM23">
+        <v>1.65</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>1</v>
+      </c>
+      <c r="AQ23">
+        <v>1</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>4</v>
+      </c>
+      <c r="AV23">
+        <v>5</v>
+      </c>
+      <c r="AW23">
+        <v>5</v>
+      </c>
+      <c r="AX23">
+        <v>11</v>
+      </c>
+      <c r="AY23">
+        <v>9</v>
+      </c>
+      <c r="AZ23">
+        <v>17</v>
+      </c>
+      <c r="BA23">
+        <v>5</v>
+      </c>
+      <c r="BB23">
+        <v>10</v>
+      </c>
+      <c r="BC23">
+        <v>15</v>
+      </c>
+      <c r="BD23">
+        <v>1.81</v>
+      </c>
+      <c r="BE23">
+        <v>6.4</v>
+      </c>
+      <c r="BF23">
+        <v>2.2</v>
+      </c>
+      <c r="BG23">
+        <v>1.33</v>
+      </c>
+      <c r="BH23">
+        <v>2.95</v>
+      </c>
+      <c r="BI23">
+        <v>1.57</v>
+      </c>
+      <c r="BJ23">
+        <v>2.23</v>
+      </c>
+      <c r="BK23">
+        <v>1.92</v>
+      </c>
+      <c r="BL23">
+        <v>1.77</v>
+      </c>
+      <c r="BM23">
+        <v>2.43</v>
+      </c>
+      <c r="BN23">
+        <v>1.48</v>
+      </c>
+      <c r="BO23">
+        <v>3.15</v>
+      </c>
+      <c r="BP23">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:68">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>7781097</v>
+      </c>
+      <c r="C24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="2">
+        <v>45717.9375</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24" t="s">
+        <v>91</v>
+      </c>
+      <c r="H24" t="s">
+        <v>81</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>2</v>
+      </c>
+      <c r="K24">
+        <v>3</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>2</v>
+      </c>
+      <c r="N24">
+        <v>3</v>
+      </c>
+      <c r="O24" t="s">
+        <v>118</v>
+      </c>
+      <c r="P24" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q24">
+        <v>2.63</v>
+      </c>
+      <c r="R24">
+        <v>2.38</v>
+      </c>
+      <c r="S24">
+        <v>3.6</v>
+      </c>
+      <c r="T24">
+        <v>1.29</v>
+      </c>
+      <c r="U24">
+        <v>3.5</v>
+      </c>
+      <c r="V24">
+        <v>2.38</v>
+      </c>
+      <c r="W24">
+        <v>1.53</v>
+      </c>
+      <c r="X24">
+        <v>5.5</v>
+      </c>
+      <c r="Y24">
+        <v>1.14</v>
+      </c>
+      <c r="Z24">
+        <v>1.93</v>
+      </c>
+      <c r="AA24">
+        <v>3.67</v>
+      </c>
+      <c r="AB24">
+        <v>3.59</v>
+      </c>
+      <c r="AC24">
+        <v>1.03</v>
+      </c>
+      <c r="AD24">
+        <v>17</v>
+      </c>
+      <c r="AE24">
+        <v>1.19</v>
+      </c>
+      <c r="AF24">
+        <v>4.75</v>
+      </c>
+      <c r="AG24">
+        <v>1.6</v>
+      </c>
+      <c r="AH24">
+        <v>2.2</v>
+      </c>
+      <c r="AI24">
+        <v>1.5</v>
+      </c>
+      <c r="AJ24">
+        <v>2.5</v>
+      </c>
+      <c r="AK24">
+        <v>1.32</v>
+      </c>
+      <c r="AL24">
+        <v>1.27</v>
+      </c>
+      <c r="AM24">
+        <v>1.73</v>
+      </c>
+      <c r="AN24">
+        <v>0</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>0</v>
+      </c>
+      <c r="AQ24">
+        <v>3</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24">
+        <v>3</v>
+      </c>
+      <c r="AV24">
+        <v>6</v>
+      </c>
+      <c r="AW24">
+        <v>8</v>
+      </c>
+      <c r="AX24">
+        <v>0</v>
+      </c>
+      <c r="AY24">
+        <v>15</v>
+      </c>
+      <c r="AZ24">
+        <v>7</v>
+      </c>
+      <c r="BA24">
+        <v>6</v>
+      </c>
+      <c r="BB24">
+        <v>2</v>
+      </c>
+      <c r="BC24">
+        <v>8</v>
+      </c>
+      <c r="BD24">
+        <v>1.56</v>
+      </c>
+      <c r="BE24">
+        <v>6.75</v>
+      </c>
+      <c r="BF24">
+        <v>2.65</v>
+      </c>
+      <c r="BG24">
+        <v>1.23</v>
+      </c>
+      <c r="BH24">
+        <v>3.65</v>
+      </c>
+      <c r="BI24">
+        <v>1.41</v>
+      </c>
+      <c r="BJ24">
+        <v>2.65</v>
+      </c>
+      <c r="BK24">
+        <v>1.67</v>
+      </c>
+      <c r="BL24">
+        <v>2.05</v>
+      </c>
+      <c r="BM24">
+        <v>2.06</v>
+      </c>
+      <c r="BN24">
+        <v>1.66</v>
+      </c>
+      <c r="BO24">
+        <v>2.55</v>
+      </c>
+      <c r="BP24">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:68">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>7781098</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="2">
+        <v>45717.9375</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" t="s">
+        <v>92</v>
+      </c>
+      <c r="H25" t="s">
+        <v>96</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25" t="s">
+        <v>119</v>
+      </c>
+      <c r="P25" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q25">
+        <v>2.05</v>
+      </c>
+      <c r="R25">
+        <v>2.38</v>
+      </c>
+      <c r="S25">
+        <v>5.5</v>
+      </c>
+      <c r="T25">
+        <v>1.33</v>
+      </c>
+      <c r="U25">
+        <v>3.25</v>
+      </c>
+      <c r="V25">
+        <v>2.5</v>
+      </c>
+      <c r="W25">
+        <v>1.5</v>
+      </c>
+      <c r="X25">
+        <v>6.5</v>
+      </c>
+      <c r="Y25">
+        <v>1.11</v>
+      </c>
+      <c r="Z25">
+        <v>1.53</v>
+      </c>
+      <c r="AA25">
+        <v>4.1</v>
+      </c>
+      <c r="AB25">
+        <v>5.9</v>
+      </c>
+      <c r="AC25">
+        <v>1.03</v>
+      </c>
+      <c r="AD25">
+        <v>15</v>
+      </c>
+      <c r="AE25">
+        <v>1.2</v>
+      </c>
+      <c r="AF25">
+        <v>4.5</v>
+      </c>
+      <c r="AG25">
+        <v>1.65</v>
+      </c>
+      <c r="AH25">
+        <v>2.1</v>
+      </c>
+      <c r="AI25">
+        <v>1.8</v>
+      </c>
+      <c r="AJ25">
+        <v>1.95</v>
+      </c>
+      <c r="AK25">
+        <v>1.14</v>
+      </c>
+      <c r="AL25">
+        <v>1.21</v>
+      </c>
+      <c r="AM25">
+        <v>2.4</v>
+      </c>
+      <c r="AN25">
+        <v>0</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>3</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>1.66</v>
+      </c>
+      <c r="AT25">
+        <v>1.66</v>
+      </c>
+      <c r="AU25">
+        <v>6</v>
+      </c>
+      <c r="AV25">
+        <v>0</v>
+      </c>
+      <c r="AW25">
+        <v>6</v>
+      </c>
+      <c r="AX25">
+        <v>4</v>
+      </c>
+      <c r="AY25">
+        <v>12</v>
+      </c>
+      <c r="AZ25">
+        <v>5</v>
+      </c>
+      <c r="BA25">
+        <v>2</v>
+      </c>
+      <c r="BB25">
+        <v>5</v>
+      </c>
+      <c r="BC25">
+        <v>7</v>
+      </c>
+      <c r="BD25">
+        <v>1.33</v>
+      </c>
+      <c r="BE25">
+        <v>7.5</v>
+      </c>
+      <c r="BF25">
+        <v>3.65</v>
+      </c>
+      <c r="BG25">
+        <v>1.29</v>
+      </c>
+      <c r="BH25">
+        <v>3.2</v>
+      </c>
+      <c r="BI25">
+        <v>1.49</v>
+      </c>
+      <c r="BJ25">
+        <v>2.4</v>
+      </c>
+      <c r="BK25">
+        <v>1.8</v>
+      </c>
+      <c r="BL25">
+        <v>1.89</v>
+      </c>
+      <c r="BM25">
+        <v>2.23</v>
+      </c>
+      <c r="BN25">
+        <v>1.56</v>
+      </c>
+      <c r="BO25">
+        <v>2.8</v>
+      </c>
+      <c r="BP25">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:68">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>7781099</v>
+      </c>
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="2">
+        <v>45717.97916666666</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" t="s">
+        <v>93</v>
+      </c>
+      <c r="H26" t="s">
+        <v>98</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26">
+        <v>2</v>
+      </c>
+      <c r="K26">
+        <v>4</v>
+      </c>
+      <c r="L26">
+        <v>3</v>
+      </c>
+      <c r="M26">
+        <v>3</v>
+      </c>
+      <c r="N26">
+        <v>6</v>
+      </c>
+      <c r="O26" t="s">
+        <v>120</v>
+      </c>
+      <c r="P26" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q26">
+        <v>2.75</v>
+      </c>
+      <c r="R26">
+        <v>2.3</v>
+      </c>
+      <c r="S26">
+        <v>3.6</v>
+      </c>
+      <c r="T26">
+        <v>1.33</v>
+      </c>
+      <c r="U26">
+        <v>3.25</v>
+      </c>
+      <c r="V26">
+        <v>2.5</v>
+      </c>
+      <c r="W26">
+        <v>1.5</v>
+      </c>
+      <c r="X26">
+        <v>6.5</v>
+      </c>
+      <c r="Y26">
+        <v>1.11</v>
+      </c>
+      <c r="Z26">
+        <v>2.1</v>
+      </c>
+      <c r="AA26">
+        <v>3.26</v>
+      </c>
+      <c r="AB26">
+        <v>3.5</v>
+      </c>
+      <c r="AC26">
+        <v>1.04</v>
+      </c>
+      <c r="AD26">
+        <v>13</v>
+      </c>
+      <c r="AE26">
+        <v>1.2</v>
+      </c>
+      <c r="AF26">
+        <v>4.5</v>
+      </c>
+      <c r="AG26">
+        <v>1.65</v>
+      </c>
+      <c r="AH26">
+        <v>2.1</v>
+      </c>
+      <c r="AI26">
+        <v>1.57</v>
+      </c>
+      <c r="AJ26">
+        <v>2.25</v>
+      </c>
+      <c r="AK26">
+        <v>1.34</v>
+      </c>
+      <c r="AL26">
+        <v>1.27</v>
+      </c>
+      <c r="AM26">
+        <v>1.7</v>
+      </c>
+      <c r="AN26">
+        <v>0</v>
+      </c>
+      <c r="AO26">
+        <v>3</v>
+      </c>
+      <c r="AP26">
+        <v>1</v>
+      </c>
+      <c r="AQ26">
+        <v>2</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>1.17</v>
+      </c>
+      <c r="AT26">
+        <v>1.17</v>
+      </c>
+      <c r="AU26">
+        <v>6</v>
+      </c>
+      <c r="AV26">
+        <v>7</v>
+      </c>
+      <c r="AW26">
+        <v>10</v>
+      </c>
+      <c r="AX26">
+        <v>6</v>
+      </c>
+      <c r="AY26">
+        <v>16</v>
+      </c>
+      <c r="AZ26">
+        <v>16</v>
+      </c>
+      <c r="BA26">
+        <v>6</v>
+      </c>
+      <c r="BB26">
+        <v>1</v>
+      </c>
+      <c r="BC26">
+        <v>7</v>
+      </c>
+      <c r="BD26">
+        <v>1.65</v>
+      </c>
+      <c r="BE26">
+        <v>6.75</v>
+      </c>
+      <c r="BF26">
+        <v>2.5</v>
+      </c>
+      <c r="BG26">
+        <v>1.36</v>
+      </c>
+      <c r="BH26">
+        <v>2.8</v>
+      </c>
+      <c r="BI26">
+        <v>1.61</v>
+      </c>
+      <c r="BJ26">
+        <v>2.15</v>
+      </c>
+      <c r="BK26">
+        <v>1.98</v>
+      </c>
+      <c r="BL26">
+        <v>1.72</v>
+      </c>
+      <c r="BM26">
+        <v>2.55</v>
+      </c>
+      <c r="BN26">
+        <v>1.44</v>
+      </c>
+      <c r="BO26">
+        <v>3.3</v>
+      </c>
+      <c r="BP26">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:68">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>7781100</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="2">
+        <v>45718.02083333334</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27" t="s">
+        <v>70</v>
+      </c>
+      <c r="H27" t="s">
+        <v>95</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27" t="s">
+        <v>121</v>
+      </c>
+      <c r="P27" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q27">
+        <v>2.3</v>
+      </c>
+      <c r="R27">
+        <v>2.38</v>
+      </c>
+      <c r="S27">
+        <v>4.5</v>
+      </c>
+      <c r="T27">
+        <v>1.3</v>
+      </c>
+      <c r="U27">
+        <v>3.4</v>
+      </c>
+      <c r="V27">
+        <v>2.5</v>
+      </c>
+      <c r="W27">
+        <v>1.5</v>
+      </c>
+      <c r="X27">
+        <v>6</v>
+      </c>
+      <c r="Y27">
+        <v>1.13</v>
+      </c>
+      <c r="Z27">
+        <v>1.77</v>
+      </c>
+      <c r="AA27">
+        <v>3.83</v>
+      </c>
+      <c r="AB27">
+        <v>4.1</v>
+      </c>
+      <c r="AC27">
+        <v>1.03</v>
+      </c>
+      <c r="AD27">
+        <v>17</v>
+      </c>
+      <c r="AE27">
+        <v>1.2</v>
+      </c>
+      <c r="AF27">
+        <v>4.5</v>
+      </c>
+      <c r="AG27">
+        <v>1.57</v>
+      </c>
+      <c r="AH27">
+        <v>2.25</v>
+      </c>
+      <c r="AI27">
+        <v>1.62</v>
+      </c>
+      <c r="AJ27">
+        <v>2.2</v>
+      </c>
+      <c r="AK27">
+        <v>1.23</v>
+      </c>
+      <c r="AL27">
+        <v>1.23</v>
+      </c>
+      <c r="AM27">
+        <v>2</v>
+      </c>
+      <c r="AN27">
+        <v>3</v>
+      </c>
+      <c r="AO27">
+        <v>1</v>
+      </c>
+      <c r="AP27">
+        <v>3</v>
+      </c>
+      <c r="AQ27">
+        <v>0.5</v>
+      </c>
+      <c r="AR27">
+        <v>1.64</v>
+      </c>
+      <c r="AS27">
+        <v>1.23</v>
+      </c>
+      <c r="AT27">
+        <v>2.87</v>
+      </c>
+      <c r="AU27">
+        <v>5</v>
+      </c>
+      <c r="AV27">
+        <v>2</v>
+      </c>
+      <c r="AW27">
+        <v>3</v>
+      </c>
+      <c r="AX27">
+        <v>9</v>
+      </c>
+      <c r="AY27">
+        <v>9</v>
+      </c>
+      <c r="AZ27">
+        <v>17</v>
+      </c>
+      <c r="BA27">
+        <v>5</v>
+      </c>
+      <c r="BB27">
+        <v>5</v>
+      </c>
+      <c r="BC27">
+        <v>10</v>
+      </c>
+      <c r="BD27">
+        <v>1.5</v>
+      </c>
+      <c r="BE27">
+        <v>7</v>
+      </c>
+      <c r="BF27">
+        <v>2.8</v>
+      </c>
+      <c r="BG27">
+        <v>1.27</v>
+      </c>
+      <c r="BH27">
+        <v>3.3</v>
+      </c>
+      <c r="BI27">
+        <v>1.48</v>
+      </c>
+      <c r="BJ27">
+        <v>2.45</v>
+      </c>
+      <c r="BK27">
+        <v>1.75</v>
+      </c>
+      <c r="BL27">
+        <v>1.95</v>
+      </c>
+      <c r="BM27">
+        <v>2.17</v>
+      </c>
+      <c r="BN27">
+        <v>1.6</v>
+      </c>
+      <c r="BO27">
+        <v>2.8</v>
+      </c>
+      <c r="BP27">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:68">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>7781101</v>
+      </c>
+      <c r="C28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="2">
+        <v>45718.02083333334</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" t="s">
+        <v>77</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>1</v>
+      </c>
+      <c r="O28" t="s">
+        <v>122</v>
+      </c>
+      <c r="P28" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q28">
+        <v>2.45</v>
+      </c>
+      <c r="R28">
+        <v>2.3</v>
+      </c>
+      <c r="S28">
+        <v>3.5</v>
+      </c>
+      <c r="T28">
+        <v>1.27</v>
+      </c>
+      <c r="U28">
+        <v>3.4</v>
+      </c>
+      <c r="V28">
+        <v>2.2</v>
+      </c>
+      <c r="W28">
+        <v>1.58</v>
+      </c>
+      <c r="X28">
+        <v>5</v>
+      </c>
+      <c r="Y28">
+        <v>1.15</v>
+      </c>
+      <c r="Z28">
+        <v>1.96</v>
+      </c>
+      <c r="AA28">
+        <v>4</v>
+      </c>
+      <c r="AB28">
+        <v>3.2</v>
+      </c>
+      <c r="AC28">
+        <v>1.03</v>
+      </c>
+      <c r="AD28">
+        <v>11</v>
+      </c>
+      <c r="AE28">
+        <v>1.18</v>
+      </c>
+      <c r="AF28">
+        <v>4.75</v>
+      </c>
+      <c r="AG28">
+        <v>1.54</v>
+      </c>
+      <c r="AH28">
+        <v>2.38</v>
+      </c>
+      <c r="AI28">
+        <v>1.49</v>
+      </c>
+      <c r="AJ28">
+        <v>2.4</v>
+      </c>
+      <c r="AK28">
+        <v>1.32</v>
+      </c>
+      <c r="AL28">
+        <v>1.25</v>
+      </c>
+      <c r="AM28">
+        <v>1.75</v>
+      </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <v>0</v>
+      </c>
+      <c r="AP28">
+        <v>1.5</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0.72</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0.72</v>
+      </c>
+      <c r="AU28">
+        <v>3</v>
+      </c>
+      <c r="AV28">
+        <v>5</v>
+      </c>
+      <c r="AW28">
+        <v>7</v>
+      </c>
+      <c r="AX28">
+        <v>7</v>
+      </c>
+      <c r="AY28">
+        <v>11</v>
+      </c>
+      <c r="AZ28">
+        <v>12</v>
+      </c>
+      <c r="BA28">
+        <v>6</v>
+      </c>
+      <c r="BB28">
+        <v>5</v>
+      </c>
+      <c r="BC28">
+        <v>11</v>
+      </c>
+      <c r="BD28">
+        <v>1.74</v>
+      </c>
+      <c r="BE28">
+        <v>6.75</v>
+      </c>
+      <c r="BF28">
+        <v>2.3</v>
+      </c>
+      <c r="BG28">
+        <v>1.26</v>
+      </c>
+      <c r="BH28">
+        <v>3.4</v>
+      </c>
+      <c r="BI28">
+        <v>1.46</v>
+      </c>
+      <c r="BJ28">
+        <v>2.5</v>
+      </c>
+      <c r="BK28">
+        <v>1.74</v>
+      </c>
+      <c r="BL28">
+        <v>1.95</v>
+      </c>
+      <c r="BM28">
+        <v>2.17</v>
+      </c>
+      <c r="BN28">
+        <v>1.6</v>
+      </c>
+      <c r="BO28">
+        <v>2.7</v>
+      </c>
+      <c r="BP28">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:68">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>7781102</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="2">
+        <v>45718.02083333334</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" t="s">
+        <v>94</v>
+      </c>
+      <c r="H29" t="s">
+        <v>80</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29" t="s">
+        <v>109</v>
+      </c>
+      <c r="P29" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>2.07</v>
+      </c>
+      <c r="AA29">
+        <v>3.34</v>
+      </c>
+      <c r="AB29">
+        <v>3.47</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>1.55</v>
+      </c>
+      <c r="AH29">
+        <v>2.36</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>0</v>
+      </c>
+      <c r="AO29">
+        <v>0</v>
+      </c>
+      <c r="AP29">
+        <v>1</v>
+      </c>
+      <c r="AQ29">
+        <v>1</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29">
+        <v>-1</v>
+      </c>
+      <c r="AV29">
+        <v>-1</v>
+      </c>
+      <c r="AW29">
+        <v>-1</v>
+      </c>
+      <c r="AX29">
+        <v>-1</v>
+      </c>
+      <c r="AY29">
+        <v>-1</v>
+      </c>
+      <c r="AZ29">
+        <v>-1</v>
+      </c>
+      <c r="BA29">
+        <v>-1</v>
+      </c>
+      <c r="BB29">
+        <v>-1</v>
+      </c>
+      <c r="BC29">
+        <v>-1</v>
+      </c>
+      <c r="BD29">
+        <v>0</v>
+      </c>
+      <c r="BE29">
+        <v>0</v>
+      </c>
+      <c r="BF29">
+        <v>0</v>
+      </c>
+      <c r="BG29">
+        <v>0</v>
+      </c>
+      <c r="BH29">
+        <v>0</v>
+      </c>
+      <c r="BI29">
+        <v>0</v>
+      </c>
+      <c r="BJ29">
+        <v>0</v>
+      </c>
+      <c r="BK29">
+        <v>0</v>
+      </c>
+      <c r="BL29">
+        <v>0</v>
+      </c>
+      <c r="BM29">
+        <v>0</v>
+      </c>
+      <c r="BN29">
+        <v>0</v>
+      </c>
+      <c r="BO29">
+        <v>0</v>
+      </c>
+      <c r="BP29">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="142">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -301,6 +301,9 @@
     <t>San Diego</t>
   </si>
   <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
     <t>New York City</t>
   </si>
   <si>
@@ -313,9 +316,6 @@
     <t>FC Dallas</t>
   </si>
   <si>
-    <t>Vancouver Whitecaps</t>
-  </si>
-  <si>
     <t>['78']</t>
   </si>
   <si>
@@ -385,6 +385,12 @@
     <t>['89']</t>
   </si>
   <si>
+    <t>['2', '87']</t>
+  </si>
+  <si>
+    <t>['85']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -428,6 +434,12 @@
   </si>
   <si>
     <t>['43', '45', '68']</t>
+  </si>
+  <si>
+    <t>['39']</t>
+  </si>
+  <si>
+    <t>['6', '37', '45+2', '79']</t>
   </si>
 </sst>
 </file>
@@ -789,7 +801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP29"/>
+  <dimension ref="A1:BP31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1227,7 +1239,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1251,7 +1263,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -1433,7 +1445,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1457,7 +1469,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1869,7 +1881,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2051,7 +2063,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I7">
         <v>2</v>
@@ -2075,7 +2087,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2281,7 +2293,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2669,7 +2681,7 @@
         <v>78</v>
       </c>
       <c r="H10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -2693,7 +2705,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -3517,7 +3529,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -3699,7 +3711,7 @@
         <v>83</v>
       </c>
       <c r="H15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -3723,7 +3735,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -3929,7 +3941,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4547,7 +4559,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -4935,7 +4947,7 @@
         <v>76</v>
       </c>
       <c r="H21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I21">
         <v>2</v>
@@ -4959,7 +4971,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -5165,7 +5177,7 @@
         <v>116</v>
       </c>
       <c r="P22" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5371,7 +5383,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -5577,7 +5589,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -5759,7 +5771,7 @@
         <v>92</v>
       </c>
       <c r="H25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -5965,7 +5977,7 @@
         <v>93</v>
       </c>
       <c r="H26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I26">
         <v>2</v>
@@ -5989,7 +6001,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6171,7 +6183,7 @@
         <v>70</v>
       </c>
       <c r="H27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -6764,6 +6776,418 @@
       </c>
       <c r="BP29">
         <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:68">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>7781103</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="2">
+        <v>45718.79166666666</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30" t="s">
+        <v>95</v>
+      </c>
+      <c r="H30" t="s">
+        <v>84</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>2</v>
+      </c>
+      <c r="L30">
+        <v>2</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>3</v>
+      </c>
+      <c r="O30" t="s">
+        <v>123</v>
+      </c>
+      <c r="P30" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q30">
+        <v>2.6</v>
+      </c>
+      <c r="R30">
+        <v>2.4</v>
+      </c>
+      <c r="S30">
+        <v>3.6</v>
+      </c>
+      <c r="T30">
+        <v>1.29</v>
+      </c>
+      <c r="U30">
+        <v>3.5</v>
+      </c>
+      <c r="V30">
+        <v>2.25</v>
+      </c>
+      <c r="W30">
+        <v>1.57</v>
+      </c>
+      <c r="X30">
+        <v>5.5</v>
+      </c>
+      <c r="Y30">
+        <v>1.14</v>
+      </c>
+      <c r="Z30">
+        <v>2.04</v>
+      </c>
+      <c r="AA30">
+        <v>3.77</v>
+      </c>
+      <c r="AB30">
+        <v>3.17</v>
+      </c>
+      <c r="AC30">
+        <v>1.02</v>
+      </c>
+      <c r="AD30">
+        <v>19</v>
+      </c>
+      <c r="AE30">
+        <v>1.18</v>
+      </c>
+      <c r="AF30">
+        <v>5</v>
+      </c>
+      <c r="AG30">
+        <v>1.56</v>
+      </c>
+      <c r="AH30">
+        <v>2.33</v>
+      </c>
+      <c r="AI30">
+        <v>1.5</v>
+      </c>
+      <c r="AJ30">
+        <v>2.5</v>
+      </c>
+      <c r="AK30">
+        <v>1.35</v>
+      </c>
+      <c r="AL30">
+        <v>1.25</v>
+      </c>
+      <c r="AM30">
+        <v>1.72</v>
+      </c>
+      <c r="AN30">
+        <v>0</v>
+      </c>
+      <c r="AO30">
+        <v>0</v>
+      </c>
+      <c r="AP30">
+        <v>3</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30">
+        <v>6</v>
+      </c>
+      <c r="AV30">
+        <v>2</v>
+      </c>
+      <c r="AW30">
+        <v>8</v>
+      </c>
+      <c r="AX30">
+        <v>5</v>
+      </c>
+      <c r="AY30">
+        <v>18</v>
+      </c>
+      <c r="AZ30">
+        <v>8</v>
+      </c>
+      <c r="BA30">
+        <v>6</v>
+      </c>
+      <c r="BB30">
+        <v>1</v>
+      </c>
+      <c r="BC30">
+        <v>7</v>
+      </c>
+      <c r="BD30">
+        <v>1.76</v>
+      </c>
+      <c r="BE30">
+        <v>6.75</v>
+      </c>
+      <c r="BF30">
+        <v>2.23</v>
+      </c>
+      <c r="BG30">
+        <v>1.21</v>
+      </c>
+      <c r="BH30">
+        <v>3.8</v>
+      </c>
+      <c r="BI30">
+        <v>1.38</v>
+      </c>
+      <c r="BJ30">
+        <v>2.7</v>
+      </c>
+      <c r="BK30">
+        <v>1.64</v>
+      </c>
+      <c r="BL30">
+        <v>2.1</v>
+      </c>
+      <c r="BM30">
+        <v>1.98</v>
+      </c>
+      <c r="BN30">
+        <v>1.72</v>
+      </c>
+      <c r="BO30">
+        <v>2.5</v>
+      </c>
+      <c r="BP30">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:68">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>7781104</v>
+      </c>
+      <c r="C31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="2">
+        <v>45718.875</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" t="s">
+        <v>71</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>3</v>
+      </c>
+      <c r="K31">
+        <v>3</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31">
+        <v>4</v>
+      </c>
+      <c r="N31">
+        <v>5</v>
+      </c>
+      <c r="O31" t="s">
+        <v>124</v>
+      </c>
+      <c r="P31" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q31">
+        <v>3</v>
+      </c>
+      <c r="R31">
+        <v>2.3</v>
+      </c>
+      <c r="S31">
+        <v>3.1</v>
+      </c>
+      <c r="T31">
+        <v>1.3</v>
+      </c>
+      <c r="U31">
+        <v>3.4</v>
+      </c>
+      <c r="V31">
+        <v>2.5</v>
+      </c>
+      <c r="W31">
+        <v>1.5</v>
+      </c>
+      <c r="X31">
+        <v>6</v>
+      </c>
+      <c r="Y31">
+        <v>1.13</v>
+      </c>
+      <c r="Z31">
+        <v>2.55</v>
+      </c>
+      <c r="AA31">
+        <v>3.5</v>
+      </c>
+      <c r="AB31">
+        <v>2.55</v>
+      </c>
+      <c r="AC31">
+        <v>1.03</v>
+      </c>
+      <c r="AD31">
+        <v>17</v>
+      </c>
+      <c r="AE31">
+        <v>1.19</v>
+      </c>
+      <c r="AF31">
+        <v>4.75</v>
+      </c>
+      <c r="AG31">
+        <v>1.6</v>
+      </c>
+      <c r="AH31">
+        <v>2.2</v>
+      </c>
+      <c r="AI31">
+        <v>1.53</v>
+      </c>
+      <c r="AJ31">
+        <v>2.38</v>
+      </c>
+      <c r="AK31">
+        <v>1.47</v>
+      </c>
+      <c r="AL31">
+        <v>1.27</v>
+      </c>
+      <c r="AM31">
+        <v>1.51</v>
+      </c>
+      <c r="AN31">
+        <v>0</v>
+      </c>
+      <c r="AO31">
+        <v>0</v>
+      </c>
+      <c r="AP31">
+        <v>0</v>
+      </c>
+      <c r="AQ31">
+        <v>3</v>
+      </c>
+      <c r="AR31">
+        <v>1.39</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>1.39</v>
+      </c>
+      <c r="AU31">
+        <v>4</v>
+      </c>
+      <c r="AV31">
+        <v>6</v>
+      </c>
+      <c r="AW31">
+        <v>5</v>
+      </c>
+      <c r="AX31">
+        <v>4</v>
+      </c>
+      <c r="AY31">
+        <v>9</v>
+      </c>
+      <c r="AZ31">
+        <v>10</v>
+      </c>
+      <c r="BA31">
+        <v>-1</v>
+      </c>
+      <c r="BB31">
+        <v>-1</v>
+      </c>
+      <c r="BC31">
+        <v>-1</v>
+      </c>
+      <c r="BD31">
+        <v>1.74</v>
+      </c>
+      <c r="BE31">
+        <v>6.5</v>
+      </c>
+      <c r="BF31">
+        <v>2.3</v>
+      </c>
+      <c r="BG31">
+        <v>1.28</v>
+      </c>
+      <c r="BH31">
+        <v>3.3</v>
+      </c>
+      <c r="BI31">
+        <v>1.47</v>
+      </c>
+      <c r="BJ31">
+        <v>2.43</v>
+      </c>
+      <c r="BK31">
+        <v>1.77</v>
+      </c>
+      <c r="BL31">
+        <v>1.91</v>
+      </c>
+      <c r="BM31">
+        <v>2.23</v>
+      </c>
+      <c r="BN31">
+        <v>1.57</v>
+      </c>
+      <c r="BO31">
+        <v>2.85</v>
+      </c>
+      <c r="BP31">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -6712,31 +6712,31 @@
         <v>0</v>
       </c>
       <c r="AU29">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AV29">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AW29">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AX29">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AY29">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AZ29">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BA29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BB29">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BC29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BD29">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -7142,13 +7142,13 @@
         <v>10</v>
       </c>
       <c r="BA31">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BB31">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BD31">
         <v>1.74</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="144">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -391,6 +391,9 @@
     <t>['85']</t>
   </si>
   <si>
+    <t>['11', '57', '77', '84', '90+4']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -440,6 +443,9 @@
   </si>
   <si>
     <t>['6', '37', '45+2', '79']</t>
+  </si>
+  <si>
+    <t>['37', '90+2']</t>
   </si>
 </sst>
 </file>
@@ -801,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP31"/>
+  <dimension ref="A1:BP33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1263,7 +1269,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -1469,7 +1475,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1881,7 +1887,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -1959,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
         <v>0</v>
@@ -2087,7 +2093,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2293,7 +2299,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2705,7 +2711,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -3529,7 +3535,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -3607,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ14">
         <v>1</v>
@@ -3735,7 +3741,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -3941,7 +3947,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4559,7 +4565,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -4971,7 +4977,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -5177,7 +5183,7 @@
         <v>116</v>
       </c>
       <c r="P22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5383,7 +5389,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -5589,7 +5595,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6001,7 +6007,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6825,7 +6831,7 @@
         <v>123</v>
       </c>
       <c r="P30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7031,7 +7037,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7188,6 +7194,418 @@
       </c>
       <c r="BP31">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:68">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>7781105</v>
+      </c>
+      <c r="C32" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45724.6875</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32" t="s">
+        <v>74</v>
+      </c>
+      <c r="H32" t="s">
+        <v>78</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32" t="s">
+        <v>109</v>
+      </c>
+      <c r="P32" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q32">
+        <v>2.38</v>
+      </c>
+      <c r="R32">
+        <v>2.3</v>
+      </c>
+      <c r="S32">
+        <v>4.5</v>
+      </c>
+      <c r="T32">
+        <v>1.33</v>
+      </c>
+      <c r="U32">
+        <v>3.25</v>
+      </c>
+      <c r="V32">
+        <v>2.63</v>
+      </c>
+      <c r="W32">
+        <v>1.44</v>
+      </c>
+      <c r="X32">
+        <v>6.5</v>
+      </c>
+      <c r="Y32">
+        <v>1.11</v>
+      </c>
+      <c r="Z32">
+        <v>1.77</v>
+      </c>
+      <c r="AA32">
+        <v>3.75</v>
+      </c>
+      <c r="AB32">
+        <v>4.2</v>
+      </c>
+      <c r="AC32">
+        <v>1.03</v>
+      </c>
+      <c r="AD32">
+        <v>13</v>
+      </c>
+      <c r="AE32">
+        <v>1.24</v>
+      </c>
+      <c r="AF32">
+        <v>4.2</v>
+      </c>
+      <c r="AG32">
+        <v>1.67</v>
+      </c>
+      <c r="AH32">
+        <v>2.05</v>
+      </c>
+      <c r="AI32">
+        <v>1.67</v>
+      </c>
+      <c r="AJ32">
+        <v>2.1</v>
+      </c>
+      <c r="AK32">
+        <v>1.22</v>
+      </c>
+      <c r="AL32">
+        <v>1.26</v>
+      </c>
+      <c r="AM32">
+        <v>1.98</v>
+      </c>
+      <c r="AN32">
+        <v>3</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>2</v>
+      </c>
+      <c r="AQ32">
+        <v>1</v>
+      </c>
+      <c r="AR32">
+        <v>1.83</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>1.83</v>
+      </c>
+      <c r="AU32">
+        <v>6</v>
+      </c>
+      <c r="AV32">
+        <v>2</v>
+      </c>
+      <c r="AW32">
+        <v>6</v>
+      </c>
+      <c r="AX32">
+        <v>3</v>
+      </c>
+      <c r="AY32">
+        <v>12</v>
+      </c>
+      <c r="AZ32">
+        <v>6</v>
+      </c>
+      <c r="BA32">
+        <v>5</v>
+      </c>
+      <c r="BB32">
+        <v>4</v>
+      </c>
+      <c r="BC32">
+        <v>9</v>
+      </c>
+      <c r="BD32">
+        <v>1.5</v>
+      </c>
+      <c r="BE32">
+        <v>6.75</v>
+      </c>
+      <c r="BF32">
+        <v>2.9</v>
+      </c>
+      <c r="BG32">
+        <v>1.36</v>
+      </c>
+      <c r="BH32">
+        <v>2.8</v>
+      </c>
+      <c r="BI32">
+        <v>1.63</v>
+      </c>
+      <c r="BJ32">
+        <v>2.12</v>
+      </c>
+      <c r="BK32">
+        <v>2.02</v>
+      </c>
+      <c r="BL32">
+        <v>1.68</v>
+      </c>
+      <c r="BM32">
+        <v>2.55</v>
+      </c>
+      <c r="BN32">
+        <v>1.44</v>
+      </c>
+      <c r="BO32">
+        <v>3.4</v>
+      </c>
+      <c r="BP32">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:68">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>7781106</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="2">
+        <v>45724.78125</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33" t="s">
+        <v>82</v>
+      </c>
+      <c r="H33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33">
+        <v>2</v>
+      </c>
+      <c r="L33">
+        <v>5</v>
+      </c>
+      <c r="M33">
+        <v>2</v>
+      </c>
+      <c r="N33">
+        <v>7</v>
+      </c>
+      <c r="O33" t="s">
+        <v>125</v>
+      </c>
+      <c r="P33" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q33">
+        <v>2.75</v>
+      </c>
+      <c r="R33">
+        <v>2.1</v>
+      </c>
+      <c r="S33">
+        <v>4.33</v>
+      </c>
+      <c r="T33">
+        <v>1.44</v>
+      </c>
+      <c r="U33">
+        <v>2.63</v>
+      </c>
+      <c r="V33">
+        <v>3.25</v>
+      </c>
+      <c r="W33">
+        <v>1.33</v>
+      </c>
+      <c r="X33">
+        <v>9</v>
+      </c>
+      <c r="Y33">
+        <v>1.07</v>
+      </c>
+      <c r="Z33">
+        <v>2.04</v>
+      </c>
+      <c r="AA33">
+        <v>3.41</v>
+      </c>
+      <c r="AB33">
+        <v>3.5</v>
+      </c>
+      <c r="AC33">
+        <v>1.03</v>
+      </c>
+      <c r="AD33">
+        <v>15</v>
+      </c>
+      <c r="AE33">
+        <v>1.25</v>
+      </c>
+      <c r="AF33">
+        <v>4</v>
+      </c>
+      <c r="AG33">
+        <v>1.7</v>
+      </c>
+      <c r="AH33">
+        <v>2.05</v>
+      </c>
+      <c r="AI33">
+        <v>1.95</v>
+      </c>
+      <c r="AJ33">
+        <v>1.8</v>
+      </c>
+      <c r="AK33">
+        <v>1.3</v>
+      </c>
+      <c r="AL33">
+        <v>1.29</v>
+      </c>
+      <c r="AM33">
+        <v>1.72</v>
+      </c>
+      <c r="AN33">
+        <v>1</v>
+      </c>
+      <c r="AO33">
+        <v>0</v>
+      </c>
+      <c r="AP33">
+        <v>2</v>
+      </c>
+      <c r="AQ33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>2.47</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
+        <v>2.47</v>
+      </c>
+      <c r="AU33">
+        <v>11</v>
+      </c>
+      <c r="AV33">
+        <v>4</v>
+      </c>
+      <c r="AW33">
+        <v>2</v>
+      </c>
+      <c r="AX33">
+        <v>3</v>
+      </c>
+      <c r="AY33">
+        <v>14</v>
+      </c>
+      <c r="AZ33">
+        <v>7</v>
+      </c>
+      <c r="BA33">
+        <v>9</v>
+      </c>
+      <c r="BB33">
+        <v>4</v>
+      </c>
+      <c r="BC33">
+        <v>13</v>
+      </c>
+      <c r="BD33">
+        <v>1.58</v>
+      </c>
+      <c r="BE33">
+        <v>6.75</v>
+      </c>
+      <c r="BF33">
+        <v>2.55</v>
+      </c>
+      <c r="BG33">
+        <v>1.24</v>
+      </c>
+      <c r="BH33">
+        <v>3.55</v>
+      </c>
+      <c r="BI33">
+        <v>1.41</v>
+      </c>
+      <c r="BJ33">
+        <v>2.63</v>
+      </c>
+      <c r="BK33">
+        <v>1.68</v>
+      </c>
+      <c r="BL33">
+        <v>2.04</v>
+      </c>
+      <c r="BM33">
+        <v>2.06</v>
+      </c>
+      <c r="BN33">
+        <v>1.66</v>
+      </c>
+      <c r="BO33">
+        <v>2.55</v>
+      </c>
+      <c r="BP33">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="156">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -307,15 +307,15 @@
     <t>New York City</t>
   </si>
   <si>
+    <t>FC Dallas</t>
+  </si>
+  <si>
     <t>Montreal Impact</t>
   </si>
   <si>
     <t>Toronto</t>
   </si>
   <si>
-    <t>FC Dallas</t>
-  </si>
-  <si>
     <t>['78']</t>
   </si>
   <si>
@@ -394,6 +394,27 @@
     <t>['11', '57', '77', '84', '90+4']</t>
   </si>
   <si>
+    <t>['73', '87']</t>
+  </si>
+  <si>
+    <t>['60', '68']</t>
+  </si>
+  <si>
+    <t>['59', '71']</t>
+  </si>
+  <si>
+    <t>['57']</t>
+  </si>
+  <si>
+    <t>['45+3', '68']</t>
+  </si>
+  <si>
+    <t>['17']</t>
+  </si>
+  <si>
+    <t>['32', '49']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -446,6 +467,21 @@
   </si>
   <si>
     <t>['37', '90+2']</t>
+  </si>
+  <si>
+    <t>['53']</t>
+  </si>
+  <si>
+    <t>['76', '90+7']</t>
+  </si>
+  <si>
+    <t>['82', '84', '90+1']</t>
+  </si>
+  <si>
+    <t>['43', '90+1', '90+6']</t>
+  </si>
+  <si>
+    <t>['32']</t>
   </si>
 </sst>
 </file>
@@ -807,7 +843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP33"/>
+  <dimension ref="A1:BP44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1144,7 +1180,7 @@
         <v>3</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1269,7 +1305,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -1451,7 +1487,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1475,7 +1511,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1553,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ4">
         <v>0</v>
@@ -1762,7 +1798,7 @@
         <v>3</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1887,7 +1923,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -1968,7 +2004,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2069,7 +2105,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I7">
         <v>2</v>
@@ -2093,7 +2129,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2171,10 +2207,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ7">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2299,7 +2335,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2583,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9">
         <v>0</v>
@@ -2687,7 +2723,7 @@
         <v>78</v>
       </c>
       <c r="H10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -2711,7 +2747,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -2995,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
         <v>1</v>
@@ -3204,7 +3240,7 @@
         <v>1</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3407,7 +3443,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ13">
         <v>0</v>
@@ -3535,7 +3571,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -3741,7 +3777,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -3947,7 +3983,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4437,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ18">
         <v>0</v>
@@ -4565,7 +4601,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -4953,7 +4989,7 @@
         <v>76</v>
       </c>
       <c r="H21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I21">
         <v>2</v>
@@ -4977,7 +5013,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -5058,7 +5094,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ21">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR21">
         <v>2.07</v>
@@ -5183,7 +5219,7 @@
         <v>116</v>
       </c>
       <c r="P22" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5389,7 +5425,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -5595,7 +5631,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -5777,7 +5813,7 @@
         <v>92</v>
       </c>
       <c r="H25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -5983,7 +6019,7 @@
         <v>93</v>
       </c>
       <c r="H26" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I26">
         <v>2</v>
@@ -6007,7 +6043,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6831,7 +6867,7 @@
         <v>123</v>
       </c>
       <c r="P30" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7037,7 +7073,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7449,7 +7485,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -7606,6 +7642,2272 @@
       </c>
       <c r="BP33">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:68">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>7781107</v>
+      </c>
+      <c r="C34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="2">
+        <v>45724.89583333334</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34" t="s">
+        <v>72</v>
+      </c>
+      <c r="H34" t="s">
+        <v>88</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34" t="s">
+        <v>109</v>
+      </c>
+      <c r="P34" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q34">
+        <v>2.75</v>
+      </c>
+      <c r="R34">
+        <v>2.25</v>
+      </c>
+      <c r="S34">
+        <v>3.6</v>
+      </c>
+      <c r="T34">
+        <v>1.33</v>
+      </c>
+      <c r="U34">
+        <v>3.25</v>
+      </c>
+      <c r="V34">
+        <v>2.63</v>
+      </c>
+      <c r="W34">
+        <v>1.44</v>
+      </c>
+      <c r="X34">
+        <v>6.5</v>
+      </c>
+      <c r="Y34">
+        <v>1.11</v>
+      </c>
+      <c r="Z34">
+        <v>2.12</v>
+      </c>
+      <c r="AA34">
+        <v>3.56</v>
+      </c>
+      <c r="AB34">
+        <v>3.14</v>
+      </c>
+      <c r="AC34">
+        <v>1.02</v>
+      </c>
+      <c r="AD34">
+        <v>17</v>
+      </c>
+      <c r="AE34">
+        <v>1.19</v>
+      </c>
+      <c r="AF34">
+        <v>4.75</v>
+      </c>
+      <c r="AG34">
+        <v>1.57</v>
+      </c>
+      <c r="AH34">
+        <v>2.25</v>
+      </c>
+      <c r="AI34">
+        <v>1.62</v>
+      </c>
+      <c r="AJ34">
+        <v>2.2</v>
+      </c>
+      <c r="AK34">
+        <v>1.34</v>
+      </c>
+      <c r="AL34">
+        <v>1.27</v>
+      </c>
+      <c r="AM34">
+        <v>1.68</v>
+      </c>
+      <c r="AN34">
+        <v>3</v>
+      </c>
+      <c r="AO34">
+        <v>0</v>
+      </c>
+      <c r="AP34">
+        <v>2</v>
+      </c>
+      <c r="AQ34">
+        <v>0.5</v>
+      </c>
+      <c r="AR34">
+        <v>1.85</v>
+      </c>
+      <c r="AS34">
+        <v>1.67</v>
+      </c>
+      <c r="AT34">
+        <v>3.52</v>
+      </c>
+      <c r="AU34">
+        <v>7</v>
+      </c>
+      <c r="AV34">
+        <v>0</v>
+      </c>
+      <c r="AW34">
+        <v>5</v>
+      </c>
+      <c r="AX34">
+        <v>9</v>
+      </c>
+      <c r="AY34">
+        <v>13</v>
+      </c>
+      <c r="AZ34">
+        <v>13</v>
+      </c>
+      <c r="BA34">
+        <v>5</v>
+      </c>
+      <c r="BB34">
+        <v>2</v>
+      </c>
+      <c r="BC34">
+        <v>7</v>
+      </c>
+      <c r="BD34">
+        <v>1.72</v>
+      </c>
+      <c r="BE34">
+        <v>6.75</v>
+      </c>
+      <c r="BF34">
+        <v>2.33</v>
+      </c>
+      <c r="BG34">
+        <v>1.26</v>
+      </c>
+      <c r="BH34">
+        <v>3.4</v>
+      </c>
+      <c r="BI34">
+        <v>1.46</v>
+      </c>
+      <c r="BJ34">
+        <v>2.5</v>
+      </c>
+      <c r="BK34">
+        <v>1.74</v>
+      </c>
+      <c r="BL34">
+        <v>1.96</v>
+      </c>
+      <c r="BM34">
+        <v>2.15</v>
+      </c>
+      <c r="BN34">
+        <v>1.61</v>
+      </c>
+      <c r="BO34">
+        <v>2.7</v>
+      </c>
+      <c r="BP34">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:68">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>7781108</v>
+      </c>
+      <c r="C35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="2">
+        <v>45724.89583333334</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35" t="s">
+        <v>73</v>
+      </c>
+      <c r="H35" t="s">
+        <v>99</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>2</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>2</v>
+      </c>
+      <c r="O35" t="s">
+        <v>126</v>
+      </c>
+      <c r="P35" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q35">
+        <v>2.25</v>
+      </c>
+      <c r="R35">
+        <v>2.38</v>
+      </c>
+      <c r="S35">
+        <v>4.75</v>
+      </c>
+      <c r="T35">
+        <v>1.33</v>
+      </c>
+      <c r="U35">
+        <v>3.25</v>
+      </c>
+      <c r="V35">
+        <v>2.5</v>
+      </c>
+      <c r="W35">
+        <v>1.5</v>
+      </c>
+      <c r="X35">
+        <v>6</v>
+      </c>
+      <c r="Y35">
+        <v>1.13</v>
+      </c>
+      <c r="Z35">
+        <v>1.68</v>
+      </c>
+      <c r="AA35">
+        <v>4</v>
+      </c>
+      <c r="AB35">
+        <v>4.4</v>
+      </c>
+      <c r="AC35">
+        <v>1.02</v>
+      </c>
+      <c r="AD35">
+        <v>19</v>
+      </c>
+      <c r="AE35">
+        <v>1.18</v>
+      </c>
+      <c r="AF35">
+        <v>5</v>
+      </c>
+      <c r="AG35">
+        <v>1.8</v>
+      </c>
+      <c r="AH35">
+        <v>1.94</v>
+      </c>
+      <c r="AI35">
+        <v>1.67</v>
+      </c>
+      <c r="AJ35">
+        <v>2.1</v>
+      </c>
+      <c r="AK35">
+        <v>1.2</v>
+      </c>
+      <c r="AL35">
+        <v>1.23</v>
+      </c>
+      <c r="AM35">
+        <v>2.1</v>
+      </c>
+      <c r="AN35">
+        <v>3</v>
+      </c>
+      <c r="AO35">
+        <v>0.5</v>
+      </c>
+      <c r="AP35">
+        <v>3</v>
+      </c>
+      <c r="AQ35">
+        <v>0.33</v>
+      </c>
+      <c r="AR35">
+        <v>1.23</v>
+      </c>
+      <c r="AS35">
+        <v>1.47</v>
+      </c>
+      <c r="AT35">
+        <v>2.7</v>
+      </c>
+      <c r="AU35">
+        <v>9</v>
+      </c>
+      <c r="AV35">
+        <v>2</v>
+      </c>
+      <c r="AW35">
+        <v>6</v>
+      </c>
+      <c r="AX35">
+        <v>6</v>
+      </c>
+      <c r="AY35">
+        <v>15</v>
+      </c>
+      <c r="AZ35">
+        <v>11</v>
+      </c>
+      <c r="BA35">
+        <v>5</v>
+      </c>
+      <c r="BB35">
+        <v>4</v>
+      </c>
+      <c r="BC35">
+        <v>9</v>
+      </c>
+      <c r="BD35">
+        <v>1.53</v>
+      </c>
+      <c r="BE35">
+        <v>6.75</v>
+      </c>
+      <c r="BF35">
+        <v>2.8</v>
+      </c>
+      <c r="BG35">
+        <v>1.3</v>
+      </c>
+      <c r="BH35">
+        <v>3.15</v>
+      </c>
+      <c r="BI35">
+        <v>1.52</v>
+      </c>
+      <c r="BJ35">
+        <v>2.33</v>
+      </c>
+      <c r="BK35">
+        <v>1.83</v>
+      </c>
+      <c r="BL35">
+        <v>1.85</v>
+      </c>
+      <c r="BM35">
+        <v>2.3</v>
+      </c>
+      <c r="BN35">
+        <v>1.53</v>
+      </c>
+      <c r="BO35">
+        <v>2.95</v>
+      </c>
+      <c r="BP35">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:68">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>7781109</v>
+      </c>
+      <c r="C36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="2">
+        <v>45724.89583333334</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36" t="s">
+        <v>75</v>
+      </c>
+      <c r="H36" t="s">
+        <v>91</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>2</v>
+      </c>
+      <c r="M36">
+        <v>1</v>
+      </c>
+      <c r="N36">
+        <v>3</v>
+      </c>
+      <c r="O36" t="s">
+        <v>127</v>
+      </c>
+      <c r="P36" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q36">
+        <v>2.4</v>
+      </c>
+      <c r="R36">
+        <v>2.3</v>
+      </c>
+      <c r="S36">
+        <v>4</v>
+      </c>
+      <c r="T36">
+        <v>1.3</v>
+      </c>
+      <c r="U36">
+        <v>3.4</v>
+      </c>
+      <c r="V36">
+        <v>2.5</v>
+      </c>
+      <c r="W36">
+        <v>1.5</v>
+      </c>
+      <c r="X36">
+        <v>6</v>
+      </c>
+      <c r="Y36">
+        <v>1.13</v>
+      </c>
+      <c r="Z36">
+        <v>1.94</v>
+      </c>
+      <c r="AA36">
+        <v>3.81</v>
+      </c>
+      <c r="AB36">
+        <v>3.41</v>
+      </c>
+      <c r="AC36">
+        <v>1.02</v>
+      </c>
+      <c r="AD36">
+        <v>17</v>
+      </c>
+      <c r="AE36">
+        <v>1.19</v>
+      </c>
+      <c r="AF36">
+        <v>4.75</v>
+      </c>
+      <c r="AG36">
+        <v>1.57</v>
+      </c>
+      <c r="AH36">
+        <v>2.25</v>
+      </c>
+      <c r="AI36">
+        <v>1.62</v>
+      </c>
+      <c r="AJ36">
+        <v>2.2</v>
+      </c>
+      <c r="AK36">
+        <v>1.29</v>
+      </c>
+      <c r="AL36">
+        <v>1.25</v>
+      </c>
+      <c r="AM36">
+        <v>1.82</v>
+      </c>
+      <c r="AN36">
+        <v>1</v>
+      </c>
+      <c r="AO36">
+        <v>0</v>
+      </c>
+      <c r="AP36">
+        <v>2</v>
+      </c>
+      <c r="AQ36">
+        <v>0</v>
+      </c>
+      <c r="AR36">
+        <v>1.23</v>
+      </c>
+      <c r="AS36">
+        <v>0.89</v>
+      </c>
+      <c r="AT36">
+        <v>2.12</v>
+      </c>
+      <c r="AU36">
+        <v>5</v>
+      </c>
+      <c r="AV36">
+        <v>2</v>
+      </c>
+      <c r="AW36">
+        <v>8</v>
+      </c>
+      <c r="AX36">
+        <v>6</v>
+      </c>
+      <c r="AY36">
+        <v>17</v>
+      </c>
+      <c r="AZ36">
+        <v>9</v>
+      </c>
+      <c r="BA36">
+        <v>6</v>
+      </c>
+      <c r="BB36">
+        <v>1</v>
+      </c>
+      <c r="BC36">
+        <v>7</v>
+      </c>
+      <c r="BD36">
+        <v>1.61</v>
+      </c>
+      <c r="BE36">
+        <v>6.75</v>
+      </c>
+      <c r="BF36">
+        <v>2.55</v>
+      </c>
+      <c r="BG36">
+        <v>1.25</v>
+      </c>
+      <c r="BH36">
+        <v>3.45</v>
+      </c>
+      <c r="BI36">
+        <v>1.44</v>
+      </c>
+      <c r="BJ36">
+        <v>2.55</v>
+      </c>
+      <c r="BK36">
+        <v>1.72</v>
+      </c>
+      <c r="BL36">
+        <v>1.98</v>
+      </c>
+      <c r="BM36">
+        <v>2.12</v>
+      </c>
+      <c r="BN36">
+        <v>1.63</v>
+      </c>
+      <c r="BO36">
+        <v>2.7</v>
+      </c>
+      <c r="BP36">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:68">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>7781110</v>
+      </c>
+      <c r="C37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="2">
+        <v>45724.89583333334</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37" t="s">
+        <v>87</v>
+      </c>
+      <c r="H37" t="s">
+        <v>89</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>2</v>
+      </c>
+      <c r="N37">
+        <v>2</v>
+      </c>
+      <c r="O37" t="s">
+        <v>109</v>
+      </c>
+      <c r="P37" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q37">
+        <v>3.1</v>
+      </c>
+      <c r="R37">
+        <v>2.25</v>
+      </c>
+      <c r="S37">
+        <v>3.2</v>
+      </c>
+      <c r="T37">
+        <v>1.33</v>
+      </c>
+      <c r="U37">
+        <v>3.25</v>
+      </c>
+      <c r="V37">
+        <v>2.63</v>
+      </c>
+      <c r="W37">
+        <v>1.44</v>
+      </c>
+      <c r="X37">
+        <v>6.5</v>
+      </c>
+      <c r="Y37">
+        <v>1.11</v>
+      </c>
+      <c r="Z37">
+        <v>2.53</v>
+      </c>
+      <c r="AA37">
+        <v>3.38</v>
+      </c>
+      <c r="AB37">
+        <v>2.64</v>
+      </c>
+      <c r="AC37">
+        <v>1.03</v>
+      </c>
+      <c r="AD37">
+        <v>15</v>
+      </c>
+      <c r="AE37">
+        <v>1.25</v>
+      </c>
+      <c r="AF37">
+        <v>4</v>
+      </c>
+      <c r="AG37">
+        <v>1.7</v>
+      </c>
+      <c r="AH37">
+        <v>2.05</v>
+      </c>
+      <c r="AI37">
+        <v>1.62</v>
+      </c>
+      <c r="AJ37">
+        <v>2.2</v>
+      </c>
+      <c r="AK37">
+        <v>1.46</v>
+      </c>
+      <c r="AL37">
+        <v>1.28</v>
+      </c>
+      <c r="AM37">
+        <v>1.52</v>
+      </c>
+      <c r="AN37">
+        <v>0</v>
+      </c>
+      <c r="AO37">
+        <v>3</v>
+      </c>
+      <c r="AP37">
+        <v>0</v>
+      </c>
+      <c r="AQ37">
+        <v>3</v>
+      </c>
+      <c r="AR37">
+        <v>0.85</v>
+      </c>
+      <c r="AS37">
+        <v>1.1</v>
+      </c>
+      <c r="AT37">
+        <v>1.95</v>
+      </c>
+      <c r="AU37">
+        <v>2</v>
+      </c>
+      <c r="AV37">
+        <v>10</v>
+      </c>
+      <c r="AW37">
+        <v>7</v>
+      </c>
+      <c r="AX37">
+        <v>10</v>
+      </c>
+      <c r="AY37">
+        <v>11</v>
+      </c>
+      <c r="AZ37">
+        <v>27</v>
+      </c>
+      <c r="BA37">
+        <v>4</v>
+      </c>
+      <c r="BB37">
+        <v>5</v>
+      </c>
+      <c r="BC37">
+        <v>9</v>
+      </c>
+      <c r="BD37">
+        <v>1.85</v>
+      </c>
+      <c r="BE37">
+        <v>6.4</v>
+      </c>
+      <c r="BF37">
+        <v>2.15</v>
+      </c>
+      <c r="BG37">
+        <v>1.3</v>
+      </c>
+      <c r="BH37">
+        <v>3.15</v>
+      </c>
+      <c r="BI37">
+        <v>1.5</v>
+      </c>
+      <c r="BJ37">
+        <v>2.33</v>
+      </c>
+      <c r="BK37">
+        <v>1.84</v>
+      </c>
+      <c r="BL37">
+        <v>1.84</v>
+      </c>
+      <c r="BM37">
+        <v>2.3</v>
+      </c>
+      <c r="BN37">
+        <v>1.54</v>
+      </c>
+      <c r="BO37">
+        <v>2.9</v>
+      </c>
+      <c r="BP37">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:68">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>7781111</v>
+      </c>
+      <c r="C38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45724.89583333334</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38" t="s">
+        <v>96</v>
+      </c>
+      <c r="H38" t="s">
+        <v>76</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>2</v>
+      </c>
+      <c r="M38">
+        <v>1</v>
+      </c>
+      <c r="N38">
+        <v>3</v>
+      </c>
+      <c r="O38" t="s">
+        <v>128</v>
+      </c>
+      <c r="P38" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q38">
+        <v>2.88</v>
+      </c>
+      <c r="R38">
+        <v>2.2</v>
+      </c>
+      <c r="S38">
+        <v>3.6</v>
+      </c>
+      <c r="T38">
+        <v>1.36</v>
+      </c>
+      <c r="U38">
+        <v>3</v>
+      </c>
+      <c r="V38">
+        <v>2.63</v>
+      </c>
+      <c r="W38">
+        <v>1.44</v>
+      </c>
+      <c r="X38">
+        <v>7</v>
+      </c>
+      <c r="Y38">
+        <v>1.1</v>
+      </c>
+      <c r="Z38">
+        <v>2.19</v>
+      </c>
+      <c r="AA38">
+        <v>3.12</v>
+      </c>
+      <c r="AB38">
+        <v>3.41</v>
+      </c>
+      <c r="AC38">
+        <v>1.03</v>
+      </c>
+      <c r="AD38">
+        <v>13</v>
+      </c>
+      <c r="AE38">
+        <v>1.21</v>
+      </c>
+      <c r="AF38">
+        <v>3.9</v>
+      </c>
+      <c r="AG38">
+        <v>1.67</v>
+      </c>
+      <c r="AH38">
+        <v>2.05</v>
+      </c>
+      <c r="AI38">
+        <v>1.67</v>
+      </c>
+      <c r="AJ38">
+        <v>2.1</v>
+      </c>
+      <c r="AK38">
+        <v>1.33</v>
+      </c>
+      <c r="AL38">
+        <v>1.3</v>
+      </c>
+      <c r="AM38">
+        <v>1.65</v>
+      </c>
+      <c r="AN38">
+        <v>0</v>
+      </c>
+      <c r="AO38">
+        <v>0</v>
+      </c>
+      <c r="AP38">
+        <v>3</v>
+      </c>
+      <c r="AQ38">
+        <v>0</v>
+      </c>
+      <c r="AR38">
+        <v>0</v>
+      </c>
+      <c r="AS38">
+        <v>0</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38">
+        <v>8</v>
+      </c>
+      <c r="AV38">
+        <v>5</v>
+      </c>
+      <c r="AW38">
+        <v>7</v>
+      </c>
+      <c r="AX38">
+        <v>11</v>
+      </c>
+      <c r="AY38">
+        <v>16</v>
+      </c>
+      <c r="AZ38">
+        <v>18</v>
+      </c>
+      <c r="BA38">
+        <v>7</v>
+      </c>
+      <c r="BB38">
+        <v>4</v>
+      </c>
+      <c r="BC38">
+        <v>11</v>
+      </c>
+      <c r="BD38">
+        <v>1.7</v>
+      </c>
+      <c r="BE38">
+        <v>6.4</v>
+      </c>
+      <c r="BF38">
+        <v>2.4</v>
+      </c>
+      <c r="BG38">
+        <v>1.33</v>
+      </c>
+      <c r="BH38">
+        <v>2.95</v>
+      </c>
+      <c r="BI38">
+        <v>1.56</v>
+      </c>
+      <c r="BJ38">
+        <v>2.23</v>
+      </c>
+      <c r="BK38">
+        <v>1.9</v>
+      </c>
+      <c r="BL38">
+        <v>1.78</v>
+      </c>
+      <c r="BM38">
+        <v>2.4</v>
+      </c>
+      <c r="BN38">
+        <v>1.49</v>
+      </c>
+      <c r="BO38">
+        <v>3.15</v>
+      </c>
+      <c r="BP38">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:68">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>7781112</v>
+      </c>
+      <c r="C39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="2">
+        <v>45724.9375</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39" t="s">
+        <v>77</v>
+      </c>
+      <c r="H39" t="s">
+        <v>93</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>1</v>
+      </c>
+      <c r="N39">
+        <v>1</v>
+      </c>
+      <c r="O39" t="s">
+        <v>109</v>
+      </c>
+      <c r="P39" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q39">
+        <v>2.38</v>
+      </c>
+      <c r="R39">
+        <v>2.3</v>
+      </c>
+      <c r="S39">
+        <v>4.5</v>
+      </c>
+      <c r="T39">
+        <v>1.33</v>
+      </c>
+      <c r="U39">
+        <v>3.25</v>
+      </c>
+      <c r="V39">
+        <v>2.63</v>
+      </c>
+      <c r="W39">
+        <v>1.44</v>
+      </c>
+      <c r="X39">
+        <v>6.5</v>
+      </c>
+      <c r="Y39">
+        <v>1.11</v>
+      </c>
+      <c r="Z39">
+        <v>1.75</v>
+      </c>
+      <c r="AA39">
+        <v>3.75</v>
+      </c>
+      <c r="AB39">
+        <v>4.33</v>
+      </c>
+      <c r="AC39">
+        <v>1.04</v>
+      </c>
+      <c r="AD39">
+        <v>13</v>
+      </c>
+      <c r="AE39">
+        <v>1.25</v>
+      </c>
+      <c r="AF39">
+        <v>4</v>
+      </c>
+      <c r="AG39">
+        <v>1.73</v>
+      </c>
+      <c r="AH39">
+        <v>2</v>
+      </c>
+      <c r="AI39">
+        <v>1.7</v>
+      </c>
+      <c r="AJ39">
+        <v>2.05</v>
+      </c>
+      <c r="AK39">
+        <v>1.22</v>
+      </c>
+      <c r="AL39">
+        <v>1.25</v>
+      </c>
+      <c r="AM39">
+        <v>1.98</v>
+      </c>
+      <c r="AN39">
+        <v>3</v>
+      </c>
+      <c r="AO39">
+        <v>1</v>
+      </c>
+      <c r="AP39">
+        <v>1.5</v>
+      </c>
+      <c r="AQ39">
+        <v>2</v>
+      </c>
+      <c r="AR39">
+        <v>1.5</v>
+      </c>
+      <c r="AS39">
+        <v>0.45</v>
+      </c>
+      <c r="AT39">
+        <v>1.95</v>
+      </c>
+      <c r="AU39">
+        <v>5</v>
+      </c>
+      <c r="AV39">
+        <v>4</v>
+      </c>
+      <c r="AW39">
+        <v>15</v>
+      </c>
+      <c r="AX39">
+        <v>3</v>
+      </c>
+      <c r="AY39">
+        <v>22</v>
+      </c>
+      <c r="AZ39">
+        <v>7</v>
+      </c>
+      <c r="BA39">
+        <v>7</v>
+      </c>
+      <c r="BB39">
+        <v>3</v>
+      </c>
+      <c r="BC39">
+        <v>10</v>
+      </c>
+      <c r="BD39">
+        <v>1.63</v>
+      </c>
+      <c r="BE39">
+        <v>6.4</v>
+      </c>
+      <c r="BF39">
+        <v>2.55</v>
+      </c>
+      <c r="BG39">
+        <v>1.36</v>
+      </c>
+      <c r="BH39">
+        <v>2.85</v>
+      </c>
+      <c r="BI39">
+        <v>1.61</v>
+      </c>
+      <c r="BJ39">
+        <v>2.15</v>
+      </c>
+      <c r="BK39">
+        <v>1.98</v>
+      </c>
+      <c r="BL39">
+        <v>1.72</v>
+      </c>
+      <c r="BM39">
+        <v>2.55</v>
+      </c>
+      <c r="BN39">
+        <v>1.44</v>
+      </c>
+      <c r="BO39">
+        <v>3.3</v>
+      </c>
+      <c r="BP39">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:68">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>7781113</v>
+      </c>
+      <c r="C40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="2">
+        <v>45724.9375</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40" t="s">
+        <v>97</v>
+      </c>
+      <c r="H40" t="s">
+        <v>90</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="M40">
+        <v>3</v>
+      </c>
+      <c r="N40">
+        <v>4</v>
+      </c>
+      <c r="O40" t="s">
+        <v>129</v>
+      </c>
+      <c r="P40" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q40">
+        <v>2.38</v>
+      </c>
+      <c r="R40">
+        <v>2.38</v>
+      </c>
+      <c r="S40">
+        <v>4.33</v>
+      </c>
+      <c r="T40">
+        <v>1.3</v>
+      </c>
+      <c r="U40">
+        <v>3.4</v>
+      </c>
+      <c r="V40">
+        <v>2.5</v>
+      </c>
+      <c r="W40">
+        <v>1.5</v>
+      </c>
+      <c r="X40">
+        <v>6</v>
+      </c>
+      <c r="Y40">
+        <v>1.13</v>
+      </c>
+      <c r="Z40">
+        <v>1.78</v>
+      </c>
+      <c r="AA40">
+        <v>3.95</v>
+      </c>
+      <c r="AB40">
+        <v>3.92</v>
+      </c>
+      <c r="AC40">
+        <v>1.02</v>
+      </c>
+      <c r="AD40">
+        <v>17</v>
+      </c>
+      <c r="AE40">
+        <v>1.19</v>
+      </c>
+      <c r="AF40">
+        <v>4.75</v>
+      </c>
+      <c r="AG40">
+        <v>1.57</v>
+      </c>
+      <c r="AH40">
+        <v>2.25</v>
+      </c>
+      <c r="AI40">
+        <v>1.62</v>
+      </c>
+      <c r="AJ40">
+        <v>2.2</v>
+      </c>
+      <c r="AK40">
+        <v>1.24</v>
+      </c>
+      <c r="AL40">
+        <v>1.24</v>
+      </c>
+      <c r="AM40">
+        <v>1.95</v>
+      </c>
+      <c r="AN40">
+        <v>0</v>
+      </c>
+      <c r="AO40">
+        <v>0</v>
+      </c>
+      <c r="AP40">
+        <v>0</v>
+      </c>
+      <c r="AQ40">
+        <v>1.5</v>
+      </c>
+      <c r="AR40">
+        <v>0</v>
+      </c>
+      <c r="AS40">
+        <v>1.57</v>
+      </c>
+      <c r="AT40">
+        <v>1.57</v>
+      </c>
+      <c r="AU40">
+        <v>8</v>
+      </c>
+      <c r="AV40">
+        <v>8</v>
+      </c>
+      <c r="AW40">
+        <v>9</v>
+      </c>
+      <c r="AX40">
+        <v>7</v>
+      </c>
+      <c r="AY40">
+        <v>19</v>
+      </c>
+      <c r="AZ40">
+        <v>16</v>
+      </c>
+      <c r="BA40">
+        <v>6</v>
+      </c>
+      <c r="BB40">
+        <v>2</v>
+      </c>
+      <c r="BC40">
+        <v>8</v>
+      </c>
+      <c r="BD40">
+        <v>1.56</v>
+      </c>
+      <c r="BE40">
+        <v>6.75</v>
+      </c>
+      <c r="BF40">
+        <v>2.65</v>
+      </c>
+      <c r="BG40">
+        <v>1.37</v>
+      </c>
+      <c r="BH40">
+        <v>2.8</v>
+      </c>
+      <c r="BI40">
+        <v>1.61</v>
+      </c>
+      <c r="BJ40">
+        <v>2.14</v>
+      </c>
+      <c r="BK40">
+        <v>1.98</v>
+      </c>
+      <c r="BL40">
+        <v>1.72</v>
+      </c>
+      <c r="BM40">
+        <v>2.5</v>
+      </c>
+      <c r="BN40">
+        <v>1.46</v>
+      </c>
+      <c r="BO40">
+        <v>3.3</v>
+      </c>
+      <c r="BP40">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:68">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>7781114</v>
+      </c>
+      <c r="C41" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="2">
+        <v>45724.9375</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41" t="s">
+        <v>79</v>
+      </c>
+      <c r="H41" t="s">
+        <v>83</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41">
+        <v>2</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>2</v>
+      </c>
+      <c r="O41" t="s">
+        <v>130</v>
+      </c>
+      <c r="P41" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q41">
+        <v>2.5</v>
+      </c>
+      <c r="R41">
+        <v>2.3</v>
+      </c>
+      <c r="S41">
+        <v>4</v>
+      </c>
+      <c r="T41">
+        <v>1.33</v>
+      </c>
+      <c r="U41">
+        <v>3.25</v>
+      </c>
+      <c r="V41">
+        <v>2.63</v>
+      </c>
+      <c r="W41">
+        <v>1.44</v>
+      </c>
+      <c r="X41">
+        <v>6.5</v>
+      </c>
+      <c r="Y41">
+        <v>1.11</v>
+      </c>
+      <c r="Z41">
+        <v>1.97</v>
+      </c>
+      <c r="AA41">
+        <v>3.6</v>
+      </c>
+      <c r="AB41">
+        <v>3.53</v>
+      </c>
+      <c r="AC41">
+        <v>1.03</v>
+      </c>
+      <c r="AD41">
+        <v>13</v>
+      </c>
+      <c r="AE41">
+        <v>1.26</v>
+      </c>
+      <c r="AF41">
+        <v>4</v>
+      </c>
+      <c r="AG41">
+        <v>1.77</v>
+      </c>
+      <c r="AH41">
+        <v>1.98</v>
+      </c>
+      <c r="AI41">
+        <v>1.67</v>
+      </c>
+      <c r="AJ41">
+        <v>2.1</v>
+      </c>
+      <c r="AK41">
+        <v>1.29</v>
+      </c>
+      <c r="AL41">
+        <v>1.26</v>
+      </c>
+      <c r="AM41">
+        <v>1.82</v>
+      </c>
+      <c r="AN41">
+        <v>1</v>
+      </c>
+      <c r="AO41">
+        <v>0</v>
+      </c>
+      <c r="AP41">
+        <v>2</v>
+      </c>
+      <c r="AQ41">
+        <v>0</v>
+      </c>
+      <c r="AR41">
+        <v>1.65</v>
+      </c>
+      <c r="AS41">
+        <v>0</v>
+      </c>
+      <c r="AT41">
+        <v>1.65</v>
+      </c>
+      <c r="AU41">
+        <v>8</v>
+      </c>
+      <c r="AV41">
+        <v>5</v>
+      </c>
+      <c r="AW41">
+        <v>13</v>
+      </c>
+      <c r="AX41">
+        <v>5</v>
+      </c>
+      <c r="AY41">
+        <v>26</v>
+      </c>
+      <c r="AZ41">
+        <v>12</v>
+      </c>
+      <c r="BA41">
+        <v>5</v>
+      </c>
+      <c r="BB41">
+        <v>2</v>
+      </c>
+      <c r="BC41">
+        <v>7</v>
+      </c>
+      <c r="BD41">
+        <v>1.41</v>
+      </c>
+      <c r="BE41">
+        <v>7</v>
+      </c>
+      <c r="BF41">
+        <v>3.2</v>
+      </c>
+      <c r="BG41">
+        <v>1.25</v>
+      </c>
+      <c r="BH41">
+        <v>3.45</v>
+      </c>
+      <c r="BI41">
+        <v>1.44</v>
+      </c>
+      <c r="BJ41">
+        <v>2.55</v>
+      </c>
+      <c r="BK41">
+        <v>1.72</v>
+      </c>
+      <c r="BL41">
+        <v>1.98</v>
+      </c>
+      <c r="BM41">
+        <v>2.12</v>
+      </c>
+      <c r="BN41">
+        <v>1.62</v>
+      </c>
+      <c r="BO41">
+        <v>2.65</v>
+      </c>
+      <c r="BP41">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:68">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>7781115</v>
+      </c>
+      <c r="C42" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="2">
+        <v>45724.97916666666</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42" t="s">
+        <v>86</v>
+      </c>
+      <c r="H42" t="s">
+        <v>94</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42">
+        <v>2</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42">
+        <v>3</v>
+      </c>
+      <c r="N42">
+        <v>4</v>
+      </c>
+      <c r="O42" t="s">
+        <v>131</v>
+      </c>
+      <c r="P42" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>1.98</v>
+      </c>
+      <c r="AA42">
+        <v>3.67</v>
+      </c>
+      <c r="AB42">
+        <v>3.41</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42">
+        <v>0</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>0</v>
+      </c>
+      <c r="AG42">
+        <v>1.79</v>
+      </c>
+      <c r="AH42">
+        <v>1.95</v>
+      </c>
+      <c r="AI42">
+        <v>0</v>
+      </c>
+      <c r="AJ42">
+        <v>0</v>
+      </c>
+      <c r="AK42">
+        <v>0</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>0</v>
+      </c>
+      <c r="AN42">
+        <v>3</v>
+      </c>
+      <c r="AO42">
+        <v>3</v>
+      </c>
+      <c r="AP42">
+        <v>1.5</v>
+      </c>
+      <c r="AQ42">
+        <v>3</v>
+      </c>
+      <c r="AR42">
+        <v>1.41</v>
+      </c>
+      <c r="AS42">
+        <v>1.49</v>
+      </c>
+      <c r="AT42">
+        <v>2.9</v>
+      </c>
+      <c r="AU42">
+        <v>-1</v>
+      </c>
+      <c r="AV42">
+        <v>-1</v>
+      </c>
+      <c r="AW42">
+        <v>-1</v>
+      </c>
+      <c r="AX42">
+        <v>-1</v>
+      </c>
+      <c r="AY42">
+        <v>-1</v>
+      </c>
+      <c r="AZ42">
+        <v>-1</v>
+      </c>
+      <c r="BA42">
+        <v>-1</v>
+      </c>
+      <c r="BB42">
+        <v>-1</v>
+      </c>
+      <c r="BC42">
+        <v>-1</v>
+      </c>
+      <c r="BD42">
+        <v>0</v>
+      </c>
+      <c r="BE42">
+        <v>0</v>
+      </c>
+      <c r="BF42">
+        <v>0</v>
+      </c>
+      <c r="BG42">
+        <v>0</v>
+      </c>
+      <c r="BH42">
+        <v>0</v>
+      </c>
+      <c r="BI42">
+        <v>0</v>
+      </c>
+      <c r="BJ42">
+        <v>0</v>
+      </c>
+      <c r="BK42">
+        <v>0</v>
+      </c>
+      <c r="BL42">
+        <v>0</v>
+      </c>
+      <c r="BM42">
+        <v>0</v>
+      </c>
+      <c r="BN42">
+        <v>0</v>
+      </c>
+      <c r="BO42">
+        <v>0</v>
+      </c>
+      <c r="BP42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:68">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>7781116</v>
+      </c>
+      <c r="C43" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="2">
+        <v>45724.97916666666</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43" t="s">
+        <v>95</v>
+      </c>
+      <c r="H43" t="s">
+        <v>98</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>1</v>
+      </c>
+      <c r="L43">
+        <v>2</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>2</v>
+      </c>
+      <c r="O43" t="s">
+        <v>132</v>
+      </c>
+      <c r="P43" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q43">
+        <v>1.95</v>
+      </c>
+      <c r="R43">
+        <v>2.5</v>
+      </c>
+      <c r="S43">
+        <v>6</v>
+      </c>
+      <c r="T43">
+        <v>1.29</v>
+      </c>
+      <c r="U43">
+        <v>3.5</v>
+      </c>
+      <c r="V43">
+        <v>2.38</v>
+      </c>
+      <c r="W43">
+        <v>1.53</v>
+      </c>
+      <c r="X43">
+        <v>5.5</v>
+      </c>
+      <c r="Y43">
+        <v>1.14</v>
+      </c>
+      <c r="Z43">
+        <v>1.47</v>
+      </c>
+      <c r="AA43">
+        <v>4.5</v>
+      </c>
+      <c r="AB43">
+        <v>5.9</v>
+      </c>
+      <c r="AC43">
+        <v>1.02</v>
+      </c>
+      <c r="AD43">
+        <v>19</v>
+      </c>
+      <c r="AE43">
+        <v>1.18</v>
+      </c>
+      <c r="AF43">
+        <v>5</v>
+      </c>
+      <c r="AG43">
+        <v>1.54</v>
+      </c>
+      <c r="AH43">
+        <v>2.37</v>
+      </c>
+      <c r="AI43">
+        <v>1.75</v>
+      </c>
+      <c r="AJ43">
+        <v>2</v>
+      </c>
+      <c r="AK43">
+        <v>1.12</v>
+      </c>
+      <c r="AL43">
+        <v>1.19</v>
+      </c>
+      <c r="AM43">
+        <v>2.6</v>
+      </c>
+      <c r="AN43">
+        <v>3</v>
+      </c>
+      <c r="AO43">
+        <v>0</v>
+      </c>
+      <c r="AP43">
+        <v>3</v>
+      </c>
+      <c r="AQ43">
+        <v>0</v>
+      </c>
+      <c r="AR43">
+        <v>1.87</v>
+      </c>
+      <c r="AS43">
+        <v>1.11</v>
+      </c>
+      <c r="AT43">
+        <v>2.98</v>
+      </c>
+      <c r="AU43">
+        <v>8</v>
+      </c>
+      <c r="AV43">
+        <v>4</v>
+      </c>
+      <c r="AW43">
+        <v>8</v>
+      </c>
+      <c r="AX43">
+        <v>8</v>
+      </c>
+      <c r="AY43">
+        <v>16</v>
+      </c>
+      <c r="AZ43">
+        <v>15</v>
+      </c>
+      <c r="BA43">
+        <v>8</v>
+      </c>
+      <c r="BB43">
+        <v>7</v>
+      </c>
+      <c r="BC43">
+        <v>15</v>
+      </c>
+      <c r="BD43">
+        <v>1.35</v>
+      </c>
+      <c r="BE43">
+        <v>7</v>
+      </c>
+      <c r="BF43">
+        <v>3.55</v>
+      </c>
+      <c r="BG43">
+        <v>1.3</v>
+      </c>
+      <c r="BH43">
+        <v>3.15</v>
+      </c>
+      <c r="BI43">
+        <v>1.52</v>
+      </c>
+      <c r="BJ43">
+        <v>2.33</v>
+      </c>
+      <c r="BK43">
+        <v>1.83</v>
+      </c>
+      <c r="BL43">
+        <v>1.85</v>
+      </c>
+      <c r="BM43">
+        <v>2.3</v>
+      </c>
+      <c r="BN43">
+        <v>1.54</v>
+      </c>
+      <c r="BO43">
+        <v>2.95</v>
+      </c>
+      <c r="BP43">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:68">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>7781117</v>
+      </c>
+      <c r="C44" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" s="2">
+        <v>45725.02083333334</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44" t="s">
+        <v>81</v>
+      </c>
+      <c r="H44" t="s">
+        <v>92</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44">
+        <v>1</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>1</v>
+      </c>
+      <c r="N44">
+        <v>1</v>
+      </c>
+      <c r="O44" t="s">
+        <v>109</v>
+      </c>
+      <c r="P44" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q44">
+        <v>2.88</v>
+      </c>
+      <c r="R44">
+        <v>2.3</v>
+      </c>
+      <c r="S44">
+        <v>3.25</v>
+      </c>
+      <c r="T44">
+        <v>1.33</v>
+      </c>
+      <c r="U44">
+        <v>3.25</v>
+      </c>
+      <c r="V44">
+        <v>2.5</v>
+      </c>
+      <c r="W44">
+        <v>1.5</v>
+      </c>
+      <c r="X44">
+        <v>6.5</v>
+      </c>
+      <c r="Y44">
+        <v>1.11</v>
+      </c>
+      <c r="Z44">
+        <v>2.34</v>
+      </c>
+      <c r="AA44">
+        <v>3.59</v>
+      </c>
+      <c r="AB44">
+        <v>2.75</v>
+      </c>
+      <c r="AC44">
+        <v>1.04</v>
+      </c>
+      <c r="AD44">
+        <v>12</v>
+      </c>
+      <c r="AE44">
+        <v>1.28</v>
+      </c>
+      <c r="AF44">
+        <v>3.75</v>
+      </c>
+      <c r="AG44">
+        <v>1.63</v>
+      </c>
+      <c r="AH44">
+        <v>2.15</v>
+      </c>
+      <c r="AI44">
+        <v>1.57</v>
+      </c>
+      <c r="AJ44">
+        <v>2.25</v>
+      </c>
+      <c r="AK44">
+        <v>1.42</v>
+      </c>
+      <c r="AL44">
+        <v>1.27</v>
+      </c>
+      <c r="AM44">
+        <v>1.57</v>
+      </c>
+      <c r="AN44">
+        <v>3</v>
+      </c>
+      <c r="AO44">
+        <v>0</v>
+      </c>
+      <c r="AP44">
+        <v>1.5</v>
+      </c>
+      <c r="AQ44">
+        <v>1.5</v>
+      </c>
+      <c r="AR44">
+        <v>1.88</v>
+      </c>
+      <c r="AS44">
+        <v>1.31</v>
+      </c>
+      <c r="AT44">
+        <v>3.19</v>
+      </c>
+      <c r="AU44">
+        <v>3</v>
+      </c>
+      <c r="AV44">
+        <v>7</v>
+      </c>
+      <c r="AW44">
+        <v>15</v>
+      </c>
+      <c r="AX44">
+        <v>3</v>
+      </c>
+      <c r="AY44">
+        <v>25</v>
+      </c>
+      <c r="AZ44">
+        <v>13</v>
+      </c>
+      <c r="BA44">
+        <v>10</v>
+      </c>
+      <c r="BB44">
+        <v>4</v>
+      </c>
+      <c r="BC44">
+        <v>14</v>
+      </c>
+      <c r="BD44">
+        <v>1.82</v>
+      </c>
+      <c r="BE44">
+        <v>6.75</v>
+      </c>
+      <c r="BF44">
+        <v>2.15</v>
+      </c>
+      <c r="BG44">
+        <v>1.19</v>
+      </c>
+      <c r="BH44">
+        <v>4.1</v>
+      </c>
+      <c r="BI44">
+        <v>1.33</v>
+      </c>
+      <c r="BJ44">
+        <v>2.95</v>
+      </c>
+      <c r="BK44">
+        <v>1.55</v>
+      </c>
+      <c r="BL44">
+        <v>2.28</v>
+      </c>
+      <c r="BM44">
+        <v>1.85</v>
+      </c>
+      <c r="BN44">
+        <v>1.83</v>
+      </c>
+      <c r="BO44">
+        <v>2.3</v>
+      </c>
+      <c r="BP44">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="158">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -415,6 +415,9 @@
     <t>['32', '49']</t>
   </si>
   <si>
+    <t>['46']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -482,6 +485,9 @@
   </si>
   <si>
     <t>['32']</t>
+  </si>
+  <si>
+    <t>['44', '49', '84']</t>
   </si>
 </sst>
 </file>
@@ -843,7 +849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP44"/>
+  <dimension ref="A1:BP46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1305,7 +1311,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -1383,7 +1389,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
         <v>0.5</v>
@@ -1511,7 +1517,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1923,7 +1929,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2129,7 +2135,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2335,7 +2341,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2747,7 +2753,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -3571,7 +3577,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -3652,7 +3658,7 @@
         <v>2</v>
       </c>
       <c r="AQ14">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3777,7 +3783,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -3983,7 +3989,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4601,7 +4607,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -5013,7 +5019,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -5219,7 +5225,7 @@
         <v>116</v>
       </c>
       <c r="P22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5425,7 +5431,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -5631,7 +5637,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6043,7 +6049,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6742,7 +6748,7 @@
         <v>1</v>
       </c>
       <c r="AQ29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -6867,7 +6873,7 @@
         <v>123</v>
       </c>
       <c r="P30" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7073,7 +7079,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7485,7 +7491,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -8103,7 +8109,7 @@
         <v>127</v>
       </c>
       <c r="P36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q36">
         <v>2.4</v>
@@ -8309,7 +8315,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8927,7 +8933,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9339,7 +9345,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -9751,7 +9757,7 @@
         <v>109</v>
       </c>
       <c r="P44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -9908,6 +9914,418 @@
       </c>
       <c r="BP44">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:68">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>7781118</v>
+      </c>
+      <c r="C45" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" s="2">
+        <v>45725.70833333334</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45" t="s">
+        <v>71</v>
+      </c>
+      <c r="H45" t="s">
+        <v>85</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>1</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>1</v>
+      </c>
+      <c r="O45" t="s">
+        <v>133</v>
+      </c>
+      <c r="P45" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q45">
+        <v>1.91</v>
+      </c>
+      <c r="R45">
+        <v>2.63</v>
+      </c>
+      <c r="S45">
+        <v>5.5</v>
+      </c>
+      <c r="T45">
+        <v>1.25</v>
+      </c>
+      <c r="U45">
+        <v>3.75</v>
+      </c>
+      <c r="V45">
+        <v>2.2</v>
+      </c>
+      <c r="W45">
+        <v>1.62</v>
+      </c>
+      <c r="X45">
+        <v>5</v>
+      </c>
+      <c r="Y45">
+        <v>1.17</v>
+      </c>
+      <c r="Z45">
+        <v>1.45</v>
+      </c>
+      <c r="AA45">
+        <v>4.8</v>
+      </c>
+      <c r="AB45">
+        <v>5.7</v>
+      </c>
+      <c r="AC45">
+        <v>1.01</v>
+      </c>
+      <c r="AD45">
+        <v>17</v>
+      </c>
+      <c r="AE45">
+        <v>1.14</v>
+      </c>
+      <c r="AF45">
+        <v>6</v>
+      </c>
+      <c r="AG45">
+        <v>1.45</v>
+      </c>
+      <c r="AH45">
+        <v>2.63</v>
+      </c>
+      <c r="AI45">
+        <v>1.62</v>
+      </c>
+      <c r="AJ45">
+        <v>2.2</v>
+      </c>
+      <c r="AK45">
+        <v>1.14</v>
+      </c>
+      <c r="AL45">
+        <v>1.18</v>
+      </c>
+      <c r="AM45">
+        <v>2.55</v>
+      </c>
+      <c r="AN45">
+        <v>1</v>
+      </c>
+      <c r="AO45">
+        <v>1</v>
+      </c>
+      <c r="AP45">
+        <v>2</v>
+      </c>
+      <c r="AQ45">
+        <v>0.5</v>
+      </c>
+      <c r="AR45">
+        <v>1.62</v>
+      </c>
+      <c r="AS45">
+        <v>1.03</v>
+      </c>
+      <c r="AT45">
+        <v>2.65</v>
+      </c>
+      <c r="AU45">
+        <v>3</v>
+      </c>
+      <c r="AV45">
+        <v>0</v>
+      </c>
+      <c r="AW45">
+        <v>2</v>
+      </c>
+      <c r="AX45">
+        <v>9</v>
+      </c>
+      <c r="AY45">
+        <v>7</v>
+      </c>
+      <c r="AZ45">
+        <v>9</v>
+      </c>
+      <c r="BA45">
+        <v>2</v>
+      </c>
+      <c r="BB45">
+        <v>13</v>
+      </c>
+      <c r="BC45">
+        <v>15</v>
+      </c>
+      <c r="BD45">
+        <v>1.36</v>
+      </c>
+      <c r="BE45">
+        <v>7</v>
+      </c>
+      <c r="BF45">
+        <v>3.4</v>
+      </c>
+      <c r="BG45">
+        <v>1.29</v>
+      </c>
+      <c r="BH45">
+        <v>3.2</v>
+      </c>
+      <c r="BI45">
+        <v>1.49</v>
+      </c>
+      <c r="BJ45">
+        <v>2.4</v>
+      </c>
+      <c r="BK45">
+        <v>1.8</v>
+      </c>
+      <c r="BL45">
+        <v>1.89</v>
+      </c>
+      <c r="BM45">
+        <v>2.25</v>
+      </c>
+      <c r="BN45">
+        <v>1.55</v>
+      </c>
+      <c r="BO45">
+        <v>2.9</v>
+      </c>
+      <c r="BP45">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:68">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>7781119</v>
+      </c>
+      <c r="C46" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" t="s">
+        <v>69</v>
+      </c>
+      <c r="E46" s="2">
+        <v>45725.83333333334</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46" t="s">
+        <v>84</v>
+      </c>
+      <c r="H46" t="s">
+        <v>80</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+      <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>3</v>
+      </c>
+      <c r="N46">
+        <v>3</v>
+      </c>
+      <c r="O46" t="s">
+        <v>109</v>
+      </c>
+      <c r="P46" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q46">
+        <v>2.2</v>
+      </c>
+      <c r="R46">
+        <v>2.5</v>
+      </c>
+      <c r="S46">
+        <v>4.5</v>
+      </c>
+      <c r="T46">
+        <v>1.25</v>
+      </c>
+      <c r="U46">
+        <v>3.75</v>
+      </c>
+      <c r="V46">
+        <v>2.2</v>
+      </c>
+      <c r="W46">
+        <v>1.62</v>
+      </c>
+      <c r="X46">
+        <v>5</v>
+      </c>
+      <c r="Y46">
+        <v>1.17</v>
+      </c>
+      <c r="Z46">
+        <v>1.65</v>
+      </c>
+      <c r="AA46">
+        <v>4.4</v>
+      </c>
+      <c r="AB46">
+        <v>4.2</v>
+      </c>
+      <c r="AC46">
+        <v>1.01</v>
+      </c>
+      <c r="AD46">
+        <v>19</v>
+      </c>
+      <c r="AE46">
+        <v>1.16</v>
+      </c>
+      <c r="AF46">
+        <v>5.5</v>
+      </c>
+      <c r="AG46">
+        <v>1.45</v>
+      </c>
+      <c r="AH46">
+        <v>2.63</v>
+      </c>
+      <c r="AI46">
+        <v>1.5</v>
+      </c>
+      <c r="AJ46">
+        <v>2.5</v>
+      </c>
+      <c r="AK46">
+        <v>1.2</v>
+      </c>
+      <c r="AL46">
+        <v>1.2</v>
+      </c>
+      <c r="AM46">
+        <v>2.2</v>
+      </c>
+      <c r="AN46">
+        <v>0</v>
+      </c>
+      <c r="AO46">
+        <v>1</v>
+      </c>
+      <c r="AP46">
+        <v>0</v>
+      </c>
+      <c r="AQ46">
+        <v>2</v>
+      </c>
+      <c r="AR46">
+        <v>0.92</v>
+      </c>
+      <c r="AS46">
+        <v>0.47</v>
+      </c>
+      <c r="AT46">
+        <v>1.39</v>
+      </c>
+      <c r="AU46">
+        <v>8</v>
+      </c>
+      <c r="AV46">
+        <v>6</v>
+      </c>
+      <c r="AW46">
+        <v>16</v>
+      </c>
+      <c r="AX46">
+        <v>8</v>
+      </c>
+      <c r="AY46">
+        <v>30</v>
+      </c>
+      <c r="AZ46">
+        <v>16</v>
+      </c>
+      <c r="BA46">
+        <v>9</v>
+      </c>
+      <c r="BB46">
+        <v>8</v>
+      </c>
+      <c r="BC46">
+        <v>17</v>
+      </c>
+      <c r="BD46">
+        <v>1.55</v>
+      </c>
+      <c r="BE46">
+        <v>6.75</v>
+      </c>
+      <c r="BF46">
+        <v>2.65</v>
+      </c>
+      <c r="BG46">
+        <v>1.21</v>
+      </c>
+      <c r="BH46">
+        <v>3.8</v>
+      </c>
+      <c r="BI46">
+        <v>1.37</v>
+      </c>
+      <c r="BJ46">
+        <v>2.8</v>
+      </c>
+      <c r="BK46">
+        <v>1.6</v>
+      </c>
+      <c r="BL46">
+        <v>2.17</v>
+      </c>
+      <c r="BM46">
+        <v>1.96</v>
+      </c>
+      <c r="BN46">
+        <v>1.74</v>
+      </c>
+      <c r="BO46">
+        <v>2.4</v>
+      </c>
+      <c r="BP46">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -9438,31 +9438,31 @@
         <v>2.9</v>
       </c>
       <c r="AU42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AV42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AW42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AX42">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AY42">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AZ42">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BA42">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BB42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BC42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BD42">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="162">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -310,12 +310,12 @@
     <t>FC Dallas</t>
   </si>
   <si>
+    <t>Toronto</t>
+  </si>
+  <si>
     <t>Montreal Impact</t>
   </si>
   <si>
-    <t>Toronto</t>
-  </si>
-  <si>
     <t>['78']</t>
   </si>
   <si>
@@ -418,6 +418,12 @@
     <t>['46']</t>
   </si>
   <si>
+    <t>['11']</t>
+  </si>
+  <si>
+    <t>['29', '47']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -488,6 +494,12 @@
   </si>
   <si>
     <t>['44', '49', '84']</t>
+  </si>
+  <si>
+    <t>['29', '44']</t>
+  </si>
+  <si>
+    <t>['18', '39']</t>
   </si>
 </sst>
 </file>
@@ -849,7 +861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP46"/>
+  <dimension ref="A1:BP49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1183,7 +1195,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ2">
         <v>1.5</v>
@@ -1311,7 +1323,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -1493,7 +1505,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1517,7 +1529,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1929,7 +1941,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2010,7 +2022,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2111,7 +2123,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I7">
         <v>2</v>
@@ -2135,7 +2147,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2341,7 +2353,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2753,7 +2765,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -3577,7 +3589,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -3783,7 +3795,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -3989,7 +4001,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4607,7 +4619,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -4891,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ20">
         <v>0</v>
@@ -4995,7 +5007,7 @@
         <v>76</v>
       </c>
       <c r="H21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I21">
         <v>2</v>
@@ -5019,7 +5031,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -5225,7 +5237,7 @@
         <v>116</v>
       </c>
       <c r="P22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5431,7 +5443,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -5637,7 +5649,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -5819,7 +5831,7 @@
         <v>92</v>
       </c>
       <c r="H25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -6049,7 +6061,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6333,7 +6345,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ27">
         <v>0.5</v>
@@ -6542,7 +6554,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR28">
         <v>0.72</v>
@@ -6873,7 +6885,7 @@
         <v>123</v>
       </c>
       <c r="P30" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7079,7 +7091,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7491,7 +7503,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -7879,7 +7891,7 @@
         <v>73</v>
       </c>
       <c r="H35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -8109,7 +8121,7 @@
         <v>127</v>
       </c>
       <c r="P36" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q36">
         <v>2.4</v>
@@ -8315,7 +8327,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8602,7 +8614,7 @@
         <v>3</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR38">
         <v>0</v>
@@ -8933,7 +8945,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9014,7 +9026,7 @@
         <v>0</v>
       </c>
       <c r="AQ40">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR40">
         <v>0</v>
@@ -9345,7 +9357,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -9527,7 +9539,7 @@
         <v>95</v>
       </c>
       <c r="H43" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I43">
         <v>1</v>
@@ -9757,7 +9769,7 @@
         <v>109</v>
       </c>
       <c r="P44" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10169,7 +10181,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10326,6 +10338,624 @@
       </c>
       <c r="BP46">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:68">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>7781121</v>
+      </c>
+      <c r="C47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="2">
+        <v>45731.64583333334</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47" t="s">
+        <v>98</v>
+      </c>
+      <c r="H47" t="s">
+        <v>90</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="J47">
+        <v>2</v>
+      </c>
+      <c r="K47">
+        <v>3</v>
+      </c>
+      <c r="L47">
+        <v>1</v>
+      </c>
+      <c r="M47">
+        <v>2</v>
+      </c>
+      <c r="N47">
+        <v>3</v>
+      </c>
+      <c r="O47" t="s">
+        <v>134</v>
+      </c>
+      <c r="P47" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q47">
+        <v>2.63</v>
+      </c>
+      <c r="R47">
+        <v>2.3</v>
+      </c>
+      <c r="S47">
+        <v>3.75</v>
+      </c>
+      <c r="T47">
+        <v>1.33</v>
+      </c>
+      <c r="U47">
+        <v>3.25</v>
+      </c>
+      <c r="V47">
+        <v>2.63</v>
+      </c>
+      <c r="W47">
+        <v>1.44</v>
+      </c>
+      <c r="X47">
+        <v>6.5</v>
+      </c>
+      <c r="Y47">
+        <v>1.11</v>
+      </c>
+      <c r="Z47">
+        <v>2.02</v>
+      </c>
+      <c r="AA47">
+        <v>3.67</v>
+      </c>
+      <c r="AB47">
+        <v>3.3</v>
+      </c>
+      <c r="AC47">
+        <v>1.04</v>
+      </c>
+      <c r="AD47">
+        <v>10</v>
+      </c>
+      <c r="AE47">
+        <v>1.22</v>
+      </c>
+      <c r="AF47">
+        <v>4.2</v>
+      </c>
+      <c r="AG47">
+        <v>1.65</v>
+      </c>
+      <c r="AH47">
+        <v>2.1</v>
+      </c>
+      <c r="AI47">
+        <v>1.62</v>
+      </c>
+      <c r="AJ47">
+        <v>2.2</v>
+      </c>
+      <c r="AK47">
+        <v>1.33</v>
+      </c>
+      <c r="AL47">
+        <v>1.27</v>
+      </c>
+      <c r="AM47">
+        <v>1.71</v>
+      </c>
+      <c r="AN47">
+        <v>0</v>
+      </c>
+      <c r="AO47">
+        <v>1.5</v>
+      </c>
+      <c r="AP47">
+        <v>0</v>
+      </c>
+      <c r="AQ47">
+        <v>2</v>
+      </c>
+      <c r="AR47">
+        <v>0</v>
+      </c>
+      <c r="AS47">
+        <v>1.67</v>
+      </c>
+      <c r="AT47">
+        <v>1.67</v>
+      </c>
+      <c r="AU47">
+        <v>3</v>
+      </c>
+      <c r="AV47">
+        <v>10</v>
+      </c>
+      <c r="AW47">
+        <v>2</v>
+      </c>
+      <c r="AX47">
+        <v>4</v>
+      </c>
+      <c r="AY47">
+        <v>6</v>
+      </c>
+      <c r="AZ47">
+        <v>16</v>
+      </c>
+      <c r="BA47">
+        <v>5</v>
+      </c>
+      <c r="BB47">
+        <v>3</v>
+      </c>
+      <c r="BC47">
+        <v>8</v>
+      </c>
+      <c r="BD47">
+        <v>1.53</v>
+      </c>
+      <c r="BE47">
+        <v>6.95</v>
+      </c>
+      <c r="BF47">
+        <v>3.38</v>
+      </c>
+      <c r="BG47">
+        <v>1.3</v>
+      </c>
+      <c r="BH47">
+        <v>2.97</v>
+      </c>
+      <c r="BI47">
+        <v>1.58</v>
+      </c>
+      <c r="BJ47">
+        <v>2.17</v>
+      </c>
+      <c r="BK47">
+        <v>2.05</v>
+      </c>
+      <c r="BL47">
+        <v>1.7</v>
+      </c>
+      <c r="BM47">
+        <v>2.64</v>
+      </c>
+      <c r="BN47">
+        <v>1.4</v>
+      </c>
+      <c r="BO47">
+        <v>3.58</v>
+      </c>
+      <c r="BP47">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:68">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>7781120</v>
+      </c>
+      <c r="C48" t="s">
+        <v>68</v>
+      </c>
+      <c r="D48" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" s="2">
+        <v>45731.64583333334</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48" t="s">
+        <v>88</v>
+      </c>
+      <c r="H48" t="s">
+        <v>76</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="J48">
+        <v>2</v>
+      </c>
+      <c r="K48">
+        <v>3</v>
+      </c>
+      <c r="L48">
+        <v>2</v>
+      </c>
+      <c r="M48">
+        <v>2</v>
+      </c>
+      <c r="N48">
+        <v>4</v>
+      </c>
+      <c r="O48" t="s">
+        <v>135</v>
+      </c>
+      <c r="P48" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q48">
+        <v>2.88</v>
+      </c>
+      <c r="R48">
+        <v>2.2</v>
+      </c>
+      <c r="S48">
+        <v>3.6</v>
+      </c>
+      <c r="T48">
+        <v>1.36</v>
+      </c>
+      <c r="U48">
+        <v>3</v>
+      </c>
+      <c r="V48">
+        <v>2.75</v>
+      </c>
+      <c r="W48">
+        <v>1.4</v>
+      </c>
+      <c r="X48">
+        <v>8</v>
+      </c>
+      <c r="Y48">
+        <v>1.08</v>
+      </c>
+      <c r="Z48">
+        <v>2.12</v>
+      </c>
+      <c r="AA48">
+        <v>3.29</v>
+      </c>
+      <c r="AB48">
+        <v>3.39</v>
+      </c>
+      <c r="AC48">
+        <v>1.05</v>
+      </c>
+      <c r="AD48">
+        <v>9</v>
+      </c>
+      <c r="AE48">
+        <v>1.28</v>
+      </c>
+      <c r="AF48">
+        <v>3.6</v>
+      </c>
+      <c r="AG48">
+        <v>1.8</v>
+      </c>
+      <c r="AH48">
+        <v>1.94</v>
+      </c>
+      <c r="AI48">
+        <v>1.67</v>
+      </c>
+      <c r="AJ48">
+        <v>2.1</v>
+      </c>
+      <c r="AK48">
+        <v>1.37</v>
+      </c>
+      <c r="AL48">
+        <v>1.3</v>
+      </c>
+      <c r="AM48">
+        <v>1.6</v>
+      </c>
+      <c r="AN48">
+        <v>3</v>
+      </c>
+      <c r="AO48">
+        <v>0</v>
+      </c>
+      <c r="AP48">
+        <v>2</v>
+      </c>
+      <c r="AQ48">
+        <v>0.5</v>
+      </c>
+      <c r="AR48">
+        <v>1.51</v>
+      </c>
+      <c r="AS48">
+        <v>1.63</v>
+      </c>
+      <c r="AT48">
+        <v>3.14</v>
+      </c>
+      <c r="AU48">
+        <v>5</v>
+      </c>
+      <c r="AV48">
+        <v>4</v>
+      </c>
+      <c r="AW48">
+        <v>4</v>
+      </c>
+      <c r="AX48">
+        <v>4</v>
+      </c>
+      <c r="AY48">
+        <v>9</v>
+      </c>
+      <c r="AZ48">
+        <v>9</v>
+      </c>
+      <c r="BA48">
+        <v>2</v>
+      </c>
+      <c r="BB48">
+        <v>6</v>
+      </c>
+      <c r="BC48">
+        <v>8</v>
+      </c>
+      <c r="BD48">
+        <v>1.69</v>
+      </c>
+      <c r="BE48">
+        <v>6.7</v>
+      </c>
+      <c r="BF48">
+        <v>2.84</v>
+      </c>
+      <c r="BG48">
+        <v>1.24</v>
+      </c>
+      <c r="BH48">
+        <v>3.34</v>
+      </c>
+      <c r="BI48">
+        <v>1.48</v>
+      </c>
+      <c r="BJ48">
+        <v>2.4</v>
+      </c>
+      <c r="BK48">
+        <v>1.85</v>
+      </c>
+      <c r="BL48">
+        <v>1.83</v>
+      </c>
+      <c r="BM48">
+        <v>2.38</v>
+      </c>
+      <c r="BN48">
+        <v>1.49</v>
+      </c>
+      <c r="BO48">
+        <v>3.14</v>
+      </c>
+      <c r="BP48">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:68">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>7781122</v>
+      </c>
+      <c r="C49" t="s">
+        <v>68</v>
+      </c>
+      <c r="D49" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" s="2">
+        <v>45731.69791666666</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49" t="s">
+        <v>70</v>
+      </c>
+      <c r="H49" t="s">
+        <v>77</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49">
+        <v>1</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>1</v>
+      </c>
+      <c r="N49">
+        <v>1</v>
+      </c>
+      <c r="O49" t="s">
+        <v>109</v>
+      </c>
+      <c r="P49" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q49">
+        <v>2.3</v>
+      </c>
+      <c r="R49">
+        <v>2.2</v>
+      </c>
+      <c r="S49">
+        <v>5</v>
+      </c>
+      <c r="T49">
+        <v>1.4</v>
+      </c>
+      <c r="U49">
+        <v>2.75</v>
+      </c>
+      <c r="V49">
+        <v>2.75</v>
+      </c>
+      <c r="W49">
+        <v>1.4</v>
+      </c>
+      <c r="X49">
+        <v>8</v>
+      </c>
+      <c r="Y49">
+        <v>1.08</v>
+      </c>
+      <c r="Z49">
+        <v>1.63</v>
+      </c>
+      <c r="AA49">
+        <v>3.71</v>
+      </c>
+      <c r="AB49">
+        <v>5.4</v>
+      </c>
+      <c r="AC49">
+        <v>1.05</v>
+      </c>
+      <c r="AD49">
+        <v>9</v>
+      </c>
+      <c r="AE49">
+        <v>1.28</v>
+      </c>
+      <c r="AF49">
+        <v>3.5</v>
+      </c>
+      <c r="AG49">
+        <v>1.83</v>
+      </c>
+      <c r="AH49">
+        <v>1.91</v>
+      </c>
+      <c r="AI49">
+        <v>1.8</v>
+      </c>
+      <c r="AJ49">
+        <v>1.95</v>
+      </c>
+      <c r="AK49">
+        <v>1.19</v>
+      </c>
+      <c r="AL49">
+        <v>1.26</v>
+      </c>
+      <c r="AM49">
+        <v>2.05</v>
+      </c>
+      <c r="AN49">
+        <v>3</v>
+      </c>
+      <c r="AO49">
+        <v>0</v>
+      </c>
+      <c r="AP49">
+        <v>2</v>
+      </c>
+      <c r="AQ49">
+        <v>1.5</v>
+      </c>
+      <c r="AR49">
+        <v>1.41</v>
+      </c>
+      <c r="AS49">
+        <v>1.33</v>
+      </c>
+      <c r="AT49">
+        <v>2.74</v>
+      </c>
+      <c r="AU49">
+        <v>-1</v>
+      </c>
+      <c r="AV49">
+        <v>-1</v>
+      </c>
+      <c r="AW49">
+        <v>-1</v>
+      </c>
+      <c r="AX49">
+        <v>-1</v>
+      </c>
+      <c r="AY49">
+        <v>-1</v>
+      </c>
+      <c r="AZ49">
+        <v>-1</v>
+      </c>
+      <c r="BA49">
+        <v>-1</v>
+      </c>
+      <c r="BB49">
+        <v>-1</v>
+      </c>
+      <c r="BC49">
+        <v>-1</v>
+      </c>
+      <c r="BD49">
+        <v>1.61</v>
+      </c>
+      <c r="BE49">
+        <v>6.85</v>
+      </c>
+      <c r="BF49">
+        <v>3.06</v>
+      </c>
+      <c r="BG49">
+        <v>1.19</v>
+      </c>
+      <c r="BH49">
+        <v>3.74</v>
+      </c>
+      <c r="BI49">
+        <v>1.4</v>
+      </c>
+      <c r="BJ49">
+        <v>2.64</v>
+      </c>
+      <c r="BK49">
+        <v>1.8</v>
+      </c>
+      <c r="BL49">
+        <v>1.91</v>
+      </c>
+      <c r="BM49">
+        <v>2.15</v>
+      </c>
+      <c r="BN49">
+        <v>1.59</v>
+      </c>
+      <c r="BO49">
+        <v>2.83</v>
+      </c>
+      <c r="BP49">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="174">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -424,6 +424,24 @@
     <t>['29', '47']</t>
   </si>
   <si>
+    <t>['48', '51']</t>
+  </si>
+  <si>
+    <t>['38', '68']</t>
+  </si>
+  <si>
+    <t>['68', '72', '80']</t>
+  </si>
+  <si>
+    <t>['16']</t>
+  </si>
+  <si>
+    <t>['15']</t>
+  </si>
+  <si>
+    <t>['45+1']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -500,6 +518,24 @@
   </si>
   <si>
     <t>['18', '39']</t>
+  </si>
+  <si>
+    <t>['26']</t>
+  </si>
+  <si>
+    <t>['15', '31', '46']</t>
+  </si>
+  <si>
+    <t>['54']</t>
+  </si>
+  <si>
+    <t>['1', '45+5']</t>
+  </si>
+  <si>
+    <t>['13']</t>
+  </si>
+  <si>
+    <t>['38', '71']</t>
   </si>
 </sst>
 </file>
@@ -861,7 +897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP49"/>
+  <dimension ref="A1:BP58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1198,7 +1234,7 @@
         <v>2</v>
       </c>
       <c r="AQ2">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1323,7 +1359,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -1529,7 +1565,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1610,7 +1646,7 @@
         <v>2</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1941,7 +1977,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2147,7 +2183,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2225,7 +2261,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ7">
         <v>0.33</v>
@@ -2353,7 +2389,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2765,7 +2801,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -3052,7 +3088,7 @@
         <v>2</v>
       </c>
       <c r="AQ11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3255,10 +3291,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ12">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3461,10 +3497,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
+        <v>1</v>
+      </c>
+      <c r="AQ13">
         <v>1.5</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3589,7 +3625,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -3795,7 +3831,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4001,7 +4037,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4619,7 +4655,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -4700,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="AQ19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5031,7 +5067,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -5237,7 +5273,7 @@
         <v>116</v>
       </c>
       <c r="P22" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5443,7 +5479,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -5649,7 +5685,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -5727,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ24">
         <v>3</v>
@@ -5936,7 +5972,7 @@
         <v>3</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6061,7 +6097,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6885,7 +6921,7 @@
         <v>123</v>
       </c>
       <c r="P30" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7091,7 +7127,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7503,7 +7539,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -8121,7 +8157,7 @@
         <v>127</v>
       </c>
       <c r="P36" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="Q36">
         <v>2.4</v>
@@ -8199,7 +8235,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ36">
         <v>0</v>
@@ -8327,7 +8363,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8820,7 +8856,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ39">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR39">
         <v>1.5</v>
@@ -8945,7 +8981,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9357,7 +9393,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -9644,7 +9680,7 @@
         <v>3</v>
       </c>
       <c r="AQ43">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AR43">
         <v>1.87</v>
@@ -9769,7 +9805,7 @@
         <v>109</v>
       </c>
       <c r="P44" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -9847,10 +9883,10 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ44">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR44">
         <v>1.88</v>
@@ -10181,7 +10217,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10387,7 +10423,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10593,7 +10629,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -10892,31 +10928,31 @@
         <v>2.74</v>
       </c>
       <c r="AU49">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AV49">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AW49">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AX49">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AY49">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AZ49">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BA49">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB49">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BC49">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD49">
         <v>1.61</v>
@@ -10956,6 +10992,1860 @@
       </c>
       <c r="BP49">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:68">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>7781123</v>
+      </c>
+      <c r="C50" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50" t="s">
+        <v>69</v>
+      </c>
+      <c r="E50" s="2">
+        <v>45731.85416666666</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50" t="s">
+        <v>85</v>
+      </c>
+      <c r="H50" t="s">
+        <v>73</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>2</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>2</v>
+      </c>
+      <c r="O50" t="s">
+        <v>136</v>
+      </c>
+      <c r="P50" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q50">
+        <v>2.88</v>
+      </c>
+      <c r="R50">
+        <v>2.2</v>
+      </c>
+      <c r="S50">
+        <v>3.6</v>
+      </c>
+      <c r="T50">
+        <v>1.36</v>
+      </c>
+      <c r="U50">
+        <v>3</v>
+      </c>
+      <c r="V50">
+        <v>2.75</v>
+      </c>
+      <c r="W50">
+        <v>1.4</v>
+      </c>
+      <c r="X50">
+        <v>7</v>
+      </c>
+      <c r="Y50">
+        <v>1.1</v>
+      </c>
+      <c r="Z50">
+        <v>2.23</v>
+      </c>
+      <c r="AA50">
+        <v>3.25</v>
+      </c>
+      <c r="AB50">
+        <v>3.18</v>
+      </c>
+      <c r="AC50">
+        <v>1.05</v>
+      </c>
+      <c r="AD50">
+        <v>9.5</v>
+      </c>
+      <c r="AE50">
+        <v>1.28</v>
+      </c>
+      <c r="AF50">
+        <v>3.6</v>
+      </c>
+      <c r="AG50">
+        <v>1.79</v>
+      </c>
+      <c r="AH50">
+        <v>1.95</v>
+      </c>
+      <c r="AI50">
+        <v>1.67</v>
+      </c>
+      <c r="AJ50">
+        <v>2.1</v>
+      </c>
+      <c r="AK50">
+        <v>1.36</v>
+      </c>
+      <c r="AL50">
+        <v>1.29</v>
+      </c>
+      <c r="AM50">
+        <v>1.63</v>
+      </c>
+      <c r="AN50">
+        <v>3</v>
+      </c>
+      <c r="AO50">
+        <v>0</v>
+      </c>
+      <c r="AP50">
+        <v>3</v>
+      </c>
+      <c r="AQ50">
+        <v>0</v>
+      </c>
+      <c r="AR50">
+        <v>1.3</v>
+      </c>
+      <c r="AS50">
+        <v>0.73</v>
+      </c>
+      <c r="AT50">
+        <v>2.03</v>
+      </c>
+      <c r="AU50">
+        <v>7</v>
+      </c>
+      <c r="AV50">
+        <v>9</v>
+      </c>
+      <c r="AW50">
+        <v>7</v>
+      </c>
+      <c r="AX50">
+        <v>4</v>
+      </c>
+      <c r="AY50">
+        <v>16</v>
+      </c>
+      <c r="AZ50">
+        <v>14</v>
+      </c>
+      <c r="BA50">
+        <v>3</v>
+      </c>
+      <c r="BB50">
+        <v>4</v>
+      </c>
+      <c r="BC50">
+        <v>7</v>
+      </c>
+      <c r="BD50">
+        <v>1.74</v>
+      </c>
+      <c r="BE50">
+        <v>6.7</v>
+      </c>
+      <c r="BF50">
+        <v>2.71</v>
+      </c>
+      <c r="BG50">
+        <v>1.23</v>
+      </c>
+      <c r="BH50">
+        <v>3.42</v>
+      </c>
+      <c r="BI50">
+        <v>1.46</v>
+      </c>
+      <c r="BJ50">
+        <v>2.45</v>
+      </c>
+      <c r="BK50">
+        <v>1.93</v>
+      </c>
+      <c r="BL50">
+        <v>1.77</v>
+      </c>
+      <c r="BM50">
+        <v>2.32</v>
+      </c>
+      <c r="BN50">
+        <v>1.51</v>
+      </c>
+      <c r="BO50">
+        <v>3.08</v>
+      </c>
+      <c r="BP50">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="51" spans="1:68">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>7781124</v>
+      </c>
+      <c r="C51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E51" s="2">
+        <v>45731.85416666666</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51" t="s">
+        <v>75</v>
+      </c>
+      <c r="H51" t="s">
+        <v>99</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51" t="s">
+        <v>109</v>
+      </c>
+      <c r="P51" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q51">
+        <v>2.1</v>
+      </c>
+      <c r="R51">
+        <v>2.5</v>
+      </c>
+      <c r="S51">
+        <v>5</v>
+      </c>
+      <c r="T51">
+        <v>1.29</v>
+      </c>
+      <c r="U51">
+        <v>3.5</v>
+      </c>
+      <c r="V51">
+        <v>2.25</v>
+      </c>
+      <c r="W51">
+        <v>1.57</v>
+      </c>
+      <c r="X51">
+        <v>5.5</v>
+      </c>
+      <c r="Y51">
+        <v>1.14</v>
+      </c>
+      <c r="Z51">
+        <v>1.58</v>
+      </c>
+      <c r="AA51">
+        <v>3.98</v>
+      </c>
+      <c r="AB51">
+        <v>5.4</v>
+      </c>
+      <c r="AC51">
+        <v>1.04</v>
+      </c>
+      <c r="AD51">
+        <v>10</v>
+      </c>
+      <c r="AE51">
+        <v>1.18</v>
+      </c>
+      <c r="AF51">
+        <v>4.75</v>
+      </c>
+      <c r="AG51">
+        <v>1.5</v>
+      </c>
+      <c r="AH51">
+        <v>2.4</v>
+      </c>
+      <c r="AI51">
+        <v>1.57</v>
+      </c>
+      <c r="AJ51">
+        <v>2.25</v>
+      </c>
+      <c r="AK51">
+        <v>1.18</v>
+      </c>
+      <c r="AL51">
+        <v>1.22</v>
+      </c>
+      <c r="AM51">
+        <v>2.2</v>
+      </c>
+      <c r="AN51">
+        <v>2</v>
+      </c>
+      <c r="AO51">
+        <v>0</v>
+      </c>
+      <c r="AP51">
+        <v>1.67</v>
+      </c>
+      <c r="AQ51">
+        <v>0.25</v>
+      </c>
+      <c r="AR51">
+        <v>1.36</v>
+      </c>
+      <c r="AS51">
+        <v>1.19</v>
+      </c>
+      <c r="AT51">
+        <v>2.55</v>
+      </c>
+      <c r="AU51">
+        <v>9</v>
+      </c>
+      <c r="AV51">
+        <v>2</v>
+      </c>
+      <c r="AW51">
+        <v>7</v>
+      </c>
+      <c r="AX51">
+        <v>6</v>
+      </c>
+      <c r="AY51">
+        <v>17</v>
+      </c>
+      <c r="AZ51">
+        <v>10</v>
+      </c>
+      <c r="BA51">
+        <v>5</v>
+      </c>
+      <c r="BB51">
+        <v>1</v>
+      </c>
+      <c r="BC51">
+        <v>6</v>
+      </c>
+      <c r="BD51">
+        <v>1.44</v>
+      </c>
+      <c r="BE51">
+        <v>9.4</v>
+      </c>
+      <c r="BF51">
+        <v>3.42</v>
+      </c>
+      <c r="BG51">
+        <v>1.18</v>
+      </c>
+      <c r="BH51">
+        <v>3.92</v>
+      </c>
+      <c r="BI51">
+        <v>1.36</v>
+      </c>
+      <c r="BJ51">
+        <v>2.7</v>
+      </c>
+      <c r="BK51">
+        <v>1.77</v>
+      </c>
+      <c r="BL51">
+        <v>1.95</v>
+      </c>
+      <c r="BM51">
+        <v>2.11</v>
+      </c>
+      <c r="BN51">
+        <v>1.65</v>
+      </c>
+      <c r="BO51">
+        <v>2.75</v>
+      </c>
+      <c r="BP51">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:68">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>7781125</v>
+      </c>
+      <c r="C52" t="s">
+        <v>68</v>
+      </c>
+      <c r="D52" t="s">
+        <v>69</v>
+      </c>
+      <c r="E52" s="2">
+        <v>45731.85416666666</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52" t="s">
+        <v>96</v>
+      </c>
+      <c r="H52" t="s">
+        <v>87</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+      <c r="K52">
+        <v>2</v>
+      </c>
+      <c r="L52">
+        <v>2</v>
+      </c>
+      <c r="M52">
+        <v>1</v>
+      </c>
+      <c r="N52">
+        <v>3</v>
+      </c>
+      <c r="O52" t="s">
+        <v>137</v>
+      </c>
+      <c r="P52" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q52">
+        <v>2.3</v>
+      </c>
+      <c r="R52">
+        <v>2.3</v>
+      </c>
+      <c r="S52">
+        <v>4.75</v>
+      </c>
+      <c r="T52">
+        <v>1.33</v>
+      </c>
+      <c r="U52">
+        <v>3.25</v>
+      </c>
+      <c r="V52">
+        <v>2.63</v>
+      </c>
+      <c r="W52">
+        <v>1.44</v>
+      </c>
+      <c r="X52">
+        <v>7</v>
+      </c>
+      <c r="Y52">
+        <v>1.1</v>
+      </c>
+      <c r="Z52">
+        <v>1.68</v>
+      </c>
+      <c r="AA52">
+        <v>3.65</v>
+      </c>
+      <c r="AB52">
+        <v>5</v>
+      </c>
+      <c r="AC52">
+        <v>1.04</v>
+      </c>
+      <c r="AD52">
+        <v>10</v>
+      </c>
+      <c r="AE52">
+        <v>1.25</v>
+      </c>
+      <c r="AF52">
+        <v>3.9</v>
+      </c>
+      <c r="AG52">
+        <v>1.67</v>
+      </c>
+      <c r="AH52">
+        <v>2.05</v>
+      </c>
+      <c r="AI52">
+        <v>1.8</v>
+      </c>
+      <c r="AJ52">
+        <v>1.95</v>
+      </c>
+      <c r="AK52">
+        <v>1.18</v>
+      </c>
+      <c r="AL52">
+        <v>1.25</v>
+      </c>
+      <c r="AM52">
+        <v>2.1</v>
+      </c>
+      <c r="AN52">
+        <v>3</v>
+      </c>
+      <c r="AO52">
+        <v>1</v>
+      </c>
+      <c r="AP52">
+        <v>3</v>
+      </c>
+      <c r="AQ52">
+        <v>0.5</v>
+      </c>
+      <c r="AR52">
+        <v>1.84</v>
+      </c>
+      <c r="AS52">
+        <v>0.9</v>
+      </c>
+      <c r="AT52">
+        <v>2.74</v>
+      </c>
+      <c r="AU52">
+        <v>4</v>
+      </c>
+      <c r="AV52">
+        <v>3</v>
+      </c>
+      <c r="AW52">
+        <v>6</v>
+      </c>
+      <c r="AX52">
+        <v>4</v>
+      </c>
+      <c r="AY52">
+        <v>11</v>
+      </c>
+      <c r="AZ52">
+        <v>9</v>
+      </c>
+      <c r="BA52">
+        <v>6</v>
+      </c>
+      <c r="BB52">
+        <v>4</v>
+      </c>
+      <c r="BC52">
+        <v>10</v>
+      </c>
+      <c r="BD52">
+        <v>1.4</v>
+      </c>
+      <c r="BE52">
+        <v>9.6</v>
+      </c>
+      <c r="BF52">
+        <v>3.64</v>
+      </c>
+      <c r="BG52">
+        <v>1.19</v>
+      </c>
+      <c r="BH52">
+        <v>3.8</v>
+      </c>
+      <c r="BI52">
+        <v>1.39</v>
+      </c>
+      <c r="BJ52">
+        <v>2.67</v>
+      </c>
+      <c r="BK52">
+        <v>1.77</v>
+      </c>
+      <c r="BL52">
+        <v>1.95</v>
+      </c>
+      <c r="BM52">
+        <v>2.14</v>
+      </c>
+      <c r="BN52">
+        <v>1.6</v>
+      </c>
+      <c r="BO52">
+        <v>2.78</v>
+      </c>
+      <c r="BP52">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:68">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>7781126</v>
+      </c>
+      <c r="C53" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53" s="2">
+        <v>45731.89236111111</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53" t="s">
+        <v>91</v>
+      </c>
+      <c r="H53" t="s">
+        <v>92</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>2</v>
+      </c>
+      <c r="K53">
+        <v>2</v>
+      </c>
+      <c r="L53">
+        <v>3</v>
+      </c>
+      <c r="M53">
+        <v>3</v>
+      </c>
+      <c r="N53">
+        <v>6</v>
+      </c>
+      <c r="O53" t="s">
+        <v>138</v>
+      </c>
+      <c r="P53" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0</v>
+      </c>
+      <c r="X53">
+        <v>0</v>
+      </c>
+      <c r="Y53">
+        <v>0</v>
+      </c>
+      <c r="Z53">
+        <v>2.33</v>
+      </c>
+      <c r="AA53">
+        <v>3.5</v>
+      </c>
+      <c r="AB53">
+        <v>2.82</v>
+      </c>
+      <c r="AC53">
+        <v>0</v>
+      </c>
+      <c r="AD53">
+        <v>0</v>
+      </c>
+      <c r="AE53">
+        <v>0</v>
+      </c>
+      <c r="AF53">
+        <v>0</v>
+      </c>
+      <c r="AG53">
+        <v>1.79</v>
+      </c>
+      <c r="AH53">
+        <v>1.95</v>
+      </c>
+      <c r="AI53">
+        <v>0</v>
+      </c>
+      <c r="AJ53">
+        <v>0</v>
+      </c>
+      <c r="AK53">
+        <v>0</v>
+      </c>
+      <c r="AL53">
+        <v>0</v>
+      </c>
+      <c r="AM53">
+        <v>0</v>
+      </c>
+      <c r="AN53">
+        <v>0</v>
+      </c>
+      <c r="AO53">
+        <v>1.5</v>
+      </c>
+      <c r="AP53">
+        <v>0.5</v>
+      </c>
+      <c r="AQ53">
+        <v>1.33</v>
+      </c>
+      <c r="AR53">
+        <v>1.56</v>
+      </c>
+      <c r="AS53">
+        <v>1.32</v>
+      </c>
+      <c r="AT53">
+        <v>2.88</v>
+      </c>
+      <c r="AU53">
+        <v>-1</v>
+      </c>
+      <c r="AV53">
+        <v>-1</v>
+      </c>
+      <c r="AW53">
+        <v>-1</v>
+      </c>
+      <c r="AX53">
+        <v>-1</v>
+      </c>
+      <c r="AY53">
+        <v>-1</v>
+      </c>
+      <c r="AZ53">
+        <v>-1</v>
+      </c>
+      <c r="BA53">
+        <v>-1</v>
+      </c>
+      <c r="BB53">
+        <v>-1</v>
+      </c>
+      <c r="BC53">
+        <v>-1</v>
+      </c>
+      <c r="BD53">
+        <v>0</v>
+      </c>
+      <c r="BE53">
+        <v>0</v>
+      </c>
+      <c r="BF53">
+        <v>0</v>
+      </c>
+      <c r="BG53">
+        <v>0</v>
+      </c>
+      <c r="BH53">
+        <v>0</v>
+      </c>
+      <c r="BI53">
+        <v>0</v>
+      </c>
+      <c r="BJ53">
+        <v>0</v>
+      </c>
+      <c r="BK53">
+        <v>0</v>
+      </c>
+      <c r="BL53">
+        <v>0</v>
+      </c>
+      <c r="BM53">
+        <v>0</v>
+      </c>
+      <c r="BN53">
+        <v>0</v>
+      </c>
+      <c r="BO53">
+        <v>0</v>
+      </c>
+      <c r="BP53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:68">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>7781127</v>
+      </c>
+      <c r="C54" t="s">
+        <v>68</v>
+      </c>
+      <c r="D54" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" s="2">
+        <v>45731.89583333334</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54" t="s">
+        <v>97</v>
+      </c>
+      <c r="H54" t="s">
+        <v>95</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>1</v>
+      </c>
+      <c r="N54">
+        <v>1</v>
+      </c>
+      <c r="O54" t="s">
+        <v>109</v>
+      </c>
+      <c r="P54" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q54">
+        <v>2.75</v>
+      </c>
+      <c r="R54">
+        <v>2.25</v>
+      </c>
+      <c r="S54">
+        <v>3.6</v>
+      </c>
+      <c r="T54">
+        <v>1.33</v>
+      </c>
+      <c r="U54">
+        <v>3.25</v>
+      </c>
+      <c r="V54">
+        <v>2.63</v>
+      </c>
+      <c r="W54">
+        <v>1.44</v>
+      </c>
+      <c r="X54">
+        <v>6.5</v>
+      </c>
+      <c r="Y54">
+        <v>1.11</v>
+      </c>
+      <c r="Z54">
+        <v>2.15</v>
+      </c>
+      <c r="AA54">
+        <v>3.62</v>
+      </c>
+      <c r="AB54">
+        <v>3.05</v>
+      </c>
+      <c r="AC54">
+        <v>1.04</v>
+      </c>
+      <c r="AD54">
+        <v>10</v>
+      </c>
+      <c r="AE54">
+        <v>1.22</v>
+      </c>
+      <c r="AF54">
+        <v>4.2</v>
+      </c>
+      <c r="AG54">
+        <v>1.6</v>
+      </c>
+      <c r="AH54">
+        <v>2.2</v>
+      </c>
+      <c r="AI54">
+        <v>1.62</v>
+      </c>
+      <c r="AJ54">
+        <v>2.2</v>
+      </c>
+      <c r="AK54">
+        <v>1.36</v>
+      </c>
+      <c r="AL54">
+        <v>1.27</v>
+      </c>
+      <c r="AM54">
+        <v>1.65</v>
+      </c>
+      <c r="AN54">
+        <v>0</v>
+      </c>
+      <c r="AO54">
+        <v>3</v>
+      </c>
+      <c r="AP54">
+        <v>0</v>
+      </c>
+      <c r="AQ54">
+        <v>3</v>
+      </c>
+      <c r="AR54">
+        <v>1.95</v>
+      </c>
+      <c r="AS54">
+        <v>2.45</v>
+      </c>
+      <c r="AT54">
+        <v>4.4</v>
+      </c>
+      <c r="AU54">
+        <v>0</v>
+      </c>
+      <c r="AV54">
+        <v>6</v>
+      </c>
+      <c r="AW54">
+        <v>7</v>
+      </c>
+      <c r="AX54">
+        <v>4</v>
+      </c>
+      <c r="AY54">
+        <v>8</v>
+      </c>
+      <c r="AZ54">
+        <v>12</v>
+      </c>
+      <c r="BA54">
+        <v>2</v>
+      </c>
+      <c r="BB54">
+        <v>8</v>
+      </c>
+      <c r="BC54">
+        <v>10</v>
+      </c>
+      <c r="BD54">
+        <v>1.74</v>
+      </c>
+      <c r="BE54">
+        <v>6.4</v>
+      </c>
+      <c r="BF54">
+        <v>2.32</v>
+      </c>
+      <c r="BG54">
+        <v>1.33</v>
+      </c>
+      <c r="BH54">
+        <v>2.95</v>
+      </c>
+      <c r="BI54">
+        <v>1.57</v>
+      </c>
+      <c r="BJ54">
+        <v>2.23</v>
+      </c>
+      <c r="BK54">
+        <v>1.92</v>
+      </c>
+      <c r="BL54">
+        <v>1.77</v>
+      </c>
+      <c r="BM54">
+        <v>2.43</v>
+      </c>
+      <c r="BN54">
+        <v>1.47</v>
+      </c>
+      <c r="BO54">
+        <v>3.15</v>
+      </c>
+      <c r="BP54">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="55" spans="1:68">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>7781128</v>
+      </c>
+      <c r="C55" t="s">
+        <v>68</v>
+      </c>
+      <c r="D55" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" s="2">
+        <v>45731.89583333334</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55" t="s">
+        <v>78</v>
+      </c>
+      <c r="H55" t="s">
+        <v>86</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+      <c r="J55">
+        <v>2</v>
+      </c>
+      <c r="K55">
+        <v>3</v>
+      </c>
+      <c r="L55">
+        <v>1</v>
+      </c>
+      <c r="M55">
+        <v>2</v>
+      </c>
+      <c r="N55">
+        <v>3</v>
+      </c>
+      <c r="O55" t="s">
+        <v>139</v>
+      </c>
+      <c r="P55" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q55">
+        <v>2.38</v>
+      </c>
+      <c r="R55">
+        <v>2.25</v>
+      </c>
+      <c r="S55">
+        <v>4.75</v>
+      </c>
+      <c r="T55">
+        <v>1.36</v>
+      </c>
+      <c r="U55">
+        <v>3</v>
+      </c>
+      <c r="V55">
+        <v>2.75</v>
+      </c>
+      <c r="W55">
+        <v>1.4</v>
+      </c>
+      <c r="X55">
+        <v>7</v>
+      </c>
+      <c r="Y55">
+        <v>1.1</v>
+      </c>
+      <c r="Z55">
+        <v>1.88</v>
+      </c>
+      <c r="AA55">
+        <v>3.45</v>
+      </c>
+      <c r="AB55">
+        <v>4</v>
+      </c>
+      <c r="AC55">
+        <v>1.05</v>
+      </c>
+      <c r="AD55">
+        <v>9.5</v>
+      </c>
+      <c r="AE55">
+        <v>1.25</v>
+      </c>
+      <c r="AF55">
+        <v>3.7</v>
+      </c>
+      <c r="AG55">
+        <v>1.67</v>
+      </c>
+      <c r="AH55">
+        <v>2.05</v>
+      </c>
+      <c r="AI55">
+        <v>1.8</v>
+      </c>
+      <c r="AJ55">
+        <v>1.95</v>
+      </c>
+      <c r="AK55">
+        <v>1.31</v>
+      </c>
+      <c r="AL55">
+        <v>1.3</v>
+      </c>
+      <c r="AM55">
+        <v>1.68</v>
+      </c>
+      <c r="AN55">
+        <v>0</v>
+      </c>
+      <c r="AO55">
+        <v>0</v>
+      </c>
+      <c r="AP55">
+        <v>0</v>
+      </c>
+      <c r="AQ55">
+        <v>1.5</v>
+      </c>
+      <c r="AR55">
+        <v>1.22</v>
+      </c>
+      <c r="AS55">
+        <v>2.15</v>
+      </c>
+      <c r="AT55">
+        <v>3.37</v>
+      </c>
+      <c r="AU55">
+        <v>6</v>
+      </c>
+      <c r="AV55">
+        <v>6</v>
+      </c>
+      <c r="AW55">
+        <v>9</v>
+      </c>
+      <c r="AX55">
+        <v>3</v>
+      </c>
+      <c r="AY55">
+        <v>18</v>
+      </c>
+      <c r="AZ55">
+        <v>11</v>
+      </c>
+      <c r="BA55">
+        <v>1</v>
+      </c>
+      <c r="BB55">
+        <v>1</v>
+      </c>
+      <c r="BC55">
+        <v>2</v>
+      </c>
+      <c r="BD55">
+        <v>1.53</v>
+      </c>
+      <c r="BE55">
+        <v>7</v>
+      </c>
+      <c r="BF55">
+        <v>2.7</v>
+      </c>
+      <c r="BG55">
+        <v>1.23</v>
+      </c>
+      <c r="BH55">
+        <v>3.65</v>
+      </c>
+      <c r="BI55">
+        <v>1.41</v>
+      </c>
+      <c r="BJ55">
+        <v>2.65</v>
+      </c>
+      <c r="BK55">
+        <v>1.65</v>
+      </c>
+      <c r="BL55">
+        <v>2.08</v>
+      </c>
+      <c r="BM55">
+        <v>2.02</v>
+      </c>
+      <c r="BN55">
+        <v>1.7</v>
+      </c>
+      <c r="BO55">
+        <v>2.55</v>
+      </c>
+      <c r="BP55">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="56" spans="1:68">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>7781129</v>
+      </c>
+      <c r="C56" t="s">
+        <v>68</v>
+      </c>
+      <c r="D56" t="s">
+        <v>69</v>
+      </c>
+      <c r="E56" s="2">
+        <v>45731.89583333334</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56" t="s">
+        <v>80</v>
+      </c>
+      <c r="H56" t="s">
+        <v>82</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>1</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>1</v>
+      </c>
+      <c r="O56" t="s">
+        <v>140</v>
+      </c>
+      <c r="P56" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q56">
+        <v>3.25</v>
+      </c>
+      <c r="R56">
+        <v>2.1</v>
+      </c>
+      <c r="S56">
+        <v>3.5</v>
+      </c>
+      <c r="T56">
+        <v>1.44</v>
+      </c>
+      <c r="U56">
+        <v>2.63</v>
+      </c>
+      <c r="V56">
+        <v>3.25</v>
+      </c>
+      <c r="W56">
+        <v>1.33</v>
+      </c>
+      <c r="X56">
+        <v>9</v>
+      </c>
+      <c r="Y56">
+        <v>1.07</v>
+      </c>
+      <c r="Z56">
+        <v>2.46</v>
+      </c>
+      <c r="AA56">
+        <v>3.3</v>
+      </c>
+      <c r="AB56">
+        <v>2.78</v>
+      </c>
+      <c r="AC56">
+        <v>1.06</v>
+      </c>
+      <c r="AD56">
+        <v>8.5</v>
+      </c>
+      <c r="AE56">
+        <v>1.33</v>
+      </c>
+      <c r="AF56">
+        <v>3.2</v>
+      </c>
+      <c r="AG56">
+        <v>2</v>
+      </c>
+      <c r="AH56">
+        <v>1.75</v>
+      </c>
+      <c r="AI56">
+        <v>1.8</v>
+      </c>
+      <c r="AJ56">
+        <v>1.95</v>
+      </c>
+      <c r="AK56">
+        <v>1.46</v>
+      </c>
+      <c r="AL56">
+        <v>1.32</v>
+      </c>
+      <c r="AM56">
+        <v>1.47</v>
+      </c>
+      <c r="AN56">
+        <v>1</v>
+      </c>
+      <c r="AO56">
+        <v>0</v>
+      </c>
+      <c r="AP56">
+        <v>2</v>
+      </c>
+      <c r="AQ56">
+        <v>0</v>
+      </c>
+      <c r="AR56">
+        <v>2.14</v>
+      </c>
+      <c r="AS56">
+        <v>1.39</v>
+      </c>
+      <c r="AT56">
+        <v>3.53</v>
+      </c>
+      <c r="AU56">
+        <v>6</v>
+      </c>
+      <c r="AV56">
+        <v>2</v>
+      </c>
+      <c r="AW56">
+        <v>7</v>
+      </c>
+      <c r="AX56">
+        <v>9</v>
+      </c>
+      <c r="AY56">
+        <v>17</v>
+      </c>
+      <c r="AZ56">
+        <v>14</v>
+      </c>
+      <c r="BA56">
+        <v>4</v>
+      </c>
+      <c r="BB56">
+        <v>7</v>
+      </c>
+      <c r="BC56">
+        <v>11</v>
+      </c>
+      <c r="BD56">
+        <v>1.88</v>
+      </c>
+      <c r="BE56">
+        <v>6.5</v>
+      </c>
+      <c r="BF56">
+        <v>2.1</v>
+      </c>
+      <c r="BG56">
+        <v>1.3</v>
+      </c>
+      <c r="BH56">
+        <v>3.05</v>
+      </c>
+      <c r="BI56">
+        <v>1.53</v>
+      </c>
+      <c r="BJ56">
+        <v>2.3</v>
+      </c>
+      <c r="BK56">
+        <v>1.86</v>
+      </c>
+      <c r="BL56">
+        <v>1.82</v>
+      </c>
+      <c r="BM56">
+        <v>2.33</v>
+      </c>
+      <c r="BN56">
+        <v>1.52</v>
+      </c>
+      <c r="BO56">
+        <v>3.05</v>
+      </c>
+      <c r="BP56">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="57" spans="1:68">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>7781130</v>
+      </c>
+      <c r="C57" t="s">
+        <v>68</v>
+      </c>
+      <c r="D57" t="s">
+        <v>69</v>
+      </c>
+      <c r="E57" s="2">
+        <v>45731.97916666666</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57" t="s">
+        <v>94</v>
+      </c>
+      <c r="H57" t="s">
+        <v>74</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+      <c r="K57">
+        <v>1</v>
+      </c>
+      <c r="L57">
+        <v>1</v>
+      </c>
+      <c r="M57">
+        <v>1</v>
+      </c>
+      <c r="N57">
+        <v>2</v>
+      </c>
+      <c r="O57" t="s">
+        <v>119</v>
+      </c>
+      <c r="P57" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57">
+        <v>0</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0</v>
+      </c>
+      <c r="X57">
+        <v>0</v>
+      </c>
+      <c r="Y57">
+        <v>0</v>
+      </c>
+      <c r="Z57">
+        <v>2.45</v>
+      </c>
+      <c r="AA57">
+        <v>3.5</v>
+      </c>
+      <c r="AB57">
+        <v>2.66</v>
+      </c>
+      <c r="AC57">
+        <v>0</v>
+      </c>
+      <c r="AD57">
+        <v>0</v>
+      </c>
+      <c r="AE57">
+        <v>0</v>
+      </c>
+      <c r="AF57">
+        <v>0</v>
+      </c>
+      <c r="AG57">
+        <v>1.77</v>
+      </c>
+      <c r="AH57">
+        <v>1.98</v>
+      </c>
+      <c r="AI57">
+        <v>0</v>
+      </c>
+      <c r="AJ57">
+        <v>0</v>
+      </c>
+      <c r="AK57">
+        <v>0</v>
+      </c>
+      <c r="AL57">
+        <v>0</v>
+      </c>
+      <c r="AM57">
+        <v>0</v>
+      </c>
+      <c r="AN57">
+        <v>1</v>
+      </c>
+      <c r="AO57">
+        <v>3</v>
+      </c>
+      <c r="AP57">
+        <v>1</v>
+      </c>
+      <c r="AQ57">
+        <v>2</v>
+      </c>
+      <c r="AR57">
+        <v>1.55</v>
+      </c>
+      <c r="AS57">
+        <v>0.99</v>
+      </c>
+      <c r="AT57">
+        <v>2.54</v>
+      </c>
+      <c r="AU57">
+        <v>-1</v>
+      </c>
+      <c r="AV57">
+        <v>-1</v>
+      </c>
+      <c r="AW57">
+        <v>-1</v>
+      </c>
+      <c r="AX57">
+        <v>-1</v>
+      </c>
+      <c r="AY57">
+        <v>-1</v>
+      </c>
+      <c r="AZ57">
+        <v>-1</v>
+      </c>
+      <c r="BA57">
+        <v>-1</v>
+      </c>
+      <c r="BB57">
+        <v>-1</v>
+      </c>
+      <c r="BC57">
+        <v>-1</v>
+      </c>
+      <c r="BD57">
+        <v>0</v>
+      </c>
+      <c r="BE57">
+        <v>0</v>
+      </c>
+      <c r="BF57">
+        <v>0</v>
+      </c>
+      <c r="BG57">
+        <v>0</v>
+      </c>
+      <c r="BH57">
+        <v>0</v>
+      </c>
+      <c r="BI57">
+        <v>0</v>
+      </c>
+      <c r="BJ57">
+        <v>0</v>
+      </c>
+      <c r="BK57">
+        <v>0</v>
+      </c>
+      <c r="BL57">
+        <v>0</v>
+      </c>
+      <c r="BM57">
+        <v>0</v>
+      </c>
+      <c r="BN57">
+        <v>0</v>
+      </c>
+      <c r="BO57">
+        <v>0</v>
+      </c>
+      <c r="BP57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:68">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>7781131</v>
+      </c>
+      <c r="C58" t="s">
+        <v>68</v>
+      </c>
+      <c r="D58" t="s">
+        <v>69</v>
+      </c>
+      <c r="E58" s="2">
+        <v>45731.97916666666</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58" t="s">
+        <v>81</v>
+      </c>
+      <c r="H58" t="s">
+        <v>93</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+      <c r="J58">
+        <v>1</v>
+      </c>
+      <c r="K58">
+        <v>2</v>
+      </c>
+      <c r="L58">
+        <v>1</v>
+      </c>
+      <c r="M58">
+        <v>2</v>
+      </c>
+      <c r="N58">
+        <v>3</v>
+      </c>
+      <c r="O58" t="s">
+        <v>141</v>
+      </c>
+      <c r="P58" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q58">
+        <v>2.6</v>
+      </c>
+      <c r="R58">
+        <v>2.38</v>
+      </c>
+      <c r="S58">
+        <v>3.6</v>
+      </c>
+      <c r="T58">
+        <v>1.3</v>
+      </c>
+      <c r="U58">
+        <v>3.4</v>
+      </c>
+      <c r="V58">
+        <v>2.38</v>
+      </c>
+      <c r="W58">
+        <v>1.53</v>
+      </c>
+      <c r="X58">
+        <v>6</v>
+      </c>
+      <c r="Y58">
+        <v>1.13</v>
+      </c>
+      <c r="Z58">
+        <v>2.05</v>
+      </c>
+      <c r="AA58">
+        <v>3.58</v>
+      </c>
+      <c r="AB58">
+        <v>3.3</v>
+      </c>
+      <c r="AC58">
+        <v>1.04</v>
+      </c>
+      <c r="AD58">
+        <v>10</v>
+      </c>
+      <c r="AE58">
+        <v>1.2</v>
+      </c>
+      <c r="AF58">
+        <v>4.33</v>
+      </c>
+      <c r="AG58">
+        <v>1.6</v>
+      </c>
+      <c r="AH58">
+        <v>2.2</v>
+      </c>
+      <c r="AI58">
+        <v>1.53</v>
+      </c>
+      <c r="AJ58">
+        <v>2.38</v>
+      </c>
+      <c r="AK58">
+        <v>1.33</v>
+      </c>
+      <c r="AL58">
+        <v>1.26</v>
+      </c>
+      <c r="AM58">
+        <v>1.73</v>
+      </c>
+      <c r="AN58">
+        <v>1.5</v>
+      </c>
+      <c r="AO58">
+        <v>2</v>
+      </c>
+      <c r="AP58">
+        <v>1</v>
+      </c>
+      <c r="AQ58">
+        <v>2.33</v>
+      </c>
+      <c r="AR58">
+        <v>1.87</v>
+      </c>
+      <c r="AS58">
+        <v>0.75</v>
+      </c>
+      <c r="AT58">
+        <v>2.62</v>
+      </c>
+      <c r="AU58">
+        <v>12</v>
+      </c>
+      <c r="AV58">
+        <v>5</v>
+      </c>
+      <c r="AW58">
+        <v>8</v>
+      </c>
+      <c r="AX58">
+        <v>3</v>
+      </c>
+      <c r="AY58">
+        <v>28</v>
+      </c>
+      <c r="AZ58">
+        <v>10</v>
+      </c>
+      <c r="BA58">
+        <v>10</v>
+      </c>
+      <c r="BB58">
+        <v>4</v>
+      </c>
+      <c r="BC58">
+        <v>14</v>
+      </c>
+      <c r="BD58">
+        <v>1.89</v>
+      </c>
+      <c r="BE58">
+        <v>6.6</v>
+      </c>
+      <c r="BF58">
+        <v>2.42</v>
+      </c>
+      <c r="BG58">
+        <v>1.18</v>
+      </c>
+      <c r="BH58">
+        <v>3.85</v>
+      </c>
+      <c r="BI58">
+        <v>1.37</v>
+      </c>
+      <c r="BJ58">
+        <v>2.66</v>
+      </c>
+      <c r="BK58">
+        <v>1.8</v>
+      </c>
+      <c r="BL58">
+        <v>1.91</v>
+      </c>
+      <c r="BM58">
+        <v>2.14</v>
+      </c>
+      <c r="BN58">
+        <v>1.63</v>
+      </c>
+      <c r="BO58">
+        <v>2.79</v>
+      </c>
+      <c r="BP58">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="176">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -442,6 +442,9 @@
     <t>['45+1']</t>
   </si>
   <si>
+    <t>['33']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -536,6 +539,9 @@
   </si>
   <si>
     <t>['38', '71']</t>
+  </si>
+  <si>
+    <t>['15', '44', '82']</t>
   </si>
 </sst>
 </file>
@@ -897,7 +903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP58"/>
+  <dimension ref="A1:BP59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1359,7 +1365,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -1565,7 +1571,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1977,7 +1983,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2183,7 +2189,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2389,7 +2395,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2801,7 +2807,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -3625,7 +3631,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -3831,7 +3837,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4037,7 +4043,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4655,7 +4661,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -4942,7 +4948,7 @@
         <v>2</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5067,7 +5073,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -5273,7 +5279,7 @@
         <v>116</v>
       </c>
       <c r="P22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5351,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ22">
         <v>0</v>
@@ -5479,7 +5485,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -5685,7 +5691,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6097,7 +6103,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6921,7 +6927,7 @@
         <v>123</v>
       </c>
       <c r="P30" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7127,7 +7133,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7539,7 +7545,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -8157,7 +8163,7 @@
         <v>127</v>
       </c>
       <c r="P36" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q36">
         <v>2.4</v>
@@ -8363,7 +8369,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8981,7 +8987,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9393,7 +9399,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -9805,7 +9811,7 @@
         <v>109</v>
       </c>
       <c r="P44" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10217,7 +10223,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10423,7 +10429,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10629,7 +10635,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11453,7 +11459,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11626,7 +11632,7 @@
         <v>69</v>
       </c>
       <c r="E53" s="2">
-        <v>45731.89236111111</v>
+        <v>45731.88541666666</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -11659,34 +11665,34 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z53">
         <v>2.33</v>
@@ -11698,16 +11704,16 @@
         <v>2.82</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AG53">
         <v>1.79</v>
@@ -11716,19 +11722,19 @@
         <v>1.95</v>
       </c>
       <c r="AI53">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL53">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AM53">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AN53">
         <v>0</v>
@@ -11752,22 +11758,22 @@
         <v>2.88</v>
       </c>
       <c r="AU53">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AV53">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AW53">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AX53">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AY53">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AZ53">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="BA53">
         <v>-1</v>
@@ -11779,43 +11785,43 @@
         <v>-1</v>
       </c>
       <c r="BD53">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BE53">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="BF53">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BG53">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BH53">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BI53">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BJ53">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BK53">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BL53">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BM53">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BN53">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BO53">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BP53">
-        <v>0</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="54" spans="1:68">
@@ -11865,7 +11871,7 @@
         <v>109</v>
       </c>
       <c r="P54" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12071,7 +12077,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -12483,7 +12489,7 @@
         <v>119</v>
       </c>
       <c r="P57" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -12689,7 +12695,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -12846,6 +12852,212 @@
       </c>
       <c r="BP58">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:68">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>7781132</v>
+      </c>
+      <c r="C59" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" s="2">
+        <v>45732.64236111111</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59" t="s">
+        <v>89</v>
+      </c>
+      <c r="H59" t="s">
+        <v>79</v>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+      <c r="J59">
+        <v>2</v>
+      </c>
+      <c r="K59">
+        <v>3</v>
+      </c>
+      <c r="L59">
+        <v>1</v>
+      </c>
+      <c r="M59">
+        <v>3</v>
+      </c>
+      <c r="N59">
+        <v>4</v>
+      </c>
+      <c r="O59" t="s">
+        <v>142</v>
+      </c>
+      <c r="P59" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q59">
+        <v>2.38</v>
+      </c>
+      <c r="R59">
+        <v>2.3</v>
+      </c>
+      <c r="S59">
+        <v>4.33</v>
+      </c>
+      <c r="T59">
+        <v>1.33</v>
+      </c>
+      <c r="U59">
+        <v>3.25</v>
+      </c>
+      <c r="V59">
+        <v>2.5</v>
+      </c>
+      <c r="W59">
+        <v>1.5</v>
+      </c>
+      <c r="X59">
+        <v>6.5</v>
+      </c>
+      <c r="Y59">
+        <v>1.11</v>
+      </c>
+      <c r="Z59">
+        <v>1.78</v>
+      </c>
+      <c r="AA59">
+        <v>3.84</v>
+      </c>
+      <c r="AB59">
+        <v>4</v>
+      </c>
+      <c r="AC59">
+        <v>1.04</v>
+      </c>
+      <c r="AD59">
+        <v>10</v>
+      </c>
+      <c r="AE59">
+        <v>1.22</v>
+      </c>
+      <c r="AF59">
+        <v>4.2</v>
+      </c>
+      <c r="AG59">
+        <v>1.68</v>
+      </c>
+      <c r="AH59">
+        <v>2.11</v>
+      </c>
+      <c r="AI59">
+        <v>1.67</v>
+      </c>
+      <c r="AJ59">
+        <v>2.1</v>
+      </c>
+      <c r="AK59">
+        <v>1.27</v>
+      </c>
+      <c r="AL59">
+        <v>1.26</v>
+      </c>
+      <c r="AM59">
+        <v>1.85</v>
+      </c>
+      <c r="AN59">
+        <v>3</v>
+      </c>
+      <c r="AO59">
+        <v>0</v>
+      </c>
+      <c r="AP59">
+        <v>1.5</v>
+      </c>
+      <c r="AQ59">
+        <v>1.5</v>
+      </c>
+      <c r="AR59">
+        <v>1.65</v>
+      </c>
+      <c r="AS59">
+        <v>1.11</v>
+      </c>
+      <c r="AT59">
+        <v>2.76</v>
+      </c>
+      <c r="AU59">
+        <v>5</v>
+      </c>
+      <c r="AV59">
+        <v>5</v>
+      </c>
+      <c r="AW59">
+        <v>2</v>
+      </c>
+      <c r="AX59">
+        <v>6</v>
+      </c>
+      <c r="AY59">
+        <v>7</v>
+      </c>
+      <c r="AZ59">
+        <v>12</v>
+      </c>
+      <c r="BA59">
+        <v>7</v>
+      </c>
+      <c r="BB59">
+        <v>2</v>
+      </c>
+      <c r="BC59">
+        <v>9</v>
+      </c>
+      <c r="BD59">
+        <v>1.57</v>
+      </c>
+      <c r="BE59">
+        <v>6.95</v>
+      </c>
+      <c r="BF59">
+        <v>3.2</v>
+      </c>
+      <c r="BG59">
+        <v>1.21</v>
+      </c>
+      <c r="BH59">
+        <v>3.58</v>
+      </c>
+      <c r="BI59">
+        <v>1.42</v>
+      </c>
+      <c r="BJ59">
+        <v>2.57</v>
+      </c>
+      <c r="BK59">
+        <v>1.85</v>
+      </c>
+      <c r="BL59">
+        <v>1.85</v>
+      </c>
+      <c r="BM59">
+        <v>2.21</v>
+      </c>
+      <c r="BN59">
+        <v>1.56</v>
+      </c>
+      <c r="BO59">
+        <v>2.92</v>
+      </c>
+      <c r="BP59">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="179">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -445,6 +445,9 @@
     <t>['33']</t>
   </si>
   <si>
+    <t>['49']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -542,6 +545,12 @@
   </si>
   <si>
     <t>['15', '44', '82']</t>
+  </si>
+  <si>
+    <t>['81']</t>
+  </si>
+  <si>
+    <t>['20', '89']</t>
   </si>
 </sst>
 </file>
@@ -903,7 +912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP59"/>
+  <dimension ref="A1:BP61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1365,7 +1374,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -1571,7 +1580,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1649,7 +1658,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4">
         <v>0.25</v>
@@ -1983,7 +1992,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2189,7 +2198,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2395,7 +2404,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2807,7 +2816,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -3631,7 +3640,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -3837,7 +3846,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -3915,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ15">
         <v>3</v>
@@ -4043,7 +4052,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4661,7 +4670,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -5073,7 +5082,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -5279,7 +5288,7 @@
         <v>116</v>
       </c>
       <c r="P22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5485,7 +5494,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -5691,7 +5700,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6103,7 +6112,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6593,7 +6602,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ28">
         <v>1.5</v>
@@ -6927,7 +6936,7 @@
         <v>123</v>
       </c>
       <c r="P30" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7008,7 +7017,7 @@
         <v>3</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR30">
         <v>0</v>
@@ -7133,7 +7142,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7545,7 +7554,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -7829,7 +7838,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ34">
         <v>0.5</v>
@@ -8163,7 +8172,7 @@
         <v>127</v>
       </c>
       <c r="P36" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q36">
         <v>2.4</v>
@@ -8369,7 +8378,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8987,7 +8996,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9399,7 +9408,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -9811,7 +9820,7 @@
         <v>109</v>
       </c>
       <c r="P44" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10223,7 +10232,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10429,7 +10438,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10635,7 +10644,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11158,13 +11167,13 @@
         <v>14</v>
       </c>
       <c r="BA50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB50">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BC50">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BD50">
         <v>1.74</v>
@@ -11364,13 +11373,13 @@
         <v>10</v>
       </c>
       <c r="BA51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC51">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD51">
         <v>1.44</v>
@@ -11459,7 +11468,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11570,13 +11579,13 @@
         <v>9</v>
       </c>
       <c r="BA52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB52">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BC52">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BD52">
         <v>1.4</v>
@@ -11665,7 +11674,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -11871,7 +11880,7 @@
         <v>109</v>
       </c>
       <c r="P54" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12077,7 +12086,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -12489,7 +12498,7 @@
         <v>119</v>
       </c>
       <c r="P57" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -12695,7 +12704,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -12901,7 +12910,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13058,6 +13067,418 @@
       </c>
       <c r="BP59">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:68">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>7781133</v>
+      </c>
+      <c r="C60" t="s">
+        <v>68</v>
+      </c>
+      <c r="D60" t="s">
+        <v>69</v>
+      </c>
+      <c r="E60" s="2">
+        <v>45732.73958333334</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60" t="s">
+        <v>83</v>
+      </c>
+      <c r="H60" t="s">
+        <v>84</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>1</v>
+      </c>
+      <c r="M60">
+        <v>1</v>
+      </c>
+      <c r="N60">
+        <v>2</v>
+      </c>
+      <c r="O60" t="s">
+        <v>143</v>
+      </c>
+      <c r="P60" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q60">
+        <v>2.88</v>
+      </c>
+      <c r="R60">
+        <v>2.38</v>
+      </c>
+      <c r="S60">
+        <v>3.25</v>
+      </c>
+      <c r="T60">
+        <v>1.3</v>
+      </c>
+      <c r="U60">
+        <v>3.4</v>
+      </c>
+      <c r="V60">
+        <v>2.38</v>
+      </c>
+      <c r="W60">
+        <v>1.53</v>
+      </c>
+      <c r="X60">
+        <v>6</v>
+      </c>
+      <c r="Y60">
+        <v>1.13</v>
+      </c>
+      <c r="Z60">
+        <v>2.27</v>
+      </c>
+      <c r="AA60">
+        <v>3.52</v>
+      </c>
+      <c r="AB60">
+        <v>2.9</v>
+      </c>
+      <c r="AC60">
+        <v>1.04</v>
+      </c>
+      <c r="AD60">
+        <v>10</v>
+      </c>
+      <c r="AE60">
+        <v>1.2</v>
+      </c>
+      <c r="AF60">
+        <v>4.33</v>
+      </c>
+      <c r="AG60">
+        <v>1.55</v>
+      </c>
+      <c r="AH60">
+        <v>2.3</v>
+      </c>
+      <c r="AI60">
+        <v>1.5</v>
+      </c>
+      <c r="AJ60">
+        <v>2.5</v>
+      </c>
+      <c r="AK60">
+        <v>1.38</v>
+      </c>
+      <c r="AL60">
+        <v>1.27</v>
+      </c>
+      <c r="AM60">
+        <v>1.62</v>
+      </c>
+      <c r="AN60">
+        <v>1.5</v>
+      </c>
+      <c r="AO60">
+        <v>0</v>
+      </c>
+      <c r="AP60">
+        <v>1.33</v>
+      </c>
+      <c r="AQ60">
+        <v>0.5</v>
+      </c>
+      <c r="AR60">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AS60">
+        <v>0.73</v>
+      </c>
+      <c r="AT60">
+        <v>1.67</v>
+      </c>
+      <c r="AU60">
+        <v>5</v>
+      </c>
+      <c r="AV60">
+        <v>4</v>
+      </c>
+      <c r="AW60">
+        <v>3</v>
+      </c>
+      <c r="AX60">
+        <v>7</v>
+      </c>
+      <c r="AY60">
+        <v>9</v>
+      </c>
+      <c r="AZ60">
+        <v>12</v>
+      </c>
+      <c r="BA60">
+        <v>5</v>
+      </c>
+      <c r="BB60">
+        <v>8</v>
+      </c>
+      <c r="BC60">
+        <v>13</v>
+      </c>
+      <c r="BD60">
+        <v>1.73</v>
+      </c>
+      <c r="BE60">
+        <v>6.75</v>
+      </c>
+      <c r="BF60">
+        <v>2.73</v>
+      </c>
+      <c r="BG60">
+        <v>1.19</v>
+      </c>
+      <c r="BH60">
+        <v>3.82</v>
+      </c>
+      <c r="BI60">
+        <v>1.39</v>
+      </c>
+      <c r="BJ60">
+        <v>2.67</v>
+      </c>
+      <c r="BK60">
+        <v>1.75</v>
+      </c>
+      <c r="BL60">
+        <v>1.95</v>
+      </c>
+      <c r="BM60">
+        <v>2.14</v>
+      </c>
+      <c r="BN60">
+        <v>1.6</v>
+      </c>
+      <c r="BO60">
+        <v>2.78</v>
+      </c>
+      <c r="BP60">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="61" spans="1:68">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>7781134</v>
+      </c>
+      <c r="C61" t="s">
+        <v>68</v>
+      </c>
+      <c r="D61" t="s">
+        <v>69</v>
+      </c>
+      <c r="E61" s="2">
+        <v>45732.83333333334</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61" t="s">
+        <v>72</v>
+      </c>
+      <c r="H61" t="s">
+        <v>71</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+      <c r="J61">
+        <v>1</v>
+      </c>
+      <c r="K61">
+        <v>2</v>
+      </c>
+      <c r="L61">
+        <v>1</v>
+      </c>
+      <c r="M61">
+        <v>2</v>
+      </c>
+      <c r="N61">
+        <v>3</v>
+      </c>
+      <c r="O61" t="s">
+        <v>134</v>
+      </c>
+      <c r="P61" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q61">
+        <v>2.88</v>
+      </c>
+      <c r="R61">
+        <v>2.4</v>
+      </c>
+      <c r="S61">
+        <v>3.1</v>
+      </c>
+      <c r="T61">
+        <v>1.25</v>
+      </c>
+      <c r="U61">
+        <v>3.75</v>
+      </c>
+      <c r="V61">
+        <v>2.25</v>
+      </c>
+      <c r="W61">
+        <v>1.57</v>
+      </c>
+      <c r="X61">
+        <v>5.5</v>
+      </c>
+      <c r="Y61">
+        <v>1.14</v>
+      </c>
+      <c r="Z61">
+        <v>2.44</v>
+      </c>
+      <c r="AA61">
+        <v>3.51</v>
+      </c>
+      <c r="AB61">
+        <v>2.66</v>
+      </c>
+      <c r="AC61">
+        <v>1.02</v>
+      </c>
+      <c r="AD61">
+        <v>10</v>
+      </c>
+      <c r="AE61">
+        <v>1.17</v>
+      </c>
+      <c r="AF61">
+        <v>5</v>
+      </c>
+      <c r="AG61">
+        <v>1.53</v>
+      </c>
+      <c r="AH61">
+        <v>2.33</v>
+      </c>
+      <c r="AI61">
+        <v>1.44</v>
+      </c>
+      <c r="AJ61">
+        <v>2.63</v>
+      </c>
+      <c r="AK61">
+        <v>1.44</v>
+      </c>
+      <c r="AL61">
+        <v>1.26</v>
+      </c>
+      <c r="AM61">
+        <v>1.57</v>
+      </c>
+      <c r="AN61">
+        <v>2</v>
+      </c>
+      <c r="AO61">
+        <v>3</v>
+      </c>
+      <c r="AP61">
+        <v>1.33</v>
+      </c>
+      <c r="AQ61">
+        <v>3</v>
+      </c>
+      <c r="AR61">
+        <v>1.66</v>
+      </c>
+      <c r="AS61">
+        <v>1.28</v>
+      </c>
+      <c r="AT61">
+        <v>2.94</v>
+      </c>
+      <c r="AU61">
+        <v>6</v>
+      </c>
+      <c r="AV61">
+        <v>9</v>
+      </c>
+      <c r="AW61">
+        <v>7</v>
+      </c>
+      <c r="AX61">
+        <v>5</v>
+      </c>
+      <c r="AY61">
+        <v>14</v>
+      </c>
+      <c r="AZ61">
+        <v>15</v>
+      </c>
+      <c r="BA61">
+        <v>3</v>
+      </c>
+      <c r="BB61">
+        <v>7</v>
+      </c>
+      <c r="BC61">
+        <v>10</v>
+      </c>
+      <c r="BD61">
+        <v>1.69</v>
+      </c>
+      <c r="BE61">
+        <v>6.8</v>
+      </c>
+      <c r="BF61">
+        <v>2.82</v>
+      </c>
+      <c r="BG61">
+        <v>1.19</v>
+      </c>
+      <c r="BH61">
+        <v>3.8</v>
+      </c>
+      <c r="BI61">
+        <v>1.39</v>
+      </c>
+      <c r="BJ61">
+        <v>2.67</v>
+      </c>
+      <c r="BK61">
+        <v>1.8</v>
+      </c>
+      <c r="BL61">
+        <v>1.91</v>
+      </c>
+      <c r="BM61">
+        <v>2.14</v>
+      </c>
+      <c r="BN61">
+        <v>1.6</v>
+      </c>
+      <c r="BO61">
+        <v>2.81</v>
+      </c>
+      <c r="BP61">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -11785,13 +11785,13 @@
         <v>18</v>
       </c>
       <c r="BA53">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BB53">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC53">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD53">
         <v>1.72</v>
@@ -12197,13 +12197,13 @@
         <v>11</v>
       </c>
       <c r="BA55">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="BB55">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BC55">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="BD55">
         <v>1.53</v>
@@ -12591,31 +12591,31 @@
         <v>2.54</v>
       </c>
       <c r="AU57">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AV57">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW57">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AX57">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AY57">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AZ57">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BA57">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BB57">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BC57">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="BD57">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="195">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -448,6 +448,30 @@
     <t>['49']</t>
   </si>
   <si>
+    <t>['70', '75']</t>
+  </si>
+  <si>
+    <t>['18', '87']</t>
+  </si>
+  <si>
+    <t>['11', '36', '40', '52']</t>
+  </si>
+  <si>
+    <t>['44', '76']</t>
+  </si>
+  <si>
+    <t>['21', '44', '50', '56']</t>
+  </si>
+  <si>
+    <t>['8']</t>
+  </si>
+  <si>
+    <t>['56', '62', '67']</t>
+  </si>
+  <si>
+    <t>['14']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -551,6 +575,30 @@
   </si>
   <si>
     <t>['20', '89']</t>
+  </si>
+  <si>
+    <t>['50', '88']</t>
+  </si>
+  <si>
+    <t>['26', '90']</t>
+  </si>
+  <si>
+    <t>['77']</t>
+  </si>
+  <si>
+    <t>['90+1']</t>
+  </si>
+  <si>
+    <t>['18', '54']</t>
+  </si>
+  <si>
+    <t>['45+1', '48', '75']</t>
+  </si>
+  <si>
+    <t>['45+7']</t>
+  </si>
+  <si>
+    <t>['1', '62', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -912,7 +960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP61"/>
+  <dimension ref="A1:BP74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1374,7 +1422,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -1455,7 +1503,7 @@
         <v>2</v>
       </c>
       <c r="AQ3">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1580,7 +1628,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1661,7 +1709,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ4">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1864,7 +1912,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ5">
         <v>0.5</v>
@@ -1992,7 +2040,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2070,10 +2118,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ6">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2198,7 +2246,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2279,7 +2327,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ7">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2404,7 +2452,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2482,7 +2530,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ8">
         <v>3</v>
@@ -2816,7 +2864,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -2897,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="AQ10">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3100,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ11">
         <v>0.5</v>
@@ -3640,7 +3688,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -3718,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ14">
         <v>0.5</v>
@@ -3846,7 +3894,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4052,7 +4100,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4339,7 +4387,7 @@
         <v>3</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4542,7 +4590,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ18">
         <v>0</v>
@@ -4670,7 +4718,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -4954,7 +5002,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ20">
         <v>1.5</v>
@@ -5082,7 +5130,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -5160,10 +5208,10 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ21">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR21">
         <v>2.07</v>
@@ -5288,7 +5336,7 @@
         <v>116</v>
       </c>
       <c r="P22" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5366,7 +5414,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ22">
         <v>0</v>
@@ -5494,7 +5542,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -5575,7 +5623,7 @@
         <v>1</v>
       </c>
       <c r="AQ23">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -5700,7 +5748,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -5778,10 +5826,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ24">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -5984,10 +6032,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ25">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6112,7 +6160,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6190,10 +6238,10 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AQ26">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR26">
         <v>0</v>
@@ -6399,7 +6447,7 @@
         <v>2</v>
       </c>
       <c r="AQ27">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR27">
         <v>1.64</v>
@@ -6811,7 +6859,7 @@
         <v>1</v>
       </c>
       <c r="AQ29">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -6936,7 +6984,7 @@
         <v>123</v>
       </c>
       <c r="P30" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7014,10 +7062,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR30">
         <v>0</v>
@@ -7142,7 +7190,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7426,7 +7474,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -7554,7 +7602,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -7632,10 +7680,10 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR33">
         <v>2.47</v>
@@ -8044,10 +8092,10 @@
         <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AQ35">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR35">
         <v>1.23</v>
@@ -8172,7 +8220,7 @@
         <v>127</v>
       </c>
       <c r="P36" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="Q36">
         <v>2.4</v>
@@ -8378,7 +8426,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8996,7 +9044,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9077,7 +9125,7 @@
         <v>0</v>
       </c>
       <c r="AQ40">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR40">
         <v>0</v>
@@ -9280,10 +9328,10 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR41">
         <v>1.65</v>
@@ -9408,7 +9456,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -9486,7 +9534,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ42">
         <v>3</v>
@@ -9692,10 +9740,10 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ43">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR43">
         <v>1.87</v>
@@ -9820,7 +9868,7 @@
         <v>109</v>
       </c>
       <c r="P44" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10232,7 +10280,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10313,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="AQ46">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR46">
         <v>0.92</v>
@@ -10438,7 +10486,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10519,7 +10567,7 @@
         <v>0</v>
       </c>
       <c r="AQ47">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR47">
         <v>0</v>
@@ -10644,7 +10692,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -10722,7 +10770,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ48">
         <v>0.5</v>
@@ -11343,7 +11391,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ51">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AR51">
         <v>1.36</v>
@@ -11468,7 +11516,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11674,7 +11722,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -11752,7 +11800,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ53">
         <v>1.33</v>
@@ -11880,7 +11928,7 @@
         <v>109</v>
       </c>
       <c r="P54" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12086,7 +12134,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -12498,7 +12546,7 @@
         <v>119</v>
       </c>
       <c r="P57" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -12704,7 +12752,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -12910,7 +12958,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -12988,7 +13036,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ59">
         <v>1.5</v>
@@ -13116,7 +13164,7 @@
         <v>143</v>
       </c>
       <c r="P60" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13197,7 +13245,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ60">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR60">
         <v>0.9399999999999999</v>
@@ -13322,7 +13370,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -13479,6 +13527,2684 @@
       </c>
       <c r="BP61">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="62" spans="1:68">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>7781135</v>
+      </c>
+      <c r="C62" t="s">
+        <v>68</v>
+      </c>
+      <c r="D62" t="s">
+        <v>69</v>
+      </c>
+      <c r="E62" s="2">
+        <v>45738.64583333334</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62" t="s">
+        <v>73</v>
+      </c>
+      <c r="H62" t="s">
+        <v>72</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>2</v>
+      </c>
+      <c r="M62">
+        <v>2</v>
+      </c>
+      <c r="N62">
+        <v>4</v>
+      </c>
+      <c r="O62" t="s">
+        <v>144</v>
+      </c>
+      <c r="P62" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q62">
+        <v>2.38</v>
+      </c>
+      <c r="R62">
+        <v>2.38</v>
+      </c>
+      <c r="S62">
+        <v>4.33</v>
+      </c>
+      <c r="T62">
+        <v>1.3</v>
+      </c>
+      <c r="U62">
+        <v>3.4</v>
+      </c>
+      <c r="V62">
+        <v>2.5</v>
+      </c>
+      <c r="W62">
+        <v>1.5</v>
+      </c>
+      <c r="X62">
+        <v>6</v>
+      </c>
+      <c r="Y62">
+        <v>1.13</v>
+      </c>
+      <c r="Z62">
+        <v>1.8</v>
+      </c>
+      <c r="AA62">
+        <v>3.72</v>
+      </c>
+      <c r="AB62">
+        <v>4.1</v>
+      </c>
+      <c r="AC62">
+        <v>1.04</v>
+      </c>
+      <c r="AD62">
+        <v>10</v>
+      </c>
+      <c r="AE62">
+        <v>1.2</v>
+      </c>
+      <c r="AF62">
+        <v>4.33</v>
+      </c>
+      <c r="AG62">
+        <v>1.65</v>
+      </c>
+      <c r="AH62">
+        <v>2.1</v>
+      </c>
+      <c r="AI62">
+        <v>1.57</v>
+      </c>
+      <c r="AJ62">
+        <v>2.25</v>
+      </c>
+      <c r="AK62">
+        <v>1.24</v>
+      </c>
+      <c r="AL62">
+        <v>1.25</v>
+      </c>
+      <c r="AM62">
+        <v>1.95</v>
+      </c>
+      <c r="AN62">
+        <v>3</v>
+      </c>
+      <c r="AO62">
+        <v>0</v>
+      </c>
+      <c r="AP62">
+        <v>2.33</v>
+      </c>
+      <c r="AQ62">
+        <v>0.5</v>
+      </c>
+      <c r="AR62">
+        <v>1.6</v>
+      </c>
+      <c r="AS62">
+        <v>1.68</v>
+      </c>
+      <c r="AT62">
+        <v>3.28</v>
+      </c>
+      <c r="AU62">
+        <v>8</v>
+      </c>
+      <c r="AV62">
+        <v>4</v>
+      </c>
+      <c r="AW62">
+        <v>9</v>
+      </c>
+      <c r="AX62">
+        <v>7</v>
+      </c>
+      <c r="AY62">
+        <v>20</v>
+      </c>
+      <c r="AZ62">
+        <v>14</v>
+      </c>
+      <c r="BA62">
+        <v>2</v>
+      </c>
+      <c r="BB62">
+        <v>2</v>
+      </c>
+      <c r="BC62">
+        <v>4</v>
+      </c>
+      <c r="BD62">
+        <v>1.5</v>
+      </c>
+      <c r="BE62">
+        <v>6.75</v>
+      </c>
+      <c r="BF62">
+        <v>2.8</v>
+      </c>
+      <c r="BG62">
+        <v>1.26</v>
+      </c>
+      <c r="BH62">
+        <v>3.4</v>
+      </c>
+      <c r="BI62">
+        <v>1.46</v>
+      </c>
+      <c r="BJ62">
+        <v>2.5</v>
+      </c>
+      <c r="BK62">
+        <v>1.72</v>
+      </c>
+      <c r="BL62">
+        <v>1.97</v>
+      </c>
+      <c r="BM62">
+        <v>2.14</v>
+      </c>
+      <c r="BN62">
+        <v>1.62</v>
+      </c>
+      <c r="BO62">
+        <v>2.7</v>
+      </c>
+      <c r="BP62">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:68">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>7781136</v>
+      </c>
+      <c r="C63" t="s">
+        <v>68</v>
+      </c>
+      <c r="D63" t="s">
+        <v>69</v>
+      </c>
+      <c r="E63" s="2">
+        <v>45738.72916666666</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63" t="s">
+        <v>92</v>
+      </c>
+      <c r="H63" t="s">
+        <v>84</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+      <c r="J63">
+        <v>1</v>
+      </c>
+      <c r="K63">
+        <v>2</v>
+      </c>
+      <c r="L63">
+        <v>2</v>
+      </c>
+      <c r="M63">
+        <v>2</v>
+      </c>
+      <c r="N63">
+        <v>4</v>
+      </c>
+      <c r="O63" t="s">
+        <v>145</v>
+      </c>
+      <c r="P63" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q63">
+        <v>2.5</v>
+      </c>
+      <c r="R63">
+        <v>2.3</v>
+      </c>
+      <c r="S63">
+        <v>4</v>
+      </c>
+      <c r="T63">
+        <v>1.33</v>
+      </c>
+      <c r="U63">
+        <v>3.25</v>
+      </c>
+      <c r="V63">
+        <v>2.63</v>
+      </c>
+      <c r="W63">
+        <v>1.44</v>
+      </c>
+      <c r="X63">
+        <v>6.5</v>
+      </c>
+      <c r="Y63">
+        <v>1.11</v>
+      </c>
+      <c r="Z63">
+        <v>1.83</v>
+      </c>
+      <c r="AA63">
+        <v>3.7</v>
+      </c>
+      <c r="AB63">
+        <v>3.97</v>
+      </c>
+      <c r="AC63">
+        <v>1.04</v>
+      </c>
+      <c r="AD63">
+        <v>10</v>
+      </c>
+      <c r="AE63">
+        <v>1.22</v>
+      </c>
+      <c r="AF63">
+        <v>4</v>
+      </c>
+      <c r="AG63">
+        <v>1.55</v>
+      </c>
+      <c r="AH63">
+        <v>2.3</v>
+      </c>
+      <c r="AI63">
+        <v>1.67</v>
+      </c>
+      <c r="AJ63">
+        <v>2.1</v>
+      </c>
+      <c r="AK63">
+        <v>1.26</v>
+      </c>
+      <c r="AL63">
+        <v>1.26</v>
+      </c>
+      <c r="AM63">
+        <v>1.87</v>
+      </c>
+      <c r="AN63">
+        <v>3</v>
+      </c>
+      <c r="AO63">
+        <v>0.5</v>
+      </c>
+      <c r="AP63">
+        <v>2</v>
+      </c>
+      <c r="AQ63">
+        <v>0.67</v>
+      </c>
+      <c r="AR63">
+        <v>1.42</v>
+      </c>
+      <c r="AS63">
+        <v>1.21</v>
+      </c>
+      <c r="AT63">
+        <v>2.63</v>
+      </c>
+      <c r="AU63">
+        <v>10</v>
+      </c>
+      <c r="AV63">
+        <v>4</v>
+      </c>
+      <c r="AW63">
+        <v>10</v>
+      </c>
+      <c r="AX63">
+        <v>10</v>
+      </c>
+      <c r="AY63">
+        <v>20</v>
+      </c>
+      <c r="AZ63">
+        <v>14</v>
+      </c>
+      <c r="BA63">
+        <v>7</v>
+      </c>
+      <c r="BB63">
+        <v>1</v>
+      </c>
+      <c r="BC63">
+        <v>8</v>
+      </c>
+      <c r="BD63">
+        <v>1.48</v>
+      </c>
+      <c r="BE63">
+        <v>7</v>
+      </c>
+      <c r="BF63">
+        <v>2.9</v>
+      </c>
+      <c r="BG63">
+        <v>1.24</v>
+      </c>
+      <c r="BH63">
+        <v>3.55</v>
+      </c>
+      <c r="BI63">
+        <v>1.41</v>
+      </c>
+      <c r="BJ63">
+        <v>2.65</v>
+      </c>
+      <c r="BK63">
+        <v>1.68</v>
+      </c>
+      <c r="BL63">
+        <v>2.02</v>
+      </c>
+      <c r="BM63">
+        <v>2.06</v>
+      </c>
+      <c r="BN63">
+        <v>1.66</v>
+      </c>
+      <c r="BO63">
+        <v>2.55</v>
+      </c>
+      <c r="BP63">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="64" spans="1:68">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>7781137</v>
+      </c>
+      <c r="C64" t="s">
+        <v>68</v>
+      </c>
+      <c r="D64" t="s">
+        <v>69</v>
+      </c>
+      <c r="E64" s="2">
+        <v>45738.85416666666</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64" t="s">
+        <v>85</v>
+      </c>
+      <c r="H64" t="s">
+        <v>81</v>
+      </c>
+      <c r="I64">
+        <v>3</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>3</v>
+      </c>
+      <c r="L64">
+        <v>4</v>
+      </c>
+      <c r="M64">
+        <v>1</v>
+      </c>
+      <c r="N64">
+        <v>5</v>
+      </c>
+      <c r="O64" t="s">
+        <v>146</v>
+      </c>
+      <c r="P64" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q64">
+        <v>2.2</v>
+      </c>
+      <c r="R64">
+        <v>2.38</v>
+      </c>
+      <c r="S64">
+        <v>5</v>
+      </c>
+      <c r="T64">
+        <v>1.33</v>
+      </c>
+      <c r="U64">
+        <v>3.25</v>
+      </c>
+      <c r="V64">
+        <v>2.5</v>
+      </c>
+      <c r="W64">
+        <v>1.5</v>
+      </c>
+      <c r="X64">
+        <v>6.5</v>
+      </c>
+      <c r="Y64">
+        <v>1.11</v>
+      </c>
+      <c r="Z64">
+        <v>1.63</v>
+      </c>
+      <c r="AA64">
+        <v>4.1</v>
+      </c>
+      <c r="AB64">
+        <v>4.7</v>
+      </c>
+      <c r="AC64">
+        <v>1.04</v>
+      </c>
+      <c r="AD64">
+        <v>10</v>
+      </c>
+      <c r="AE64">
+        <v>1.2</v>
+      </c>
+      <c r="AF64">
+        <v>4</v>
+      </c>
+      <c r="AG64">
+        <v>1.6</v>
+      </c>
+      <c r="AH64">
+        <v>2.2</v>
+      </c>
+      <c r="AI64">
+        <v>1.7</v>
+      </c>
+      <c r="AJ64">
+        <v>2.05</v>
+      </c>
+      <c r="AK64">
+        <v>1.17</v>
+      </c>
+      <c r="AL64">
+        <v>1.22</v>
+      </c>
+      <c r="AM64">
+        <v>2.25</v>
+      </c>
+      <c r="AN64">
+        <v>3</v>
+      </c>
+      <c r="AO64">
+        <v>3</v>
+      </c>
+      <c r="AP64">
+        <v>3</v>
+      </c>
+      <c r="AQ64">
+        <v>1.5</v>
+      </c>
+      <c r="AR64">
+        <v>1.62</v>
+      </c>
+      <c r="AS64">
+        <v>0.88</v>
+      </c>
+      <c r="AT64">
+        <v>2.5</v>
+      </c>
+      <c r="AU64">
+        <v>8</v>
+      </c>
+      <c r="AV64">
+        <v>6</v>
+      </c>
+      <c r="AW64">
+        <v>7</v>
+      </c>
+      <c r="AX64">
+        <v>20</v>
+      </c>
+      <c r="AY64">
+        <v>15</v>
+      </c>
+      <c r="AZ64">
+        <v>30</v>
+      </c>
+      <c r="BA64">
+        <v>0</v>
+      </c>
+      <c r="BB64">
+        <v>5</v>
+      </c>
+      <c r="BC64">
+        <v>5</v>
+      </c>
+      <c r="BD64">
+        <v>1.43</v>
+      </c>
+      <c r="BE64">
+        <v>7</v>
+      </c>
+      <c r="BF64">
+        <v>3.15</v>
+      </c>
+      <c r="BG64">
+        <v>1.27</v>
+      </c>
+      <c r="BH64">
+        <v>3.3</v>
+      </c>
+      <c r="BI64">
+        <v>1.47</v>
+      </c>
+      <c r="BJ64">
+        <v>2.48</v>
+      </c>
+      <c r="BK64">
+        <v>1.75</v>
+      </c>
+      <c r="BL64">
+        <v>1.95</v>
+      </c>
+      <c r="BM64">
+        <v>2.17</v>
+      </c>
+      <c r="BN64">
+        <v>1.6</v>
+      </c>
+      <c r="BO64">
+        <v>2.75</v>
+      </c>
+      <c r="BP64">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="65" spans="1:68">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>7781138</v>
+      </c>
+      <c r="C65" t="s">
+        <v>68</v>
+      </c>
+      <c r="D65" t="s">
+        <v>69</v>
+      </c>
+      <c r="E65" s="2">
+        <v>45738.85416666666</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65" t="s">
+        <v>74</v>
+      </c>
+      <c r="H65" t="s">
+        <v>96</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65" t="s">
+        <v>109</v>
+      </c>
+      <c r="P65" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q65">
+        <v>2.3</v>
+      </c>
+      <c r="R65">
+        <v>2.38</v>
+      </c>
+      <c r="S65">
+        <v>4.5</v>
+      </c>
+      <c r="T65">
+        <v>1.3</v>
+      </c>
+      <c r="U65">
+        <v>3.4</v>
+      </c>
+      <c r="V65">
+        <v>2.5</v>
+      </c>
+      <c r="W65">
+        <v>1.5</v>
+      </c>
+      <c r="X65">
+        <v>6</v>
+      </c>
+      <c r="Y65">
+        <v>1.13</v>
+      </c>
+      <c r="Z65">
+        <v>1.71</v>
+      </c>
+      <c r="AA65">
+        <v>3.41</v>
+      </c>
+      <c r="AB65">
+        <v>5.2</v>
+      </c>
+      <c r="AC65">
+        <v>1.04</v>
+      </c>
+      <c r="AD65">
+        <v>10</v>
+      </c>
+      <c r="AE65">
+        <v>1.2</v>
+      </c>
+      <c r="AF65">
+        <v>4.33</v>
+      </c>
+      <c r="AG65">
+        <v>1.55</v>
+      </c>
+      <c r="AH65">
+        <v>2.3</v>
+      </c>
+      <c r="AI65">
+        <v>1.62</v>
+      </c>
+      <c r="AJ65">
+        <v>2.2</v>
+      </c>
+      <c r="AK65">
+        <v>1.22</v>
+      </c>
+      <c r="AL65">
+        <v>1.24</v>
+      </c>
+      <c r="AM65">
+        <v>2</v>
+      </c>
+      <c r="AN65">
+        <v>2</v>
+      </c>
+      <c r="AO65">
+        <v>0.5</v>
+      </c>
+      <c r="AP65">
+        <v>1.67</v>
+      </c>
+      <c r="AQ65">
+        <v>0.67</v>
+      </c>
+      <c r="AR65">
+        <v>1.71</v>
+      </c>
+      <c r="AS65">
+        <v>1.21</v>
+      </c>
+      <c r="AT65">
+        <v>2.92</v>
+      </c>
+      <c r="AU65">
+        <v>7</v>
+      </c>
+      <c r="AV65">
+        <v>0</v>
+      </c>
+      <c r="AW65">
+        <v>20</v>
+      </c>
+      <c r="AX65">
+        <v>6</v>
+      </c>
+      <c r="AY65">
+        <v>33</v>
+      </c>
+      <c r="AZ65">
+        <v>9</v>
+      </c>
+      <c r="BA65">
+        <v>10</v>
+      </c>
+      <c r="BB65">
+        <v>0</v>
+      </c>
+      <c r="BC65">
+        <v>10</v>
+      </c>
+      <c r="BD65">
+        <v>1.41</v>
+      </c>
+      <c r="BE65">
+        <v>6.75</v>
+      </c>
+      <c r="BF65">
+        <v>3.3</v>
+      </c>
+      <c r="BG65">
+        <v>1.37</v>
+      </c>
+      <c r="BH65">
+        <v>2.8</v>
+      </c>
+      <c r="BI65">
+        <v>1.63</v>
+      </c>
+      <c r="BJ65">
+        <v>2.12</v>
+      </c>
+      <c r="BK65">
+        <v>2</v>
+      </c>
+      <c r="BL65">
+        <v>1.71</v>
+      </c>
+      <c r="BM65">
+        <v>2.55</v>
+      </c>
+      <c r="BN65">
+        <v>1.44</v>
+      </c>
+      <c r="BO65">
+        <v>3.3</v>
+      </c>
+      <c r="BP65">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:68">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>7781139</v>
+      </c>
+      <c r="C66" t="s">
+        <v>68</v>
+      </c>
+      <c r="D66" t="s">
+        <v>69</v>
+      </c>
+      <c r="E66" s="2">
+        <v>45738.85416666666</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66" t="s">
+        <v>88</v>
+      </c>
+      <c r="H66" t="s">
+        <v>98</v>
+      </c>
+      <c r="I66">
+        <v>1</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>1</v>
+      </c>
+      <c r="L66">
+        <v>2</v>
+      </c>
+      <c r="M66">
+        <v>1</v>
+      </c>
+      <c r="N66">
+        <v>3</v>
+      </c>
+      <c r="O66" t="s">
+        <v>147</v>
+      </c>
+      <c r="P66" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q66">
+        <v>2.3</v>
+      </c>
+      <c r="R66">
+        <v>2.25</v>
+      </c>
+      <c r="S66">
+        <v>4.75</v>
+      </c>
+      <c r="T66">
+        <v>1.36</v>
+      </c>
+      <c r="U66">
+        <v>3</v>
+      </c>
+      <c r="V66">
+        <v>2.63</v>
+      </c>
+      <c r="W66">
+        <v>1.44</v>
+      </c>
+      <c r="X66">
+        <v>7</v>
+      </c>
+      <c r="Y66">
+        <v>1.1</v>
+      </c>
+      <c r="Z66">
+        <v>1.74</v>
+      </c>
+      <c r="AA66">
+        <v>3.41</v>
+      </c>
+      <c r="AB66">
+        <v>4.9</v>
+      </c>
+      <c r="AC66">
+        <v>1.04</v>
+      </c>
+      <c r="AD66">
+        <v>10</v>
+      </c>
+      <c r="AE66">
+        <v>1.25</v>
+      </c>
+      <c r="AF66">
+        <v>3.6</v>
+      </c>
+      <c r="AG66">
+        <v>1.79</v>
+      </c>
+      <c r="AH66">
+        <v>1.95</v>
+      </c>
+      <c r="AI66">
+        <v>1.75</v>
+      </c>
+      <c r="AJ66">
+        <v>2</v>
+      </c>
+      <c r="AK66">
+        <v>1.21</v>
+      </c>
+      <c r="AL66">
+        <v>1.26</v>
+      </c>
+      <c r="AM66">
+        <v>1.98</v>
+      </c>
+      <c r="AN66">
+        <v>2</v>
+      </c>
+      <c r="AO66">
+        <v>0.33</v>
+      </c>
+      <c r="AP66">
+        <v>2.33</v>
+      </c>
+      <c r="AQ66">
+        <v>0.25</v>
+      </c>
+      <c r="AR66">
+        <v>1.35</v>
+      </c>
+      <c r="AS66">
+        <v>1.26</v>
+      </c>
+      <c r="AT66">
+        <v>2.61</v>
+      </c>
+      <c r="AU66">
+        <v>7</v>
+      </c>
+      <c r="AV66">
+        <v>3</v>
+      </c>
+      <c r="AW66">
+        <v>6</v>
+      </c>
+      <c r="AX66">
+        <v>3</v>
+      </c>
+      <c r="AY66">
+        <v>13</v>
+      </c>
+      <c r="AZ66">
+        <v>6</v>
+      </c>
+      <c r="BA66">
+        <v>5</v>
+      </c>
+      <c r="BB66">
+        <v>1</v>
+      </c>
+      <c r="BC66">
+        <v>6</v>
+      </c>
+      <c r="BD66">
+        <v>1.54</v>
+      </c>
+      <c r="BE66">
+        <v>6.75</v>
+      </c>
+      <c r="BF66">
+        <v>2.7</v>
+      </c>
+      <c r="BG66">
+        <v>1.37</v>
+      </c>
+      <c r="BH66">
+        <v>2.8</v>
+      </c>
+      <c r="BI66">
+        <v>1.63</v>
+      </c>
+      <c r="BJ66">
+        <v>2.12</v>
+      </c>
+      <c r="BK66">
+        <v>2.02</v>
+      </c>
+      <c r="BL66">
+        <v>1.7</v>
+      </c>
+      <c r="BM66">
+        <v>2.55</v>
+      </c>
+      <c r="BN66">
+        <v>1.44</v>
+      </c>
+      <c r="BO66">
+        <v>3.3</v>
+      </c>
+      <c r="BP66">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="67" spans="1:68">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>7781140</v>
+      </c>
+      <c r="C67" t="s">
+        <v>68</v>
+      </c>
+      <c r="D67" t="s">
+        <v>69</v>
+      </c>
+      <c r="E67" s="2">
+        <v>45738.85416666666</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67" t="s">
+        <v>76</v>
+      </c>
+      <c r="H67" t="s">
+        <v>75</v>
+      </c>
+      <c r="I67">
+        <v>2</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>2</v>
+      </c>
+      <c r="L67">
+        <v>4</v>
+      </c>
+      <c r="M67">
+        <v>1</v>
+      </c>
+      <c r="N67">
+        <v>5</v>
+      </c>
+      <c r="O67" t="s">
+        <v>148</v>
+      </c>
+      <c r="P67" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q67">
+        <v>2.3</v>
+      </c>
+      <c r="R67">
+        <v>2.4</v>
+      </c>
+      <c r="S67">
+        <v>4.33</v>
+      </c>
+      <c r="T67">
+        <v>1.29</v>
+      </c>
+      <c r="U67">
+        <v>3.5</v>
+      </c>
+      <c r="V67">
+        <v>2.38</v>
+      </c>
+      <c r="W67">
+        <v>1.53</v>
+      </c>
+      <c r="X67">
+        <v>5.5</v>
+      </c>
+      <c r="Y67">
+        <v>1.14</v>
+      </c>
+      <c r="Z67">
+        <v>1.76</v>
+      </c>
+      <c r="AA67">
+        <v>3.81</v>
+      </c>
+      <c r="AB67">
+        <v>4.2</v>
+      </c>
+      <c r="AC67">
+        <v>1.02</v>
+      </c>
+      <c r="AD67">
+        <v>13</v>
+      </c>
+      <c r="AE67">
+        <v>1.18</v>
+      </c>
+      <c r="AF67">
+        <v>4.4</v>
+      </c>
+      <c r="AG67">
+        <v>1.55</v>
+      </c>
+      <c r="AH67">
+        <v>2.28</v>
+      </c>
+      <c r="AI67">
+        <v>1.57</v>
+      </c>
+      <c r="AJ67">
+        <v>2.25</v>
+      </c>
+      <c r="AK67">
+        <v>1.24</v>
+      </c>
+      <c r="AL67">
+        <v>1.24</v>
+      </c>
+      <c r="AM67">
+        <v>1.98</v>
+      </c>
+      <c r="AN67">
+        <v>1.5</v>
+      </c>
+      <c r="AO67">
+        <v>1</v>
+      </c>
+      <c r="AP67">
+        <v>2</v>
+      </c>
+      <c r="AQ67">
+        <v>0.5</v>
+      </c>
+      <c r="AR67">
+        <v>1.65</v>
+      </c>
+      <c r="AS67">
+        <v>1.8</v>
+      </c>
+      <c r="AT67">
+        <v>3.45</v>
+      </c>
+      <c r="AU67">
+        <v>11</v>
+      </c>
+      <c r="AV67">
+        <v>8</v>
+      </c>
+      <c r="AW67">
+        <v>9</v>
+      </c>
+      <c r="AX67">
+        <v>9</v>
+      </c>
+      <c r="AY67">
+        <v>22</v>
+      </c>
+      <c r="AZ67">
+        <v>20</v>
+      </c>
+      <c r="BA67">
+        <v>1</v>
+      </c>
+      <c r="BB67">
+        <v>10</v>
+      </c>
+      <c r="BC67">
+        <v>11</v>
+      </c>
+      <c r="BD67">
+        <v>1.61</v>
+      </c>
+      <c r="BE67">
+        <v>6.5</v>
+      </c>
+      <c r="BF67">
+        <v>2.55</v>
+      </c>
+      <c r="BG67">
+        <v>1.33</v>
+      </c>
+      <c r="BH67">
+        <v>2.95</v>
+      </c>
+      <c r="BI67">
+        <v>1.57</v>
+      </c>
+      <c r="BJ67">
+        <v>2.23</v>
+      </c>
+      <c r="BK67">
+        <v>1.92</v>
+      </c>
+      <c r="BL67">
+        <v>1.77</v>
+      </c>
+      <c r="BM67">
+        <v>2.4</v>
+      </c>
+      <c r="BN67">
+        <v>1.49</v>
+      </c>
+      <c r="BO67">
+        <v>3.15</v>
+      </c>
+      <c r="BP67">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:68">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>7781141</v>
+      </c>
+      <c r="C68" t="s">
+        <v>68</v>
+      </c>
+      <c r="D68" t="s">
+        <v>69</v>
+      </c>
+      <c r="E68" s="2">
+        <v>45738.85416666666</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68" t="s">
+        <v>89</v>
+      </c>
+      <c r="H68" t="s">
+        <v>80</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>1</v>
+      </c>
+      <c r="L68">
+        <v>1</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>1</v>
+      </c>
+      <c r="O68" t="s">
+        <v>149</v>
+      </c>
+      <c r="P68" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q68">
+        <v>2.75</v>
+      </c>
+      <c r="R68">
+        <v>2.3</v>
+      </c>
+      <c r="S68">
+        <v>3.4</v>
+      </c>
+      <c r="T68">
+        <v>1.3</v>
+      </c>
+      <c r="U68">
+        <v>3.4</v>
+      </c>
+      <c r="V68">
+        <v>2.5</v>
+      </c>
+      <c r="W68">
+        <v>1.5</v>
+      </c>
+      <c r="X68">
+        <v>6</v>
+      </c>
+      <c r="Y68">
+        <v>1.13</v>
+      </c>
+      <c r="Z68">
+        <v>2.03</v>
+      </c>
+      <c r="AA68">
+        <v>3.51</v>
+      </c>
+      <c r="AB68">
+        <v>3.41</v>
+      </c>
+      <c r="AC68">
+        <v>1.03</v>
+      </c>
+      <c r="AD68">
+        <v>12</v>
+      </c>
+      <c r="AE68">
+        <v>1.19</v>
+      </c>
+      <c r="AF68">
+        <v>4.2</v>
+      </c>
+      <c r="AG68">
+        <v>1.55</v>
+      </c>
+      <c r="AH68">
+        <v>2.3</v>
+      </c>
+      <c r="AI68">
+        <v>1.53</v>
+      </c>
+      <c r="AJ68">
+        <v>2.38</v>
+      </c>
+      <c r="AK68">
+        <v>1.38</v>
+      </c>
+      <c r="AL68">
+        <v>1.27</v>
+      </c>
+      <c r="AM68">
+        <v>1.65</v>
+      </c>
+      <c r="AN68">
+        <v>1.5</v>
+      </c>
+      <c r="AO68">
+        <v>2</v>
+      </c>
+      <c r="AP68">
+        <v>2</v>
+      </c>
+      <c r="AQ68">
+        <v>1.33</v>
+      </c>
+      <c r="AR68">
+        <v>1.48</v>
+      </c>
+      <c r="AS68">
+        <v>0.97</v>
+      </c>
+      <c r="AT68">
+        <v>2.45</v>
+      </c>
+      <c r="AU68">
+        <v>9</v>
+      </c>
+      <c r="AV68">
+        <v>2</v>
+      </c>
+      <c r="AW68">
+        <v>10</v>
+      </c>
+      <c r="AX68">
+        <v>7</v>
+      </c>
+      <c r="AY68">
+        <v>19</v>
+      </c>
+      <c r="AZ68">
+        <v>10</v>
+      </c>
+      <c r="BA68">
+        <v>6</v>
+      </c>
+      <c r="BB68">
+        <v>5</v>
+      </c>
+      <c r="BC68">
+        <v>11</v>
+      </c>
+      <c r="BD68">
+        <v>1.6</v>
+      </c>
+      <c r="BE68">
+        <v>6.75</v>
+      </c>
+      <c r="BF68">
+        <v>2.55</v>
+      </c>
+      <c r="BG68">
+        <v>1.28</v>
+      </c>
+      <c r="BH68">
+        <v>3.2</v>
+      </c>
+      <c r="BI68">
+        <v>1.49</v>
+      </c>
+      <c r="BJ68">
+        <v>2.4</v>
+      </c>
+      <c r="BK68">
+        <v>1.8</v>
+      </c>
+      <c r="BL68">
+        <v>1.88</v>
+      </c>
+      <c r="BM68">
+        <v>2.23</v>
+      </c>
+      <c r="BN68">
+        <v>1.56</v>
+      </c>
+      <c r="BO68">
+        <v>2.9</v>
+      </c>
+      <c r="BP68">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="69" spans="1:68">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>7781142</v>
+      </c>
+      <c r="C69" t="s">
+        <v>68</v>
+      </c>
+      <c r="D69" t="s">
+        <v>69</v>
+      </c>
+      <c r="E69" s="2">
+        <v>45738.89583333334</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69" t="s">
+        <v>91</v>
+      </c>
+      <c r="H69" t="s">
+        <v>70</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
+      <c r="K69">
+        <v>1</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>2</v>
+      </c>
+      <c r="N69">
+        <v>2</v>
+      </c>
+      <c r="O69" t="s">
+        <v>109</v>
+      </c>
+      <c r="P69" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q69">
+        <v>3.4</v>
+      </c>
+      <c r="R69">
+        <v>2.2</v>
+      </c>
+      <c r="S69">
+        <v>3</v>
+      </c>
+      <c r="T69">
+        <v>1.36</v>
+      </c>
+      <c r="U69">
+        <v>3</v>
+      </c>
+      <c r="V69">
+        <v>2.75</v>
+      </c>
+      <c r="W69">
+        <v>1.4</v>
+      </c>
+      <c r="X69">
+        <v>7</v>
+      </c>
+      <c r="Y69">
+        <v>1.1</v>
+      </c>
+      <c r="Z69">
+        <v>2.82</v>
+      </c>
+      <c r="AA69">
+        <v>3.45</v>
+      </c>
+      <c r="AB69">
+        <v>2.35</v>
+      </c>
+      <c r="AC69">
+        <v>1.04</v>
+      </c>
+      <c r="AD69">
+        <v>10</v>
+      </c>
+      <c r="AE69">
+        <v>1.25</v>
+      </c>
+      <c r="AF69">
+        <v>3.6</v>
+      </c>
+      <c r="AG69">
+        <v>1.79</v>
+      </c>
+      <c r="AH69">
+        <v>1.95</v>
+      </c>
+      <c r="AI69">
+        <v>1.62</v>
+      </c>
+      <c r="AJ69">
+        <v>2.2</v>
+      </c>
+      <c r="AK69">
+        <v>1.58</v>
+      </c>
+      <c r="AL69">
+        <v>1.29</v>
+      </c>
+      <c r="AM69">
+        <v>1.39</v>
+      </c>
+      <c r="AN69">
+        <v>0.5</v>
+      </c>
+      <c r="AO69">
+        <v>0</v>
+      </c>
+      <c r="AP69">
+        <v>0.33</v>
+      </c>
+      <c r="AQ69">
+        <v>1.5</v>
+      </c>
+      <c r="AR69">
+        <v>1.7</v>
+      </c>
+      <c r="AS69">
+        <v>0.93</v>
+      </c>
+      <c r="AT69">
+        <v>2.63</v>
+      </c>
+      <c r="AU69">
+        <v>4</v>
+      </c>
+      <c r="AV69">
+        <v>5</v>
+      </c>
+      <c r="AW69">
+        <v>8</v>
+      </c>
+      <c r="AX69">
+        <v>3</v>
+      </c>
+      <c r="AY69">
+        <v>19</v>
+      </c>
+      <c r="AZ69">
+        <v>9</v>
+      </c>
+      <c r="BA69">
+        <v>11</v>
+      </c>
+      <c r="BB69">
+        <v>1</v>
+      </c>
+      <c r="BC69">
+        <v>12</v>
+      </c>
+      <c r="BD69">
+        <v>1.91</v>
+      </c>
+      <c r="BE69">
+        <v>6.5</v>
+      </c>
+      <c r="BF69">
+        <v>2.07</v>
+      </c>
+      <c r="BG69">
+        <v>1.25</v>
+      </c>
+      <c r="BH69">
+        <v>3.45</v>
+      </c>
+      <c r="BI69">
+        <v>1.44</v>
+      </c>
+      <c r="BJ69">
+        <v>2.55</v>
+      </c>
+      <c r="BK69">
+        <v>1.72</v>
+      </c>
+      <c r="BL69">
+        <v>1.98</v>
+      </c>
+      <c r="BM69">
+        <v>2.12</v>
+      </c>
+      <c r="BN69">
+        <v>1.63</v>
+      </c>
+      <c r="BO69">
+        <v>2.65</v>
+      </c>
+      <c r="BP69">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:68">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>7781143</v>
+      </c>
+      <c r="C70" t="s">
+        <v>68</v>
+      </c>
+      <c r="D70" t="s">
+        <v>69</v>
+      </c>
+      <c r="E70" s="2">
+        <v>45738.89583333334</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70" t="s">
+        <v>79</v>
+      </c>
+      <c r="H70" t="s">
+        <v>99</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>3</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>3</v>
+      </c>
+      <c r="O70" t="s">
+        <v>150</v>
+      </c>
+      <c r="P70" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q70">
+        <v>2.1</v>
+      </c>
+      <c r="R70">
+        <v>2.38</v>
+      </c>
+      <c r="S70">
+        <v>5.5</v>
+      </c>
+      <c r="T70">
+        <v>1.33</v>
+      </c>
+      <c r="U70">
+        <v>3.25</v>
+      </c>
+      <c r="V70">
+        <v>2.5</v>
+      </c>
+      <c r="W70">
+        <v>1.5</v>
+      </c>
+      <c r="X70">
+        <v>6.5</v>
+      </c>
+      <c r="Y70">
+        <v>1.11</v>
+      </c>
+      <c r="Z70">
+        <v>1.58</v>
+      </c>
+      <c r="AA70">
+        <v>4.1</v>
+      </c>
+      <c r="AB70">
+        <v>5.1</v>
+      </c>
+      <c r="AC70">
+        <v>1.03</v>
+      </c>
+      <c r="AD70">
+        <v>11.5</v>
+      </c>
+      <c r="AE70">
+        <v>1.21</v>
+      </c>
+      <c r="AF70">
+        <v>4</v>
+      </c>
+      <c r="AG70">
+        <v>1.65</v>
+      </c>
+      <c r="AH70">
+        <v>2.13</v>
+      </c>
+      <c r="AI70">
+        <v>1.7</v>
+      </c>
+      <c r="AJ70">
+        <v>2.05</v>
+      </c>
+      <c r="AK70">
+        <v>1.16</v>
+      </c>
+      <c r="AL70">
+        <v>1.22</v>
+      </c>
+      <c r="AM70">
+        <v>2.25</v>
+      </c>
+      <c r="AN70">
+        <v>2</v>
+      </c>
+      <c r="AO70">
+        <v>0.25</v>
+      </c>
+      <c r="AP70">
+        <v>2.33</v>
+      </c>
+      <c r="AQ70">
+        <v>0.2</v>
+      </c>
+      <c r="AR70">
+        <v>1.96</v>
+      </c>
+      <c r="AS70">
+        <v>1.12</v>
+      </c>
+      <c r="AT70">
+        <v>3.08</v>
+      </c>
+      <c r="AU70">
+        <v>8</v>
+      </c>
+      <c r="AV70">
+        <v>2</v>
+      </c>
+      <c r="AW70">
+        <v>6</v>
+      </c>
+      <c r="AX70">
+        <v>9</v>
+      </c>
+      <c r="AY70">
+        <v>15</v>
+      </c>
+      <c r="AZ70">
+        <v>13</v>
+      </c>
+      <c r="BA70">
+        <v>5</v>
+      </c>
+      <c r="BB70">
+        <v>3</v>
+      </c>
+      <c r="BC70">
+        <v>8</v>
+      </c>
+      <c r="BD70">
+        <v>1.3</v>
+      </c>
+      <c r="BE70">
+        <v>7</v>
+      </c>
+      <c r="BF70">
+        <v>3.9</v>
+      </c>
+      <c r="BG70">
+        <v>1.36</v>
+      </c>
+      <c r="BH70">
+        <v>2.8</v>
+      </c>
+      <c r="BI70">
+        <v>1.61</v>
+      </c>
+      <c r="BJ70">
+        <v>2.15</v>
+      </c>
+      <c r="BK70">
+        <v>1.98</v>
+      </c>
+      <c r="BL70">
+        <v>1.72</v>
+      </c>
+      <c r="BM70">
+        <v>2.55</v>
+      </c>
+      <c r="BN70">
+        <v>1.44</v>
+      </c>
+      <c r="BO70">
+        <v>3.3</v>
+      </c>
+      <c r="BP70">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="71" spans="1:68">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>7781144</v>
+      </c>
+      <c r="C71" t="s">
+        <v>68</v>
+      </c>
+      <c r="D71" t="s">
+        <v>69</v>
+      </c>
+      <c r="E71" s="2">
+        <v>45738.9375</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71" t="s">
+        <v>93</v>
+      </c>
+      <c r="H71" t="s">
+        <v>83</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+      <c r="K71">
+        <v>1</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>3</v>
+      </c>
+      <c r="N71">
+        <v>3</v>
+      </c>
+      <c r="O71" t="s">
+        <v>109</v>
+      </c>
+      <c r="P71" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q71">
+        <v>2.38</v>
+      </c>
+      <c r="R71">
+        <v>2.38</v>
+      </c>
+      <c r="S71">
+        <v>4.33</v>
+      </c>
+      <c r="T71">
+        <v>1.3</v>
+      </c>
+      <c r="U71">
+        <v>3.4</v>
+      </c>
+      <c r="V71">
+        <v>2.5</v>
+      </c>
+      <c r="W71">
+        <v>1.5</v>
+      </c>
+      <c r="X71">
+        <v>6</v>
+      </c>
+      <c r="Y71">
+        <v>1.13</v>
+      </c>
+      <c r="Z71">
+        <v>1.83</v>
+      </c>
+      <c r="AA71">
+        <v>3.81</v>
+      </c>
+      <c r="AB71">
+        <v>3.83</v>
+      </c>
+      <c r="AC71">
+        <v>1.03</v>
+      </c>
+      <c r="AD71">
+        <v>12</v>
+      </c>
+      <c r="AE71">
+        <v>1.2</v>
+      </c>
+      <c r="AF71">
+        <v>4.2</v>
+      </c>
+      <c r="AG71">
+        <v>1.57</v>
+      </c>
+      <c r="AH71">
+        <v>2.31</v>
+      </c>
+      <c r="AI71">
+        <v>1.57</v>
+      </c>
+      <c r="AJ71">
+        <v>2.25</v>
+      </c>
+      <c r="AK71">
+        <v>1.25</v>
+      </c>
+      <c r="AL71">
+        <v>1.25</v>
+      </c>
+      <c r="AM71">
+        <v>1.9</v>
+      </c>
+      <c r="AN71">
+        <v>1</v>
+      </c>
+      <c r="AO71">
+        <v>0</v>
+      </c>
+      <c r="AP71">
+        <v>0.5</v>
+      </c>
+      <c r="AQ71">
+        <v>1.5</v>
+      </c>
+      <c r="AR71">
+        <v>1.88</v>
+      </c>
+      <c r="AS71">
+        <v>1.27</v>
+      </c>
+      <c r="AT71">
+        <v>3.15</v>
+      </c>
+      <c r="AU71">
+        <v>2</v>
+      </c>
+      <c r="AV71">
+        <v>6</v>
+      </c>
+      <c r="AW71">
+        <v>7</v>
+      </c>
+      <c r="AX71">
+        <v>7</v>
+      </c>
+      <c r="AY71">
+        <v>12</v>
+      </c>
+      <c r="AZ71">
+        <v>15</v>
+      </c>
+      <c r="BA71">
+        <v>6</v>
+      </c>
+      <c r="BB71">
+        <v>3</v>
+      </c>
+      <c r="BC71">
+        <v>9</v>
+      </c>
+      <c r="BD71">
+        <v>1.44</v>
+      </c>
+      <c r="BE71">
+        <v>6.75</v>
+      </c>
+      <c r="BF71">
+        <v>3.15</v>
+      </c>
+      <c r="BG71">
+        <v>1.26</v>
+      </c>
+      <c r="BH71">
+        <v>3.4</v>
+      </c>
+      <c r="BI71">
+        <v>1.44</v>
+      </c>
+      <c r="BJ71">
+        <v>2.55</v>
+      </c>
+      <c r="BK71">
+        <v>1.72</v>
+      </c>
+      <c r="BL71">
+        <v>1.98</v>
+      </c>
+      <c r="BM71">
+        <v>2.12</v>
+      </c>
+      <c r="BN71">
+        <v>1.63</v>
+      </c>
+      <c r="BO71">
+        <v>2.65</v>
+      </c>
+      <c r="BP71">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="72" spans="1:68">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>7781145</v>
+      </c>
+      <c r="C72" t="s">
+        <v>68</v>
+      </c>
+      <c r="D72" t="s">
+        <v>69</v>
+      </c>
+      <c r="E72" s="2">
+        <v>45738.9375</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72" t="s">
+        <v>86</v>
+      </c>
+      <c r="H72" t="s">
+        <v>97</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72">
+        <v>1</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>1</v>
+      </c>
+      <c r="N72">
+        <v>1</v>
+      </c>
+      <c r="O72" t="s">
+        <v>109</v>
+      </c>
+      <c r="P72" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q72">
+        <v>2.6</v>
+      </c>
+      <c r="R72">
+        <v>2.3</v>
+      </c>
+      <c r="S72">
+        <v>3.75</v>
+      </c>
+      <c r="T72">
+        <v>1.33</v>
+      </c>
+      <c r="U72">
+        <v>3.25</v>
+      </c>
+      <c r="V72">
+        <v>2.63</v>
+      </c>
+      <c r="W72">
+        <v>1.44</v>
+      </c>
+      <c r="X72">
+        <v>6.5</v>
+      </c>
+      <c r="Y72">
+        <v>1.11</v>
+      </c>
+      <c r="Z72">
+        <v>2.01</v>
+      </c>
+      <c r="AA72">
+        <v>3.32</v>
+      </c>
+      <c r="AB72">
+        <v>3.7</v>
+      </c>
+      <c r="AC72">
+        <v>1.03</v>
+      </c>
+      <c r="AD72">
+        <v>11.5</v>
+      </c>
+      <c r="AE72">
+        <v>1.21</v>
+      </c>
+      <c r="AF72">
+        <v>4</v>
+      </c>
+      <c r="AG72">
+        <v>1.66</v>
+      </c>
+      <c r="AH72">
+        <v>2.14</v>
+      </c>
+      <c r="AI72">
+        <v>1.62</v>
+      </c>
+      <c r="AJ72">
+        <v>2.2</v>
+      </c>
+      <c r="AK72">
+        <v>1.31</v>
+      </c>
+      <c r="AL72">
+        <v>1.26</v>
+      </c>
+      <c r="AM72">
+        <v>1.75</v>
+      </c>
+      <c r="AN72">
+        <v>1.5</v>
+      </c>
+      <c r="AO72">
+        <v>2</v>
+      </c>
+      <c r="AP72">
+        <v>1</v>
+      </c>
+      <c r="AQ72">
+        <v>2.33</v>
+      </c>
+      <c r="AR72">
+        <v>1.41</v>
+      </c>
+      <c r="AS72">
+        <v>1.36</v>
+      </c>
+      <c r="AT72">
+        <v>2.77</v>
+      </c>
+      <c r="AU72">
+        <v>3</v>
+      </c>
+      <c r="AV72">
+        <v>5</v>
+      </c>
+      <c r="AW72">
+        <v>9</v>
+      </c>
+      <c r="AX72">
+        <v>8</v>
+      </c>
+      <c r="AY72">
+        <v>14</v>
+      </c>
+      <c r="AZ72">
+        <v>14</v>
+      </c>
+      <c r="BA72">
+        <v>4</v>
+      </c>
+      <c r="BB72">
+        <v>6</v>
+      </c>
+      <c r="BC72">
+        <v>10</v>
+      </c>
+      <c r="BD72">
+        <v>1.6</v>
+      </c>
+      <c r="BE72">
+        <v>6.75</v>
+      </c>
+      <c r="BF72">
+        <v>2.55</v>
+      </c>
+      <c r="BG72">
+        <v>1.29</v>
+      </c>
+      <c r="BH72">
+        <v>3.2</v>
+      </c>
+      <c r="BI72">
+        <v>1.49</v>
+      </c>
+      <c r="BJ72">
+        <v>2.4</v>
+      </c>
+      <c r="BK72">
+        <v>1.8</v>
+      </c>
+      <c r="BL72">
+        <v>1.89</v>
+      </c>
+      <c r="BM72">
+        <v>2.28</v>
+      </c>
+      <c r="BN72">
+        <v>1.55</v>
+      </c>
+      <c r="BO72">
+        <v>2.9</v>
+      </c>
+      <c r="BP72">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="73" spans="1:68">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>7781146</v>
+      </c>
+      <c r="C73" t="s">
+        <v>68</v>
+      </c>
+      <c r="D73" t="s">
+        <v>69</v>
+      </c>
+      <c r="E73" s="2">
+        <v>45738.97916666666</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73" t="s">
+        <v>82</v>
+      </c>
+      <c r="H73" t="s">
+        <v>78</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73" t="s">
+        <v>109</v>
+      </c>
+      <c r="P73" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q73">
+        <v>2.38</v>
+      </c>
+      <c r="R73">
+        <v>2.1</v>
+      </c>
+      <c r="S73">
+        <v>5.5</v>
+      </c>
+      <c r="T73">
+        <v>1.44</v>
+      </c>
+      <c r="U73">
+        <v>2.63</v>
+      </c>
+      <c r="V73">
+        <v>3.25</v>
+      </c>
+      <c r="W73">
+        <v>1.33</v>
+      </c>
+      <c r="X73">
+        <v>9</v>
+      </c>
+      <c r="Y73">
+        <v>1.07</v>
+      </c>
+      <c r="Z73">
+        <v>1.7</v>
+      </c>
+      <c r="AA73">
+        <v>3.59</v>
+      </c>
+      <c r="AB73">
+        <v>4.9</v>
+      </c>
+      <c r="AC73">
+        <v>1.06</v>
+      </c>
+      <c r="AD73">
+        <v>8.25</v>
+      </c>
+      <c r="AE73">
+        <v>1.34</v>
+      </c>
+      <c r="AF73">
+        <v>2.95</v>
+      </c>
+      <c r="AG73">
+        <v>1.98</v>
+      </c>
+      <c r="AH73">
+        <v>1.77</v>
+      </c>
+      <c r="AI73">
+        <v>2</v>
+      </c>
+      <c r="AJ73">
+        <v>1.75</v>
+      </c>
+      <c r="AK73">
+        <v>1.18</v>
+      </c>
+      <c r="AL73">
+        <v>1.27</v>
+      </c>
+      <c r="AM73">
+        <v>2.1</v>
+      </c>
+      <c r="AN73">
+        <v>2</v>
+      </c>
+      <c r="AO73">
+        <v>1</v>
+      </c>
+      <c r="AP73">
+        <v>1.67</v>
+      </c>
+      <c r="AQ73">
+        <v>1</v>
+      </c>
+      <c r="AR73">
+        <v>2.23</v>
+      </c>
+      <c r="AS73">
+        <v>0.61</v>
+      </c>
+      <c r="AT73">
+        <v>2.84</v>
+      </c>
+      <c r="AU73">
+        <v>4</v>
+      </c>
+      <c r="AV73">
+        <v>2</v>
+      </c>
+      <c r="AW73">
+        <v>9</v>
+      </c>
+      <c r="AX73">
+        <v>5</v>
+      </c>
+      <c r="AY73">
+        <v>18</v>
+      </c>
+      <c r="AZ73">
+        <v>8</v>
+      </c>
+      <c r="BA73">
+        <v>7</v>
+      </c>
+      <c r="BB73">
+        <v>0</v>
+      </c>
+      <c r="BC73">
+        <v>7</v>
+      </c>
+      <c r="BD73">
+        <v>1.42</v>
+      </c>
+      <c r="BE73">
+        <v>7</v>
+      </c>
+      <c r="BF73">
+        <v>3.15</v>
+      </c>
+      <c r="BG73">
+        <v>1.29</v>
+      </c>
+      <c r="BH73">
+        <v>3.2</v>
+      </c>
+      <c r="BI73">
+        <v>1.49</v>
+      </c>
+      <c r="BJ73">
+        <v>2.4</v>
+      </c>
+      <c r="BK73">
+        <v>1.8</v>
+      </c>
+      <c r="BL73">
+        <v>1.88</v>
+      </c>
+      <c r="BM73">
+        <v>2.23</v>
+      </c>
+      <c r="BN73">
+        <v>1.57</v>
+      </c>
+      <c r="BO73">
+        <v>2.8</v>
+      </c>
+      <c r="BP73">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="74" spans="1:68">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>7781147</v>
+      </c>
+      <c r="C74" t="s">
+        <v>68</v>
+      </c>
+      <c r="D74" t="s">
+        <v>69</v>
+      </c>
+      <c r="E74" s="2">
+        <v>45738.97916666666</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74" t="s">
+        <v>95</v>
+      </c>
+      <c r="H74" t="s">
+        <v>90</v>
+      </c>
+      <c r="I74">
+        <v>1</v>
+      </c>
+      <c r="J74">
+        <v>1</v>
+      </c>
+      <c r="K74">
+        <v>2</v>
+      </c>
+      <c r="L74">
+        <v>1</v>
+      </c>
+      <c r="M74">
+        <v>3</v>
+      </c>
+      <c r="N74">
+        <v>4</v>
+      </c>
+      <c r="O74" t="s">
+        <v>151</v>
+      </c>
+      <c r="P74" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q74">
+        <v>2.5</v>
+      </c>
+      <c r="R74">
+        <v>2.3</v>
+      </c>
+      <c r="S74">
+        <v>4</v>
+      </c>
+      <c r="T74">
+        <v>1.33</v>
+      </c>
+      <c r="U74">
+        <v>3.25</v>
+      </c>
+      <c r="V74">
+        <v>2.5</v>
+      </c>
+      <c r="W74">
+        <v>1.5</v>
+      </c>
+      <c r="X74">
+        <v>6.5</v>
+      </c>
+      <c r="Y74">
+        <v>1.11</v>
+      </c>
+      <c r="Z74">
+        <v>1.75</v>
+      </c>
+      <c r="AA74">
+        <v>3.61</v>
+      </c>
+      <c r="AB74">
+        <v>4.5</v>
+      </c>
+      <c r="AC74">
+        <v>1.03</v>
+      </c>
+      <c r="AD74">
+        <v>12</v>
+      </c>
+      <c r="AE74">
+        <v>1.2</v>
+      </c>
+      <c r="AF74">
+        <v>4.1</v>
+      </c>
+      <c r="AG74">
+        <v>1.61</v>
+      </c>
+      <c r="AH74">
+        <v>2.15</v>
+      </c>
+      <c r="AI74">
+        <v>1.62</v>
+      </c>
+      <c r="AJ74">
+        <v>2.2</v>
+      </c>
+      <c r="AK74">
+        <v>1.27</v>
+      </c>
+      <c r="AL74">
+        <v>1.26</v>
+      </c>
+      <c r="AM74">
+        <v>1.85</v>
+      </c>
+      <c r="AN74">
+        <v>3</v>
+      </c>
+      <c r="AO74">
+        <v>2</v>
+      </c>
+      <c r="AP74">
+        <v>2</v>
+      </c>
+      <c r="AQ74">
+        <v>2.25</v>
+      </c>
+      <c r="AR74">
+        <v>1.88</v>
+      </c>
+      <c r="AS74">
+        <v>1.73</v>
+      </c>
+      <c r="AT74">
+        <v>3.61</v>
+      </c>
+      <c r="AU74">
+        <v>4</v>
+      </c>
+      <c r="AV74">
+        <v>7</v>
+      </c>
+      <c r="AW74">
+        <v>10</v>
+      </c>
+      <c r="AX74">
+        <v>5</v>
+      </c>
+      <c r="AY74">
+        <v>16</v>
+      </c>
+      <c r="AZ74">
+        <v>12</v>
+      </c>
+      <c r="BA74">
+        <v>4</v>
+      </c>
+      <c r="BB74">
+        <v>6</v>
+      </c>
+      <c r="BC74">
+        <v>10</v>
+      </c>
+      <c r="BD74">
+        <v>1.56</v>
+      </c>
+      <c r="BE74">
+        <v>6.75</v>
+      </c>
+      <c r="BF74">
+        <v>2.65</v>
+      </c>
+      <c r="BG74">
+        <v>1.3</v>
+      </c>
+      <c r="BH74">
+        <v>3.15</v>
+      </c>
+      <c r="BI74">
+        <v>1.5</v>
+      </c>
+      <c r="BJ74">
+        <v>2.33</v>
+      </c>
+      <c r="BK74">
+        <v>1.82</v>
+      </c>
+      <c r="BL74">
+        <v>1.86</v>
+      </c>
+      <c r="BM74">
+        <v>2.3</v>
+      </c>
+      <c r="BN74">
+        <v>1.54</v>
+      </c>
+      <c r="BO74">
+        <v>2.9</v>
+      </c>
+      <c r="BP74">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="196">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -470,6 +470,9 @@
   </si>
   <si>
     <t>['14']</t>
+  </si>
+  <si>
+    <t>['10', '19']</t>
   </si>
   <si>
     <t>['26', '55']</t>
@@ -960,7 +963,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP74"/>
+  <dimension ref="A1:BP75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1422,7 +1425,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -1628,7 +1631,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2040,7 +2043,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2246,7 +2249,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2452,7 +2455,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2736,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ9">
         <v>0</v>
@@ -2864,7 +2867,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -3688,7 +3691,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -3894,7 +3897,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4100,7 +4103,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4181,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="AQ16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4718,7 +4721,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -5130,7 +5133,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -5336,7 +5339,7 @@
         <v>116</v>
       </c>
       <c r="P22" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5542,7 +5545,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -5748,7 +5751,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6160,7 +6163,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6984,7 +6987,7 @@
         <v>123</v>
       </c>
       <c r="P30" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7190,7 +7193,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7602,7 +7605,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -8220,7 +8223,7 @@
         <v>127</v>
       </c>
       <c r="P36" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q36">
         <v>2.4</v>
@@ -8426,7 +8429,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8916,7 +8919,7 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ39">
         <v>2.33</v>
@@ -9044,7 +9047,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9456,7 +9459,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -9537,7 +9540,7 @@
         <v>1</v>
       </c>
       <c r="AQ42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR42">
         <v>1.41</v>
@@ -9868,7 +9871,7 @@
         <v>109</v>
       </c>
       <c r="P44" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10280,7 +10283,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10486,7 +10489,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10692,7 +10695,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11516,7 +11519,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11722,7 +11725,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -11928,7 +11931,7 @@
         <v>109</v>
       </c>
       <c r="P54" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12134,7 +12137,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -12546,7 +12549,7 @@
         <v>119</v>
       </c>
       <c r="P57" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -12752,7 +12755,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -12958,7 +12961,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13164,7 +13167,7 @@
         <v>143</v>
       </c>
       <c r="P60" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13370,7 +13373,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -13576,7 +13579,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -13782,7 +13785,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -13988,7 +13991,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -14606,7 +14609,7 @@
         <v>148</v>
       </c>
       <c r="P67" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15018,7 +15021,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15430,7 +15433,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15636,7 +15639,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16048,7 +16051,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16205,6 +16208,212 @@
       </c>
       <c r="BP74">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="75" spans="1:68">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>7781148</v>
+      </c>
+      <c r="C75" t="s">
+        <v>68</v>
+      </c>
+      <c r="D75" t="s">
+        <v>69</v>
+      </c>
+      <c r="E75" s="2">
+        <v>45739.70833333334</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75" t="s">
+        <v>77</v>
+      </c>
+      <c r="H75" t="s">
+        <v>94</v>
+      </c>
+      <c r="I75">
+        <v>2</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
+      </c>
+      <c r="K75">
+        <v>3</v>
+      </c>
+      <c r="L75">
+        <v>2</v>
+      </c>
+      <c r="M75">
+        <v>1</v>
+      </c>
+      <c r="N75">
+        <v>3</v>
+      </c>
+      <c r="O75" t="s">
+        <v>152</v>
+      </c>
+      <c r="P75" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>0</v>
+      </c>
+      <c r="T75">
+        <v>0</v>
+      </c>
+      <c r="U75">
+        <v>0</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0</v>
+      </c>
+      <c r="X75">
+        <v>0</v>
+      </c>
+      <c r="Y75">
+        <v>0</v>
+      </c>
+      <c r="Z75">
+        <v>1.97</v>
+      </c>
+      <c r="AA75">
+        <v>3.71</v>
+      </c>
+      <c r="AB75">
+        <v>3.41</v>
+      </c>
+      <c r="AC75">
+        <v>0</v>
+      </c>
+      <c r="AD75">
+        <v>0</v>
+      </c>
+      <c r="AE75">
+        <v>0</v>
+      </c>
+      <c r="AF75">
+        <v>0</v>
+      </c>
+      <c r="AG75">
+        <v>1.83</v>
+      </c>
+      <c r="AH75">
+        <v>1.89</v>
+      </c>
+      <c r="AI75">
+        <v>0</v>
+      </c>
+      <c r="AJ75">
+        <v>0</v>
+      </c>
+      <c r="AK75">
+        <v>0</v>
+      </c>
+      <c r="AL75">
+        <v>0</v>
+      </c>
+      <c r="AM75">
+        <v>0</v>
+      </c>
+      <c r="AN75">
+        <v>1.5</v>
+      </c>
+      <c r="AO75">
+        <v>3</v>
+      </c>
+      <c r="AP75">
+        <v>2</v>
+      </c>
+      <c r="AQ75">
+        <v>2</v>
+      </c>
+      <c r="AR75">
+        <v>1.74</v>
+      </c>
+      <c r="AS75">
+        <v>1.53</v>
+      </c>
+      <c r="AT75">
+        <v>3.27</v>
+      </c>
+      <c r="AU75">
+        <v>-1</v>
+      </c>
+      <c r="AV75">
+        <v>-1</v>
+      </c>
+      <c r="AW75">
+        <v>-1</v>
+      </c>
+      <c r="AX75">
+        <v>-1</v>
+      </c>
+      <c r="AY75">
+        <v>-1</v>
+      </c>
+      <c r="AZ75">
+        <v>-1</v>
+      </c>
+      <c r="BA75">
+        <v>-1</v>
+      </c>
+      <c r="BB75">
+        <v>-1</v>
+      </c>
+      <c r="BC75">
+        <v>-1</v>
+      </c>
+      <c r="BD75">
+        <v>0</v>
+      </c>
+      <c r="BE75">
+        <v>0</v>
+      </c>
+      <c r="BF75">
+        <v>0</v>
+      </c>
+      <c r="BG75">
+        <v>0</v>
+      </c>
+      <c r="BH75">
+        <v>0</v>
+      </c>
+      <c r="BI75">
+        <v>0</v>
+      </c>
+      <c r="BJ75">
+        <v>0</v>
+      </c>
+      <c r="BK75">
+        <v>0</v>
+      </c>
+      <c r="BL75">
+        <v>0</v>
+      </c>
+      <c r="BM75">
+        <v>0</v>
+      </c>
+      <c r="BN75">
+        <v>0</v>
+      </c>
+      <c r="BO75">
+        <v>0</v>
+      </c>
+      <c r="BP75">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14723,10 +14723,10 @@
         <v>1</v>
       </c>
       <c r="BB67">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC67">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD67">
         <v>1.61</v>
@@ -14926,13 +14926,13 @@
         <v>10</v>
       </c>
       <c r="BA68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB68">
         <v>5</v>
       </c>
       <c r="BC68">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD68">
         <v>1.6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -16350,31 +16350,31 @@
         <v>3.27</v>
       </c>
       <c r="AU75">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AV75">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW75">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AX75">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AY75">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AZ75">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="BA75">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BB75">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BC75">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="BD75">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="199">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -475,6 +475,12 @@
     <t>['10', '19']</t>
   </si>
   <si>
+    <t>['28', '90+7']</t>
+  </si>
+  <si>
+    <t>['77', '81']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -602,6 +608,9 @@
   </si>
   <si>
     <t>['1', '62', '90+4']</t>
+  </si>
+  <si>
+    <t>['45+2']</t>
   </si>
 </sst>
 </file>
@@ -963,7 +972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP75"/>
+  <dimension ref="A1:BP78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1425,7 +1434,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -1631,7 +1640,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1918,7 +1927,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ5">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2043,7 +2052,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2249,7 +2258,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2455,7 +2464,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2867,7 +2876,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -3691,7 +3700,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -3772,7 +3781,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ14">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3897,7 +3906,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -3978,7 +3987,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ15">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4103,7 +4112,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4721,7 +4730,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -4799,7 +4808,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ19">
         <v>2</v>
@@ -5133,7 +5142,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -5339,7 +5348,7 @@
         <v>116</v>
       </c>
       <c r="P22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5545,7 +5554,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -5751,7 +5760,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6163,7 +6172,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6241,7 +6250,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ26">
         <v>2.33</v>
@@ -6987,7 +6996,7 @@
         <v>123</v>
       </c>
       <c r="P30" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7193,7 +7202,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7605,7 +7614,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -7892,7 +7901,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ34">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR34">
         <v>1.85</v>
@@ -8223,7 +8232,7 @@
         <v>127</v>
       </c>
       <c r="P36" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q36">
         <v>2.4</v>
@@ -8429,7 +8438,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8507,7 +8516,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ37">
         <v>3</v>
@@ -9047,7 +9056,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9459,7 +9468,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -9871,7 +9880,7 @@
         <v>109</v>
       </c>
       <c r="P44" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10158,7 +10167,7 @@
         <v>2</v>
       </c>
       <c r="AQ45">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR45">
         <v>1.62</v>
@@ -10283,7 +10292,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10489,7 +10498,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10567,7 +10576,7 @@
         <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ47">
         <v>2.25</v>
@@ -10695,7 +10704,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11519,7 +11528,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11725,7 +11734,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -11931,7 +11940,7 @@
         <v>109</v>
       </c>
       <c r="P54" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12012,7 +12021,7 @@
         <v>0</v>
       </c>
       <c r="AQ54">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AR54">
         <v>1.95</v>
@@ -12137,7 +12146,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -12549,7 +12558,7 @@
         <v>119</v>
       </c>
       <c r="P57" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -12755,7 +12764,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -12961,7 +12970,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13167,7 +13176,7 @@
         <v>143</v>
       </c>
       <c r="P60" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13373,7 +13382,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -13579,7 +13588,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -13785,7 +13794,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -13991,7 +14000,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -14609,7 +14618,7 @@
         <v>148</v>
       </c>
       <c r="P67" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15021,7 +15030,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15433,7 +15442,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15511,7 +15520,7 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ71">
         <v>1.5</v>
@@ -15639,7 +15648,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16051,7 +16060,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16414,6 +16423,624 @@
       </c>
       <c r="BP75">
         <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:68">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>7781149</v>
+      </c>
+      <c r="C76" t="s">
+        <v>68</v>
+      </c>
+      <c r="D76" t="s">
+        <v>69</v>
+      </c>
+      <c r="E76" s="2">
+        <v>45745.64583333334</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76" t="s">
+        <v>87</v>
+      </c>
+      <c r="H76" t="s">
+        <v>88</v>
+      </c>
+      <c r="I76">
+        <v>1</v>
+      </c>
+      <c r="J76">
+        <v>1</v>
+      </c>
+      <c r="K76">
+        <v>2</v>
+      </c>
+      <c r="L76">
+        <v>2</v>
+      </c>
+      <c r="M76">
+        <v>1</v>
+      </c>
+      <c r="N76">
+        <v>3</v>
+      </c>
+      <c r="O76" t="s">
+        <v>153</v>
+      </c>
+      <c r="P76" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q76">
+        <v>3.6</v>
+      </c>
+      <c r="R76">
+        <v>2.05</v>
+      </c>
+      <c r="S76">
+        <v>3.2</v>
+      </c>
+      <c r="T76">
+        <v>1.44</v>
+      </c>
+      <c r="U76">
+        <v>2.63</v>
+      </c>
+      <c r="V76">
+        <v>3.25</v>
+      </c>
+      <c r="W76">
+        <v>1.33</v>
+      </c>
+      <c r="X76">
+        <v>9</v>
+      </c>
+      <c r="Y76">
+        <v>1.07</v>
+      </c>
+      <c r="Z76">
+        <v>2.85</v>
+      </c>
+      <c r="AA76">
+        <v>3.09</v>
+      </c>
+      <c r="AB76">
+        <v>2.53</v>
+      </c>
+      <c r="AC76">
+        <v>1.07</v>
+      </c>
+      <c r="AD76">
+        <v>8</v>
+      </c>
+      <c r="AE76">
+        <v>1.35</v>
+      </c>
+      <c r="AF76">
+        <v>3.1</v>
+      </c>
+      <c r="AG76">
+        <v>1.91</v>
+      </c>
+      <c r="AH76">
+        <v>1.8</v>
+      </c>
+      <c r="AI76">
+        <v>1.8</v>
+      </c>
+      <c r="AJ76">
+        <v>1.95</v>
+      </c>
+      <c r="AK76">
+        <v>1.46</v>
+      </c>
+      <c r="AL76">
+        <v>1.32</v>
+      </c>
+      <c r="AM76">
+        <v>1.47</v>
+      </c>
+      <c r="AN76">
+        <v>0</v>
+      </c>
+      <c r="AO76">
+        <v>0.5</v>
+      </c>
+      <c r="AP76">
+        <v>1</v>
+      </c>
+      <c r="AQ76">
+        <v>0.33</v>
+      </c>
+      <c r="AR76">
+        <v>0.97</v>
+      </c>
+      <c r="AS76">
+        <v>1.23</v>
+      </c>
+      <c r="AT76">
+        <v>2.2</v>
+      </c>
+      <c r="AU76">
+        <v>7</v>
+      </c>
+      <c r="AV76">
+        <v>5</v>
+      </c>
+      <c r="AW76">
+        <v>7</v>
+      </c>
+      <c r="AX76">
+        <v>8</v>
+      </c>
+      <c r="AY76">
+        <v>18</v>
+      </c>
+      <c r="AZ76">
+        <v>18</v>
+      </c>
+      <c r="BA76">
+        <v>3</v>
+      </c>
+      <c r="BB76">
+        <v>4</v>
+      </c>
+      <c r="BC76">
+        <v>7</v>
+      </c>
+      <c r="BD76">
+        <v>1.95</v>
+      </c>
+      <c r="BE76">
+        <v>6.75</v>
+      </c>
+      <c r="BF76">
+        <v>2.02</v>
+      </c>
+      <c r="BG76">
+        <v>1.34</v>
+      </c>
+      <c r="BH76">
+        <v>2.9</v>
+      </c>
+      <c r="BI76">
+        <v>1.57</v>
+      </c>
+      <c r="BJ76">
+        <v>2.2</v>
+      </c>
+      <c r="BK76">
+        <v>1.94</v>
+      </c>
+      <c r="BL76">
+        <v>1.76</v>
+      </c>
+      <c r="BM76">
+        <v>2.43</v>
+      </c>
+      <c r="BN76">
+        <v>1.48</v>
+      </c>
+      <c r="BO76">
+        <v>3.15</v>
+      </c>
+      <c r="BP76">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="77" spans="1:68">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>7781150</v>
+      </c>
+      <c r="C77" t="s">
+        <v>68</v>
+      </c>
+      <c r="D77" t="s">
+        <v>69</v>
+      </c>
+      <c r="E77" s="2">
+        <v>45745.64583333334</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77" t="s">
+        <v>98</v>
+      </c>
+      <c r="H77" t="s">
+        <v>95</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77" t="s">
+        <v>109</v>
+      </c>
+      <c r="P77" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q77">
+        <v>3.4</v>
+      </c>
+      <c r="R77">
+        <v>2.2</v>
+      </c>
+      <c r="S77">
+        <v>3.1</v>
+      </c>
+      <c r="T77">
+        <v>1.4</v>
+      </c>
+      <c r="U77">
+        <v>2.75</v>
+      </c>
+      <c r="V77">
+        <v>2.75</v>
+      </c>
+      <c r="W77">
+        <v>1.4</v>
+      </c>
+      <c r="X77">
+        <v>8</v>
+      </c>
+      <c r="Y77">
+        <v>1.08</v>
+      </c>
+      <c r="Z77">
+        <v>2.68</v>
+      </c>
+      <c r="AA77">
+        <v>3.33</v>
+      </c>
+      <c r="AB77">
+        <v>2.52</v>
+      </c>
+      <c r="AC77">
+        <v>1.05</v>
+      </c>
+      <c r="AD77">
+        <v>9</v>
+      </c>
+      <c r="AE77">
+        <v>1.3</v>
+      </c>
+      <c r="AF77">
+        <v>3.45</v>
+      </c>
+      <c r="AG77">
+        <v>1.87</v>
+      </c>
+      <c r="AH77">
+        <v>1.87</v>
+      </c>
+      <c r="AI77">
+        <v>1.7</v>
+      </c>
+      <c r="AJ77">
+        <v>2.05</v>
+      </c>
+      <c r="AK77">
+        <v>1.58</v>
+      </c>
+      <c r="AL77">
+        <v>1.29</v>
+      </c>
+      <c r="AM77">
+        <v>1.39</v>
+      </c>
+      <c r="AN77">
+        <v>0</v>
+      </c>
+      <c r="AO77">
+        <v>3</v>
+      </c>
+      <c r="AP77">
+        <v>0.5</v>
+      </c>
+      <c r="AQ77">
+        <v>2.33</v>
+      </c>
+      <c r="AR77">
+        <v>0.9</v>
+      </c>
+      <c r="AS77">
+        <v>2.01</v>
+      </c>
+      <c r="AT77">
+        <v>2.91</v>
+      </c>
+      <c r="AU77">
+        <v>6</v>
+      </c>
+      <c r="AV77">
+        <v>7</v>
+      </c>
+      <c r="AW77">
+        <v>1</v>
+      </c>
+      <c r="AX77">
+        <v>9</v>
+      </c>
+      <c r="AY77">
+        <v>9</v>
+      </c>
+      <c r="AZ77">
+        <v>16</v>
+      </c>
+      <c r="BA77">
+        <v>3</v>
+      </c>
+      <c r="BB77">
+        <v>12</v>
+      </c>
+      <c r="BC77">
+        <v>15</v>
+      </c>
+      <c r="BD77">
+        <v>1.84</v>
+      </c>
+      <c r="BE77">
+        <v>6.4</v>
+      </c>
+      <c r="BF77">
+        <v>2.17</v>
+      </c>
+      <c r="BG77">
+        <v>1.34</v>
+      </c>
+      <c r="BH77">
+        <v>2.9</v>
+      </c>
+      <c r="BI77">
+        <v>1.58</v>
+      </c>
+      <c r="BJ77">
+        <v>2.2</v>
+      </c>
+      <c r="BK77">
+        <v>1.94</v>
+      </c>
+      <c r="BL77">
+        <v>1.76</v>
+      </c>
+      <c r="BM77">
+        <v>2.43</v>
+      </c>
+      <c r="BN77">
+        <v>1.48</v>
+      </c>
+      <c r="BO77">
+        <v>3.15</v>
+      </c>
+      <c r="BP77">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="78" spans="1:68">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>7781151</v>
+      </c>
+      <c r="C78" t="s">
+        <v>68</v>
+      </c>
+      <c r="D78" t="s">
+        <v>69</v>
+      </c>
+      <c r="E78" s="2">
+        <v>45745.72916666666</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78" t="s">
+        <v>93</v>
+      </c>
+      <c r="H78" t="s">
+        <v>85</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>2</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>2</v>
+      </c>
+      <c r="O78" t="s">
+        <v>154</v>
+      </c>
+      <c r="P78" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q78">
+        <v>3</v>
+      </c>
+      <c r="R78">
+        <v>2.25</v>
+      </c>
+      <c r="S78">
+        <v>3.4</v>
+      </c>
+      <c r="T78">
+        <v>1.33</v>
+      </c>
+      <c r="U78">
+        <v>3.25</v>
+      </c>
+      <c r="V78">
+        <v>2.63</v>
+      </c>
+      <c r="W78">
+        <v>1.44</v>
+      </c>
+      <c r="X78">
+        <v>6.5</v>
+      </c>
+      <c r="Y78">
+        <v>1.11</v>
+      </c>
+      <c r="Z78">
+        <v>2.29</v>
+      </c>
+      <c r="AA78">
+        <v>3.47</v>
+      </c>
+      <c r="AB78">
+        <v>2.9</v>
+      </c>
+      <c r="AC78">
+        <v>1.05</v>
+      </c>
+      <c r="AD78">
+        <v>9.5</v>
+      </c>
+      <c r="AE78">
+        <v>1.25</v>
+      </c>
+      <c r="AF78">
+        <v>3.95</v>
+      </c>
+      <c r="AG78">
+        <v>1.6</v>
+      </c>
+      <c r="AH78">
+        <v>2.2</v>
+      </c>
+      <c r="AI78">
+        <v>1.57</v>
+      </c>
+      <c r="AJ78">
+        <v>2.25</v>
+      </c>
+      <c r="AK78">
+        <v>1.35</v>
+      </c>
+      <c r="AL78">
+        <v>1.31</v>
+      </c>
+      <c r="AM78">
+        <v>1.61</v>
+      </c>
+      <c r="AN78">
+        <v>0.5</v>
+      </c>
+      <c r="AO78">
+        <v>0.5</v>
+      </c>
+      <c r="AP78">
+        <v>1.33</v>
+      </c>
+      <c r="AQ78">
+        <v>0.33</v>
+      </c>
+      <c r="AR78">
+        <v>1.49</v>
+      </c>
+      <c r="AS78">
+        <v>1.16</v>
+      </c>
+      <c r="AT78">
+        <v>2.65</v>
+      </c>
+      <c r="AU78">
+        <v>7</v>
+      </c>
+      <c r="AV78">
+        <v>4</v>
+      </c>
+      <c r="AW78">
+        <v>16</v>
+      </c>
+      <c r="AX78">
+        <v>6</v>
+      </c>
+      <c r="AY78">
+        <v>25</v>
+      </c>
+      <c r="AZ78">
+        <v>12</v>
+      </c>
+      <c r="BA78">
+        <v>6</v>
+      </c>
+      <c r="BB78">
+        <v>3</v>
+      </c>
+      <c r="BC78">
+        <v>9</v>
+      </c>
+      <c r="BD78">
+        <v>1.66</v>
+      </c>
+      <c r="BE78">
+        <v>6.75</v>
+      </c>
+      <c r="BF78">
+        <v>2.48</v>
+      </c>
+      <c r="BG78">
+        <v>1.3</v>
+      </c>
+      <c r="BH78">
+        <v>3.05</v>
+      </c>
+      <c r="BI78">
+        <v>1.54</v>
+      </c>
+      <c r="BJ78">
+        <v>2.28</v>
+      </c>
+      <c r="BK78">
+        <v>1.88</v>
+      </c>
+      <c r="BL78">
+        <v>1.81</v>
+      </c>
+      <c r="BM78">
+        <v>2.38</v>
+      </c>
+      <c r="BN78">
+        <v>1.5</v>
+      </c>
+      <c r="BO78">
+        <v>3.05</v>
+      </c>
+      <c r="BP78">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="212">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -481,6 +481,33 @@
     <t>['77', '81']</t>
   </si>
   <si>
+    <t>['23', '57']</t>
+  </si>
+  <si>
+    <t>['13']</t>
+  </si>
+  <si>
+    <t>['42', '62', '75', '84']</t>
+  </si>
+  <si>
+    <t>['40']</t>
+  </si>
+  <si>
+    <t>['37', '39']</t>
+  </si>
+  <si>
+    <t>['30', '55']</t>
+  </si>
+  <si>
+    <t>['39']</t>
+  </si>
+  <si>
+    <t>['21', '33', '40']</t>
+  </si>
+  <si>
+    <t>['32']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -526,9 +553,6 @@
     <t>['43', '45', '68']</t>
   </si>
   <si>
-    <t>['39']</t>
-  </si>
-  <si>
     <t>['6', '37', '45+2', '79']</t>
   </si>
   <si>
@@ -547,9 +571,6 @@
     <t>['43', '90+1', '90+6']</t>
   </si>
   <si>
-    <t>['32']</t>
-  </si>
-  <si>
     <t>['44', '49', '84']</t>
   </si>
   <si>
@@ -571,9 +592,6 @@
     <t>['1', '45+5']</t>
   </si>
   <si>
-    <t>['13']</t>
-  </si>
-  <si>
     <t>['38', '71']</t>
   </si>
   <si>
@@ -611,6 +629,27 @@
   </si>
   <si>
     <t>['45+2']</t>
+  </si>
+  <si>
+    <t>['80']</t>
+  </si>
+  <si>
+    <t>['16', '65']</t>
+  </si>
+  <si>
+    <t>['15', '48', '51']</t>
+  </si>
+  <si>
+    <t>['50']</t>
+  </si>
+  <si>
+    <t>['43', '90+1']</t>
+  </si>
+  <si>
+    <t>['76', '90']</t>
+  </si>
+  <si>
+    <t>['43', '45+5']</t>
   </si>
 </sst>
 </file>
@@ -972,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP78"/>
+  <dimension ref="A1:BP88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1434,7 +1473,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -1512,10 +1551,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ3">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1640,7 +1679,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1718,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ4">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2052,7 +2091,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2258,7 +2297,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2336,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ7">
         <v>0.25</v>
@@ -2464,7 +2503,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2545,7 +2584,7 @@
         <v>2</v>
       </c>
       <c r="AQ8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2876,7 +2915,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -3160,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ11">
         <v>0.5</v>
@@ -3575,7 +3614,7 @@
         <v>1</v>
       </c>
       <c r="AQ13">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3700,7 +3739,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -3906,7 +3945,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4112,7 +4151,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4605,7 +4644,7 @@
         <v>1</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4730,7 +4769,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -4811,7 +4850,7 @@
         <v>1</v>
       </c>
       <c r="AQ19">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5142,7 +5181,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -5348,7 +5387,7 @@
         <v>116</v>
       </c>
       <c r="P22" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5429,7 +5468,7 @@
         <v>2</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5554,7 +5593,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -5760,7 +5799,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6044,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ25">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6172,7 +6211,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6459,7 +6498,7 @@
         <v>2</v>
       </c>
       <c r="AQ27">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR27">
         <v>1.64</v>
@@ -6868,7 +6907,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AQ29">
         <v>1.33</v>
@@ -6996,7 +7035,7 @@
         <v>123</v>
       </c>
       <c r="P30" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="Q30">
         <v>2.6</v>
@@ -7202,7 +7241,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7614,7 +7653,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -7695,7 +7734,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ33">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR33">
         <v>2.47</v>
@@ -7898,7 +7937,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ34">
         <v>0.33</v>
@@ -8232,7 +8271,7 @@
         <v>127</v>
       </c>
       <c r="P36" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="Q36">
         <v>2.4</v>
@@ -8310,7 +8349,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ36">
         <v>0</v>
@@ -8438,7 +8477,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8519,7 +8558,7 @@
         <v>1</v>
       </c>
       <c r="AQ37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR37">
         <v>0.85</v>
@@ -8725,7 +8764,7 @@
         <v>3</v>
       </c>
       <c r="AQ38">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR38">
         <v>0</v>
@@ -9056,7 +9095,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9134,7 +9173,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ40">
         <v>2.25</v>
@@ -9340,7 +9379,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ41">
         <v>1.5</v>
@@ -9468,7 +9507,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -9755,7 +9794,7 @@
         <v>2</v>
       </c>
       <c r="AQ43">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AR43">
         <v>1.87</v>
@@ -9880,7 +9919,7 @@
         <v>109</v>
       </c>
       <c r="P44" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10164,7 +10203,7 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ45">
         <v>0.33</v>
@@ -10292,7 +10331,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10498,7 +10537,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10704,7 +10743,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -10785,7 +10824,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ48">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR48">
         <v>1.51</v>
@@ -11197,7 +11236,7 @@
         <v>3</v>
       </c>
       <c r="AQ50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR50">
         <v>1.3</v>
@@ -11400,10 +11439,10 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ51">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AR51">
         <v>1.36</v>
@@ -11528,7 +11567,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11734,7 +11773,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -11940,7 +11979,7 @@
         <v>109</v>
       </c>
       <c r="P54" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12018,7 +12057,7 @@
         <v>3</v>
       </c>
       <c r="AP54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ54">
         <v>2.33</v>
@@ -12146,7 +12185,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -12227,7 +12266,7 @@
         <v>0</v>
       </c>
       <c r="AQ55">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR55">
         <v>1.22</v>
@@ -12433,7 +12472,7 @@
         <v>2</v>
       </c>
       <c r="AQ56">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR56">
         <v>2.14</v>
@@ -12558,7 +12597,7 @@
         <v>119</v>
       </c>
       <c r="P57" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -12636,10 +12675,10 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AQ57">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AR57">
         <v>1.55</v>
@@ -12764,7 +12803,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -12970,7 +13009,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13176,7 +13215,7 @@
         <v>143</v>
       </c>
       <c r="P60" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13382,7 +13421,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -13460,7 +13499,7 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ61">
         <v>3</v>
@@ -13588,7 +13627,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -13794,7 +13833,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -13872,7 +13911,7 @@
         <v>0.5</v>
       </c>
       <c r="AP63">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ63">
         <v>0.67</v>
@@ -14000,7 +14039,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -14287,7 +14326,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ65">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR65">
         <v>1.71</v>
@@ -14618,7 +14657,7 @@
         <v>148</v>
       </c>
       <c r="P67" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15030,7 +15069,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15111,7 +15150,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ69">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR69">
         <v>1.7</v>
@@ -15314,10 +15353,10 @@
         <v>0.25</v>
       </c>
       <c r="AP70">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ70">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AR70">
         <v>1.96</v>
@@ -15442,7 +15481,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15648,7 +15687,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16060,7 +16099,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16472,7 +16511,7 @@
         <v>153</v>
       </c>
       <c r="P76" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="Q76">
         <v>3.6</v>
@@ -17041,6 +17080,2066 @@
       </c>
       <c r="BP78">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="79" spans="1:68">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>7781154</v>
+      </c>
+      <c r="C79" t="s">
+        <v>68</v>
+      </c>
+      <c r="D79" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79" s="2">
+        <v>45745.85416666666</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79" t="s">
+        <v>71</v>
+      </c>
+      <c r="H79" t="s">
+        <v>89</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>1</v>
+      </c>
+      <c r="L79">
+        <v>2</v>
+      </c>
+      <c r="M79">
+        <v>1</v>
+      </c>
+      <c r="N79">
+        <v>3</v>
+      </c>
+      <c r="O79" t="s">
+        <v>155</v>
+      </c>
+      <c r="P79" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q79">
+        <v>2.1</v>
+      </c>
+      <c r="R79">
+        <v>2.6</v>
+      </c>
+      <c r="S79">
+        <v>4.75</v>
+      </c>
+      <c r="T79">
+        <v>1.25</v>
+      </c>
+      <c r="U79">
+        <v>3.75</v>
+      </c>
+      <c r="V79">
+        <v>2.2</v>
+      </c>
+      <c r="W79">
+        <v>1.62</v>
+      </c>
+      <c r="X79">
+        <v>5</v>
+      </c>
+      <c r="Y79">
+        <v>1.17</v>
+      </c>
+      <c r="Z79">
+        <v>1.57</v>
+      </c>
+      <c r="AA79">
+        <v>4.7</v>
+      </c>
+      <c r="AB79">
+        <v>4.6</v>
+      </c>
+      <c r="AC79">
+        <v>1.01</v>
+      </c>
+      <c r="AD79">
+        <v>17</v>
+      </c>
+      <c r="AE79">
+        <v>1.14</v>
+      </c>
+      <c r="AF79">
+        <v>5.5</v>
+      </c>
+      <c r="AG79">
+        <v>1.45</v>
+      </c>
+      <c r="AH79">
+        <v>2.63</v>
+      </c>
+      <c r="AI79">
+        <v>1.53</v>
+      </c>
+      <c r="AJ79">
+        <v>2.38</v>
+      </c>
+      <c r="AK79">
+        <v>1.12</v>
+      </c>
+      <c r="AL79">
+        <v>1.19</v>
+      </c>
+      <c r="AM79">
+        <v>2.65</v>
+      </c>
+      <c r="AN79">
+        <v>2</v>
+      </c>
+      <c r="AO79">
+        <v>3</v>
+      </c>
+      <c r="AP79">
+        <v>2.33</v>
+      </c>
+      <c r="AQ79">
+        <v>2</v>
+      </c>
+      <c r="AR79">
+        <v>1.15</v>
+      </c>
+      <c r="AS79">
+        <v>1.73</v>
+      </c>
+      <c r="AT79">
+        <v>2.88</v>
+      </c>
+      <c r="AU79">
+        <v>4</v>
+      </c>
+      <c r="AV79">
+        <v>7</v>
+      </c>
+      <c r="AW79">
+        <v>4</v>
+      </c>
+      <c r="AX79">
+        <v>11</v>
+      </c>
+      <c r="AY79">
+        <v>10</v>
+      </c>
+      <c r="AZ79">
+        <v>21</v>
+      </c>
+      <c r="BA79">
+        <v>3</v>
+      </c>
+      <c r="BB79">
+        <v>5</v>
+      </c>
+      <c r="BC79">
+        <v>8</v>
+      </c>
+      <c r="BD79">
+        <v>1.58</v>
+      </c>
+      <c r="BE79">
+        <v>6.75</v>
+      </c>
+      <c r="BF79">
+        <v>2.63</v>
+      </c>
+      <c r="BG79">
+        <v>1.27</v>
+      </c>
+      <c r="BH79">
+        <v>3.3</v>
+      </c>
+      <c r="BI79">
+        <v>1.47</v>
+      </c>
+      <c r="BJ79">
+        <v>2.48</v>
+      </c>
+      <c r="BK79">
+        <v>1.74</v>
+      </c>
+      <c r="BL79">
+        <v>1.96</v>
+      </c>
+      <c r="BM79">
+        <v>2.15</v>
+      </c>
+      <c r="BN79">
+        <v>1.61</v>
+      </c>
+      <c r="BO79">
+        <v>2.7</v>
+      </c>
+      <c r="BP79">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="80" spans="1:68">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>7781153</v>
+      </c>
+      <c r="C80" t="s">
+        <v>68</v>
+      </c>
+      <c r="D80" t="s">
+        <v>69</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45745.85416666666</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80" t="s">
+        <v>75</v>
+      </c>
+      <c r="H80" t="s">
+        <v>74</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+      <c r="J80">
+        <v>1</v>
+      </c>
+      <c r="K80">
+        <v>2</v>
+      </c>
+      <c r="L80">
+        <v>1</v>
+      </c>
+      <c r="M80">
+        <v>2</v>
+      </c>
+      <c r="N80">
+        <v>3</v>
+      </c>
+      <c r="O80" t="s">
+        <v>156</v>
+      </c>
+      <c r="P80" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q80">
+        <v>3</v>
+      </c>
+      <c r="R80">
+        <v>2.3</v>
+      </c>
+      <c r="S80">
+        <v>3.1</v>
+      </c>
+      <c r="T80">
+        <v>1.3</v>
+      </c>
+      <c r="U80">
+        <v>3.4</v>
+      </c>
+      <c r="V80">
+        <v>2.5</v>
+      </c>
+      <c r="W80">
+        <v>1.5</v>
+      </c>
+      <c r="X80">
+        <v>6</v>
+      </c>
+      <c r="Y80">
+        <v>1.13</v>
+      </c>
+      <c r="Z80">
+        <v>2.32</v>
+      </c>
+      <c r="AA80">
+        <v>3.5</v>
+      </c>
+      <c r="AB80">
+        <v>2.83</v>
+      </c>
+      <c r="AC80">
+        <v>1.04</v>
+      </c>
+      <c r="AD80">
+        <v>10</v>
+      </c>
+      <c r="AE80">
+        <v>1.2</v>
+      </c>
+      <c r="AF80">
+        <v>4.33</v>
+      </c>
+      <c r="AG80">
+        <v>1.6</v>
+      </c>
+      <c r="AH80">
+        <v>2.25</v>
+      </c>
+      <c r="AI80">
+        <v>1.53</v>
+      </c>
+      <c r="AJ80">
+        <v>2.38</v>
+      </c>
+      <c r="AK80">
+        <v>1.49</v>
+      </c>
+      <c r="AL80">
+        <v>1.27</v>
+      </c>
+      <c r="AM80">
+        <v>1.51</v>
+      </c>
+      <c r="AN80">
+        <v>1.67</v>
+      </c>
+      <c r="AO80">
+        <v>2</v>
+      </c>
+      <c r="AP80">
+        <v>1.25</v>
+      </c>
+      <c r="AQ80">
+        <v>2.33</v>
+      </c>
+      <c r="AR80">
+        <v>1.6</v>
+      </c>
+      <c r="AS80">
+        <v>1.05</v>
+      </c>
+      <c r="AT80">
+        <v>2.65</v>
+      </c>
+      <c r="AU80">
+        <v>4</v>
+      </c>
+      <c r="AV80">
+        <v>8</v>
+      </c>
+      <c r="AW80">
+        <v>5</v>
+      </c>
+      <c r="AX80">
+        <v>2</v>
+      </c>
+      <c r="AY80">
+        <v>10</v>
+      </c>
+      <c r="AZ80">
+        <v>11</v>
+      </c>
+      <c r="BA80">
+        <v>3</v>
+      </c>
+      <c r="BB80">
+        <v>4</v>
+      </c>
+      <c r="BC80">
+        <v>7</v>
+      </c>
+      <c r="BD80">
+        <v>1.76</v>
+      </c>
+      <c r="BE80">
+        <v>6.4</v>
+      </c>
+      <c r="BF80">
+        <v>2.28</v>
+      </c>
+      <c r="BG80">
+        <v>1.38</v>
+      </c>
+      <c r="BH80">
+        <v>2.7</v>
+      </c>
+      <c r="BI80">
+        <v>1.65</v>
+      </c>
+      <c r="BJ80">
+        <v>2.08</v>
+      </c>
+      <c r="BK80">
+        <v>2.06</v>
+      </c>
+      <c r="BL80">
+        <v>1.66</v>
+      </c>
+      <c r="BM80">
+        <v>2.65</v>
+      </c>
+      <c r="BN80">
+        <v>1.41</v>
+      </c>
+      <c r="BO80">
+        <v>3.45</v>
+      </c>
+      <c r="BP80">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="81" spans="1:68">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>7781152</v>
+      </c>
+      <c r="C81" t="s">
+        <v>68</v>
+      </c>
+      <c r="D81" t="s">
+        <v>69</v>
+      </c>
+      <c r="E81" s="2">
+        <v>45745.85416666666</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81" t="s">
+        <v>72</v>
+      </c>
+      <c r="H81" t="s">
+        <v>96</v>
+      </c>
+      <c r="I81">
+        <v>1</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="K81">
+        <v>2</v>
+      </c>
+      <c r="L81">
+        <v>4</v>
+      </c>
+      <c r="M81">
+        <v>3</v>
+      </c>
+      <c r="N81">
+        <v>7</v>
+      </c>
+      <c r="O81" t="s">
+        <v>157</v>
+      </c>
+      <c r="P81" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q81">
+        <v>2.5</v>
+      </c>
+      <c r="R81">
+        <v>2.3</v>
+      </c>
+      <c r="S81">
+        <v>4</v>
+      </c>
+      <c r="T81">
+        <v>1.33</v>
+      </c>
+      <c r="U81">
+        <v>3.25</v>
+      </c>
+      <c r="V81">
+        <v>2.5</v>
+      </c>
+      <c r="W81">
+        <v>1.5</v>
+      </c>
+      <c r="X81">
+        <v>6.5</v>
+      </c>
+      <c r="Y81">
+        <v>1.11</v>
+      </c>
+      <c r="Z81">
+        <v>1.86</v>
+      </c>
+      <c r="AA81">
+        <v>3.56</v>
+      </c>
+      <c r="AB81">
+        <v>3.96</v>
+      </c>
+      <c r="AC81">
+        <v>1.04</v>
+      </c>
+      <c r="AD81">
+        <v>10</v>
+      </c>
+      <c r="AE81">
+        <v>1.22</v>
+      </c>
+      <c r="AF81">
+        <v>4.2</v>
+      </c>
+      <c r="AG81">
+        <v>1.67</v>
+      </c>
+      <c r="AH81">
+        <v>2.05</v>
+      </c>
+      <c r="AI81">
+        <v>1.57</v>
+      </c>
+      <c r="AJ81">
+        <v>2.25</v>
+      </c>
+      <c r="AK81">
+        <v>1.32</v>
+      </c>
+      <c r="AL81">
+        <v>1.31</v>
+      </c>
+      <c r="AM81">
+        <v>1.66</v>
+      </c>
+      <c r="AN81">
+        <v>1.33</v>
+      </c>
+      <c r="AO81">
+        <v>0.67</v>
+      </c>
+      <c r="AP81">
+        <v>1.75</v>
+      </c>
+      <c r="AQ81">
+        <v>0.5</v>
+      </c>
+      <c r="AR81">
+        <v>1.62</v>
+      </c>
+      <c r="AS81">
+        <v>0.98</v>
+      </c>
+      <c r="AT81">
+        <v>2.6</v>
+      </c>
+      <c r="AU81">
+        <v>8</v>
+      </c>
+      <c r="AV81">
+        <v>6</v>
+      </c>
+      <c r="AW81">
+        <v>8</v>
+      </c>
+      <c r="AX81">
+        <v>3</v>
+      </c>
+      <c r="AY81">
+        <v>17</v>
+      </c>
+      <c r="AZ81">
+        <v>9</v>
+      </c>
+      <c r="BA81">
+        <v>7</v>
+      </c>
+      <c r="BB81">
+        <v>1</v>
+      </c>
+      <c r="BC81">
+        <v>8</v>
+      </c>
+      <c r="BD81">
+        <v>1.54</v>
+      </c>
+      <c r="BE81">
+        <v>6.75</v>
+      </c>
+      <c r="BF81">
+        <v>2.7</v>
+      </c>
+      <c r="BG81">
+        <v>1.25</v>
+      </c>
+      <c r="BH81">
+        <v>3.45</v>
+      </c>
+      <c r="BI81">
+        <v>1.44</v>
+      </c>
+      <c r="BJ81">
+        <v>2.55</v>
+      </c>
+      <c r="BK81">
+        <v>1.72</v>
+      </c>
+      <c r="BL81">
+        <v>1.98</v>
+      </c>
+      <c r="BM81">
+        <v>2.12</v>
+      </c>
+      <c r="BN81">
+        <v>1.63</v>
+      </c>
+      <c r="BO81">
+        <v>2.65</v>
+      </c>
+      <c r="BP81">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:68">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>7781155</v>
+      </c>
+      <c r="C82" t="s">
+        <v>68</v>
+      </c>
+      <c r="D82" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82" s="2">
+        <v>45745.89583333334</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82" t="s">
+        <v>90</v>
+      </c>
+      <c r="H82" t="s">
+        <v>99</v>
+      </c>
+      <c r="I82">
+        <v>1</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>1</v>
+      </c>
+      <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="M82">
+        <v>1</v>
+      </c>
+      <c r="N82">
+        <v>2</v>
+      </c>
+      <c r="O82" t="s">
+        <v>158</v>
+      </c>
+      <c r="P82" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q82">
+        <v>2.1</v>
+      </c>
+      <c r="R82">
+        <v>2.5</v>
+      </c>
+      <c r="S82">
+        <v>5</v>
+      </c>
+      <c r="T82">
+        <v>1.29</v>
+      </c>
+      <c r="U82">
+        <v>3.5</v>
+      </c>
+      <c r="V82">
+        <v>2.38</v>
+      </c>
+      <c r="W82">
+        <v>1.53</v>
+      </c>
+      <c r="X82">
+        <v>5.5</v>
+      </c>
+      <c r="Y82">
+        <v>1.14</v>
+      </c>
+      <c r="Z82">
+        <v>1.56</v>
+      </c>
+      <c r="AA82">
+        <v>4.2</v>
+      </c>
+      <c r="AB82">
+        <v>5.2</v>
+      </c>
+      <c r="AC82">
+        <v>0</v>
+      </c>
+      <c r="AD82">
+        <v>0</v>
+      </c>
+      <c r="AE82">
+        <v>0</v>
+      </c>
+      <c r="AF82">
+        <v>0</v>
+      </c>
+      <c r="AG82">
+        <v>1.6</v>
+      </c>
+      <c r="AH82">
+        <v>2.2</v>
+      </c>
+      <c r="AI82">
+        <v>1.67</v>
+      </c>
+      <c r="AJ82">
+        <v>2.1</v>
+      </c>
+      <c r="AK82">
+        <v>0</v>
+      </c>
+      <c r="AL82">
+        <v>0</v>
+      </c>
+      <c r="AM82">
+        <v>0</v>
+      </c>
+      <c r="AN82">
+        <v>1</v>
+      </c>
+      <c r="AO82">
+        <v>0.2</v>
+      </c>
+      <c r="AP82">
+        <v>1</v>
+      </c>
+      <c r="AQ82">
+        <v>0.33</v>
+      </c>
+      <c r="AR82">
+        <v>1.1</v>
+      </c>
+      <c r="AS82">
+        <v>1.12</v>
+      </c>
+      <c r="AT82">
+        <v>2.22</v>
+      </c>
+      <c r="AU82">
+        <v>3</v>
+      </c>
+      <c r="AV82">
+        <v>7</v>
+      </c>
+      <c r="AW82">
+        <v>4</v>
+      </c>
+      <c r="AX82">
+        <v>10</v>
+      </c>
+      <c r="AY82">
+        <v>8</v>
+      </c>
+      <c r="AZ82">
+        <v>18</v>
+      </c>
+      <c r="BA82">
+        <v>2</v>
+      </c>
+      <c r="BB82">
+        <v>8</v>
+      </c>
+      <c r="BC82">
+        <v>10</v>
+      </c>
+      <c r="BD82">
+        <v>0</v>
+      </c>
+      <c r="BE82">
+        <v>0</v>
+      </c>
+      <c r="BF82">
+        <v>0</v>
+      </c>
+      <c r="BG82">
+        <v>0</v>
+      </c>
+      <c r="BH82">
+        <v>0</v>
+      </c>
+      <c r="BI82">
+        <v>0</v>
+      </c>
+      <c r="BJ82">
+        <v>0</v>
+      </c>
+      <c r="BK82">
+        <v>0</v>
+      </c>
+      <c r="BL82">
+        <v>0</v>
+      </c>
+      <c r="BM82">
+        <v>0</v>
+      </c>
+      <c r="BN82">
+        <v>0</v>
+      </c>
+      <c r="BO82">
+        <v>0</v>
+      </c>
+      <c r="BP82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:68">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>7781156</v>
+      </c>
+      <c r="C83" t="s">
+        <v>68</v>
+      </c>
+      <c r="D83" t="s">
+        <v>69</v>
+      </c>
+      <c r="E83" s="2">
+        <v>45745.89583333334</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83" t="s">
+        <v>97</v>
+      </c>
+      <c r="H83" t="s">
+        <v>91</v>
+      </c>
+      <c r="I83">
+        <v>2</v>
+      </c>
+      <c r="J83">
+        <v>1</v>
+      </c>
+      <c r="K83">
+        <v>3</v>
+      </c>
+      <c r="L83">
+        <v>2</v>
+      </c>
+      <c r="M83">
+        <v>1</v>
+      </c>
+      <c r="N83">
+        <v>3</v>
+      </c>
+      <c r="O83" t="s">
+        <v>159</v>
+      </c>
+      <c r="P83" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q83">
+        <v>2.4</v>
+      </c>
+      <c r="R83">
+        <v>2.3</v>
+      </c>
+      <c r="S83">
+        <v>4.33</v>
+      </c>
+      <c r="T83">
+        <v>1.33</v>
+      </c>
+      <c r="U83">
+        <v>3.25</v>
+      </c>
+      <c r="V83">
+        <v>2.5</v>
+      </c>
+      <c r="W83">
+        <v>1.5</v>
+      </c>
+      <c r="X83">
+        <v>6.5</v>
+      </c>
+      <c r="Y83">
+        <v>1.11</v>
+      </c>
+      <c r="Z83">
+        <v>1.83</v>
+      </c>
+      <c r="AA83">
+        <v>3.84</v>
+      </c>
+      <c r="AB83">
+        <v>3.81</v>
+      </c>
+      <c r="AC83">
+        <v>0</v>
+      </c>
+      <c r="AD83">
+        <v>0</v>
+      </c>
+      <c r="AE83">
+        <v>0</v>
+      </c>
+      <c r="AF83">
+        <v>0</v>
+      </c>
+      <c r="AG83">
+        <v>1.67</v>
+      </c>
+      <c r="AH83">
+        <v>2.12</v>
+      </c>
+      <c r="AI83">
+        <v>1.62</v>
+      </c>
+      <c r="AJ83">
+        <v>2.2</v>
+      </c>
+      <c r="AK83">
+        <v>0</v>
+      </c>
+      <c r="AL83">
+        <v>0</v>
+      </c>
+      <c r="AM83">
+        <v>0</v>
+      </c>
+      <c r="AN83">
+        <v>0</v>
+      </c>
+      <c r="AO83">
+        <v>0</v>
+      </c>
+      <c r="AP83">
+        <v>1</v>
+      </c>
+      <c r="AQ83">
+        <v>0</v>
+      </c>
+      <c r="AR83">
+        <v>1.35</v>
+      </c>
+      <c r="AS83">
+        <v>0.91</v>
+      </c>
+      <c r="AT83">
+        <v>2.26</v>
+      </c>
+      <c r="AU83">
+        <v>3</v>
+      </c>
+      <c r="AV83">
+        <v>6</v>
+      </c>
+      <c r="AW83">
+        <v>5</v>
+      </c>
+      <c r="AX83">
+        <v>8</v>
+      </c>
+      <c r="AY83">
+        <v>9</v>
+      </c>
+      <c r="AZ83">
+        <v>14</v>
+      </c>
+      <c r="BA83">
+        <v>2</v>
+      </c>
+      <c r="BB83">
+        <v>7</v>
+      </c>
+      <c r="BC83">
+        <v>9</v>
+      </c>
+      <c r="BD83">
+        <v>0</v>
+      </c>
+      <c r="BE83">
+        <v>0</v>
+      </c>
+      <c r="BF83">
+        <v>0</v>
+      </c>
+      <c r="BG83">
+        <v>0</v>
+      </c>
+      <c r="BH83">
+        <v>0</v>
+      </c>
+      <c r="BI83">
+        <v>0</v>
+      </c>
+      <c r="BJ83">
+        <v>0</v>
+      </c>
+      <c r="BK83">
+        <v>0</v>
+      </c>
+      <c r="BL83">
+        <v>0</v>
+      </c>
+      <c r="BM83">
+        <v>0</v>
+      </c>
+      <c r="BN83">
+        <v>0</v>
+      </c>
+      <c r="BO83">
+        <v>0</v>
+      </c>
+      <c r="BP83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:68">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>7781157</v>
+      </c>
+      <c r="C84" t="s">
+        <v>68</v>
+      </c>
+      <c r="D84" t="s">
+        <v>69</v>
+      </c>
+      <c r="E84" s="2">
+        <v>45745.89583333334</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84" t="s">
+        <v>92</v>
+      </c>
+      <c r="H84" t="s">
+        <v>86</v>
+      </c>
+      <c r="I84">
+        <v>1</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>1</v>
+      </c>
+      <c r="L84">
+        <v>2</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>2</v>
+      </c>
+      <c r="O84" t="s">
+        <v>160</v>
+      </c>
+      <c r="P84" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q84">
+        <v>2.3</v>
+      </c>
+      <c r="R84">
+        <v>2.3</v>
+      </c>
+      <c r="S84">
+        <v>4.5</v>
+      </c>
+      <c r="T84">
+        <v>1.33</v>
+      </c>
+      <c r="U84">
+        <v>3.25</v>
+      </c>
+      <c r="V84">
+        <v>2.63</v>
+      </c>
+      <c r="W84">
+        <v>1.44</v>
+      </c>
+      <c r="X84">
+        <v>6.5</v>
+      </c>
+      <c r="Y84">
+        <v>1.11</v>
+      </c>
+      <c r="Z84">
+        <v>1.74</v>
+      </c>
+      <c r="AA84">
+        <v>3.6</v>
+      </c>
+      <c r="AB84">
+        <v>4.6</v>
+      </c>
+      <c r="AC84">
+        <v>0</v>
+      </c>
+      <c r="AD84">
+        <v>0</v>
+      </c>
+      <c r="AE84">
+        <v>0</v>
+      </c>
+      <c r="AF84">
+        <v>0</v>
+      </c>
+      <c r="AG84">
+        <v>1.6</v>
+      </c>
+      <c r="AH84">
+        <v>2.2</v>
+      </c>
+      <c r="AI84">
+        <v>1.7</v>
+      </c>
+      <c r="AJ84">
+        <v>2.05</v>
+      </c>
+      <c r="AK84">
+        <v>0</v>
+      </c>
+      <c r="AL84">
+        <v>0</v>
+      </c>
+      <c r="AM84">
+        <v>0</v>
+      </c>
+      <c r="AN84">
+        <v>2</v>
+      </c>
+      <c r="AO84">
+        <v>1.5</v>
+      </c>
+      <c r="AP84">
+        <v>2.33</v>
+      </c>
+      <c r="AQ84">
+        <v>1</v>
+      </c>
+      <c r="AR84">
+        <v>1.92</v>
+      </c>
+      <c r="AS84">
+        <v>1.79</v>
+      </c>
+      <c r="AT84">
+        <v>3.71</v>
+      </c>
+      <c r="AU84">
+        <v>7</v>
+      </c>
+      <c r="AV84">
+        <v>5</v>
+      </c>
+      <c r="AW84">
+        <v>9</v>
+      </c>
+      <c r="AX84">
+        <v>12</v>
+      </c>
+      <c r="AY84">
+        <v>18</v>
+      </c>
+      <c r="AZ84">
+        <v>20</v>
+      </c>
+      <c r="BA84">
+        <v>5</v>
+      </c>
+      <c r="BB84">
+        <v>2</v>
+      </c>
+      <c r="BC84">
+        <v>7</v>
+      </c>
+      <c r="BD84">
+        <v>0</v>
+      </c>
+      <c r="BE84">
+        <v>0</v>
+      </c>
+      <c r="BF84">
+        <v>0</v>
+      </c>
+      <c r="BG84">
+        <v>0</v>
+      </c>
+      <c r="BH84">
+        <v>0</v>
+      </c>
+      <c r="BI84">
+        <v>0</v>
+      </c>
+      <c r="BJ84">
+        <v>0</v>
+      </c>
+      <c r="BK84">
+        <v>0</v>
+      </c>
+      <c r="BL84">
+        <v>0</v>
+      </c>
+      <c r="BM84">
+        <v>0</v>
+      </c>
+      <c r="BN84">
+        <v>0</v>
+      </c>
+      <c r="BO84">
+        <v>0</v>
+      </c>
+      <c r="BP84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:68">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>7781158</v>
+      </c>
+      <c r="C85" t="s">
+        <v>68</v>
+      </c>
+      <c r="D85" t="s">
+        <v>69</v>
+      </c>
+      <c r="E85" s="2">
+        <v>45745.89583333334</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85" t="s">
+        <v>79</v>
+      </c>
+      <c r="H85" t="s">
+        <v>73</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+      <c r="J85">
+        <v>1</v>
+      </c>
+      <c r="K85">
+        <v>2</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85">
+        <v>2</v>
+      </c>
+      <c r="N85">
+        <v>3</v>
+      </c>
+      <c r="O85" t="s">
+        <v>161</v>
+      </c>
+      <c r="P85" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q85">
+        <v>2.88</v>
+      </c>
+      <c r="R85">
+        <v>2.2</v>
+      </c>
+      <c r="S85">
+        <v>3.5</v>
+      </c>
+      <c r="T85">
+        <v>1.36</v>
+      </c>
+      <c r="U85">
+        <v>3</v>
+      </c>
+      <c r="V85">
+        <v>2.75</v>
+      </c>
+      <c r="W85">
+        <v>1.4</v>
+      </c>
+      <c r="X85">
+        <v>7</v>
+      </c>
+      <c r="Y85">
+        <v>1.1</v>
+      </c>
+      <c r="Z85">
+        <v>2.39</v>
+      </c>
+      <c r="AA85">
+        <v>3.41</v>
+      </c>
+      <c r="AB85">
+        <v>2.79</v>
+      </c>
+      <c r="AC85">
+        <v>0</v>
+      </c>
+      <c r="AD85">
+        <v>0</v>
+      </c>
+      <c r="AE85">
+        <v>0</v>
+      </c>
+      <c r="AF85">
+        <v>0</v>
+      </c>
+      <c r="AG85">
+        <v>1.8</v>
+      </c>
+      <c r="AH85">
+        <v>1.94</v>
+      </c>
+      <c r="AI85">
+        <v>1.67</v>
+      </c>
+      <c r="AJ85">
+        <v>2.1</v>
+      </c>
+      <c r="AK85">
+        <v>0</v>
+      </c>
+      <c r="AL85">
+        <v>0</v>
+      </c>
+      <c r="AM85">
+        <v>0</v>
+      </c>
+      <c r="AN85">
+        <v>2.33</v>
+      </c>
+      <c r="AO85">
+        <v>0</v>
+      </c>
+      <c r="AP85">
+        <v>1.75</v>
+      </c>
+      <c r="AQ85">
+        <v>1</v>
+      </c>
+      <c r="AR85">
+        <v>1.87</v>
+      </c>
+      <c r="AS85">
+        <v>1.35</v>
+      </c>
+      <c r="AT85">
+        <v>3.22</v>
+      </c>
+      <c r="AU85">
+        <v>7</v>
+      </c>
+      <c r="AV85">
+        <v>6</v>
+      </c>
+      <c r="AW85">
+        <v>7</v>
+      </c>
+      <c r="AX85">
+        <v>10</v>
+      </c>
+      <c r="AY85">
+        <v>17</v>
+      </c>
+      <c r="AZ85">
+        <v>18</v>
+      </c>
+      <c r="BA85">
+        <v>4</v>
+      </c>
+      <c r="BB85">
+        <v>5</v>
+      </c>
+      <c r="BC85">
+        <v>9</v>
+      </c>
+      <c r="BD85">
+        <v>0</v>
+      </c>
+      <c r="BE85">
+        <v>0</v>
+      </c>
+      <c r="BF85">
+        <v>0</v>
+      </c>
+      <c r="BG85">
+        <v>0</v>
+      </c>
+      <c r="BH85">
+        <v>0</v>
+      </c>
+      <c r="BI85">
+        <v>0</v>
+      </c>
+      <c r="BJ85">
+        <v>0</v>
+      </c>
+      <c r="BK85">
+        <v>0</v>
+      </c>
+      <c r="BL85">
+        <v>0</v>
+      </c>
+      <c r="BM85">
+        <v>0</v>
+      </c>
+      <c r="BN85">
+        <v>0</v>
+      </c>
+      <c r="BO85">
+        <v>0</v>
+      </c>
+      <c r="BP85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:68">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>7781159</v>
+      </c>
+      <c r="C86" t="s">
+        <v>68</v>
+      </c>
+      <c r="D86" t="s">
+        <v>69</v>
+      </c>
+      <c r="E86" s="2">
+        <v>45745.97916666666</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86" t="s">
+        <v>84</v>
+      </c>
+      <c r="H86" t="s">
+        <v>76</v>
+      </c>
+      <c r="I86">
+        <v>1</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>1</v>
+      </c>
+      <c r="L86">
+        <v>1</v>
+      </c>
+      <c r="M86">
+        <v>2</v>
+      </c>
+      <c r="N86">
+        <v>3</v>
+      </c>
+      <c r="O86" t="s">
+        <v>151</v>
+      </c>
+      <c r="P86" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q86">
+        <v>2.75</v>
+      </c>
+      <c r="R86">
+        <v>2.38</v>
+      </c>
+      <c r="S86">
+        <v>3.4</v>
+      </c>
+      <c r="T86">
+        <v>1.3</v>
+      </c>
+      <c r="U86">
+        <v>3.4</v>
+      </c>
+      <c r="V86">
+        <v>2.38</v>
+      </c>
+      <c r="W86">
+        <v>1.53</v>
+      </c>
+      <c r="X86">
+        <v>6</v>
+      </c>
+      <c r="Y86">
+        <v>1.13</v>
+      </c>
+      <c r="Z86">
+        <v>2.15</v>
+      </c>
+      <c r="AA86">
+        <v>3.78</v>
+      </c>
+      <c r="AB86">
+        <v>2.94</v>
+      </c>
+      <c r="AC86">
+        <v>1.04</v>
+      </c>
+      <c r="AD86">
+        <v>10</v>
+      </c>
+      <c r="AE86">
+        <v>1.2</v>
+      </c>
+      <c r="AF86">
+        <v>4.33</v>
+      </c>
+      <c r="AG86">
+        <v>1.56</v>
+      </c>
+      <c r="AH86">
+        <v>2.33</v>
+      </c>
+      <c r="AI86">
+        <v>1.5</v>
+      </c>
+      <c r="AJ86">
+        <v>2.5</v>
+      </c>
+      <c r="AK86">
+        <v>1.36</v>
+      </c>
+      <c r="AL86">
+        <v>1.28</v>
+      </c>
+      <c r="AM86">
+        <v>1.65</v>
+      </c>
+      <c r="AN86">
+        <v>0</v>
+      </c>
+      <c r="AO86">
+        <v>0.5</v>
+      </c>
+      <c r="AP86">
+        <v>0</v>
+      </c>
+      <c r="AQ86">
+        <v>1.33</v>
+      </c>
+      <c r="AR86">
+        <v>1.7</v>
+      </c>
+      <c r="AS86">
+        <v>1.34</v>
+      </c>
+      <c r="AT86">
+        <v>3.04</v>
+      </c>
+      <c r="AU86">
+        <v>4</v>
+      </c>
+      <c r="AV86">
+        <v>5</v>
+      </c>
+      <c r="AW86">
+        <v>7</v>
+      </c>
+      <c r="AX86">
+        <v>10</v>
+      </c>
+      <c r="AY86">
+        <v>14</v>
+      </c>
+      <c r="AZ86">
+        <v>16</v>
+      </c>
+      <c r="BA86">
+        <v>6</v>
+      </c>
+      <c r="BB86">
+        <v>2</v>
+      </c>
+      <c r="BC86">
+        <v>8</v>
+      </c>
+      <c r="BD86">
+        <v>1.93</v>
+      </c>
+      <c r="BE86">
+        <v>6.5</v>
+      </c>
+      <c r="BF86">
+        <v>2.05</v>
+      </c>
+      <c r="BG86">
+        <v>1.3</v>
+      </c>
+      <c r="BH86">
+        <v>3.15</v>
+      </c>
+      <c r="BI86">
+        <v>1.52</v>
+      </c>
+      <c r="BJ86">
+        <v>2.32</v>
+      </c>
+      <c r="BK86">
+        <v>1.86</v>
+      </c>
+      <c r="BL86">
+        <v>1.82</v>
+      </c>
+      <c r="BM86">
+        <v>2.33</v>
+      </c>
+      <c r="BN86">
+        <v>1.5</v>
+      </c>
+      <c r="BO86">
+        <v>3.05</v>
+      </c>
+      <c r="BP86">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="87" spans="1:68">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>7781160</v>
+      </c>
+      <c r="C87" t="s">
+        <v>68</v>
+      </c>
+      <c r="D87" t="s">
+        <v>69</v>
+      </c>
+      <c r="E87" s="2">
+        <v>45745.97916666666</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87" t="s">
+        <v>94</v>
+      </c>
+      <c r="H87" t="s">
+        <v>70</v>
+      </c>
+      <c r="I87">
+        <v>3</v>
+      </c>
+      <c r="J87">
+        <v>2</v>
+      </c>
+      <c r="K87">
+        <v>5</v>
+      </c>
+      <c r="L87">
+        <v>3</v>
+      </c>
+      <c r="M87">
+        <v>2</v>
+      </c>
+      <c r="N87">
+        <v>5</v>
+      </c>
+      <c r="O87" t="s">
+        <v>162</v>
+      </c>
+      <c r="P87" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q87">
+        <v>0</v>
+      </c>
+      <c r="R87">
+        <v>0</v>
+      </c>
+      <c r="S87">
+        <v>0</v>
+      </c>
+      <c r="T87">
+        <v>0</v>
+      </c>
+      <c r="U87">
+        <v>0</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <v>0</v>
+      </c>
+      <c r="X87">
+        <v>0</v>
+      </c>
+      <c r="Y87">
+        <v>0</v>
+      </c>
+      <c r="Z87">
+        <v>2.22</v>
+      </c>
+      <c r="AA87">
+        <v>3.45</v>
+      </c>
+      <c r="AB87">
+        <v>3.03</v>
+      </c>
+      <c r="AC87">
+        <v>0</v>
+      </c>
+      <c r="AD87">
+        <v>0</v>
+      </c>
+      <c r="AE87">
+        <v>0</v>
+      </c>
+      <c r="AF87">
+        <v>0</v>
+      </c>
+      <c r="AG87">
+        <v>1.89</v>
+      </c>
+      <c r="AH87">
+        <v>1.85</v>
+      </c>
+      <c r="AI87">
+        <v>0</v>
+      </c>
+      <c r="AJ87">
+        <v>0</v>
+      </c>
+      <c r="AK87">
+        <v>0</v>
+      </c>
+      <c r="AL87">
+        <v>0</v>
+      </c>
+      <c r="AM87">
+        <v>0</v>
+      </c>
+      <c r="AN87">
+        <v>1</v>
+      </c>
+      <c r="AO87">
+        <v>1.5</v>
+      </c>
+      <c r="AP87">
+        <v>1.67</v>
+      </c>
+      <c r="AQ87">
+        <v>1</v>
+      </c>
+      <c r="AR87">
+        <v>1.99</v>
+      </c>
+      <c r="AS87">
+        <v>0.97</v>
+      </c>
+      <c r="AT87">
+        <v>2.96</v>
+      </c>
+      <c r="AU87">
+        <v>-1</v>
+      </c>
+      <c r="AV87">
+        <v>-1</v>
+      </c>
+      <c r="AW87">
+        <v>-1</v>
+      </c>
+      <c r="AX87">
+        <v>-1</v>
+      </c>
+      <c r="AY87">
+        <v>-1</v>
+      </c>
+      <c r="AZ87">
+        <v>-1</v>
+      </c>
+      <c r="BA87">
+        <v>-1</v>
+      </c>
+      <c r="BB87">
+        <v>-1</v>
+      </c>
+      <c r="BC87">
+        <v>-1</v>
+      </c>
+      <c r="BD87">
+        <v>0</v>
+      </c>
+      <c r="BE87">
+        <v>0</v>
+      </c>
+      <c r="BF87">
+        <v>0</v>
+      </c>
+      <c r="BG87">
+        <v>0</v>
+      </c>
+      <c r="BH87">
+        <v>0</v>
+      </c>
+      <c r="BI87">
+        <v>0</v>
+      </c>
+      <c r="BJ87">
+        <v>0</v>
+      </c>
+      <c r="BK87">
+        <v>0</v>
+      </c>
+      <c r="BL87">
+        <v>0</v>
+      </c>
+      <c r="BM87">
+        <v>0</v>
+      </c>
+      <c r="BN87">
+        <v>0</v>
+      </c>
+      <c r="BO87">
+        <v>0</v>
+      </c>
+      <c r="BP87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:68">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>7781161</v>
+      </c>
+      <c r="C88" t="s">
+        <v>68</v>
+      </c>
+      <c r="D88" t="s">
+        <v>69</v>
+      </c>
+      <c r="E88" s="2">
+        <v>45745.97916666666</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88" t="s">
+        <v>81</v>
+      </c>
+      <c r="H88" t="s">
+        <v>82</v>
+      </c>
+      <c r="I88">
+        <v>1</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>1</v>
+      </c>
+      <c r="L88">
+        <v>1</v>
+      </c>
+      <c r="M88">
+        <v>1</v>
+      </c>
+      <c r="N88">
+        <v>2</v>
+      </c>
+      <c r="O88" t="s">
+        <v>163</v>
+      </c>
+      <c r="P88" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q88">
+        <v>3.25</v>
+      </c>
+      <c r="R88">
+        <v>2.2</v>
+      </c>
+      <c r="S88">
+        <v>3.1</v>
+      </c>
+      <c r="T88">
+        <v>1.36</v>
+      </c>
+      <c r="U88">
+        <v>3</v>
+      </c>
+      <c r="V88">
+        <v>2.75</v>
+      </c>
+      <c r="W88">
+        <v>1.4</v>
+      </c>
+      <c r="X88">
+        <v>7</v>
+      </c>
+      <c r="Y88">
+        <v>1.1</v>
+      </c>
+      <c r="Z88">
+        <v>2.71</v>
+      </c>
+      <c r="AA88">
+        <v>3.45</v>
+      </c>
+      <c r="AB88">
+        <v>2.44</v>
+      </c>
+      <c r="AC88">
+        <v>1.05</v>
+      </c>
+      <c r="AD88">
+        <v>9.5</v>
+      </c>
+      <c r="AE88">
+        <v>1.25</v>
+      </c>
+      <c r="AF88">
+        <v>3.7</v>
+      </c>
+      <c r="AG88">
+        <v>1.79</v>
+      </c>
+      <c r="AH88">
+        <v>1.95</v>
+      </c>
+      <c r="AI88">
+        <v>1.67</v>
+      </c>
+      <c r="AJ88">
+        <v>2.1</v>
+      </c>
+      <c r="AK88">
+        <v>1.39</v>
+      </c>
+      <c r="AL88">
+        <v>1.31</v>
+      </c>
+      <c r="AM88">
+        <v>1.57</v>
+      </c>
+      <c r="AN88">
+        <v>1</v>
+      </c>
+      <c r="AO88">
+        <v>0</v>
+      </c>
+      <c r="AP88">
+        <v>1</v>
+      </c>
+      <c r="AQ88">
+        <v>0.33</v>
+      </c>
+      <c r="AR88">
+        <v>2.16</v>
+      </c>
+      <c r="AS88">
+        <v>1.35</v>
+      </c>
+      <c r="AT88">
+        <v>3.51</v>
+      </c>
+      <c r="AU88">
+        <v>4</v>
+      </c>
+      <c r="AV88">
+        <v>10</v>
+      </c>
+      <c r="AW88">
+        <v>8</v>
+      </c>
+      <c r="AX88">
+        <v>15</v>
+      </c>
+      <c r="AY88">
+        <v>13</v>
+      </c>
+      <c r="AZ88">
+        <v>32</v>
+      </c>
+      <c r="BA88">
+        <v>4</v>
+      </c>
+      <c r="BB88">
+        <v>12</v>
+      </c>
+      <c r="BC88">
+        <v>16</v>
+      </c>
+      <c r="BD88">
+        <v>2.08</v>
+      </c>
+      <c r="BE88">
+        <v>6.75</v>
+      </c>
+      <c r="BF88">
+        <v>1.88</v>
+      </c>
+      <c r="BG88">
+        <v>1.22</v>
+      </c>
+      <c r="BH88">
+        <v>3.65</v>
+      </c>
+      <c r="BI88">
+        <v>1.4</v>
+      </c>
+      <c r="BJ88">
+        <v>2.65</v>
+      </c>
+      <c r="BK88">
+        <v>1.66</v>
+      </c>
+      <c r="BL88">
+        <v>2.06</v>
+      </c>
+      <c r="BM88">
+        <v>2.02</v>
+      </c>
+      <c r="BN88">
+        <v>1.68</v>
+      </c>
+      <c r="BO88">
+        <v>2.55</v>
+      </c>
+      <c r="BP88">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="214">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -508,6 +508,9 @@
     <t>['32']</t>
   </si>
   <si>
+    <t>['6', '23', '71']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -650,6 +653,9 @@
   </si>
   <si>
     <t>['43', '45+5']</t>
+  </si>
+  <si>
+    <t>['12']</t>
   </si>
 </sst>
 </file>
@@ -1011,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP88"/>
+  <dimension ref="A1:BP90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1473,7 +1479,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -1679,7 +1685,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2091,7 +2097,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2297,7 +2303,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2503,7 +2509,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2915,7 +2921,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -3405,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12">
         <v>2.33</v>
@@ -3739,7 +3745,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -3945,7 +3951,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4023,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ15">
         <v>2.33</v>
@@ -4151,7 +4157,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4769,7 +4775,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -5181,7 +5187,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -5387,7 +5393,7 @@
         <v>116</v>
       </c>
       <c r="P22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5593,7 +5599,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -5799,7 +5805,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6211,7 +6217,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6701,10 +6707,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ28">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR28">
         <v>0.72</v>
@@ -7241,7 +7247,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7528,7 +7534,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AR32">
         <v>1.83</v>
@@ -7653,7 +7659,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -8271,7 +8277,7 @@
         <v>127</v>
       </c>
       <c r="P36" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q36">
         <v>2.4</v>
@@ -8477,7 +8483,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9095,7 +9101,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9507,7 +9513,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -10331,7 +10337,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10537,7 +10543,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10743,7 +10749,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11030,7 +11036,7 @@
         <v>2</v>
       </c>
       <c r="AQ49">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR49">
         <v>1.41</v>
@@ -11567,7 +11573,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11773,7 +11779,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -11979,7 +11985,7 @@
         <v>109</v>
       </c>
       <c r="P54" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12185,7 +12191,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -12469,7 +12475,7 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ56">
         <v>0.33</v>
@@ -12803,7 +12809,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13009,7 +13015,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13215,7 +13221,7 @@
         <v>143</v>
       </c>
       <c r="P60" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13293,7 +13299,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ60">
         <v>0.67</v>
@@ -13421,7 +13427,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -13627,7 +13633,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -13833,7 +13839,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14039,7 +14045,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -14657,7 +14663,7 @@
         <v>148</v>
       </c>
       <c r="P67" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15069,7 +15075,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15481,7 +15487,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15687,7 +15693,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -15974,7 +15980,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ73">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AR73">
         <v>2.23</v>
@@ -16099,7 +16105,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16511,7 +16517,7 @@
         <v>153</v>
       </c>
       <c r="P76" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q76">
         <v>3.6</v>
@@ -17129,7 +17135,7 @@
         <v>155</v>
       </c>
       <c r="P79" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q79">
         <v>2.1</v>
@@ -17335,7 +17341,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -17541,7 +17547,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -17747,7 +17753,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -18365,7 +18371,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -18571,7 +18577,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -18777,7 +18783,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -18983,7 +18989,7 @@
         <v>163</v>
       </c>
       <c r="P88" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q88">
         <v>3.25</v>
@@ -19140,6 +19146,418 @@
       </c>
       <c r="BP88">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="89" spans="1:68">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>7781162</v>
+      </c>
+      <c r="C89" t="s">
+        <v>68</v>
+      </c>
+      <c r="D89" t="s">
+        <v>69</v>
+      </c>
+      <c r="E89" s="2">
+        <v>45746.63541666666</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89" t="s">
+        <v>80</v>
+      </c>
+      <c r="H89" t="s">
+        <v>77</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1</v>
+      </c>
+      <c r="K89">
+        <v>1</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>1</v>
+      </c>
+      <c r="N89">
+        <v>1</v>
+      </c>
+      <c r="O89" t="s">
+        <v>109</v>
+      </c>
+      <c r="P89" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q89">
+        <v>2.88</v>
+      </c>
+      <c r="R89">
+        <v>2.2</v>
+      </c>
+      <c r="S89">
+        <v>3.75</v>
+      </c>
+      <c r="T89">
+        <v>1.4</v>
+      </c>
+      <c r="U89">
+        <v>2.75</v>
+      </c>
+      <c r="V89">
+        <v>2.75</v>
+      </c>
+      <c r="W89">
+        <v>1.4</v>
+      </c>
+      <c r="X89">
+        <v>8</v>
+      </c>
+      <c r="Y89">
+        <v>1.08</v>
+      </c>
+      <c r="Z89">
+        <v>2.15</v>
+      </c>
+      <c r="AA89">
+        <v>3.55</v>
+      </c>
+      <c r="AB89">
+        <v>3.1</v>
+      </c>
+      <c r="AC89">
+        <v>1.05</v>
+      </c>
+      <c r="AD89">
+        <v>9</v>
+      </c>
+      <c r="AE89">
+        <v>1.28</v>
+      </c>
+      <c r="AF89">
+        <v>3.6</v>
+      </c>
+      <c r="AG89">
+        <v>1.73</v>
+      </c>
+      <c r="AH89">
+        <v>2</v>
+      </c>
+      <c r="AI89">
+        <v>1.67</v>
+      </c>
+      <c r="AJ89">
+        <v>2.1</v>
+      </c>
+      <c r="AK89">
+        <v>1.23</v>
+      </c>
+      <c r="AL89">
+        <v>1.3</v>
+      </c>
+      <c r="AM89">
+        <v>1.85</v>
+      </c>
+      <c r="AN89">
+        <v>2</v>
+      </c>
+      <c r="AO89">
+        <v>1.5</v>
+      </c>
+      <c r="AP89">
+        <v>1.33</v>
+      </c>
+      <c r="AQ89">
+        <v>2</v>
+      </c>
+      <c r="AR89">
+        <v>1.83</v>
+      </c>
+      <c r="AS89">
+        <v>1.25</v>
+      </c>
+      <c r="AT89">
+        <v>3.08</v>
+      </c>
+      <c r="AU89">
+        <v>3</v>
+      </c>
+      <c r="AV89">
+        <v>4</v>
+      </c>
+      <c r="AW89">
+        <v>14</v>
+      </c>
+      <c r="AX89">
+        <v>6</v>
+      </c>
+      <c r="AY89">
+        <v>21</v>
+      </c>
+      <c r="AZ89">
+        <v>12</v>
+      </c>
+      <c r="BA89">
+        <v>8</v>
+      </c>
+      <c r="BB89">
+        <v>3</v>
+      </c>
+      <c r="BC89">
+        <v>11</v>
+      </c>
+      <c r="BD89">
+        <v>1.68</v>
+      </c>
+      <c r="BE89">
+        <v>6.75</v>
+      </c>
+      <c r="BF89">
+        <v>2.43</v>
+      </c>
+      <c r="BG89">
+        <v>1.3</v>
+      </c>
+      <c r="BH89">
+        <v>3.05</v>
+      </c>
+      <c r="BI89">
+        <v>1.54</v>
+      </c>
+      <c r="BJ89">
+        <v>2.3</v>
+      </c>
+      <c r="BK89">
+        <v>1.88</v>
+      </c>
+      <c r="BL89">
+        <v>1.81</v>
+      </c>
+      <c r="BM89">
+        <v>2.38</v>
+      </c>
+      <c r="BN89">
+        <v>1.5</v>
+      </c>
+      <c r="BO89">
+        <v>3.05</v>
+      </c>
+      <c r="BP89">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:68">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>7781163</v>
+      </c>
+      <c r="C90" t="s">
+        <v>68</v>
+      </c>
+      <c r="D90" t="s">
+        <v>69</v>
+      </c>
+      <c r="E90" s="2">
+        <v>45746.83333333334</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90" t="s">
+        <v>83</v>
+      </c>
+      <c r="H90" t="s">
+        <v>78</v>
+      </c>
+      <c r="I90">
+        <v>2</v>
+      </c>
+      <c r="J90">
+        <v>1</v>
+      </c>
+      <c r="K90">
+        <v>3</v>
+      </c>
+      <c r="L90">
+        <v>3</v>
+      </c>
+      <c r="M90">
+        <v>1</v>
+      </c>
+      <c r="N90">
+        <v>4</v>
+      </c>
+      <c r="O90" t="s">
+        <v>164</v>
+      </c>
+      <c r="P90" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q90">
+        <v>2.75</v>
+      </c>
+      <c r="R90">
+        <v>2.25</v>
+      </c>
+      <c r="S90">
+        <v>3.6</v>
+      </c>
+      <c r="T90">
+        <v>1.33</v>
+      </c>
+      <c r="U90">
+        <v>3.25</v>
+      </c>
+      <c r="V90">
+        <v>2.63</v>
+      </c>
+      <c r="W90">
+        <v>1.44</v>
+      </c>
+      <c r="X90">
+        <v>7</v>
+      </c>
+      <c r="Y90">
+        <v>1.1</v>
+      </c>
+      <c r="Z90">
+        <v>2.13</v>
+      </c>
+      <c r="AA90">
+        <v>3.55</v>
+      </c>
+      <c r="AB90">
+        <v>3.14</v>
+      </c>
+      <c r="AC90">
+        <v>1.05</v>
+      </c>
+      <c r="AD90">
+        <v>9.5</v>
+      </c>
+      <c r="AE90">
+        <v>1.25</v>
+      </c>
+      <c r="AF90">
+        <v>3.95</v>
+      </c>
+      <c r="AG90">
+        <v>1.8</v>
+      </c>
+      <c r="AH90">
+        <v>1.94</v>
+      </c>
+      <c r="AI90">
+        <v>1.62</v>
+      </c>
+      <c r="AJ90">
+        <v>2.2</v>
+      </c>
+      <c r="AK90">
+        <v>1.28</v>
+      </c>
+      <c r="AL90">
+        <v>1.28</v>
+      </c>
+      <c r="AM90">
+        <v>1.78</v>
+      </c>
+      <c r="AN90">
+        <v>1.33</v>
+      </c>
+      <c r="AO90">
+        <v>1</v>
+      </c>
+      <c r="AP90">
+        <v>1.75</v>
+      </c>
+      <c r="AQ90">
+        <v>0.67</v>
+      </c>
+      <c r="AR90">
+        <v>1.08</v>
+      </c>
+      <c r="AS90">
+        <v>0.68</v>
+      </c>
+      <c r="AT90">
+        <v>1.76</v>
+      </c>
+      <c r="AU90">
+        <v>10</v>
+      </c>
+      <c r="AV90">
+        <v>2</v>
+      </c>
+      <c r="AW90">
+        <v>5</v>
+      </c>
+      <c r="AX90">
+        <v>9</v>
+      </c>
+      <c r="AY90">
+        <v>18</v>
+      </c>
+      <c r="AZ90">
+        <v>11</v>
+      </c>
+      <c r="BA90">
+        <v>7</v>
+      </c>
+      <c r="BB90">
+        <v>8</v>
+      </c>
+      <c r="BC90">
+        <v>15</v>
+      </c>
+      <c r="BD90">
+        <v>1.75</v>
+      </c>
+      <c r="BE90">
+        <v>6.4</v>
+      </c>
+      <c r="BF90">
+        <v>2.3</v>
+      </c>
+      <c r="BG90">
+        <v>1.27</v>
+      </c>
+      <c r="BH90">
+        <v>3.3</v>
+      </c>
+      <c r="BI90">
+        <v>1.48</v>
+      </c>
+      <c r="BJ90">
+        <v>2.45</v>
+      </c>
+      <c r="BK90">
+        <v>1.76</v>
+      </c>
+      <c r="BL90">
+        <v>1.93</v>
+      </c>
+      <c r="BM90">
+        <v>2.18</v>
+      </c>
+      <c r="BN90">
+        <v>1.58</v>
+      </c>
+      <c r="BO90">
+        <v>2.8</v>
+      </c>
+      <c r="BP90">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -18876,31 +18876,31 @@
         <v>2.96</v>
       </c>
       <c r="AU87">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AV87">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW87">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AX87">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AY87">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AZ87">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="BA87">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB87">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC87">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BD87">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="216">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -509,6 +509,12 @@
   </si>
   <si>
     <t>['6', '23', '71']</t>
+  </si>
+  <si>
+    <t>['85', '90']</t>
+  </si>
+  <si>
+    <t>['21', '26']</t>
   </si>
   <si>
     <t>['26', '55']</t>
@@ -1017,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP90"/>
+  <dimension ref="A1:BP92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1479,7 +1485,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -1685,7 +1691,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2097,7 +2103,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2303,7 +2309,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2509,7 +2515,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2921,7 +2927,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -3745,7 +3751,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -3951,7 +3957,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4157,7 +4163,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4647,7 +4653,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ18">
         <v>0.33</v>
@@ -4775,7 +4781,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -5062,7 +5068,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ20">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5187,7 +5193,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -5393,7 +5399,7 @@
         <v>116</v>
       </c>
       <c r="P22" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5599,7 +5605,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -5805,7 +5811,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6217,7 +6223,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -7122,7 +7128,7 @@
         <v>2</v>
       </c>
       <c r="AQ30">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR30">
         <v>0</v>
@@ -7247,7 +7253,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7659,7 +7665,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -8277,7 +8283,7 @@
         <v>127</v>
       </c>
       <c r="P36" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q36">
         <v>2.4</v>
@@ -8483,7 +8489,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9101,7 +9107,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9513,7 +9519,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -9591,7 +9597,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ42">
         <v>2</v>
@@ -10337,7 +10343,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10543,7 +10549,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10749,7 +10755,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11573,7 +11579,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11779,7 +11785,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -11985,7 +11991,7 @@
         <v>109</v>
       </c>
       <c r="P54" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12191,7 +12197,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -12809,7 +12815,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13015,7 +13021,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13096,7 +13102,7 @@
         <v>2</v>
       </c>
       <c r="AQ59">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR59">
         <v>1.65</v>
@@ -13221,7 +13227,7 @@
         <v>143</v>
       </c>
       <c r="P60" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13302,7 +13308,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ60">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR60">
         <v>0.9399999999999999</v>
@@ -13427,7 +13433,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -13633,7 +13639,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -13839,7 +13845,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -13920,7 +13926,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ63">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR63">
         <v>1.42</v>
@@ -14045,7 +14051,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -14663,7 +14669,7 @@
         <v>148</v>
       </c>
       <c r="P67" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -15075,7 +15081,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15487,7 +15493,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15693,7 +15699,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -15771,7 +15777,7 @@
         <v>2</v>
       </c>
       <c r="AP72">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ72">
         <v>2.33</v>
@@ -16105,7 +16111,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16517,7 +16523,7 @@
         <v>153</v>
       </c>
       <c r="P76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q76">
         <v>3.6</v>
@@ -17135,7 +17141,7 @@
         <v>155</v>
       </c>
       <c r="P79" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q79">
         <v>2.1</v>
@@ -17341,7 +17347,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -17547,7 +17553,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -17753,7 +17759,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -18371,7 +18377,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -18577,7 +18583,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -18783,7 +18789,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -18989,7 +18995,7 @@
         <v>163</v>
       </c>
       <c r="P88" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q88">
         <v>3.25</v>
@@ -19401,7 +19407,7 @@
         <v>164</v>
       </c>
       <c r="P90" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
@@ -19558,6 +19564,418 @@
       </c>
       <c r="BP90">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="91" spans="1:68">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>7781164</v>
+      </c>
+      <c r="C91" t="s">
+        <v>68</v>
+      </c>
+      <c r="D91" t="s">
+        <v>69</v>
+      </c>
+      <c r="E91" s="2">
+        <v>45752.64583333334</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91" t="s">
+        <v>85</v>
+      </c>
+      <c r="H91" t="s">
+        <v>79</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
+      </c>
+      <c r="K91">
+        <v>1</v>
+      </c>
+      <c r="L91">
+        <v>2</v>
+      </c>
+      <c r="M91">
+        <v>1</v>
+      </c>
+      <c r="N91">
+        <v>3</v>
+      </c>
+      <c r="O91" t="s">
+        <v>165</v>
+      </c>
+      <c r="P91" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q91">
+        <v>2.63</v>
+      </c>
+      <c r="R91">
+        <v>2.2</v>
+      </c>
+      <c r="S91">
+        <v>4</v>
+      </c>
+      <c r="T91">
+        <v>1.4</v>
+      </c>
+      <c r="U91">
+        <v>2.75</v>
+      </c>
+      <c r="V91">
+        <v>2.75</v>
+      </c>
+      <c r="W91">
+        <v>1.4</v>
+      </c>
+      <c r="X91">
+        <v>8</v>
+      </c>
+      <c r="Y91">
+        <v>1.08</v>
+      </c>
+      <c r="Z91">
+        <v>1.91</v>
+      </c>
+      <c r="AA91">
+        <v>3.32</v>
+      </c>
+      <c r="AB91">
+        <v>4.1</v>
+      </c>
+      <c r="AC91">
+        <v>1.01</v>
+      </c>
+      <c r="AD91">
+        <v>8.5</v>
+      </c>
+      <c r="AE91">
+        <v>1.26</v>
+      </c>
+      <c r="AF91">
+        <v>4.05</v>
+      </c>
+      <c r="AG91">
+        <v>1.85</v>
+      </c>
+      <c r="AH91">
+        <v>1.89</v>
+      </c>
+      <c r="AI91">
+        <v>1.75</v>
+      </c>
+      <c r="AJ91">
+        <v>2</v>
+      </c>
+      <c r="AK91">
+        <v>1.28</v>
+      </c>
+      <c r="AL91">
+        <v>1.34</v>
+      </c>
+      <c r="AM91">
+        <v>1.84</v>
+      </c>
+      <c r="AN91">
+        <v>3</v>
+      </c>
+      <c r="AO91">
+        <v>1.5</v>
+      </c>
+      <c r="AP91">
+        <v>3</v>
+      </c>
+      <c r="AQ91">
+        <v>1</v>
+      </c>
+      <c r="AR91">
+        <v>1.64</v>
+      </c>
+      <c r="AS91">
+        <v>1.26</v>
+      </c>
+      <c r="AT91">
+        <v>2.9</v>
+      </c>
+      <c r="AU91">
+        <v>6</v>
+      </c>
+      <c r="AV91">
+        <v>8</v>
+      </c>
+      <c r="AW91">
+        <v>2</v>
+      </c>
+      <c r="AX91">
+        <v>6</v>
+      </c>
+      <c r="AY91">
+        <v>8</v>
+      </c>
+      <c r="AZ91">
+        <v>18</v>
+      </c>
+      <c r="BA91">
+        <v>3</v>
+      </c>
+      <c r="BB91">
+        <v>8</v>
+      </c>
+      <c r="BC91">
+        <v>11</v>
+      </c>
+      <c r="BD91">
+        <v>1.68</v>
+      </c>
+      <c r="BE91">
+        <v>6.65</v>
+      </c>
+      <c r="BF91">
+        <v>2.88</v>
+      </c>
+      <c r="BG91">
+        <v>1.26</v>
+      </c>
+      <c r="BH91">
+        <v>3.22</v>
+      </c>
+      <c r="BI91">
+        <v>1.56</v>
+      </c>
+      <c r="BJ91">
+        <v>2.31</v>
+      </c>
+      <c r="BK91">
+        <v>1.92</v>
+      </c>
+      <c r="BL91">
+        <v>1.87</v>
+      </c>
+      <c r="BM91">
+        <v>2.4</v>
+      </c>
+      <c r="BN91">
+        <v>1.52</v>
+      </c>
+      <c r="BO91">
+        <v>3.28</v>
+      </c>
+      <c r="BP91">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:68">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>7781165</v>
+      </c>
+      <c r="C92" t="s">
+        <v>68</v>
+      </c>
+      <c r="D92" t="s">
+        <v>69</v>
+      </c>
+      <c r="E92" s="2">
+        <v>45752.72916666666</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92" t="s">
+        <v>86</v>
+      </c>
+      <c r="H92" t="s">
+        <v>84</v>
+      </c>
+      <c r="I92">
+        <v>2</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>2</v>
+      </c>
+      <c r="L92">
+        <v>2</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>2</v>
+      </c>
+      <c r="O92" t="s">
+        <v>166</v>
+      </c>
+      <c r="P92" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q92">
+        <v>2.75</v>
+      </c>
+      <c r="R92">
+        <v>2.3</v>
+      </c>
+      <c r="S92">
+        <v>3.5</v>
+      </c>
+      <c r="T92">
+        <v>1.33</v>
+      </c>
+      <c r="U92">
+        <v>3.25</v>
+      </c>
+      <c r="V92">
+        <v>2.5</v>
+      </c>
+      <c r="W92">
+        <v>1.5</v>
+      </c>
+      <c r="X92">
+        <v>6.5</v>
+      </c>
+      <c r="Y92">
+        <v>1.11</v>
+      </c>
+      <c r="Z92">
+        <v>2.2</v>
+      </c>
+      <c r="AA92">
+        <v>3.31</v>
+      </c>
+      <c r="AB92">
+        <v>3.2</v>
+      </c>
+      <c r="AC92">
+        <v>0</v>
+      </c>
+      <c r="AD92">
+        <v>0</v>
+      </c>
+      <c r="AE92">
+        <v>1.2</v>
+      </c>
+      <c r="AF92">
+        <v>4.74</v>
+      </c>
+      <c r="AG92">
+        <v>1.58</v>
+      </c>
+      <c r="AH92">
+        <v>2.29</v>
+      </c>
+      <c r="AI92">
+        <v>1.53</v>
+      </c>
+      <c r="AJ92">
+        <v>2.38</v>
+      </c>
+      <c r="AK92">
+        <v>1.27</v>
+      </c>
+      <c r="AL92">
+        <v>1.31</v>
+      </c>
+      <c r="AM92">
+        <v>1.92</v>
+      </c>
+      <c r="AN92">
+        <v>1</v>
+      </c>
+      <c r="AO92">
+        <v>0.67</v>
+      </c>
+      <c r="AP92">
+        <v>1.5</v>
+      </c>
+      <c r="AQ92">
+        <v>0.5</v>
+      </c>
+      <c r="AR92">
+        <v>1.35</v>
+      </c>
+      <c r="AS92">
+        <v>1.28</v>
+      </c>
+      <c r="AT92">
+        <v>2.63</v>
+      </c>
+      <c r="AU92">
+        <v>3</v>
+      </c>
+      <c r="AV92">
+        <v>2</v>
+      </c>
+      <c r="AW92">
+        <v>4</v>
+      </c>
+      <c r="AX92">
+        <v>6</v>
+      </c>
+      <c r="AY92">
+        <v>8</v>
+      </c>
+      <c r="AZ92">
+        <v>12</v>
+      </c>
+      <c r="BA92">
+        <v>4</v>
+      </c>
+      <c r="BB92">
+        <v>1</v>
+      </c>
+      <c r="BC92">
+        <v>5</v>
+      </c>
+      <c r="BD92">
+        <v>1.49</v>
+      </c>
+      <c r="BE92">
+        <v>7.3</v>
+      </c>
+      <c r="BF92">
+        <v>3.52</v>
+      </c>
+      <c r="BG92">
+        <v>1.16</v>
+      </c>
+      <c r="BH92">
+        <v>4.2</v>
+      </c>
+      <c r="BI92">
+        <v>1.32</v>
+      </c>
+      <c r="BJ92">
+        <v>2.88</v>
+      </c>
+      <c r="BK92">
+        <v>1.64</v>
+      </c>
+      <c r="BL92">
+        <v>2.2</v>
+      </c>
+      <c r="BM92">
+        <v>2.04</v>
+      </c>
+      <c r="BN92">
+        <v>1.76</v>
+      </c>
+      <c r="BO92">
+        <v>2.6</v>
+      </c>
+      <c r="BP92">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="223">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -517,6 +517,24 @@
     <t>['21', '26']</t>
   </si>
   <si>
+    <t>['65']</t>
+  </si>
+  <si>
+    <t>['11', '26']</t>
+  </si>
+  <si>
+    <t>['41', '45+2']</t>
+  </si>
+  <si>
+    <t>['71', '88']</t>
+  </si>
+  <si>
+    <t>['19', '38']</t>
+  </si>
+  <si>
+    <t>['2', '41', '45+3']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -662,6 +680,9 @@
   </si>
   <si>
     <t>['12']</t>
+  </si>
+  <si>
+    <t>['60']</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP92"/>
+  <dimension ref="A1:BP102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1485,7 +1506,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -1691,7 +1712,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -1769,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ4">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1975,7 +1996,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ5">
         <v>0.33</v>
@@ -2103,7 +2124,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2181,10 +2202,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2309,7 +2330,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2515,7 +2536,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2799,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ9">
         <v>0</v>
@@ -2927,7 +2948,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -3005,10 +3026,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AQ10">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3214,7 +3235,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ11">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3420,7 +3441,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ12">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3751,7 +3772,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -3957,7 +3978,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4163,7 +4184,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4656,7 +4677,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ18">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4781,7 +4802,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -5065,7 +5086,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -5193,7 +5214,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -5399,7 +5420,7 @@
         <v>116</v>
       </c>
       <c r="P22" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5477,7 +5498,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ22">
         <v>1</v>
@@ -5605,7 +5626,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -5811,7 +5832,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -5889,7 +5910,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AQ24">
         <v>1.5</v>
@@ -6098,7 +6119,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ25">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6223,7 +6244,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6304,7 +6325,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ26">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR26">
         <v>0</v>
@@ -6919,10 +6940,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AQ29">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -7125,7 +7146,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ30">
         <v>0.5</v>
@@ -7253,7 +7274,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7331,7 +7352,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AQ31">
         <v>3</v>
@@ -7537,7 +7558,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AQ32">
         <v>0.67</v>
@@ -7665,7 +7686,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -7746,7 +7767,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ33">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR33">
         <v>2.47</v>
@@ -7949,7 +7970,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ34">
         <v>0.33</v>
@@ -8155,7 +8176,7 @@
         <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ35">
         <v>0.25</v>
@@ -8283,7 +8304,7 @@
         <v>127</v>
       </c>
       <c r="P36" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="Q36">
         <v>2.4</v>
@@ -8489,7 +8510,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8776,7 +8797,7 @@
         <v>3</v>
       </c>
       <c r="AQ38">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR38">
         <v>0</v>
@@ -8979,10 +9000,10 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ39">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR39">
         <v>1.5</v>
@@ -9107,7 +9128,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9188,7 +9209,7 @@
         <v>1</v>
       </c>
       <c r="AQ40">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AR40">
         <v>0</v>
@@ -9394,7 +9415,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ41">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR41">
         <v>1.65</v>
@@ -9519,7 +9540,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -9803,10 +9824,10 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ43">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AR43">
         <v>1.87</v>
@@ -10343,7 +10364,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10424,7 +10445,7 @@
         <v>0</v>
       </c>
       <c r="AQ46">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR46">
         <v>0.92</v>
@@ -10549,7 +10570,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10630,7 +10651,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ47">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AR47">
         <v>0</v>
@@ -10755,7 +10776,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -10833,10 +10854,10 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ48">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR48">
         <v>1.51</v>
@@ -11454,7 +11475,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ51">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AR51">
         <v>1.36</v>
@@ -11579,7 +11600,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11660,7 +11681,7 @@
         <v>3</v>
       </c>
       <c r="AQ52">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR52">
         <v>1.84</v>
@@ -11785,7 +11806,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -11863,7 +11884,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AQ53">
         <v>1.33</v>
@@ -11991,7 +12012,7 @@
         <v>109</v>
       </c>
       <c r="P54" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12197,7 +12218,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -12275,7 +12296,7 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AQ55">
         <v>1</v>
@@ -12484,7 +12505,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ56">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR56">
         <v>2.14</v>
@@ -12687,7 +12708,7 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AQ57">
         <v>2.33</v>
@@ -12815,7 +12836,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -12896,7 +12917,7 @@
         <v>1</v>
       </c>
       <c r="AQ58">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR58">
         <v>1.87</v>
@@ -13021,7 +13042,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13099,7 +13120,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -13227,7 +13248,7 @@
         <v>143</v>
       </c>
       <c r="P60" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13433,7 +13454,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -13511,7 +13532,7 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ61">
         <v>3</v>
@@ -13639,7 +13660,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -13717,7 +13738,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ62">
         <v>0.5</v>
@@ -13845,7 +13866,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14051,7 +14072,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -14335,7 +14356,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AQ65">
         <v>0.5</v>
@@ -14541,7 +14562,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ66">
         <v>0.25</v>
@@ -14669,7 +14690,7 @@
         <v>148</v>
       </c>
       <c r="P67" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14953,10 +14974,10 @@
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ68">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR68">
         <v>1.48</v>
@@ -15081,7 +15102,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15159,10 +15180,10 @@
         <v>0</v>
       </c>
       <c r="AP69">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AQ69">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR69">
         <v>1.7</v>
@@ -15368,7 +15389,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ70">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AR70">
         <v>1.96</v>
@@ -15493,7 +15514,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15574,7 +15595,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ71">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR71">
         <v>1.88</v>
@@ -15699,7 +15720,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -15780,7 +15801,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ72">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AR72">
         <v>1.41</v>
@@ -16111,7 +16132,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16189,10 +16210,10 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ74">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AR74">
         <v>1.88</v>
@@ -16395,7 +16416,7 @@
         <v>3</v>
       </c>
       <c r="AP75">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ75">
         <v>2</v>
@@ -16523,7 +16544,7 @@
         <v>153</v>
       </c>
       <c r="P76" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="Q76">
         <v>3.6</v>
@@ -17141,7 +17162,7 @@
         <v>155</v>
       </c>
       <c r="P79" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="Q79">
         <v>2.1</v>
@@ -17347,7 +17368,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -17553,7 +17574,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -17631,7 +17652,7 @@
         <v>0.67</v>
       </c>
       <c r="AP81">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AQ81">
         <v>0.5</v>
@@ -17759,7 +17780,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -17840,7 +17861,7 @@
         <v>1</v>
       </c>
       <c r="AQ82">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AR82">
         <v>1.1</v>
@@ -18377,7 +18398,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -18583,7 +18604,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -18664,7 +18685,7 @@
         <v>0</v>
       </c>
       <c r="AQ86">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR86">
         <v>1.7</v>
@@ -18789,7 +18810,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -18867,10 +18888,10 @@
         <v>1.5</v>
       </c>
       <c r="AP87">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AQ87">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR87">
         <v>1.99</v>
@@ -18995,7 +19016,7 @@
         <v>163</v>
       </c>
       <c r="P88" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="Q88">
         <v>3.25</v>
@@ -19076,7 +19097,7 @@
         <v>1</v>
       </c>
       <c r="AQ88">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR88">
         <v>2.16</v>
@@ -19407,7 +19428,7 @@
         <v>164</v>
       </c>
       <c r="P90" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
@@ -19976,6 +19997,2066 @@
       </c>
       <c r="BP92">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="93" spans="1:68">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>7781166</v>
+      </c>
+      <c r="C93" t="s">
+        <v>68</v>
+      </c>
+      <c r="D93" t="s">
+        <v>69</v>
+      </c>
+      <c r="E93" s="2">
+        <v>45752.85416666666</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93" t="s">
+        <v>72</v>
+      </c>
+      <c r="H93" t="s">
+        <v>97</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>1</v>
+      </c>
+      <c r="L93">
+        <v>1</v>
+      </c>
+      <c r="M93">
+        <v>1</v>
+      </c>
+      <c r="N93">
+        <v>2</v>
+      </c>
+      <c r="O93" t="s">
+        <v>131</v>
+      </c>
+      <c r="P93" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q93">
+        <v>2.2</v>
+      </c>
+      <c r="R93">
+        <v>2.4</v>
+      </c>
+      <c r="S93">
+        <v>4.5</v>
+      </c>
+      <c r="T93">
+        <v>1.29</v>
+      </c>
+      <c r="U93">
+        <v>3.5</v>
+      </c>
+      <c r="V93">
+        <v>2.25</v>
+      </c>
+      <c r="W93">
+        <v>1.57</v>
+      </c>
+      <c r="X93">
+        <v>5.5</v>
+      </c>
+      <c r="Y93">
+        <v>1.14</v>
+      </c>
+      <c r="Z93">
+        <v>1.68</v>
+      </c>
+      <c r="AA93">
+        <v>4</v>
+      </c>
+      <c r="AB93">
+        <v>4.4</v>
+      </c>
+      <c r="AC93">
+        <v>0</v>
+      </c>
+      <c r="AD93">
+        <v>0</v>
+      </c>
+      <c r="AE93">
+        <v>1.18</v>
+      </c>
+      <c r="AF93">
+        <v>5.15</v>
+      </c>
+      <c r="AG93">
+        <v>1.55</v>
+      </c>
+      <c r="AH93">
+        <v>2.28</v>
+      </c>
+      <c r="AI93">
+        <v>1.57</v>
+      </c>
+      <c r="AJ93">
+        <v>2.25</v>
+      </c>
+      <c r="AK93">
+        <v>1.2</v>
+      </c>
+      <c r="AL93">
+        <v>1.24</v>
+      </c>
+      <c r="AM93">
+        <v>2.32</v>
+      </c>
+      <c r="AN93">
+        <v>1.75</v>
+      </c>
+      <c r="AO93">
+        <v>2.33</v>
+      </c>
+      <c r="AP93">
+        <v>1.6</v>
+      </c>
+      <c r="AQ93">
+        <v>2</v>
+      </c>
+      <c r="AR93">
+        <v>1.68</v>
+      </c>
+      <c r="AS93">
+        <v>1.4</v>
+      </c>
+      <c r="AT93">
+        <v>3.08</v>
+      </c>
+      <c r="AU93">
+        <v>3</v>
+      </c>
+      <c r="AV93">
+        <v>3</v>
+      </c>
+      <c r="AW93">
+        <v>11</v>
+      </c>
+      <c r="AX93">
+        <v>6</v>
+      </c>
+      <c r="AY93">
+        <v>18</v>
+      </c>
+      <c r="AZ93">
+        <v>14</v>
+      </c>
+      <c r="BA93">
+        <v>9</v>
+      </c>
+      <c r="BB93">
+        <v>4</v>
+      </c>
+      <c r="BC93">
+        <v>13</v>
+      </c>
+      <c r="BD93">
+        <v>1.42</v>
+      </c>
+      <c r="BE93">
+        <v>9</v>
+      </c>
+      <c r="BF93">
+        <v>3.6</v>
+      </c>
+      <c r="BG93">
+        <v>1.33</v>
+      </c>
+      <c r="BH93">
+        <v>2.93</v>
+      </c>
+      <c r="BI93">
+        <v>1.61</v>
+      </c>
+      <c r="BJ93">
+        <v>2.23</v>
+      </c>
+      <c r="BK93">
+        <v>2</v>
+      </c>
+      <c r="BL93">
+        <v>1.79</v>
+      </c>
+      <c r="BM93">
+        <v>2.59</v>
+      </c>
+      <c r="BN93">
+        <v>1.45</v>
+      </c>
+      <c r="BO93">
+        <v>3.68</v>
+      </c>
+      <c r="BP93">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:68">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>7781171</v>
+      </c>
+      <c r="C94" t="s">
+        <v>68</v>
+      </c>
+      <c r="D94" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" s="2">
+        <v>45752.85416666666</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94" t="s">
+        <v>89</v>
+      </c>
+      <c r="H94" t="s">
+        <v>76</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94" t="s">
+        <v>109</v>
+      </c>
+      <c r="P94" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q94">
+        <v>2.75</v>
+      </c>
+      <c r="R94">
+        <v>2.38</v>
+      </c>
+      <c r="S94">
+        <v>3.5</v>
+      </c>
+      <c r="T94">
+        <v>1.3</v>
+      </c>
+      <c r="U94">
+        <v>3.4</v>
+      </c>
+      <c r="V94">
+        <v>2.5</v>
+      </c>
+      <c r="W94">
+        <v>1.5</v>
+      </c>
+      <c r="X94">
+        <v>6</v>
+      </c>
+      <c r="Y94">
+        <v>1.13</v>
+      </c>
+      <c r="Z94">
+        <v>2.15</v>
+      </c>
+      <c r="AA94">
+        <v>3.64</v>
+      </c>
+      <c r="AB94">
+        <v>3.04</v>
+      </c>
+      <c r="AC94">
+        <v>1</v>
+      </c>
+      <c r="AD94">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE94">
+        <v>1.31</v>
+      </c>
+      <c r="AF94">
+        <v>3.61</v>
+      </c>
+      <c r="AG94">
+        <v>1.54</v>
+      </c>
+      <c r="AH94">
+        <v>2.26</v>
+      </c>
+      <c r="AI94">
+        <v>1.53</v>
+      </c>
+      <c r="AJ94">
+        <v>2.38</v>
+      </c>
+      <c r="AK94">
+        <v>1.39</v>
+      </c>
+      <c r="AL94">
+        <v>1.32</v>
+      </c>
+      <c r="AM94">
+        <v>1.67</v>
+      </c>
+      <c r="AN94">
+        <v>2</v>
+      </c>
+      <c r="AO94">
+        <v>1.33</v>
+      </c>
+      <c r="AP94">
+        <v>1.75</v>
+      </c>
+      <c r="AQ94">
+        <v>1.25</v>
+      </c>
+      <c r="AR94">
+        <v>1.73</v>
+      </c>
+      <c r="AS94">
+        <v>1.45</v>
+      </c>
+      <c r="AT94">
+        <v>3.18</v>
+      </c>
+      <c r="AU94">
+        <v>5</v>
+      </c>
+      <c r="AV94">
+        <v>4</v>
+      </c>
+      <c r="AW94">
+        <v>17</v>
+      </c>
+      <c r="AX94">
+        <v>3</v>
+      </c>
+      <c r="AY94">
+        <v>29</v>
+      </c>
+      <c r="AZ94">
+        <v>10</v>
+      </c>
+      <c r="BA94">
+        <v>8</v>
+      </c>
+      <c r="BB94">
+        <v>2</v>
+      </c>
+      <c r="BC94">
+        <v>10</v>
+      </c>
+      <c r="BD94">
+        <v>1.53</v>
+      </c>
+      <c r="BE94">
+        <v>7.1</v>
+      </c>
+      <c r="BF94">
+        <v>3.35</v>
+      </c>
+      <c r="BG94">
+        <v>1.19</v>
+      </c>
+      <c r="BH94">
+        <v>3.8</v>
+      </c>
+      <c r="BI94">
+        <v>1.39</v>
+      </c>
+      <c r="BJ94">
+        <v>2.67</v>
+      </c>
+      <c r="BK94">
+        <v>1.7</v>
+      </c>
+      <c r="BL94">
+        <v>2.09</v>
+      </c>
+      <c r="BM94">
+        <v>2.13</v>
+      </c>
+      <c r="BN94">
+        <v>1.68</v>
+      </c>
+      <c r="BO94">
+        <v>2.81</v>
+      </c>
+      <c r="BP94">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="95" spans="1:68">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>7781168</v>
+      </c>
+      <c r="C95" t="s">
+        <v>68</v>
+      </c>
+      <c r="D95" t="s">
+        <v>69</v>
+      </c>
+      <c r="E95" s="2">
+        <v>45752.85416666666</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95" t="s">
+        <v>73</v>
+      </c>
+      <c r="H95" t="s">
+        <v>87</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>1</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>1</v>
+      </c>
+      <c r="O95" t="s">
+        <v>167</v>
+      </c>
+      <c r="P95" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q95">
+        <v>2.1</v>
+      </c>
+      <c r="R95">
+        <v>2.38</v>
+      </c>
+      <c r="S95">
+        <v>5.5</v>
+      </c>
+      <c r="T95">
+        <v>1.33</v>
+      </c>
+      <c r="U95">
+        <v>3.25</v>
+      </c>
+      <c r="V95">
+        <v>2.63</v>
+      </c>
+      <c r="W95">
+        <v>1.44</v>
+      </c>
+      <c r="X95">
+        <v>6.5</v>
+      </c>
+      <c r="Y95">
+        <v>1.11</v>
+      </c>
+      <c r="Z95">
+        <v>1.54</v>
+      </c>
+      <c r="AA95">
+        <v>4.2</v>
+      </c>
+      <c r="AB95">
+        <v>5.5</v>
+      </c>
+      <c r="AC95">
+        <v>1.01</v>
+      </c>
+      <c r="AD95">
+        <v>15</v>
+      </c>
+      <c r="AE95">
+        <v>1.24</v>
+      </c>
+      <c r="AF95">
+        <v>4.13</v>
+      </c>
+      <c r="AG95">
+        <v>1.65</v>
+      </c>
+      <c r="AH95">
+        <v>2.1</v>
+      </c>
+      <c r="AI95">
+        <v>1.8</v>
+      </c>
+      <c r="AJ95">
+        <v>1.95</v>
+      </c>
+      <c r="AK95">
+        <v>1.18</v>
+      </c>
+      <c r="AL95">
+        <v>1.25</v>
+      </c>
+      <c r="AM95">
+        <v>2.35</v>
+      </c>
+      <c r="AN95">
+        <v>2.33</v>
+      </c>
+      <c r="AO95">
+        <v>0.5</v>
+      </c>
+      <c r="AP95">
+        <v>2.5</v>
+      </c>
+      <c r="AQ95">
+        <v>0.33</v>
+      </c>
+      <c r="AR95">
+        <v>1.75</v>
+      </c>
+      <c r="AS95">
+        <v>1.06</v>
+      </c>
+      <c r="AT95">
+        <v>2.81</v>
+      </c>
+      <c r="AU95">
+        <v>2</v>
+      </c>
+      <c r="AV95">
+        <v>0</v>
+      </c>
+      <c r="AW95">
+        <v>0</v>
+      </c>
+      <c r="AX95">
+        <v>0</v>
+      </c>
+      <c r="AY95">
+        <v>6</v>
+      </c>
+      <c r="AZ95">
+        <v>1</v>
+      </c>
+      <c r="BA95">
+        <v>7</v>
+      </c>
+      <c r="BB95">
+        <v>10</v>
+      </c>
+      <c r="BC95">
+        <v>17</v>
+      </c>
+      <c r="BD95">
+        <v>1.36</v>
+      </c>
+      <c r="BE95">
+        <v>9.9</v>
+      </c>
+      <c r="BF95">
+        <v>3.86</v>
+      </c>
+      <c r="BG95">
+        <v>1.19</v>
+      </c>
+      <c r="BH95">
+        <v>3.74</v>
+      </c>
+      <c r="BI95">
+        <v>1.4</v>
+      </c>
+      <c r="BJ95">
+        <v>2.64</v>
+      </c>
+      <c r="BK95">
+        <v>1.73</v>
+      </c>
+      <c r="BL95">
+        <v>2.06</v>
+      </c>
+      <c r="BM95">
+        <v>2.18</v>
+      </c>
+      <c r="BN95">
+        <v>1.65</v>
+      </c>
+      <c r="BO95">
+        <v>2.83</v>
+      </c>
+      <c r="BP95">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="96" spans="1:68">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>7781169</v>
+      </c>
+      <c r="C96" t="s">
+        <v>68</v>
+      </c>
+      <c r="D96" t="s">
+        <v>69</v>
+      </c>
+      <c r="E96" s="2">
+        <v>45752.85416666666</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96" t="s">
+        <v>74</v>
+      </c>
+      <c r="H96" t="s">
+        <v>99</v>
+      </c>
+      <c r="I96">
+        <v>2</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>2</v>
+      </c>
+      <c r="L96">
+        <v>2</v>
+      </c>
+      <c r="M96">
+        <v>1</v>
+      </c>
+      <c r="N96">
+        <v>3</v>
+      </c>
+      <c r="O96" t="s">
+        <v>168</v>
+      </c>
+      <c r="P96" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q96">
+        <v>1.95</v>
+      </c>
+      <c r="R96">
+        <v>2.5</v>
+      </c>
+      <c r="S96">
+        <v>6.5</v>
+      </c>
+      <c r="T96">
+        <v>1.3</v>
+      </c>
+      <c r="U96">
+        <v>3.4</v>
+      </c>
+      <c r="V96">
+        <v>2.5</v>
+      </c>
+      <c r="W96">
+        <v>1.5</v>
+      </c>
+      <c r="X96">
+        <v>6</v>
+      </c>
+      <c r="Y96">
+        <v>1.13</v>
+      </c>
+      <c r="Z96">
+        <v>1.46</v>
+      </c>
+      <c r="AA96">
+        <v>4.6</v>
+      </c>
+      <c r="AB96">
+        <v>6</v>
+      </c>
+      <c r="AC96">
+        <v>1.01</v>
+      </c>
+      <c r="AD96">
+        <v>15</v>
+      </c>
+      <c r="AE96">
+        <v>1.25</v>
+      </c>
+      <c r="AF96">
+        <v>4.11</v>
+      </c>
+      <c r="AG96">
+        <v>1.61</v>
+      </c>
+      <c r="AH96">
+        <v>2.15</v>
+      </c>
+      <c r="AI96">
+        <v>1.8</v>
+      </c>
+      <c r="AJ96">
+        <v>1.95</v>
+      </c>
+      <c r="AK96">
+        <v>1.18</v>
+      </c>
+      <c r="AL96">
+        <v>1.25</v>
+      </c>
+      <c r="AM96">
+        <v>2.36</v>
+      </c>
+      <c r="AN96">
+        <v>1.67</v>
+      </c>
+      <c r="AO96">
+        <v>0.33</v>
+      </c>
+      <c r="AP96">
+        <v>2</v>
+      </c>
+      <c r="AQ96">
+        <v>0.29</v>
+      </c>
+      <c r="AR96">
+        <v>2.09</v>
+      </c>
+      <c r="AS96">
+        <v>1.24</v>
+      </c>
+      <c r="AT96">
+        <v>3.33</v>
+      </c>
+      <c r="AU96">
+        <v>6</v>
+      </c>
+      <c r="AV96">
+        <v>5</v>
+      </c>
+      <c r="AW96">
+        <v>5</v>
+      </c>
+      <c r="AX96">
+        <v>5</v>
+      </c>
+      <c r="AY96">
+        <v>13</v>
+      </c>
+      <c r="AZ96">
+        <v>11</v>
+      </c>
+      <c r="BA96">
+        <v>5</v>
+      </c>
+      <c r="BB96">
+        <v>3</v>
+      </c>
+      <c r="BC96">
+        <v>8</v>
+      </c>
+      <c r="BD96">
+        <v>1.28</v>
+      </c>
+      <c r="BE96">
+        <v>10.25</v>
+      </c>
+      <c r="BF96">
+        <v>4.65</v>
+      </c>
+      <c r="BG96">
+        <v>1.24</v>
+      </c>
+      <c r="BH96">
+        <v>3.34</v>
+      </c>
+      <c r="BI96">
+        <v>1.5</v>
+      </c>
+      <c r="BJ96">
+        <v>2.46</v>
+      </c>
+      <c r="BK96">
+        <v>1.87</v>
+      </c>
+      <c r="BL96">
+        <v>1.92</v>
+      </c>
+      <c r="BM96">
+        <v>2.33</v>
+      </c>
+      <c r="BN96">
+        <v>1.55</v>
+      </c>
+      <c r="BO96">
+        <v>3.14</v>
+      </c>
+      <c r="BP96">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="97" spans="1:68">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>7781170</v>
+      </c>
+      <c r="C97" t="s">
+        <v>68</v>
+      </c>
+      <c r="D97" t="s">
+        <v>69</v>
+      </c>
+      <c r="E97" s="2">
+        <v>45752.85416666666</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97" t="s">
+        <v>88</v>
+      </c>
+      <c r="H97" t="s">
+        <v>90</v>
+      </c>
+      <c r="I97">
+        <v>2</v>
+      </c>
+      <c r="J97">
+        <v>1</v>
+      </c>
+      <c r="K97">
+        <v>3</v>
+      </c>
+      <c r="L97">
+        <v>2</v>
+      </c>
+      <c r="M97">
+        <v>1</v>
+      </c>
+      <c r="N97">
+        <v>3</v>
+      </c>
+      <c r="O97" t="s">
+        <v>169</v>
+      </c>
+      <c r="P97" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q97">
+        <v>2.3</v>
+      </c>
+      <c r="R97">
+        <v>2.25</v>
+      </c>
+      <c r="S97">
+        <v>5</v>
+      </c>
+      <c r="T97">
+        <v>1.36</v>
+      </c>
+      <c r="U97">
+        <v>3</v>
+      </c>
+      <c r="V97">
+        <v>2.75</v>
+      </c>
+      <c r="W97">
+        <v>1.4</v>
+      </c>
+      <c r="X97">
+        <v>7</v>
+      </c>
+      <c r="Y97">
+        <v>1.1</v>
+      </c>
+      <c r="Z97">
+        <v>1.72</v>
+      </c>
+      <c r="AA97">
+        <v>3.53</v>
+      </c>
+      <c r="AB97">
+        <v>4.9</v>
+      </c>
+      <c r="AC97">
+        <v>1.02</v>
+      </c>
+      <c r="AD97">
+        <v>13</v>
+      </c>
+      <c r="AE97">
+        <v>1.26</v>
+      </c>
+      <c r="AF97">
+        <v>3.91</v>
+      </c>
+      <c r="AG97">
+        <v>1.8</v>
+      </c>
+      <c r="AH97">
+        <v>1.94</v>
+      </c>
+      <c r="AI97">
+        <v>1.8</v>
+      </c>
+      <c r="AJ97">
+        <v>1.95</v>
+      </c>
+      <c r="AK97">
+        <v>1.21</v>
+      </c>
+      <c r="AL97">
+        <v>1.32</v>
+      </c>
+      <c r="AM97">
+        <v>2.03</v>
+      </c>
+      <c r="AN97">
+        <v>2.33</v>
+      </c>
+      <c r="AO97">
+        <v>2.25</v>
+      </c>
+      <c r="AP97">
+        <v>2.5</v>
+      </c>
+      <c r="AQ97">
+        <v>1.8</v>
+      </c>
+      <c r="AR97">
+        <v>1.49</v>
+      </c>
+      <c r="AS97">
+        <v>1.65</v>
+      </c>
+      <c r="AT97">
+        <v>3.14</v>
+      </c>
+      <c r="AU97">
+        <v>8</v>
+      </c>
+      <c r="AV97">
+        <v>9</v>
+      </c>
+      <c r="AW97">
+        <v>1</v>
+      </c>
+      <c r="AX97">
+        <v>4</v>
+      </c>
+      <c r="AY97">
+        <v>9</v>
+      </c>
+      <c r="AZ97">
+        <v>13</v>
+      </c>
+      <c r="BA97">
+        <v>2</v>
+      </c>
+      <c r="BB97">
+        <v>4</v>
+      </c>
+      <c r="BC97">
+        <v>6</v>
+      </c>
+      <c r="BD97">
+        <v>1.45</v>
+      </c>
+      <c r="BE97">
+        <v>9</v>
+      </c>
+      <c r="BF97">
+        <v>3.42</v>
+      </c>
+      <c r="BG97">
+        <v>1.33</v>
+      </c>
+      <c r="BH97">
+        <v>2.83</v>
+      </c>
+      <c r="BI97">
+        <v>1.68</v>
+      </c>
+      <c r="BJ97">
+        <v>2.13</v>
+      </c>
+      <c r="BK97">
+        <v>2.13</v>
+      </c>
+      <c r="BL97">
+        <v>1.68</v>
+      </c>
+      <c r="BM97">
+        <v>2.78</v>
+      </c>
+      <c r="BN97">
+        <v>1.36</v>
+      </c>
+      <c r="BO97">
+        <v>3.84</v>
+      </c>
+      <c r="BP97">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="98" spans="1:68">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>7781167</v>
+      </c>
+      <c r="C98" t="s">
+        <v>68</v>
+      </c>
+      <c r="D98" t="s">
+        <v>69</v>
+      </c>
+      <c r="E98" s="2">
+        <v>45752.86458333334</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98" t="s">
+        <v>77</v>
+      </c>
+      <c r="H98" t="s">
+        <v>83</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98" t="s">
+        <v>109</v>
+      </c>
+      <c r="P98" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q98">
+        <v>2.4</v>
+      </c>
+      <c r="R98">
+        <v>2.2</v>
+      </c>
+      <c r="S98">
+        <v>4.75</v>
+      </c>
+      <c r="T98">
+        <v>1.36</v>
+      </c>
+      <c r="U98">
+        <v>3</v>
+      </c>
+      <c r="V98">
+        <v>2.75</v>
+      </c>
+      <c r="W98">
+        <v>1.4</v>
+      </c>
+      <c r="X98">
+        <v>8</v>
+      </c>
+      <c r="Y98">
+        <v>1.08</v>
+      </c>
+      <c r="Z98">
+        <v>1.79</v>
+      </c>
+      <c r="AA98">
+        <v>3.66</v>
+      </c>
+      <c r="AB98">
+        <v>4.2</v>
+      </c>
+      <c r="AC98">
+        <v>1</v>
+      </c>
+      <c r="AD98">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE98">
+        <v>1.21</v>
+      </c>
+      <c r="AF98">
+        <v>4.61</v>
+      </c>
+      <c r="AG98">
+        <v>1.81</v>
+      </c>
+      <c r="AH98">
+        <v>1.89</v>
+      </c>
+      <c r="AI98">
+        <v>1.8</v>
+      </c>
+      <c r="AJ98">
+        <v>1.95</v>
+      </c>
+      <c r="AK98">
+        <v>1.25</v>
+      </c>
+      <c r="AL98">
+        <v>1.28</v>
+      </c>
+      <c r="AM98">
+        <v>2.02</v>
+      </c>
+      <c r="AN98">
+        <v>2</v>
+      </c>
+      <c r="AO98">
+        <v>1.5</v>
+      </c>
+      <c r="AP98">
+        <v>1.75</v>
+      </c>
+      <c r="AQ98">
+        <v>1.33</v>
+      </c>
+      <c r="AR98">
+        <v>1.57</v>
+      </c>
+      <c r="AS98">
+        <v>1.33</v>
+      </c>
+      <c r="AT98">
+        <v>2.9</v>
+      </c>
+      <c r="AU98">
+        <v>2</v>
+      </c>
+      <c r="AV98">
+        <v>5</v>
+      </c>
+      <c r="AW98">
+        <v>11</v>
+      </c>
+      <c r="AX98">
+        <v>8</v>
+      </c>
+      <c r="AY98">
+        <v>15</v>
+      </c>
+      <c r="AZ98">
+        <v>18</v>
+      </c>
+      <c r="BA98">
+        <v>4</v>
+      </c>
+      <c r="BB98">
+        <v>6</v>
+      </c>
+      <c r="BC98">
+        <v>10</v>
+      </c>
+      <c r="BD98">
+        <v>1.44</v>
+      </c>
+      <c r="BE98">
+        <v>7.5</v>
+      </c>
+      <c r="BF98">
+        <v>3.78</v>
+      </c>
+      <c r="BG98">
+        <v>1.16</v>
+      </c>
+      <c r="BH98">
+        <v>4.05</v>
+      </c>
+      <c r="BI98">
+        <v>1.34</v>
+      </c>
+      <c r="BJ98">
+        <v>2.78</v>
+      </c>
+      <c r="BK98">
+        <v>1.64</v>
+      </c>
+      <c r="BL98">
+        <v>2.18</v>
+      </c>
+      <c r="BM98">
+        <v>2.04</v>
+      </c>
+      <c r="BN98">
+        <v>1.74</v>
+      </c>
+      <c r="BO98">
+        <v>2.67</v>
+      </c>
+      <c r="BP98">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="99" spans="1:68">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>7781172</v>
+      </c>
+      <c r="C99" t="s">
+        <v>68</v>
+      </c>
+      <c r="D99" t="s">
+        <v>69</v>
+      </c>
+      <c r="E99" s="2">
+        <v>45752.89583333334</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99" t="s">
+        <v>78</v>
+      </c>
+      <c r="H99" t="s">
+        <v>70</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="L99">
+        <v>1</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>1</v>
+      </c>
+      <c r="O99" t="s">
+        <v>129</v>
+      </c>
+      <c r="P99" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q99">
+        <v>3.1</v>
+      </c>
+      <c r="R99">
+        <v>2.1</v>
+      </c>
+      <c r="S99">
+        <v>3.5</v>
+      </c>
+      <c r="T99">
+        <v>1.4</v>
+      </c>
+      <c r="U99">
+        <v>2.75</v>
+      </c>
+      <c r="V99">
+        <v>3</v>
+      </c>
+      <c r="W99">
+        <v>1.36</v>
+      </c>
+      <c r="X99">
+        <v>8</v>
+      </c>
+      <c r="Y99">
+        <v>1.08</v>
+      </c>
+      <c r="Z99">
+        <v>2.41</v>
+      </c>
+      <c r="AA99">
+        <v>3.23</v>
+      </c>
+      <c r="AB99">
+        <v>2.9</v>
+      </c>
+      <c r="AC99">
+        <v>1.06</v>
+      </c>
+      <c r="AD99">
+        <v>8.5</v>
+      </c>
+      <c r="AE99">
+        <v>1.33</v>
+      </c>
+      <c r="AF99">
+        <v>3.25</v>
+      </c>
+      <c r="AG99">
+        <v>1.92</v>
+      </c>
+      <c r="AH99">
+        <v>1.82</v>
+      </c>
+      <c r="AI99">
+        <v>1.75</v>
+      </c>
+      <c r="AJ99">
+        <v>2</v>
+      </c>
+      <c r="AK99">
+        <v>1.4</v>
+      </c>
+      <c r="AL99">
+        <v>1.32</v>
+      </c>
+      <c r="AM99">
+        <v>1.53</v>
+      </c>
+      <c r="AN99">
+        <v>0</v>
+      </c>
+      <c r="AO99">
+        <v>1</v>
+      </c>
+      <c r="AP99">
+        <v>0.75</v>
+      </c>
+      <c r="AQ99">
+        <v>0.75</v>
+      </c>
+      <c r="AR99">
+        <v>1.45</v>
+      </c>
+      <c r="AS99">
+        <v>1.08</v>
+      </c>
+      <c r="AT99">
+        <v>2.53</v>
+      </c>
+      <c r="AU99">
+        <v>4</v>
+      </c>
+      <c r="AV99">
+        <v>3</v>
+      </c>
+      <c r="AW99">
+        <v>8</v>
+      </c>
+      <c r="AX99">
+        <v>8</v>
+      </c>
+      <c r="AY99">
+        <v>15</v>
+      </c>
+      <c r="AZ99">
+        <v>13</v>
+      </c>
+      <c r="BA99">
+        <v>9</v>
+      </c>
+      <c r="BB99">
+        <v>4</v>
+      </c>
+      <c r="BC99">
+        <v>13</v>
+      </c>
+      <c r="BD99">
+        <v>1.86</v>
+      </c>
+      <c r="BE99">
+        <v>6.5</v>
+      </c>
+      <c r="BF99">
+        <v>2.12</v>
+      </c>
+      <c r="BG99">
+        <v>1.32</v>
+      </c>
+      <c r="BH99">
+        <v>3.05</v>
+      </c>
+      <c r="BI99">
+        <v>1.55</v>
+      </c>
+      <c r="BJ99">
+        <v>2.28</v>
+      </c>
+      <c r="BK99">
+        <v>1.89</v>
+      </c>
+      <c r="BL99">
+        <v>1.8</v>
+      </c>
+      <c r="BM99">
+        <v>2.38</v>
+      </c>
+      <c r="BN99">
+        <v>1.5</v>
+      </c>
+      <c r="BO99">
+        <v>3.05</v>
+      </c>
+      <c r="BP99">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:68">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>7781173</v>
+      </c>
+      <c r="C100" t="s">
+        <v>68</v>
+      </c>
+      <c r="D100" t="s">
+        <v>69</v>
+      </c>
+      <c r="E100" s="2">
+        <v>45752.89583333334</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100" t="s">
+        <v>91</v>
+      </c>
+      <c r="H100" t="s">
+        <v>80</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+      <c r="L100">
+        <v>2</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>2</v>
+      </c>
+      <c r="O100" t="s">
+        <v>170</v>
+      </c>
+      <c r="P100" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q100">
+        <v>2.88</v>
+      </c>
+      <c r="R100">
+        <v>2.2</v>
+      </c>
+      <c r="S100">
+        <v>3.6</v>
+      </c>
+      <c r="T100">
+        <v>1.36</v>
+      </c>
+      <c r="U100">
+        <v>3</v>
+      </c>
+      <c r="V100">
+        <v>2.63</v>
+      </c>
+      <c r="W100">
+        <v>1.44</v>
+      </c>
+      <c r="X100">
+        <v>7</v>
+      </c>
+      <c r="Y100">
+        <v>1.1</v>
+      </c>
+      <c r="Z100">
+        <v>2.14</v>
+      </c>
+      <c r="AA100">
+        <v>3.66</v>
+      </c>
+      <c r="AB100">
+        <v>3.04</v>
+      </c>
+      <c r="AC100">
+        <v>1.05</v>
+      </c>
+      <c r="AD100">
+        <v>9.5</v>
+      </c>
+      <c r="AE100">
+        <v>1.25</v>
+      </c>
+      <c r="AF100">
+        <v>3.85</v>
+      </c>
+      <c r="AG100">
+        <v>1.79</v>
+      </c>
+      <c r="AH100">
+        <v>1.95</v>
+      </c>
+      <c r="AI100">
+        <v>1.62</v>
+      </c>
+      <c r="AJ100">
+        <v>2.2</v>
+      </c>
+      <c r="AK100">
+        <v>1.36</v>
+      </c>
+      <c r="AL100">
+        <v>1.27</v>
+      </c>
+      <c r="AM100">
+        <v>1.65</v>
+      </c>
+      <c r="AN100">
+        <v>0.33</v>
+      </c>
+      <c r="AO100">
+        <v>1.33</v>
+      </c>
+      <c r="AP100">
+        <v>1</v>
+      </c>
+      <c r="AQ100">
+        <v>1</v>
+      </c>
+      <c r="AR100">
+        <v>1.7</v>
+      </c>
+      <c r="AS100">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AT100">
+        <v>2.64</v>
+      </c>
+      <c r="AU100">
+        <v>7</v>
+      </c>
+      <c r="AV100">
+        <v>4</v>
+      </c>
+      <c r="AW100">
+        <v>6</v>
+      </c>
+      <c r="AX100">
+        <v>8</v>
+      </c>
+      <c r="AY100">
+        <v>13</v>
+      </c>
+      <c r="AZ100">
+        <v>12</v>
+      </c>
+      <c r="BA100">
+        <v>3</v>
+      </c>
+      <c r="BB100">
+        <v>4</v>
+      </c>
+      <c r="BC100">
+        <v>7</v>
+      </c>
+      <c r="BD100">
+        <v>1.68</v>
+      </c>
+      <c r="BE100">
+        <v>6.5</v>
+      </c>
+      <c r="BF100">
+        <v>2.4</v>
+      </c>
+      <c r="BG100">
+        <v>1.32</v>
+      </c>
+      <c r="BH100">
+        <v>3.05</v>
+      </c>
+      <c r="BI100">
+        <v>1.54</v>
+      </c>
+      <c r="BJ100">
+        <v>2.28</v>
+      </c>
+      <c r="BK100">
+        <v>1.9</v>
+      </c>
+      <c r="BL100">
+        <v>1.79</v>
+      </c>
+      <c r="BM100">
+        <v>2.38</v>
+      </c>
+      <c r="BN100">
+        <v>1.5</v>
+      </c>
+      <c r="BO100">
+        <v>3.05</v>
+      </c>
+      <c r="BP100">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="101" spans="1:68">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>7781174</v>
+      </c>
+      <c r="C101" t="s">
+        <v>68</v>
+      </c>
+      <c r="D101" t="s">
+        <v>69</v>
+      </c>
+      <c r="E101" s="2">
+        <v>45752.9375</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101" t="s">
+        <v>95</v>
+      </c>
+      <c r="H101" t="s">
+        <v>93</v>
+      </c>
+      <c r="I101">
+        <v>2</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>2</v>
+      </c>
+      <c r="L101">
+        <v>2</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>2</v>
+      </c>
+      <c r="O101" t="s">
+        <v>171</v>
+      </c>
+      <c r="P101" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q101">
+        <v>2.25</v>
+      </c>
+      <c r="R101">
+        <v>2.38</v>
+      </c>
+      <c r="S101">
+        <v>4.75</v>
+      </c>
+      <c r="T101">
+        <v>1.33</v>
+      </c>
+      <c r="U101">
+        <v>3.25</v>
+      </c>
+      <c r="V101">
+        <v>2.5</v>
+      </c>
+      <c r="W101">
+        <v>1.5</v>
+      </c>
+      <c r="X101">
+        <v>6</v>
+      </c>
+      <c r="Y101">
+        <v>1.13</v>
+      </c>
+      <c r="Z101">
+        <v>1.69</v>
+      </c>
+      <c r="AA101">
+        <v>3.88</v>
+      </c>
+      <c r="AB101">
+        <v>4.5</v>
+      </c>
+      <c r="AC101">
+        <v>1.04</v>
+      </c>
+      <c r="AD101">
+        <v>10</v>
+      </c>
+      <c r="AE101">
+        <v>1.22</v>
+      </c>
+      <c r="AF101">
+        <v>4.2</v>
+      </c>
+      <c r="AG101">
+        <v>1.57</v>
+      </c>
+      <c r="AH101">
+        <v>2.25</v>
+      </c>
+      <c r="AI101">
+        <v>1.67</v>
+      </c>
+      <c r="AJ101">
+        <v>2.1</v>
+      </c>
+      <c r="AK101">
+        <v>1.21</v>
+      </c>
+      <c r="AL101">
+        <v>1.24</v>
+      </c>
+      <c r="AM101">
+        <v>2.05</v>
+      </c>
+      <c r="AN101">
+        <v>2</v>
+      </c>
+      <c r="AO101">
+        <v>2.33</v>
+      </c>
+      <c r="AP101">
+        <v>2.25</v>
+      </c>
+      <c r="AQ101">
+        <v>1.75</v>
+      </c>
+      <c r="AR101">
+        <v>1.75</v>
+      </c>
+      <c r="AS101">
+        <v>0.92</v>
+      </c>
+      <c r="AT101">
+        <v>2.67</v>
+      </c>
+      <c r="AU101">
+        <v>8</v>
+      </c>
+      <c r="AV101">
+        <v>0</v>
+      </c>
+      <c r="AW101">
+        <v>10</v>
+      </c>
+      <c r="AX101">
+        <v>9</v>
+      </c>
+      <c r="AY101">
+        <v>20</v>
+      </c>
+      <c r="AZ101">
+        <v>12</v>
+      </c>
+      <c r="BA101">
+        <v>7</v>
+      </c>
+      <c r="BB101">
+        <v>8</v>
+      </c>
+      <c r="BC101">
+        <v>15</v>
+      </c>
+      <c r="BD101">
+        <v>1.49</v>
+      </c>
+      <c r="BE101">
+        <v>6.75</v>
+      </c>
+      <c r="BF101">
+        <v>2.9</v>
+      </c>
+      <c r="BG101">
+        <v>1.29</v>
+      </c>
+      <c r="BH101">
+        <v>3.2</v>
+      </c>
+      <c r="BI101">
+        <v>1.5</v>
+      </c>
+      <c r="BJ101">
+        <v>2.4</v>
+      </c>
+      <c r="BK101">
+        <v>1.8</v>
+      </c>
+      <c r="BL101">
+        <v>1.88</v>
+      </c>
+      <c r="BM101">
+        <v>2.28</v>
+      </c>
+      <c r="BN101">
+        <v>1.55</v>
+      </c>
+      <c r="BO101">
+        <v>2.9</v>
+      </c>
+      <c r="BP101">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="102" spans="1:68">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>7781175</v>
+      </c>
+      <c r="C102" t="s">
+        <v>68</v>
+      </c>
+      <c r="D102" t="s">
+        <v>69</v>
+      </c>
+      <c r="E102" s="2">
+        <v>45752.97916666666</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102" t="s">
+        <v>94</v>
+      </c>
+      <c r="H102" t="s">
+        <v>82</v>
+      </c>
+      <c r="I102">
+        <v>3</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>3</v>
+      </c>
+      <c r="L102">
+        <v>3</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>3</v>
+      </c>
+      <c r="O102" t="s">
+        <v>172</v>
+      </c>
+      <c r="P102" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q102">
+        <v>0</v>
+      </c>
+      <c r="R102">
+        <v>0</v>
+      </c>
+      <c r="S102">
+        <v>0</v>
+      </c>
+      <c r="T102">
+        <v>0</v>
+      </c>
+      <c r="U102">
+        <v>0</v>
+      </c>
+      <c r="V102">
+        <v>0</v>
+      </c>
+      <c r="W102">
+        <v>0</v>
+      </c>
+      <c r="X102">
+        <v>0</v>
+      </c>
+      <c r="Y102">
+        <v>0</v>
+      </c>
+      <c r="Z102">
+        <v>2.27</v>
+      </c>
+      <c r="AA102">
+        <v>3.33</v>
+      </c>
+      <c r="AB102">
+        <v>3.03</v>
+      </c>
+      <c r="AC102">
+        <v>0</v>
+      </c>
+      <c r="AD102">
+        <v>0</v>
+      </c>
+      <c r="AE102">
+        <v>0</v>
+      </c>
+      <c r="AF102">
+        <v>0</v>
+      </c>
+      <c r="AG102">
+        <v>1.95</v>
+      </c>
+      <c r="AH102">
+        <v>1.79</v>
+      </c>
+      <c r="AI102">
+        <v>0</v>
+      </c>
+      <c r="AJ102">
+        <v>0</v>
+      </c>
+      <c r="AK102">
+        <v>0</v>
+      </c>
+      <c r="AL102">
+        <v>0</v>
+      </c>
+      <c r="AM102">
+        <v>0</v>
+      </c>
+      <c r="AN102">
+        <v>1.67</v>
+      </c>
+      <c r="AO102">
+        <v>0.33</v>
+      </c>
+      <c r="AP102">
+        <v>2</v>
+      </c>
+      <c r="AQ102">
+        <v>0.25</v>
+      </c>
+      <c r="AR102">
+        <v>2.01</v>
+      </c>
+      <c r="AS102">
+        <v>1.83</v>
+      </c>
+      <c r="AT102">
+        <v>3.84</v>
+      </c>
+      <c r="AU102">
+        <v>-1</v>
+      </c>
+      <c r="AV102">
+        <v>-1</v>
+      </c>
+      <c r="AW102">
+        <v>-1</v>
+      </c>
+      <c r="AX102">
+        <v>-1</v>
+      </c>
+      <c r="AY102">
+        <v>-1</v>
+      </c>
+      <c r="AZ102">
+        <v>-1</v>
+      </c>
+      <c r="BA102">
+        <v>-1</v>
+      </c>
+      <c r="BB102">
+        <v>-1</v>
+      </c>
+      <c r="BC102">
+        <v>-1</v>
+      </c>
+      <c r="BD102">
+        <v>0</v>
+      </c>
+      <c r="BE102">
+        <v>0</v>
+      </c>
+      <c r="BF102">
+        <v>0</v>
+      </c>
+      <c r="BG102">
+        <v>0</v>
+      </c>
+      <c r="BH102">
+        <v>0</v>
+      </c>
+      <c r="BI102">
+        <v>0</v>
+      </c>
+      <c r="BJ102">
+        <v>0</v>
+      </c>
+      <c r="BK102">
+        <v>0</v>
+      </c>
+      <c r="BL102">
+        <v>0</v>
+      </c>
+      <c r="BM102">
+        <v>0</v>
+      </c>
+      <c r="BN102">
+        <v>0</v>
+      </c>
+      <c r="BO102">
+        <v>0</v>
+      </c>
+      <c r="BP102">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="226">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -535,6 +535,12 @@
     <t>['2', '41', '45+3']</t>
   </si>
   <si>
+    <t>['8', '16', '20', '81', '89', '90+2']</t>
+  </si>
+  <si>
+    <t>['45+5']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -683,6 +689,9 @@
   </si>
   <si>
     <t>['60']</t>
+  </si>
+  <si>
+    <t>['1', '29']</t>
   </si>
 </sst>
 </file>
@@ -1044,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP102"/>
+  <dimension ref="A1:BP105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1381,7 +1390,7 @@
         <v>2</v>
       </c>
       <c r="AQ2">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1506,7 +1515,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -1584,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
         <v>0.5</v>
@@ -1712,7 +1721,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2124,7 +2133,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2330,7 +2339,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2411,7 +2420,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ7">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2536,7 +2545,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -2948,7 +2957,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -3644,7 +3653,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AQ13">
         <v>1</v>
@@ -3772,7 +3781,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -3978,7 +3987,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4184,7 +4193,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4802,7 +4811,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -5214,7 +5223,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -5295,7 +5304,7 @@
         <v>2</v>
       </c>
       <c r="AQ21">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AR21">
         <v>2.07</v>
@@ -5420,7 +5429,7 @@
         <v>116</v>
       </c>
       <c r="P22" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5626,7 +5635,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -5707,7 +5716,7 @@
         <v>1</v>
       </c>
       <c r="AQ23">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -5832,7 +5841,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6244,7 +6253,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -7274,7 +7283,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7686,7 +7695,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -8179,7 +8188,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ35">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AR35">
         <v>1.23</v>
@@ -8304,7 +8313,7 @@
         <v>127</v>
       </c>
       <c r="P36" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q36">
         <v>2.4</v>
@@ -8510,7 +8519,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -8794,7 +8803,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ38">
         <v>1.25</v>
@@ -9128,7 +9137,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9540,7 +9549,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -10030,10 +10039,10 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AQ44">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR44">
         <v>1.88</v>
@@ -10236,7 +10245,7 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ45">
         <v>0.33</v>
@@ -10364,7 +10373,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10570,7 +10579,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -10776,7 +10785,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11600,7 +11609,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -11678,7 +11687,7 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ52">
         <v>0.33</v>
@@ -11806,7 +11815,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -11887,7 +11896,7 @@
         <v>1</v>
       </c>
       <c r="AQ53">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR53">
         <v>1.56</v>
@@ -12012,7 +12021,7 @@
         <v>109</v>
       </c>
       <c r="P54" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12218,7 +12227,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -12836,7 +12845,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -12914,7 +12923,7 @@
         <v>2</v>
       </c>
       <c r="AP58">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AQ58">
         <v>1.75</v>
@@ -13042,7 +13051,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13248,7 +13257,7 @@
         <v>143</v>
       </c>
       <c r="P60" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13454,7 +13463,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -13660,7 +13669,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -13866,7 +13875,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14072,7 +14081,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -14565,7 +14574,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ66">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AR66">
         <v>1.35</v>
@@ -14690,7 +14699,7 @@
         <v>148</v>
       </c>
       <c r="P67" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q67">
         <v>2.3</v>
@@ -14771,7 +14780,7 @@
         <v>2</v>
       </c>
       <c r="AQ67">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR67">
         <v>1.65</v>
@@ -15102,7 +15111,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15514,7 +15523,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -15720,7 +15729,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16132,7 +16141,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16544,7 +16553,7 @@
         <v>153</v>
       </c>
       <c r="P76" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q76">
         <v>3.6</v>
@@ -17162,7 +17171,7 @@
         <v>155</v>
       </c>
       <c r="P79" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q79">
         <v>2.1</v>
@@ -17240,7 +17249,7 @@
         <v>3</v>
       </c>
       <c r="AP79">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ79">
         <v>2</v>
@@ -17368,7 +17377,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -17574,7 +17583,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -17780,7 +17789,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -18398,7 +18407,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -18604,7 +18613,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -18810,7 +18819,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -19016,7 +19025,7 @@
         <v>163</v>
       </c>
       <c r="P88" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q88">
         <v>3.25</v>
@@ -19094,7 +19103,7 @@
         <v>0</v>
       </c>
       <c r="AP88">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AQ88">
         <v>0.25</v>
@@ -19428,7 +19437,7 @@
         <v>164</v>
       </c>
       <c r="P90" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
@@ -20046,7 +20055,7 @@
         <v>131</v>
       </c>
       <c r="P93" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q93">
         <v>2.2</v>
@@ -20664,7 +20673,7 @@
         <v>168</v>
       </c>
       <c r="P96" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -22057,6 +22066,624 @@
       </c>
       <c r="BP102">
         <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:68">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>7781176</v>
+      </c>
+      <c r="C103" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103" s="2">
+        <v>45753.66666666666</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103" t="s">
+        <v>96</v>
+      </c>
+      <c r="H103" t="s">
+        <v>92</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>2</v>
+      </c>
+      <c r="K103">
+        <v>2</v>
+      </c>
+      <c r="L103">
+        <v>1</v>
+      </c>
+      <c r="M103">
+        <v>2</v>
+      </c>
+      <c r="N103">
+        <v>3</v>
+      </c>
+      <c r="O103" t="s">
+        <v>122</v>
+      </c>
+      <c r="P103" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q103">
+        <v>2.75</v>
+      </c>
+      <c r="R103">
+        <v>2.25</v>
+      </c>
+      <c r="S103">
+        <v>3.75</v>
+      </c>
+      <c r="T103">
+        <v>1.36</v>
+      </c>
+      <c r="U103">
+        <v>3</v>
+      </c>
+      <c r="V103">
+        <v>2.63</v>
+      </c>
+      <c r="W103">
+        <v>1.44</v>
+      </c>
+      <c r="X103">
+        <v>7</v>
+      </c>
+      <c r="Y103">
+        <v>1.1</v>
+      </c>
+      <c r="Z103">
+        <v>2.05</v>
+      </c>
+      <c r="AA103">
+        <v>3.6</v>
+      </c>
+      <c r="AB103">
+        <v>3.27</v>
+      </c>
+      <c r="AC103">
+        <v>1.05</v>
+      </c>
+      <c r="AD103">
+        <v>9.5</v>
+      </c>
+      <c r="AE103">
+        <v>1.25</v>
+      </c>
+      <c r="AF103">
+        <v>3.8</v>
+      </c>
+      <c r="AG103">
+        <v>1.6</v>
+      </c>
+      <c r="AH103">
+        <v>2.2</v>
+      </c>
+      <c r="AI103">
+        <v>1.67</v>
+      </c>
+      <c r="AJ103">
+        <v>2.1</v>
+      </c>
+      <c r="AK103">
+        <v>1.34</v>
+      </c>
+      <c r="AL103">
+        <v>1.28</v>
+      </c>
+      <c r="AM103">
+        <v>1.68</v>
+      </c>
+      <c r="AN103">
+        <v>3</v>
+      </c>
+      <c r="AO103">
+        <v>1.33</v>
+      </c>
+      <c r="AP103">
+        <v>2</v>
+      </c>
+      <c r="AQ103">
+        <v>1.75</v>
+      </c>
+      <c r="AR103">
+        <v>1.61</v>
+      </c>
+      <c r="AS103">
+        <v>1.49</v>
+      </c>
+      <c r="AT103">
+        <v>3.1</v>
+      </c>
+      <c r="AU103">
+        <v>5</v>
+      </c>
+      <c r="AV103">
+        <v>10</v>
+      </c>
+      <c r="AW103">
+        <v>19</v>
+      </c>
+      <c r="AX103">
+        <v>7</v>
+      </c>
+      <c r="AY103">
+        <v>26</v>
+      </c>
+      <c r="AZ103">
+        <v>17</v>
+      </c>
+      <c r="BA103">
+        <v>9</v>
+      </c>
+      <c r="BB103">
+        <v>8</v>
+      </c>
+      <c r="BC103">
+        <v>17</v>
+      </c>
+      <c r="BD103">
+        <v>1.65</v>
+      </c>
+      <c r="BE103">
+        <v>6.5</v>
+      </c>
+      <c r="BF103">
+        <v>2.48</v>
+      </c>
+      <c r="BG103">
+        <v>1.27</v>
+      </c>
+      <c r="BH103">
+        <v>3.3</v>
+      </c>
+      <c r="BI103">
+        <v>1.48</v>
+      </c>
+      <c r="BJ103">
+        <v>2.45</v>
+      </c>
+      <c r="BK103">
+        <v>1.77</v>
+      </c>
+      <c r="BL103">
+        <v>1.92</v>
+      </c>
+      <c r="BM103">
+        <v>2.18</v>
+      </c>
+      <c r="BN103">
+        <v>1.58</v>
+      </c>
+      <c r="BO103">
+        <v>2.8</v>
+      </c>
+      <c r="BP103">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="104" spans="1:68">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>7781178</v>
+      </c>
+      <c r="C104" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45753.75</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104" t="s">
+        <v>81</v>
+      </c>
+      <c r="H104" t="s">
+        <v>75</v>
+      </c>
+      <c r="I104">
+        <v>3</v>
+      </c>
+      <c r="J104">
+        <v>1</v>
+      </c>
+      <c r="K104">
+        <v>4</v>
+      </c>
+      <c r="L104">
+        <v>6</v>
+      </c>
+      <c r="M104">
+        <v>1</v>
+      </c>
+      <c r="N104">
+        <v>7</v>
+      </c>
+      <c r="O104" t="s">
+        <v>173</v>
+      </c>
+      <c r="P104" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q104">
+        <v>2.75</v>
+      </c>
+      <c r="R104">
+        <v>2.38</v>
+      </c>
+      <c r="S104">
+        <v>3.4</v>
+      </c>
+      <c r="T104">
+        <v>1.29</v>
+      </c>
+      <c r="U104">
+        <v>3.5</v>
+      </c>
+      <c r="V104">
+        <v>2.25</v>
+      </c>
+      <c r="W104">
+        <v>1.57</v>
+      </c>
+      <c r="X104">
+        <v>5.5</v>
+      </c>
+      <c r="Y104">
+        <v>1.14</v>
+      </c>
+      <c r="Z104">
+        <v>2.22</v>
+      </c>
+      <c r="AA104">
+        <v>3.59</v>
+      </c>
+      <c r="AB104">
+        <v>2.93</v>
+      </c>
+      <c r="AC104">
+        <v>1.04</v>
+      </c>
+      <c r="AD104">
+        <v>10</v>
+      </c>
+      <c r="AE104">
+        <v>1.18</v>
+      </c>
+      <c r="AF104">
+        <v>4.75</v>
+      </c>
+      <c r="AG104">
+        <v>1.55</v>
+      </c>
+      <c r="AH104">
+        <v>2.3</v>
+      </c>
+      <c r="AI104">
+        <v>1.5</v>
+      </c>
+      <c r="AJ104">
+        <v>2.5</v>
+      </c>
+      <c r="AK104">
+        <v>1.4</v>
+      </c>
+      <c r="AL104">
+        <v>1.27</v>
+      </c>
+      <c r="AM104">
+        <v>1.61</v>
+      </c>
+      <c r="AN104">
+        <v>1</v>
+      </c>
+      <c r="AO104">
+        <v>0.5</v>
+      </c>
+      <c r="AP104">
+        <v>1.4</v>
+      </c>
+      <c r="AQ104">
+        <v>0.33</v>
+      </c>
+      <c r="AR104">
+        <v>1.95</v>
+      </c>
+      <c r="AS104">
+        <v>1.9</v>
+      </c>
+      <c r="AT104">
+        <v>3.85</v>
+      </c>
+      <c r="AU104">
+        <v>11</v>
+      </c>
+      <c r="AV104">
+        <v>12</v>
+      </c>
+      <c r="AW104">
+        <v>10</v>
+      </c>
+      <c r="AX104">
+        <v>6</v>
+      </c>
+      <c r="AY104">
+        <v>23</v>
+      </c>
+      <c r="AZ104">
+        <v>19</v>
+      </c>
+      <c r="BA104">
+        <v>3</v>
+      </c>
+      <c r="BB104">
+        <v>4</v>
+      </c>
+      <c r="BC104">
+        <v>7</v>
+      </c>
+      <c r="BD104">
+        <v>1.95</v>
+      </c>
+      <c r="BE104">
+        <v>6.75</v>
+      </c>
+      <c r="BF104">
+        <v>2.02</v>
+      </c>
+      <c r="BG104">
+        <v>1.23</v>
+      </c>
+      <c r="BH104">
+        <v>3.65</v>
+      </c>
+      <c r="BI104">
+        <v>1.41</v>
+      </c>
+      <c r="BJ104">
+        <v>2.65</v>
+      </c>
+      <c r="BK104">
+        <v>1.66</v>
+      </c>
+      <c r="BL104">
+        <v>2.07</v>
+      </c>
+      <c r="BM104">
+        <v>2.04</v>
+      </c>
+      <c r="BN104">
+        <v>1.68</v>
+      </c>
+      <c r="BO104">
+        <v>2.55</v>
+      </c>
+      <c r="BP104">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="105" spans="1:68">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>7781177</v>
+      </c>
+      <c r="C105" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105" s="2">
+        <v>45753.83333333334</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105" t="s">
+        <v>71</v>
+      </c>
+      <c r="H105" t="s">
+        <v>98</v>
+      </c>
+      <c r="I105">
+        <v>1</v>
+      </c>
+      <c r="J105">
+        <v>1</v>
+      </c>
+      <c r="K105">
+        <v>2</v>
+      </c>
+      <c r="L105">
+        <v>1</v>
+      </c>
+      <c r="M105">
+        <v>1</v>
+      </c>
+      <c r="N105">
+        <v>2</v>
+      </c>
+      <c r="O105" t="s">
+        <v>174</v>
+      </c>
+      <c r="P105" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q105">
+        <v>1.91</v>
+      </c>
+      <c r="R105">
+        <v>2.6</v>
+      </c>
+      <c r="S105">
+        <v>6</v>
+      </c>
+      <c r="T105">
+        <v>1.29</v>
+      </c>
+      <c r="U105">
+        <v>3.5</v>
+      </c>
+      <c r="V105">
+        <v>2.25</v>
+      </c>
+      <c r="W105">
+        <v>1.57</v>
+      </c>
+      <c r="X105">
+        <v>5.5</v>
+      </c>
+      <c r="Y105">
+        <v>1.14</v>
+      </c>
+      <c r="Z105">
+        <v>1.41</v>
+      </c>
+      <c r="AA105">
+        <v>4.9</v>
+      </c>
+      <c r="AB105">
+        <v>6.4</v>
+      </c>
+      <c r="AC105">
+        <v>1.01</v>
+      </c>
+      <c r="AD105">
+        <v>13</v>
+      </c>
+      <c r="AE105">
+        <v>1.18</v>
+      </c>
+      <c r="AF105">
+        <v>4.75</v>
+      </c>
+      <c r="AG105">
+        <v>1.52</v>
+      </c>
+      <c r="AH105">
+        <v>2.43</v>
+      </c>
+      <c r="AI105">
+        <v>1.7</v>
+      </c>
+      <c r="AJ105">
+        <v>2.05</v>
+      </c>
+      <c r="AK105">
+        <v>1.12</v>
+      </c>
+      <c r="AL105">
+        <v>1.17</v>
+      </c>
+      <c r="AM105">
+        <v>2.75</v>
+      </c>
+      <c r="AN105">
+        <v>2.33</v>
+      </c>
+      <c r="AO105">
+        <v>0.25</v>
+      </c>
+      <c r="AP105">
+        <v>2</v>
+      </c>
+      <c r="AQ105">
+        <v>0.4</v>
+      </c>
+      <c r="AR105">
+        <v>1.1</v>
+      </c>
+      <c r="AS105">
+        <v>1.16</v>
+      </c>
+      <c r="AT105">
+        <v>2.26</v>
+      </c>
+      <c r="AU105">
+        <v>11</v>
+      </c>
+      <c r="AV105">
+        <v>3</v>
+      </c>
+      <c r="AW105">
+        <v>15</v>
+      </c>
+      <c r="AX105">
+        <v>10</v>
+      </c>
+      <c r="AY105">
+        <v>31</v>
+      </c>
+      <c r="AZ105">
+        <v>15</v>
+      </c>
+      <c r="BA105">
+        <v>10</v>
+      </c>
+      <c r="BB105">
+        <v>3</v>
+      </c>
+      <c r="BC105">
+        <v>13</v>
+      </c>
+      <c r="BD105">
+        <v>1.46</v>
+      </c>
+      <c r="BE105">
+        <v>6.75</v>
+      </c>
+      <c r="BF105">
+        <v>3.05</v>
+      </c>
+      <c r="BG105">
+        <v>1.35</v>
+      </c>
+      <c r="BH105">
+        <v>2.9</v>
+      </c>
+      <c r="BI105">
+        <v>1.6</v>
+      </c>
+      <c r="BJ105">
+        <v>2.17</v>
+      </c>
+      <c r="BK105">
+        <v>1.96</v>
+      </c>
+      <c r="BL105">
+        <v>1.74</v>
+      </c>
+      <c r="BM105">
+        <v>2.48</v>
+      </c>
+      <c r="BN105">
+        <v>1.47</v>
+      </c>
+      <c r="BO105">
+        <v>3.3</v>
+      </c>
+      <c r="BP105">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -21249,7 +21249,7 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>7781172</v>
+        <v>7781173</v>
       </c>
       <c r="C99" t="s">
         <v>68</v>
@@ -21264,10 +21264,10 @@
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="H99" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -21279,145 +21279,145 @@
         <v>0</v>
       </c>
       <c r="L99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M99">
         <v>0</v>
       </c>
       <c r="N99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O99" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="P99" t="s">
         <v>109</v>
       </c>
       <c r="Q99">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R99">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S99">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T99">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U99">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="V99">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="W99">
+        <v>1.44</v>
+      </c>
+      <c r="X99">
+        <v>7</v>
+      </c>
+      <c r="Y99">
+        <v>1.1</v>
+      </c>
+      <c r="Z99">
+        <v>2.14</v>
+      </c>
+      <c r="AA99">
+        <v>3.66</v>
+      </c>
+      <c r="AB99">
+        <v>3.04</v>
+      </c>
+      <c r="AC99">
+        <v>1.05</v>
+      </c>
+      <c r="AD99">
+        <v>9.5</v>
+      </c>
+      <c r="AE99">
+        <v>1.25</v>
+      </c>
+      <c r="AF99">
+        <v>3.85</v>
+      </c>
+      <c r="AG99">
+        <v>1.79</v>
+      </c>
+      <c r="AH99">
+        <v>1.95</v>
+      </c>
+      <c r="AI99">
+        <v>1.62</v>
+      </c>
+      <c r="AJ99">
+        <v>2.2</v>
+      </c>
+      <c r="AK99">
         <v>1.36</v>
       </c>
-      <c r="X99">
-        <v>8</v>
-      </c>
-      <c r="Y99">
-        <v>1.08</v>
-      </c>
-      <c r="Z99">
-        <v>2.41</v>
-      </c>
-      <c r="AA99">
-        <v>3.23</v>
-      </c>
-      <c r="AB99">
-        <v>2.9</v>
-      </c>
-      <c r="AC99">
-        <v>1.06</v>
-      </c>
-      <c r="AD99">
-        <v>8.5</v>
-      </c>
-      <c r="AE99">
+      <c r="AL99">
+        <v>1.27</v>
+      </c>
+      <c r="AM99">
+        <v>1.65</v>
+      </c>
+      <c r="AN99">
+        <v>0.33</v>
+      </c>
+      <c r="AO99">
         <v>1.33</v>
       </c>
-      <c r="AF99">
-        <v>3.25</v>
-      </c>
-      <c r="AG99">
-        <v>1.92</v>
-      </c>
-      <c r="AH99">
-        <v>1.82</v>
-      </c>
-      <c r="AI99">
-        <v>1.75</v>
-      </c>
-      <c r="AJ99">
-        <v>2</v>
-      </c>
-      <c r="AK99">
-        <v>1.4</v>
-      </c>
-      <c r="AL99">
-        <v>1.32</v>
-      </c>
-      <c r="AM99">
-        <v>1.53</v>
-      </c>
-      <c r="AN99">
-        <v>0</v>
-      </c>
-      <c r="AO99">
-        <v>1</v>
-      </c>
       <c r="AP99">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ99">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR99">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AS99">
-        <v>1.08</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AT99">
-        <v>2.53</v>
+        <v>2.64</v>
       </c>
       <c r="AU99">
+        <v>7</v>
+      </c>
+      <c r="AV99">
         <v>4</v>
       </c>
-      <c r="AV99">
-        <v>3</v>
-      </c>
       <c r="AW99">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX99">
         <v>8</v>
       </c>
       <c r="AY99">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ99">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA99">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BB99">
         <v>4</v>
       </c>
       <c r="BC99">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BD99">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="BE99">
         <v>6.5</v>
       </c>
       <c r="BF99">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="BG99">
         <v>1.32</v>
@@ -21426,16 +21426,16 @@
         <v>3.05</v>
       </c>
       <c r="BI99">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="BJ99">
         <v>2.28</v>
       </c>
       <c r="BK99">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BL99">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="BM99">
         <v>2.38</v>
@@ -21447,7 +21447,7 @@
         <v>3.05</v>
       </c>
       <c r="BP99">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="100" spans="1:68">
@@ -21455,7 +21455,7 @@
         <v>99</v>
       </c>
       <c r="B100">
-        <v>7781173</v>
+        <v>7781172</v>
       </c>
       <c r="C100" t="s">
         <v>68</v>
@@ -21464,16 +21464,16 @@
         <v>69</v>
       </c>
       <c r="E100" s="2">
-        <v>45752.89583333334</v>
+        <v>45752.91666666666</v>
       </c>
       <c r="F100">
         <v>0</v>
       </c>
       <c r="G100" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="H100" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -21485,145 +21485,145 @@
         <v>0</v>
       </c>
       <c r="L100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M100">
         <v>0</v>
       </c>
       <c r="N100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="P100" t="s">
         <v>109</v>
       </c>
       <c r="Q100">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R100">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S100">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T100">
+        <v>1.4</v>
+      </c>
+      <c r="U100">
+        <v>2.75</v>
+      </c>
+      <c r="V100">
+        <v>3</v>
+      </c>
+      <c r="W100">
         <v>1.36</v>
       </c>
-      <c r="U100">
+      <c r="X100">
+        <v>8</v>
+      </c>
+      <c r="Y100">
+        <v>1.08</v>
+      </c>
+      <c r="Z100">
+        <v>2.41</v>
+      </c>
+      <c r="AA100">
+        <v>3.23</v>
+      </c>
+      <c r="AB100">
+        <v>2.9</v>
+      </c>
+      <c r="AC100">
+        <v>1.06</v>
+      </c>
+      <c r="AD100">
+        <v>8.5</v>
+      </c>
+      <c r="AE100">
+        <v>1.33</v>
+      </c>
+      <c r="AF100">
+        <v>3.25</v>
+      </c>
+      <c r="AG100">
+        <v>1.92</v>
+      </c>
+      <c r="AH100">
+        <v>1.82</v>
+      </c>
+      <c r="AI100">
+        <v>1.75</v>
+      </c>
+      <c r="AJ100">
+        <v>2</v>
+      </c>
+      <c r="AK100">
+        <v>1.4</v>
+      </c>
+      <c r="AL100">
+        <v>1.32</v>
+      </c>
+      <c r="AM100">
+        <v>1.53</v>
+      </c>
+      <c r="AN100">
+        <v>0</v>
+      </c>
+      <c r="AO100">
+        <v>1</v>
+      </c>
+      <c r="AP100">
+        <v>0.75</v>
+      </c>
+      <c r="AQ100">
+        <v>0.75</v>
+      </c>
+      <c r="AR100">
+        <v>1.45</v>
+      </c>
+      <c r="AS100">
+        <v>1.08</v>
+      </c>
+      <c r="AT100">
+        <v>2.53</v>
+      </c>
+      <c r="AU100">
+        <v>4</v>
+      </c>
+      <c r="AV100">
         <v>3</v>
       </c>
-      <c r="V100">
-        <v>2.63</v>
-      </c>
-      <c r="W100">
-        <v>1.44</v>
-      </c>
-      <c r="X100">
-        <v>7</v>
-      </c>
-      <c r="Y100">
-        <v>1.1</v>
-      </c>
-      <c r="Z100">
-        <v>2.14</v>
-      </c>
-      <c r="AA100">
-        <v>3.66</v>
-      </c>
-      <c r="AB100">
-        <v>3.04</v>
-      </c>
-      <c r="AC100">
-        <v>1.05</v>
-      </c>
-      <c r="AD100">
-        <v>9.5</v>
-      </c>
-      <c r="AE100">
-        <v>1.25</v>
-      </c>
-      <c r="AF100">
-        <v>3.85</v>
-      </c>
-      <c r="AG100">
-        <v>1.79</v>
-      </c>
-      <c r="AH100">
-        <v>1.95</v>
-      </c>
-      <c r="AI100">
-        <v>1.62</v>
-      </c>
-      <c r="AJ100">
-        <v>2.2</v>
-      </c>
-      <c r="AK100">
-        <v>1.36</v>
-      </c>
-      <c r="AL100">
-        <v>1.27</v>
-      </c>
-      <c r="AM100">
-        <v>1.65</v>
-      </c>
-      <c r="AN100">
-        <v>0.33</v>
-      </c>
-      <c r="AO100">
-        <v>1.33</v>
-      </c>
-      <c r="AP100">
-        <v>1</v>
-      </c>
-      <c r="AQ100">
-        <v>1</v>
-      </c>
-      <c r="AR100">
-        <v>1.7</v>
-      </c>
-      <c r="AS100">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AT100">
-        <v>2.64</v>
-      </c>
-      <c r="AU100">
-        <v>7</v>
-      </c>
-      <c r="AV100">
-        <v>4</v>
-      </c>
       <c r="AW100">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX100">
         <v>8</v>
       </c>
       <c r="AY100">
+        <v>15</v>
+      </c>
+      <c r="AZ100">
         <v>13</v>
       </c>
-      <c r="AZ100">
-        <v>12</v>
-      </c>
       <c r="BA100">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="BB100">
         <v>4</v>
       </c>
       <c r="BC100">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BD100">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="BE100">
         <v>6.5</v>
       </c>
       <c r="BF100">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="BG100">
         <v>1.32</v>
@@ -21632,16 +21632,16 @@
         <v>3.05</v>
       </c>
       <c r="BI100">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="BJ100">
         <v>2.28</v>
       </c>
       <c r="BK100">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="BL100">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BM100">
         <v>2.38</v>
@@ -21653,7 +21653,7 @@
         <v>3.05</v>
       </c>
       <c r="BP100">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="101" spans="1:68">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -21611,10 +21611,10 @@
         <v>9</v>
       </c>
       <c r="BB100">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC100">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD100">
         <v>1.86</v>
@@ -22002,31 +22002,31 @@
         <v>3.84</v>
       </c>
       <c r="AU102">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AV102">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW102">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AX102">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AY102">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AZ102">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="BA102">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BB102">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BC102">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD102">
         <v>0</v>
@@ -22641,10 +22641,10 @@
         <v>10</v>
       </c>
       <c r="BB105">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC105">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD105">
         <v>1.46</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="388">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -811,6 +811,15 @@
     <t>['60']</t>
   </si>
   <si>
+    <t>['55', '9001']</t>
+  </si>
+  <si>
+    <t>['40', '70', '88']</t>
+  </si>
+  <si>
+    <t>['4501', '59', '9003']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -1530,7 +1539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP251"/>
+  <dimension ref="A1:BP254"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1864,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ2">
         <v>1.67</v>
@@ -1992,7 +2001,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -2198,7 +2207,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2610,7 +2619,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2816,7 +2825,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3022,7 +3031,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -3309,7 +3318,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ9">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3434,7 +3443,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -4258,7 +4267,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -4464,7 +4473,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4542,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ15">
         <v>2.14</v>
@@ -4670,7 +4679,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -5163,7 +5172,7 @@
         <v>1</v>
       </c>
       <c r="AQ18">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5288,7 +5297,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -5700,7 +5709,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -6112,7 +6121,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6318,7 +6327,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6730,7 +6739,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -7014,7 +7023,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ27">
         <v>0.88</v>
@@ -7220,7 +7229,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ28">
         <v>1.11</v>
@@ -7429,7 +7438,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ29">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -7632,7 +7641,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ30">
         <v>0.22</v>
@@ -7760,7 +7769,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -8172,7 +8181,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -8871,7 +8880,7 @@
         <v>1</v>
       </c>
       <c r="AQ36">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR36">
         <v>1.23</v>
@@ -8996,7 +9005,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9614,7 +9623,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -10026,7 +10035,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -10310,7 +10319,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ43">
         <v>0.5</v>
@@ -10850,7 +10859,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -10931,7 +10940,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ46">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR46">
         <v>0.92</v>
@@ -11056,7 +11065,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -11262,7 +11271,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11546,7 +11555,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ49">
         <v>1.11</v>
@@ -12086,7 +12095,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12292,7 +12301,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12704,7 +12713,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -12991,7 +13000,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ56">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR56">
         <v>2.14</v>
@@ -13322,7 +13331,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13528,7 +13537,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13812,7 +13821,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ60">
         <v>0.22</v>
@@ -13940,7 +13949,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14146,7 +14155,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -14352,7 +14361,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14558,7 +14567,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -15463,7 +15472,7 @@
         <v>2</v>
       </c>
       <c r="AQ68">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR68">
         <v>1.48</v>
@@ -15588,7 +15597,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -16000,7 +16009,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16206,7 +16215,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16618,7 +16627,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16696,7 +16705,7 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ74">
         <v>1.8</v>
@@ -17030,7 +17039,7 @@
         <v>153</v>
       </c>
       <c r="P76" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q76">
         <v>3.6</v>
@@ -17854,7 +17863,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18060,7 +18069,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18266,7 +18275,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -18553,7 +18562,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ83">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR83">
         <v>1.35</v>
@@ -18884,7 +18893,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -19090,7 +19099,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -19296,7 +19305,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -19583,7 +19592,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ88">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR88">
         <v>2.16</v>
@@ -19914,7 +19923,7 @@
         <v>164</v>
       </c>
       <c r="P90" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
@@ -19992,7 +20001,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ90">
         <v>1.25</v>
@@ -21150,7 +21159,7 @@
         <v>168</v>
       </c>
       <c r="P96" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21849,7 +21858,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ99">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR99">
         <v>1.7</v>
@@ -22258,7 +22267,7 @@
         <v>2.33</v>
       </c>
       <c r="AP101">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ101">
         <v>1</v>
@@ -22467,7 +22476,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ102">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR102">
         <v>2.01</v>
@@ -22592,7 +22601,7 @@
         <v>122</v>
       </c>
       <c r="P103" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q103">
         <v>2.75</v>
@@ -22798,7 +22807,7 @@
         <v>173</v>
       </c>
       <c r="P104" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q104">
         <v>2.75</v>
@@ -23004,7 +23013,7 @@
         <v>174</v>
       </c>
       <c r="P105" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q105">
         <v>1.91</v>
@@ -24034,7 +24043,7 @@
         <v>175</v>
       </c>
       <c r="P110" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24112,7 +24121,7 @@
         <v>2</v>
       </c>
       <c r="AP110">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ110">
         <v>1.11</v>
@@ -24240,7 +24249,7 @@
         <v>109</v>
       </c>
       <c r="P111" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q111">
         <v>2.88</v>
@@ -24733,7 +24742,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ113">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR113">
         <v>1.19</v>
@@ -24858,7 +24867,7 @@
         <v>177</v>
       </c>
       <c r="P114" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25064,7 +25073,7 @@
         <v>178</v>
       </c>
       <c r="P115" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -25476,7 +25485,7 @@
         <v>179</v>
       </c>
       <c r="P117" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25554,7 +25563,7 @@
         <v>1.5</v>
       </c>
       <c r="AP117">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ117">
         <v>1.25</v>
@@ -25682,7 +25691,7 @@
         <v>180</v>
       </c>
       <c r="P118" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -26094,7 +26103,7 @@
         <v>181</v>
       </c>
       <c r="P120" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -26506,7 +26515,7 @@
         <v>109</v>
       </c>
       <c r="P122" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q122">
         <v>2.75</v>
@@ -26918,7 +26927,7 @@
         <v>129</v>
       </c>
       <c r="P124" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q124">
         <v>2.5</v>
@@ -27948,7 +27957,7 @@
         <v>187</v>
       </c>
       <c r="P129" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28154,7 +28163,7 @@
         <v>188</v>
       </c>
       <c r="P130" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q130">
         <v>2.4</v>
@@ -28978,7 +28987,7 @@
         <v>189</v>
       </c>
       <c r="P134" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q134">
         <v>3</v>
@@ -29056,7 +29065,7 @@
         <v>0.75</v>
       </c>
       <c r="AP134">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ134">
         <v>0.88</v>
@@ -29184,7 +29193,7 @@
         <v>190</v>
       </c>
       <c r="P135" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -29265,7 +29274,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ135">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR135">
         <v>2.04</v>
@@ -29471,7 +29480,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ136">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR136">
         <v>1.75</v>
@@ -30420,7 +30429,7 @@
         <v>109</v>
       </c>
       <c r="P141" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q141">
         <v>2.38</v>
@@ -30832,7 +30841,7 @@
         <v>174</v>
       </c>
       <c r="P143" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -31244,7 +31253,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q145">
         <v>2.4</v>
@@ -31450,7 +31459,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31531,7 +31540,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ146">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR146">
         <v>1.83</v>
@@ -31656,7 +31665,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q147">
         <v>2.6</v>
@@ -31862,7 +31871,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q148">
         <v>2.05</v>
@@ -32068,7 +32077,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -32146,10 +32155,10 @@
         <v>1</v>
       </c>
       <c r="AP149">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ149">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR149">
         <v>1.48</v>
@@ -32274,7 +32283,7 @@
         <v>202</v>
       </c>
       <c r="P150" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q150">
         <v>2.4</v>
@@ -32480,7 +32489,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q151">
         <v>2.63</v>
@@ -32686,7 +32695,7 @@
         <v>109</v>
       </c>
       <c r="P152" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q152">
         <v>2.88</v>
@@ -32892,7 +32901,7 @@
         <v>204</v>
       </c>
       <c r="P153" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -33098,7 +33107,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q154">
         <v>3.1</v>
@@ -33304,7 +33313,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q155">
         <v>2.2</v>
@@ -33510,7 +33519,7 @@
         <v>207</v>
       </c>
       <c r="P156" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33716,7 +33725,7 @@
         <v>109</v>
       </c>
       <c r="P157" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q157">
         <v>3.2</v>
@@ -34334,7 +34343,7 @@
         <v>209</v>
       </c>
       <c r="P160" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q160">
         <v>2.1</v>
@@ -34412,7 +34421,7 @@
         <v>1.2</v>
       </c>
       <c r="AP160">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ160">
         <v>0.8</v>
@@ -34618,7 +34627,7 @@
         <v>0.75</v>
       </c>
       <c r="AP161">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ161">
         <v>1.25</v>
@@ -34746,7 +34755,7 @@
         <v>211</v>
       </c>
       <c r="P162" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q162">
         <v>2.5</v>
@@ -35033,7 +35042,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ163">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR163">
         <v>1.87</v>
@@ -35776,7 +35785,7 @@
         <v>215</v>
       </c>
       <c r="P167" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -36188,7 +36197,7 @@
         <v>217</v>
       </c>
       <c r="P169" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q169">
         <v>3</v>
@@ -36394,7 +36403,7 @@
         <v>218</v>
       </c>
       <c r="P170" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36600,7 +36609,7 @@
         <v>109</v>
       </c>
       <c r="P171" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q171">
         <v>2.25</v>
@@ -36806,7 +36815,7 @@
         <v>219</v>
       </c>
       <c r="P172" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q172">
         <v>2.4</v>
@@ -37218,7 +37227,7 @@
         <v>221</v>
       </c>
       <c r="P174" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q174">
         <v>2.5</v>
@@ -37424,7 +37433,7 @@
         <v>163</v>
       </c>
       <c r="P175" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -37505,7 +37514,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ175">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR175">
         <v>1.61</v>
@@ -37630,7 +37639,7 @@
         <v>113</v>
       </c>
       <c r="P176" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q176">
         <v>2.4</v>
@@ -37836,7 +37845,7 @@
         <v>222</v>
       </c>
       <c r="P177" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -38042,7 +38051,7 @@
         <v>109</v>
       </c>
       <c r="P178" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q178">
         <v>2.38</v>
@@ -38326,10 +38335,10 @@
         <v>0.6</v>
       </c>
       <c r="AP179">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ179">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR179">
         <v>1.28</v>
@@ -38454,7 +38463,7 @@
         <v>224</v>
       </c>
       <c r="P180" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38532,7 +38541,7 @@
         <v>0.8</v>
       </c>
       <c r="AP180">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ180">
         <v>0.88</v>
@@ -38866,7 +38875,7 @@
         <v>225</v>
       </c>
       <c r="P182" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q182">
         <v>3.75</v>
@@ -39072,7 +39081,7 @@
         <v>226</v>
       </c>
       <c r="P183" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q183">
         <v>2.5</v>
@@ -39278,7 +39287,7 @@
         <v>227</v>
       </c>
       <c r="P184" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q184">
         <v>2.05</v>
@@ -39690,7 +39699,7 @@
         <v>228</v>
       </c>
       <c r="P186" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q186">
         <v>2.4</v>
@@ -40102,7 +40111,7 @@
         <v>230</v>
       </c>
       <c r="P188" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40183,7 +40192,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ188">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR188">
         <v>1.67</v>
@@ -40308,7 +40317,7 @@
         <v>176</v>
       </c>
       <c r="P189" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40798,10 +40807,10 @@
         <v>1.14</v>
       </c>
       <c r="AP191">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AQ191">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR191">
         <v>1.76</v>
@@ -41132,7 +41141,7 @@
         <v>233</v>
       </c>
       <c r="P193" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41338,7 +41347,7 @@
         <v>234</v>
       </c>
       <c r="P194" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41750,7 +41759,7 @@
         <v>198</v>
       </c>
       <c r="P196" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q196">
         <v>2.63</v>
@@ -41956,7 +41965,7 @@
         <v>109</v>
       </c>
       <c r="P197" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q197">
         <v>2.75</v>
@@ -42162,7 +42171,7 @@
         <v>103</v>
       </c>
       <c r="P198" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q198">
         <v>2.63</v>
@@ -42655,7 +42664,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ200">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR200">
         <v>1.69</v>
@@ -43192,7 +43201,7 @@
         <v>109</v>
       </c>
       <c r="P203" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q203">
         <v>2.63</v>
@@ -43604,7 +43613,7 @@
         <v>237</v>
       </c>
       <c r="P205" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -43682,10 +43691,10 @@
         <v>1</v>
       </c>
       <c r="AP205">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ205">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR205">
         <v>1.3</v>
@@ -43891,7 +43900,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ206">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR206">
         <v>1.84</v>
@@ -44016,7 +44025,7 @@
         <v>109</v>
       </c>
       <c r="P207" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q207">
         <v>2.25</v>
@@ -44840,7 +44849,7 @@
         <v>240</v>
       </c>
       <c r="P211" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q211">
         <v>3.2</v>
@@ -45046,7 +45055,7 @@
         <v>109</v>
       </c>
       <c r="P212" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45252,7 +45261,7 @@
         <v>241</v>
       </c>
       <c r="P213" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q213">
         <v>4</v>
@@ -45664,7 +45673,7 @@
         <v>242</v>
       </c>
       <c r="P215" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -45870,7 +45879,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="Q216">
         <v>3.4</v>
@@ -46076,7 +46085,7 @@
         <v>243</v>
       </c>
       <c r="P217" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="Q217">
         <v>2.75</v>
@@ -46488,7 +46497,7 @@
         <v>244</v>
       </c>
       <c r="P219" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="Q219">
         <v>3.1</v>
@@ -46775,7 +46784,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ220">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR220">
         <v>1.69</v>
@@ -46900,7 +46909,7 @@
         <v>246</v>
       </c>
       <c r="P221" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Q221">
         <v>2.6</v>
@@ -47106,7 +47115,7 @@
         <v>247</v>
       </c>
       <c r="P222" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="Q222">
         <v>2.5</v>
@@ -47312,7 +47321,7 @@
         <v>248</v>
       </c>
       <c r="P223" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47518,7 +47527,7 @@
         <v>249</v>
       </c>
       <c r="P224" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47724,7 +47733,7 @@
         <v>250</v>
       </c>
       <c r="P225" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -47930,7 +47939,7 @@
         <v>251</v>
       </c>
       <c r="P226" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q226">
         <v>2.75</v>
@@ -48136,7 +48145,7 @@
         <v>252</v>
       </c>
       <c r="P227" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Q227">
         <v>1.83</v>
@@ -48342,7 +48351,7 @@
         <v>253</v>
       </c>
       <c r="P228" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48548,7 +48557,7 @@
         <v>109</v>
       </c>
       <c r="P229" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="Q229">
         <v>2.5</v>
@@ -48754,7 +48763,7 @@
         <v>254</v>
       </c>
       <c r="P230" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q230">
         <v>3.25</v>
@@ -48960,7 +48969,7 @@
         <v>119</v>
       </c>
       <c r="P231" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="Q231">
         <v>2.4</v>
@@ -49578,7 +49587,7 @@
         <v>109</v>
       </c>
       <c r="P234" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q234">
         <v>2.5</v>
@@ -49862,7 +49871,7 @@
         <v>1.14</v>
       </c>
       <c r="AP235">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ235">
         <v>1</v>
@@ -50068,7 +50077,7 @@
         <v>1.57</v>
       </c>
       <c r="AP236">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ236">
         <v>1.67</v>
@@ -50196,7 +50205,7 @@
         <v>258</v>
       </c>
       <c r="P237" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Q237">
         <v>2.75</v>
@@ -50402,7 +50411,7 @@
         <v>259</v>
       </c>
       <c r="P238" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Q238">
         <v>2.6</v>
@@ -50608,7 +50617,7 @@
         <v>109</v>
       </c>
       <c r="P239" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -50814,7 +50823,7 @@
         <v>140</v>
       </c>
       <c r="P240" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -51226,7 +51235,7 @@
         <v>109</v>
       </c>
       <c r="P242" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="Q242">
         <v>3.1</v>
@@ -51638,7 +51647,7 @@
         <v>161</v>
       </c>
       <c r="P244" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="Q244">
         <v>2.1</v>
@@ -52050,7 +52059,7 @@
         <v>156</v>
       </c>
       <c r="P246" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="Q246">
         <v>2.5</v>
@@ -52131,7 +52140,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ246">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR246">
         <v>1.72</v>
@@ -52668,7 +52677,7 @@
         <v>176</v>
       </c>
       <c r="P249" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q249">
         <v>2.5</v>
@@ -52874,7 +52883,7 @@
         <v>264</v>
       </c>
       <c r="P250" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="Q250">
         <v>3.2</v>
@@ -52970,19 +52979,19 @@
         <v>4</v>
       </c>
       <c r="AV250">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AW250">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX250">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY250">
+        <v>10</v>
+      </c>
+      <c r="AZ250">
         <v>13</v>
-      </c>
-      <c r="AZ250">
-        <v>15</v>
       </c>
       <c r="BA250">
         <v>9</v>
@@ -53080,7 +53089,7 @@
         <v>109</v>
       </c>
       <c r="P251" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q251">
         <v>2.75</v>
@@ -53173,22 +53182,22 @@
         <v>2.84</v>
       </c>
       <c r="AU251">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AV251">
         <v>7</v>
       </c>
       <c r="AW251">
+        <v>5</v>
+      </c>
+      <c r="AX251">
         <v>6</v>
       </c>
-      <c r="AX251">
-        <v>2</v>
-      </c>
       <c r="AY251">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AZ251">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BA251">
         <v>11</v>
@@ -53237,6 +53246,624 @@
       </c>
       <c r="BP251">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="252" spans="1:68">
+      <c r="A252" s="1">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>7781328</v>
+      </c>
+      <c r="C252" t="s">
+        <v>68</v>
+      </c>
+      <c r="D252" t="s">
+        <v>69</v>
+      </c>
+      <c r="E252" s="2">
+        <v>45816.83333333334</v>
+      </c>
+      <c r="F252">
+        <v>0</v>
+      </c>
+      <c r="G252" t="s">
+        <v>83</v>
+      </c>
+      <c r="H252" t="s">
+        <v>80</v>
+      </c>
+      <c r="I252">
+        <v>0</v>
+      </c>
+      <c r="J252">
+        <v>0</v>
+      </c>
+      <c r="K252">
+        <v>0</v>
+      </c>
+      <c r="L252">
+        <v>2</v>
+      </c>
+      <c r="M252">
+        <v>1</v>
+      </c>
+      <c r="N252">
+        <v>3</v>
+      </c>
+      <c r="O252" t="s">
+        <v>265</v>
+      </c>
+      <c r="P252" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q252">
+        <v>2.25</v>
+      </c>
+      <c r="R252">
+        <v>2.5</v>
+      </c>
+      <c r="S252">
+        <v>4.33</v>
+      </c>
+      <c r="T252">
+        <v>1.25</v>
+      </c>
+      <c r="U252">
+        <v>3.75</v>
+      </c>
+      <c r="V252">
+        <v>2.2</v>
+      </c>
+      <c r="W252">
+        <v>1.62</v>
+      </c>
+      <c r="X252">
+        <v>5</v>
+      </c>
+      <c r="Y252">
+        <v>1.17</v>
+      </c>
+      <c r="Z252">
+        <v>1.7</v>
+      </c>
+      <c r="AA252">
+        <v>3.75</v>
+      </c>
+      <c r="AB252">
+        <v>3.8</v>
+      </c>
+      <c r="AC252">
+        <v>1.04</v>
+      </c>
+      <c r="AD252">
+        <v>10</v>
+      </c>
+      <c r="AE252">
+        <v>1.18</v>
+      </c>
+      <c r="AF252">
+        <v>4.75</v>
+      </c>
+      <c r="AG252">
+        <v>1.51</v>
+      </c>
+      <c r="AH252">
+        <v>2.39</v>
+      </c>
+      <c r="AI252">
+        <v>1.53</v>
+      </c>
+      <c r="AJ252">
+        <v>2.38</v>
+      </c>
+      <c r="AK252">
+        <v>1.22</v>
+      </c>
+      <c r="AL252">
+        <v>1.24</v>
+      </c>
+      <c r="AM252">
+        <v>2.05</v>
+      </c>
+      <c r="AN252">
+        <v>1.88</v>
+      </c>
+      <c r="AO252">
+        <v>0.63</v>
+      </c>
+      <c r="AP252">
+        <v>2</v>
+      </c>
+      <c r="AQ252">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR252">
+        <v>1.24</v>
+      </c>
+      <c r="AS252">
+        <v>1.17</v>
+      </c>
+      <c r="AT252">
+        <v>2.41</v>
+      </c>
+      <c r="AU252">
+        <v>3</v>
+      </c>
+      <c r="AV252">
+        <v>2</v>
+      </c>
+      <c r="AW252">
+        <v>0</v>
+      </c>
+      <c r="AX252">
+        <v>0</v>
+      </c>
+      <c r="AY252">
+        <v>3</v>
+      </c>
+      <c r="AZ252">
+        <v>2</v>
+      </c>
+      <c r="BA252">
+        <v>7</v>
+      </c>
+      <c r="BB252">
+        <v>4</v>
+      </c>
+      <c r="BC252">
+        <v>11</v>
+      </c>
+      <c r="BD252">
+        <v>1.65</v>
+      </c>
+      <c r="BE252">
+        <v>6.5</v>
+      </c>
+      <c r="BF252">
+        <v>2.48</v>
+      </c>
+      <c r="BG252">
+        <v>1.28</v>
+      </c>
+      <c r="BH252">
+        <v>3.3</v>
+      </c>
+      <c r="BI252">
+        <v>1.48</v>
+      </c>
+      <c r="BJ252">
+        <v>2.43</v>
+      </c>
+      <c r="BK252">
+        <v>1.78</v>
+      </c>
+      <c r="BL252">
+        <v>1.91</v>
+      </c>
+      <c r="BM252">
+        <v>2.2</v>
+      </c>
+      <c r="BN252">
+        <v>1.58</v>
+      </c>
+      <c r="BO252">
+        <v>2.8</v>
+      </c>
+      <c r="BP252">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="253" spans="1:68">
+      <c r="A253" s="1">
+        <v>252</v>
+      </c>
+      <c r="B253">
+        <v>7781329</v>
+      </c>
+      <c r="C253" t="s">
+        <v>68</v>
+      </c>
+      <c r="D253" t="s">
+        <v>69</v>
+      </c>
+      <c r="E253" s="2">
+        <v>45816.91666666666</v>
+      </c>
+      <c r="F253">
+        <v>0</v>
+      </c>
+      <c r="G253" t="s">
+        <v>95</v>
+      </c>
+      <c r="H253" t="s">
+        <v>82</v>
+      </c>
+      <c r="I253">
+        <v>1</v>
+      </c>
+      <c r="J253">
+        <v>0</v>
+      </c>
+      <c r="K253">
+        <v>1</v>
+      </c>
+      <c r="L253">
+        <v>3</v>
+      </c>
+      <c r="M253">
+        <v>0</v>
+      </c>
+      <c r="N253">
+        <v>3</v>
+      </c>
+      <c r="O253" t="s">
+        <v>266</v>
+      </c>
+      <c r="P253" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q253">
+        <v>3.75</v>
+      </c>
+      <c r="R253">
+        <v>2.2</v>
+      </c>
+      <c r="S253">
+        <v>2.88</v>
+      </c>
+      <c r="T253">
+        <v>1.36</v>
+      </c>
+      <c r="U253">
+        <v>3</v>
+      </c>
+      <c r="V253">
+        <v>2.75</v>
+      </c>
+      <c r="W253">
+        <v>1.4</v>
+      </c>
+      <c r="X253">
+        <v>7</v>
+      </c>
+      <c r="Y253">
+        <v>1.1</v>
+      </c>
+      <c r="Z253">
+        <v>2.82</v>
+      </c>
+      <c r="AA253">
+        <v>3.13</v>
+      </c>
+      <c r="AB253">
+        <v>2.24</v>
+      </c>
+      <c r="AC253">
+        <v>1.06</v>
+      </c>
+      <c r="AD253">
+        <v>8.5</v>
+      </c>
+      <c r="AE253">
+        <v>1.3</v>
+      </c>
+      <c r="AF253">
+        <v>3.45</v>
+      </c>
+      <c r="AG253">
+        <v>1.86</v>
+      </c>
+      <c r="AH253">
+        <v>1.84</v>
+      </c>
+      <c r="AI253">
+        <v>1.7</v>
+      </c>
+      <c r="AJ253">
+        <v>2.05</v>
+      </c>
+      <c r="AK253">
+        <v>1.57</v>
+      </c>
+      <c r="AL253">
+        <v>1.3</v>
+      </c>
+      <c r="AM253">
+        <v>1.38</v>
+      </c>
+      <c r="AN253">
+        <v>2.13</v>
+      </c>
+      <c r="AO253">
+        <v>1</v>
+      </c>
+      <c r="AP253">
+        <v>2.22</v>
+      </c>
+      <c r="AQ253">
+        <v>0.9</v>
+      </c>
+      <c r="AR253">
+        <v>1.96</v>
+      </c>
+      <c r="AS253">
+        <v>1.56</v>
+      </c>
+      <c r="AT253">
+        <v>3.52</v>
+      </c>
+      <c r="AU253">
+        <v>7</v>
+      </c>
+      <c r="AV253">
+        <v>2</v>
+      </c>
+      <c r="AW253">
+        <v>9</v>
+      </c>
+      <c r="AX253">
+        <v>8</v>
+      </c>
+      <c r="AY253">
+        <v>16</v>
+      </c>
+      <c r="AZ253">
+        <v>10</v>
+      </c>
+      <c r="BA253">
+        <v>3</v>
+      </c>
+      <c r="BB253">
+        <v>3</v>
+      </c>
+      <c r="BC253">
+        <v>6</v>
+      </c>
+      <c r="BD253">
+        <v>2.17</v>
+      </c>
+      <c r="BE253">
+        <v>6.75</v>
+      </c>
+      <c r="BF253">
+        <v>1.82</v>
+      </c>
+      <c r="BG253">
+        <v>1.23</v>
+      </c>
+      <c r="BH253">
+        <v>3.65</v>
+      </c>
+      <c r="BI253">
+        <v>1.41</v>
+      </c>
+      <c r="BJ253">
+        <v>2.65</v>
+      </c>
+      <c r="BK253">
+        <v>1.66</v>
+      </c>
+      <c r="BL253">
+        <v>2.06</v>
+      </c>
+      <c r="BM253">
+        <v>2.04</v>
+      </c>
+      <c r="BN253">
+        <v>1.68</v>
+      </c>
+      <c r="BO253">
+        <v>2.55</v>
+      </c>
+      <c r="BP253">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="254" spans="1:68">
+      <c r="A254" s="1">
+        <v>253</v>
+      </c>
+      <c r="B254">
+        <v>7781308</v>
+      </c>
+      <c r="C254" t="s">
+        <v>68</v>
+      </c>
+      <c r="D254" t="s">
+        <v>69</v>
+      </c>
+      <c r="E254" s="2">
+        <v>45816.91666666666</v>
+      </c>
+      <c r="F254">
+        <v>0</v>
+      </c>
+      <c r="G254" t="s">
+        <v>70</v>
+      </c>
+      <c r="H254" t="s">
+        <v>91</v>
+      </c>
+      <c r="I254">
+        <v>1</v>
+      </c>
+      <c r="J254">
+        <v>1</v>
+      </c>
+      <c r="K254">
+        <v>2</v>
+      </c>
+      <c r="L254">
+        <v>3</v>
+      </c>
+      <c r="M254">
+        <v>1</v>
+      </c>
+      <c r="N254">
+        <v>4</v>
+      </c>
+      <c r="O254" t="s">
+        <v>267</v>
+      </c>
+      <c r="P254" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q254">
+        <v>1.91</v>
+      </c>
+      <c r="R254">
+        <v>2.75</v>
+      </c>
+      <c r="S254">
+        <v>5.5</v>
+      </c>
+      <c r="T254">
+        <v>1.22</v>
+      </c>
+      <c r="U254">
+        <v>4</v>
+      </c>
+      <c r="V254">
+        <v>2</v>
+      </c>
+      <c r="W254">
+        <v>1.73</v>
+      </c>
+      <c r="X254">
+        <v>4.33</v>
+      </c>
+      <c r="Y254">
+        <v>1.2</v>
+      </c>
+      <c r="Z254">
+        <v>1.43</v>
+      </c>
+      <c r="AA254">
+        <v>4.3</v>
+      </c>
+      <c r="AB254">
+        <v>5.3</v>
+      </c>
+      <c r="AC254">
+        <v>1.03</v>
+      </c>
+      <c r="AD254">
+        <v>11</v>
+      </c>
+      <c r="AE254">
+        <v>1.14</v>
+      </c>
+      <c r="AF254">
+        <v>5.5</v>
+      </c>
+      <c r="AG254">
+        <v>1.57</v>
+      </c>
+      <c r="AH254">
+        <v>2.25</v>
+      </c>
+      <c r="AI254">
+        <v>1.57</v>
+      </c>
+      <c r="AJ254">
+        <v>2.25</v>
+      </c>
+      <c r="AK254">
+        <v>1.14</v>
+      </c>
+      <c r="AL254">
+        <v>1.18</v>
+      </c>
+      <c r="AM254">
+        <v>2.55</v>
+      </c>
+      <c r="AN254">
+        <v>2.29</v>
+      </c>
+      <c r="AO254">
+        <v>0.89</v>
+      </c>
+      <c r="AP254">
+        <v>2.38</v>
+      </c>
+      <c r="AQ254">
+        <v>0.8</v>
+      </c>
+      <c r="AR254">
+        <v>1.77</v>
+      </c>
+      <c r="AS254">
+        <v>1.34</v>
+      </c>
+      <c r="AT254">
+        <v>3.11</v>
+      </c>
+      <c r="AU254">
+        <v>8</v>
+      </c>
+      <c r="AV254">
+        <v>3</v>
+      </c>
+      <c r="AW254">
+        <v>14</v>
+      </c>
+      <c r="AX254">
+        <v>3</v>
+      </c>
+      <c r="AY254">
+        <v>22</v>
+      </c>
+      <c r="AZ254">
+        <v>6</v>
+      </c>
+      <c r="BA254">
+        <v>8</v>
+      </c>
+      <c r="BB254">
+        <v>2</v>
+      </c>
+      <c r="BC254">
+        <v>10</v>
+      </c>
+      <c r="BD254">
+        <v>1.41</v>
+      </c>
+      <c r="BE254">
+        <v>9.4</v>
+      </c>
+      <c r="BF254">
+        <v>3.6</v>
+      </c>
+      <c r="BG254">
+        <v>1.22</v>
+      </c>
+      <c r="BH254">
+        <v>3.48</v>
+      </c>
+      <c r="BI254">
+        <v>1.45</v>
+      </c>
+      <c r="BJ254">
+        <v>2.48</v>
+      </c>
+      <c r="BK254">
+        <v>1.8</v>
+      </c>
+      <c r="BL254">
+        <v>1.9</v>
+      </c>
+      <c r="BM254">
+        <v>2.28</v>
+      </c>
+      <c r="BN254">
+        <v>1.53</v>
+      </c>
+      <c r="BO254">
+        <v>3.04</v>
+      </c>
+      <c r="BP254">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="390">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -820,6 +820,12 @@
     <t>['4501', '59', '9003']</t>
   </si>
   <si>
+    <t>['44', '55', '57', '59']</t>
+  </si>
+  <si>
+    <t>['71']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -1539,7 +1545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP254"/>
+  <dimension ref="A1:BP256"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2001,7 +2007,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -2207,7 +2213,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2619,7 +2625,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2825,7 +2831,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3031,7 +3037,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -3443,7 +3449,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -4267,7 +4273,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -4473,7 +4479,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4551,7 +4557,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ15">
         <v>2.14</v>
@@ -4679,7 +4685,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4966,7 +4972,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ17">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5297,7 +5303,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -5709,7 +5715,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -6121,7 +6127,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6327,7 +6333,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6408,7 +6414,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6739,7 +6745,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -7229,7 +7235,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ28">
         <v>1.11</v>
@@ -7769,7 +7775,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -8181,7 +8187,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -9005,7 +9011,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9289,7 +9295,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ38">
         <v>1.25</v>
@@ -9623,7 +9629,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -10035,7 +10041,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -10859,7 +10865,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -11065,7 +11071,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -11271,7 +11277,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -12095,7 +12101,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12173,7 +12179,7 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ52">
         <v>1.6</v>
@@ -12301,7 +12307,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12713,7 +12719,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -13331,7 +13337,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13537,7 +13543,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13821,7 +13827,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ60">
         <v>0.22</v>
@@ -13949,7 +13955,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14155,7 +14161,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -14236,7 +14242,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ62">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR62">
         <v>1.6</v>
@@ -14361,7 +14367,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14567,7 +14573,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -14648,7 +14654,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ64">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR64">
         <v>1.62</v>
@@ -15597,7 +15603,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -16009,7 +16015,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16215,7 +16221,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16627,7 +16633,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -17039,7 +17045,7 @@
         <v>153</v>
       </c>
       <c r="P76" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q76">
         <v>3.6</v>
@@ -17863,7 +17869,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18069,7 +18075,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18275,7 +18281,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -18893,7 +18899,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -19099,7 +19105,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -19305,7 +19311,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -19923,7 +19929,7 @@
         <v>164</v>
       </c>
       <c r="P90" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
@@ -20001,7 +20007,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ90">
         <v>1.25</v>
@@ -21159,7 +21165,7 @@
         <v>168</v>
       </c>
       <c r="P96" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -22601,7 +22607,7 @@
         <v>122</v>
       </c>
       <c r="P103" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q103">
         <v>2.75</v>
@@ -22679,7 +22685,7 @@
         <v>1.33</v>
       </c>
       <c r="AP103">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ103">
         <v>1.67</v>
@@ -22807,7 +22813,7 @@
         <v>173</v>
       </c>
       <c r="P104" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q104">
         <v>2.75</v>
@@ -23013,7 +23019,7 @@
         <v>174</v>
       </c>
       <c r="P105" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q105">
         <v>1.91</v>
@@ -24043,7 +24049,7 @@
         <v>175</v>
       </c>
       <c r="P110" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24249,7 +24255,7 @@
         <v>109</v>
       </c>
       <c r="P111" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q111">
         <v>2.88</v>
@@ -24533,7 +24539,7 @@
         <v>2</v>
       </c>
       <c r="AP112">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ112">
         <v>2</v>
@@ -24867,7 +24873,7 @@
         <v>177</v>
       </c>
       <c r="P114" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25073,7 +25079,7 @@
         <v>178</v>
       </c>
       <c r="P115" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -25485,7 +25491,7 @@
         <v>179</v>
       </c>
       <c r="P117" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25566,7 +25572,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ117">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR117">
         <v>1.48</v>
@@ -25691,7 +25697,7 @@
         <v>180</v>
       </c>
       <c r="P118" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -26103,7 +26109,7 @@
         <v>181</v>
       </c>
       <c r="P120" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -26515,7 +26521,7 @@
         <v>109</v>
       </c>
       <c r="P122" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q122">
         <v>2.75</v>
@@ -26927,7 +26933,7 @@
         <v>129</v>
       </c>
       <c r="P124" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q124">
         <v>2.5</v>
@@ -27214,7 +27220,7 @@
         <v>2</v>
       </c>
       <c r="AQ125">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR125">
         <v>1.84</v>
@@ -27957,7 +27963,7 @@
         <v>187</v>
       </c>
       <c r="P129" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28163,7 +28169,7 @@
         <v>188</v>
       </c>
       <c r="P130" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q130">
         <v>2.4</v>
@@ -28987,7 +28993,7 @@
         <v>189</v>
       </c>
       <c r="P134" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q134">
         <v>3</v>
@@ -29065,7 +29071,7 @@
         <v>0.75</v>
       </c>
       <c r="AP134">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ134">
         <v>0.88</v>
@@ -29193,7 +29199,7 @@
         <v>190</v>
       </c>
       <c r="P135" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -30304,7 +30310,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ140">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR140">
         <v>1.89</v>
@@ -30429,7 +30435,7 @@
         <v>109</v>
       </c>
       <c r="P141" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q141">
         <v>2.38</v>
@@ -30716,7 +30722,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ142">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR142">
         <v>1.65</v>
@@ -30841,7 +30847,7 @@
         <v>174</v>
       </c>
       <c r="P143" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -31253,7 +31259,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q145">
         <v>2.4</v>
@@ -31459,7 +31465,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31665,7 +31671,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q147">
         <v>2.6</v>
@@ -31871,7 +31877,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q148">
         <v>2.05</v>
@@ -32077,7 +32083,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -32283,7 +32289,7 @@
         <v>202</v>
       </c>
       <c r="P150" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q150">
         <v>2.4</v>
@@ -32489,7 +32495,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q151">
         <v>2.63</v>
@@ -32695,7 +32701,7 @@
         <v>109</v>
       </c>
       <c r="P152" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q152">
         <v>2.88</v>
@@ -32901,7 +32907,7 @@
         <v>204</v>
       </c>
       <c r="P153" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -33107,7 +33113,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q154">
         <v>3.1</v>
@@ -33313,7 +33319,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q155">
         <v>2.2</v>
@@ -33519,7 +33525,7 @@
         <v>207</v>
       </c>
       <c r="P156" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33725,7 +33731,7 @@
         <v>109</v>
       </c>
       <c r="P157" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q157">
         <v>3.2</v>
@@ -34343,7 +34349,7 @@
         <v>209</v>
       </c>
       <c r="P160" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q160">
         <v>2.1</v>
@@ -34755,7 +34761,7 @@
         <v>211</v>
       </c>
       <c r="P162" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q162">
         <v>2.5</v>
@@ -35245,7 +35251,7 @@
         <v>1.8</v>
       </c>
       <c r="AP164">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ164">
         <v>1.44</v>
@@ -35660,7 +35666,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ166">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR166">
         <v>1.6</v>
@@ -35785,7 +35791,7 @@
         <v>215</v>
       </c>
       <c r="P167" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -36197,7 +36203,7 @@
         <v>217</v>
       </c>
       <c r="P169" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q169">
         <v>3</v>
@@ -36403,7 +36409,7 @@
         <v>218</v>
       </c>
       <c r="P170" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36609,7 +36615,7 @@
         <v>109</v>
       </c>
       <c r="P171" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q171">
         <v>2.25</v>
@@ -36687,7 +36693,7 @@
         <v>0.25</v>
       </c>
       <c r="AP171">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ171">
         <v>0.5</v>
@@ -36815,7 +36821,7 @@
         <v>219</v>
       </c>
       <c r="P172" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q172">
         <v>2.4</v>
@@ -37227,7 +37233,7 @@
         <v>221</v>
       </c>
       <c r="P174" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q174">
         <v>2.5</v>
@@ -37433,7 +37439,7 @@
         <v>163</v>
       </c>
       <c r="P175" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -37639,7 +37645,7 @@
         <v>113</v>
       </c>
       <c r="P176" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q176">
         <v>2.4</v>
@@ -37845,7 +37851,7 @@
         <v>222</v>
       </c>
       <c r="P177" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -38051,7 +38057,7 @@
         <v>109</v>
       </c>
       <c r="P178" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q178">
         <v>2.38</v>
@@ -38132,7 +38138,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ178">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR178">
         <v>1.84</v>
@@ -38335,7 +38341,7 @@
         <v>0.6</v>
       </c>
       <c r="AP179">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ179">
         <v>0.8</v>
@@ -38463,7 +38469,7 @@
         <v>224</v>
       </c>
       <c r="P180" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38875,7 +38881,7 @@
         <v>225</v>
       </c>
       <c r="P182" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q182">
         <v>3.75</v>
@@ -39081,7 +39087,7 @@
         <v>226</v>
       </c>
       <c r="P183" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q183">
         <v>2.5</v>
@@ -39287,7 +39293,7 @@
         <v>227</v>
       </c>
       <c r="P184" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q184">
         <v>2.05</v>
@@ -39699,7 +39705,7 @@
         <v>228</v>
       </c>
       <c r="P186" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q186">
         <v>2.4</v>
@@ -40111,7 +40117,7 @@
         <v>230</v>
       </c>
       <c r="P188" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40317,7 +40323,7 @@
         <v>176</v>
       </c>
       <c r="P189" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40398,7 +40404,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ189">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR189">
         <v>1.57</v>
@@ -41141,7 +41147,7 @@
         <v>233</v>
       </c>
       <c r="P193" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41347,7 +41353,7 @@
         <v>234</v>
       </c>
       <c r="P194" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41631,7 +41637,7 @@
         <v>0.33</v>
       </c>
       <c r="AP195">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ195">
         <v>0.63</v>
@@ -41759,7 +41765,7 @@
         <v>198</v>
       </c>
       <c r="P196" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q196">
         <v>2.63</v>
@@ -41965,7 +41971,7 @@
         <v>109</v>
       </c>
       <c r="P197" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q197">
         <v>2.75</v>
@@ -42171,7 +42177,7 @@
         <v>103</v>
       </c>
       <c r="P198" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q198">
         <v>2.63</v>
@@ -42458,7 +42464,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ199">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR199">
         <v>1.32</v>
@@ -43201,7 +43207,7 @@
         <v>109</v>
       </c>
       <c r="P203" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q203">
         <v>2.63</v>
@@ -43613,7 +43619,7 @@
         <v>237</v>
       </c>
       <c r="P205" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -43691,7 +43697,7 @@
         <v>1</v>
       </c>
       <c r="AP205">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ205">
         <v>0.9</v>
@@ -44025,7 +44031,7 @@
         <v>109</v>
       </c>
       <c r="P207" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q207">
         <v>2.25</v>
@@ -44849,7 +44855,7 @@
         <v>240</v>
       </c>
       <c r="P211" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q211">
         <v>3.2</v>
@@ -45055,7 +45061,7 @@
         <v>109</v>
       </c>
       <c r="P212" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45261,7 +45267,7 @@
         <v>241</v>
       </c>
       <c r="P213" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q213">
         <v>4</v>
@@ -45673,7 +45679,7 @@
         <v>242</v>
       </c>
       <c r="P215" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -45879,7 +45885,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q216">
         <v>3.4</v>
@@ -46085,7 +46091,7 @@
         <v>243</v>
       </c>
       <c r="P217" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q217">
         <v>2.75</v>
@@ -46497,7 +46503,7 @@
         <v>244</v>
       </c>
       <c r="P219" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q219">
         <v>3.1</v>
@@ -46909,7 +46915,7 @@
         <v>246</v>
       </c>
       <c r="P221" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q221">
         <v>2.6</v>
@@ -47115,7 +47121,7 @@
         <v>247</v>
       </c>
       <c r="P222" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q222">
         <v>2.5</v>
@@ -47193,7 +47199,7 @@
         <v>1.71</v>
       </c>
       <c r="AP222">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ222">
         <v>1.8</v>
@@ -47321,7 +47327,7 @@
         <v>248</v>
       </c>
       <c r="P223" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47527,7 +47533,7 @@
         <v>249</v>
       </c>
       <c r="P224" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47733,7 +47739,7 @@
         <v>250</v>
       </c>
       <c r="P225" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -47939,7 +47945,7 @@
         <v>251</v>
       </c>
       <c r="P226" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q226">
         <v>2.75</v>
@@ -48145,7 +48151,7 @@
         <v>252</v>
       </c>
       <c r="P227" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q227">
         <v>1.83</v>
@@ -48351,7 +48357,7 @@
         <v>253</v>
       </c>
       <c r="P228" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48557,7 +48563,7 @@
         <v>109</v>
       </c>
       <c r="P229" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q229">
         <v>2.5</v>
@@ -48635,7 +48641,7 @@
         <v>1</v>
       </c>
       <c r="AP229">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ229">
         <v>1.25</v>
@@ -48763,7 +48769,7 @@
         <v>254</v>
       </c>
       <c r="P230" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q230">
         <v>3.25</v>
@@ -48969,7 +48975,7 @@
         <v>119</v>
       </c>
       <c r="P231" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q231">
         <v>2.4</v>
@@ -49587,7 +49593,7 @@
         <v>109</v>
       </c>
       <c r="P234" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q234">
         <v>2.5</v>
@@ -49668,7 +49674,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ234">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR234">
         <v>1.45</v>
@@ -49871,7 +49877,7 @@
         <v>1.14</v>
       </c>
       <c r="AP235">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ235">
         <v>1</v>
@@ -50205,7 +50211,7 @@
         <v>258</v>
       </c>
       <c r="P237" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q237">
         <v>2.75</v>
@@ -50286,7 +50292,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ237">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR237">
         <v>1.68</v>
@@ -50411,7 +50417,7 @@
         <v>259</v>
       </c>
       <c r="P238" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q238">
         <v>2.6</v>
@@ -50617,7 +50623,7 @@
         <v>109</v>
       </c>
       <c r="P239" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -50823,7 +50829,7 @@
         <v>140</v>
       </c>
       <c r="P240" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -51235,7 +51241,7 @@
         <v>109</v>
       </c>
       <c r="P242" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q242">
         <v>3.1</v>
@@ -51522,7 +51528,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ243">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR243">
         <v>1.63</v>
@@ -51647,7 +51653,7 @@
         <v>161</v>
       </c>
       <c r="P244" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q244">
         <v>2.1</v>
@@ -52059,7 +52065,7 @@
         <v>156</v>
       </c>
       <c r="P246" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q246">
         <v>2.5</v>
@@ -52677,7 +52683,7 @@
         <v>176</v>
       </c>
       <c r="P249" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q249">
         <v>2.5</v>
@@ -52883,7 +52889,7 @@
         <v>264</v>
       </c>
       <c r="P250" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q250">
         <v>3.2</v>
@@ -53089,7 +53095,7 @@
         <v>109</v>
       </c>
       <c r="P251" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q251">
         <v>2.75</v>
@@ -53295,7 +53301,7 @@
         <v>265</v>
       </c>
       <c r="P252" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q252">
         <v>2.25</v>
@@ -53373,7 +53379,7 @@
         <v>0.63</v>
       </c>
       <c r="AP252">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ252">
         <v>0.5600000000000001</v>
@@ -53864,6 +53870,418 @@
       </c>
       <c r="BP254">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="255" spans="1:68">
+      <c r="A255" s="1">
+        <v>254</v>
+      </c>
+      <c r="B255">
+        <v>7781330</v>
+      </c>
+      <c r="C255" t="s">
+        <v>68</v>
+      </c>
+      <c r="D255" t="s">
+        <v>69</v>
+      </c>
+      <c r="E255" s="2">
+        <v>45820.85416666666</v>
+      </c>
+      <c r="F255">
+        <v>0</v>
+      </c>
+      <c r="G255" t="s">
+        <v>96</v>
+      </c>
+      <c r="H255" t="s">
+        <v>72</v>
+      </c>
+      <c r="I255">
+        <v>1</v>
+      </c>
+      <c r="J255">
+        <v>0</v>
+      </c>
+      <c r="K255">
+        <v>1</v>
+      </c>
+      <c r="L255">
+        <v>4</v>
+      </c>
+      <c r="M255">
+        <v>0</v>
+      </c>
+      <c r="N255">
+        <v>4</v>
+      </c>
+      <c r="O255" t="s">
+        <v>268</v>
+      </c>
+      <c r="P255" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q255">
+        <v>2.5</v>
+      </c>
+      <c r="R255">
+        <v>2.38</v>
+      </c>
+      <c r="S255">
+        <v>4</v>
+      </c>
+      <c r="T255">
+        <v>1.3</v>
+      </c>
+      <c r="U255">
+        <v>3.4</v>
+      </c>
+      <c r="V255">
+        <v>2.38</v>
+      </c>
+      <c r="W255">
+        <v>1.53</v>
+      </c>
+      <c r="X255">
+        <v>6</v>
+      </c>
+      <c r="Y255">
+        <v>1.13</v>
+      </c>
+      <c r="Z255">
+        <v>1.86</v>
+      </c>
+      <c r="AA255">
+        <v>3.51</v>
+      </c>
+      <c r="AB255">
+        <v>3.38</v>
+      </c>
+      <c r="AC255">
+        <v>1.04</v>
+      </c>
+      <c r="AD255">
+        <v>10</v>
+      </c>
+      <c r="AE255">
+        <v>1.2</v>
+      </c>
+      <c r="AF255">
+        <v>4.33</v>
+      </c>
+      <c r="AG255">
+        <v>1.63</v>
+      </c>
+      <c r="AH255">
+        <v>2.13</v>
+      </c>
+      <c r="AI255">
+        <v>1.57</v>
+      </c>
+      <c r="AJ255">
+        <v>2.25</v>
+      </c>
+      <c r="AK255">
+        <v>1.28</v>
+      </c>
+      <c r="AL255">
+        <v>1.26</v>
+      </c>
+      <c r="AM255">
+        <v>1.8</v>
+      </c>
+      <c r="AN255">
+        <v>2</v>
+      </c>
+      <c r="AO255">
+        <v>0.29</v>
+      </c>
+      <c r="AP255">
+        <v>2.1</v>
+      </c>
+      <c r="AQ255">
+        <v>0.25</v>
+      </c>
+      <c r="AR255">
+        <v>1.83</v>
+      </c>
+      <c r="AS255">
+        <v>1.39</v>
+      </c>
+      <c r="AT255">
+        <v>3.22</v>
+      </c>
+      <c r="AU255">
+        <v>7</v>
+      </c>
+      <c r="AV255">
+        <v>4</v>
+      </c>
+      <c r="AW255">
+        <v>3</v>
+      </c>
+      <c r="AX255">
+        <v>4</v>
+      </c>
+      <c r="AY255">
+        <v>10</v>
+      </c>
+      <c r="AZ255">
+        <v>8</v>
+      </c>
+      <c r="BA255">
+        <v>5</v>
+      </c>
+      <c r="BB255">
+        <v>5</v>
+      </c>
+      <c r="BC255">
+        <v>10</v>
+      </c>
+      <c r="BD255">
+        <v>1.68</v>
+      </c>
+      <c r="BE255">
+        <v>6.75</v>
+      </c>
+      <c r="BF255">
+        <v>2.4</v>
+      </c>
+      <c r="BG255">
+        <v>1.21</v>
+      </c>
+      <c r="BH255">
+        <v>3.8</v>
+      </c>
+      <c r="BI255">
+        <v>1.38</v>
+      </c>
+      <c r="BJ255">
+        <v>2.75</v>
+      </c>
+      <c r="BK255">
+        <v>1.64</v>
+      </c>
+      <c r="BL255">
+        <v>2.1</v>
+      </c>
+      <c r="BM255">
+        <v>1.98</v>
+      </c>
+      <c r="BN255">
+        <v>1.72</v>
+      </c>
+      <c r="BO255">
+        <v>2.5</v>
+      </c>
+      <c r="BP255">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="256" spans="1:68">
+      <c r="A256" s="1">
+        <v>255</v>
+      </c>
+      <c r="B256">
+        <v>7781332</v>
+      </c>
+      <c r="C256" t="s">
+        <v>68</v>
+      </c>
+      <c r="D256" t="s">
+        <v>69</v>
+      </c>
+      <c r="E256" s="2">
+        <v>45821.97916666666</v>
+      </c>
+      <c r="F256">
+        <v>0</v>
+      </c>
+      <c r="G256" t="s">
+        <v>83</v>
+      </c>
+      <c r="H256" t="s">
+        <v>81</v>
+      </c>
+      <c r="I256">
+        <v>0</v>
+      </c>
+      <c r="J256">
+        <v>0</v>
+      </c>
+      <c r="K256">
+        <v>0</v>
+      </c>
+      <c r="L256">
+        <v>1</v>
+      </c>
+      <c r="M256">
+        <v>1</v>
+      </c>
+      <c r="N256">
+        <v>2</v>
+      </c>
+      <c r="O256" t="s">
+        <v>269</v>
+      </c>
+      <c r="P256" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q256">
+        <v>2.25</v>
+      </c>
+      <c r="R256">
+        <v>2.6</v>
+      </c>
+      <c r="S256">
+        <v>4</v>
+      </c>
+      <c r="T256">
+        <v>1.22</v>
+      </c>
+      <c r="U256">
+        <v>4</v>
+      </c>
+      <c r="V256">
+        <v>2.1</v>
+      </c>
+      <c r="W256">
+        <v>1.67</v>
+      </c>
+      <c r="X256">
+        <v>4.5</v>
+      </c>
+      <c r="Y256">
+        <v>1.18</v>
+      </c>
+      <c r="Z256">
+        <v>1.77</v>
+      </c>
+      <c r="AA256">
+        <v>3.81</v>
+      </c>
+      <c r="AB256">
+        <v>3.45</v>
+      </c>
+      <c r="AC256">
+        <v>1.01</v>
+      </c>
+      <c r="AD256">
+        <v>17</v>
+      </c>
+      <c r="AE256">
+        <v>1.15</v>
+      </c>
+      <c r="AF256">
+        <v>5.25</v>
+      </c>
+      <c r="AG256">
+        <v>1.41</v>
+      </c>
+      <c r="AH256">
+        <v>2.78</v>
+      </c>
+      <c r="AI256">
+        <v>1.44</v>
+      </c>
+      <c r="AJ256">
+        <v>2.63</v>
+      </c>
+      <c r="AK256">
+        <v>1.25</v>
+      </c>
+      <c r="AL256">
+        <v>1.23</v>
+      </c>
+      <c r="AM256">
+        <v>1.98</v>
+      </c>
+      <c r="AN256">
+        <v>2</v>
+      </c>
+      <c r="AO256">
+        <v>1.25</v>
+      </c>
+      <c r="AP256">
+        <v>1.9</v>
+      </c>
+      <c r="AQ256">
+        <v>1.22</v>
+      </c>
+      <c r="AR256">
+        <v>1.24</v>
+      </c>
+      <c r="AS256">
+        <v>1.76</v>
+      </c>
+      <c r="AT256">
+        <v>3</v>
+      </c>
+      <c r="AU256">
+        <v>9</v>
+      </c>
+      <c r="AV256">
+        <v>7</v>
+      </c>
+      <c r="AW256">
+        <v>6</v>
+      </c>
+      <c r="AX256">
+        <v>10</v>
+      </c>
+      <c r="AY256">
+        <v>15</v>
+      </c>
+      <c r="AZ256">
+        <v>17</v>
+      </c>
+      <c r="BA256">
+        <v>8</v>
+      </c>
+      <c r="BB256">
+        <v>7</v>
+      </c>
+      <c r="BC256">
+        <v>15</v>
+      </c>
+      <c r="BD256">
+        <v>1.68</v>
+      </c>
+      <c r="BE256">
+        <v>6.4</v>
+      </c>
+      <c r="BF256">
+        <v>2.4</v>
+      </c>
+      <c r="BG256">
+        <v>1.27</v>
+      </c>
+      <c r="BH256">
+        <v>3.3</v>
+      </c>
+      <c r="BI256">
+        <v>1.48</v>
+      </c>
+      <c r="BJ256">
+        <v>2.43</v>
+      </c>
+      <c r="BK256">
+        <v>1.78</v>
+      </c>
+      <c r="BL256">
+        <v>1.91</v>
+      </c>
+      <c r="BM256">
+        <v>2.23</v>
+      </c>
+      <c r="BN256">
+        <v>1.57</v>
+      </c>
+      <c r="BO256">
+        <v>2.88</v>
+      </c>
+      <c r="BP256">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="402">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -826,6 +826,27 @@
     <t>['71']</t>
   </si>
   <si>
+    <t>['35', '47', '9004']</t>
+  </si>
+  <si>
+    <t>['2', '23']</t>
+  </si>
+  <si>
+    <t>['4502', '9008']</t>
+  </si>
+  <si>
+    <t>['6', '51']</t>
+  </si>
+  <si>
+    <t>['38']</t>
+  </si>
+  <si>
+    <t>['8', '9001']</t>
+  </si>
+  <si>
+    <t>['23', '77']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -1184,6 +1205,21 @@
   </si>
   <si>
     <t>['8', '23', '30', '44', '56', '65', '9001']</t>
+  </si>
+  <si>
+    <t>['41', '51', '87']</t>
+  </si>
+  <si>
+    <t>['11', '66', '75', '9002']</t>
+  </si>
+  <si>
+    <t>['11', '59', '69', '82']</t>
+  </si>
+  <si>
+    <t>['56', '75']</t>
+  </si>
+  <si>
+    <t>['30', '32', '54']</t>
   </si>
 </sst>
 </file>
@@ -1545,7 +1581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP256"/>
+  <dimension ref="A1:BP267"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2007,7 +2043,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -2213,7 +2249,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2294,7 +2330,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ4">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2500,7 +2536,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ5">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2625,7 +2661,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2703,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ6">
         <v>1.8</v>
@@ -2831,7 +2867,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3037,7 +3073,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -3321,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ9">
         <v>0.8</v>
@@ -3449,7 +3485,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -3527,10 +3563,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ10">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3939,7 +3975,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ12">
         <v>1</v>
@@ -4273,7 +4309,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -4354,7 +4390,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ14">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4479,7 +4515,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4560,7 +4596,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ15">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4685,7 +4721,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4766,7 +4802,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ16">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5175,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ18">
         <v>0.9</v>
@@ -5303,7 +5339,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -5381,7 +5417,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ19">
         <v>1.5</v>
@@ -5590,7 +5626,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ20">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5715,7 +5751,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -5999,10 +6035,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ22">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6127,7 +6163,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6205,10 +6241,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ23">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6333,7 +6369,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6411,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ24">
         <v>1.22</v>
@@ -6617,10 +6653,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ25">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6745,7 +6781,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6823,10 +6859,10 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ26">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR26">
         <v>0</v>
@@ -7650,7 +7686,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ30">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR30">
         <v>0</v>
@@ -7775,7 +7811,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7853,7 +7889,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ31">
         <v>1.71</v>
@@ -8059,7 +8095,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ32">
         <v>1.25</v>
@@ -8187,7 +8223,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -8474,7 +8510,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ34">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR34">
         <v>1.85</v>
@@ -9011,7 +9047,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9089,7 +9125,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ37">
         <v>2</v>
@@ -9298,7 +9334,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ38">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR38">
         <v>0</v>
@@ -9501,7 +9537,7 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ39">
         <v>1</v>
@@ -9629,7 +9665,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -10041,7 +10077,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -10119,10 +10155,10 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ42">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR42">
         <v>1.41</v>
@@ -10328,7 +10364,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ43">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR43">
         <v>1.87</v>
@@ -10740,7 +10776,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ45">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR45">
         <v>1.62</v>
@@ -10865,7 +10901,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -11071,7 +11107,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -11277,7 +11313,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11358,7 +11394,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ48">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR48">
         <v>1.51</v>
@@ -11770,7 +11806,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ50">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR50">
         <v>1.3</v>
@@ -11976,7 +12012,7 @@
         <v>1</v>
       </c>
       <c r="AQ51">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR51">
         <v>1.36</v>
@@ -12101,7 +12137,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12307,7 +12343,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12385,7 +12421,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ53">
         <v>1.67</v>
@@ -12594,7 +12630,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ54">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AR54">
         <v>1.95</v>
@@ -12719,7 +12755,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -12797,7 +12833,7 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ55">
         <v>0.8</v>
@@ -13003,7 +13039,7 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ56">
         <v>0.9</v>
@@ -13337,7 +13373,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13543,7 +13579,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13621,10 +13657,10 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ59">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR59">
         <v>1.65</v>
@@ -13830,7 +13866,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ60">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR60">
         <v>0.9399999999999999</v>
@@ -13955,7 +13991,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14161,7 +14197,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -14367,7 +14403,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14445,10 +14481,10 @@
         <v>0.5</v>
       </c>
       <c r="AP63">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ63">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR63">
         <v>1.42</v>
@@ -14573,7 +14609,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -14857,7 +14893,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ65">
         <v>0.88</v>
@@ -15272,7 +15308,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ67">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR67">
         <v>1.65</v>
@@ -15475,7 +15511,7 @@
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ68">
         <v>0.5600000000000001</v>
@@ -15603,7 +15639,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15681,7 +15717,7 @@
         <v>0</v>
       </c>
       <c r="AP69">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ69">
         <v>0.88</v>
@@ -15890,7 +15926,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ70">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR70">
         <v>1.96</v>
@@ -16015,7 +16051,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16093,7 +16129,7 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ71">
         <v>1.38</v>
@@ -16221,7 +16257,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16299,10 +16335,10 @@
         <v>2</v>
       </c>
       <c r="AP72">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ72">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR72">
         <v>1.41</v>
@@ -16633,7 +16669,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16917,10 +16953,10 @@
         <v>3</v>
       </c>
       <c r="AP75">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ75">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR75">
         <v>1.74</v>
@@ -17045,7 +17081,7 @@
         <v>153</v>
       </c>
       <c r="P76" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="Q76">
         <v>3.6</v>
@@ -17123,10 +17159,10 @@
         <v>0.5</v>
       </c>
       <c r="AP76">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ76">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR76">
         <v>0.97</v>
@@ -17332,7 +17368,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ77">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AR77">
         <v>0.9</v>
@@ -17535,10 +17571,10 @@
         <v>0.5</v>
       </c>
       <c r="AP78">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ78">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR78">
         <v>1.49</v>
@@ -17869,7 +17905,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18075,7 +18111,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18281,7 +18317,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -18359,10 +18395,10 @@
         <v>0.2</v>
       </c>
       <c r="AP82">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ82">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR82">
         <v>1.1</v>
@@ -18771,7 +18807,7 @@
         <v>1.5</v>
       </c>
       <c r="AP84">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ84">
         <v>0.8</v>
@@ -18899,7 +18935,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -18980,7 +19016,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ85">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR85">
         <v>1.87</v>
@@ -19105,7 +19141,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -19186,7 +19222,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ86">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR86">
         <v>1.7</v>
@@ -19311,7 +19347,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -19801,7 +19837,7 @@
         <v>1.5</v>
       </c>
       <c r="AP89">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ89">
         <v>1.11</v>
@@ -19929,7 +19965,7 @@
         <v>164</v>
       </c>
       <c r="P90" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
@@ -20216,7 +20252,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ91">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR91">
         <v>1.64</v>
@@ -20419,10 +20455,10 @@
         <v>0.67</v>
       </c>
       <c r="AP92">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ92">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR92">
         <v>1.35</v>
@@ -20628,7 +20664,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ93">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR93">
         <v>1.68</v>
@@ -20831,10 +20867,10 @@
         <v>1.33</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ94">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR94">
         <v>1.73</v>
@@ -21165,7 +21201,7 @@
         <v>168</v>
       </c>
       <c r="P96" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21243,10 +21279,10 @@
         <v>0.33</v>
       </c>
       <c r="AP96">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ96">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR96">
         <v>2.09</v>
@@ -21655,7 +21691,7 @@
         <v>1.5</v>
       </c>
       <c r="AP98">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ98">
         <v>1.38</v>
@@ -21861,7 +21897,7 @@
         <v>1.33</v>
       </c>
       <c r="AP99">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ99">
         <v>0.5600000000000001</v>
@@ -22067,7 +22103,7 @@
         <v>1</v>
       </c>
       <c r="AP100">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ100">
         <v>0.88</v>
@@ -22607,7 +22643,7 @@
         <v>122</v>
       </c>
       <c r="P103" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="Q103">
         <v>2.75</v>
@@ -22813,7 +22849,7 @@
         <v>173</v>
       </c>
       <c r="P104" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="Q104">
         <v>2.75</v>
@@ -22894,7 +22930,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ104">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR104">
         <v>1.95</v>
@@ -23019,7 +23055,7 @@
         <v>174</v>
       </c>
       <c r="P105" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="Q105">
         <v>1.91</v>
@@ -23718,7 +23754,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ108">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR108">
         <v>1.87</v>
@@ -23924,7 +23960,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ109">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR109">
         <v>0</v>
@@ -24049,7 +24085,7 @@
         <v>175</v>
       </c>
       <c r="P110" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24255,7 +24291,7 @@
         <v>109</v>
       </c>
       <c r="P111" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="Q111">
         <v>2.88</v>
@@ -24336,7 +24372,7 @@
         <v>1</v>
       </c>
       <c r="AQ111">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR111">
         <v>1.53</v>
@@ -24873,7 +24909,7 @@
         <v>177</v>
       </c>
       <c r="P114" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25079,7 +25115,7 @@
         <v>178</v>
       </c>
       <c r="P115" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -25157,10 +25193,10 @@
         <v>2</v>
       </c>
       <c r="AP115">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ115">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR115">
         <v>1.76</v>
@@ -25491,7 +25527,7 @@
         <v>179</v>
       </c>
       <c r="P117" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25697,7 +25733,7 @@
         <v>180</v>
       </c>
       <c r="P118" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25775,7 +25811,7 @@
         <v>1.33</v>
       </c>
       <c r="AP118">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ118">
         <v>1.38</v>
@@ -25981,7 +26017,7 @@
         <v>3</v>
       </c>
       <c r="AP119">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ119">
         <v>1.71</v>
@@ -26109,7 +26145,7 @@
         <v>181</v>
       </c>
       <c r="P120" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -26187,7 +26223,7 @@
         <v>2.33</v>
       </c>
       <c r="AP120">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ120">
         <v>1.5</v>
@@ -26393,10 +26429,10 @@
         <v>0.5</v>
       </c>
       <c r="AP121">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ121">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR121">
         <v>1.5</v>
@@ -26521,7 +26557,7 @@
         <v>109</v>
       </c>
       <c r="P122" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="Q122">
         <v>2.75</v>
@@ -26599,7 +26635,7 @@
         <v>2.33</v>
       </c>
       <c r="AP122">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ122">
         <v>1.71</v>
@@ -26808,7 +26844,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ123">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR123">
         <v>1.96</v>
@@ -26933,7 +26969,7 @@
         <v>129</v>
       </c>
       <c r="P124" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="Q124">
         <v>2.5</v>
@@ -27014,7 +27050,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ124">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR124">
         <v>1.48</v>
@@ -27217,7 +27253,7 @@
         <v>0.5</v>
       </c>
       <c r="AP125">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ125">
         <v>0.25</v>
@@ -27426,7 +27462,7 @@
         <v>0.43</v>
       </c>
       <c r="AQ126">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR126">
         <v>1.94</v>
@@ -27629,7 +27665,7 @@
         <v>0.5</v>
       </c>
       <c r="AP127">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ127">
         <v>0.88</v>
@@ -27838,7 +27874,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ128">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR128">
         <v>1.53</v>
@@ -27963,7 +27999,7 @@
         <v>187</v>
       </c>
       <c r="P129" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28041,10 +28077,10 @@
         <v>1.5</v>
       </c>
       <c r="AP129">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ129">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR129">
         <v>1.29</v>
@@ -28169,7 +28205,7 @@
         <v>188</v>
       </c>
       <c r="P130" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="Q130">
         <v>2.4</v>
@@ -28247,7 +28283,7 @@
         <v>1.75</v>
       </c>
       <c r="AP130">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ130">
         <v>1</v>
@@ -28453,10 +28489,10 @@
         <v>2</v>
       </c>
       <c r="AP131">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ131">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR131">
         <v>1.86</v>
@@ -28659,10 +28695,10 @@
         <v>2.33</v>
       </c>
       <c r="AP132">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ132">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AR132">
         <v>1.77</v>
@@ -28865,7 +28901,7 @@
         <v>0.4</v>
       </c>
       <c r="AP133">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ133">
         <v>1.14</v>
@@ -28993,7 +29029,7 @@
         <v>189</v>
       </c>
       <c r="P134" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="Q134">
         <v>3</v>
@@ -29199,7 +29235,7 @@
         <v>190</v>
       </c>
       <c r="P135" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -29895,10 +29931,10 @@
         <v>1</v>
       </c>
       <c r="AP138">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ138">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR138">
         <v>1.73</v>
@@ -30104,7 +30140,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ139">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR139">
         <v>1.51</v>
@@ -30435,7 +30471,7 @@
         <v>109</v>
       </c>
       <c r="P141" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="Q141">
         <v>2.38</v>
@@ -30719,7 +30755,7 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ142">
         <v>1.22</v>
@@ -30847,7 +30883,7 @@
         <v>174</v>
       </c>
       <c r="P143" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -31131,7 +31167,7 @@
         <v>1.5</v>
       </c>
       <c r="AP144">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ144">
         <v>1.11</v>
@@ -31259,7 +31295,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="Q145">
         <v>2.4</v>
@@ -31465,7 +31501,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31543,7 +31579,7 @@
         <v>0.8</v>
       </c>
       <c r="AP146">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ146">
         <v>0.9</v>
@@ -31671,7 +31707,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="Q147">
         <v>2.6</v>
@@ -31749,10 +31785,10 @@
         <v>2</v>
       </c>
       <c r="AP147">
+        <v>1.67</v>
+      </c>
+      <c r="AQ147">
         <v>1.88</v>
-      </c>
-      <c r="AQ147">
-        <v>2.14</v>
       </c>
       <c r="AR147">
         <v>1.85</v>
@@ -31877,7 +31913,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="Q148">
         <v>2.05</v>
@@ -31958,7 +31994,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ148">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR148">
         <v>1.55</v>
@@ -32083,7 +32119,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -32289,7 +32325,7 @@
         <v>202</v>
       </c>
       <c r="P150" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="Q150">
         <v>2.4</v>
@@ -32495,7 +32531,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="Q151">
         <v>2.63</v>
@@ -32576,7 +32612,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ151">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR151">
         <v>1.66</v>
@@ -32701,7 +32737,7 @@
         <v>109</v>
       </c>
       <c r="P152" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="Q152">
         <v>2.88</v>
@@ -32907,7 +32943,7 @@
         <v>204</v>
       </c>
       <c r="P153" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -32988,7 +33024,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ153">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR153">
         <v>1.52</v>
@@ -33113,7 +33149,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="Q154">
         <v>3.1</v>
@@ -33319,7 +33355,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="Q155">
         <v>2.2</v>
@@ -33397,10 +33433,10 @@
         <v>1</v>
       </c>
       <c r="AP155">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ155">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR155">
         <v>1.65</v>
@@ -33525,7 +33561,7 @@
         <v>207</v>
       </c>
       <c r="P156" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33731,7 +33767,7 @@
         <v>109</v>
       </c>
       <c r="P157" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="Q157">
         <v>3.2</v>
@@ -33809,7 +33845,7 @@
         <v>1.6</v>
       </c>
       <c r="AP157">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ157">
         <v>1.67</v>
@@ -34015,10 +34051,10 @@
         <v>1.2</v>
       </c>
       <c r="AP158">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ158">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR158">
         <v>1.51</v>
@@ -34224,7 +34260,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ159">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR159">
         <v>1.77</v>
@@ -34349,7 +34385,7 @@
         <v>209</v>
       </c>
       <c r="P160" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="Q160">
         <v>2.1</v>
@@ -34761,7 +34797,7 @@
         <v>211</v>
       </c>
       <c r="P162" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="Q162">
         <v>2.5</v>
@@ -35254,7 +35290,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ164">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR164">
         <v>1.81</v>
@@ -35457,10 +35493,10 @@
         <v>0.4</v>
       </c>
       <c r="AP165">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ165">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR165">
         <v>1.6</v>
@@ -35663,7 +35699,7 @@
         <v>0.25</v>
       </c>
       <c r="AP166">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ166">
         <v>0.25</v>
@@ -35791,7 +35827,7 @@
         <v>215</v>
       </c>
       <c r="P167" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35869,7 +35905,7 @@
         <v>2.5</v>
       </c>
       <c r="AP167">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ167">
         <v>1.71</v>
@@ -36078,7 +36114,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ168">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR168">
         <v>1.25</v>
@@ -36203,7 +36239,7 @@
         <v>217</v>
       </c>
       <c r="P169" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="Q169">
         <v>3</v>
@@ -36281,7 +36317,7 @@
         <v>2.5</v>
       </c>
       <c r="AP169">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ169">
         <v>1.5</v>
@@ -36409,7 +36445,7 @@
         <v>218</v>
       </c>
       <c r="P170" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36615,7 +36651,7 @@
         <v>109</v>
       </c>
       <c r="P171" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="Q171">
         <v>2.25</v>
@@ -36696,7 +36732,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ171">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR171">
         <v>1.87</v>
@@ -36821,7 +36857,7 @@
         <v>219</v>
       </c>
       <c r="P172" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="Q172">
         <v>2.4</v>
@@ -37108,7 +37144,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ173">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR173">
         <v>1.49</v>
@@ -37233,7 +37269,7 @@
         <v>221</v>
       </c>
       <c r="P174" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="Q174">
         <v>2.5</v>
@@ -37439,7 +37475,7 @@
         <v>163</v>
       </c>
       <c r="P175" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -37517,7 +37553,7 @@
         <v>0.83</v>
       </c>
       <c r="AP175">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ175">
         <v>0.9</v>
@@ -37645,7 +37681,7 @@
         <v>113</v>
       </c>
       <c r="P176" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="Q176">
         <v>2.4</v>
@@ -37726,7 +37762,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ176">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR176">
         <v>1.93</v>
@@ -37851,7 +37887,7 @@
         <v>222</v>
       </c>
       <c r="P177" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -37929,10 +37965,10 @@
         <v>1.2</v>
       </c>
       <c r="AP177">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ177">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR177">
         <v>1.66</v>
@@ -38057,7 +38093,7 @@
         <v>109</v>
       </c>
       <c r="P178" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="Q178">
         <v>2.38</v>
@@ -38135,7 +38171,7 @@
         <v>0.75</v>
       </c>
       <c r="AP178">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ178">
         <v>1.22</v>
@@ -38469,7 +38505,7 @@
         <v>224</v>
       </c>
       <c r="P180" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38881,7 +38917,7 @@
         <v>225</v>
       </c>
       <c r="P182" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="Q182">
         <v>3.75</v>
@@ -39087,7 +39123,7 @@
         <v>226</v>
       </c>
       <c r="P183" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="Q183">
         <v>2.5</v>
@@ -39168,7 +39204,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ183">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR183">
         <v>1.98</v>
@@ -39293,7 +39329,7 @@
         <v>227</v>
       </c>
       <c r="P184" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="Q184">
         <v>2.05</v>
@@ -39371,10 +39407,10 @@
         <v>0.29</v>
       </c>
       <c r="AP184">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ184">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR184">
         <v>1.71</v>
@@ -39580,7 +39616,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ185">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR185">
         <v>1.44</v>
@@ -39705,7 +39741,7 @@
         <v>228</v>
       </c>
       <c r="P186" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="Q186">
         <v>2.4</v>
@@ -39786,7 +39822,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ186">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR186">
         <v>1.92</v>
@@ -39989,7 +40025,7 @@
         <v>1.83</v>
       </c>
       <c r="AP187">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ187">
         <v>1.67</v>
@@ -40117,7 +40153,7 @@
         <v>230</v>
       </c>
       <c r="P188" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40195,7 +40231,7 @@
         <v>0.5</v>
       </c>
       <c r="AP188">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ188">
         <v>0.8</v>
@@ -40323,7 +40359,7 @@
         <v>176</v>
       </c>
       <c r="P189" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40401,7 +40437,7 @@
         <v>0.2</v>
       </c>
       <c r="AP189">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ189">
         <v>0.25</v>
@@ -40607,7 +40643,7 @@
         <v>1.67</v>
       </c>
       <c r="AP190">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ190">
         <v>1.38</v>
@@ -41147,7 +41183,7 @@
         <v>233</v>
       </c>
       <c r="P193" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41353,7 +41389,7 @@
         <v>234</v>
       </c>
       <c r="P194" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41640,7 +41676,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ195">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR195">
         <v>1.77</v>
@@ -41765,7 +41801,7 @@
         <v>198</v>
       </c>
       <c r="P196" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="Q196">
         <v>2.63</v>
@@ -41843,10 +41879,10 @@
         <v>1.71</v>
       </c>
       <c r="AP196">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ196">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR196">
         <v>1.74</v>
@@ -41971,7 +42007,7 @@
         <v>109</v>
       </c>
       <c r="P197" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="Q197">
         <v>2.75</v>
@@ -42177,7 +42213,7 @@
         <v>103</v>
       </c>
       <c r="P198" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="Q198">
         <v>2.63</v>
@@ -42461,7 +42497,7 @@
         <v>1.2</v>
       </c>
       <c r="AP199">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ199">
         <v>1.22</v>
@@ -42667,7 +42703,7 @@
         <v>0.83</v>
       </c>
       <c r="AP200">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ200">
         <v>0.5600000000000001</v>
@@ -42876,7 +42912,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ201">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR201">
         <v>1.89</v>
@@ -43079,10 +43115,10 @@
         <v>2.2</v>
       </c>
       <c r="AP202">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ202">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AR202">
         <v>1.61</v>
@@ -43207,7 +43243,7 @@
         <v>109</v>
       </c>
       <c r="P203" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="Q203">
         <v>2.63</v>
@@ -43491,7 +43527,7 @@
         <v>1</v>
       </c>
       <c r="AP204">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ204">
         <v>0.8</v>
@@ -43619,7 +43655,7 @@
         <v>237</v>
       </c>
       <c r="P205" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -44031,7 +44067,7 @@
         <v>109</v>
       </c>
       <c r="P207" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="Q207">
         <v>2.25</v>
@@ -44112,7 +44148,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ207">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR207">
         <v>1.4</v>
@@ -44524,7 +44560,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ209">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR209">
         <v>2.06</v>
@@ -44730,7 +44766,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ210">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR210">
         <v>1.8</v>
@@ -44855,7 +44891,7 @@
         <v>240</v>
       </c>
       <c r="P211" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="Q211">
         <v>3.2</v>
@@ -45061,7 +45097,7 @@
         <v>109</v>
       </c>
       <c r="P212" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45142,7 +45178,7 @@
         <v>1</v>
       </c>
       <c r="AQ212">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR212">
         <v>1.33</v>
@@ -45267,7 +45303,7 @@
         <v>241</v>
       </c>
       <c r="P213" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="Q213">
         <v>4</v>
@@ -45679,7 +45715,7 @@
         <v>242</v>
       </c>
       <c r="P215" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -45757,7 +45793,7 @@
         <v>1.83</v>
       </c>
       <c r="AP215">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ215">
         <v>1.71</v>
@@ -45885,7 +45921,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="Q216">
         <v>3.4</v>
@@ -45966,7 +46002,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ216">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR216">
         <v>1.44</v>
@@ -46091,7 +46127,7 @@
         <v>243</v>
       </c>
       <c r="P217" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="Q217">
         <v>2.75</v>
@@ -46169,7 +46205,7 @@
         <v>1.57</v>
       </c>
       <c r="AP217">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ217">
         <v>1.6</v>
@@ -46375,7 +46411,7 @@
         <v>1</v>
       </c>
       <c r="AP218">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ218">
         <v>1.11</v>
@@ -46503,7 +46539,7 @@
         <v>244</v>
       </c>
       <c r="P219" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="Q219">
         <v>3.1</v>
@@ -46581,10 +46617,10 @@
         <v>2</v>
       </c>
       <c r="AP219">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AQ219">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AR219">
         <v>1.44</v>
@@ -46787,7 +46823,7 @@
         <v>0.71</v>
       </c>
       <c r="AP220">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ220">
         <v>0.5600000000000001</v>
@@ -46915,7 +46951,7 @@
         <v>246</v>
       </c>
       <c r="P221" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="Q221">
         <v>2.6</v>
@@ -47121,7 +47157,7 @@
         <v>247</v>
       </c>
       <c r="P222" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="Q222">
         <v>2.5</v>
@@ -47327,7 +47363,7 @@
         <v>248</v>
       </c>
       <c r="P223" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47408,7 +47444,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ223">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR223">
         <v>1.57</v>
@@ -47533,7 +47569,7 @@
         <v>249</v>
       </c>
       <c r="P224" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47614,7 +47650,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ224">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR224">
         <v>1.56</v>
@@ -47739,7 +47775,7 @@
         <v>250</v>
       </c>
       <c r="P225" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -47820,7 +47856,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ225">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR225">
         <v>1.88</v>
@@ -47945,7 +47981,7 @@
         <v>251</v>
       </c>
       <c r="P226" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="Q226">
         <v>2.75</v>
@@ -48151,7 +48187,7 @@
         <v>252</v>
       </c>
       <c r="P227" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="Q227">
         <v>1.83</v>
@@ -48232,7 +48268,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ227">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR227">
         <v>1.5</v>
@@ -48357,7 +48393,7 @@
         <v>253</v>
       </c>
       <c r="P228" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48438,7 +48474,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ228">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR228">
         <v>1.63</v>
@@ -48563,7 +48599,7 @@
         <v>109</v>
       </c>
       <c r="P229" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="Q229">
         <v>2.5</v>
@@ -48769,7 +48805,7 @@
         <v>254</v>
       </c>
       <c r="P230" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="Q230">
         <v>3.25</v>
@@ -48975,7 +49011,7 @@
         <v>119</v>
       </c>
       <c r="P231" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="Q231">
         <v>2.4</v>
@@ -49053,10 +49089,10 @@
         <v>1.17</v>
       </c>
       <c r="AP231">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ231">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR231">
         <v>1.85</v>
@@ -49262,7 +49298,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ232">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR232">
         <v>1.98</v>
@@ -49465,7 +49501,7 @@
         <v>0.88</v>
       </c>
       <c r="AP233">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ233">
         <v>0.8</v>
@@ -49593,7 +49629,7 @@
         <v>109</v>
       </c>
       <c r="P234" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="Q234">
         <v>2.5</v>
@@ -50211,7 +50247,7 @@
         <v>258</v>
       </c>
       <c r="P237" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="Q237">
         <v>2.75</v>
@@ -50289,7 +50325,7 @@
         <v>1.43</v>
       </c>
       <c r="AP237">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ237">
         <v>1.22</v>
@@ -50417,7 +50453,7 @@
         <v>259</v>
       </c>
       <c r="P238" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="Q238">
         <v>2.6</v>
@@ -50623,7 +50659,7 @@
         <v>109</v>
       </c>
       <c r="P239" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -50704,7 +50740,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ239">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR239">
         <v>1.42</v>
@@ -50829,7 +50865,7 @@
         <v>140</v>
       </c>
       <c r="P240" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -50910,7 +50946,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ240">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR240">
         <v>1.88</v>
@@ -51241,7 +51277,7 @@
         <v>109</v>
       </c>
       <c r="P242" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="Q242">
         <v>3.1</v>
@@ -51653,7 +51689,7 @@
         <v>161</v>
       </c>
       <c r="P244" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="Q244">
         <v>2.1</v>
@@ -52065,7 +52101,7 @@
         <v>156</v>
       </c>
       <c r="P246" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="Q246">
         <v>2.5</v>
@@ -52143,7 +52179,7 @@
         <v>0.63</v>
       </c>
       <c r="AP246">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ246">
         <v>0.8</v>
@@ -52683,7 +52719,7 @@
         <v>176</v>
       </c>
       <c r="P249" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="Q249">
         <v>2.5</v>
@@ -52889,7 +52925,7 @@
         <v>264</v>
       </c>
       <c r="P250" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="Q250">
         <v>3.2</v>
@@ -53095,7 +53131,7 @@
         <v>109</v>
       </c>
       <c r="P251" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="Q251">
         <v>2.75</v>
@@ -53173,7 +53209,7 @@
         <v>0.88</v>
       </c>
       <c r="AP251">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ251">
         <v>1.11</v>
@@ -53301,7 +53337,7 @@
         <v>265</v>
       </c>
       <c r="P252" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="Q252">
         <v>2.25</v>
@@ -54282,6 +54318,2272 @@
       </c>
       <c r="BP256">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="257" spans="1:68">
+      <c r="A257" s="1">
+        <v>256</v>
+      </c>
+      <c r="B257">
+        <v>7781333</v>
+      </c>
+      <c r="C257" t="s">
+        <v>68</v>
+      </c>
+      <c r="D257" t="s">
+        <v>69</v>
+      </c>
+      <c r="E257" s="2">
+        <v>45822.72916666666</v>
+      </c>
+      <c r="F257">
+        <v>0</v>
+      </c>
+      <c r="G257" t="s">
+        <v>80</v>
+      </c>
+      <c r="H257" t="s">
+        <v>84</v>
+      </c>
+      <c r="I257">
+        <v>1</v>
+      </c>
+      <c r="J257">
+        <v>1</v>
+      </c>
+      <c r="K257">
+        <v>2</v>
+      </c>
+      <c r="L257">
+        <v>3</v>
+      </c>
+      <c r="M257">
+        <v>3</v>
+      </c>
+      <c r="N257">
+        <v>6</v>
+      </c>
+      <c r="O257" t="s">
+        <v>270</v>
+      </c>
+      <c r="P257" t="s">
+        <v>397</v>
+      </c>
+      <c r="Q257">
+        <v>2.63</v>
+      </c>
+      <c r="R257">
+        <v>2.4</v>
+      </c>
+      <c r="S257">
+        <v>3.5</v>
+      </c>
+      <c r="T257">
+        <v>1.29</v>
+      </c>
+      <c r="U257">
+        <v>3.5</v>
+      </c>
+      <c r="V257">
+        <v>2.25</v>
+      </c>
+      <c r="W257">
+        <v>1.57</v>
+      </c>
+      <c r="X257">
+        <v>5.5</v>
+      </c>
+      <c r="Y257">
+        <v>1.14</v>
+      </c>
+      <c r="Z257">
+        <v>2.03</v>
+      </c>
+      <c r="AA257">
+        <v>3.51</v>
+      </c>
+      <c r="AB257">
+        <v>2.93</v>
+      </c>
+      <c r="AC257">
+        <v>1.04</v>
+      </c>
+      <c r="AD257">
+        <v>10</v>
+      </c>
+      <c r="AE257">
+        <v>1.2</v>
+      </c>
+      <c r="AF257">
+        <v>4.33</v>
+      </c>
+      <c r="AG257">
+        <v>1.58</v>
+      </c>
+      <c r="AH257">
+        <v>2.22</v>
+      </c>
+      <c r="AI257">
+        <v>1.5</v>
+      </c>
+      <c r="AJ257">
+        <v>2.5</v>
+      </c>
+      <c r="AK257">
+        <v>1.35</v>
+      </c>
+      <c r="AL257">
+        <v>1.27</v>
+      </c>
+      <c r="AM257">
+        <v>1.66</v>
+      </c>
+      <c r="AN257">
+        <v>1.13</v>
+      </c>
+      <c r="AO257">
+        <v>0.22</v>
+      </c>
+      <c r="AP257">
+        <v>1.11</v>
+      </c>
+      <c r="AQ257">
+        <v>0.3</v>
+      </c>
+      <c r="AR257">
+        <v>1.68</v>
+      </c>
+      <c r="AS257">
+        <v>1.21</v>
+      </c>
+      <c r="AT257">
+        <v>2.89</v>
+      </c>
+      <c r="AU257">
+        <v>6</v>
+      </c>
+      <c r="AV257">
+        <v>7</v>
+      </c>
+      <c r="AW257">
+        <v>6</v>
+      </c>
+      <c r="AX257">
+        <v>10</v>
+      </c>
+      <c r="AY257">
+        <v>12</v>
+      </c>
+      <c r="AZ257">
+        <v>17</v>
+      </c>
+      <c r="BA257">
+        <v>4</v>
+      </c>
+      <c r="BB257">
+        <v>5</v>
+      </c>
+      <c r="BC257">
+        <v>9</v>
+      </c>
+      <c r="BD257">
+        <v>1.64</v>
+      </c>
+      <c r="BE257">
+        <v>6.75</v>
+      </c>
+      <c r="BF257">
+        <v>2.48</v>
+      </c>
+      <c r="BG257">
+        <v>1.24</v>
+      </c>
+      <c r="BH257">
+        <v>3.55</v>
+      </c>
+      <c r="BI257">
+        <v>1.43</v>
+      </c>
+      <c r="BJ257">
+        <v>2.6</v>
+      </c>
+      <c r="BK257">
+        <v>1.68</v>
+      </c>
+      <c r="BL257">
+        <v>2.02</v>
+      </c>
+      <c r="BM257">
+        <v>2.07</v>
+      </c>
+      <c r="BN257">
+        <v>1.66</v>
+      </c>
+      <c r="BO257">
+        <v>2.63</v>
+      </c>
+      <c r="BP257">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="258" spans="1:68">
+      <c r="A258" s="1">
+        <v>257</v>
+      </c>
+      <c r="B258">
+        <v>7781334</v>
+      </c>
+      <c r="C258" t="s">
+        <v>68</v>
+      </c>
+      <c r="D258" t="s">
+        <v>69</v>
+      </c>
+      <c r="E258" s="2">
+        <v>45822.85416666666</v>
+      </c>
+      <c r="F258">
+        <v>0</v>
+      </c>
+      <c r="G258" t="s">
+        <v>74</v>
+      </c>
+      <c r="H258" t="s">
+        <v>95</v>
+      </c>
+      <c r="I258">
+        <v>2</v>
+      </c>
+      <c r="J258">
+        <v>1</v>
+      </c>
+      <c r="K258">
+        <v>3</v>
+      </c>
+      <c r="L258">
+        <v>2</v>
+      </c>
+      <c r="M258">
+        <v>1</v>
+      </c>
+      <c r="N258">
+        <v>3</v>
+      </c>
+      <c r="O258" t="s">
+        <v>271</v>
+      </c>
+      <c r="P258" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q258">
+        <v>2.3</v>
+      </c>
+      <c r="R258">
+        <v>2.38</v>
+      </c>
+      <c r="S258">
+        <v>4.33</v>
+      </c>
+      <c r="T258">
+        <v>1.3</v>
+      </c>
+      <c r="U258">
+        <v>3.4</v>
+      </c>
+      <c r="V258">
+        <v>2.38</v>
+      </c>
+      <c r="W258">
+        <v>1.53</v>
+      </c>
+      <c r="X258">
+        <v>6</v>
+      </c>
+      <c r="Y258">
+        <v>1.13</v>
+      </c>
+      <c r="Z258">
+        <v>1.73</v>
+      </c>
+      <c r="AA258">
+        <v>3.68</v>
+      </c>
+      <c r="AB258">
+        <v>3.69</v>
+      </c>
+      <c r="AC258">
+        <v>1.03</v>
+      </c>
+      <c r="AD258">
+        <v>11.5</v>
+      </c>
+      <c r="AE258">
+        <v>1.21</v>
+      </c>
+      <c r="AF258">
+        <v>4</v>
+      </c>
+      <c r="AG258">
+        <v>1.75</v>
+      </c>
+      <c r="AH258">
+        <v>1.95</v>
+      </c>
+      <c r="AI258">
+        <v>1.67</v>
+      </c>
+      <c r="AJ258">
+        <v>2.1</v>
+      </c>
+      <c r="AK258">
+        <v>1.24</v>
+      </c>
+      <c r="AL258">
+        <v>1.26</v>
+      </c>
+      <c r="AM258">
+        <v>1.93</v>
+      </c>
+      <c r="AN258">
+        <v>1.67</v>
+      </c>
+      <c r="AO258">
+        <v>2.14</v>
+      </c>
+      <c r="AP258">
+        <v>1.8</v>
+      </c>
+      <c r="AQ258">
+        <v>1.88</v>
+      </c>
+      <c r="AR258">
+        <v>1.85</v>
+      </c>
+      <c r="AS258">
+        <v>1.65</v>
+      </c>
+      <c r="AT258">
+        <v>3.5</v>
+      </c>
+      <c r="AU258">
+        <v>9</v>
+      </c>
+      <c r="AV258">
+        <v>4</v>
+      </c>
+      <c r="AW258">
+        <v>3</v>
+      </c>
+      <c r="AX258">
+        <v>5</v>
+      </c>
+      <c r="AY258">
+        <v>12</v>
+      </c>
+      <c r="AZ258">
+        <v>9</v>
+      </c>
+      <c r="BA258">
+        <v>4</v>
+      </c>
+      <c r="BB258">
+        <v>1</v>
+      </c>
+      <c r="BC258">
+        <v>5</v>
+      </c>
+      <c r="BD258">
+        <v>1.58</v>
+      </c>
+      <c r="BE258">
+        <v>6.5</v>
+      </c>
+      <c r="BF258">
+        <v>2.65</v>
+      </c>
+      <c r="BG258">
+        <v>1.29</v>
+      </c>
+      <c r="BH258">
+        <v>3.15</v>
+      </c>
+      <c r="BI258">
+        <v>1.5</v>
+      </c>
+      <c r="BJ258">
+        <v>2.35</v>
+      </c>
+      <c r="BK258">
+        <v>1.83</v>
+      </c>
+      <c r="BL258">
+        <v>1.85</v>
+      </c>
+      <c r="BM258">
+        <v>2.3</v>
+      </c>
+      <c r="BN258">
+        <v>1.53</v>
+      </c>
+      <c r="BO258">
+        <v>2.95</v>
+      </c>
+      <c r="BP258">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="259" spans="1:68">
+      <c r="A259" s="1">
+        <v>258</v>
+      </c>
+      <c r="B259">
+        <v>7781335</v>
+      </c>
+      <c r="C259" t="s">
+        <v>68</v>
+      </c>
+      <c r="D259" t="s">
+        <v>69</v>
+      </c>
+      <c r="E259" s="2">
+        <v>45822.85416666666</v>
+      </c>
+      <c r="F259">
+        <v>0</v>
+      </c>
+      <c r="G259" t="s">
+        <v>87</v>
+      </c>
+      <c r="H259" t="s">
+        <v>73</v>
+      </c>
+      <c r="I259">
+        <v>0</v>
+      </c>
+      <c r="J259">
+        <v>1</v>
+      </c>
+      <c r="K259">
+        <v>1</v>
+      </c>
+      <c r="L259">
+        <v>0</v>
+      </c>
+      <c r="M259">
+        <v>1</v>
+      </c>
+      <c r="N259">
+        <v>1</v>
+      </c>
+      <c r="O259" t="s">
+        <v>109</v>
+      </c>
+      <c r="P259" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q259">
+        <v>3.1</v>
+      </c>
+      <c r="R259">
+        <v>2.3</v>
+      </c>
+      <c r="S259">
+        <v>3.1</v>
+      </c>
+      <c r="T259">
+        <v>1.33</v>
+      </c>
+      <c r="U259">
+        <v>3.25</v>
+      </c>
+      <c r="V259">
+        <v>2.5</v>
+      </c>
+      <c r="W259">
+        <v>1.5</v>
+      </c>
+      <c r="X259">
+        <v>6</v>
+      </c>
+      <c r="Y259">
+        <v>1.13</v>
+      </c>
+      <c r="Z259">
+        <v>2.42</v>
+      </c>
+      <c r="AA259">
+        <v>3.3</v>
+      </c>
+      <c r="AB259">
+        <v>2.48</v>
+      </c>
+      <c r="AC259">
+        <v>1.04</v>
+      </c>
+      <c r="AD259">
+        <v>10.5</v>
+      </c>
+      <c r="AE259">
+        <v>1.23</v>
+      </c>
+      <c r="AF259">
+        <v>3.8</v>
+      </c>
+      <c r="AG259">
+        <v>1.69</v>
+      </c>
+      <c r="AH259">
+        <v>2.04</v>
+      </c>
+      <c r="AI259">
+        <v>1.57</v>
+      </c>
+      <c r="AJ259">
+        <v>2.25</v>
+      </c>
+      <c r="AK259">
+        <v>1.47</v>
+      </c>
+      <c r="AL259">
+        <v>1.3</v>
+      </c>
+      <c r="AM259">
+        <v>1.49</v>
+      </c>
+      <c r="AN259">
+        <v>1.4</v>
+      </c>
+      <c r="AO259">
+        <v>1.44</v>
+      </c>
+      <c r="AP259">
+        <v>1.17</v>
+      </c>
+      <c r="AQ259">
+        <v>1.6</v>
+      </c>
+      <c r="AR259">
+        <v>1.33</v>
+      </c>
+      <c r="AS259">
+        <v>1.65</v>
+      </c>
+      <c r="AT259">
+        <v>2.98</v>
+      </c>
+      <c r="AU259">
+        <v>3</v>
+      </c>
+      <c r="AV259">
+        <v>9</v>
+      </c>
+      <c r="AW259">
+        <v>10</v>
+      </c>
+      <c r="AX259">
+        <v>2</v>
+      </c>
+      <c r="AY259">
+        <v>13</v>
+      </c>
+      <c r="AZ259">
+        <v>11</v>
+      </c>
+      <c r="BA259">
+        <v>8</v>
+      </c>
+      <c r="BB259">
+        <v>3</v>
+      </c>
+      <c r="BC259">
+        <v>11</v>
+      </c>
+      <c r="BD259">
+        <v>1.85</v>
+      </c>
+      <c r="BE259">
+        <v>6.5</v>
+      </c>
+      <c r="BF259">
+        <v>2.15</v>
+      </c>
+      <c r="BG259">
+        <v>1.3</v>
+      </c>
+      <c r="BH259">
+        <v>3.15</v>
+      </c>
+      <c r="BI259">
+        <v>1.5</v>
+      </c>
+      <c r="BJ259">
+        <v>2.35</v>
+      </c>
+      <c r="BK259">
+        <v>1.82</v>
+      </c>
+      <c r="BL259">
+        <v>1.86</v>
+      </c>
+      <c r="BM259">
+        <v>2.3</v>
+      </c>
+      <c r="BN259">
+        <v>1.54</v>
+      </c>
+      <c r="BO259">
+        <v>2.9</v>
+      </c>
+      <c r="BP259">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="260" spans="1:68">
+      <c r="A260" s="1">
+        <v>259</v>
+      </c>
+      <c r="B260">
+        <v>7781336</v>
+      </c>
+      <c r="C260" t="s">
+        <v>68</v>
+      </c>
+      <c r="D260" t="s">
+        <v>69</v>
+      </c>
+      <c r="E260" s="2">
+        <v>45822.85416666666</v>
+      </c>
+      <c r="F260">
+        <v>0</v>
+      </c>
+      <c r="G260" t="s">
+        <v>89</v>
+      </c>
+      <c r="H260" t="s">
+        <v>85</v>
+      </c>
+      <c r="I260">
+        <v>1</v>
+      </c>
+      <c r="J260">
+        <v>0</v>
+      </c>
+      <c r="K260">
+        <v>1</v>
+      </c>
+      <c r="L260">
+        <v>2</v>
+      </c>
+      <c r="M260">
+        <v>1</v>
+      </c>
+      <c r="N260">
+        <v>3</v>
+      </c>
+      <c r="O260" t="s">
+        <v>272</v>
+      </c>
+      <c r="P260" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q260">
+        <v>2.2</v>
+      </c>
+      <c r="R260">
+        <v>2.4</v>
+      </c>
+      <c r="S260">
+        <v>4.5</v>
+      </c>
+      <c r="T260">
+        <v>1.29</v>
+      </c>
+      <c r="U260">
+        <v>3.5</v>
+      </c>
+      <c r="V260">
+        <v>2.25</v>
+      </c>
+      <c r="W260">
+        <v>1.57</v>
+      </c>
+      <c r="X260">
+        <v>5.5</v>
+      </c>
+      <c r="Y260">
+        <v>1.14</v>
+      </c>
+      <c r="Z260">
+        <v>1.67</v>
+      </c>
+      <c r="AA260">
+        <v>3.66</v>
+      </c>
+      <c r="AB260">
+        <v>4</v>
+      </c>
+      <c r="AC260">
+        <v>1.03</v>
+      </c>
+      <c r="AD260">
+        <v>12</v>
+      </c>
+      <c r="AE260">
+        <v>1.19</v>
+      </c>
+      <c r="AF260">
+        <v>4.33</v>
+      </c>
+      <c r="AG260">
+        <v>1.57</v>
+      </c>
+      <c r="AH260">
+        <v>2.31</v>
+      </c>
+      <c r="AI260">
+        <v>1.57</v>
+      </c>
+      <c r="AJ260">
+        <v>2.25</v>
+      </c>
+      <c r="AK260">
+        <v>1.21</v>
+      </c>
+      <c r="AL260">
+        <v>1.24</v>
+      </c>
+      <c r="AM260">
+        <v>2.05</v>
+      </c>
+      <c r="AN260">
+        <v>2</v>
+      </c>
+      <c r="AO260">
+        <v>0.78</v>
+      </c>
+      <c r="AP260">
+        <v>2.1</v>
+      </c>
+      <c r="AQ260">
+        <v>0.7</v>
+      </c>
+      <c r="AR260">
+        <v>1.87</v>
+      </c>
+      <c r="AS260">
+        <v>1.18</v>
+      </c>
+      <c r="AT260">
+        <v>3.05</v>
+      </c>
+      <c r="AU260">
+        <v>10</v>
+      </c>
+      <c r="AV260">
+        <v>4</v>
+      </c>
+      <c r="AW260">
+        <v>7</v>
+      </c>
+      <c r="AX260">
+        <v>3</v>
+      </c>
+      <c r="AY260">
+        <v>17</v>
+      </c>
+      <c r="AZ260">
+        <v>7</v>
+      </c>
+      <c r="BA260">
+        <v>8</v>
+      </c>
+      <c r="BB260">
+        <v>4</v>
+      </c>
+      <c r="BC260">
+        <v>12</v>
+      </c>
+      <c r="BD260">
+        <v>1.41</v>
+      </c>
+      <c r="BE260">
+        <v>7</v>
+      </c>
+      <c r="BF260">
+        <v>3.2</v>
+      </c>
+      <c r="BG260">
+        <v>1.25</v>
+      </c>
+      <c r="BH260">
+        <v>3.4</v>
+      </c>
+      <c r="BI260">
+        <v>1.44</v>
+      </c>
+      <c r="BJ260">
+        <v>2.55</v>
+      </c>
+      <c r="BK260">
+        <v>1.73</v>
+      </c>
+      <c r="BL260">
+        <v>1.98</v>
+      </c>
+      <c r="BM260">
+        <v>2.14</v>
+      </c>
+      <c r="BN260">
+        <v>1.62</v>
+      </c>
+      <c r="BO260">
+        <v>2.7</v>
+      </c>
+      <c r="BP260">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="261" spans="1:68">
+      <c r="A261" s="1">
+        <v>260</v>
+      </c>
+      <c r="B261">
+        <v>7781337</v>
+      </c>
+      <c r="C261" t="s">
+        <v>68</v>
+      </c>
+      <c r="D261" t="s">
+        <v>69</v>
+      </c>
+      <c r="E261" s="2">
+        <v>45822.89583333334</v>
+      </c>
+      <c r="F261">
+        <v>0</v>
+      </c>
+      <c r="G261" t="s">
+        <v>77</v>
+      </c>
+      <c r="H261" t="s">
+        <v>88</v>
+      </c>
+      <c r="I261">
+        <v>1</v>
+      </c>
+      <c r="J261">
+        <v>0</v>
+      </c>
+      <c r="K261">
+        <v>1</v>
+      </c>
+      <c r="L261">
+        <v>2</v>
+      </c>
+      <c r="M261">
+        <v>0</v>
+      </c>
+      <c r="N261">
+        <v>2</v>
+      </c>
+      <c r="O261" t="s">
+        <v>273</v>
+      </c>
+      <c r="P261" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q261">
+        <v>2.88</v>
+      </c>
+      <c r="R261">
+        <v>2.1</v>
+      </c>
+      <c r="S261">
+        <v>4</v>
+      </c>
+      <c r="T261">
+        <v>1.44</v>
+      </c>
+      <c r="U261">
+        <v>2.63</v>
+      </c>
+      <c r="V261">
+        <v>3.25</v>
+      </c>
+      <c r="W261">
+        <v>1.33</v>
+      </c>
+      <c r="X261">
+        <v>9</v>
+      </c>
+      <c r="Y261">
+        <v>1.07</v>
+      </c>
+      <c r="Z261">
+        <v>2.15</v>
+      </c>
+      <c r="AA261">
+        <v>3.03</v>
+      </c>
+      <c r="AB261">
+        <v>3.08</v>
+      </c>
+      <c r="AC261">
+        <v>1.07</v>
+      </c>
+      <c r="AD261">
+        <v>7.75</v>
+      </c>
+      <c r="AE261">
+        <v>1.35</v>
+      </c>
+      <c r="AF261">
+        <v>2.9</v>
+      </c>
+      <c r="AG261">
+        <v>1.98</v>
+      </c>
+      <c r="AH261">
+        <v>1.73</v>
+      </c>
+      <c r="AI261">
+        <v>1.91</v>
+      </c>
+      <c r="AJ261">
+        <v>1.91</v>
+      </c>
+      <c r="AK261">
+        <v>1.31</v>
+      </c>
+      <c r="AL261">
+        <v>1.32</v>
+      </c>
+      <c r="AM261">
+        <v>1.65</v>
+      </c>
+      <c r="AN261">
+        <v>1.44</v>
+      </c>
+      <c r="AO261">
+        <v>0.63</v>
+      </c>
+      <c r="AP261">
+        <v>1.6</v>
+      </c>
+      <c r="AQ261">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR261">
+        <v>1.67</v>
+      </c>
+      <c r="AS261">
+        <v>1.17</v>
+      </c>
+      <c r="AT261">
+        <v>2.84</v>
+      </c>
+      <c r="AU261">
+        <v>8</v>
+      </c>
+      <c r="AV261">
+        <v>9</v>
+      </c>
+      <c r="AW261">
+        <v>0</v>
+      </c>
+      <c r="AX261">
+        <v>4</v>
+      </c>
+      <c r="AY261">
+        <v>8</v>
+      </c>
+      <c r="AZ261">
+        <v>13</v>
+      </c>
+      <c r="BA261">
+        <v>2</v>
+      </c>
+      <c r="BB261">
+        <v>7</v>
+      </c>
+      <c r="BC261">
+        <v>9</v>
+      </c>
+      <c r="BD261">
+        <v>1.74</v>
+      </c>
+      <c r="BE261">
+        <v>8.5</v>
+      </c>
+      <c r="BF261">
+        <v>2.49</v>
+      </c>
+      <c r="BG261">
+        <v>1.23</v>
+      </c>
+      <c r="BH261">
+        <v>3.42</v>
+      </c>
+      <c r="BI261">
+        <v>1.46</v>
+      </c>
+      <c r="BJ261">
+        <v>2.45</v>
+      </c>
+      <c r="BK261">
+        <v>1.75</v>
+      </c>
+      <c r="BL261">
+        <v>1.95</v>
+      </c>
+      <c r="BM261">
+        <v>2.32</v>
+      </c>
+      <c r="BN261">
+        <v>1.51</v>
+      </c>
+      <c r="BO261">
+        <v>3.08</v>
+      </c>
+      <c r="BP261">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="262" spans="1:68">
+      <c r="A262" s="1">
+        <v>261</v>
+      </c>
+      <c r="B262">
+        <v>7781341</v>
+      </c>
+      <c r="C262" t="s">
+        <v>68</v>
+      </c>
+      <c r="D262" t="s">
+        <v>69</v>
+      </c>
+      <c r="E262" s="2">
+        <v>45822.89583333334</v>
+      </c>
+      <c r="F262">
+        <v>0</v>
+      </c>
+      <c r="G262" t="s">
+        <v>92</v>
+      </c>
+      <c r="H262" t="s">
+        <v>94</v>
+      </c>
+      <c r="I262">
+        <v>1</v>
+      </c>
+      <c r="J262">
+        <v>1</v>
+      </c>
+      <c r="K262">
+        <v>2</v>
+      </c>
+      <c r="L262">
+        <v>1</v>
+      </c>
+      <c r="M262">
+        <v>4</v>
+      </c>
+      <c r="N262">
+        <v>5</v>
+      </c>
+      <c r="O262" t="s">
+        <v>274</v>
+      </c>
+      <c r="P262" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q262">
+        <v>0</v>
+      </c>
+      <c r="R262">
+        <v>0</v>
+      </c>
+      <c r="S262">
+        <v>0</v>
+      </c>
+      <c r="T262">
+        <v>0</v>
+      </c>
+      <c r="U262">
+        <v>0</v>
+      </c>
+      <c r="V262">
+        <v>0</v>
+      </c>
+      <c r="W262">
+        <v>0</v>
+      </c>
+      <c r="X262">
+        <v>0</v>
+      </c>
+      <c r="Y262">
+        <v>0</v>
+      </c>
+      <c r="Z262">
+        <v>1.96</v>
+      </c>
+      <c r="AA262">
+        <v>3.41</v>
+      </c>
+      <c r="AB262">
+        <v>3.16</v>
+      </c>
+      <c r="AC262">
+        <v>0</v>
+      </c>
+      <c r="AD262">
+        <v>0</v>
+      </c>
+      <c r="AE262">
+        <v>0</v>
+      </c>
+      <c r="AF262">
+        <v>0</v>
+      </c>
+      <c r="AG262">
+        <v>1.78</v>
+      </c>
+      <c r="AH262">
+        <v>1.92</v>
+      </c>
+      <c r="AI262">
+        <v>0</v>
+      </c>
+      <c r="AJ262">
+        <v>0</v>
+      </c>
+      <c r="AK262">
+        <v>0</v>
+      </c>
+      <c r="AL262">
+        <v>0</v>
+      </c>
+      <c r="AM262">
+        <v>0</v>
+      </c>
+      <c r="AN262">
+        <v>1.88</v>
+      </c>
+      <c r="AO262">
+        <v>1.29</v>
+      </c>
+      <c r="AP262">
+        <v>1.67</v>
+      </c>
+      <c r="AQ262">
+        <v>1.5</v>
+      </c>
+      <c r="AR262">
+        <v>1.82</v>
+      </c>
+      <c r="AS262">
+        <v>1.67</v>
+      </c>
+      <c r="AT262">
+        <v>3.49</v>
+      </c>
+      <c r="AU262">
+        <v>7</v>
+      </c>
+      <c r="AV262">
+        <v>8</v>
+      </c>
+      <c r="AW262">
+        <v>2</v>
+      </c>
+      <c r="AX262">
+        <v>5</v>
+      </c>
+      <c r="AY262">
+        <v>9</v>
+      </c>
+      <c r="AZ262">
+        <v>13</v>
+      </c>
+      <c r="BA262">
+        <v>3</v>
+      </c>
+      <c r="BB262">
+        <v>4</v>
+      </c>
+      <c r="BC262">
+        <v>7</v>
+      </c>
+      <c r="BD262">
+        <v>0</v>
+      </c>
+      <c r="BE262">
+        <v>0</v>
+      </c>
+      <c r="BF262">
+        <v>0</v>
+      </c>
+      <c r="BG262">
+        <v>0</v>
+      </c>
+      <c r="BH262">
+        <v>0</v>
+      </c>
+      <c r="BI262">
+        <v>0</v>
+      </c>
+      <c r="BJ262">
+        <v>0</v>
+      </c>
+      <c r="BK262">
+        <v>0</v>
+      </c>
+      <c r="BL262">
+        <v>0</v>
+      </c>
+      <c r="BM262">
+        <v>0</v>
+      </c>
+      <c r="BN262">
+        <v>0</v>
+      </c>
+      <c r="BO262">
+        <v>0</v>
+      </c>
+      <c r="BP262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:68">
+      <c r="A263" s="1">
+        <v>262</v>
+      </c>
+      <c r="B263">
+        <v>7781340</v>
+      </c>
+      <c r="C263" t="s">
+        <v>68</v>
+      </c>
+      <c r="D263" t="s">
+        <v>69</v>
+      </c>
+      <c r="E263" s="2">
+        <v>45822.89583333334</v>
+      </c>
+      <c r="F263">
+        <v>0</v>
+      </c>
+      <c r="G263" t="s">
+        <v>91</v>
+      </c>
+      <c r="H263" t="s">
+        <v>97</v>
+      </c>
+      <c r="I263">
+        <v>1</v>
+      </c>
+      <c r="J263">
+        <v>1</v>
+      </c>
+      <c r="K263">
+        <v>2</v>
+      </c>
+      <c r="L263">
+        <v>2</v>
+      </c>
+      <c r="M263">
+        <v>4</v>
+      </c>
+      <c r="N263">
+        <v>6</v>
+      </c>
+      <c r="O263" t="s">
+        <v>275</v>
+      </c>
+      <c r="P263" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q263">
+        <v>2.5</v>
+      </c>
+      <c r="R263">
+        <v>2.3</v>
+      </c>
+      <c r="S263">
+        <v>4</v>
+      </c>
+      <c r="T263">
+        <v>1.3</v>
+      </c>
+      <c r="U263">
+        <v>3.4</v>
+      </c>
+      <c r="V263">
+        <v>2.5</v>
+      </c>
+      <c r="W263">
+        <v>1.5</v>
+      </c>
+      <c r="X263">
+        <v>6</v>
+      </c>
+      <c r="Y263">
+        <v>1.13</v>
+      </c>
+      <c r="Z263">
+        <v>1.92</v>
+      </c>
+      <c r="AA263">
+        <v>3.41</v>
+      </c>
+      <c r="AB263">
+        <v>3.29</v>
+      </c>
+      <c r="AC263">
+        <v>1.04</v>
+      </c>
+      <c r="AD263">
+        <v>10.5</v>
+      </c>
+      <c r="AE263">
+        <v>1.22</v>
+      </c>
+      <c r="AF263">
+        <v>3.8</v>
+      </c>
+      <c r="AG263">
+        <v>1.6</v>
+      </c>
+      <c r="AH263">
+        <v>2.19</v>
+      </c>
+      <c r="AI263">
+        <v>1.62</v>
+      </c>
+      <c r="AJ263">
+        <v>2.2</v>
+      </c>
+      <c r="AK263">
+        <v>1.3</v>
+      </c>
+      <c r="AL263">
+        <v>1.28</v>
+      </c>
+      <c r="AM263">
+        <v>1.75</v>
+      </c>
+      <c r="AN263">
+        <v>1.14</v>
+      </c>
+      <c r="AO263">
+        <v>1.44</v>
+      </c>
+      <c r="AP263">
+        <v>1</v>
+      </c>
+      <c r="AQ263">
+        <v>1.6</v>
+      </c>
+      <c r="AR263">
+        <v>1.61</v>
+      </c>
+      <c r="AS263">
+        <v>1.38</v>
+      </c>
+      <c r="AT263">
+        <v>2.99</v>
+      </c>
+      <c r="AU263">
+        <v>6</v>
+      </c>
+      <c r="AV263">
+        <v>5</v>
+      </c>
+      <c r="AW263">
+        <v>4</v>
+      </c>
+      <c r="AX263">
+        <v>6</v>
+      </c>
+      <c r="AY263">
+        <v>10</v>
+      </c>
+      <c r="AZ263">
+        <v>11</v>
+      </c>
+      <c r="BA263">
+        <v>6</v>
+      </c>
+      <c r="BB263">
+        <v>3</v>
+      </c>
+      <c r="BC263">
+        <v>9</v>
+      </c>
+      <c r="BD263">
+        <v>1.51</v>
+      </c>
+      <c r="BE263">
+        <v>9</v>
+      </c>
+      <c r="BF263">
+        <v>3.12</v>
+      </c>
+      <c r="BG263">
+        <v>1.25</v>
+      </c>
+      <c r="BH263">
+        <v>3.28</v>
+      </c>
+      <c r="BI263">
+        <v>1.49</v>
+      </c>
+      <c r="BJ263">
+        <v>2.38</v>
+      </c>
+      <c r="BK263">
+        <v>1.85</v>
+      </c>
+      <c r="BL263">
+        <v>1.85</v>
+      </c>
+      <c r="BM263">
+        <v>2.4</v>
+      </c>
+      <c r="BN263">
+        <v>1.48</v>
+      </c>
+      <c r="BO263">
+        <v>3.2</v>
+      </c>
+      <c r="BP263">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="264" spans="1:68">
+      <c r="A264" s="1">
+        <v>263</v>
+      </c>
+      <c r="B264">
+        <v>7781338</v>
+      </c>
+      <c r="C264" t="s">
+        <v>68</v>
+      </c>
+      <c r="D264" t="s">
+        <v>69</v>
+      </c>
+      <c r="E264" s="2">
+        <v>45822.89583333334</v>
+      </c>
+      <c r="F264">
+        <v>0</v>
+      </c>
+      <c r="G264" t="s">
+        <v>90</v>
+      </c>
+      <c r="H264" t="s">
+        <v>79</v>
+      </c>
+      <c r="I264">
+        <v>0</v>
+      </c>
+      <c r="J264">
+        <v>0</v>
+      </c>
+      <c r="K264">
+        <v>0</v>
+      </c>
+      <c r="L264">
+        <v>0</v>
+      </c>
+      <c r="M264">
+        <v>2</v>
+      </c>
+      <c r="N264">
+        <v>2</v>
+      </c>
+      <c r="O264" t="s">
+        <v>109</v>
+      </c>
+      <c r="P264" t="s">
+        <v>400</v>
+      </c>
+      <c r="Q264">
+        <v>2.75</v>
+      </c>
+      <c r="R264">
+        <v>2.25</v>
+      </c>
+      <c r="S264">
+        <v>3.1</v>
+      </c>
+      <c r="T264">
+        <v>1.27</v>
+      </c>
+      <c r="U264">
+        <v>3.4</v>
+      </c>
+      <c r="V264">
+        <v>2.2</v>
+      </c>
+      <c r="W264">
+        <v>1.58</v>
+      </c>
+      <c r="X264">
+        <v>5</v>
+      </c>
+      <c r="Y264">
+        <v>1.15</v>
+      </c>
+      <c r="Z264">
+        <v>2.29</v>
+      </c>
+      <c r="AA264">
+        <v>3.33</v>
+      </c>
+      <c r="AB264">
+        <v>2.61</v>
+      </c>
+      <c r="AC264">
+        <v>1.02</v>
+      </c>
+      <c r="AD264">
+        <v>13</v>
+      </c>
+      <c r="AE264">
+        <v>1.16</v>
+      </c>
+      <c r="AF264">
+        <v>4.6</v>
+      </c>
+      <c r="AG264">
+        <v>1.6</v>
+      </c>
+      <c r="AH264">
+        <v>2.19</v>
+      </c>
+      <c r="AI264">
+        <v>1.46</v>
+      </c>
+      <c r="AJ264">
+        <v>2.5</v>
+      </c>
+      <c r="AK264">
+        <v>1.43</v>
+      </c>
+      <c r="AL264">
+        <v>1.27</v>
+      </c>
+      <c r="AM264">
+        <v>1.57</v>
+      </c>
+      <c r="AN264">
+        <v>1.17</v>
+      </c>
+      <c r="AO264">
+        <v>1.43</v>
+      </c>
+      <c r="AP264">
+        <v>1</v>
+      </c>
+      <c r="AQ264">
+        <v>1.63</v>
+      </c>
+      <c r="AR264">
+        <v>1.64</v>
+      </c>
+      <c r="AS264">
+        <v>1.6</v>
+      </c>
+      <c r="AT264">
+        <v>3.24</v>
+      </c>
+      <c r="AU264">
+        <v>8</v>
+      </c>
+      <c r="AV264">
+        <v>4</v>
+      </c>
+      <c r="AW264">
+        <v>5</v>
+      </c>
+      <c r="AX264">
+        <v>6</v>
+      </c>
+      <c r="AY264">
+        <v>13</v>
+      </c>
+      <c r="AZ264">
+        <v>10</v>
+      </c>
+      <c r="BA264">
+        <v>9</v>
+      </c>
+      <c r="BB264">
+        <v>4</v>
+      </c>
+      <c r="BC264">
+        <v>13</v>
+      </c>
+      <c r="BD264">
+        <v>2.13</v>
+      </c>
+      <c r="BE264">
+        <v>6.45</v>
+      </c>
+      <c r="BF264">
+        <v>2.13</v>
+      </c>
+      <c r="BG264">
+        <v>1.23</v>
+      </c>
+      <c r="BH264">
+        <v>3.42</v>
+      </c>
+      <c r="BI264">
+        <v>1.46</v>
+      </c>
+      <c r="BJ264">
+        <v>2.45</v>
+      </c>
+      <c r="BK264">
+        <v>1.85</v>
+      </c>
+      <c r="BL264">
+        <v>1.85</v>
+      </c>
+      <c r="BM264">
+        <v>2.3</v>
+      </c>
+      <c r="BN264">
+        <v>1.52</v>
+      </c>
+      <c r="BO264">
+        <v>3.08</v>
+      </c>
+      <c r="BP264">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="265" spans="1:68">
+      <c r="A265" s="1">
+        <v>264</v>
+      </c>
+      <c r="B265">
+        <v>7781339</v>
+      </c>
+      <c r="C265" t="s">
+        <v>68</v>
+      </c>
+      <c r="D265" t="s">
+        <v>69</v>
+      </c>
+      <c r="E265" s="2">
+        <v>45822.89583333334</v>
+      </c>
+      <c r="F265">
+        <v>0</v>
+      </c>
+      <c r="G265" t="s">
+        <v>78</v>
+      </c>
+      <c r="H265" t="s">
+        <v>99</v>
+      </c>
+      <c r="I265">
+        <v>0</v>
+      </c>
+      <c r="J265">
+        <v>2</v>
+      </c>
+      <c r="K265">
+        <v>2</v>
+      </c>
+      <c r="L265">
+        <v>1</v>
+      </c>
+      <c r="M265">
+        <v>3</v>
+      </c>
+      <c r="N265">
+        <v>4</v>
+      </c>
+      <c r="O265" t="s">
+        <v>234</v>
+      </c>
+      <c r="P265" t="s">
+        <v>401</v>
+      </c>
+      <c r="Q265">
+        <v>2.25</v>
+      </c>
+      <c r="R265">
+        <v>2.3</v>
+      </c>
+      <c r="S265">
+        <v>5</v>
+      </c>
+      <c r="T265">
+        <v>1.36</v>
+      </c>
+      <c r="U265">
+        <v>3</v>
+      </c>
+      <c r="V265">
+        <v>2.63</v>
+      </c>
+      <c r="W265">
+        <v>1.44</v>
+      </c>
+      <c r="X265">
+        <v>7</v>
+      </c>
+      <c r="Y265">
+        <v>1.1</v>
+      </c>
+      <c r="Z265">
+        <v>1.62</v>
+      </c>
+      <c r="AA265">
+        <v>3.64</v>
+      </c>
+      <c r="AB265">
+        <v>4.4</v>
+      </c>
+      <c r="AC265">
+        <v>1.04</v>
+      </c>
+      <c r="AD265">
+        <v>10</v>
+      </c>
+      <c r="AE265">
+        <v>1.25</v>
+      </c>
+      <c r="AF265">
+        <v>3.5</v>
+      </c>
+      <c r="AG265">
+        <v>1.78</v>
+      </c>
+      <c r="AH265">
+        <v>1.92</v>
+      </c>
+      <c r="AI265">
+        <v>1.8</v>
+      </c>
+      <c r="AJ265">
+        <v>1.95</v>
+      </c>
+      <c r="AK265">
+        <v>1.18</v>
+      </c>
+      <c r="AL265">
+        <v>1.25</v>
+      </c>
+      <c r="AM265">
+        <v>2.15</v>
+      </c>
+      <c r="AN265">
+        <v>1.11</v>
+      </c>
+      <c r="AO265">
+        <v>0.5</v>
+      </c>
+      <c r="AP265">
+        <v>1</v>
+      </c>
+      <c r="AQ265">
+        <v>0.73</v>
+      </c>
+      <c r="AR265">
+        <v>1.72</v>
+      </c>
+      <c r="AS265">
+        <v>1.36</v>
+      </c>
+      <c r="AT265">
+        <v>3.08</v>
+      </c>
+      <c r="AU265">
+        <v>4</v>
+      </c>
+      <c r="AV265">
+        <v>4</v>
+      </c>
+      <c r="AW265">
+        <v>8</v>
+      </c>
+      <c r="AX265">
+        <v>9</v>
+      </c>
+      <c r="AY265">
+        <v>12</v>
+      </c>
+      <c r="AZ265">
+        <v>13</v>
+      </c>
+      <c r="BA265">
+        <v>7</v>
+      </c>
+      <c r="BB265">
+        <v>7</v>
+      </c>
+      <c r="BC265">
+        <v>14</v>
+      </c>
+      <c r="BD265">
+        <v>1.56</v>
+      </c>
+      <c r="BE265">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF265">
+        <v>2.85</v>
+      </c>
+      <c r="BG265">
+        <v>1.22</v>
+      </c>
+      <c r="BH265">
+        <v>3.48</v>
+      </c>
+      <c r="BI265">
+        <v>1.45</v>
+      </c>
+      <c r="BJ265">
+        <v>2.48</v>
+      </c>
+      <c r="BK265">
+        <v>1.85</v>
+      </c>
+      <c r="BL265">
+        <v>1.85</v>
+      </c>
+      <c r="BM265">
+        <v>2.28</v>
+      </c>
+      <c r="BN265">
+        <v>1.53</v>
+      </c>
+      <c r="BO265">
+        <v>3.04</v>
+      </c>
+      <c r="BP265">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="266" spans="1:68">
+      <c r="A266" s="1">
+        <v>265</v>
+      </c>
+      <c r="B266">
+        <v>7781343</v>
+      </c>
+      <c r="C266" t="s">
+        <v>68</v>
+      </c>
+      <c r="D266" t="s">
+        <v>69</v>
+      </c>
+      <c r="E266" s="2">
+        <v>45822.9375</v>
+      </c>
+      <c r="F266">
+        <v>0</v>
+      </c>
+      <c r="G266" t="s">
+        <v>86</v>
+      </c>
+      <c r="H266" t="s">
+        <v>75</v>
+      </c>
+      <c r="I266">
+        <v>1</v>
+      </c>
+      <c r="J266">
+        <v>0</v>
+      </c>
+      <c r="K266">
+        <v>1</v>
+      </c>
+      <c r="L266">
+        <v>2</v>
+      </c>
+      <c r="M266">
+        <v>0</v>
+      </c>
+      <c r="N266">
+        <v>2</v>
+      </c>
+      <c r="O266" t="s">
+        <v>276</v>
+      </c>
+      <c r="P266" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q266">
+        <v>2.3</v>
+      </c>
+      <c r="R266">
+        <v>2.38</v>
+      </c>
+      <c r="S266">
+        <v>4.75</v>
+      </c>
+      <c r="T266">
+        <v>1.33</v>
+      </c>
+      <c r="U266">
+        <v>3.25</v>
+      </c>
+      <c r="V266">
+        <v>2.5</v>
+      </c>
+      <c r="W266">
+        <v>1.5</v>
+      </c>
+      <c r="X266">
+        <v>6.5</v>
+      </c>
+      <c r="Y266">
+        <v>1.11</v>
+      </c>
+      <c r="Z266">
+        <v>1.66</v>
+      </c>
+      <c r="AA266">
+        <v>3.64</v>
+      </c>
+      <c r="AB266">
+        <v>4.1</v>
+      </c>
+      <c r="AC266">
+        <v>1.04</v>
+      </c>
+      <c r="AD266">
+        <v>10.5</v>
+      </c>
+      <c r="AE266">
+        <v>1.23</v>
+      </c>
+      <c r="AF266">
+        <v>3.75</v>
+      </c>
+      <c r="AG266">
+        <v>1.7</v>
+      </c>
+      <c r="AH266">
+        <v>2.02</v>
+      </c>
+      <c r="AI266">
+        <v>1.7</v>
+      </c>
+      <c r="AJ266">
+        <v>2.05</v>
+      </c>
+      <c r="AK266">
+        <v>1.2</v>
+      </c>
+      <c r="AL266">
+        <v>1.25</v>
+      </c>
+      <c r="AM266">
+        <v>2.05</v>
+      </c>
+      <c r="AN266">
+        <v>1</v>
+      </c>
+      <c r="AO266">
+        <v>1</v>
+      </c>
+      <c r="AP266">
+        <v>1.25</v>
+      </c>
+      <c r="AQ266">
+        <v>0.89</v>
+      </c>
+      <c r="AR266">
+        <v>1.45</v>
+      </c>
+      <c r="AS266">
+        <v>1.65</v>
+      </c>
+      <c r="AT266">
+        <v>3.1</v>
+      </c>
+      <c r="AU266">
+        <v>9</v>
+      </c>
+      <c r="AV266">
+        <v>2</v>
+      </c>
+      <c r="AW266">
+        <v>14</v>
+      </c>
+      <c r="AX266">
+        <v>6</v>
+      </c>
+      <c r="AY266">
+        <v>23</v>
+      </c>
+      <c r="AZ266">
+        <v>8</v>
+      </c>
+      <c r="BA266">
+        <v>10</v>
+      </c>
+      <c r="BB266">
+        <v>2</v>
+      </c>
+      <c r="BC266">
+        <v>12</v>
+      </c>
+      <c r="BD266">
+        <v>1.52</v>
+      </c>
+      <c r="BE266">
+        <v>8.9</v>
+      </c>
+      <c r="BF266">
+        <v>3.1</v>
+      </c>
+      <c r="BG266">
+        <v>1.22</v>
+      </c>
+      <c r="BH266">
+        <v>3.48</v>
+      </c>
+      <c r="BI266">
+        <v>1.44</v>
+      </c>
+      <c r="BJ266">
+        <v>2.5</v>
+      </c>
+      <c r="BK266">
+        <v>1.83</v>
+      </c>
+      <c r="BL266">
+        <v>1.85</v>
+      </c>
+      <c r="BM266">
+        <v>2.28</v>
+      </c>
+      <c r="BN266">
+        <v>1.53</v>
+      </c>
+      <c r="BO266">
+        <v>3.04</v>
+      </c>
+      <c r="BP266">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="267" spans="1:68">
+      <c r="A267" s="1">
+        <v>266</v>
+      </c>
+      <c r="B267">
+        <v>7781342</v>
+      </c>
+      <c r="C267" t="s">
+        <v>68</v>
+      </c>
+      <c r="D267" t="s">
+        <v>69</v>
+      </c>
+      <c r="E267" s="2">
+        <v>45822.9375</v>
+      </c>
+      <c r="F267">
+        <v>0</v>
+      </c>
+      <c r="G267" t="s">
+        <v>93</v>
+      </c>
+      <c r="H267" t="s">
+        <v>76</v>
+      </c>
+      <c r="I267">
+        <v>0</v>
+      </c>
+      <c r="J267">
+        <v>1</v>
+      </c>
+      <c r="K267">
+        <v>1</v>
+      </c>
+      <c r="L267">
+        <v>0</v>
+      </c>
+      <c r="M267">
+        <v>1</v>
+      </c>
+      <c r="N267">
+        <v>1</v>
+      </c>
+      <c r="O267" t="s">
+        <v>109</v>
+      </c>
+      <c r="P267" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q267">
+        <v>3.4</v>
+      </c>
+      <c r="R267">
+        <v>2.38</v>
+      </c>
+      <c r="S267">
+        <v>2.75</v>
+      </c>
+      <c r="T267">
+        <v>1.29</v>
+      </c>
+      <c r="U267">
+        <v>3.5</v>
+      </c>
+      <c r="V267">
+        <v>2.38</v>
+      </c>
+      <c r="W267">
+        <v>1.53</v>
+      </c>
+      <c r="X267">
+        <v>5.5</v>
+      </c>
+      <c r="Y267">
+        <v>1.14</v>
+      </c>
+      <c r="Z267">
+        <v>2.74</v>
+      </c>
+      <c r="AA267">
+        <v>3.35</v>
+      </c>
+      <c r="AB267">
+        <v>2.19</v>
+      </c>
+      <c r="AC267">
+        <v>1.03</v>
+      </c>
+      <c r="AD267">
+        <v>12</v>
+      </c>
+      <c r="AE267">
+        <v>1.19</v>
+      </c>
+      <c r="AF267">
+        <v>4.2</v>
+      </c>
+      <c r="AG267">
+        <v>1.65</v>
+      </c>
+      <c r="AH267">
+        <v>2.1</v>
+      </c>
+      <c r="AI267">
+        <v>1.5</v>
+      </c>
+      <c r="AJ267">
+        <v>2.5</v>
+      </c>
+      <c r="AK267">
+        <v>1.6</v>
+      </c>
+      <c r="AL267">
+        <v>1.27</v>
+      </c>
+      <c r="AM267">
+        <v>1.41</v>
+      </c>
+      <c r="AN267">
+        <v>1.56</v>
+      </c>
+      <c r="AO267">
+        <v>1.25</v>
+      </c>
+      <c r="AP267">
+        <v>1.4</v>
+      </c>
+      <c r="AQ267">
+        <v>1.44</v>
+      </c>
+      <c r="AR267">
+        <v>1.57</v>
+      </c>
+      <c r="AS267">
+        <v>1.42</v>
+      </c>
+      <c r="AT267">
+        <v>2.99</v>
+      </c>
+      <c r="AU267">
+        <v>3</v>
+      </c>
+      <c r="AV267">
+        <v>5</v>
+      </c>
+      <c r="AW267">
+        <v>12</v>
+      </c>
+      <c r="AX267">
+        <v>3</v>
+      </c>
+      <c r="AY267">
+        <v>15</v>
+      </c>
+      <c r="AZ267">
+        <v>8</v>
+      </c>
+      <c r="BA267">
+        <v>9</v>
+      </c>
+      <c r="BB267">
+        <v>2</v>
+      </c>
+      <c r="BC267">
+        <v>11</v>
+      </c>
+      <c r="BD267">
+        <v>2.15</v>
+      </c>
+      <c r="BE267">
+        <v>6.4</v>
+      </c>
+      <c r="BF267">
+        <v>2.12</v>
+      </c>
+      <c r="BG267">
+        <v>1.25</v>
+      </c>
+      <c r="BH267">
+        <v>3.28</v>
+      </c>
+      <c r="BI267">
+        <v>1.5</v>
+      </c>
+      <c r="BJ267">
+        <v>2.35</v>
+      </c>
+      <c r="BK267">
+        <v>1.91</v>
+      </c>
+      <c r="BL267">
+        <v>1.8</v>
+      </c>
+      <c r="BM267">
+        <v>2.42</v>
+      </c>
+      <c r="BN267">
+        <v>1.47</v>
+      </c>
+      <c r="BO267">
+        <v>3.2</v>
+      </c>
+      <c r="BP267">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -835,13 +835,13 @@
     <t>['4502', '9008']</t>
   </si>
   <si>
-    <t>['6', '51']</t>
-  </si>
-  <si>
     <t>['38']</t>
   </si>
   <si>
     <t>['8', '9001']</t>
+  </si>
+  <si>
+    <t>['6', '51']</t>
   </si>
   <si>
     <t>['23', '77']</t>
@@ -1216,10 +1216,10 @@
     <t>['11', '59', '69', '82']</t>
   </si>
   <si>
-    <t>['56', '75']</t>
+    <t>['30', '32', '54']</t>
   </si>
   <si>
-    <t>['30', '32', '54']</t>
+    <t>['56', '75']</t>
   </si>
 </sst>
 </file>
@@ -54128,7 +54128,7 @@
         <v>69</v>
       </c>
       <c r="E256" s="2">
-        <v>45821.97916666666</v>
+        <v>45821.99652777778</v>
       </c>
       <c r="F256">
         <v>0</v>
@@ -54254,22 +54254,22 @@
         <v>3</v>
       </c>
       <c r="AU256">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AV256">
         <v>7</v>
       </c>
       <c r="AW256">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AX256">
+        <v>8</v>
+      </c>
+      <c r="AY256">
         <v>10</v>
       </c>
-      <c r="AY256">
+      <c r="AZ256">
         <v>15</v>
-      </c>
-      <c r="AZ256">
-        <v>17</v>
       </c>
       <c r="BA256">
         <v>8</v>
@@ -55149,7 +55149,7 @@
         <v>260</v>
       </c>
       <c r="B261">
-        <v>7781337</v>
+        <v>7781341</v>
       </c>
       <c r="C261" t="s">
         <v>68</v>
@@ -55164,190 +55164,190 @@
         <v>0</v>
       </c>
       <c r="G261" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="H261" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="I261">
         <v>1</v>
       </c>
       <c r="J261">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K261">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L261">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M261">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N261">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O261" t="s">
         <v>273</v>
       </c>
       <c r="P261" t="s">
-        <v>109</v>
+        <v>398</v>
       </c>
       <c r="Q261">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R261">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S261">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T261">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="U261">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V261">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="W261">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X261">
+        <v>0</v>
+      </c>
+      <c r="Y261">
+        <v>0</v>
+      </c>
+      <c r="Z261">
+        <v>1.96</v>
+      </c>
+      <c r="AA261">
+        <v>3.41</v>
+      </c>
+      <c r="AB261">
+        <v>3.16</v>
+      </c>
+      <c r="AC261">
+        <v>0</v>
+      </c>
+      <c r="AD261">
+        <v>0</v>
+      </c>
+      <c r="AE261">
+        <v>0</v>
+      </c>
+      <c r="AF261">
+        <v>0</v>
+      </c>
+      <c r="AG261">
+        <v>1.78</v>
+      </c>
+      <c r="AH261">
+        <v>1.92</v>
+      </c>
+      <c r="AI261">
+        <v>0</v>
+      </c>
+      <c r="AJ261">
+        <v>0</v>
+      </c>
+      <c r="AK261">
+        <v>0</v>
+      </c>
+      <c r="AL261">
+        <v>0</v>
+      </c>
+      <c r="AM261">
+        <v>0</v>
+      </c>
+      <c r="AN261">
+        <v>1.88</v>
+      </c>
+      <c r="AO261">
+        <v>1.29</v>
+      </c>
+      <c r="AP261">
+        <v>1.67</v>
+      </c>
+      <c r="AQ261">
+        <v>1.5</v>
+      </c>
+      <c r="AR261">
+        <v>1.82</v>
+      </c>
+      <c r="AS261">
+        <v>1.67</v>
+      </c>
+      <c r="AT261">
+        <v>3.49</v>
+      </c>
+      <c r="AU261">
+        <v>7</v>
+      </c>
+      <c r="AV261">
+        <v>8</v>
+      </c>
+      <c r="AW261">
+        <v>2</v>
+      </c>
+      <c r="AX261">
+        <v>5</v>
+      </c>
+      <c r="AY261">
         <v>9</v>
-      </c>
-      <c r="Y261">
-        <v>1.07</v>
-      </c>
-      <c r="Z261">
-        <v>2.15</v>
-      </c>
-      <c r="AA261">
-        <v>3.03</v>
-      </c>
-      <c r="AB261">
-        <v>3.08</v>
-      </c>
-      <c r="AC261">
-        <v>1.07</v>
-      </c>
-      <c r="AD261">
-        <v>7.75</v>
-      </c>
-      <c r="AE261">
-        <v>1.35</v>
-      </c>
-      <c r="AF261">
-        <v>2.9</v>
-      </c>
-      <c r="AG261">
-        <v>1.98</v>
-      </c>
-      <c r="AH261">
-        <v>1.73</v>
-      </c>
-      <c r="AI261">
-        <v>1.91</v>
-      </c>
-      <c r="AJ261">
-        <v>1.91</v>
-      </c>
-      <c r="AK261">
-        <v>1.31</v>
-      </c>
-      <c r="AL261">
-        <v>1.32</v>
-      </c>
-      <c r="AM261">
-        <v>1.65</v>
-      </c>
-      <c r="AN261">
-        <v>1.44</v>
-      </c>
-      <c r="AO261">
-        <v>0.63</v>
-      </c>
-      <c r="AP261">
-        <v>1.6</v>
-      </c>
-      <c r="AQ261">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AR261">
-        <v>1.67</v>
-      </c>
-      <c r="AS261">
-        <v>1.17</v>
-      </c>
-      <c r="AT261">
-        <v>2.84</v>
-      </c>
-      <c r="AU261">
-        <v>8</v>
-      </c>
-      <c r="AV261">
-        <v>9</v>
-      </c>
-      <c r="AW261">
-        <v>0</v>
-      </c>
-      <c r="AX261">
-        <v>4</v>
-      </c>
-      <c r="AY261">
-        <v>8</v>
       </c>
       <c r="AZ261">
         <v>13</v>
       </c>
       <c r="BA261">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB261">
+        <v>4</v>
+      </c>
+      <c r="BC261">
         <v>7</v>
       </c>
-      <c r="BC261">
-        <v>9</v>
-      </c>
       <c r="BD261">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BE261">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="BF261">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="BG261">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BH261">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BI261">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BJ261">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BK261">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BL261">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BM261">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BN261">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BO261">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="BP261">
-        <v>1.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262" spans="1:68">
@@ -55355,7 +55355,7 @@
         <v>261</v>
       </c>
       <c r="B262">
-        <v>7781341</v>
+        <v>7781340</v>
       </c>
       <c r="C262" t="s">
         <v>68</v>
@@ -55370,10 +55370,10 @@
         <v>0</v>
       </c>
       <c r="G262" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H262" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I262">
         <v>1</v>
@@ -55385,175 +55385,175 @@
         <v>2</v>
       </c>
       <c r="L262">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M262">
         <v>4</v>
       </c>
       <c r="N262">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O262" t="s">
         <v>274</v>
       </c>
       <c r="P262" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q262">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R262">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S262">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T262">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="U262">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V262">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="W262">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X262">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y262">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z262">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AA262">
         <v>3.41</v>
       </c>
       <c r="AB262">
-        <v>3.16</v>
+        <v>3.29</v>
       </c>
       <c r="AC262">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AD262">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AE262">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF262">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AG262">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AH262">
-        <v>1.92</v>
+        <v>2.19</v>
       </c>
       <c r="AI262">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AJ262">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK262">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL262">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AM262">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AN262">
-        <v>1.88</v>
+        <v>1.14</v>
       </c>
       <c r="AO262">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AP262">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AQ262">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AR262">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AS262">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AT262">
-        <v>3.49</v>
+        <v>2.99</v>
       </c>
       <c r="AU262">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV262">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AW262">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX262">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY262">
+        <v>10</v>
+      </c>
+      <c r="AZ262">
+        <v>11</v>
+      </c>
+      <c r="BA262">
+        <v>6</v>
+      </c>
+      <c r="BB262">
+        <v>3</v>
+      </c>
+      <c r="BC262">
         <v>9</v>
       </c>
-      <c r="AZ262">
-        <v>13</v>
-      </c>
-      <c r="BA262">
-        <v>3</v>
-      </c>
-      <c r="BB262">
-        <v>4</v>
-      </c>
-      <c r="BC262">
-        <v>7</v>
-      </c>
       <c r="BD262">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BE262">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BF262">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="BG262">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BH262">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BI262">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BJ262">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BK262">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BL262">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BM262">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BN262">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BO262">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BP262">
-        <v>0</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="263" spans="1:68">
@@ -55561,7 +55561,7 @@
         <v>262</v>
       </c>
       <c r="B263">
-        <v>7781340</v>
+        <v>7781339</v>
       </c>
       <c r="C263" t="s">
         <v>68</v>
@@ -55576,172 +55576,172 @@
         <v>0</v>
       </c>
       <c r="G263" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="H263" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I263">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J263">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K263">
         <v>2</v>
       </c>
       <c r="L263">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M263">
+        <v>3</v>
+      </c>
+      <c r="N263">
         <v>4</v>
       </c>
-      <c r="N263">
-        <v>6</v>
-      </c>
       <c r="O263" t="s">
-        <v>275</v>
+        <v>234</v>
       </c>
       <c r="P263" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q263">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="R263">
         <v>2.3</v>
       </c>
       <c r="S263">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T263">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="U263">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="V263">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="W263">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X263">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y263">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z263">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="AA263">
-        <v>3.41</v>
+        <v>3.64</v>
       </c>
       <c r="AB263">
-        <v>3.29</v>
+        <v>4.4</v>
       </c>
       <c r="AC263">
         <v>1.04</v>
       </c>
       <c r="AD263">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE263">
+        <v>1.25</v>
+      </c>
+      <c r="AF263">
+        <v>3.5</v>
+      </c>
+      <c r="AG263">
+        <v>1.78</v>
+      </c>
+      <c r="AH263">
+        <v>1.92</v>
+      </c>
+      <c r="AI263">
+        <v>1.8</v>
+      </c>
+      <c r="AJ263">
+        <v>1.95</v>
+      </c>
+      <c r="AK263">
+        <v>1.18</v>
+      </c>
+      <c r="AL263">
+        <v>1.25</v>
+      </c>
+      <c r="AM263">
+        <v>2.15</v>
+      </c>
+      <c r="AN263">
+        <v>1.11</v>
+      </c>
+      <c r="AO263">
+        <v>0.5</v>
+      </c>
+      <c r="AP263">
+        <v>1</v>
+      </c>
+      <c r="AQ263">
+        <v>0.73</v>
+      </c>
+      <c r="AR263">
+        <v>1.72</v>
+      </c>
+      <c r="AS263">
+        <v>1.36</v>
+      </c>
+      <c r="AT263">
+        <v>3.08</v>
+      </c>
+      <c r="AU263">
+        <v>4</v>
+      </c>
+      <c r="AV263">
+        <v>4</v>
+      </c>
+      <c r="AW263">
+        <v>8</v>
+      </c>
+      <c r="AX263">
+        <v>9</v>
+      </c>
+      <c r="AY263">
+        <v>12</v>
+      </c>
+      <c r="AZ263">
+        <v>13</v>
+      </c>
+      <c r="BA263">
+        <v>7</v>
+      </c>
+      <c r="BB263">
+        <v>7</v>
+      </c>
+      <c r="BC263">
+        <v>14</v>
+      </c>
+      <c r="BD263">
+        <v>1.56</v>
+      </c>
+      <c r="BE263">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF263">
+        <v>2.85</v>
+      </c>
+      <c r="BG263">
         <v>1.22</v>
       </c>
-      <c r="AF263">
-        <v>3.8</v>
-      </c>
-      <c r="AG263">
-        <v>1.6</v>
-      </c>
-      <c r="AH263">
-        <v>2.19</v>
-      </c>
-      <c r="AI263">
-        <v>1.62</v>
-      </c>
-      <c r="AJ263">
-        <v>2.2</v>
-      </c>
-      <c r="AK263">
-        <v>1.3</v>
-      </c>
-      <c r="AL263">
-        <v>1.28</v>
-      </c>
-      <c r="AM263">
-        <v>1.75</v>
-      </c>
-      <c r="AN263">
-        <v>1.14</v>
-      </c>
-      <c r="AO263">
-        <v>1.44</v>
-      </c>
-      <c r="AP263">
-        <v>1</v>
-      </c>
-      <c r="AQ263">
-        <v>1.6</v>
-      </c>
-      <c r="AR263">
-        <v>1.61</v>
-      </c>
-      <c r="AS263">
-        <v>1.38</v>
-      </c>
-      <c r="AT263">
-        <v>2.99</v>
-      </c>
-      <c r="AU263">
-        <v>6</v>
-      </c>
-      <c r="AV263">
-        <v>5</v>
-      </c>
-      <c r="AW263">
-        <v>4</v>
-      </c>
-      <c r="AX263">
-        <v>6</v>
-      </c>
-      <c r="AY263">
-        <v>10</v>
-      </c>
-      <c r="AZ263">
-        <v>11</v>
-      </c>
-      <c r="BA263">
-        <v>6</v>
-      </c>
-      <c r="BB263">
-        <v>3</v>
-      </c>
-      <c r="BC263">
-        <v>9</v>
-      </c>
-      <c r="BD263">
-        <v>1.51</v>
-      </c>
-      <c r="BE263">
-        <v>9</v>
-      </c>
-      <c r="BF263">
-        <v>3.12</v>
-      </c>
-      <c r="BG263">
-        <v>1.25</v>
-      </c>
       <c r="BH263">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="BI263">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="BJ263">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="BK263">
         <v>1.85</v>
@@ -55750,16 +55750,16 @@
         <v>1.85</v>
       </c>
       <c r="BM263">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="BN263">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="BO263">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="BP263">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="264" spans="1:68">
@@ -55809,7 +55809,7 @@
         <v>109</v>
       </c>
       <c r="P264" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q264">
         <v>2.75</v>
@@ -55973,7 +55973,7 @@
         <v>264</v>
       </c>
       <c r="B265">
-        <v>7781339</v>
+        <v>7781337</v>
       </c>
       <c r="C265" t="s">
         <v>68</v>
@@ -55988,190 +55988,190 @@
         <v>0</v>
       </c>
       <c r="G265" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H265" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="I265">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J265">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K265">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L265">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M265">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N265">
+        <v>2</v>
+      </c>
+      <c r="O265" t="s">
+        <v>275</v>
+      </c>
+      <c r="P265" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q265">
+        <v>2.88</v>
+      </c>
+      <c r="R265">
+        <v>2.1</v>
+      </c>
+      <c r="S265">
         <v>4</v>
       </c>
-      <c r="O265" t="s">
-        <v>234</v>
-      </c>
-      <c r="P265" t="s">
-        <v>401</v>
-      </c>
-      <c r="Q265">
-        <v>2.25</v>
-      </c>
-      <c r="R265">
-        <v>2.3</v>
-      </c>
-      <c r="S265">
-        <v>5</v>
-      </c>
       <c r="T265">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="U265">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="V265">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="W265">
+        <v>1.33</v>
+      </c>
+      <c r="X265">
+        <v>9</v>
+      </c>
+      <c r="Y265">
+        <v>1.07</v>
+      </c>
+      <c r="Z265">
+        <v>2.15</v>
+      </c>
+      <c r="AA265">
+        <v>3.03</v>
+      </c>
+      <c r="AB265">
+        <v>3.08</v>
+      </c>
+      <c r="AC265">
+        <v>1.07</v>
+      </c>
+      <c r="AD265">
+        <v>7.75</v>
+      </c>
+      <c r="AE265">
+        <v>1.35</v>
+      </c>
+      <c r="AF265">
+        <v>2.9</v>
+      </c>
+      <c r="AG265">
+        <v>1.98</v>
+      </c>
+      <c r="AH265">
+        <v>1.73</v>
+      </c>
+      <c r="AI265">
+        <v>1.91</v>
+      </c>
+      <c r="AJ265">
+        <v>1.91</v>
+      </c>
+      <c r="AK265">
+        <v>1.31</v>
+      </c>
+      <c r="AL265">
+        <v>1.32</v>
+      </c>
+      <c r="AM265">
+        <v>1.65</v>
+      </c>
+      <c r="AN265">
         <v>1.44</v>
       </c>
-      <c r="X265">
-        <v>7</v>
-      </c>
-      <c r="Y265">
-        <v>1.1</v>
-      </c>
-      <c r="Z265">
-        <v>1.62</v>
-      </c>
-      <c r="AA265">
-        <v>3.64</v>
-      </c>
-      <c r="AB265">
-        <v>4.4</v>
-      </c>
-      <c r="AC265">
-        <v>1.04</v>
-      </c>
-      <c r="AD265">
-        <v>10</v>
-      </c>
-      <c r="AE265">
-        <v>1.25</v>
-      </c>
-      <c r="AF265">
-        <v>3.5</v>
-      </c>
-      <c r="AG265">
-        <v>1.78</v>
-      </c>
-      <c r="AH265">
-        <v>1.92</v>
-      </c>
-      <c r="AI265">
-        <v>1.8</v>
-      </c>
-      <c r="AJ265">
-        <v>1.95</v>
-      </c>
-      <c r="AK265">
-        <v>1.18</v>
-      </c>
-      <c r="AL265">
-        <v>1.25</v>
-      </c>
-      <c r="AM265">
-        <v>2.15</v>
-      </c>
-      <c r="AN265">
-        <v>1.11</v>
-      </c>
       <c r="AO265">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AP265">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AQ265">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR265">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AS265">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AT265">
-        <v>3.08</v>
+        <v>2.84</v>
       </c>
       <c r="AU265">
+        <v>8</v>
+      </c>
+      <c r="AV265">
+        <v>9</v>
+      </c>
+      <c r="AW265">
+        <v>0</v>
+      </c>
+      <c r="AX265">
         <v>4</v>
       </c>
-      <c r="AV265">
-        <v>4</v>
-      </c>
-      <c r="AW265">
+      <c r="AY265">
         <v>8</v>
-      </c>
-      <c r="AX265">
-        <v>9</v>
-      </c>
-      <c r="AY265">
-        <v>12</v>
       </c>
       <c r="AZ265">
         <v>13</v>
       </c>
       <c r="BA265">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BB265">
         <v>7</v>
       </c>
       <c r="BC265">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BD265">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="BE265">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="BF265">
-        <v>2.85</v>
+        <v>2.49</v>
       </c>
       <c r="BG265">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BH265">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="BI265">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BJ265">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="BK265">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="BL265">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="BM265">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="BN265">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="BO265">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="BP265">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="266" spans="1:68">
@@ -56179,7 +56179,7 @@
         <v>265</v>
       </c>
       <c r="B266">
-        <v>7781343</v>
+        <v>7781342</v>
       </c>
       <c r="C266" t="s">
         <v>68</v>
@@ -56194,190 +56194,190 @@
         <v>0</v>
       </c>
       <c r="G266" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="H266" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I266">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J266">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K266">
         <v>1</v>
       </c>
       <c r="L266">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M266">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N266">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O266" t="s">
-        <v>276</v>
+        <v>109</v>
       </c>
       <c r="P266" t="s">
-        <v>109</v>
+        <v>351</v>
       </c>
       <c r="Q266">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="R266">
         <v>2.38</v>
       </c>
       <c r="S266">
-        <v>4.75</v>
+        <v>2.75</v>
       </c>
       <c r="T266">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="U266">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="V266">
+        <v>2.38</v>
+      </c>
+      <c r="W266">
+        <v>1.53</v>
+      </c>
+      <c r="X266">
+        <v>5.5</v>
+      </c>
+      <c r="Y266">
+        <v>1.14</v>
+      </c>
+      <c r="Z266">
+        <v>2.74</v>
+      </c>
+      <c r="AA266">
+        <v>3.35</v>
+      </c>
+      <c r="AB266">
+        <v>2.19</v>
+      </c>
+      <c r="AC266">
+        <v>1.03</v>
+      </c>
+      <c r="AD266">
+        <v>12</v>
+      </c>
+      <c r="AE266">
+        <v>1.19</v>
+      </c>
+      <c r="AF266">
+        <v>4.2</v>
+      </c>
+      <c r="AG266">
+        <v>1.65</v>
+      </c>
+      <c r="AH266">
+        <v>2.1</v>
+      </c>
+      <c r="AI266">
+        <v>1.5</v>
+      </c>
+      <c r="AJ266">
         <v>2.5</v>
       </c>
-      <c r="W266">
-        <v>1.5</v>
-      </c>
-      <c r="X266">
-        <v>6.5</v>
-      </c>
-      <c r="Y266">
-        <v>1.11</v>
-      </c>
-      <c r="Z266">
-        <v>1.66</v>
-      </c>
-      <c r="AA266">
-        <v>3.64</v>
-      </c>
-      <c r="AB266">
-        <v>4.1</v>
-      </c>
-      <c r="AC266">
-        <v>1.04</v>
-      </c>
-      <c r="AD266">
-        <v>10.5</v>
-      </c>
-      <c r="AE266">
-        <v>1.23</v>
-      </c>
-      <c r="AF266">
-        <v>3.75</v>
-      </c>
-      <c r="AG266">
-        <v>1.7</v>
-      </c>
-      <c r="AH266">
-        <v>2.02</v>
-      </c>
-      <c r="AI266">
-        <v>1.7</v>
-      </c>
-      <c r="AJ266">
-        <v>2.05</v>
-      </c>
       <c r="AK266">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AL266">
+        <v>1.27</v>
+      </c>
+      <c r="AM266">
+        <v>1.41</v>
+      </c>
+      <c r="AN266">
+        <v>1.56</v>
+      </c>
+      <c r="AO266">
         <v>1.25</v>
       </c>
-      <c r="AM266">
-        <v>2.05</v>
-      </c>
-      <c r="AN266">
-        <v>1</v>
-      </c>
-      <c r="AO266">
-        <v>1</v>
-      </c>
       <c r="AP266">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AQ266">
-        <v>0.89</v>
+        <v>1.44</v>
       </c>
       <c r="AR266">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AS266">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AT266">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AU266">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AV266">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AW266">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AX266">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY266">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AZ266">
         <v>8</v>
       </c>
       <c r="BA266">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB266">
         <v>2</v>
       </c>
       <c r="BC266">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD266">
-        <v>1.52</v>
+        <v>2.15</v>
       </c>
       <c r="BE266">
-        <v>8.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF266">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="BG266">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BH266">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="BI266">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BJ266">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="BK266">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="BL266">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="BM266">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="BN266">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="BO266">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="BP266">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="267" spans="1:68">
@@ -56385,7 +56385,7 @@
         <v>266</v>
       </c>
       <c r="B267">
-        <v>7781342</v>
+        <v>7781343</v>
       </c>
       <c r="C267" t="s">
         <v>68</v>
@@ -56400,190 +56400,190 @@
         <v>0</v>
       </c>
       <c r="G267" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="H267" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I267">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J267">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K267">
         <v>1</v>
       </c>
       <c r="L267">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M267">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N267">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O267" t="s">
+        <v>276</v>
+      </c>
+      <c r="P267" t="s">
         <v>109</v>
       </c>
-      <c r="P267" t="s">
-        <v>351</v>
-      </c>
       <c r="Q267">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="R267">
         <v>2.38</v>
       </c>
       <c r="S267">
-        <v>2.75</v>
+        <v>4.75</v>
       </c>
       <c r="T267">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="U267">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="V267">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="W267">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X267">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y267">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z267">
-        <v>2.74</v>
+        <v>1.66</v>
       </c>
       <c r="AA267">
-        <v>3.35</v>
+        <v>3.64</v>
       </c>
       <c r="AB267">
-        <v>2.19</v>
+        <v>4.1</v>
       </c>
       <c r="AC267">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AD267">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE267">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AF267">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="AG267">
+        <v>1.7</v>
+      </c>
+      <c r="AH267">
+        <v>2.02</v>
+      </c>
+      <c r="AI267">
+        <v>1.7</v>
+      </c>
+      <c r="AJ267">
+        <v>2.05</v>
+      </c>
+      <c r="AK267">
+        <v>1.2</v>
+      </c>
+      <c r="AL267">
+        <v>1.25</v>
+      </c>
+      <c r="AM267">
+        <v>2.05</v>
+      </c>
+      <c r="AN267">
+        <v>1</v>
+      </c>
+      <c r="AO267">
+        <v>1</v>
+      </c>
+      <c r="AP267">
+        <v>1.25</v>
+      </c>
+      <c r="AQ267">
+        <v>0.89</v>
+      </c>
+      <c r="AR267">
+        <v>1.45</v>
+      </c>
+      <c r="AS267">
         <v>1.65</v>
       </c>
-      <c r="AH267">
-        <v>2.1</v>
-      </c>
-      <c r="AI267">
-        <v>1.5</v>
-      </c>
-      <c r="AJ267">
-        <v>2.5</v>
-      </c>
-      <c r="AK267">
-        <v>1.6</v>
-      </c>
-      <c r="AL267">
-        <v>1.27</v>
-      </c>
-      <c r="AM267">
-        <v>1.41</v>
-      </c>
-      <c r="AN267">
-        <v>1.56</v>
-      </c>
-      <c r="AO267">
-        <v>1.25</v>
-      </c>
-      <c r="AP267">
-        <v>1.4</v>
-      </c>
-      <c r="AQ267">
-        <v>1.44</v>
-      </c>
-      <c r="AR267">
-        <v>1.57</v>
-      </c>
-      <c r="AS267">
-        <v>1.42</v>
-      </c>
       <c r="AT267">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AU267">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AV267">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW267">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX267">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY267">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AZ267">
         <v>8</v>
       </c>
       <c r="BA267">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB267">
         <v>2</v>
       </c>
       <c r="BC267">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD267">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="BE267">
-        <v>6.4</v>
+        <v>8.9</v>
       </c>
       <c r="BF267">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="BG267">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BH267">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="BI267">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BJ267">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="BK267">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BL267">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BM267">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="BN267">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="BO267">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="BP267">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -54254,22 +54254,22 @@
         <v>3</v>
       </c>
       <c r="AU256">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AV256">
         <v>7</v>
       </c>
       <c r="AW256">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX256">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY256">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AZ256">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA256">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="416">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -847,6 +847,36 @@
     <t>['23', '77']</t>
   </si>
   <si>
+    <t>['23', '32', '42']</t>
+  </si>
+  <si>
+    <t>['90']</t>
+  </si>
+  <si>
+    <t>['15', '49']</t>
+  </si>
+  <si>
+    <t>['51']</t>
+  </si>
+  <si>
+    <t>['60', '63', '70']</t>
+  </si>
+  <si>
+    <t>['40', '4503']</t>
+  </si>
+  <si>
+    <t>['9003', '9006']</t>
+  </si>
+  <si>
+    <t>['24', '28']</t>
+  </si>
+  <si>
+    <t>['30', '68']</t>
+  </si>
+  <si>
+    <t>['43', '66', '9006']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -872,9 +902,6 @@
   </si>
   <si>
     <t>['52', '90+3']</t>
-  </si>
-  <si>
-    <t>['51']</t>
   </si>
   <si>
     <t>['72', '86']</t>
@@ -977,9 +1004,6 @@
   </si>
   <si>
     <t>['1', '29']</t>
-  </si>
-  <si>
-    <t>['90']</t>
   </si>
   <si>
     <t>['28']</t>
@@ -1220,6 +1244,24 @@
   </si>
   <si>
     <t>['56', '75']</t>
+  </si>
+  <si>
+    <t>['45', '65', '83']</t>
+  </si>
+  <si>
+    <t>['4502', '51', '58']</t>
+  </si>
+  <si>
+    <t>['9004']</t>
+  </si>
+  <si>
+    <t>['7', '9', '22', '82']</t>
+  </si>
+  <si>
+    <t>['50', '57', '76', '9009']</t>
+  </si>
+  <si>
+    <t>['35', '37', '44', '47', '90']</t>
   </si>
 </sst>
 </file>
@@ -1581,7 +1623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP267"/>
+  <dimension ref="A1:BP278"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2043,7 +2085,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -2249,7 +2291,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2536,7 +2578,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ5">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2661,7 +2703,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2739,7 +2781,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ6">
         <v>1.8</v>
@@ -2867,7 +2909,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3073,7 +3115,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -3154,7 +3196,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ8">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3485,7 +3527,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -3975,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ12">
         <v>1</v>
@@ -4309,7 +4351,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -4390,7 +4432,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ14">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4515,7 +4557,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4721,7 +4763,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4802,7 +4844,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ16">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5008,7 +5050,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ17">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5339,7 +5381,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -5417,7 +5459,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ19">
         <v>1.5</v>
@@ -5626,7 +5668,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ20">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5751,7 +5793,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -6038,7 +6080,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ22">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6163,7 +6205,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6241,7 +6283,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ23">
         <v>0.89</v>
@@ -6369,7 +6411,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6447,10 +6489,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ24">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6653,7 +6695,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ25">
         <v>0.73</v>
@@ -6781,7 +6823,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6859,7 +6901,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ26">
         <v>1.6</v>
@@ -7683,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR30">
         <v>0</v>
@@ -7811,7 +7853,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -8095,10 +8137,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ32">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR32">
         <v>1.83</v>
@@ -8223,7 +8265,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -8510,7 +8552,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ34">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR34">
         <v>1.85</v>
@@ -9047,7 +9089,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9125,10 +9167,10 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ37">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR37">
         <v>0.85</v>
@@ -9334,7 +9376,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ38">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR38">
         <v>0</v>
@@ -9665,7 +9707,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9743,7 +9785,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ40">
         <v>1.8</v>
@@ -10077,7 +10119,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -10158,7 +10200,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ42">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR42">
         <v>1.41</v>
@@ -10361,7 +10403,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ43">
         <v>0.73</v>
@@ -10776,7 +10818,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ45">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR45">
         <v>1.62</v>
@@ -10901,7 +10943,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -11107,7 +11149,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -11185,7 +11227,7 @@
         <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ47">
         <v>1.8</v>
@@ -11313,7 +11355,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11394,7 +11436,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ48">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR48">
         <v>1.51</v>
@@ -11806,7 +11848,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ50">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR50">
         <v>1.3</v>
@@ -12137,7 +12179,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12343,7 +12385,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12421,7 +12463,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ53">
         <v>1.67</v>
@@ -12627,7 +12669,7 @@
         <v>3</v>
       </c>
       <c r="AP54">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ54">
         <v>1.88</v>
@@ -12755,7 +12797,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -13039,7 +13081,7 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ56">
         <v>0.9</v>
@@ -13373,7 +13415,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13579,7 +13621,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13660,7 +13702,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ59">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR59">
         <v>1.65</v>
@@ -13866,7 +13908,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ60">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR60">
         <v>0.9399999999999999</v>
@@ -13991,7 +14033,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14197,7 +14239,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -14278,7 +14320,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ62">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR62">
         <v>1.6</v>
@@ -14403,7 +14445,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14481,10 +14523,10 @@
         <v>0.5</v>
       </c>
       <c r="AP63">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ63">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR63">
         <v>1.42</v>
@@ -14609,7 +14651,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -14690,7 +14732,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ64">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR64">
         <v>1.62</v>
@@ -14893,7 +14935,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ65">
         <v>0.88</v>
@@ -15639,7 +15681,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15717,7 +15759,7 @@
         <v>0</v>
       </c>
       <c r="AP69">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ69">
         <v>0.88</v>
@@ -16051,7 +16093,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16129,7 +16171,7 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ71">
         <v>1.38</v>
@@ -16257,7 +16299,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16544,7 +16586,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ73">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR73">
         <v>2.23</v>
@@ -16669,7 +16711,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16747,7 +16789,7 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ74">
         <v>1.8</v>
@@ -16956,7 +16998,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ75">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR75">
         <v>1.74</v>
@@ -17081,7 +17123,7 @@
         <v>153</v>
       </c>
       <c r="P76" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="Q76">
         <v>3.6</v>
@@ -17159,10 +17201,10 @@
         <v>0.5</v>
       </c>
       <c r="AP76">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ76">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR76">
         <v>0.97</v>
@@ -17365,7 +17407,7 @@
         <v>3</v>
       </c>
       <c r="AP77">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ77">
         <v>1.88</v>
@@ -17571,10 +17613,10 @@
         <v>0.5</v>
       </c>
       <c r="AP78">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ78">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR78">
         <v>1.49</v>
@@ -17780,7 +17822,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ79">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR79">
         <v>1.15</v>
@@ -17905,7 +17947,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18111,7 +18153,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18317,7 +18359,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -18395,7 +18437,7 @@
         <v>0.2</v>
       </c>
       <c r="AP82">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ82">
         <v>0.73</v>
@@ -18601,7 +18643,7 @@
         <v>0</v>
       </c>
       <c r="AP83">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ83">
         <v>0.8</v>
@@ -18807,7 +18849,7 @@
         <v>1.5</v>
       </c>
       <c r="AP84">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ84">
         <v>0.8</v>
@@ -18935,7 +18977,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -19016,7 +19058,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ85">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR85">
         <v>1.87</v>
@@ -19141,7 +19183,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -19222,7 +19264,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ86">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR86">
         <v>1.7</v>
@@ -19347,7 +19389,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -19837,7 +19879,7 @@
         <v>1.5</v>
       </c>
       <c r="AP89">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ89">
         <v>1.11</v>
@@ -19965,7 +20007,7 @@
         <v>164</v>
       </c>
       <c r="P90" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
@@ -20046,7 +20088,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ90">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR90">
         <v>1.08</v>
@@ -20252,7 +20294,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ91">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR91">
         <v>1.64</v>
@@ -20458,7 +20500,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ92">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR92">
         <v>1.35</v>
@@ -20870,7 +20912,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ94">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR94">
         <v>1.73</v>
@@ -21201,7 +21243,7 @@
         <v>168</v>
       </c>
       <c r="P96" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21279,7 +21321,7 @@
         <v>0.33</v>
       </c>
       <c r="AP96">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ96">
         <v>0.73</v>
@@ -21897,7 +21939,7 @@
         <v>1.33</v>
       </c>
       <c r="AP99">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ99">
         <v>0.5600000000000001</v>
@@ -22309,7 +22351,7 @@
         <v>2.33</v>
       </c>
       <c r="AP101">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ101">
         <v>1</v>
@@ -22643,7 +22685,7 @@
         <v>122</v>
       </c>
       <c r="P103" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="Q103">
         <v>2.75</v>
@@ -22849,7 +22891,7 @@
         <v>173</v>
       </c>
       <c r="P104" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="Q104">
         <v>2.75</v>
@@ -23055,7 +23097,7 @@
         <v>174</v>
       </c>
       <c r="P105" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="Q105">
         <v>1.91</v>
@@ -23339,7 +23381,7 @@
         <v>1.75</v>
       </c>
       <c r="AP106">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ106">
         <v>1.67</v>
@@ -23754,7 +23796,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ108">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR108">
         <v>1.87</v>
@@ -23957,10 +23999,10 @@
         <v>0.33</v>
       </c>
       <c r="AP109">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AQ109">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR109">
         <v>0</v>
@@ -24085,7 +24127,7 @@
         <v>175</v>
       </c>
       <c r="P110" t="s">
-        <v>321</v>
+        <v>278</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -24163,7 +24205,7 @@
         <v>2</v>
       </c>
       <c r="AP110">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ110">
         <v>1.11</v>
@@ -24291,7 +24333,7 @@
         <v>109</v>
       </c>
       <c r="P111" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="Q111">
         <v>2.88</v>
@@ -24372,7 +24414,7 @@
         <v>1</v>
       </c>
       <c r="AQ111">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR111">
         <v>1.53</v>
@@ -24578,7 +24620,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ112">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR112">
         <v>1.95</v>
@@ -24781,7 +24823,7 @@
         <v>0.25</v>
       </c>
       <c r="AP113">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ113">
         <v>0.9</v>
@@ -24909,7 +24951,7 @@
         <v>177</v>
       </c>
       <c r="P114" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25115,7 +25157,7 @@
         <v>178</v>
       </c>
       <c r="P115" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -25193,10 +25235,10 @@
         <v>2</v>
       </c>
       <c r="AP115">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ115">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR115">
         <v>1.76</v>
@@ -25402,7 +25444,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ116">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR116">
         <v>1.62</v>
@@ -25527,7 +25569,7 @@
         <v>179</v>
       </c>
       <c r="P117" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25608,7 +25650,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ117">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR117">
         <v>1.48</v>
@@ -25733,7 +25775,7 @@
         <v>180</v>
       </c>
       <c r="P118" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25811,7 +25853,7 @@
         <v>1.33</v>
       </c>
       <c r="AP118">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ118">
         <v>1.38</v>
@@ -26017,7 +26059,7 @@
         <v>3</v>
       </c>
       <c r="AP119">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ119">
         <v>1.71</v>
@@ -26145,7 +26187,7 @@
         <v>181</v>
       </c>
       <c r="P120" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -26223,7 +26265,7 @@
         <v>2.33</v>
       </c>
       <c r="AP120">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ120">
         <v>1.5</v>
@@ -26432,7 +26474,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ121">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR121">
         <v>1.5</v>
@@ -26557,7 +26599,7 @@
         <v>109</v>
       </c>
       <c r="P122" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="Q122">
         <v>2.75</v>
@@ -26635,7 +26677,7 @@
         <v>2.33</v>
       </c>
       <c r="AP122">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ122">
         <v>1.71</v>
@@ -26844,7 +26886,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ123">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR123">
         <v>1.96</v>
@@ -26969,7 +27011,7 @@
         <v>129</v>
       </c>
       <c r="P124" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="Q124">
         <v>2.5</v>
@@ -27256,7 +27298,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ125">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR125">
         <v>1.84</v>
@@ -27459,10 +27501,10 @@
         <v>1.25</v>
       </c>
       <c r="AP126">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AQ126">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR126">
         <v>1.94</v>
@@ -27665,7 +27707,7 @@
         <v>0.5</v>
       </c>
       <c r="AP127">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ127">
         <v>0.88</v>
@@ -27874,7 +27916,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ128">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR128">
         <v>1.53</v>
@@ -27999,7 +28041,7 @@
         <v>187</v>
       </c>
       <c r="P129" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28077,10 +28119,10 @@
         <v>1.5</v>
       </c>
       <c r="AP129">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ129">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR129">
         <v>1.29</v>
@@ -28205,7 +28247,7 @@
         <v>188</v>
       </c>
       <c r="P130" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="Q130">
         <v>2.4</v>
@@ -28489,7 +28531,7 @@
         <v>2</v>
       </c>
       <c r="AP131">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ131">
         <v>1.6</v>
@@ -28695,7 +28737,7 @@
         <v>2.33</v>
       </c>
       <c r="AP132">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ132">
         <v>1.88</v>
@@ -29029,7 +29071,7 @@
         <v>189</v>
       </c>
       <c r="P134" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="Q134">
         <v>3</v>
@@ -29235,7 +29277,7 @@
         <v>190</v>
       </c>
       <c r="P135" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -29725,7 +29767,7 @@
         <v>0.4</v>
       </c>
       <c r="AP137">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ137">
         <v>0.88</v>
@@ -30346,7 +30388,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ140">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR140">
         <v>1.89</v>
@@ -30471,7 +30513,7 @@
         <v>109</v>
       </c>
       <c r="P141" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="Q141">
         <v>2.38</v>
@@ -30755,10 +30797,10 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ142">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR142">
         <v>1.65</v>
@@ -30883,7 +30925,7 @@
         <v>174</v>
       </c>
       <c r="P143" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -31295,7 +31337,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="Q145">
         <v>2.4</v>
@@ -31501,7 +31543,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31579,7 +31621,7 @@
         <v>0.8</v>
       </c>
       <c r="AP146">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ146">
         <v>0.9</v>
@@ -31707,7 +31749,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="Q147">
         <v>2.6</v>
@@ -31785,7 +31827,7 @@
         <v>2</v>
       </c>
       <c r="AP147">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ147">
         <v>1.88</v>
@@ -31913,7 +31955,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="Q148">
         <v>2.05</v>
@@ -32119,7 +32161,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -32325,7 +32367,7 @@
         <v>202</v>
       </c>
       <c r="P150" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="Q150">
         <v>2.4</v>
@@ -32531,7 +32573,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="Q151">
         <v>2.63</v>
@@ -32612,7 +32654,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ151">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR151">
         <v>1.66</v>
@@ -32737,7 +32779,7 @@
         <v>109</v>
       </c>
       <c r="P152" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="Q152">
         <v>2.88</v>
@@ -32815,7 +32857,7 @@
         <v>1.4</v>
       </c>
       <c r="AP152">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ152">
         <v>1.6</v>
@@ -32943,7 +32985,7 @@
         <v>204</v>
       </c>
       <c r="P153" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -33024,7 +33066,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ153">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR153">
         <v>1.52</v>
@@ -33149,7 +33191,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="Q154">
         <v>3.1</v>
@@ -33227,10 +33269,10 @@
         <v>1.5</v>
       </c>
       <c r="AP154">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AQ154">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR154">
         <v>2.06</v>
@@ -33355,7 +33397,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="Q155">
         <v>2.2</v>
@@ -33433,10 +33475,10 @@
         <v>1</v>
       </c>
       <c r="AP155">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ155">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR155">
         <v>1.65</v>
@@ -33561,7 +33603,7 @@
         <v>207</v>
       </c>
       <c r="P156" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33767,7 +33809,7 @@
         <v>109</v>
       </c>
       <c r="P157" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="Q157">
         <v>3.2</v>
@@ -34051,10 +34093,10 @@
         <v>1.2</v>
       </c>
       <c r="AP158">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ158">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR158">
         <v>1.51</v>
@@ -34385,7 +34427,7 @@
         <v>209</v>
       </c>
       <c r="P160" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="Q160">
         <v>2.1</v>
@@ -34463,7 +34505,7 @@
         <v>1.2</v>
       </c>
       <c r="AP160">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ160">
         <v>0.8</v>
@@ -34672,7 +34714,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ161">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR161">
         <v>1.68</v>
@@ -34797,7 +34839,7 @@
         <v>211</v>
       </c>
       <c r="P162" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="Q162">
         <v>2.5</v>
@@ -35290,7 +35332,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ164">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR164">
         <v>1.81</v>
@@ -35493,10 +35535,10 @@
         <v>0.4</v>
       </c>
       <c r="AP165">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ165">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR165">
         <v>1.6</v>
@@ -35699,10 +35741,10 @@
         <v>0.25</v>
       </c>
       <c r="AP166">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ166">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR166">
         <v>1.6</v>
@@ -35827,7 +35869,7 @@
         <v>215</v>
       </c>
       <c r="P167" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35905,7 +35947,7 @@
         <v>2.5</v>
       </c>
       <c r="AP167">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ167">
         <v>1.71</v>
@@ -36111,7 +36153,7 @@
         <v>0.8</v>
       </c>
       <c r="AP168">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ168">
         <v>0.89</v>
@@ -36239,7 +36281,7 @@
         <v>217</v>
       </c>
       <c r="P169" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="Q169">
         <v>3</v>
@@ -36445,7 +36487,7 @@
         <v>218</v>
       </c>
       <c r="P170" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36651,7 +36693,7 @@
         <v>109</v>
       </c>
       <c r="P171" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="Q171">
         <v>2.25</v>
@@ -36857,7 +36899,7 @@
         <v>219</v>
       </c>
       <c r="P172" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="Q172">
         <v>2.4</v>
@@ -37144,7 +37186,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ173">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR173">
         <v>1.49</v>
@@ -37269,7 +37311,7 @@
         <v>221</v>
       </c>
       <c r="P174" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="Q174">
         <v>2.5</v>
@@ -37347,7 +37389,7 @@
         <v>1</v>
       </c>
       <c r="AP174">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ174">
         <v>0.8</v>
@@ -37475,7 +37517,7 @@
         <v>163</v>
       </c>
       <c r="P175" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -37681,7 +37723,7 @@
         <v>113</v>
       </c>
       <c r="P176" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="Q176">
         <v>2.4</v>
@@ -37762,7 +37804,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ176">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR176">
         <v>1.93</v>
@@ -37887,7 +37929,7 @@
         <v>222</v>
       </c>
       <c r="P177" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -37965,10 +38007,10 @@
         <v>1.2</v>
       </c>
       <c r="AP177">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ177">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR177">
         <v>1.66</v>
@@ -38093,7 +38135,7 @@
         <v>109</v>
       </c>
       <c r="P178" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="Q178">
         <v>2.38</v>
@@ -38171,10 +38213,10 @@
         <v>0.75</v>
       </c>
       <c r="AP178">
+        <v>1.55</v>
+      </c>
+      <c r="AQ178">
         <v>1.4</v>
-      </c>
-      <c r="AQ178">
-        <v>1.22</v>
       </c>
       <c r="AR178">
         <v>1.84</v>
@@ -38505,7 +38547,7 @@
         <v>224</v>
       </c>
       <c r="P180" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38583,7 +38625,7 @@
         <v>0.8</v>
       </c>
       <c r="AP180">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ180">
         <v>0.88</v>
@@ -38917,7 +38959,7 @@
         <v>225</v>
       </c>
       <c r="P182" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Q182">
         <v>3.75</v>
@@ -38995,7 +39037,7 @@
         <v>2.2</v>
       </c>
       <c r="AP182">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AQ182">
         <v>1.5</v>
@@ -39123,7 +39165,7 @@
         <v>226</v>
       </c>
       <c r="P183" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="Q183">
         <v>2.5</v>
@@ -39204,7 +39246,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ183">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR183">
         <v>1.98</v>
@@ -39329,7 +39371,7 @@
         <v>227</v>
       </c>
       <c r="P184" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="Q184">
         <v>2.05</v>
@@ -39410,7 +39452,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ184">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR184">
         <v>1.71</v>
@@ -39613,10 +39655,10 @@
         <v>1.5</v>
       </c>
       <c r="AP185">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ185">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR185">
         <v>1.44</v>
@@ -39741,7 +39783,7 @@
         <v>228</v>
       </c>
       <c r="P186" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="Q186">
         <v>2.4</v>
@@ -39822,7 +39864,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ186">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR186">
         <v>1.92</v>
@@ -40153,7 +40195,7 @@
         <v>230</v>
       </c>
       <c r="P188" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40231,7 +40273,7 @@
         <v>0.5</v>
       </c>
       <c r="AP188">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ188">
         <v>0.8</v>
@@ -40359,7 +40401,7 @@
         <v>176</v>
       </c>
       <c r="P189" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40440,7 +40482,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ189">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR189">
         <v>1.57</v>
@@ -41183,7 +41225,7 @@
         <v>233</v>
       </c>
       <c r="P193" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41389,7 +41431,7 @@
         <v>234</v>
       </c>
       <c r="P194" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41467,7 +41509,7 @@
         <v>0.83</v>
       </c>
       <c r="AP194">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AQ194">
         <v>1.14</v>
@@ -41676,7 +41718,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ195">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR195">
         <v>1.77</v>
@@ -41801,7 +41843,7 @@
         <v>198</v>
       </c>
       <c r="P196" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Q196">
         <v>2.63</v>
@@ -41879,10 +41921,10 @@
         <v>1.71</v>
       </c>
       <c r="AP196">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ196">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR196">
         <v>1.74</v>
@@ -42007,7 +42049,7 @@
         <v>109</v>
       </c>
       <c r="P197" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="Q197">
         <v>2.75</v>
@@ -42088,7 +42130,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ197">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR197">
         <v>1.53</v>
@@ -42213,7 +42255,7 @@
         <v>103</v>
       </c>
       <c r="P198" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="Q198">
         <v>2.63</v>
@@ -42497,10 +42539,10 @@
         <v>1.2</v>
       </c>
       <c r="AP199">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ199">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR199">
         <v>1.32</v>
@@ -42703,7 +42745,7 @@
         <v>0.83</v>
       </c>
       <c r="AP200">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ200">
         <v>0.5600000000000001</v>
@@ -43243,7 +43285,7 @@
         <v>109</v>
       </c>
       <c r="P203" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="Q203">
         <v>2.63</v>
@@ -43321,10 +43363,10 @@
         <v>0.6</v>
       </c>
       <c r="AP203">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ203">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR203">
         <v>1.04</v>
@@ -43527,7 +43569,7 @@
         <v>1</v>
       </c>
       <c r="AP204">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ204">
         <v>0.8</v>
@@ -43655,7 +43697,7 @@
         <v>237</v>
       </c>
       <c r="P205" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -44067,7 +44109,7 @@
         <v>109</v>
       </c>
       <c r="P207" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="Q207">
         <v>2.25</v>
@@ -44148,7 +44190,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ207">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR207">
         <v>1.4</v>
@@ -44766,7 +44808,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ210">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR210">
         <v>1.8</v>
@@ -44891,7 +44933,7 @@
         <v>240</v>
       </c>
       <c r="P211" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="Q211">
         <v>3.2</v>
@@ -45097,7 +45139,7 @@
         <v>109</v>
       </c>
       <c r="P212" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45178,7 +45220,7 @@
         <v>1</v>
       </c>
       <c r="AQ212">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR212">
         <v>1.33</v>
@@ -45303,7 +45345,7 @@
         <v>241</v>
       </c>
       <c r="P213" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="Q213">
         <v>4</v>
@@ -45381,7 +45423,7 @@
         <v>0.86</v>
       </c>
       <c r="AP213">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AQ213">
         <v>0.88</v>
@@ -45715,7 +45757,7 @@
         <v>242</v>
       </c>
       <c r="P215" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -45921,7 +45963,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="Q216">
         <v>3.4</v>
@@ -45999,10 +46041,10 @@
         <v>0.8</v>
       </c>
       <c r="AP216">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ216">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR216">
         <v>1.44</v>
@@ -46127,7 +46169,7 @@
         <v>243</v>
       </c>
       <c r="P217" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="Q217">
         <v>2.75</v>
@@ -46205,7 +46247,7 @@
         <v>1.57</v>
       </c>
       <c r="AP217">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ217">
         <v>1.6</v>
@@ -46411,7 +46453,7 @@
         <v>1</v>
       </c>
       <c r="AP218">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ218">
         <v>1.11</v>
@@ -46539,7 +46581,7 @@
         <v>244</v>
       </c>
       <c r="P219" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="Q219">
         <v>3.1</v>
@@ -46823,7 +46865,7 @@
         <v>0.71</v>
       </c>
       <c r="AP220">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ220">
         <v>0.5600000000000001</v>
@@ -46951,7 +46993,7 @@
         <v>246</v>
       </c>
       <c r="P221" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="Q221">
         <v>2.6</v>
@@ -47032,7 +47074,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ221">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR221">
         <v>2.04</v>
@@ -47157,7 +47199,7 @@
         <v>247</v>
       </c>
       <c r="P222" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="Q222">
         <v>2.5</v>
@@ -47363,7 +47405,7 @@
         <v>248</v>
       </c>
       <c r="P223" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47444,7 +47486,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ223">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR223">
         <v>1.57</v>
@@ -47569,7 +47611,7 @@
         <v>249</v>
       </c>
       <c r="P224" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47650,7 +47692,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ224">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR224">
         <v>1.56</v>
@@ -47775,7 +47817,7 @@
         <v>250</v>
       </c>
       <c r="P225" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -47981,7 +48023,7 @@
         <v>251</v>
       </c>
       <c r="P226" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="Q226">
         <v>2.75</v>
@@ -48187,7 +48229,7 @@
         <v>252</v>
       </c>
       <c r="P227" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="Q227">
         <v>1.83</v>
@@ -48393,7 +48435,7 @@
         <v>253</v>
       </c>
       <c r="P228" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48474,7 +48516,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ228">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR228">
         <v>1.63</v>
@@ -48599,7 +48641,7 @@
         <v>109</v>
       </c>
       <c r="P229" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="Q229">
         <v>2.5</v>
@@ -48680,7 +48722,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ229">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR229">
         <v>1.83</v>
@@ -48805,7 +48847,7 @@
         <v>254</v>
       </c>
       <c r="P230" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="Q230">
         <v>3.25</v>
@@ -48883,10 +48925,10 @@
         <v>2</v>
       </c>
       <c r="AP230">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ230">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR230">
         <v>1.42</v>
@@ -49011,7 +49053,7 @@
         <v>119</v>
       </c>
       <c r="P231" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="Q231">
         <v>2.4</v>
@@ -49089,10 +49131,10 @@
         <v>1.17</v>
       </c>
       <c r="AP231">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ231">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR231">
         <v>1.85</v>
@@ -49298,7 +49340,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ232">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AR232">
         <v>1.98</v>
@@ -49629,7 +49671,7 @@
         <v>109</v>
       </c>
       <c r="P234" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="Q234">
         <v>2.5</v>
@@ -49710,7 +49752,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ234">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR234">
         <v>1.45</v>
@@ -50119,7 +50161,7 @@
         <v>1.57</v>
       </c>
       <c r="AP236">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ236">
         <v>1.67</v>
@@ -50247,7 +50289,7 @@
         <v>258</v>
       </c>
       <c r="P237" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="Q237">
         <v>2.75</v>
@@ -50325,10 +50367,10 @@
         <v>1.43</v>
       </c>
       <c r="AP237">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ237">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR237">
         <v>1.68</v>
@@ -50453,7 +50495,7 @@
         <v>259</v>
       </c>
       <c r="P238" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="Q238">
         <v>2.6</v>
@@ -50659,7 +50701,7 @@
         <v>109</v>
       </c>
       <c r="P239" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -50737,10 +50779,10 @@
         <v>0.5</v>
       </c>
       <c r="AP239">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AQ239">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR239">
         <v>1.42</v>
@@ -50865,7 +50907,7 @@
         <v>140</v>
       </c>
       <c r="P240" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -51277,7 +51319,7 @@
         <v>109</v>
       </c>
       <c r="P242" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="Q242">
         <v>3.1</v>
@@ -51355,7 +51397,7 @@
         <v>1.44</v>
       </c>
       <c r="AP242">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AQ242">
         <v>1.6</v>
@@ -51564,7 +51606,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ243">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR243">
         <v>1.63</v>
@@ -51689,7 +51731,7 @@
         <v>161</v>
       </c>
       <c r="P244" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="Q244">
         <v>2.1</v>
@@ -51973,10 +52015,10 @@
         <v>2.14</v>
       </c>
       <c r="AP245">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ245">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR245">
         <v>1.17</v>
@@ -52101,7 +52143,7 @@
         <v>156</v>
       </c>
       <c r="P246" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="Q246">
         <v>2.5</v>
@@ -52719,7 +52761,7 @@
         <v>176</v>
       </c>
       <c r="P249" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="Q249">
         <v>2.5</v>
@@ -52925,7 +52967,7 @@
         <v>264</v>
       </c>
       <c r="P250" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="Q250">
         <v>3.2</v>
@@ -53131,7 +53173,7 @@
         <v>109</v>
       </c>
       <c r="P251" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Q251">
         <v>2.75</v>
@@ -53209,7 +53251,7 @@
         <v>0.88</v>
       </c>
       <c r="AP251">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ251">
         <v>1.11</v>
@@ -53337,7 +53379,7 @@
         <v>265</v>
       </c>
       <c r="P252" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="Q252">
         <v>2.25</v>
@@ -53621,7 +53663,7 @@
         <v>1</v>
       </c>
       <c r="AP253">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ253">
         <v>0.9</v>
@@ -54036,7 +54078,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ255">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR255">
         <v>1.83</v>
@@ -54242,7 +54284,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ256">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR256">
         <v>1.24</v>
@@ -54367,7 +54409,7 @@
         <v>270</v>
       </c>
       <c r="P257" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="Q257">
         <v>2.63</v>
@@ -54445,10 +54487,10 @@
         <v>0.22</v>
       </c>
       <c r="AP257">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ257">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AR257">
         <v>1.68</v>
@@ -54573,7 +54615,7 @@
         <v>271</v>
       </c>
       <c r="P258" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Q258">
         <v>2.3</v>
@@ -54651,7 +54693,7 @@
         <v>2.14</v>
       </c>
       <c r="AP258">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ258">
         <v>1.88</v>
@@ -54779,7 +54821,7 @@
         <v>109</v>
       </c>
       <c r="P259" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="Q259">
         <v>3.1</v>
@@ -54857,10 +54899,10 @@
         <v>1.44</v>
       </c>
       <c r="AP259">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ259">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR259">
         <v>1.33</v>
@@ -55066,7 +55108,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ260">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR260">
         <v>1.87</v>
@@ -55191,7 +55233,7 @@
         <v>273</v>
       </c>
       <c r="P261" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -55269,10 +55311,10 @@
         <v>1.29</v>
       </c>
       <c r="AP261">
+        <v>1.8</v>
+      </c>
+      <c r="AQ261">
         <v>1.67</v>
-      </c>
-      <c r="AQ261">
-        <v>1.5</v>
       </c>
       <c r="AR261">
         <v>1.82</v>
@@ -55397,7 +55439,7 @@
         <v>274</v>
       </c>
       <c r="P262" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="Q262">
         <v>2.5</v>
@@ -55475,7 +55517,7 @@
         <v>1.44</v>
       </c>
       <c r="AP262">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ262">
         <v>1.6</v>
@@ -55603,7 +55645,7 @@
         <v>234</v>
       </c>
       <c r="P263" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="Q263">
         <v>2.25</v>
@@ -55809,7 +55851,7 @@
         <v>109</v>
       </c>
       <c r="P264" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="Q264">
         <v>2.75</v>
@@ -55887,10 +55929,10 @@
         <v>1.43</v>
       </c>
       <c r="AP264">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ264">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR264">
         <v>1.64</v>
@@ -56096,7 +56138,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ265">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR265">
         <v>1.67</v>
@@ -56221,7 +56263,7 @@
         <v>109</v>
       </c>
       <c r="P266" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="Q266">
         <v>3.4</v>
@@ -56299,10 +56341,10 @@
         <v>1.25</v>
       </c>
       <c r="AP266">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ266">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR266">
         <v>1.57</v>
@@ -56584,6 +56626,2272 @@
       </c>
       <c r="BP267">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="268" spans="1:68">
+      <c r="A268" s="1">
+        <v>267</v>
+      </c>
+      <c r="B268">
+        <v>7781344</v>
+      </c>
+      <c r="C268" t="s">
+        <v>68</v>
+      </c>
+      <c r="D268" t="s">
+        <v>69</v>
+      </c>
+      <c r="E268" s="2">
+        <v>45833.85416666666</v>
+      </c>
+      <c r="F268">
+        <v>0</v>
+      </c>
+      <c r="G268" t="s">
+        <v>74</v>
+      </c>
+      <c r="H268" t="s">
+        <v>72</v>
+      </c>
+      <c r="I268">
+        <v>3</v>
+      </c>
+      <c r="J268">
+        <v>0</v>
+      </c>
+      <c r="K268">
+        <v>3</v>
+      </c>
+      <c r="L268">
+        <v>3</v>
+      </c>
+      <c r="M268">
+        <v>1</v>
+      </c>
+      <c r="N268">
+        <v>4</v>
+      </c>
+      <c r="O268" t="s">
+        <v>277</v>
+      </c>
+      <c r="P268" t="s">
+        <v>367</v>
+      </c>
+      <c r="Q268">
+        <v>2.2</v>
+      </c>
+      <c r="R268">
+        <v>2.5</v>
+      </c>
+      <c r="S268">
+        <v>4.5</v>
+      </c>
+      <c r="T268">
+        <v>1.25</v>
+      </c>
+      <c r="U268">
+        <v>3.75</v>
+      </c>
+      <c r="V268">
+        <v>2.2</v>
+      </c>
+      <c r="W268">
+        <v>1.62</v>
+      </c>
+      <c r="X268">
+        <v>5</v>
+      </c>
+      <c r="Y268">
+        <v>1.17</v>
+      </c>
+      <c r="Z268">
+        <v>1.63</v>
+      </c>
+      <c r="AA268">
+        <v>3.91</v>
+      </c>
+      <c r="AB268">
+        <v>3.98</v>
+      </c>
+      <c r="AC268">
+        <v>1.03</v>
+      </c>
+      <c r="AD268">
+        <v>11</v>
+      </c>
+      <c r="AE268">
+        <v>1.15</v>
+      </c>
+      <c r="AF268">
+        <v>5.25</v>
+      </c>
+      <c r="AG268">
+        <v>1.69</v>
+      </c>
+      <c r="AH268">
+        <v>2.17</v>
+      </c>
+      <c r="AI268">
+        <v>1.53</v>
+      </c>
+      <c r="AJ268">
+        <v>2.38</v>
+      </c>
+      <c r="AK268">
+        <v>1.2</v>
+      </c>
+      <c r="AL268">
+        <v>1.18</v>
+      </c>
+      <c r="AM268">
+        <v>2.1</v>
+      </c>
+      <c r="AN268">
+        <v>1.8</v>
+      </c>
+      <c r="AO268">
+        <v>0.25</v>
+      </c>
+      <c r="AP268">
+        <v>1.91</v>
+      </c>
+      <c r="AQ268">
+        <v>0.22</v>
+      </c>
+      <c r="AR268">
+        <v>1.84</v>
+      </c>
+      <c r="AS268">
+        <v>1.35</v>
+      </c>
+      <c r="AT268">
+        <v>3.19</v>
+      </c>
+      <c r="AU268">
+        <v>10</v>
+      </c>
+      <c r="AV268">
+        <v>2</v>
+      </c>
+      <c r="AW268">
+        <v>6</v>
+      </c>
+      <c r="AX268">
+        <v>4</v>
+      </c>
+      <c r="AY268">
+        <v>16</v>
+      </c>
+      <c r="AZ268">
+        <v>6</v>
+      </c>
+      <c r="BA268">
+        <v>7</v>
+      </c>
+      <c r="BB268">
+        <v>3</v>
+      </c>
+      <c r="BC268">
+        <v>10</v>
+      </c>
+      <c r="BD268">
+        <v>1.45</v>
+      </c>
+      <c r="BE268">
+        <v>6.75</v>
+      </c>
+      <c r="BF268">
+        <v>3.15</v>
+      </c>
+      <c r="BG268">
+        <v>1.3</v>
+      </c>
+      <c r="BH268">
+        <v>3.05</v>
+      </c>
+      <c r="BI268">
+        <v>1.53</v>
+      </c>
+      <c r="BJ268">
+        <v>2.3</v>
+      </c>
+      <c r="BK268">
+        <v>1.85</v>
+      </c>
+      <c r="BL268">
+        <v>1.83</v>
+      </c>
+      <c r="BM268">
+        <v>2.32</v>
+      </c>
+      <c r="BN268">
+        <v>1.52</v>
+      </c>
+      <c r="BO268">
+        <v>2.95</v>
+      </c>
+      <c r="BP268">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="269" spans="1:68">
+      <c r="A269" s="1">
+        <v>268</v>
+      </c>
+      <c r="B269">
+        <v>7781345</v>
+      </c>
+      <c r="C269" t="s">
+        <v>68</v>
+      </c>
+      <c r="D269" t="s">
+        <v>69</v>
+      </c>
+      <c r="E269" s="2">
+        <v>45833.85416666666</v>
+      </c>
+      <c r="F269">
+        <v>0</v>
+      </c>
+      <c r="G269" t="s">
+        <v>99</v>
+      </c>
+      <c r="H269" t="s">
+        <v>73</v>
+      </c>
+      <c r="I269">
+        <v>0</v>
+      </c>
+      <c r="J269">
+        <v>1</v>
+      </c>
+      <c r="K269">
+        <v>1</v>
+      </c>
+      <c r="L269">
+        <v>1</v>
+      </c>
+      <c r="M269">
+        <v>3</v>
+      </c>
+      <c r="N269">
+        <v>4</v>
+      </c>
+      <c r="O269" t="s">
+        <v>278</v>
+      </c>
+      <c r="P269" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q269">
+        <v>3.5</v>
+      </c>
+      <c r="R269">
+        <v>2.25</v>
+      </c>
+      <c r="S269">
+        <v>2.88</v>
+      </c>
+      <c r="T269">
+        <v>1.33</v>
+      </c>
+      <c r="U269">
+        <v>3.25</v>
+      </c>
+      <c r="V269">
+        <v>2.63</v>
+      </c>
+      <c r="W269">
+        <v>1.44</v>
+      </c>
+      <c r="X269">
+        <v>6.5</v>
+      </c>
+      <c r="Y269">
+        <v>1.11</v>
+      </c>
+      <c r="Z269">
+        <v>2.78</v>
+      </c>
+      <c r="AA269">
+        <v>3.34</v>
+      </c>
+      <c r="AB269">
+        <v>2.17</v>
+      </c>
+      <c r="AC269">
+        <v>1.05</v>
+      </c>
+      <c r="AD269">
+        <v>9.5</v>
+      </c>
+      <c r="AE269">
+        <v>1.25</v>
+      </c>
+      <c r="AF269">
+        <v>3.75</v>
+      </c>
+      <c r="AG269">
+        <v>1.73</v>
+      </c>
+      <c r="AH269">
+        <v>1.97</v>
+      </c>
+      <c r="AI269">
+        <v>1.62</v>
+      </c>
+      <c r="AJ269">
+        <v>2.2</v>
+      </c>
+      <c r="AK269">
+        <v>1.62</v>
+      </c>
+      <c r="AL269">
+        <v>1.25</v>
+      </c>
+      <c r="AM269">
+        <v>1.36</v>
+      </c>
+      <c r="AN269">
+        <v>0.43</v>
+      </c>
+      <c r="AO269">
+        <v>1.6</v>
+      </c>
+      <c r="AP269">
+        <v>0.38</v>
+      </c>
+      <c r="AQ269">
+        <v>1.73</v>
+      </c>
+      <c r="AR269">
+        <v>1.55</v>
+      </c>
+      <c r="AS269">
+        <v>1.64</v>
+      </c>
+      <c r="AT269">
+        <v>3.19</v>
+      </c>
+      <c r="AU269">
+        <v>5</v>
+      </c>
+      <c r="AV269">
+        <v>9</v>
+      </c>
+      <c r="AW269">
+        <v>6</v>
+      </c>
+      <c r="AX269">
+        <v>3</v>
+      </c>
+      <c r="AY269">
+        <v>11</v>
+      </c>
+      <c r="AZ269">
+        <v>12</v>
+      </c>
+      <c r="BA269">
+        <v>3</v>
+      </c>
+      <c r="BB269">
+        <v>0</v>
+      </c>
+      <c r="BC269">
+        <v>3</v>
+      </c>
+      <c r="BD269">
+        <v>1.97</v>
+      </c>
+      <c r="BE269">
+        <v>6.4</v>
+      </c>
+      <c r="BF269">
+        <v>2.02</v>
+      </c>
+      <c r="BG269">
+        <v>1.33</v>
+      </c>
+      <c r="BH269">
+        <v>2.95</v>
+      </c>
+      <c r="BI269">
+        <v>1.57</v>
+      </c>
+      <c r="BJ269">
+        <v>2.23</v>
+      </c>
+      <c r="BK269">
+        <v>1.92</v>
+      </c>
+      <c r="BL269">
+        <v>1.77</v>
+      </c>
+      <c r="BM269">
+        <v>2.43</v>
+      </c>
+      <c r="BN269">
+        <v>1.48</v>
+      </c>
+      <c r="BO269">
+        <v>3.15</v>
+      </c>
+      <c r="BP269">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="270" spans="1:68">
+      <c r="A270" s="1">
+        <v>269</v>
+      </c>
+      <c r="B270">
+        <v>7781346</v>
+      </c>
+      <c r="C270" t="s">
+        <v>68</v>
+      </c>
+      <c r="D270" t="s">
+        <v>69</v>
+      </c>
+      <c r="E270" s="2">
+        <v>45833.85416666666</v>
+      </c>
+      <c r="F270">
+        <v>0</v>
+      </c>
+      <c r="G270" t="s">
+        <v>87</v>
+      </c>
+      <c r="H270" t="s">
+        <v>79</v>
+      </c>
+      <c r="I270">
+        <v>1</v>
+      </c>
+      <c r="J270">
+        <v>1</v>
+      </c>
+      <c r="K270">
+        <v>2</v>
+      </c>
+      <c r="L270">
+        <v>2</v>
+      </c>
+      <c r="M270">
+        <v>3</v>
+      </c>
+      <c r="N270">
+        <v>5</v>
+      </c>
+      <c r="O270" t="s">
+        <v>279</v>
+      </c>
+      <c r="P270" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q270">
+        <v>3.35</v>
+      </c>
+      <c r="R270">
+        <v>2.1</v>
+      </c>
+      <c r="S270">
+        <v>2.88</v>
+      </c>
+      <c r="T270">
+        <v>1.36</v>
+      </c>
+      <c r="U270">
+        <v>2.88</v>
+      </c>
+      <c r="V270">
+        <v>2.62</v>
+      </c>
+      <c r="W270">
+        <v>1.42</v>
+      </c>
+      <c r="X270">
+        <v>6</v>
+      </c>
+      <c r="Y270">
+        <v>1.09</v>
+      </c>
+      <c r="Z270">
+        <v>2.67</v>
+      </c>
+      <c r="AA270">
+        <v>3.31</v>
+      </c>
+      <c r="AB270">
+        <v>2.26</v>
+      </c>
+      <c r="AC270">
+        <v>1.05</v>
+      </c>
+      <c r="AD270">
+        <v>9.5</v>
+      </c>
+      <c r="AE270">
+        <v>1.28</v>
+      </c>
+      <c r="AF270">
+        <v>3.65</v>
+      </c>
+      <c r="AG270">
+        <v>1.78</v>
+      </c>
+      <c r="AH270">
+        <v>1.92</v>
+      </c>
+      <c r="AI270">
+        <v>1.62</v>
+      </c>
+      <c r="AJ270">
+        <v>2.15</v>
+      </c>
+      <c r="AK270">
+        <v>1.55</v>
+      </c>
+      <c r="AL270">
+        <v>1.25</v>
+      </c>
+      <c r="AM270">
+        <v>1.4</v>
+      </c>
+      <c r="AN270">
+        <v>1.17</v>
+      </c>
+      <c r="AO270">
+        <v>1.63</v>
+      </c>
+      <c r="AP270">
+        <v>1</v>
+      </c>
+      <c r="AQ270">
+        <v>1.78</v>
+      </c>
+      <c r="AR270">
+        <v>1.36</v>
+      </c>
+      <c r="AS270">
+        <v>1.6</v>
+      </c>
+      <c r="AT270">
+        <v>2.96</v>
+      </c>
+      <c r="AU270">
+        <v>5</v>
+      </c>
+      <c r="AV270">
+        <v>7</v>
+      </c>
+      <c r="AW270">
+        <v>4</v>
+      </c>
+      <c r="AX270">
+        <v>2</v>
+      </c>
+      <c r="AY270">
+        <v>9</v>
+      </c>
+      <c r="AZ270">
+        <v>9</v>
+      </c>
+      <c r="BA270">
+        <v>5</v>
+      </c>
+      <c r="BB270">
+        <v>6</v>
+      </c>
+      <c r="BC270">
+        <v>11</v>
+      </c>
+      <c r="BD270">
+        <v>2.07</v>
+      </c>
+      <c r="BE270">
+        <v>6.5</v>
+      </c>
+      <c r="BF270">
+        <v>1.92</v>
+      </c>
+      <c r="BG270">
+        <v>1.29</v>
+      </c>
+      <c r="BH270">
+        <v>3.2</v>
+      </c>
+      <c r="BI270">
+        <v>1.49</v>
+      </c>
+      <c r="BJ270">
+        <v>2.4</v>
+      </c>
+      <c r="BK270">
+        <v>1.81</v>
+      </c>
+      <c r="BL270">
+        <v>1.88</v>
+      </c>
+      <c r="BM270">
+        <v>2.28</v>
+      </c>
+      <c r="BN270">
+        <v>1.55</v>
+      </c>
+      <c r="BO270">
+        <v>2.9</v>
+      </c>
+      <c r="BP270">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="271" spans="1:68">
+      <c r="A271" s="1">
+        <v>270</v>
+      </c>
+      <c r="B271">
+        <v>7781347</v>
+      </c>
+      <c r="C271" t="s">
+        <v>68</v>
+      </c>
+      <c r="D271" t="s">
+        <v>69</v>
+      </c>
+      <c r="E271" s="2">
+        <v>45833.85416666666</v>
+      </c>
+      <c r="F271">
+        <v>0</v>
+      </c>
+      <c r="G271" t="s">
+        <v>98</v>
+      </c>
+      <c r="H271" t="s">
+        <v>88</v>
+      </c>
+      <c r="I271">
+        <v>0</v>
+      </c>
+      <c r="J271">
+        <v>1</v>
+      </c>
+      <c r="K271">
+        <v>1</v>
+      </c>
+      <c r="L271">
+        <v>1</v>
+      </c>
+      <c r="M271">
+        <v>1</v>
+      </c>
+      <c r="N271">
+        <v>2</v>
+      </c>
+      <c r="O271" t="s">
+        <v>280</v>
+      </c>
+      <c r="P271" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q271">
+        <v>3.6</v>
+      </c>
+      <c r="R271">
+        <v>2.1</v>
+      </c>
+      <c r="S271">
+        <v>3</v>
+      </c>
+      <c r="T271">
+        <v>1.4</v>
+      </c>
+      <c r="U271">
+        <v>2.75</v>
+      </c>
+      <c r="V271">
+        <v>3</v>
+      </c>
+      <c r="W271">
+        <v>1.36</v>
+      </c>
+      <c r="X271">
+        <v>8</v>
+      </c>
+      <c r="Y271">
+        <v>1.08</v>
+      </c>
+      <c r="Z271">
+        <v>2.94</v>
+      </c>
+      <c r="AA271">
+        <v>3.12</v>
+      </c>
+      <c r="AB271">
+        <v>2.18</v>
+      </c>
+      <c r="AC271">
+        <v>1.07</v>
+      </c>
+      <c r="AD271">
+        <v>8</v>
+      </c>
+      <c r="AE271">
+        <v>1.35</v>
+      </c>
+      <c r="AF271">
+        <v>3.1</v>
+      </c>
+      <c r="AG271">
+        <v>1.97</v>
+      </c>
+      <c r="AH271">
+        <v>1.73</v>
+      </c>
+      <c r="AI271">
+        <v>1.8</v>
+      </c>
+      <c r="AJ271">
+        <v>1.95</v>
+      </c>
+      <c r="AK271">
+        <v>1.6</v>
+      </c>
+      <c r="AL271">
+        <v>1.28</v>
+      </c>
+      <c r="AM271">
+        <v>1.35</v>
+      </c>
+      <c r="AN271">
+        <v>0.5</v>
+      </c>
+      <c r="AO271">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP271">
+        <v>0.55</v>
+      </c>
+      <c r="AQ271">
+        <v>0.6</v>
+      </c>
+      <c r="AR271">
+        <v>1.42</v>
+      </c>
+      <c r="AS271">
+        <v>1.23</v>
+      </c>
+      <c r="AT271">
+        <v>2.65</v>
+      </c>
+      <c r="AU271">
+        <v>3</v>
+      </c>
+      <c r="AV271">
+        <v>2</v>
+      </c>
+      <c r="AW271">
+        <v>0</v>
+      </c>
+      <c r="AX271">
+        <v>1</v>
+      </c>
+      <c r="AY271">
+        <v>3</v>
+      </c>
+      <c r="AZ271">
+        <v>3</v>
+      </c>
+      <c r="BA271">
+        <v>4</v>
+      </c>
+      <c r="BB271">
+        <v>6</v>
+      </c>
+      <c r="BC271">
+        <v>10</v>
+      </c>
+      <c r="BD271">
+        <v>2.08</v>
+      </c>
+      <c r="BE271">
+        <v>6.5</v>
+      </c>
+      <c r="BF271">
+        <v>1.9</v>
+      </c>
+      <c r="BG271">
+        <v>1.34</v>
+      </c>
+      <c r="BH271">
+        <v>2.9</v>
+      </c>
+      <c r="BI271">
+        <v>1.58</v>
+      </c>
+      <c r="BJ271">
+        <v>2.18</v>
+      </c>
+      <c r="BK271">
+        <v>1.96</v>
+      </c>
+      <c r="BL271">
+        <v>1.74</v>
+      </c>
+      <c r="BM271">
+        <v>2.48</v>
+      </c>
+      <c r="BN271">
+        <v>1.47</v>
+      </c>
+      <c r="BO271">
+        <v>3.2</v>
+      </c>
+      <c r="BP271">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="272" spans="1:68">
+      <c r="A272" s="1">
+        <v>271</v>
+      </c>
+      <c r="B272">
+        <v>7781351</v>
+      </c>
+      <c r="C272" t="s">
+        <v>68</v>
+      </c>
+      <c r="D272" t="s">
+        <v>69</v>
+      </c>
+      <c r="E272" s="2">
+        <v>45833.89583333334</v>
+      </c>
+      <c r="F272">
+        <v>0</v>
+      </c>
+      <c r="G272" t="s">
+        <v>92</v>
+      </c>
+      <c r="H272" t="s">
+        <v>78</v>
+      </c>
+      <c r="I272">
+        <v>0</v>
+      </c>
+      <c r="J272">
+        <v>0</v>
+      </c>
+      <c r="K272">
+        <v>0</v>
+      </c>
+      <c r="L272">
+        <v>3</v>
+      </c>
+      <c r="M272">
+        <v>1</v>
+      </c>
+      <c r="N272">
+        <v>4</v>
+      </c>
+      <c r="O272" t="s">
+        <v>281</v>
+      </c>
+      <c r="P272" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q272">
+        <v>2.38</v>
+      </c>
+      <c r="R272">
+        <v>2.25</v>
+      </c>
+      <c r="S272">
+        <v>4.5</v>
+      </c>
+      <c r="T272">
+        <v>1.36</v>
+      </c>
+      <c r="U272">
+        <v>3</v>
+      </c>
+      <c r="V272">
+        <v>2.63</v>
+      </c>
+      <c r="W272">
+        <v>1.44</v>
+      </c>
+      <c r="X272">
+        <v>7</v>
+      </c>
+      <c r="Y272">
+        <v>1.1</v>
+      </c>
+      <c r="Z272">
+        <v>1.71</v>
+      </c>
+      <c r="AA272">
+        <v>3.64</v>
+      </c>
+      <c r="AB272">
+        <v>3.82</v>
+      </c>
+      <c r="AC272">
+        <v>1.05</v>
+      </c>
+      <c r="AD272">
+        <v>9.5</v>
+      </c>
+      <c r="AE272">
+        <v>1.25</v>
+      </c>
+      <c r="AF272">
+        <v>3.7</v>
+      </c>
+      <c r="AG272">
+        <v>1.76</v>
+      </c>
+      <c r="AH272">
+        <v>1.94</v>
+      </c>
+      <c r="AI272">
+        <v>1.75</v>
+      </c>
+      <c r="AJ272">
+        <v>2</v>
+      </c>
+      <c r="AK272">
+        <v>1.22</v>
+      </c>
+      <c r="AL272">
+        <v>1.22</v>
+      </c>
+      <c r="AM272">
+        <v>1.95</v>
+      </c>
+      <c r="AN272">
+        <v>1.67</v>
+      </c>
+      <c r="AO272">
+        <v>1.25</v>
+      </c>
+      <c r="AP272">
+        <v>1.8</v>
+      </c>
+      <c r="AQ272">
+        <v>1.11</v>
+      </c>
+      <c r="AR272">
+        <v>1.82</v>
+      </c>
+      <c r="AS272">
+        <v>1.14</v>
+      </c>
+      <c r="AT272">
+        <v>2.96</v>
+      </c>
+      <c r="AU272">
+        <v>5</v>
+      </c>
+      <c r="AV272">
+        <v>2</v>
+      </c>
+      <c r="AW272">
+        <v>3</v>
+      </c>
+      <c r="AX272">
+        <v>7</v>
+      </c>
+      <c r="AY272">
+        <v>8</v>
+      </c>
+      <c r="AZ272">
+        <v>9</v>
+      </c>
+      <c r="BA272">
+        <v>6</v>
+      </c>
+      <c r="BB272">
+        <v>4</v>
+      </c>
+      <c r="BC272">
+        <v>10</v>
+      </c>
+      <c r="BD272">
+        <v>1.63</v>
+      </c>
+      <c r="BE272">
+        <v>6.75</v>
+      </c>
+      <c r="BF272">
+        <v>2.5</v>
+      </c>
+      <c r="BG272">
+        <v>1.24</v>
+      </c>
+      <c r="BH272">
+        <v>3.55</v>
+      </c>
+      <c r="BI272">
+        <v>1.43</v>
+      </c>
+      <c r="BJ272">
+        <v>2.55</v>
+      </c>
+      <c r="BK272">
+        <v>1.71</v>
+      </c>
+      <c r="BL272">
+        <v>2</v>
+      </c>
+      <c r="BM272">
+        <v>2.1</v>
+      </c>
+      <c r="BN272">
+        <v>1.64</v>
+      </c>
+      <c r="BO272">
+        <v>2.65</v>
+      </c>
+      <c r="BP272">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="273" spans="1:68">
+      <c r="A273" s="1">
+        <v>272</v>
+      </c>
+      <c r="B273">
+        <v>7781352</v>
+      </c>
+      <c r="C273" t="s">
+        <v>68</v>
+      </c>
+      <c r="D273" t="s">
+        <v>69</v>
+      </c>
+      <c r="E273" s="2">
+        <v>45833.89583333334</v>
+      </c>
+      <c r="F273">
+        <v>0</v>
+      </c>
+      <c r="G273" t="s">
+        <v>80</v>
+      </c>
+      <c r="H273" t="s">
+        <v>76</v>
+      </c>
+      <c r="I273">
+        <v>2</v>
+      </c>
+      <c r="J273">
+        <v>3</v>
+      </c>
+      <c r="K273">
+        <v>5</v>
+      </c>
+      <c r="L273">
+        <v>2</v>
+      </c>
+      <c r="M273">
+        <v>4</v>
+      </c>
+      <c r="N273">
+        <v>6</v>
+      </c>
+      <c r="O273" t="s">
+        <v>282</v>
+      </c>
+      <c r="P273" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q273">
+        <v>3.4</v>
+      </c>
+      <c r="R273">
+        <v>2.38</v>
+      </c>
+      <c r="S273">
+        <v>2.75</v>
+      </c>
+      <c r="T273">
+        <v>1.29</v>
+      </c>
+      <c r="U273">
+        <v>3.5</v>
+      </c>
+      <c r="V273">
+        <v>2.38</v>
+      </c>
+      <c r="W273">
+        <v>1.53</v>
+      </c>
+      <c r="X273">
+        <v>5.5</v>
+      </c>
+      <c r="Y273">
+        <v>1.14</v>
+      </c>
+      <c r="Z273">
+        <v>2.78</v>
+      </c>
+      <c r="AA273">
+        <v>3.41</v>
+      </c>
+      <c r="AB273">
+        <v>2.14</v>
+      </c>
+      <c r="AC273">
+        <v>1.04</v>
+      </c>
+      <c r="AD273">
+        <v>10</v>
+      </c>
+      <c r="AE273">
+        <v>1.2</v>
+      </c>
+      <c r="AF273">
+        <v>4.33</v>
+      </c>
+      <c r="AG273">
+        <v>1.54</v>
+      </c>
+      <c r="AH273">
+        <v>2.3</v>
+      </c>
+      <c r="AI273">
+        <v>1.53</v>
+      </c>
+      <c r="AJ273">
+        <v>2.38</v>
+      </c>
+      <c r="AK273">
+        <v>1.57</v>
+      </c>
+      <c r="AL273">
+        <v>1.25</v>
+      </c>
+      <c r="AM273">
+        <v>1.4</v>
+      </c>
+      <c r="AN273">
+        <v>1.11</v>
+      </c>
+      <c r="AO273">
+        <v>1.44</v>
+      </c>
+      <c r="AP273">
+        <v>1</v>
+      </c>
+      <c r="AQ273">
+        <v>1.6</v>
+      </c>
+      <c r="AR273">
+        <v>1.67</v>
+      </c>
+      <c r="AS273">
+        <v>1.36</v>
+      </c>
+      <c r="AT273">
+        <v>3.03</v>
+      </c>
+      <c r="AU273">
+        <v>12</v>
+      </c>
+      <c r="AV273">
+        <v>19</v>
+      </c>
+      <c r="AW273">
+        <v>3</v>
+      </c>
+      <c r="AX273">
+        <v>5</v>
+      </c>
+      <c r="AY273">
+        <v>15</v>
+      </c>
+      <c r="AZ273">
+        <v>24</v>
+      </c>
+      <c r="BA273">
+        <v>5</v>
+      </c>
+      <c r="BB273">
+        <v>6</v>
+      </c>
+      <c r="BC273">
+        <v>11</v>
+      </c>
+      <c r="BD273">
+        <v>2.1</v>
+      </c>
+      <c r="BE273">
+        <v>6.4</v>
+      </c>
+      <c r="BF273">
+        <v>1.88</v>
+      </c>
+      <c r="BG273">
+        <v>1.25</v>
+      </c>
+      <c r="BH273">
+        <v>3.4</v>
+      </c>
+      <c r="BI273">
+        <v>1.44</v>
+      </c>
+      <c r="BJ273">
+        <v>2.55</v>
+      </c>
+      <c r="BK273">
+        <v>1.72</v>
+      </c>
+      <c r="BL273">
+        <v>1.98</v>
+      </c>
+      <c r="BM273">
+        <v>2.14</v>
+      </c>
+      <c r="BN273">
+        <v>1.62</v>
+      </c>
+      <c r="BO273">
+        <v>2.7</v>
+      </c>
+      <c r="BP273">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="274" spans="1:68">
+      <c r="A274" s="1">
+        <v>273</v>
+      </c>
+      <c r="B274">
+        <v>7781348</v>
+      </c>
+      <c r="C274" t="s">
+        <v>68</v>
+      </c>
+      <c r="D274" t="s">
+        <v>69</v>
+      </c>
+      <c r="E274" s="2">
+        <v>45833.89583333334</v>
+      </c>
+      <c r="F274">
+        <v>0</v>
+      </c>
+      <c r="G274" t="s">
+        <v>90</v>
+      </c>
+      <c r="H274" t="s">
+        <v>89</v>
+      </c>
+      <c r="I274">
+        <v>0</v>
+      </c>
+      <c r="J274">
+        <v>1</v>
+      </c>
+      <c r="K274">
+        <v>1</v>
+      </c>
+      <c r="L274">
+        <v>0</v>
+      </c>
+      <c r="M274">
+        <v>1</v>
+      </c>
+      <c r="N274">
+        <v>1</v>
+      </c>
+      <c r="O274" t="s">
+        <v>109</v>
+      </c>
+      <c r="P274" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q274">
+        <v>2.75</v>
+      </c>
+      <c r="R274">
+        <v>2.38</v>
+      </c>
+      <c r="S274">
+        <v>3.5</v>
+      </c>
+      <c r="T274">
+        <v>1.29</v>
+      </c>
+      <c r="U274">
+        <v>3.5</v>
+      </c>
+      <c r="V274">
+        <v>2.38</v>
+      </c>
+      <c r="W274">
+        <v>1.53</v>
+      </c>
+      <c r="X274">
+        <v>5.5</v>
+      </c>
+      <c r="Y274">
+        <v>1.14</v>
+      </c>
+      <c r="Z274">
+        <v>2.08</v>
+      </c>
+      <c r="AA274">
+        <v>3.47</v>
+      </c>
+      <c r="AB274">
+        <v>2.84</v>
+      </c>
+      <c r="AC274">
+        <v>1.04</v>
+      </c>
+      <c r="AD274">
+        <v>10</v>
+      </c>
+      <c r="AE274">
+        <v>1.2</v>
+      </c>
+      <c r="AF274">
+        <v>4.33</v>
+      </c>
+      <c r="AG274">
+        <v>1.56</v>
+      </c>
+      <c r="AH274">
+        <v>2.27</v>
+      </c>
+      <c r="AI274">
+        <v>1.53</v>
+      </c>
+      <c r="AJ274">
+        <v>2.38</v>
+      </c>
+      <c r="AK274">
+        <v>1.36</v>
+      </c>
+      <c r="AL274">
+        <v>1.22</v>
+      </c>
+      <c r="AM274">
+        <v>1.65</v>
+      </c>
+      <c r="AN274">
+        <v>1</v>
+      </c>
+      <c r="AO274">
+        <v>2</v>
+      </c>
+      <c r="AP274">
+        <v>0.88</v>
+      </c>
+      <c r="AQ274">
+        <v>2.11</v>
+      </c>
+      <c r="AR274">
+        <v>1.64</v>
+      </c>
+      <c r="AS274">
+        <v>1.75</v>
+      </c>
+      <c r="AT274">
+        <v>3.39</v>
+      </c>
+      <c r="AU274">
+        <v>3</v>
+      </c>
+      <c r="AV274">
+        <v>2</v>
+      </c>
+      <c r="AW274">
+        <v>7</v>
+      </c>
+      <c r="AX274">
+        <v>4</v>
+      </c>
+      <c r="AY274">
+        <v>10</v>
+      </c>
+      <c r="AZ274">
+        <v>6</v>
+      </c>
+      <c r="BA274">
+        <v>1</v>
+      </c>
+      <c r="BB274">
+        <v>4</v>
+      </c>
+      <c r="BC274">
+        <v>5</v>
+      </c>
+      <c r="BD274">
+        <v>1.85</v>
+      </c>
+      <c r="BE274">
+        <v>6.4</v>
+      </c>
+      <c r="BF274">
+        <v>2.17</v>
+      </c>
+      <c r="BG274">
+        <v>1.28</v>
+      </c>
+      <c r="BH274">
+        <v>3.2</v>
+      </c>
+      <c r="BI274">
+        <v>1.5</v>
+      </c>
+      <c r="BJ274">
+        <v>2.38</v>
+      </c>
+      <c r="BK274">
+        <v>1.81</v>
+      </c>
+      <c r="BL274">
+        <v>1.88</v>
+      </c>
+      <c r="BM274">
+        <v>2.25</v>
+      </c>
+      <c r="BN274">
+        <v>1.55</v>
+      </c>
+      <c r="BO274">
+        <v>2.9</v>
+      </c>
+      <c r="BP274">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="275" spans="1:68">
+      <c r="A275" s="1">
+        <v>274</v>
+      </c>
+      <c r="B275">
+        <v>7781350</v>
+      </c>
+      <c r="C275" t="s">
+        <v>68</v>
+      </c>
+      <c r="D275" t="s">
+        <v>69</v>
+      </c>
+      <c r="E275" s="2">
+        <v>45833.89583333334</v>
+      </c>
+      <c r="F275">
+        <v>0</v>
+      </c>
+      <c r="G275" t="s">
+        <v>91</v>
+      </c>
+      <c r="H275" t="s">
+        <v>85</v>
+      </c>
+      <c r="I275">
+        <v>0</v>
+      </c>
+      <c r="J275">
+        <v>1</v>
+      </c>
+      <c r="K275">
+        <v>1</v>
+      </c>
+      <c r="L275">
+        <v>2</v>
+      </c>
+      <c r="M275">
+        <v>1</v>
+      </c>
+      <c r="N275">
+        <v>3</v>
+      </c>
+      <c r="O275" t="s">
+        <v>283</v>
+      </c>
+      <c r="P275" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q275">
+        <v>3</v>
+      </c>
+      <c r="R275">
+        <v>2.4</v>
+      </c>
+      <c r="S275">
+        <v>3</v>
+      </c>
+      <c r="T275">
+        <v>1.29</v>
+      </c>
+      <c r="U275">
+        <v>3.5</v>
+      </c>
+      <c r="V275">
+        <v>2.25</v>
+      </c>
+      <c r="W275">
+        <v>1.57</v>
+      </c>
+      <c r="X275">
+        <v>5.5</v>
+      </c>
+      <c r="Y275">
+        <v>1.14</v>
+      </c>
+      <c r="Z275">
+        <v>2.39</v>
+      </c>
+      <c r="AA275">
+        <v>3.5</v>
+      </c>
+      <c r="AB275">
+        <v>2.41</v>
+      </c>
+      <c r="AC275">
+        <v>1.04</v>
+      </c>
+      <c r="AD275">
+        <v>10</v>
+      </c>
+      <c r="AE275">
+        <v>1.2</v>
+      </c>
+      <c r="AF275">
+        <v>4.33</v>
+      </c>
+      <c r="AG275">
+        <v>1.6</v>
+      </c>
+      <c r="AH275">
+        <v>1.02</v>
+      </c>
+      <c r="AI275">
+        <v>1.5</v>
+      </c>
+      <c r="AJ275">
+        <v>2.5</v>
+      </c>
+      <c r="AK275">
+        <v>1.48</v>
+      </c>
+      <c r="AL275">
+        <v>1.25</v>
+      </c>
+      <c r="AM275">
+        <v>1.48</v>
+      </c>
+      <c r="AN275">
+        <v>1</v>
+      </c>
+      <c r="AO275">
+        <v>0.7</v>
+      </c>
+      <c r="AP275">
+        <v>1.22</v>
+      </c>
+      <c r="AQ275">
+        <v>0.64</v>
+      </c>
+      <c r="AR275">
+        <v>1.59</v>
+      </c>
+      <c r="AS275">
+        <v>1.16</v>
+      </c>
+      <c r="AT275">
+        <v>2.75</v>
+      </c>
+      <c r="AU275">
+        <v>7</v>
+      </c>
+      <c r="AV275">
+        <v>6</v>
+      </c>
+      <c r="AW275">
+        <v>10</v>
+      </c>
+      <c r="AX275">
+        <v>10</v>
+      </c>
+      <c r="AY275">
+        <v>17</v>
+      </c>
+      <c r="AZ275">
+        <v>16</v>
+      </c>
+      <c r="BA275">
+        <v>5</v>
+      </c>
+      <c r="BB275">
+        <v>4</v>
+      </c>
+      <c r="BC275">
+        <v>9</v>
+      </c>
+      <c r="BD275">
+        <v>1.68</v>
+      </c>
+      <c r="BE275">
+        <v>6.75</v>
+      </c>
+      <c r="BF275">
+        <v>2.4</v>
+      </c>
+      <c r="BG275">
+        <v>1.28</v>
+      </c>
+      <c r="BH275">
+        <v>3.3</v>
+      </c>
+      <c r="BI275">
+        <v>1.49</v>
+      </c>
+      <c r="BJ275">
+        <v>2.4</v>
+      </c>
+      <c r="BK275">
+        <v>1.79</v>
+      </c>
+      <c r="BL275">
+        <v>1.9</v>
+      </c>
+      <c r="BM275">
+        <v>2.23</v>
+      </c>
+      <c r="BN275">
+        <v>1.57</v>
+      </c>
+      <c r="BO275">
+        <v>2.88</v>
+      </c>
+      <c r="BP275">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="276" spans="1:68">
+      <c r="A276" s="1">
+        <v>275</v>
+      </c>
+      <c r="B276">
+        <v>7781353</v>
+      </c>
+      <c r="C276" t="s">
+        <v>68</v>
+      </c>
+      <c r="D276" t="s">
+        <v>69</v>
+      </c>
+      <c r="E276" s="2">
+        <v>45833.9375</v>
+      </c>
+      <c r="F276">
+        <v>0</v>
+      </c>
+      <c r="G276" t="s">
+        <v>93</v>
+      </c>
+      <c r="H276" t="s">
+        <v>84</v>
+      </c>
+      <c r="I276">
+        <v>2</v>
+      </c>
+      <c r="J276">
+        <v>0</v>
+      </c>
+      <c r="K276">
+        <v>2</v>
+      </c>
+      <c r="L276">
+        <v>2</v>
+      </c>
+      <c r="M276">
+        <v>0</v>
+      </c>
+      <c r="N276">
+        <v>2</v>
+      </c>
+      <c r="O276" t="s">
+        <v>284</v>
+      </c>
+      <c r="P276" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q276">
+        <v>2.75</v>
+      </c>
+      <c r="R276">
+        <v>2.38</v>
+      </c>
+      <c r="S276">
+        <v>3.4</v>
+      </c>
+      <c r="T276">
+        <v>1.29</v>
+      </c>
+      <c r="U276">
+        <v>3.5</v>
+      </c>
+      <c r="V276">
+        <v>2.38</v>
+      </c>
+      <c r="W276">
+        <v>1.53</v>
+      </c>
+      <c r="X276">
+        <v>5.5</v>
+      </c>
+      <c r="Y276">
+        <v>1.14</v>
+      </c>
+      <c r="Z276">
+        <v>2.09</v>
+      </c>
+      <c r="AA276">
+        <v>3.36</v>
+      </c>
+      <c r="AB276">
+        <v>2.9</v>
+      </c>
+      <c r="AC276">
+        <v>1.04</v>
+      </c>
+      <c r="AD276">
+        <v>10</v>
+      </c>
+      <c r="AE276">
+        <v>1.2</v>
+      </c>
+      <c r="AF276">
+        <v>4.33</v>
+      </c>
+      <c r="AG276">
+        <v>1.6</v>
+      </c>
+      <c r="AH276">
+        <v>2.19</v>
+      </c>
+      <c r="AI276">
+        <v>1.53</v>
+      </c>
+      <c r="AJ276">
+        <v>2.38</v>
+      </c>
+      <c r="AK276">
+        <v>1.36</v>
+      </c>
+      <c r="AL276">
+        <v>1.25</v>
+      </c>
+      <c r="AM276">
+        <v>1.65</v>
+      </c>
+      <c r="AN276">
+        <v>1.4</v>
+      </c>
+      <c r="AO276">
+        <v>0.3</v>
+      </c>
+      <c r="AP276">
+        <v>1.55</v>
+      </c>
+      <c r="AQ276">
+        <v>0.27</v>
+      </c>
+      <c r="AR276">
+        <v>1.57</v>
+      </c>
+      <c r="AS276">
+        <v>1.28</v>
+      </c>
+      <c r="AT276">
+        <v>2.85</v>
+      </c>
+      <c r="AU276">
+        <v>5</v>
+      </c>
+      <c r="AV276">
+        <v>2</v>
+      </c>
+      <c r="AW276">
+        <v>0</v>
+      </c>
+      <c r="AX276">
+        <v>1</v>
+      </c>
+      <c r="AY276">
+        <v>5</v>
+      </c>
+      <c r="AZ276">
+        <v>3</v>
+      </c>
+      <c r="BA276">
+        <v>0</v>
+      </c>
+      <c r="BB276">
+        <v>5</v>
+      </c>
+      <c r="BC276">
+        <v>5</v>
+      </c>
+      <c r="BD276">
+        <v>1.71</v>
+      </c>
+      <c r="BE276">
+        <v>6.4</v>
+      </c>
+      <c r="BF276">
+        <v>2.4</v>
+      </c>
+      <c r="BG276">
+        <v>1.29</v>
+      </c>
+      <c r="BH276">
+        <v>3.15</v>
+      </c>
+      <c r="BI276">
+        <v>1.5</v>
+      </c>
+      <c r="BJ276">
+        <v>2.38</v>
+      </c>
+      <c r="BK276">
+        <v>1.81</v>
+      </c>
+      <c r="BL276">
+        <v>1.88</v>
+      </c>
+      <c r="BM276">
+        <v>2.3</v>
+      </c>
+      <c r="BN276">
+        <v>1.54</v>
+      </c>
+      <c r="BO276">
+        <v>2.9</v>
+      </c>
+      <c r="BP276">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="277" spans="1:68">
+      <c r="A277" s="1">
+        <v>276</v>
+      </c>
+      <c r="B277">
+        <v>7781349</v>
+      </c>
+      <c r="C277" t="s">
+        <v>68</v>
+      </c>
+      <c r="D277" t="s">
+        <v>69</v>
+      </c>
+      <c r="E277" s="2">
+        <v>45833.96180555555</v>
+      </c>
+      <c r="F277">
+        <v>0</v>
+      </c>
+      <c r="G277" t="s">
+        <v>97</v>
+      </c>
+      <c r="H277" t="s">
+        <v>81</v>
+      </c>
+      <c r="I277">
+        <v>1</v>
+      </c>
+      <c r="J277">
+        <v>0</v>
+      </c>
+      <c r="K277">
+        <v>1</v>
+      </c>
+      <c r="L277">
+        <v>2</v>
+      </c>
+      <c r="M277">
+        <v>4</v>
+      </c>
+      <c r="N277">
+        <v>6</v>
+      </c>
+      <c r="O277" t="s">
+        <v>285</v>
+      </c>
+      <c r="P277" t="s">
+        <v>414</v>
+      </c>
+      <c r="Q277">
+        <v>2.63</v>
+      </c>
+      <c r="R277">
+        <v>2.4</v>
+      </c>
+      <c r="S277">
+        <v>3.4</v>
+      </c>
+      <c r="T277">
+        <v>1.25</v>
+      </c>
+      <c r="U277">
+        <v>3.75</v>
+      </c>
+      <c r="V277">
+        <v>2.2</v>
+      </c>
+      <c r="W277">
+        <v>1.62</v>
+      </c>
+      <c r="X277">
+        <v>5</v>
+      </c>
+      <c r="Y277">
+        <v>1.17</v>
+      </c>
+      <c r="Z277">
+        <v>2.1</v>
+      </c>
+      <c r="AA277">
+        <v>3.33</v>
+      </c>
+      <c r="AB277">
+        <v>2.91</v>
+      </c>
+      <c r="AC277">
+        <v>1.04</v>
+      </c>
+      <c r="AD277">
+        <v>10</v>
+      </c>
+      <c r="AE277">
+        <v>1.18</v>
+      </c>
+      <c r="AF277">
+        <v>4.75</v>
+      </c>
+      <c r="AG277">
+        <v>1.67</v>
+      </c>
+      <c r="AH277">
+        <v>2.21</v>
+      </c>
+      <c r="AI277">
+        <v>1.5</v>
+      </c>
+      <c r="AJ277">
+        <v>2.5</v>
+      </c>
+      <c r="AK277">
+        <v>1.35</v>
+      </c>
+      <c r="AL277">
+        <v>1.22</v>
+      </c>
+      <c r="AM277">
+        <v>1.67</v>
+      </c>
+      <c r="AN277">
+        <v>0.71</v>
+      </c>
+      <c r="AO277">
+        <v>1.22</v>
+      </c>
+      <c r="AP277">
+        <v>0.63</v>
+      </c>
+      <c r="AQ277">
+        <v>1.4</v>
+      </c>
+      <c r="AR277">
+        <v>1.17</v>
+      </c>
+      <c r="AS277">
+        <v>1.76</v>
+      </c>
+      <c r="AT277">
+        <v>2.93</v>
+      </c>
+      <c r="AU277">
+        <v>9</v>
+      </c>
+      <c r="AV277">
+        <v>16</v>
+      </c>
+      <c r="AW277">
+        <v>4</v>
+      </c>
+      <c r="AX277">
+        <v>6</v>
+      </c>
+      <c r="AY277">
+        <v>13</v>
+      </c>
+      <c r="AZ277">
+        <v>22</v>
+      </c>
+      <c r="BA277">
+        <v>0</v>
+      </c>
+      <c r="BB277">
+        <v>8</v>
+      </c>
+      <c r="BC277">
+        <v>8</v>
+      </c>
+      <c r="BD277">
+        <v>1.66</v>
+      </c>
+      <c r="BE277">
+        <v>6.5</v>
+      </c>
+      <c r="BF277">
+        <v>2.48</v>
+      </c>
+      <c r="BG277">
+        <v>1.26</v>
+      </c>
+      <c r="BH277">
+        <v>3.4</v>
+      </c>
+      <c r="BI277">
+        <v>1.46</v>
+      </c>
+      <c r="BJ277">
+        <v>2.48</v>
+      </c>
+      <c r="BK277">
+        <v>1.74</v>
+      </c>
+      <c r="BL277">
+        <v>1.95</v>
+      </c>
+      <c r="BM277">
+        <v>2.17</v>
+      </c>
+      <c r="BN277">
+        <v>1.6</v>
+      </c>
+      <c r="BO277">
+        <v>2.75</v>
+      </c>
+      <c r="BP277">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="278" spans="1:68">
+      <c r="A278" s="1">
+        <v>277</v>
+      </c>
+      <c r="B278">
+        <v>7781355</v>
+      </c>
+      <c r="C278" t="s">
+        <v>68</v>
+      </c>
+      <c r="D278" t="s">
+        <v>69</v>
+      </c>
+      <c r="E278" s="2">
+        <v>45833.97916666666</v>
+      </c>
+      <c r="F278">
+        <v>0</v>
+      </c>
+      <c r="G278" t="s">
+        <v>95</v>
+      </c>
+      <c r="H278" t="s">
+        <v>94</v>
+      </c>
+      <c r="I278">
+        <v>1</v>
+      </c>
+      <c r="J278">
+        <v>3</v>
+      </c>
+      <c r="K278">
+        <v>4</v>
+      </c>
+      <c r="L278">
+        <v>3</v>
+      </c>
+      <c r="M278">
+        <v>5</v>
+      </c>
+      <c r="N278">
+        <v>8</v>
+      </c>
+      <c r="O278" t="s">
+        <v>286</v>
+      </c>
+      <c r="P278" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q278">
+        <v>0</v>
+      </c>
+      <c r="R278">
+        <v>0</v>
+      </c>
+      <c r="S278">
+        <v>0</v>
+      </c>
+      <c r="T278">
+        <v>0</v>
+      </c>
+      <c r="U278">
+        <v>0</v>
+      </c>
+      <c r="V278">
+        <v>0</v>
+      </c>
+      <c r="W278">
+        <v>0</v>
+      </c>
+      <c r="X278">
+        <v>0</v>
+      </c>
+      <c r="Y278">
+        <v>0</v>
+      </c>
+      <c r="Z278">
+        <v>2.07</v>
+      </c>
+      <c r="AA278">
+        <v>3.27</v>
+      </c>
+      <c r="AB278">
+        <v>3.02</v>
+      </c>
+      <c r="AC278">
+        <v>0</v>
+      </c>
+      <c r="AD278">
+        <v>0</v>
+      </c>
+      <c r="AE278">
+        <v>0</v>
+      </c>
+      <c r="AF278">
+        <v>0</v>
+      </c>
+      <c r="AG278">
+        <v>1.7</v>
+      </c>
+      <c r="AH278">
+        <v>2.02</v>
+      </c>
+      <c r="AI278">
+        <v>0</v>
+      </c>
+      <c r="AJ278">
+        <v>0</v>
+      </c>
+      <c r="AK278">
+        <v>0</v>
+      </c>
+      <c r="AL278">
+        <v>0</v>
+      </c>
+      <c r="AM278">
+        <v>0</v>
+      </c>
+      <c r="AN278">
+        <v>2.22</v>
+      </c>
+      <c r="AO278">
+        <v>1.5</v>
+      </c>
+      <c r="AP278">
+        <v>2</v>
+      </c>
+      <c r="AQ278">
+        <v>1.67</v>
+      </c>
+      <c r="AR278">
+        <v>1.94</v>
+      </c>
+      <c r="AS278">
+        <v>1.67</v>
+      </c>
+      <c r="AT278">
+        <v>3.61</v>
+      </c>
+      <c r="AU278">
+        <v>6</v>
+      </c>
+      <c r="AV278">
+        <v>9</v>
+      </c>
+      <c r="AW278">
+        <v>10</v>
+      </c>
+      <c r="AX278">
+        <v>1</v>
+      </c>
+      <c r="AY278">
+        <v>16</v>
+      </c>
+      <c r="AZ278">
+        <v>10</v>
+      </c>
+      <c r="BA278">
+        <v>7</v>
+      </c>
+      <c r="BB278">
+        <v>3</v>
+      </c>
+      <c r="BC278">
+        <v>10</v>
+      </c>
+      <c r="BD278">
+        <v>0</v>
+      </c>
+      <c r="BE278">
+        <v>0</v>
+      </c>
+      <c r="BF278">
+        <v>0</v>
+      </c>
+      <c r="BG278">
+        <v>0</v>
+      </c>
+      <c r="BH278">
+        <v>0</v>
+      </c>
+      <c r="BI278">
+        <v>0</v>
+      </c>
+      <c r="BJ278">
+        <v>0</v>
+      </c>
+      <c r="BK278">
+        <v>0</v>
+      </c>
+      <c r="BL278">
+        <v>0</v>
+      </c>
+      <c r="BM278">
+        <v>0</v>
+      </c>
+      <c r="BN278">
+        <v>0</v>
+      </c>
+      <c r="BO278">
+        <v>0</v>
+      </c>
+      <c r="BP278">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -826,7 +826,7 @@
     <t>['71']</t>
   </si>
   <si>
-    <t>['35', '47', '9004']</t>
+    <t>['35', '47', '9005']</t>
   </si>
   <si>
     <t>['2', '23']</t>
@@ -868,13 +868,13 @@
     <t>['9003', '9006']</t>
   </si>
   <si>
-    <t>['24', '28']</t>
-  </si>
-  <si>
     <t>['30', '68']</t>
   </si>
   <si>
     <t>['43', '66', '9006']</t>
+  </si>
+  <si>
+    <t>['24', '28']</t>
   </si>
   <si>
     <t>['26', '55']</t>
@@ -55329,19 +55329,19 @@
         <v>7</v>
       </c>
       <c r="AV261">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW261">
         <v>2</v>
       </c>
       <c r="AX261">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY261">
         <v>9</v>
       </c>
       <c r="AZ261">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA261">
         <v>3</v>
@@ -57869,7 +57869,7 @@
         <v>273</v>
       </c>
       <c r="B274">
-        <v>7781348</v>
+        <v>7781350</v>
       </c>
       <c r="C274" t="s">
         <v>68</v>
@@ -57884,10 +57884,10 @@
         <v>0</v>
       </c>
       <c r="G274" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H274" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I274">
         <v>0</v>
@@ -57899,28 +57899,28 @@
         <v>1</v>
       </c>
       <c r="L274">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M274">
         <v>1</v>
       </c>
       <c r="N274">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O274" t="s">
-        <v>109</v>
+        <v>283</v>
       </c>
       <c r="P274" t="s">
-        <v>223</v>
+        <v>365</v>
       </c>
       <c r="Q274">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R274">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S274">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="T274">
         <v>1.29</v>
@@ -57929,10 +57929,10 @@
         <v>3.5</v>
       </c>
       <c r="V274">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="W274">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="X274">
         <v>5.5</v>
@@ -57941,13 +57941,13 @@
         <v>1.14</v>
       </c>
       <c r="Z274">
-        <v>2.08</v>
+        <v>2.39</v>
       </c>
       <c r="AA274">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="AB274">
-        <v>2.84</v>
+        <v>2.41</v>
       </c>
       <c r="AC274">
         <v>1.04</v>
@@ -57962,109 +57962,109 @@
         <v>4.33</v>
       </c>
       <c r="AG274">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AH274">
-        <v>2.27</v>
+        <v>1.02</v>
       </c>
       <c r="AI274">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AJ274">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AK274">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AL274">
+        <v>1.25</v>
+      </c>
+      <c r="AM274">
+        <v>1.48</v>
+      </c>
+      <c r="AN274">
+        <v>1</v>
+      </c>
+      <c r="AO274">
+        <v>0.7</v>
+      </c>
+      <c r="AP274">
         <v>1.22</v>
       </c>
-      <c r="AM274">
-        <v>1.65</v>
-      </c>
-      <c r="AN274">
-        <v>1</v>
-      </c>
-      <c r="AO274">
-        <v>2</v>
-      </c>
-      <c r="AP274">
-        <v>0.88</v>
-      </c>
       <c r="AQ274">
-        <v>2.11</v>
+        <v>0.64</v>
       </c>
       <c r="AR274">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AS274">
-        <v>1.75</v>
+        <v>1.16</v>
       </c>
       <c r="AT274">
-        <v>3.39</v>
+        <v>2.75</v>
       </c>
       <c r="AU274">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AV274">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AW274">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX274">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AY274">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AZ274">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BA274">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BB274">
         <v>4</v>
       </c>
       <c r="BC274">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BD274">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="BE274">
-        <v>6.4</v>
+        <v>6.75</v>
       </c>
       <c r="BF274">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="BG274">
         <v>1.28</v>
       </c>
       <c r="BH274">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BI274">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="BJ274">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BK274">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="BL274">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="BM274">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BN274">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BO274">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BP274">
         <v>1.35</v>
@@ -58075,7 +58075,7 @@
         <v>274</v>
       </c>
       <c r="B275">
-        <v>7781350</v>
+        <v>7781348</v>
       </c>
       <c r="C275" t="s">
         <v>68</v>
@@ -58090,10 +58090,10 @@
         <v>0</v>
       </c>
       <c r="G275" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H275" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I275">
         <v>0</v>
@@ -58105,28 +58105,28 @@
         <v>1</v>
       </c>
       <c r="L275">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M275">
         <v>1</v>
       </c>
       <c r="N275">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O275" t="s">
-        <v>283</v>
+        <v>109</v>
       </c>
       <c r="P275" t="s">
-        <v>365</v>
+        <v>223</v>
       </c>
       <c r="Q275">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R275">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S275">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="T275">
         <v>1.29</v>
@@ -58135,10 +58135,10 @@
         <v>3.5</v>
       </c>
       <c r="V275">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="W275">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="X275">
         <v>5.5</v>
@@ -58147,13 +58147,13 @@
         <v>1.14</v>
       </c>
       <c r="Z275">
-        <v>2.39</v>
+        <v>2.08</v>
       </c>
       <c r="AA275">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="AB275">
-        <v>2.41</v>
+        <v>2.84</v>
       </c>
       <c r="AC275">
         <v>1.04</v>
@@ -58168,109 +58168,109 @@
         <v>4.33</v>
       </c>
       <c r="AG275">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AH275">
-        <v>1.02</v>
+        <v>2.27</v>
       </c>
       <c r="AI275">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AJ275">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AK275">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AL275">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AM275">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AN275">
         <v>1</v>
       </c>
       <c r="AO275">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="AP275">
-        <v>1.22</v>
+        <v>0.88</v>
       </c>
       <c r="AQ275">
-        <v>0.64</v>
+        <v>2.11</v>
       </c>
       <c r="AR275">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AS275">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="AT275">
-        <v>2.75</v>
+        <v>3.39</v>
       </c>
       <c r="AU275">
+        <v>3</v>
+      </c>
+      <c r="AV275">
+        <v>2</v>
+      </c>
+      <c r="AW275">
         <v>7</v>
       </c>
-      <c r="AV275">
+      <c r="AX275">
+        <v>4</v>
+      </c>
+      <c r="AY275">
+        <v>10</v>
+      </c>
+      <c r="AZ275">
         <v>6</v>
       </c>
-      <c r="AW275">
-        <v>10</v>
-      </c>
-      <c r="AX275">
-        <v>10</v>
-      </c>
-      <c r="AY275">
-        <v>17</v>
-      </c>
-      <c r="AZ275">
-        <v>16</v>
-      </c>
       <c r="BA275">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BB275">
         <v>4</v>
       </c>
       <c r="BC275">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BD275">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="BE275">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="BF275">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="BG275">
         <v>1.28</v>
       </c>
       <c r="BH275">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BI275">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="BJ275">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BK275">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="BL275">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="BM275">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="BN275">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BO275">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BP275">
         <v>1.35</v>
@@ -58281,7 +58281,7 @@
         <v>275</v>
       </c>
       <c r="B276">
-        <v>7781353</v>
+        <v>7781349</v>
       </c>
       <c r="C276" t="s">
         <v>68</v>
@@ -58290,76 +58290,76 @@
         <v>69</v>
       </c>
       <c r="E276" s="2">
-        <v>45833.9375</v>
+        <v>45833.96180555555</v>
       </c>
       <c r="F276">
         <v>0</v>
       </c>
       <c r="G276" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H276" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I276">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J276">
         <v>0</v>
       </c>
       <c r="K276">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L276">
         <v>2</v>
       </c>
       <c r="M276">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N276">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O276" t="s">
         <v>284</v>
       </c>
       <c r="P276" t="s">
-        <v>109</v>
+        <v>414</v>
       </c>
       <c r="Q276">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="R276">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S276">
         <v>3.4</v>
       </c>
       <c r="T276">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="U276">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="V276">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="W276">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="X276">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Y276">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z276">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AA276">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="AB276">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="AC276">
         <v>1.04</v>
@@ -58368,118 +58368,118 @@
         <v>10</v>
       </c>
       <c r="AE276">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF276">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AG276">
+        <v>1.67</v>
+      </c>
+      <c r="AH276">
+        <v>2.21</v>
+      </c>
+      <c r="AI276">
+        <v>1.5</v>
+      </c>
+      <c r="AJ276">
+        <v>2.5</v>
+      </c>
+      <c r="AK276">
+        <v>1.35</v>
+      </c>
+      <c r="AL276">
+        <v>1.22</v>
+      </c>
+      <c r="AM276">
+        <v>1.67</v>
+      </c>
+      <c r="AN276">
+        <v>0.71</v>
+      </c>
+      <c r="AO276">
+        <v>1.22</v>
+      </c>
+      <c r="AP276">
+        <v>0.63</v>
+      </c>
+      <c r="AQ276">
+        <v>1.4</v>
+      </c>
+      <c r="AR276">
+        <v>1.17</v>
+      </c>
+      <c r="AS276">
+        <v>1.76</v>
+      </c>
+      <c r="AT276">
+        <v>2.93</v>
+      </c>
+      <c r="AU276">
+        <v>9</v>
+      </c>
+      <c r="AV276">
+        <v>16</v>
+      </c>
+      <c r="AW276">
+        <v>4</v>
+      </c>
+      <c r="AX276">
+        <v>6</v>
+      </c>
+      <c r="AY276">
+        <v>13</v>
+      </c>
+      <c r="AZ276">
+        <v>22</v>
+      </c>
+      <c r="BA276">
+        <v>0</v>
+      </c>
+      <c r="BB276">
+        <v>8</v>
+      </c>
+      <c r="BC276">
+        <v>8</v>
+      </c>
+      <c r="BD276">
+        <v>1.66</v>
+      </c>
+      <c r="BE276">
+        <v>6.5</v>
+      </c>
+      <c r="BF276">
+        <v>2.48</v>
+      </c>
+      <c r="BG276">
+        <v>1.26</v>
+      </c>
+      <c r="BH276">
+        <v>3.4</v>
+      </c>
+      <c r="BI276">
+        <v>1.46</v>
+      </c>
+      <c r="BJ276">
+        <v>2.48</v>
+      </c>
+      <c r="BK276">
+        <v>1.74</v>
+      </c>
+      <c r="BL276">
+        <v>1.95</v>
+      </c>
+      <c r="BM276">
+        <v>2.17</v>
+      </c>
+      <c r="BN276">
         <v>1.6</v>
       </c>
-      <c r="AH276">
-        <v>2.19</v>
-      </c>
-      <c r="AI276">
-        <v>1.53</v>
-      </c>
-      <c r="AJ276">
-        <v>2.38</v>
-      </c>
-      <c r="AK276">
-        <v>1.36</v>
-      </c>
-      <c r="AL276">
-        <v>1.25</v>
-      </c>
-      <c r="AM276">
-        <v>1.65</v>
-      </c>
-      <c r="AN276">
-        <v>1.4</v>
-      </c>
-      <c r="AO276">
-        <v>0.3</v>
-      </c>
-      <c r="AP276">
-        <v>1.55</v>
-      </c>
-      <c r="AQ276">
-        <v>0.27</v>
-      </c>
-      <c r="AR276">
-        <v>1.57</v>
-      </c>
-      <c r="AS276">
-        <v>1.28</v>
-      </c>
-      <c r="AT276">
-        <v>2.85</v>
-      </c>
-      <c r="AU276">
-        <v>5</v>
-      </c>
-      <c r="AV276">
-        <v>2</v>
-      </c>
-      <c r="AW276">
-        <v>0</v>
-      </c>
-      <c r="AX276">
-        <v>1</v>
-      </c>
-      <c r="AY276">
-        <v>5</v>
-      </c>
-      <c r="AZ276">
-        <v>3</v>
-      </c>
-      <c r="BA276">
-        <v>0</v>
-      </c>
-      <c r="BB276">
-        <v>5</v>
-      </c>
-      <c r="BC276">
-        <v>5</v>
-      </c>
-      <c r="BD276">
-        <v>1.71</v>
-      </c>
-      <c r="BE276">
-        <v>6.4</v>
-      </c>
-      <c r="BF276">
-        <v>2.4</v>
-      </c>
-      <c r="BG276">
-        <v>1.29</v>
-      </c>
-      <c r="BH276">
-        <v>3.15</v>
-      </c>
-      <c r="BI276">
-        <v>1.5</v>
-      </c>
-      <c r="BJ276">
-        <v>2.38</v>
-      </c>
-      <c r="BK276">
-        <v>1.81</v>
-      </c>
-      <c r="BL276">
-        <v>1.88</v>
-      </c>
-      <c r="BM276">
-        <v>2.3</v>
-      </c>
-      <c r="BN276">
-        <v>1.54</v>
-      </c>
       <c r="BO276">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="BP276">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="277" spans="1:68">
@@ -58487,7 +58487,7 @@
         <v>276</v>
       </c>
       <c r="B277">
-        <v>7781349</v>
+        <v>7781355</v>
       </c>
       <c r="C277" t="s">
         <v>68</v>
@@ -58496,196 +58496,196 @@
         <v>69</v>
       </c>
       <c r="E277" s="2">
-        <v>45833.96180555555</v>
+        <v>45833.97916666666</v>
       </c>
       <c r="F277">
         <v>0</v>
       </c>
       <c r="G277" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H277" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I277">
         <v>1</v>
       </c>
       <c r="J277">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K277">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L277">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M277">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N277">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O277" t="s">
         <v>285</v>
       </c>
       <c r="P277" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q277">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R277">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S277">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T277">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U277">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V277">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="W277">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="X277">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y277">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z277">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AA277">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="AB277">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="AC277">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AD277">
+        <v>0</v>
+      </c>
+      <c r="AE277">
+        <v>0</v>
+      </c>
+      <c r="AF277">
+        <v>0</v>
+      </c>
+      <c r="AG277">
+        <v>1.7</v>
+      </c>
+      <c r="AH277">
+        <v>2.02</v>
+      </c>
+      <c r="AI277">
+        <v>0</v>
+      </c>
+      <c r="AJ277">
+        <v>0</v>
+      </c>
+      <c r="AK277">
+        <v>0</v>
+      </c>
+      <c r="AL277">
+        <v>0</v>
+      </c>
+      <c r="AM277">
+        <v>0</v>
+      </c>
+      <c r="AN277">
+        <v>2.22</v>
+      </c>
+      <c r="AO277">
+        <v>1.5</v>
+      </c>
+      <c r="AP277">
+        <v>2</v>
+      </c>
+      <c r="AQ277">
+        <v>1.67</v>
+      </c>
+      <c r="AR277">
+        <v>1.94</v>
+      </c>
+      <c r="AS277">
+        <v>1.67</v>
+      </c>
+      <c r="AT277">
+        <v>3.61</v>
+      </c>
+      <c r="AU277">
+        <v>6</v>
+      </c>
+      <c r="AV277">
+        <v>9</v>
+      </c>
+      <c r="AW277">
         <v>10</v>
       </c>
-      <c r="AE277">
-        <v>1.18</v>
-      </c>
-      <c r="AF277">
-        <v>4.75</v>
-      </c>
-      <c r="AG277">
-        <v>1.67</v>
-      </c>
-      <c r="AH277">
-        <v>2.21</v>
-      </c>
-      <c r="AI277">
-        <v>1.5</v>
-      </c>
-      <c r="AJ277">
-        <v>2.5</v>
-      </c>
-      <c r="AK277">
-        <v>1.35</v>
-      </c>
-      <c r="AL277">
-        <v>1.22</v>
-      </c>
-      <c r="AM277">
-        <v>1.67</v>
-      </c>
-      <c r="AN277">
-        <v>0.71</v>
-      </c>
-      <c r="AO277">
-        <v>1.22</v>
-      </c>
-      <c r="AP277">
-        <v>0.63</v>
-      </c>
-      <c r="AQ277">
-        <v>1.4</v>
-      </c>
-      <c r="AR277">
-        <v>1.17</v>
-      </c>
-      <c r="AS277">
-        <v>1.76</v>
-      </c>
-      <c r="AT277">
-        <v>2.93</v>
-      </c>
-      <c r="AU277">
-        <v>9</v>
-      </c>
-      <c r="AV277">
+      <c r="AX277">
+        <v>1</v>
+      </c>
+      <c r="AY277">
         <v>16</v>
       </c>
-      <c r="AW277">
-        <v>4</v>
-      </c>
-      <c r="AX277">
-        <v>6</v>
-      </c>
-      <c r="AY277">
-        <v>13</v>
-      </c>
       <c r="AZ277">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="BA277">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB277">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BC277">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD277">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BE277">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BF277">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BG277">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BH277">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BI277">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BJ277">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BK277">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BL277">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BM277">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="BN277">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BO277">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BP277">
-        <v>1.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278" spans="1:68">
@@ -58693,7 +58693,7 @@
         <v>277</v>
       </c>
       <c r="B278">
-        <v>7781355</v>
+        <v>7781353</v>
       </c>
       <c r="C278" t="s">
         <v>68</v>
@@ -58702,196 +58702,196 @@
         <v>69</v>
       </c>
       <c r="E278" s="2">
-        <v>45833.97916666666</v>
+        <v>45834.02847222222</v>
       </c>
       <c r="F278">
         <v>0</v>
       </c>
       <c r="G278" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H278" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I278">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J278">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K278">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L278">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M278">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N278">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O278" t="s">
         <v>286</v>
       </c>
       <c r="P278" t="s">
-        <v>415</v>
+        <v>109</v>
       </c>
       <c r="Q278">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R278">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S278">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T278">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="U278">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V278">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="W278">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X278">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Y278">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z278">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AA278">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="AB278">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="AC278">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AD278">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE278">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF278">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AG278">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AH278">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="AI278">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AJ278">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AK278">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL278">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AM278">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AN278">
-        <v>2.22</v>
+        <v>1.4</v>
       </c>
       <c r="AO278">
+        <v>0.3</v>
+      </c>
+      <c r="AP278">
+        <v>1.55</v>
+      </c>
+      <c r="AQ278">
+        <v>0.27</v>
+      </c>
+      <c r="AR278">
+        <v>1.57</v>
+      </c>
+      <c r="AS278">
+        <v>1.28</v>
+      </c>
+      <c r="AT278">
+        <v>2.85</v>
+      </c>
+      <c r="AU278">
+        <v>5</v>
+      </c>
+      <c r="AV278">
+        <v>2</v>
+      </c>
+      <c r="AW278">
+        <v>0</v>
+      </c>
+      <c r="AX278">
+        <v>1</v>
+      </c>
+      <c r="AY278">
+        <v>5</v>
+      </c>
+      <c r="AZ278">
+        <v>3</v>
+      </c>
+      <c r="BA278">
+        <v>0</v>
+      </c>
+      <c r="BB278">
+        <v>5</v>
+      </c>
+      <c r="BC278">
+        <v>5</v>
+      </c>
+      <c r="BD278">
+        <v>1.71</v>
+      </c>
+      <c r="BE278">
+        <v>6.4</v>
+      </c>
+      <c r="BF278">
+        <v>2.4</v>
+      </c>
+      <c r="BG278">
+        <v>1.29</v>
+      </c>
+      <c r="BH278">
+        <v>3.15</v>
+      </c>
+      <c r="BI278">
         <v>1.5</v>
       </c>
-      <c r="AP278">
-        <v>2</v>
-      </c>
-      <c r="AQ278">
-        <v>1.67</v>
-      </c>
-      <c r="AR278">
-        <v>1.94</v>
-      </c>
-      <c r="AS278">
-        <v>1.67</v>
-      </c>
-      <c r="AT278">
-        <v>3.61</v>
-      </c>
-      <c r="AU278">
-        <v>6</v>
-      </c>
-      <c r="AV278">
-        <v>9</v>
-      </c>
-      <c r="AW278">
-        <v>10</v>
-      </c>
-      <c r="AX278">
-        <v>1</v>
-      </c>
-      <c r="AY278">
-        <v>16</v>
-      </c>
-      <c r="AZ278">
-        <v>10</v>
-      </c>
-      <c r="BA278">
-        <v>7</v>
-      </c>
-      <c r="BB278">
-        <v>3</v>
-      </c>
-      <c r="BC278">
-        <v>10</v>
-      </c>
-      <c r="BD278">
-        <v>0</v>
-      </c>
-      <c r="BE278">
-        <v>0</v>
-      </c>
-      <c r="BF278">
-        <v>0</v>
-      </c>
-      <c r="BG278">
-        <v>0</v>
-      </c>
-      <c r="BH278">
-        <v>0</v>
-      </c>
-      <c r="BI278">
-        <v>0</v>
-      </c>
       <c r="BJ278">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BK278">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BL278">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BM278">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BN278">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BO278">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BP278">
-        <v>0</v>
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="429">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -877,6 +877,33 @@
     <t>['24', '28']</t>
   </si>
   <si>
+    <t>['87']</t>
+  </si>
+  <si>
+    <t>['11', '56']</t>
+  </si>
+  <si>
+    <t>['86', '9003']</t>
+  </si>
+  <si>
+    <t>['11', '90']</t>
+  </si>
+  <si>
+    <t>['22']</t>
+  </si>
+  <si>
+    <t>['23', '25', '33']</t>
+  </si>
+  <si>
+    <t>['44', '56']</t>
+  </si>
+  <si>
+    <t>['66']</t>
+  </si>
+  <si>
+    <t>['59']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -1060,9 +1087,6 @@
     <t>['38', '53', '63', '76']</t>
   </si>
   <si>
-    <t>['66']</t>
-  </si>
-  <si>
     <t>['11', '27']</t>
   </si>
   <si>
@@ -1133,9 +1157,6 @@
   </si>
   <si>
     <t>['6']</t>
-  </si>
-  <si>
-    <t>['59']</t>
   </si>
   <si>
     <t>['42', '60', '63', '79']</t>
@@ -1262,6 +1283,24 @@
   </si>
   <si>
     <t>['35', '37', '44', '47', '90']</t>
+  </si>
+  <si>
+    <t>['4504', '74']</t>
+  </si>
+  <si>
+    <t>['29', '40', '55']</t>
+  </si>
+  <si>
+    <t>['32', '45']</t>
+  </si>
+  <si>
+    <t>['56', '59']</t>
+  </si>
+  <si>
+    <t>['26', '77', '9006']</t>
+  </si>
+  <si>
+    <t>['4501']</t>
   </si>
 </sst>
 </file>
@@ -1623,7 +1662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP278"/>
+  <dimension ref="A1:BP288"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1960,7 +1999,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ2">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2085,7 +2124,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -2166,7 +2205,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ3">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2291,7 +2330,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2703,7 +2742,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2909,7 +2948,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -2987,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ7">
         <v>1.14</v>
@@ -3115,7 +3154,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -3193,7 +3232,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ8">
         <v>2.11</v>
@@ -3527,7 +3566,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -3605,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ10">
         <v>1.6</v>
@@ -4020,7 +4059,7 @@
         <v>1</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4226,7 +4265,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ13">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4351,7 +4390,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -4432,7 +4471,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ14">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4557,7 +4596,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4763,7 +4802,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4844,7 +4883,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ16">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5459,7 +5498,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ19">
         <v>1.5</v>
@@ -5665,10 +5704,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ20">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5793,7 +5832,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -5871,7 +5910,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ21">
         <v>1.14</v>
@@ -6080,7 +6119,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ22">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6205,7 +6244,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6283,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ23">
         <v>0.89</v>
@@ -6411,7 +6450,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6489,7 +6528,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ24">
         <v>1.4</v>
@@ -6823,7 +6862,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -7110,7 +7149,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ27">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR27">
         <v>1.64</v>
@@ -7522,7 +7561,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ29">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -7853,7 +7892,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7931,7 +7970,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ31">
         <v>1.71</v>
@@ -8265,7 +8304,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -8961,7 +9000,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ36">
         <v>0.8</v>
@@ -9089,7 +9128,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9167,7 +9206,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ37">
         <v>2.11</v>
@@ -9582,7 +9621,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ39">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR39">
         <v>1.5</v>
@@ -9707,7 +9746,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9785,7 +9824,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ40">
         <v>1.8</v>
@@ -9994,7 +10033,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ41">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR41">
         <v>1.65</v>
@@ -10119,7 +10158,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -10200,7 +10239,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ42">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR42">
         <v>1.41</v>
@@ -10612,7 +10651,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ44">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR44">
         <v>1.88</v>
@@ -10818,7 +10857,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ45">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR45">
         <v>1.62</v>
@@ -10943,7 +10982,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -11024,7 +11063,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ46">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR46">
         <v>0.92</v>
@@ -11149,7 +11188,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -11227,7 +11266,7 @@
         <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ47">
         <v>1.8</v>
@@ -11355,7 +11394,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11433,7 +11472,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ48">
         <v>1.6</v>
@@ -11848,7 +11887,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ50">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR50">
         <v>1.3</v>
@@ -12051,7 +12090,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ51">
         <v>0.73</v>
@@ -12179,7 +12218,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12385,7 +12424,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12463,10 +12502,10 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ53">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR53">
         <v>1.56</v>
@@ -12669,7 +12708,7 @@
         <v>3</v>
       </c>
       <c r="AP54">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ54">
         <v>1.88</v>
@@ -12797,7 +12836,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -12875,10 +12914,10 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ55">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR55">
         <v>1.22</v>
@@ -13415,7 +13454,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13496,7 +13535,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ58">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR58">
         <v>1.87</v>
@@ -13621,7 +13660,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13702,7 +13741,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ59">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR59">
         <v>1.65</v>
@@ -14033,7 +14072,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14239,7 +14278,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -14445,7 +14484,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14651,7 +14690,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -14938,7 +14977,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ65">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR65">
         <v>1.71</v>
@@ -15141,7 +15180,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ66">
         <v>1.14</v>
@@ -15347,7 +15386,7 @@
         <v>1</v>
       </c>
       <c r="AP67">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ67">
         <v>0.89</v>
@@ -15556,7 +15595,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ68">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR68">
         <v>1.48</v>
@@ -15681,7 +15720,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15759,7 +15798,7 @@
         <v>0</v>
       </c>
       <c r="AP69">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ69">
         <v>0.88</v>
@@ -16093,7 +16132,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16174,7 +16213,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ71">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR71">
         <v>1.88</v>
@@ -16299,7 +16338,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16711,7 +16750,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16998,7 +17037,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ75">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR75">
         <v>1.74</v>
@@ -17123,7 +17162,7 @@
         <v>153</v>
       </c>
       <c r="P76" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="Q76">
         <v>3.6</v>
@@ -17201,7 +17240,7 @@
         <v>0.5</v>
       </c>
       <c r="AP76">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ76">
         <v>0.6</v>
@@ -17407,7 +17446,7 @@
         <v>3</v>
       </c>
       <c r="AP77">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ77">
         <v>1.88</v>
@@ -17616,7 +17655,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ78">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR78">
         <v>1.49</v>
@@ -17947,7 +17986,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18025,7 +18064,7 @@
         <v>2</v>
       </c>
       <c r="AP80">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ80">
         <v>1.5</v>
@@ -18153,7 +18192,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18234,7 +18273,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ81">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR81">
         <v>1.62</v>
@@ -18359,7 +18398,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -18437,7 +18476,7 @@
         <v>0.2</v>
       </c>
       <c r="AP82">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ82">
         <v>0.73</v>
@@ -18643,7 +18682,7 @@
         <v>0</v>
       </c>
       <c r="AP83">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ83">
         <v>0.8</v>
@@ -18852,7 +18891,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ84">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR84">
         <v>1.92</v>
@@ -18977,7 +19016,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -19058,7 +19097,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ85">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR85">
         <v>1.87</v>
@@ -19183,7 +19222,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -19389,7 +19428,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -20007,7 +20046,7 @@
         <v>164</v>
       </c>
       <c r="P90" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
@@ -20294,7 +20333,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ91">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR91">
         <v>1.64</v>
@@ -21243,7 +21282,7 @@
         <v>168</v>
       </c>
       <c r="P96" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21527,7 +21566,7 @@
         <v>2.25</v>
       </c>
       <c r="AP97">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ97">
         <v>1.8</v>
@@ -21736,7 +21775,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ98">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR98">
         <v>1.57</v>
@@ -21939,10 +21978,10 @@
         <v>1.33</v>
       </c>
       <c r="AP99">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ99">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR99">
         <v>1.7</v>
@@ -22145,7 +22184,7 @@
         <v>1</v>
       </c>
       <c r="AP100">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ100">
         <v>0.88</v>
@@ -22354,7 +22393,7 @@
         <v>2</v>
       </c>
       <c r="AQ101">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR101">
         <v>1.75</v>
@@ -22685,7 +22724,7 @@
         <v>122</v>
       </c>
       <c r="P103" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="Q103">
         <v>2.75</v>
@@ -22766,7 +22805,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ103">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR103">
         <v>1.61</v>
@@ -22891,7 +22930,7 @@
         <v>173</v>
       </c>
       <c r="P104" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="Q104">
         <v>2.75</v>
@@ -23097,7 +23136,7 @@
         <v>174</v>
       </c>
       <c r="P105" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="Q105">
         <v>1.91</v>
@@ -23381,10 +23420,10 @@
         <v>1.75</v>
       </c>
       <c r="AP106">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ106">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR106">
         <v>1.03</v>
@@ -23793,7 +23832,7 @@
         <v>0.33</v>
       </c>
       <c r="AP108">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ108">
         <v>0.6</v>
@@ -23999,10 +24038,10 @@
         <v>0.33</v>
       </c>
       <c r="AP109">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="AQ109">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR109">
         <v>0</v>
@@ -24333,7 +24372,7 @@
         <v>109</v>
       </c>
       <c r="P111" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="Q111">
         <v>2.88</v>
@@ -24411,10 +24450,10 @@
         <v>1</v>
       </c>
       <c r="AP111">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ111">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR111">
         <v>1.53</v>
@@ -24823,7 +24862,7 @@
         <v>0.25</v>
       </c>
       <c r="AP113">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ113">
         <v>0.9</v>
@@ -24951,7 +24990,7 @@
         <v>177</v>
       </c>
       <c r="P114" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25032,7 +25071,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ114">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR114">
         <v>1.81</v>
@@ -25157,7 +25196,7 @@
         <v>178</v>
       </c>
       <c r="P115" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -25238,7 +25277,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ115">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR115">
         <v>1.76</v>
@@ -25569,7 +25608,7 @@
         <v>179</v>
       </c>
       <c r="P117" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25775,7 +25814,7 @@
         <v>180</v>
       </c>
       <c r="P118" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25853,10 +25892,10 @@
         <v>1.33</v>
       </c>
       <c r="AP118">
+        <v>1.2</v>
+      </c>
+      <c r="AQ118">
         <v>1.22</v>
-      </c>
-      <c r="AQ118">
-        <v>1.38</v>
       </c>
       <c r="AR118">
         <v>1.68</v>
@@ -26059,7 +26098,7 @@
         <v>3</v>
       </c>
       <c r="AP119">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ119">
         <v>1.71</v>
@@ -26187,7 +26226,7 @@
         <v>181</v>
       </c>
       <c r="P120" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -26599,7 +26638,7 @@
         <v>109</v>
       </c>
       <c r="P122" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="Q122">
         <v>2.75</v>
@@ -26886,7 +26925,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ123">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR123">
         <v>1.96</v>
@@ -27011,7 +27050,7 @@
         <v>129</v>
       </c>
       <c r="P124" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="Q124">
         <v>2.5</v>
@@ -27089,7 +27128,7 @@
         <v>0.33</v>
       </c>
       <c r="AP124">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ124">
         <v>0.89</v>
@@ -27501,7 +27540,7 @@
         <v>1.25</v>
       </c>
       <c r="AP126">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="AQ126">
         <v>1.6</v>
@@ -27707,10 +27746,10 @@
         <v>0.5</v>
       </c>
       <c r="AP127">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ127">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR127">
         <v>1.21</v>
@@ -27916,7 +27955,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ128">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR128">
         <v>1.53</v>
@@ -28041,7 +28080,7 @@
         <v>187</v>
       </c>
       <c r="P129" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28119,10 +28158,10 @@
         <v>1.5</v>
       </c>
       <c r="AP129">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ129">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR129">
         <v>1.29</v>
@@ -28247,7 +28286,7 @@
         <v>188</v>
       </c>
       <c r="P130" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="Q130">
         <v>2.4</v>
@@ -28325,10 +28364,10 @@
         <v>1.75</v>
       </c>
       <c r="AP130">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ130">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR130">
         <v>1.45</v>
@@ -29071,7 +29110,7 @@
         <v>189</v>
       </c>
       <c r="P134" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="Q134">
         <v>3</v>
@@ -29277,7 +29316,7 @@
         <v>190</v>
       </c>
       <c r="P135" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -29767,10 +29806,10 @@
         <v>0.4</v>
       </c>
       <c r="AP137">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ137">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR137">
         <v>1.09</v>
@@ -30179,7 +30218,7 @@
         <v>0.29</v>
       </c>
       <c r="AP139">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ139">
         <v>0.73</v>
@@ -30385,7 +30424,7 @@
         <v>0.33</v>
       </c>
       <c r="AP140">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ140">
         <v>0.22</v>
@@ -30513,7 +30552,7 @@
         <v>109</v>
       </c>
       <c r="P141" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="Q141">
         <v>2.38</v>
@@ -30925,7 +30964,7 @@
         <v>174</v>
       </c>
       <c r="P143" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -31006,7 +31045,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ143">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR143">
         <v>1.8</v>
@@ -31209,7 +31248,7 @@
         <v>1.5</v>
       </c>
       <c r="AP144">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ144">
         <v>1.11</v>
@@ -31337,7 +31376,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="Q145">
         <v>2.4</v>
@@ -31543,7 +31582,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31749,7 +31788,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="Q147">
         <v>2.6</v>
@@ -31955,7 +31994,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="Q148">
         <v>2.05</v>
@@ -32161,7 +32200,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -32242,7 +32281,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ149">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR149">
         <v>1.48</v>
@@ -32367,7 +32406,7 @@
         <v>202</v>
       </c>
       <c r="P150" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="Q150">
         <v>2.4</v>
@@ -32448,7 +32487,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ150">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR150">
         <v>1.41</v>
@@ -32573,7 +32612,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>348</v>
+        <v>294</v>
       </c>
       <c r="Q151">
         <v>2.63</v>
@@ -32654,7 +32693,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ151">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR151">
         <v>1.66</v>
@@ -32779,7 +32818,7 @@
         <v>109</v>
       </c>
       <c r="P152" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="Q152">
         <v>2.88</v>
@@ -32857,7 +32896,7 @@
         <v>1.4</v>
       </c>
       <c r="AP152">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ152">
         <v>1.6</v>
@@ -32985,7 +33024,7 @@
         <v>204</v>
       </c>
       <c r="P153" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -33191,7 +33230,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="Q154">
         <v>3.1</v>
@@ -33269,7 +33308,7 @@
         <v>1.5</v>
       </c>
       <c r="AP154">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="AQ154">
         <v>2.11</v>
@@ -33397,7 +33436,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="Q155">
         <v>2.2</v>
@@ -33478,7 +33517,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ155">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR155">
         <v>1.65</v>
@@ -33603,7 +33642,7 @@
         <v>207</v>
       </c>
       <c r="P156" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33681,10 +33720,10 @@
         <v>1.6</v>
       </c>
       <c r="AP156">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ156">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR156">
         <v>1.51</v>
@@ -33809,7 +33848,7 @@
         <v>109</v>
       </c>
       <c r="P157" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="Q157">
         <v>3.2</v>
@@ -33890,7 +33929,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ157">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR157">
         <v>1.56</v>
@@ -34093,7 +34132,7 @@
         <v>1.2</v>
       </c>
       <c r="AP158">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ158">
         <v>1.6</v>
@@ -34427,7 +34466,7 @@
         <v>209</v>
       </c>
       <c r="P160" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="Q160">
         <v>2.1</v>
@@ -34508,7 +34547,7 @@
         <v>2</v>
       </c>
       <c r="AQ160">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR160">
         <v>1.99</v>
@@ -34839,7 +34878,7 @@
         <v>211</v>
       </c>
       <c r="P162" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="Q162">
         <v>2.5</v>
@@ -34920,7 +34959,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ162">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR162">
         <v>2.1</v>
@@ -35126,7 +35165,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ163">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR163">
         <v>1.87</v>
@@ -35332,7 +35371,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ164">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR164">
         <v>1.81</v>
@@ -35535,7 +35574,7 @@
         <v>0.4</v>
       </c>
       <c r="AP165">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ165">
         <v>0.27</v>
@@ -35741,7 +35780,7 @@
         <v>0.25</v>
       </c>
       <c r="AP166">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ166">
         <v>0.22</v>
@@ -35869,7 +35908,7 @@
         <v>215</v>
       </c>
       <c r="P167" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -36153,7 +36192,7 @@
         <v>0.8</v>
       </c>
       <c r="AP168">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ168">
         <v>0.89</v>
@@ -36281,7 +36320,7 @@
         <v>217</v>
       </c>
       <c r="P169" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="Q169">
         <v>3</v>
@@ -36487,7 +36526,7 @@
         <v>218</v>
       </c>
       <c r="P170" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36565,7 +36604,7 @@
         <v>1.67</v>
       </c>
       <c r="AP170">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ170">
         <v>1.6</v>
@@ -36693,7 +36732,7 @@
         <v>109</v>
       </c>
       <c r="P171" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Q171">
         <v>2.25</v>
@@ -36899,7 +36938,7 @@
         <v>219</v>
       </c>
       <c r="P172" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Q172">
         <v>2.4</v>
@@ -37183,7 +37222,7 @@
         <v>0.33</v>
       </c>
       <c r="AP173">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ173">
         <v>0.27</v>
@@ -37311,7 +37350,7 @@
         <v>221</v>
       </c>
       <c r="P174" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="Q174">
         <v>2.5</v>
@@ -37389,10 +37428,10 @@
         <v>1</v>
       </c>
       <c r="AP174">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ174">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR174">
         <v>1.03</v>
@@ -37517,7 +37556,7 @@
         <v>163</v>
       </c>
       <c r="P175" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -37595,7 +37634,7 @@
         <v>0.83</v>
       </c>
       <c r="AP175">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ175">
         <v>0.9</v>
@@ -37723,7 +37762,7 @@
         <v>113</v>
       </c>
       <c r="P176" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Q176">
         <v>2.4</v>
@@ -37804,7 +37843,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ176">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR176">
         <v>1.93</v>
@@ -37929,7 +37968,7 @@
         <v>222</v>
       </c>
       <c r="P177" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -38010,7 +38049,7 @@
         <v>1</v>
       </c>
       <c r="AQ177">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR177">
         <v>1.66</v>
@@ -38135,7 +38174,7 @@
         <v>109</v>
       </c>
       <c r="P178" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="Q178">
         <v>2.38</v>
@@ -38547,7 +38586,7 @@
         <v>224</v>
       </c>
       <c r="P180" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38831,10 +38870,10 @@
         <v>0.83</v>
       </c>
       <c r="AP181">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ181">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR181">
         <v>1.42</v>
@@ -38959,7 +38998,7 @@
         <v>225</v>
       </c>
       <c r="P182" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="Q182">
         <v>3.75</v>
@@ -39037,7 +39076,7 @@
         <v>2.2</v>
       </c>
       <c r="AP182">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="AQ182">
         <v>1.5</v>
@@ -39165,7 +39204,7 @@
         <v>226</v>
       </c>
       <c r="P183" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="Q183">
         <v>2.5</v>
@@ -39243,10 +39282,10 @@
         <v>0.67</v>
       </c>
       <c r="AP183">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ183">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR183">
         <v>1.98</v>
@@ -39371,7 +39410,7 @@
         <v>227</v>
       </c>
       <c r="P184" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="Q184">
         <v>2.05</v>
@@ -39655,10 +39694,10 @@
         <v>1.5</v>
       </c>
       <c r="AP185">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ185">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR185">
         <v>1.44</v>
@@ -39783,7 +39822,7 @@
         <v>228</v>
       </c>
       <c r="P186" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="Q186">
         <v>2.4</v>
@@ -40067,10 +40106,10 @@
         <v>1.83</v>
       </c>
       <c r="AP187">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ187">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR187">
         <v>1.64</v>
@@ -40195,7 +40234,7 @@
         <v>230</v>
       </c>
       <c r="P188" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40401,7 +40440,7 @@
         <v>176</v>
       </c>
       <c r="P189" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40688,7 +40727,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ190">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR190">
         <v>1.5</v>
@@ -41100,7 +41139,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ192">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR192">
         <v>1.75</v>
@@ -41225,7 +41264,7 @@
         <v>233</v>
       </c>
       <c r="P193" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41431,7 +41470,7 @@
         <v>234</v>
       </c>
       <c r="P194" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41509,7 +41548,7 @@
         <v>0.83</v>
       </c>
       <c r="AP194">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="AQ194">
         <v>1.14</v>
@@ -41843,7 +41882,7 @@
         <v>198</v>
       </c>
       <c r="P196" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="Q196">
         <v>2.63</v>
@@ -41924,7 +41963,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ196">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR196">
         <v>1.74</v>
@@ -42049,7 +42088,7 @@
         <v>109</v>
       </c>
       <c r="P197" t="s">
-        <v>373</v>
+        <v>295</v>
       </c>
       <c r="Q197">
         <v>2.75</v>
@@ -42255,7 +42294,7 @@
         <v>103</v>
       </c>
       <c r="P198" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="Q198">
         <v>2.63</v>
@@ -42539,7 +42578,7 @@
         <v>1.2</v>
       </c>
       <c r="AP199">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ199">
         <v>1.4</v>
@@ -42748,7 +42787,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ200">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR200">
         <v>1.69</v>
@@ -43285,7 +43324,7 @@
         <v>109</v>
       </c>
       <c r="P203" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="Q203">
         <v>2.63</v>
@@ -43363,7 +43402,7 @@
         <v>0.6</v>
       </c>
       <c r="AP203">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ203">
         <v>1.11</v>
@@ -43572,7 +43611,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ204">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR204">
         <v>1.79</v>
@@ -43697,7 +43736,7 @@
         <v>237</v>
       </c>
       <c r="P205" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -44109,7 +44148,7 @@
         <v>109</v>
       </c>
       <c r="P207" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="Q207">
         <v>2.25</v>
@@ -44933,7 +44972,7 @@
         <v>240</v>
       </c>
       <c r="P211" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="Q211">
         <v>3.2</v>
@@ -45139,7 +45178,7 @@
         <v>109</v>
       </c>
       <c r="P212" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45217,7 +45256,7 @@
         <v>0.29</v>
       </c>
       <c r="AP212">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ212">
         <v>0.6</v>
@@ -45345,7 +45384,7 @@
         <v>241</v>
       </c>
       <c r="P213" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="Q213">
         <v>4</v>
@@ -45423,7 +45462,7 @@
         <v>0.86</v>
       </c>
       <c r="AP213">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="AQ213">
         <v>0.88</v>
@@ -45629,10 +45668,10 @@
         <v>1.57</v>
       </c>
       <c r="AP214">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ214">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR214">
         <v>1.93</v>
@@ -45757,7 +45796,7 @@
         <v>242</v>
       </c>
       <c r="P215" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -45963,7 +46002,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="Q216">
         <v>3.4</v>
@@ -46041,10 +46080,10 @@
         <v>0.8</v>
       </c>
       <c r="AP216">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ216">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR216">
         <v>1.44</v>
@@ -46169,7 +46208,7 @@
         <v>243</v>
       </c>
       <c r="P217" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="Q217">
         <v>2.75</v>
@@ -46247,7 +46286,7 @@
         <v>1.57</v>
       </c>
       <c r="AP217">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ217">
         <v>1.6</v>
@@ -46581,7 +46620,7 @@
         <v>244</v>
       </c>
       <c r="P219" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="Q219">
         <v>3.1</v>
@@ -46868,7 +46907,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ220">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR220">
         <v>1.69</v>
@@ -46993,7 +47032,7 @@
         <v>246</v>
       </c>
       <c r="P221" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="Q221">
         <v>2.6</v>
@@ -47199,7 +47238,7 @@
         <v>247</v>
       </c>
       <c r="P222" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="Q222">
         <v>2.5</v>
@@ -47405,7 +47444,7 @@
         <v>248</v>
       </c>
       <c r="P223" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47486,7 +47525,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ223">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR223">
         <v>1.57</v>
@@ -47611,7 +47650,7 @@
         <v>249</v>
       </c>
       <c r="P224" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47817,7 +47856,7 @@
         <v>250</v>
       </c>
       <c r="P225" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -48023,7 +48062,7 @@
         <v>251</v>
       </c>
       <c r="P226" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="Q226">
         <v>2.75</v>
@@ -48101,7 +48140,7 @@
         <v>1.5</v>
       </c>
       <c r="AP226">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ226">
         <v>1.6</v>
@@ -48229,7 +48268,7 @@
         <v>252</v>
       </c>
       <c r="P227" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="Q227">
         <v>1.83</v>
@@ -48435,7 +48474,7 @@
         <v>253</v>
       </c>
       <c r="P228" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48513,10 +48552,10 @@
         <v>0.57</v>
       </c>
       <c r="AP228">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ228">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR228">
         <v>1.63</v>
@@ -48641,7 +48680,7 @@
         <v>109</v>
       </c>
       <c r="P229" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="Q229">
         <v>2.5</v>
@@ -48847,7 +48886,7 @@
         <v>254</v>
       </c>
       <c r="P230" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="Q230">
         <v>3.25</v>
@@ -48925,7 +48964,7 @@
         <v>2</v>
       </c>
       <c r="AP230">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ230">
         <v>2.11</v>
@@ -49053,7 +49092,7 @@
         <v>119</v>
       </c>
       <c r="P231" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="Q231">
         <v>2.4</v>
@@ -49134,7 +49173,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ231">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR231">
         <v>1.85</v>
@@ -49340,7 +49379,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ232">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR232">
         <v>1.98</v>
@@ -49546,7 +49585,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ233">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR233">
         <v>1.67</v>
@@ -49671,7 +49710,7 @@
         <v>109</v>
       </c>
       <c r="P234" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="Q234">
         <v>2.5</v>
@@ -49958,7 +49997,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ235">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR235">
         <v>1.24</v>
@@ -50164,7 +50203,7 @@
         <v>2</v>
       </c>
       <c r="AQ236">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR236">
         <v>1.96</v>
@@ -50289,7 +50328,7 @@
         <v>258</v>
       </c>
       <c r="P237" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="Q237">
         <v>2.75</v>
@@ -50495,7 +50534,7 @@
         <v>259</v>
       </c>
       <c r="P238" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="Q238">
         <v>2.6</v>
@@ -50576,7 +50615,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ238">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR238">
         <v>1.87</v>
@@ -50701,7 +50740,7 @@
         <v>109</v>
       </c>
       <c r="P239" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -50779,10 +50818,10 @@
         <v>0.5</v>
       </c>
       <c r="AP239">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ239">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR239">
         <v>1.42</v>
@@ -50907,7 +50946,7 @@
         <v>140</v>
       </c>
       <c r="P240" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -51319,7 +51358,7 @@
         <v>109</v>
       </c>
       <c r="P242" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="Q242">
         <v>3.1</v>
@@ -51397,7 +51436,7 @@
         <v>1.44</v>
       </c>
       <c r="AP242">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="AQ242">
         <v>1.6</v>
@@ -51603,7 +51642,7 @@
         <v>0.33</v>
       </c>
       <c r="AP243">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ243">
         <v>0.22</v>
@@ -51731,7 +51770,7 @@
         <v>161</v>
       </c>
       <c r="P244" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="Q244">
         <v>2.1</v>
@@ -51809,7 +51848,7 @@
         <v>1.5</v>
       </c>
       <c r="AP244">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AQ244">
         <v>1.8</v>
@@ -52015,7 +52054,7 @@
         <v>2.14</v>
       </c>
       <c r="AP245">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ245">
         <v>2.11</v>
@@ -52143,7 +52182,7 @@
         <v>156</v>
       </c>
       <c r="P246" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="Q246">
         <v>2.5</v>
@@ -52221,7 +52260,7 @@
         <v>0.63</v>
       </c>
       <c r="AP246">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ246">
         <v>0.8</v>
@@ -52430,7 +52469,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ247">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AR247">
         <v>1.45</v>
@@ -52761,7 +52800,7 @@
         <v>176</v>
       </c>
       <c r="P249" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="Q249">
         <v>2.5</v>
@@ -52842,7 +52881,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ249">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR249">
         <v>1.98</v>
@@ -52967,7 +53006,7 @@
         <v>264</v>
       </c>
       <c r="P250" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="Q250">
         <v>3.2</v>
@@ -53045,7 +53084,7 @@
         <v>1.67</v>
       </c>
       <c r="AP250">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ250">
         <v>1.8</v>
@@ -53173,7 +53212,7 @@
         <v>109</v>
       </c>
       <c r="P251" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="Q251">
         <v>2.75</v>
@@ -53379,7 +53418,7 @@
         <v>265</v>
       </c>
       <c r="P252" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="Q252">
         <v>2.25</v>
@@ -53460,7 +53499,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ252">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR252">
         <v>1.24</v>
@@ -54409,7 +54448,7 @@
         <v>270</v>
       </c>
       <c r="P257" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="Q257">
         <v>2.63</v>
@@ -54615,7 +54654,7 @@
         <v>271</v>
       </c>
       <c r="P258" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="Q258">
         <v>2.3</v>
@@ -54821,7 +54860,7 @@
         <v>109</v>
       </c>
       <c r="P259" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="Q259">
         <v>3.1</v>
@@ -54899,10 +54938,10 @@
         <v>1.44</v>
       </c>
       <c r="AP259">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ259">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR259">
         <v>1.33</v>
@@ -55108,7 +55147,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ260">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR260">
         <v>1.87</v>
@@ -55233,7 +55272,7 @@
         <v>273</v>
       </c>
       <c r="P261" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -55314,7 +55353,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ261">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR261">
         <v>1.82</v>
@@ -55439,7 +55478,7 @@
         <v>274</v>
       </c>
       <c r="P262" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="Q262">
         <v>2.5</v>
@@ -55517,7 +55556,7 @@
         <v>1.44</v>
       </c>
       <c r="AP262">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ262">
         <v>1.6</v>
@@ -55645,7 +55684,7 @@
         <v>234</v>
       </c>
       <c r="P263" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="Q263">
         <v>2.25</v>
@@ -55723,7 +55762,7 @@
         <v>0.5</v>
       </c>
       <c r="AP263">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ263">
         <v>0.73</v>
@@ -55851,7 +55890,7 @@
         <v>109</v>
       </c>
       <c r="P264" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="Q264">
         <v>2.75</v>
@@ -55929,10 +55968,10 @@
         <v>1.43</v>
       </c>
       <c r="AP264">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ264">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR264">
         <v>1.64</v>
@@ -56263,7 +56302,7 @@
         <v>109</v>
       </c>
       <c r="P266" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="Q266">
         <v>3.4</v>
@@ -56675,7 +56714,7 @@
         <v>277</v>
       </c>
       <c r="P268" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="Q268">
         <v>2.2</v>
@@ -56881,7 +56920,7 @@
         <v>278</v>
       </c>
       <c r="P269" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -56959,10 +56998,10 @@
         <v>1.6</v>
       </c>
       <c r="AP269">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="AQ269">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AR269">
         <v>1.55</v>
@@ -57087,7 +57126,7 @@
         <v>279</v>
       </c>
       <c r="P270" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="Q270">
         <v>3.35</v>
@@ -57165,10 +57204,10 @@
         <v>1.63</v>
       </c>
       <c r="AP270">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ270">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AR270">
         <v>1.36</v>
@@ -57371,7 +57410,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP271">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="AQ271">
         <v>0.6</v>
@@ -57499,7 +57538,7 @@
         <v>281</v>
       </c>
       <c r="P272" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="Q272">
         <v>2.38</v>
@@ -57705,7 +57744,7 @@
         <v>282</v>
       </c>
       <c r="P273" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="Q273">
         <v>3.4</v>
@@ -57911,7 +57950,7 @@
         <v>283</v>
       </c>
       <c r="P274" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="Q274">
         <v>3</v>
@@ -57989,10 +58028,10 @@
         <v>0.7</v>
       </c>
       <c r="AP274">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ274">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR274">
         <v>1.59</v>
@@ -58195,7 +58234,7 @@
         <v>2</v>
       </c>
       <c r="AP275">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ275">
         <v>2.11</v>
@@ -58323,7 +58362,7 @@
         <v>284</v>
       </c>
       <c r="P276" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="Q276">
         <v>2.63</v>
@@ -58401,7 +58440,7 @@
         <v>1.22</v>
       </c>
       <c r="AP276">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ276">
         <v>1.4</v>
@@ -58529,7 +58568,7 @@
         <v>285</v>
       </c>
       <c r="P277" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -58610,7 +58649,7 @@
         <v>2</v>
       </c>
       <c r="AQ277">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR277">
         <v>1.94</v>
@@ -58892,6 +58931,2066 @@
       </c>
       <c r="BP278">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="279" spans="1:68">
+      <c r="A279" s="1">
+        <v>278</v>
+      </c>
+      <c r="B279">
+        <v>7781361</v>
+      </c>
+      <c r="C279" t="s">
+        <v>68</v>
+      </c>
+      <c r="D279" t="s">
+        <v>69</v>
+      </c>
+      <c r="E279" s="2">
+        <v>45836.85416666666</v>
+      </c>
+      <c r="F279">
+        <v>0</v>
+      </c>
+      <c r="G279" t="s">
+        <v>76</v>
+      </c>
+      <c r="H279" t="s">
+        <v>73</v>
+      </c>
+      <c r="I279">
+        <v>0</v>
+      </c>
+      <c r="J279">
+        <v>1</v>
+      </c>
+      <c r="K279">
+        <v>1</v>
+      </c>
+      <c r="L279">
+        <v>1</v>
+      </c>
+      <c r="M279">
+        <v>2</v>
+      </c>
+      <c r="N279">
+        <v>3</v>
+      </c>
+      <c r="O279" t="s">
+        <v>287</v>
+      </c>
+      <c r="P279" t="s">
+        <v>423</v>
+      </c>
+      <c r="Q279">
+        <v>2.63</v>
+      </c>
+      <c r="R279">
+        <v>2.38</v>
+      </c>
+      <c r="S279">
+        <v>3.5</v>
+      </c>
+      <c r="T279">
+        <v>1.29</v>
+      </c>
+      <c r="U279">
+        <v>3.5</v>
+      </c>
+      <c r="V279">
+        <v>2.38</v>
+      </c>
+      <c r="W279">
+        <v>1.53</v>
+      </c>
+      <c r="X279">
+        <v>5.5</v>
+      </c>
+      <c r="Y279">
+        <v>1.14</v>
+      </c>
+      <c r="Z279">
+        <v>2.06</v>
+      </c>
+      <c r="AA279">
+        <v>3.08</v>
+      </c>
+      <c r="AB279">
+        <v>3.21</v>
+      </c>
+      <c r="AC279">
+        <v>1.04</v>
+      </c>
+      <c r="AD279">
+        <v>10</v>
+      </c>
+      <c r="AE279">
+        <v>1.2</v>
+      </c>
+      <c r="AF279">
+        <v>4.33</v>
+      </c>
+      <c r="AG279">
+        <v>1.54</v>
+      </c>
+      <c r="AH279">
+        <v>2.3</v>
+      </c>
+      <c r="AI279">
+        <v>1.5</v>
+      </c>
+      <c r="AJ279">
+        <v>2.5</v>
+      </c>
+      <c r="AK279">
+        <v>1.3</v>
+      </c>
+      <c r="AL279">
+        <v>1.25</v>
+      </c>
+      <c r="AM279">
+        <v>1.7</v>
+      </c>
+      <c r="AN279">
+        <v>1.89</v>
+      </c>
+      <c r="AO279">
+        <v>1.73</v>
+      </c>
+      <c r="AP279">
+        <v>1.7</v>
+      </c>
+      <c r="AQ279">
+        <v>1.83</v>
+      </c>
+      <c r="AR279">
+        <v>1.92</v>
+      </c>
+      <c r="AS279">
+        <v>1.66</v>
+      </c>
+      <c r="AT279">
+        <v>3.58</v>
+      </c>
+      <c r="AU279">
+        <v>4</v>
+      </c>
+      <c r="AV279">
+        <v>5</v>
+      </c>
+      <c r="AW279">
+        <v>7</v>
+      </c>
+      <c r="AX279">
+        <v>3</v>
+      </c>
+      <c r="AY279">
+        <v>11</v>
+      </c>
+      <c r="AZ279">
+        <v>8</v>
+      </c>
+      <c r="BA279">
+        <v>3</v>
+      </c>
+      <c r="BB279">
+        <v>2</v>
+      </c>
+      <c r="BC279">
+        <v>5</v>
+      </c>
+      <c r="BD279">
+        <v>1.68</v>
+      </c>
+      <c r="BE279">
+        <v>6.75</v>
+      </c>
+      <c r="BF279">
+        <v>2.4</v>
+      </c>
+      <c r="BG279">
+        <v>1.3</v>
+      </c>
+      <c r="BH279">
+        <v>3.15</v>
+      </c>
+      <c r="BI279">
+        <v>1.52</v>
+      </c>
+      <c r="BJ279">
+        <v>2.33</v>
+      </c>
+      <c r="BK279">
+        <v>1.84</v>
+      </c>
+      <c r="BL279">
+        <v>1.84</v>
+      </c>
+      <c r="BM279">
+        <v>2.3</v>
+      </c>
+      <c r="BN279">
+        <v>1.53</v>
+      </c>
+      <c r="BO279">
+        <v>2.95</v>
+      </c>
+      <c r="BP279">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="280" spans="1:68">
+      <c r="A280" s="1">
+        <v>279</v>
+      </c>
+      <c r="B280">
+        <v>7781362</v>
+      </c>
+      <c r="C280" t="s">
+        <v>68</v>
+      </c>
+      <c r="D280" t="s">
+        <v>69</v>
+      </c>
+      <c r="E280" s="2">
+        <v>45836.85416666666</v>
+      </c>
+      <c r="F280">
+        <v>0</v>
+      </c>
+      <c r="G280" t="s">
+        <v>98</v>
+      </c>
+      <c r="H280" t="s">
+        <v>83</v>
+      </c>
+      <c r="I280">
+        <v>1</v>
+      </c>
+      <c r="J280">
+        <v>0</v>
+      </c>
+      <c r="K280">
+        <v>1</v>
+      </c>
+      <c r="L280">
+        <v>2</v>
+      </c>
+      <c r="M280">
+        <v>0</v>
+      </c>
+      <c r="N280">
+        <v>2</v>
+      </c>
+      <c r="O280" t="s">
+        <v>288</v>
+      </c>
+      <c r="P280" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q280">
+        <v>3.5</v>
+      </c>
+      <c r="R280">
+        <v>2.25</v>
+      </c>
+      <c r="S280">
+        <v>2.88</v>
+      </c>
+      <c r="T280">
+        <v>1.33</v>
+      </c>
+      <c r="U280">
+        <v>3.25</v>
+      </c>
+      <c r="V280">
+        <v>2.63</v>
+      </c>
+      <c r="W280">
+        <v>1.44</v>
+      </c>
+      <c r="X280">
+        <v>7</v>
+      </c>
+      <c r="Y280">
+        <v>1.1</v>
+      </c>
+      <c r="Z280">
+        <v>3.02</v>
+      </c>
+      <c r="AA280">
+        <v>3.11</v>
+      </c>
+      <c r="AB280">
+        <v>2.14</v>
+      </c>
+      <c r="AC280">
+        <v>1.01</v>
+      </c>
+      <c r="AD280">
+        <v>8.9</v>
+      </c>
+      <c r="AE280">
+        <v>1.22</v>
+      </c>
+      <c r="AF280">
+        <v>3.64</v>
+      </c>
+      <c r="AG280">
+        <v>1.76</v>
+      </c>
+      <c r="AH280">
+        <v>1.94</v>
+      </c>
+      <c r="AI280">
+        <v>1.62</v>
+      </c>
+      <c r="AJ280">
+        <v>2.2</v>
+      </c>
+      <c r="AK280">
+        <v>1.62</v>
+      </c>
+      <c r="AL280">
+        <v>1.33</v>
+      </c>
+      <c r="AM280">
+        <v>1.38</v>
+      </c>
+      <c r="AN280">
+        <v>0.55</v>
+      </c>
+      <c r="AO280">
+        <v>1.38</v>
+      </c>
+      <c r="AP280">
+        <v>0.75</v>
+      </c>
+      <c r="AQ280">
+        <v>1.22</v>
+      </c>
+      <c r="AR280">
+        <v>1.3</v>
+      </c>
+      <c r="AS280">
+        <v>1.51</v>
+      </c>
+      <c r="AT280">
+        <v>2.81</v>
+      </c>
+      <c r="AU280">
+        <v>9</v>
+      </c>
+      <c r="AV280">
+        <v>0</v>
+      </c>
+      <c r="AW280">
+        <v>5</v>
+      </c>
+      <c r="AX280">
+        <v>3</v>
+      </c>
+      <c r="AY280">
+        <v>14</v>
+      </c>
+      <c r="AZ280">
+        <v>3</v>
+      </c>
+      <c r="BA280">
+        <v>9</v>
+      </c>
+      <c r="BB280">
+        <v>3</v>
+      </c>
+      <c r="BC280">
+        <v>12</v>
+      </c>
+      <c r="BD280">
+        <v>1.74</v>
+      </c>
+      <c r="BE280">
+        <v>6.5</v>
+      </c>
+      <c r="BF280">
+        <v>2.32</v>
+      </c>
+      <c r="BG280">
+        <v>1.33</v>
+      </c>
+      <c r="BH280">
+        <v>2.95</v>
+      </c>
+      <c r="BI280">
+        <v>1.56</v>
+      </c>
+      <c r="BJ280">
+        <v>2.23</v>
+      </c>
+      <c r="BK280">
+        <v>1.91</v>
+      </c>
+      <c r="BL280">
+        <v>1.78</v>
+      </c>
+      <c r="BM280">
+        <v>2.4</v>
+      </c>
+      <c r="BN280">
+        <v>1.49</v>
+      </c>
+      <c r="BO280">
+        <v>3.15</v>
+      </c>
+      <c r="BP280">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="281" spans="1:68">
+      <c r="A281" s="1">
+        <v>280</v>
+      </c>
+      <c r="B281">
+        <v>7781359</v>
+      </c>
+      <c r="C281" t="s">
+        <v>68</v>
+      </c>
+      <c r="D281" t="s">
+        <v>69</v>
+      </c>
+      <c r="E281" s="2">
+        <v>45836.85416666666</v>
+      </c>
+      <c r="F281">
+        <v>0</v>
+      </c>
+      <c r="G281" t="s">
+        <v>87</v>
+      </c>
+      <c r="H281" t="s">
+        <v>93</v>
+      </c>
+      <c r="I281">
+        <v>0</v>
+      </c>
+      <c r="J281">
+        <v>2</v>
+      </c>
+      <c r="K281">
+        <v>2</v>
+      </c>
+      <c r="L281">
+        <v>2</v>
+      </c>
+      <c r="M281">
+        <v>3</v>
+      </c>
+      <c r="N281">
+        <v>5</v>
+      </c>
+      <c r="O281" t="s">
+        <v>289</v>
+      </c>
+      <c r="P281" t="s">
+        <v>424</v>
+      </c>
+      <c r="Q281">
+        <v>2.25</v>
+      </c>
+      <c r="R281">
+        <v>2.2</v>
+      </c>
+      <c r="S281">
+        <v>5.5</v>
+      </c>
+      <c r="T281">
+        <v>1.4</v>
+      </c>
+      <c r="U281">
+        <v>2.75</v>
+      </c>
+      <c r="V281">
+        <v>2.75</v>
+      </c>
+      <c r="W281">
+        <v>1.4</v>
+      </c>
+      <c r="X281">
+        <v>8</v>
+      </c>
+      <c r="Y281">
+        <v>1.08</v>
+      </c>
+      <c r="Z281">
+        <v>1.62</v>
+      </c>
+      <c r="AA281">
+        <v>3.32</v>
+      </c>
+      <c r="AB281">
+        <v>4.9</v>
+      </c>
+      <c r="AC281">
+        <v>1.06</v>
+      </c>
+      <c r="AD281">
+        <v>8.5</v>
+      </c>
+      <c r="AE281">
+        <v>1.33</v>
+      </c>
+      <c r="AF281">
+        <v>3.25</v>
+      </c>
+      <c r="AG281">
+        <v>1.94</v>
+      </c>
+      <c r="AH281">
+        <v>1.76</v>
+      </c>
+      <c r="AI281">
+        <v>1.95</v>
+      </c>
+      <c r="AJ281">
+        <v>1.8</v>
+      </c>
+      <c r="AK281">
+        <v>1.15</v>
+      </c>
+      <c r="AL281">
+        <v>1.22</v>
+      </c>
+      <c r="AM281">
+        <v>2.15</v>
+      </c>
+      <c r="AN281">
+        <v>1</v>
+      </c>
+      <c r="AO281">
+        <v>1</v>
+      </c>
+      <c r="AP281">
+        <v>0.88</v>
+      </c>
+      <c r="AQ281">
+        <v>1.22</v>
+      </c>
+      <c r="AR281">
+        <v>1.36</v>
+      </c>
+      <c r="AS281">
+        <v>0.97</v>
+      </c>
+      <c r="AT281">
+        <v>2.33</v>
+      </c>
+      <c r="AU281">
+        <v>11</v>
+      </c>
+      <c r="AV281">
+        <v>5</v>
+      </c>
+      <c r="AW281">
+        <v>3</v>
+      </c>
+      <c r="AX281">
+        <v>1</v>
+      </c>
+      <c r="AY281">
+        <v>14</v>
+      </c>
+      <c r="AZ281">
+        <v>6</v>
+      </c>
+      <c r="BA281">
+        <v>11</v>
+      </c>
+      <c r="BB281">
+        <v>2</v>
+      </c>
+      <c r="BC281">
+        <v>13</v>
+      </c>
+      <c r="BD281">
+        <v>1.37</v>
+      </c>
+      <c r="BE281">
+        <v>7</v>
+      </c>
+      <c r="BF281">
+        <v>3.4</v>
+      </c>
+      <c r="BG281">
+        <v>1.35</v>
+      </c>
+      <c r="BH281">
+        <v>2.9</v>
+      </c>
+      <c r="BI281">
+        <v>1.6</v>
+      </c>
+      <c r="BJ281">
+        <v>2.17</v>
+      </c>
+      <c r="BK281">
+        <v>1.96</v>
+      </c>
+      <c r="BL281">
+        <v>1.73</v>
+      </c>
+      <c r="BM281">
+        <v>2.48</v>
+      </c>
+      <c r="BN281">
+        <v>1.47</v>
+      </c>
+      <c r="BO281">
+        <v>3.2</v>
+      </c>
+      <c r="BP281">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="282" spans="1:68">
+      <c r="A282" s="1">
+        <v>281</v>
+      </c>
+      <c r="B282">
+        <v>7781360</v>
+      </c>
+      <c r="C282" t="s">
+        <v>68</v>
+      </c>
+      <c r="D282" t="s">
+        <v>69</v>
+      </c>
+      <c r="E282" s="2">
+        <v>45836.85416666666</v>
+      </c>
+      <c r="F282">
+        <v>0</v>
+      </c>
+      <c r="G282" t="s">
+        <v>88</v>
+      </c>
+      <c r="H282" t="s">
+        <v>92</v>
+      </c>
+      <c r="I282">
+        <v>1</v>
+      </c>
+      <c r="J282">
+        <v>2</v>
+      </c>
+      <c r="K282">
+        <v>3</v>
+      </c>
+      <c r="L282">
+        <v>2</v>
+      </c>
+      <c r="M282">
+        <v>2</v>
+      </c>
+      <c r="N282">
+        <v>4</v>
+      </c>
+      <c r="O282" t="s">
+        <v>290</v>
+      </c>
+      <c r="P282" t="s">
+        <v>425</v>
+      </c>
+      <c r="Q282">
+        <v>2.88</v>
+      </c>
+      <c r="R282">
+        <v>2.2</v>
+      </c>
+      <c r="S282">
+        <v>3.6</v>
+      </c>
+      <c r="T282">
+        <v>1.36</v>
+      </c>
+      <c r="U282">
+        <v>3</v>
+      </c>
+      <c r="V282">
+        <v>2.75</v>
+      </c>
+      <c r="W282">
+        <v>1.4</v>
+      </c>
+      <c r="X282">
+        <v>7</v>
+      </c>
+      <c r="Y282">
+        <v>1.1</v>
+      </c>
+      <c r="Z282">
+        <v>2.14</v>
+      </c>
+      <c r="AA282">
+        <v>3.11</v>
+      </c>
+      <c r="AB282">
+        <v>3.02</v>
+      </c>
+      <c r="AC282">
+        <v>1.05</v>
+      </c>
+      <c r="AD282">
+        <v>9</v>
+      </c>
+      <c r="AE282">
+        <v>1.28</v>
+      </c>
+      <c r="AF282">
+        <v>3.55</v>
+      </c>
+      <c r="AG282">
+        <v>1.82</v>
+      </c>
+      <c r="AH282">
+        <v>1.88</v>
+      </c>
+      <c r="AI282">
+        <v>1.7</v>
+      </c>
+      <c r="AJ282">
+        <v>2.05</v>
+      </c>
+      <c r="AK282">
+        <v>1.3</v>
+      </c>
+      <c r="AL282">
+        <v>1.25</v>
+      </c>
+      <c r="AM282">
+        <v>1.67</v>
+      </c>
+      <c r="AN282">
+        <v>2.44</v>
+      </c>
+      <c r="AO282">
+        <v>1.67</v>
+      </c>
+      <c r="AP282">
+        <v>2.3</v>
+      </c>
+      <c r="AQ282">
+        <v>1.6</v>
+      </c>
+      <c r="AR282">
+        <v>1.63</v>
+      </c>
+      <c r="AS282">
+        <v>1.45</v>
+      </c>
+      <c r="AT282">
+        <v>3.08</v>
+      </c>
+      <c r="AU282">
+        <v>8</v>
+      </c>
+      <c r="AV282">
+        <v>3</v>
+      </c>
+      <c r="AW282">
+        <v>8</v>
+      </c>
+      <c r="AX282">
+        <v>3</v>
+      </c>
+      <c r="AY282">
+        <v>16</v>
+      </c>
+      <c r="AZ282">
+        <v>6</v>
+      </c>
+      <c r="BA282">
+        <v>6</v>
+      </c>
+      <c r="BB282">
+        <v>6</v>
+      </c>
+      <c r="BC282">
+        <v>12</v>
+      </c>
+      <c r="BD282">
+        <v>1.49</v>
+      </c>
+      <c r="BE282">
+        <v>6.75</v>
+      </c>
+      <c r="BF282">
+        <v>2.9</v>
+      </c>
+      <c r="BG282">
+        <v>1.28</v>
+      </c>
+      <c r="BH282">
+        <v>3.2</v>
+      </c>
+      <c r="BI282">
+        <v>1.49</v>
+      </c>
+      <c r="BJ282">
+        <v>2.4</v>
+      </c>
+      <c r="BK282">
+        <v>1.8</v>
+      </c>
+      <c r="BL282">
+        <v>1.89</v>
+      </c>
+      <c r="BM282">
+        <v>2.25</v>
+      </c>
+      <c r="BN282">
+        <v>1.55</v>
+      </c>
+      <c r="BO282">
+        <v>2.9</v>
+      </c>
+      <c r="BP282">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="283" spans="1:68">
+      <c r="A283" s="1">
+        <v>282</v>
+      </c>
+      <c r="B283">
+        <v>7781358</v>
+      </c>
+      <c r="C283" t="s">
+        <v>68</v>
+      </c>
+      <c r="D283" t="s">
+        <v>69</v>
+      </c>
+      <c r="E283" s="2">
+        <v>45836.85416666666</v>
+      </c>
+      <c r="F283">
+        <v>0</v>
+      </c>
+      <c r="G283" t="s">
+        <v>99</v>
+      </c>
+      <c r="H283" t="s">
+        <v>96</v>
+      </c>
+      <c r="I283">
+        <v>1</v>
+      </c>
+      <c r="J283">
+        <v>0</v>
+      </c>
+      <c r="K283">
+        <v>1</v>
+      </c>
+      <c r="L283">
+        <v>1</v>
+      </c>
+      <c r="M283">
+        <v>0</v>
+      </c>
+      <c r="N283">
+        <v>1</v>
+      </c>
+      <c r="O283" t="s">
+        <v>291</v>
+      </c>
+      <c r="P283" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q283">
+        <v>3.2</v>
+      </c>
+      <c r="R283">
+        <v>2.1</v>
+      </c>
+      <c r="S283">
+        <v>3</v>
+      </c>
+      <c r="T283">
+        <v>1.36</v>
+      </c>
+      <c r="U283">
+        <v>2.85</v>
+      </c>
+      <c r="V283">
+        <v>2.62</v>
+      </c>
+      <c r="W283">
+        <v>1.42</v>
+      </c>
+      <c r="X283">
+        <v>6.25</v>
+      </c>
+      <c r="Y283">
+        <v>1.09</v>
+      </c>
+      <c r="Z283">
+        <v>2.64</v>
+      </c>
+      <c r="AA283">
+        <v>3.07</v>
+      </c>
+      <c r="AB283">
+        <v>2.41</v>
+      </c>
+      <c r="AC283">
+        <v>1.05</v>
+      </c>
+      <c r="AD283">
+        <v>9</v>
+      </c>
+      <c r="AE283">
+        <v>1.28</v>
+      </c>
+      <c r="AF283">
+        <v>3.6</v>
+      </c>
+      <c r="AG283">
+        <v>1.8</v>
+      </c>
+      <c r="AH283">
+        <v>1.9</v>
+      </c>
+      <c r="AI283">
+        <v>1.62</v>
+      </c>
+      <c r="AJ283">
+        <v>2.15</v>
+      </c>
+      <c r="AK283">
+        <v>1.53</v>
+      </c>
+      <c r="AL283">
+        <v>1.25</v>
+      </c>
+      <c r="AM283">
+        <v>1.42</v>
+      </c>
+      <c r="AN283">
+        <v>0.38</v>
+      </c>
+      <c r="AO283">
+        <v>0.88</v>
+      </c>
+      <c r="AP283">
+        <v>0.67</v>
+      </c>
+      <c r="AQ283">
+        <v>0.78</v>
+      </c>
+      <c r="AR283">
+        <v>1.54</v>
+      </c>
+      <c r="AS283">
+        <v>1.26</v>
+      </c>
+      <c r="AT283">
+        <v>2.8</v>
+      </c>
+      <c r="AU283">
+        <v>7</v>
+      </c>
+      <c r="AV283">
+        <v>3</v>
+      </c>
+      <c r="AW283">
+        <v>3</v>
+      </c>
+      <c r="AX283">
+        <v>4</v>
+      </c>
+      <c r="AY283">
+        <v>10</v>
+      </c>
+      <c r="AZ283">
+        <v>7</v>
+      </c>
+      <c r="BA283">
+        <v>5</v>
+      </c>
+      <c r="BB283">
+        <v>8</v>
+      </c>
+      <c r="BC283">
+        <v>13</v>
+      </c>
+      <c r="BD283">
+        <v>1.83</v>
+      </c>
+      <c r="BE283">
+        <v>6.5</v>
+      </c>
+      <c r="BF283">
+        <v>2.17</v>
+      </c>
+      <c r="BG283">
+        <v>1.29</v>
+      </c>
+      <c r="BH283">
+        <v>3.2</v>
+      </c>
+      <c r="BI283">
+        <v>1.5</v>
+      </c>
+      <c r="BJ283">
+        <v>2.38</v>
+      </c>
+      <c r="BK283">
+        <v>1.81</v>
+      </c>
+      <c r="BL283">
+        <v>1.88</v>
+      </c>
+      <c r="BM283">
+        <v>2.28</v>
+      </c>
+      <c r="BN283">
+        <v>1.54</v>
+      </c>
+      <c r="BO283">
+        <v>2.9</v>
+      </c>
+      <c r="BP283">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="284" spans="1:68">
+      <c r="A284" s="1">
+        <v>283</v>
+      </c>
+      <c r="B284">
+        <v>7781356</v>
+      </c>
+      <c r="C284" t="s">
+        <v>68</v>
+      </c>
+      <c r="D284" t="s">
+        <v>69</v>
+      </c>
+      <c r="E284" s="2">
+        <v>45836.85416666666</v>
+      </c>
+      <c r="F284">
+        <v>0</v>
+      </c>
+      <c r="G284" t="s">
+        <v>75</v>
+      </c>
+      <c r="H284" t="s">
+        <v>79</v>
+      </c>
+      <c r="I284">
+        <v>0</v>
+      </c>
+      <c r="J284">
+        <v>1</v>
+      </c>
+      <c r="K284">
+        <v>1</v>
+      </c>
+      <c r="L284">
+        <v>0</v>
+      </c>
+      <c r="M284">
+        <v>1</v>
+      </c>
+      <c r="N284">
+        <v>1</v>
+      </c>
+      <c r="O284" t="s">
+        <v>109</v>
+      </c>
+      <c r="P284" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q284">
+        <v>3.6</v>
+      </c>
+      <c r="R284">
+        <v>2.3</v>
+      </c>
+      <c r="S284">
+        <v>2.45</v>
+      </c>
+      <c r="T284">
+        <v>1.25</v>
+      </c>
+      <c r="U284">
+        <v>3.5</v>
+      </c>
+      <c r="V284">
+        <v>2.15</v>
+      </c>
+      <c r="W284">
+        <v>1.62</v>
+      </c>
+      <c r="X284">
+        <v>4.5</v>
+      </c>
+      <c r="Y284">
+        <v>1.17</v>
+      </c>
+      <c r="Z284">
+        <v>3.57</v>
+      </c>
+      <c r="AA284">
+        <v>3.34</v>
+      </c>
+      <c r="AB284">
+        <v>1.85</v>
+      </c>
+      <c r="AC284">
+        <v>1.01</v>
+      </c>
+      <c r="AD284">
+        <v>17</v>
+      </c>
+      <c r="AE284">
+        <v>1.17</v>
+      </c>
+      <c r="AF284">
+        <v>5</v>
+      </c>
+      <c r="AG284">
+        <v>1.66</v>
+      </c>
+      <c r="AH284">
+        <v>2.08</v>
+      </c>
+      <c r="AI284">
+        <v>1.42</v>
+      </c>
+      <c r="AJ284">
+        <v>2.62</v>
+      </c>
+      <c r="AK284">
+        <v>1.73</v>
+      </c>
+      <c r="AL284">
+        <v>1.22</v>
+      </c>
+      <c r="AM284">
+        <v>1.33</v>
+      </c>
+      <c r="AN284">
+        <v>1</v>
+      </c>
+      <c r="AO284">
+        <v>1.78</v>
+      </c>
+      <c r="AP284">
+        <v>0.91</v>
+      </c>
+      <c r="AQ284">
+        <v>1.9</v>
+      </c>
+      <c r="AR284">
+        <v>1.23</v>
+      </c>
+      <c r="AS284">
+        <v>1.6</v>
+      </c>
+      <c r="AT284">
+        <v>2.83</v>
+      </c>
+      <c r="AU284">
+        <v>2</v>
+      </c>
+      <c r="AV284">
+        <v>3</v>
+      </c>
+      <c r="AW284">
+        <v>2</v>
+      </c>
+      <c r="AX284">
+        <v>2</v>
+      </c>
+      <c r="AY284">
+        <v>4</v>
+      </c>
+      <c r="AZ284">
+        <v>5</v>
+      </c>
+      <c r="BA284">
+        <v>4</v>
+      </c>
+      <c r="BB284">
+        <v>3</v>
+      </c>
+      <c r="BC284">
+        <v>7</v>
+      </c>
+      <c r="BD284">
+        <v>2.05</v>
+      </c>
+      <c r="BE284">
+        <v>6.4</v>
+      </c>
+      <c r="BF284">
+        <v>1.95</v>
+      </c>
+      <c r="BG284">
+        <v>1.25</v>
+      </c>
+      <c r="BH284">
+        <v>3.4</v>
+      </c>
+      <c r="BI284">
+        <v>1.44</v>
+      </c>
+      <c r="BJ284">
+        <v>2.55</v>
+      </c>
+      <c r="BK284">
+        <v>1.73</v>
+      </c>
+      <c r="BL284">
+        <v>1.98</v>
+      </c>
+      <c r="BM284">
+        <v>2.15</v>
+      </c>
+      <c r="BN284">
+        <v>1.61</v>
+      </c>
+      <c r="BO284">
+        <v>2.7</v>
+      </c>
+      <c r="BP284">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="285" spans="1:68">
+      <c r="A285" s="1">
+        <v>284</v>
+      </c>
+      <c r="B285">
+        <v>7781363</v>
+      </c>
+      <c r="C285" t="s">
+        <v>68</v>
+      </c>
+      <c r="D285" t="s">
+        <v>69</v>
+      </c>
+      <c r="E285" s="2">
+        <v>45836.89583333334</v>
+      </c>
+      <c r="F285">
+        <v>0</v>
+      </c>
+      <c r="G285" t="s">
+        <v>90</v>
+      </c>
+      <c r="H285" t="s">
+        <v>85</v>
+      </c>
+      <c r="I285">
+        <v>3</v>
+      </c>
+      <c r="J285">
+        <v>0</v>
+      </c>
+      <c r="K285">
+        <v>3</v>
+      </c>
+      <c r="L285">
+        <v>3</v>
+      </c>
+      <c r="M285">
+        <v>2</v>
+      </c>
+      <c r="N285">
+        <v>5</v>
+      </c>
+      <c r="O285" t="s">
+        <v>292</v>
+      </c>
+      <c r="P285" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q285">
+        <v>2.5</v>
+      </c>
+      <c r="R285">
+        <v>2.5</v>
+      </c>
+      <c r="S285">
+        <v>3.5</v>
+      </c>
+      <c r="T285">
+        <v>1.25</v>
+      </c>
+      <c r="U285">
+        <v>3.75</v>
+      </c>
+      <c r="V285">
+        <v>2.1</v>
+      </c>
+      <c r="W285">
+        <v>1.67</v>
+      </c>
+      <c r="X285">
+        <v>5</v>
+      </c>
+      <c r="Y285">
+        <v>1.17</v>
+      </c>
+      <c r="Z285">
+        <v>1.94</v>
+      </c>
+      <c r="AA285">
+        <v>3.11</v>
+      </c>
+      <c r="AB285">
+        <v>3.53</v>
+      </c>
+      <c r="AC285">
+        <v>1.01</v>
+      </c>
+      <c r="AD285">
+        <v>17</v>
+      </c>
+      <c r="AE285">
+        <v>1.09</v>
+      </c>
+      <c r="AF285">
+        <v>5.25</v>
+      </c>
+      <c r="AG285">
+        <v>1.45</v>
+      </c>
+      <c r="AH285">
+        <v>2.63</v>
+      </c>
+      <c r="AI285">
+        <v>1.44</v>
+      </c>
+      <c r="AJ285">
+        <v>2.63</v>
+      </c>
+      <c r="AK285">
+        <v>1.29</v>
+      </c>
+      <c r="AL285">
+        <v>1.3</v>
+      </c>
+      <c r="AM285">
+        <v>1.83</v>
+      </c>
+      <c r="AN285">
+        <v>0.88</v>
+      </c>
+      <c r="AO285">
+        <v>0.64</v>
+      </c>
+      <c r="AP285">
+        <v>1.11</v>
+      </c>
+      <c r="AQ285">
+        <v>0.58</v>
+      </c>
+      <c r="AR285">
+        <v>1.56</v>
+      </c>
+      <c r="AS285">
+        <v>1.23</v>
+      </c>
+      <c r="AT285">
+        <v>2.79</v>
+      </c>
+      <c r="AU285">
+        <v>6</v>
+      </c>
+      <c r="AV285">
+        <v>3</v>
+      </c>
+      <c r="AW285">
+        <v>2</v>
+      </c>
+      <c r="AX285">
+        <v>5</v>
+      </c>
+      <c r="AY285">
+        <v>8</v>
+      </c>
+      <c r="AZ285">
+        <v>8</v>
+      </c>
+      <c r="BA285">
+        <v>3</v>
+      </c>
+      <c r="BB285">
+        <v>1</v>
+      </c>
+      <c r="BC285">
+        <v>4</v>
+      </c>
+      <c r="BD285">
+        <v>1.56</v>
+      </c>
+      <c r="BE285">
+        <v>6.75</v>
+      </c>
+      <c r="BF285">
+        <v>2.65</v>
+      </c>
+      <c r="BG285">
+        <v>1.28</v>
+      </c>
+      <c r="BH285">
+        <v>3.2</v>
+      </c>
+      <c r="BI285">
+        <v>1.5</v>
+      </c>
+      <c r="BJ285">
+        <v>2.4</v>
+      </c>
+      <c r="BK285">
+        <v>1.81</v>
+      </c>
+      <c r="BL285">
+        <v>1.88</v>
+      </c>
+      <c r="BM285">
+        <v>2.25</v>
+      </c>
+      <c r="BN285">
+        <v>1.55</v>
+      </c>
+      <c r="BO285">
+        <v>2.9</v>
+      </c>
+      <c r="BP285">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="286" spans="1:68">
+      <c r="A286" s="1">
+        <v>285</v>
+      </c>
+      <c r="B286">
+        <v>7781364</v>
+      </c>
+      <c r="C286" t="s">
+        <v>68</v>
+      </c>
+      <c r="D286" t="s">
+        <v>69</v>
+      </c>
+      <c r="E286" s="2">
+        <v>45836.89583333334</v>
+      </c>
+      <c r="F286">
+        <v>0</v>
+      </c>
+      <c r="G286" t="s">
+        <v>97</v>
+      </c>
+      <c r="H286" t="s">
+        <v>94</v>
+      </c>
+      <c r="I286">
+        <v>1</v>
+      </c>
+      <c r="J286">
+        <v>1</v>
+      </c>
+      <c r="K286">
+        <v>2</v>
+      </c>
+      <c r="L286">
+        <v>2</v>
+      </c>
+      <c r="M286">
+        <v>3</v>
+      </c>
+      <c r="N286">
+        <v>5</v>
+      </c>
+      <c r="O286" t="s">
+        <v>293</v>
+      </c>
+      <c r="P286" t="s">
+        <v>427</v>
+      </c>
+      <c r="Q286">
+        <v>0</v>
+      </c>
+      <c r="R286">
+        <v>0</v>
+      </c>
+      <c r="S286">
+        <v>0</v>
+      </c>
+      <c r="T286">
+        <v>0</v>
+      </c>
+      <c r="U286">
+        <v>0</v>
+      </c>
+      <c r="V286">
+        <v>0</v>
+      </c>
+      <c r="W286">
+        <v>0</v>
+      </c>
+      <c r="X286">
+        <v>0</v>
+      </c>
+      <c r="Y286">
+        <v>0</v>
+      </c>
+      <c r="Z286">
+        <v>2.88</v>
+      </c>
+      <c r="AA286">
+        <v>3.11</v>
+      </c>
+      <c r="AB286">
+        <v>2.22</v>
+      </c>
+      <c r="AC286">
+        <v>0</v>
+      </c>
+      <c r="AD286">
+        <v>0</v>
+      </c>
+      <c r="AE286">
+        <v>0</v>
+      </c>
+      <c r="AF286">
+        <v>0</v>
+      </c>
+      <c r="AG286">
+        <v>1.67</v>
+      </c>
+      <c r="AH286">
+        <v>2.1</v>
+      </c>
+      <c r="AI286">
+        <v>0</v>
+      </c>
+      <c r="AJ286">
+        <v>0</v>
+      </c>
+      <c r="AK286">
+        <v>0</v>
+      </c>
+      <c r="AL286">
+        <v>0</v>
+      </c>
+      <c r="AM286">
+        <v>0</v>
+      </c>
+      <c r="AN286">
+        <v>0.63</v>
+      </c>
+      <c r="AO286">
+        <v>1.67</v>
+      </c>
+      <c r="AP286">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AQ286">
+        <v>1.8</v>
+      </c>
+      <c r="AR286">
+        <v>1.24</v>
+      </c>
+      <c r="AS286">
+        <v>1.67</v>
+      </c>
+      <c r="AT286">
+        <v>2.91</v>
+      </c>
+      <c r="AU286">
+        <v>6</v>
+      </c>
+      <c r="AV286">
+        <v>4</v>
+      </c>
+      <c r="AW286">
+        <v>5</v>
+      </c>
+      <c r="AX286">
+        <v>5</v>
+      </c>
+      <c r="AY286">
+        <v>11</v>
+      </c>
+      <c r="AZ286">
+        <v>9</v>
+      </c>
+      <c r="BA286">
+        <v>5</v>
+      </c>
+      <c r="BB286">
+        <v>4</v>
+      </c>
+      <c r="BC286">
+        <v>9</v>
+      </c>
+      <c r="BD286">
+        <v>0</v>
+      </c>
+      <c r="BE286">
+        <v>0</v>
+      </c>
+      <c r="BF286">
+        <v>0</v>
+      </c>
+      <c r="BG286">
+        <v>0</v>
+      </c>
+      <c r="BH286">
+        <v>0</v>
+      </c>
+      <c r="BI286">
+        <v>0</v>
+      </c>
+      <c r="BJ286">
+        <v>0</v>
+      </c>
+      <c r="BK286">
+        <v>0</v>
+      </c>
+      <c r="BL286">
+        <v>0</v>
+      </c>
+      <c r="BM286">
+        <v>0</v>
+      </c>
+      <c r="BN286">
+        <v>0</v>
+      </c>
+      <c r="BO286">
+        <v>0</v>
+      </c>
+      <c r="BP286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:68">
+      <c r="A287" s="1">
+        <v>286</v>
+      </c>
+      <c r="B287">
+        <v>7781365</v>
+      </c>
+      <c r="C287" t="s">
+        <v>68</v>
+      </c>
+      <c r="D287" t="s">
+        <v>69</v>
+      </c>
+      <c r="E287" s="2">
+        <v>45836.89583333334</v>
+      </c>
+      <c r="F287">
+        <v>0</v>
+      </c>
+      <c r="G287" t="s">
+        <v>78</v>
+      </c>
+      <c r="H287" t="s">
+        <v>80</v>
+      </c>
+      <c r="I287">
+        <v>0</v>
+      </c>
+      <c r="J287">
+        <v>0</v>
+      </c>
+      <c r="K287">
+        <v>0</v>
+      </c>
+      <c r="L287">
+        <v>1</v>
+      </c>
+      <c r="M287">
+        <v>0</v>
+      </c>
+      <c r="N287">
+        <v>1</v>
+      </c>
+      <c r="O287" t="s">
+        <v>294</v>
+      </c>
+      <c r="P287" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q287">
+        <v>2.5</v>
+      </c>
+      <c r="R287">
+        <v>2.3</v>
+      </c>
+      <c r="S287">
+        <v>4</v>
+      </c>
+      <c r="T287">
+        <v>1.3</v>
+      </c>
+      <c r="U287">
+        <v>3.4</v>
+      </c>
+      <c r="V287">
+        <v>2.5</v>
+      </c>
+      <c r="W287">
+        <v>1.5</v>
+      </c>
+      <c r="X287">
+        <v>6</v>
+      </c>
+      <c r="Y287">
+        <v>1.13</v>
+      </c>
+      <c r="Z287">
+        <v>1.84</v>
+      </c>
+      <c r="AA287">
+        <v>3.21</v>
+      </c>
+      <c r="AB287">
+        <v>3.77</v>
+      </c>
+      <c r="AC287">
+        <v>1.02</v>
+      </c>
+      <c r="AD287">
+        <v>10</v>
+      </c>
+      <c r="AE287">
+        <v>1.19</v>
+      </c>
+      <c r="AF287">
+        <v>3.95</v>
+      </c>
+      <c r="AG287">
+        <v>1.68</v>
+      </c>
+      <c r="AH287">
+        <v>2.05</v>
+      </c>
+      <c r="AI287">
+        <v>1.62</v>
+      </c>
+      <c r="AJ287">
+        <v>2.2</v>
+      </c>
+      <c r="AK287">
+        <v>1.29</v>
+      </c>
+      <c r="AL287">
+        <v>1.3</v>
+      </c>
+      <c r="AM287">
+        <v>1.83</v>
+      </c>
+      <c r="AN287">
+        <v>1</v>
+      </c>
+      <c r="AO287">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP287">
+        <v>1.18</v>
+      </c>
+      <c r="AQ287">
+        <v>0.5</v>
+      </c>
+      <c r="AR287">
+        <v>1.67</v>
+      </c>
+      <c r="AS287">
+        <v>1.17</v>
+      </c>
+      <c r="AT287">
+        <v>2.84</v>
+      </c>
+      <c r="AU287">
+        <v>7</v>
+      </c>
+      <c r="AV287">
+        <v>2</v>
+      </c>
+      <c r="AW287">
+        <v>9</v>
+      </c>
+      <c r="AX287">
+        <v>2</v>
+      </c>
+      <c r="AY287">
+        <v>16</v>
+      </c>
+      <c r="AZ287">
+        <v>4</v>
+      </c>
+      <c r="BA287">
+        <v>7</v>
+      </c>
+      <c r="BB287">
+        <v>0</v>
+      </c>
+      <c r="BC287">
+        <v>7</v>
+      </c>
+      <c r="BD287">
+        <v>1.53</v>
+      </c>
+      <c r="BE287">
+        <v>7</v>
+      </c>
+      <c r="BF287">
+        <v>2.7</v>
+      </c>
+      <c r="BG287">
+        <v>1.23</v>
+      </c>
+      <c r="BH287">
+        <v>3.65</v>
+      </c>
+      <c r="BI287">
+        <v>1.41</v>
+      </c>
+      <c r="BJ287">
+        <v>2.65</v>
+      </c>
+      <c r="BK287">
+        <v>1.66</v>
+      </c>
+      <c r="BL287">
+        <v>2.07</v>
+      </c>
+      <c r="BM287">
+        <v>2.02</v>
+      </c>
+      <c r="BN287">
+        <v>1.68</v>
+      </c>
+      <c r="BO287">
+        <v>2.55</v>
+      </c>
+      <c r="BP287">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="288" spans="1:68">
+      <c r="A288" s="1">
+        <v>287</v>
+      </c>
+      <c r="B288">
+        <v>7781366</v>
+      </c>
+      <c r="C288" t="s">
+        <v>68</v>
+      </c>
+      <c r="D288" t="s">
+        <v>69</v>
+      </c>
+      <c r="E288" s="2">
+        <v>45836.89583333334</v>
+      </c>
+      <c r="F288">
+        <v>0</v>
+      </c>
+      <c r="G288" t="s">
+        <v>91</v>
+      </c>
+      <c r="H288" t="s">
+        <v>86</v>
+      </c>
+      <c r="I288">
+        <v>0</v>
+      </c>
+      <c r="J288">
+        <v>1</v>
+      </c>
+      <c r="K288">
+        <v>1</v>
+      </c>
+      <c r="L288">
+        <v>1</v>
+      </c>
+      <c r="M288">
+        <v>1</v>
+      </c>
+      <c r="N288">
+        <v>2</v>
+      </c>
+      <c r="O288" t="s">
+        <v>295</v>
+      </c>
+      <c r="P288" t="s">
+        <v>428</v>
+      </c>
+      <c r="Q288">
+        <v>2.5</v>
+      </c>
+      <c r="R288">
+        <v>2.5</v>
+      </c>
+      <c r="S288">
+        <v>3.5</v>
+      </c>
+      <c r="T288">
+        <v>1.25</v>
+      </c>
+      <c r="U288">
+        <v>3.75</v>
+      </c>
+      <c r="V288">
+        <v>2.2</v>
+      </c>
+      <c r="W288">
+        <v>1.62</v>
+      </c>
+      <c r="X288">
+        <v>5</v>
+      </c>
+      <c r="Y288">
+        <v>1.17</v>
+      </c>
+      <c r="Z288">
+        <v>1.94</v>
+      </c>
+      <c r="AA288">
+        <v>3.26</v>
+      </c>
+      <c r="AB288">
+        <v>3.35</v>
+      </c>
+      <c r="AC288">
+        <v>1.01</v>
+      </c>
+      <c r="AD288">
+        <v>17</v>
+      </c>
+      <c r="AE288">
+        <v>1.12</v>
+      </c>
+      <c r="AF288">
+        <v>4.65</v>
+      </c>
+      <c r="AG288">
+        <v>1.6</v>
+      </c>
+      <c r="AH288">
+        <v>2.25</v>
+      </c>
+      <c r="AI288">
+        <v>1.44</v>
+      </c>
+      <c r="AJ288">
+        <v>2.63</v>
+      </c>
+      <c r="AK288">
+        <v>1.35</v>
+      </c>
+      <c r="AL288">
+        <v>1.29</v>
+      </c>
+      <c r="AM288">
+        <v>1.73</v>
+      </c>
+      <c r="AN288">
+        <v>1.22</v>
+      </c>
+      <c r="AO288">
+        <v>0.8</v>
+      </c>
+      <c r="AP288">
+        <v>1.2</v>
+      </c>
+      <c r="AQ288">
+        <v>0.82</v>
+      </c>
+      <c r="AR288">
+        <v>1.64</v>
+      </c>
+      <c r="AS288">
+        <v>1.57</v>
+      </c>
+      <c r="AT288">
+        <v>3.21</v>
+      </c>
+      <c r="AU288">
+        <v>6</v>
+      </c>
+      <c r="AV288">
+        <v>10</v>
+      </c>
+      <c r="AW288">
+        <v>4</v>
+      </c>
+      <c r="AX288">
+        <v>8</v>
+      </c>
+      <c r="AY288">
+        <v>10</v>
+      </c>
+      <c r="AZ288">
+        <v>18</v>
+      </c>
+      <c r="BA288">
+        <v>6</v>
+      </c>
+      <c r="BB288">
+        <v>3</v>
+      </c>
+      <c r="BC288">
+        <v>9</v>
+      </c>
+      <c r="BD288">
+        <v>1.68</v>
+      </c>
+      <c r="BE288">
+        <v>6.75</v>
+      </c>
+      <c r="BF288">
+        <v>2.4</v>
+      </c>
+      <c r="BG288">
+        <v>1.23</v>
+      </c>
+      <c r="BH288">
+        <v>3.65</v>
+      </c>
+      <c r="BI288">
+        <v>1.41</v>
+      </c>
+      <c r="BJ288">
+        <v>2.65</v>
+      </c>
+      <c r="BK288">
+        <v>1.66</v>
+      </c>
+      <c r="BL288">
+        <v>2.06</v>
+      </c>
+      <c r="BM288">
+        <v>2.04</v>
+      </c>
+      <c r="BN288">
+        <v>1.68</v>
+      </c>
+      <c r="BO288">
+        <v>2.55</v>
+      </c>
+      <c r="BP288">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -59079,16 +59079,16 @@
         <v>5</v>
       </c>
       <c r="AW279">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AX279">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY279">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AZ279">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA279">
         <v>3</v>
@@ -59279,22 +59279,22 @@
         <v>2.81</v>
       </c>
       <c r="AU280">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV280">
         <v>0</v>
       </c>
       <c r="AW280">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX280">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY280">
         <v>14</v>
       </c>
       <c r="AZ280">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BA280">
         <v>9</v>
@@ -59488,19 +59488,19 @@
         <v>11</v>
       </c>
       <c r="AV281">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW281">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AX281">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AY281">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AZ281">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BA281">
         <v>11</v>
@@ -59697,16 +59697,16 @@
         <v>3</v>
       </c>
       <c r="AW282">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AX282">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY282">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AZ282">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BA282">
         <v>6</v>
@@ -59903,16 +59903,16 @@
         <v>3</v>
       </c>
       <c r="AW283">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AX283">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY283">
+        <v>14</v>
+      </c>
+      <c r="AZ283">
         <v>10</v>
-      </c>
-      <c r="AZ283">
-        <v>7</v>
       </c>
       <c r="BA283">
         <v>5</v>
@@ -60315,16 +60315,16 @@
         <v>3</v>
       </c>
       <c r="AW285">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AX285">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY285">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AZ285">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA285">
         <v>3</v>
@@ -60730,13 +60730,13 @@
         <v>9</v>
       </c>
       <c r="AX287">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AY287">
         <v>16</v>
       </c>
       <c r="AZ287">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BA287">
         <v>7</v>
@@ -60927,22 +60927,22 @@
         <v>3.21</v>
       </c>
       <c r="AU288">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV288">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW288">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AX288">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AY288">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AZ288">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA288">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="430">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -904,6 +904,9 @@
     <t>['59']</t>
   </si>
   <si>
+    <t>['4502', '54']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -1662,7 +1665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP288"/>
+  <dimension ref="A1:BP290"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2124,7 +2127,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -2330,7 +2333,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2742,7 +2745,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2948,7 +2951,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3154,7 +3157,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -3566,7 +3569,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -4262,7 +4265,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ13">
         <v>0.82</v>
@@ -4390,7 +4393,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -4468,7 +4471,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ14">
         <v>0.58</v>
@@ -4596,7 +4599,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4802,7 +4805,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -5832,7 +5835,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -6244,7 +6247,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6450,7 +6453,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6862,7 +6865,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -7355,7 +7358,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ28">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR28">
         <v>0.72</v>
@@ -7767,7 +7770,7 @@
         <v>2</v>
       </c>
       <c r="AQ30">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR30">
         <v>0</v>
@@ -7892,7 +7895,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -8304,7 +8307,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -8382,7 +8385,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ33">
         <v>0.88</v>
@@ -9128,7 +9131,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9746,7 +9749,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -10158,7 +10161,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -10648,7 +10651,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ44">
         <v>1.6</v>
@@ -10982,7 +10985,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -11188,7 +11191,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -11394,7 +11397,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11681,7 +11684,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ49">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR49">
         <v>1.41</v>
@@ -12218,7 +12221,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12424,7 +12427,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12836,7 +12839,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -13454,7 +13457,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13532,7 +13535,7 @@
         <v>2</v>
       </c>
       <c r="AP58">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ58">
         <v>1.22</v>
@@ -13660,7 +13663,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13947,7 +13950,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ60">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR60">
         <v>0.9399999999999999</v>
@@ -14072,7 +14075,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14278,7 +14281,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -14484,7 +14487,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14565,7 +14568,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ63">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR63">
         <v>1.42</v>
@@ -14690,7 +14693,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -15720,7 +15723,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -16132,7 +16135,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16338,7 +16341,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16622,7 +16625,7 @@
         <v>1</v>
       </c>
       <c r="AP73">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ73">
         <v>1.11</v>
@@ -16750,7 +16753,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -17162,7 +17165,7 @@
         <v>153</v>
       </c>
       <c r="P76" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q76">
         <v>3.6</v>
@@ -17986,7 +17989,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18192,7 +18195,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18398,7 +18401,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -19016,7 +19019,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -19222,7 +19225,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -19428,7 +19431,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -19712,7 +19715,7 @@
         <v>0</v>
       </c>
       <c r="AP88">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ88">
         <v>0.9</v>
@@ -19921,7 +19924,7 @@
         <v>1</v>
       </c>
       <c r="AQ89">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR89">
         <v>1.83</v>
@@ -20046,7 +20049,7 @@
         <v>164</v>
       </c>
       <c r="P90" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
@@ -20539,7 +20542,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ92">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR92">
         <v>1.35</v>
@@ -21282,7 +21285,7 @@
         <v>168</v>
       </c>
       <c r="P96" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -22724,7 +22727,7 @@
         <v>122</v>
       </c>
       <c r="P103" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q103">
         <v>2.75</v>
@@ -22930,7 +22933,7 @@
         <v>173</v>
       </c>
       <c r="P104" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q104">
         <v>2.75</v>
@@ -23008,7 +23011,7 @@
         <v>0.5</v>
       </c>
       <c r="AP104">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ104">
         <v>0.89</v>
@@ -23136,7 +23139,7 @@
         <v>174</v>
       </c>
       <c r="P105" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q105">
         <v>1.91</v>
@@ -24247,7 +24250,7 @@
         <v>2</v>
       </c>
       <c r="AQ110">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR110">
         <v>1.84</v>
@@ -24372,7 +24375,7 @@
         <v>109</v>
       </c>
       <c r="P111" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q111">
         <v>2.88</v>
@@ -24990,7 +24993,7 @@
         <v>177</v>
       </c>
       <c r="P114" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25196,7 +25199,7 @@
         <v>178</v>
       </c>
       <c r="P115" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -25608,7 +25611,7 @@
         <v>179</v>
       </c>
       <c r="P117" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25814,7 +25817,7 @@
         <v>180</v>
       </c>
       <c r="P118" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -26226,7 +26229,7 @@
         <v>181</v>
       </c>
       <c r="P120" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -26513,7 +26516,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ121">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR121">
         <v>1.5</v>
@@ -26638,7 +26641,7 @@
         <v>109</v>
       </c>
       <c r="P122" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q122">
         <v>2.75</v>
@@ -26922,7 +26925,7 @@
         <v>1</v>
       </c>
       <c r="AP123">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ123">
         <v>1.9</v>
@@ -27050,7 +27053,7 @@
         <v>129</v>
       </c>
       <c r="P124" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q124">
         <v>2.5</v>
@@ -28080,7 +28083,7 @@
         <v>187</v>
       </c>
       <c r="P129" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28286,7 +28289,7 @@
         <v>188</v>
       </c>
       <c r="P130" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q130">
         <v>2.4</v>
@@ -29110,7 +29113,7 @@
         <v>189</v>
       </c>
       <c r="P134" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q134">
         <v>3</v>
@@ -29316,7 +29319,7 @@
         <v>190</v>
       </c>
       <c r="P135" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -29394,7 +29397,7 @@
         <v>0</v>
       </c>
       <c r="AP135">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ135">
         <v>0.8</v>
@@ -30552,7 +30555,7 @@
         <v>109</v>
       </c>
       <c r="P141" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q141">
         <v>2.38</v>
@@ -30964,7 +30967,7 @@
         <v>174</v>
       </c>
       <c r="P143" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -31251,7 +31254,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ144">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR144">
         <v>1.61</v>
@@ -31376,7 +31379,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q145">
         <v>2.4</v>
@@ -31582,7 +31585,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31788,7 +31791,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q147">
         <v>2.6</v>
@@ -31994,7 +31997,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q148">
         <v>2.05</v>
@@ -32200,7 +32203,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -32406,7 +32409,7 @@
         <v>202</v>
       </c>
       <c r="P150" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q150">
         <v>2.4</v>
@@ -32818,7 +32821,7 @@
         <v>109</v>
       </c>
       <c r="P152" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q152">
         <v>2.88</v>
@@ -33024,7 +33027,7 @@
         <v>204</v>
       </c>
       <c r="P153" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -33230,7 +33233,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q154">
         <v>3.1</v>
@@ -33436,7 +33439,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q155">
         <v>2.2</v>
@@ -33642,7 +33645,7 @@
         <v>207</v>
       </c>
       <c r="P156" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33848,7 +33851,7 @@
         <v>109</v>
       </c>
       <c r="P157" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q157">
         <v>3.2</v>
@@ -34466,7 +34469,7 @@
         <v>209</v>
       </c>
       <c r="P160" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q160">
         <v>2.1</v>
@@ -34878,7 +34881,7 @@
         <v>211</v>
       </c>
       <c r="P162" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q162">
         <v>2.5</v>
@@ -34956,7 +34959,7 @@
         <v>2</v>
       </c>
       <c r="AP162">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ162">
         <v>1.22</v>
@@ -35162,7 +35165,7 @@
         <v>1</v>
       </c>
       <c r="AP163">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ163">
         <v>0.5</v>
@@ -35577,7 +35580,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ165">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR165">
         <v>1.6</v>
@@ -35908,7 +35911,7 @@
         <v>215</v>
       </c>
       <c r="P167" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -36320,7 +36323,7 @@
         <v>217</v>
       </c>
       <c r="P169" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q169">
         <v>3</v>
@@ -36526,7 +36529,7 @@
         <v>218</v>
       </c>
       <c r="P170" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36732,7 +36735,7 @@
         <v>109</v>
       </c>
       <c r="P171" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q171">
         <v>2.25</v>
@@ -36938,7 +36941,7 @@
         <v>219</v>
       </c>
       <c r="P172" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q172">
         <v>2.4</v>
@@ -37019,7 +37022,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ172">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR172">
         <v>1.8</v>
@@ -37225,7 +37228,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ173">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR173">
         <v>1.49</v>
@@ -37350,7 +37353,7 @@
         <v>221</v>
       </c>
       <c r="P174" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q174">
         <v>2.5</v>
@@ -37556,7 +37559,7 @@
         <v>163</v>
       </c>
       <c r="P175" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -37762,7 +37765,7 @@
         <v>113</v>
       </c>
       <c r="P176" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q176">
         <v>2.4</v>
@@ -37968,7 +37971,7 @@
         <v>222</v>
       </c>
       <c r="P177" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -38174,7 +38177,7 @@
         <v>109</v>
       </c>
       <c r="P178" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q178">
         <v>2.38</v>
@@ -38586,7 +38589,7 @@
         <v>224</v>
       </c>
       <c r="P180" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38998,7 +39001,7 @@
         <v>225</v>
       </c>
       <c r="P182" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q182">
         <v>3.75</v>
@@ -39204,7 +39207,7 @@
         <v>226</v>
       </c>
       <c r="P183" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q183">
         <v>2.5</v>
@@ -39410,7 +39413,7 @@
         <v>227</v>
       </c>
       <c r="P184" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q184">
         <v>2.05</v>
@@ -39491,7 +39494,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ184">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR184">
         <v>1.71</v>
@@ -39822,7 +39825,7 @@
         <v>228</v>
       </c>
       <c r="P186" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q186">
         <v>2.4</v>
@@ -40234,7 +40237,7 @@
         <v>230</v>
       </c>
       <c r="P188" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40440,7 +40443,7 @@
         <v>176</v>
       </c>
       <c r="P189" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -41264,7 +41267,7 @@
         <v>233</v>
       </c>
       <c r="P193" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41342,7 +41345,7 @@
         <v>2</v>
       </c>
       <c r="AP193">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ193">
         <v>1.71</v>
@@ -41470,7 +41473,7 @@
         <v>234</v>
       </c>
       <c r="P194" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41882,7 +41885,7 @@
         <v>198</v>
       </c>
       <c r="P196" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q196">
         <v>2.63</v>
@@ -42294,7 +42297,7 @@
         <v>103</v>
       </c>
       <c r="P198" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q198">
         <v>2.63</v>
@@ -43324,7 +43327,7 @@
         <v>109</v>
       </c>
       <c r="P203" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q203">
         <v>2.63</v>
@@ -43736,7 +43739,7 @@
         <v>237</v>
       </c>
       <c r="P205" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -44148,7 +44151,7 @@
         <v>109</v>
       </c>
       <c r="P207" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q207">
         <v>2.25</v>
@@ -44638,7 +44641,7 @@
         <v>1.71</v>
       </c>
       <c r="AP209">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ209">
         <v>1.6</v>
@@ -44847,7 +44850,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ210">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR210">
         <v>1.8</v>
@@ -44972,7 +44975,7 @@
         <v>240</v>
       </c>
       <c r="P211" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q211">
         <v>3.2</v>
@@ -45178,7 +45181,7 @@
         <v>109</v>
       </c>
       <c r="P212" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45384,7 +45387,7 @@
         <v>241</v>
       </c>
       <c r="P213" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q213">
         <v>4</v>
@@ -45796,7 +45799,7 @@
         <v>242</v>
       </c>
       <c r="P215" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -46002,7 +46005,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q216">
         <v>3.4</v>
@@ -46208,7 +46211,7 @@
         <v>243</v>
       </c>
       <c r="P217" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q217">
         <v>2.75</v>
@@ -46495,7 +46498,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ218">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR218">
         <v>1.82</v>
@@ -46620,7 +46623,7 @@
         <v>244</v>
       </c>
       <c r="P219" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q219">
         <v>3.1</v>
@@ -47032,7 +47035,7 @@
         <v>246</v>
       </c>
       <c r="P221" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q221">
         <v>2.6</v>
@@ -47110,7 +47113,7 @@
         <v>1</v>
       </c>
       <c r="AP221">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ221">
         <v>1.11</v>
@@ -47238,7 +47241,7 @@
         <v>247</v>
       </c>
       <c r="P222" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q222">
         <v>2.5</v>
@@ -47444,7 +47447,7 @@
         <v>248</v>
       </c>
       <c r="P223" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47650,7 +47653,7 @@
         <v>249</v>
       </c>
       <c r="P224" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47856,7 +47859,7 @@
         <v>250</v>
       </c>
       <c r="P225" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -48062,7 +48065,7 @@
         <v>251</v>
       </c>
       <c r="P226" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q226">
         <v>2.75</v>
@@ -48268,7 +48271,7 @@
         <v>252</v>
       </c>
       <c r="P227" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q227">
         <v>1.83</v>
@@ -48474,7 +48477,7 @@
         <v>253</v>
       </c>
       <c r="P228" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48680,7 +48683,7 @@
         <v>109</v>
       </c>
       <c r="P229" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q229">
         <v>2.5</v>
@@ -48886,7 +48889,7 @@
         <v>254</v>
       </c>
       <c r="P230" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q230">
         <v>3.25</v>
@@ -49092,7 +49095,7 @@
         <v>119</v>
       </c>
       <c r="P231" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q231">
         <v>2.4</v>
@@ -49376,7 +49379,7 @@
         <v>1.5</v>
       </c>
       <c r="AP232">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ232">
         <v>1.8</v>
@@ -49710,7 +49713,7 @@
         <v>109</v>
       </c>
       <c r="P234" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q234">
         <v>2.5</v>
@@ -50328,7 +50331,7 @@
         <v>258</v>
       </c>
       <c r="P237" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q237">
         <v>2.75</v>
@@ -50534,7 +50537,7 @@
         <v>259</v>
       </c>
       <c r="P238" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q238">
         <v>2.6</v>
@@ -50740,7 +50743,7 @@
         <v>109</v>
       </c>
       <c r="P239" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -50946,7 +50949,7 @@
         <v>140</v>
       </c>
       <c r="P240" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -51358,7 +51361,7 @@
         <v>109</v>
       </c>
       <c r="P242" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q242">
         <v>3.1</v>
@@ -51770,7 +51773,7 @@
         <v>161</v>
       </c>
       <c r="P244" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q244">
         <v>2.1</v>
@@ -52182,7 +52185,7 @@
         <v>156</v>
       </c>
       <c r="P246" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q246">
         <v>2.5</v>
@@ -52675,7 +52678,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ248">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR248">
         <v>1.82</v>
@@ -52800,7 +52803,7 @@
         <v>176</v>
       </c>
       <c r="P249" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q249">
         <v>2.5</v>
@@ -52878,7 +52881,7 @@
         <v>1.5</v>
       </c>
       <c r="AP249">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ249">
         <v>1.6</v>
@@ -53006,7 +53009,7 @@
         <v>264</v>
       </c>
       <c r="P250" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q250">
         <v>3.2</v>
@@ -53212,7 +53215,7 @@
         <v>109</v>
       </c>
       <c r="P251" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q251">
         <v>2.75</v>
@@ -53293,7 +53296,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ251">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR251">
         <v>1.67</v>
@@ -53418,7 +53421,7 @@
         <v>265</v>
       </c>
       <c r="P252" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q252">
         <v>2.25</v>
@@ -54448,7 +54451,7 @@
         <v>270</v>
       </c>
       <c r="P257" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q257">
         <v>2.63</v>
@@ -54529,7 +54532,7 @@
         <v>1</v>
       </c>
       <c r="AQ257">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR257">
         <v>1.68</v>
@@ -54654,7 +54657,7 @@
         <v>271</v>
       </c>
       <c r="P258" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q258">
         <v>2.3</v>
@@ -54860,7 +54863,7 @@
         <v>109</v>
       </c>
       <c r="P259" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q259">
         <v>3.1</v>
@@ -55272,7 +55275,7 @@
         <v>273</v>
       </c>
       <c r="P261" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -55478,7 +55481,7 @@
         <v>274</v>
       </c>
       <c r="P262" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q262">
         <v>2.5</v>
@@ -55684,7 +55687,7 @@
         <v>234</v>
       </c>
       <c r="P263" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q263">
         <v>2.25</v>
@@ -55890,7 +55893,7 @@
         <v>109</v>
       </c>
       <c r="P264" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q264">
         <v>2.75</v>
@@ -56302,7 +56305,7 @@
         <v>109</v>
       </c>
       <c r="P266" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q266">
         <v>3.4</v>
@@ -56714,7 +56717,7 @@
         <v>277</v>
       </c>
       <c r="P268" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q268">
         <v>2.2</v>
@@ -56920,7 +56923,7 @@
         <v>278</v>
       </c>
       <c r="P269" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57126,7 +57129,7 @@
         <v>279</v>
       </c>
       <c r="P270" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q270">
         <v>3.35</v>
@@ -57538,7 +57541,7 @@
         <v>281</v>
       </c>
       <c r="P272" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q272">
         <v>2.38</v>
@@ -57744,7 +57747,7 @@
         <v>282</v>
       </c>
       <c r="P273" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q273">
         <v>3.4</v>
@@ -57950,7 +57953,7 @@
         <v>283</v>
       </c>
       <c r="P274" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q274">
         <v>3</v>
@@ -58362,7 +58365,7 @@
         <v>284</v>
       </c>
       <c r="P276" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q276">
         <v>2.63</v>
@@ -58568,7 +58571,7 @@
         <v>285</v>
       </c>
       <c r="P277" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -58855,7 +58858,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ278">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AR278">
         <v>1.57</v>
@@ -58980,7 +58983,7 @@
         <v>287</v>
       </c>
       <c r="P279" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q279">
         <v>2.63</v>
@@ -59392,7 +59395,7 @@
         <v>289</v>
       </c>
       <c r="P281" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q281">
         <v>2.25</v>
@@ -59598,7 +59601,7 @@
         <v>290</v>
       </c>
       <c r="P282" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q282">
         <v>2.88</v>
@@ -60216,7 +60219,7 @@
         <v>292</v>
       </c>
       <c r="P285" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q285">
         <v>2.5</v>
@@ -60422,7 +60425,7 @@
         <v>293</v>
       </c>
       <c r="P286" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -60834,7 +60837,7 @@
         <v>295</v>
       </c>
       <c r="P288" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q288">
         <v>2.5</v>
@@ -60991,6 +60994,418 @@
       </c>
       <c r="BP288">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="289" spans="1:68">
+      <c r="A289" s="1">
+        <v>288</v>
+      </c>
+      <c r="B289">
+        <v>7781368</v>
+      </c>
+      <c r="C289" t="s">
+        <v>68</v>
+      </c>
+      <c r="D289" t="s">
+        <v>69</v>
+      </c>
+      <c r="E289" s="2">
+        <v>45836.97916666666</v>
+      </c>
+      <c r="F289">
+        <v>0</v>
+      </c>
+      <c r="G289" t="s">
+        <v>81</v>
+      </c>
+      <c r="H289" t="s">
+        <v>84</v>
+      </c>
+      <c r="I289">
+        <v>1</v>
+      </c>
+      <c r="J289">
+        <v>0</v>
+      </c>
+      <c r="K289">
+        <v>1</v>
+      </c>
+      <c r="L289">
+        <v>1</v>
+      </c>
+      <c r="M289">
+        <v>1</v>
+      </c>
+      <c r="N289">
+        <v>2</v>
+      </c>
+      <c r="O289" t="s">
+        <v>139</v>
+      </c>
+      <c r="P289" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q289">
+        <v>2.75</v>
+      </c>
+      <c r="R289">
+        <v>2.5</v>
+      </c>
+      <c r="S289">
+        <v>3.25</v>
+      </c>
+      <c r="T289">
+        <v>1.25</v>
+      </c>
+      <c r="U289">
+        <v>3.75</v>
+      </c>
+      <c r="V289">
+        <v>2.2</v>
+      </c>
+      <c r="W289">
+        <v>1.62</v>
+      </c>
+      <c r="X289">
+        <v>5</v>
+      </c>
+      <c r="Y289">
+        <v>1.17</v>
+      </c>
+      <c r="Z289">
+        <v>2.12</v>
+      </c>
+      <c r="AA289">
+        <v>3.14</v>
+      </c>
+      <c r="AB289">
+        <v>3.04</v>
+      </c>
+      <c r="AC289">
+        <v>1.01</v>
+      </c>
+      <c r="AD289">
+        <v>17</v>
+      </c>
+      <c r="AE289">
+        <v>1.17</v>
+      </c>
+      <c r="AF289">
+        <v>5</v>
+      </c>
+      <c r="AG289">
+        <v>1.38</v>
+      </c>
+      <c r="AH289">
+        <v>2.9</v>
+      </c>
+      <c r="AI289">
+        <v>1.44</v>
+      </c>
+      <c r="AJ289">
+        <v>2.63</v>
+      </c>
+      <c r="AK289">
+        <v>1.35</v>
+      </c>
+      <c r="AL289">
+        <v>1.25</v>
+      </c>
+      <c r="AM289">
+        <v>1.67</v>
+      </c>
+      <c r="AN289">
+        <v>1.33</v>
+      </c>
+      <c r="AO289">
+        <v>0.27</v>
+      </c>
+      <c r="AP289">
+        <v>1.3</v>
+      </c>
+      <c r="AQ289">
+        <v>0.33</v>
+      </c>
+      <c r="AR289">
+        <v>2.04</v>
+      </c>
+      <c r="AS289">
+        <v>1.2</v>
+      </c>
+      <c r="AT289">
+        <v>3.24</v>
+      </c>
+      <c r="AU289">
+        <v>3</v>
+      </c>
+      <c r="AV289">
+        <v>6</v>
+      </c>
+      <c r="AW289">
+        <v>9</v>
+      </c>
+      <c r="AX289">
+        <v>6</v>
+      </c>
+      <c r="AY289">
+        <v>12</v>
+      </c>
+      <c r="AZ289">
+        <v>12</v>
+      </c>
+      <c r="BA289">
+        <v>3</v>
+      </c>
+      <c r="BB289">
+        <v>7</v>
+      </c>
+      <c r="BC289">
+        <v>10</v>
+      </c>
+      <c r="BD289">
+        <v>1.76</v>
+      </c>
+      <c r="BE289">
+        <v>6.75</v>
+      </c>
+      <c r="BF289">
+        <v>2.25</v>
+      </c>
+      <c r="BG289">
+        <v>1.22</v>
+      </c>
+      <c r="BH289">
+        <v>3.7</v>
+      </c>
+      <c r="BI289">
+        <v>1.41</v>
+      </c>
+      <c r="BJ289">
+        <v>2.65</v>
+      </c>
+      <c r="BK289">
+        <v>1.66</v>
+      </c>
+      <c r="BL289">
+        <v>2.06</v>
+      </c>
+      <c r="BM289">
+        <v>2.04</v>
+      </c>
+      <c r="BN289">
+        <v>1.68</v>
+      </c>
+      <c r="BO289">
+        <v>2.55</v>
+      </c>
+      <c r="BP289">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="290" spans="1:68">
+      <c r="A290" s="1">
+        <v>289</v>
+      </c>
+      <c r="B290">
+        <v>7781369</v>
+      </c>
+      <c r="C290" t="s">
+        <v>68</v>
+      </c>
+      <c r="D290" t="s">
+        <v>69</v>
+      </c>
+      <c r="E290" s="2">
+        <v>45836.97916666666</v>
+      </c>
+      <c r="F290">
+        <v>0</v>
+      </c>
+      <c r="G290" t="s">
+        <v>82</v>
+      </c>
+      <c r="H290" t="s">
+        <v>77</v>
+      </c>
+      <c r="I290">
+        <v>1</v>
+      </c>
+      <c r="J290">
+        <v>0</v>
+      </c>
+      <c r="K290">
+        <v>1</v>
+      </c>
+      <c r="L290">
+        <v>2</v>
+      </c>
+      <c r="M290">
+        <v>0</v>
+      </c>
+      <c r="N290">
+        <v>2</v>
+      </c>
+      <c r="O290" t="s">
+        <v>296</v>
+      </c>
+      <c r="P290" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q290">
+        <v>2.2</v>
+      </c>
+      <c r="R290">
+        <v>2.3</v>
+      </c>
+      <c r="S290">
+        <v>5.5</v>
+      </c>
+      <c r="T290">
+        <v>1.36</v>
+      </c>
+      <c r="U290">
+        <v>3</v>
+      </c>
+      <c r="V290">
+        <v>2.75</v>
+      </c>
+      <c r="W290">
+        <v>1.4</v>
+      </c>
+      <c r="X290">
+        <v>7</v>
+      </c>
+      <c r="Y290">
+        <v>1.1</v>
+      </c>
+      <c r="Z290">
+        <v>1.55</v>
+      </c>
+      <c r="AA290">
+        <v>3.67</v>
+      </c>
+      <c r="AB290">
+        <v>5</v>
+      </c>
+      <c r="AC290">
+        <v>1.05</v>
+      </c>
+      <c r="AD290">
+        <v>9.5</v>
+      </c>
+      <c r="AE290">
+        <v>1.28</v>
+      </c>
+      <c r="AF290">
+        <v>3.55</v>
+      </c>
+      <c r="AG290">
+        <v>1.79</v>
+      </c>
+      <c r="AH290">
+        <v>1.91</v>
+      </c>
+      <c r="AI290">
+        <v>1.95</v>
+      </c>
+      <c r="AJ290">
+        <v>1.8</v>
+      </c>
+      <c r="AK290">
+        <v>1.14</v>
+      </c>
+      <c r="AL290">
+        <v>1.2</v>
+      </c>
+      <c r="AM290">
+        <v>2.25</v>
+      </c>
+      <c r="AN290">
+        <v>2.13</v>
+      </c>
+      <c r="AO290">
+        <v>1.11</v>
+      </c>
+      <c r="AP290">
+        <v>2.22</v>
+      </c>
+      <c r="AQ290">
+        <v>1</v>
+      </c>
+      <c r="AR290">
+        <v>1.98</v>
+      </c>
+      <c r="AS290">
+        <v>1.2</v>
+      </c>
+      <c r="AT290">
+        <v>3.18</v>
+      </c>
+      <c r="AU290">
+        <v>7</v>
+      </c>
+      <c r="AV290">
+        <v>2</v>
+      </c>
+      <c r="AW290">
+        <v>6</v>
+      </c>
+      <c r="AX290">
+        <v>10</v>
+      </c>
+      <c r="AY290">
+        <v>13</v>
+      </c>
+      <c r="AZ290">
+        <v>12</v>
+      </c>
+      <c r="BA290">
+        <v>3</v>
+      </c>
+      <c r="BB290">
+        <v>5</v>
+      </c>
+      <c r="BC290">
+        <v>8</v>
+      </c>
+      <c r="BD290">
+        <v>1.35</v>
+      </c>
+      <c r="BE290">
+        <v>7.5</v>
+      </c>
+      <c r="BF290">
+        <v>3.45</v>
+      </c>
+      <c r="BG290">
+        <v>1.22</v>
+      </c>
+      <c r="BH290">
+        <v>3.7</v>
+      </c>
+      <c r="BI290">
+        <v>1.4</v>
+      </c>
+      <c r="BJ290">
+        <v>2.7</v>
+      </c>
+      <c r="BK290">
+        <v>1.65</v>
+      </c>
+      <c r="BL290">
+        <v>2.08</v>
+      </c>
+      <c r="BM290">
+        <v>2</v>
+      </c>
+      <c r="BN290">
+        <v>1.7</v>
+      </c>
+      <c r="BO290">
+        <v>2.5</v>
+      </c>
+      <c r="BP290">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="431">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -907,6 +907,9 @@
     <t>['4502', '54']</t>
   </si>
   <si>
+    <t>['4502']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -1665,7 +1668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP290"/>
+  <dimension ref="A1:BP291"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2127,7 +2130,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -2333,7 +2336,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2745,7 +2748,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2823,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
         <v>1.8</v>
@@ -2951,7 +2954,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3157,7 +3160,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -3238,7 +3241,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ8">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3569,7 +3572,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -4393,7 +4396,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -4599,7 +4602,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4805,7 +4808,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -5835,7 +5838,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -6247,7 +6250,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6453,7 +6456,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6865,7 +6868,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -7895,7 +7898,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -8179,7 +8182,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ32">
         <v>1.11</v>
@@ -8307,7 +8310,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -9131,7 +9134,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9212,7 +9215,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ37">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR37">
         <v>0.85</v>
@@ -9749,7 +9752,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -10161,7 +10164,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -10985,7 +10988,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -11191,7 +11194,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -11397,7 +11400,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -12221,7 +12224,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12427,7 +12430,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12839,7 +12842,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -13457,7 +13460,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13663,7 +13666,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -14075,7 +14078,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14281,7 +14284,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -14487,7 +14490,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14693,7 +14696,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -14977,7 +14980,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ65">
         <v>0.78</v>
@@ -15723,7 +15726,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -16135,7 +16138,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16341,7 +16344,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16753,7 +16756,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -17165,7 +17168,7 @@
         <v>153</v>
       </c>
       <c r="P76" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q76">
         <v>3.6</v>
@@ -17864,7 +17867,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ79">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR79">
         <v>1.15</v>
@@ -17989,7 +17992,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18195,7 +18198,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18401,7 +18404,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -19019,7 +19022,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -19225,7 +19228,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -19431,7 +19434,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -20049,7 +20052,7 @@
         <v>164</v>
       </c>
       <c r="P90" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
@@ -21285,7 +21288,7 @@
         <v>168</v>
       </c>
       <c r="P96" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21363,7 +21366,7 @@
         <v>0.33</v>
       </c>
       <c r="AP96">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ96">
         <v>0.73</v>
@@ -22727,7 +22730,7 @@
         <v>122</v>
       </c>
       <c r="P103" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q103">
         <v>2.75</v>
@@ -22933,7 +22936,7 @@
         <v>173</v>
       </c>
       <c r="P104" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q104">
         <v>2.75</v>
@@ -23139,7 +23142,7 @@
         <v>174</v>
       </c>
       <c r="P105" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q105">
         <v>1.91</v>
@@ -24375,7 +24378,7 @@
         <v>109</v>
       </c>
       <c r="P111" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q111">
         <v>2.88</v>
@@ -24662,7 +24665,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ112">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR112">
         <v>1.95</v>
@@ -24993,7 +24996,7 @@
         <v>177</v>
       </c>
       <c r="P114" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25199,7 +25202,7 @@
         <v>178</v>
       </c>
       <c r="P115" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -25611,7 +25614,7 @@
         <v>179</v>
       </c>
       <c r="P117" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25817,7 +25820,7 @@
         <v>180</v>
       </c>
       <c r="P118" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -26229,7 +26232,7 @@
         <v>181</v>
       </c>
       <c r="P120" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -26641,7 +26644,7 @@
         <v>109</v>
       </c>
       <c r="P122" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q122">
         <v>2.75</v>
@@ -26719,7 +26722,7 @@
         <v>2.33</v>
       </c>
       <c r="AP122">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ122">
         <v>1.71</v>
@@ -27053,7 +27056,7 @@
         <v>129</v>
       </c>
       <c r="P124" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q124">
         <v>2.5</v>
@@ -28083,7 +28086,7 @@
         <v>187</v>
       </c>
       <c r="P129" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28289,7 +28292,7 @@
         <v>188</v>
       </c>
       <c r="P130" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q130">
         <v>2.4</v>
@@ -29113,7 +29116,7 @@
         <v>189</v>
       </c>
       <c r="P134" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q134">
         <v>3</v>
@@ -29319,7 +29322,7 @@
         <v>190</v>
       </c>
       <c r="P135" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -30555,7 +30558,7 @@
         <v>109</v>
       </c>
       <c r="P141" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q141">
         <v>2.38</v>
@@ -30839,7 +30842,7 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ142">
         <v>1.4</v>
@@ -30967,7 +30970,7 @@
         <v>174</v>
       </c>
       <c r="P143" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -31379,7 +31382,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q145">
         <v>2.4</v>
@@ -31585,7 +31588,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31791,7 +31794,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q147">
         <v>2.6</v>
@@ -31997,7 +32000,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q148">
         <v>2.05</v>
@@ -32203,7 +32206,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -32409,7 +32412,7 @@
         <v>202</v>
       </c>
       <c r="P150" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q150">
         <v>2.4</v>
@@ -32821,7 +32824,7 @@
         <v>109</v>
       </c>
       <c r="P152" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q152">
         <v>2.88</v>
@@ -33027,7 +33030,7 @@
         <v>204</v>
       </c>
       <c r="P153" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -33233,7 +33236,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q154">
         <v>3.1</v>
@@ -33314,7 +33317,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ154">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR154">
         <v>2.06</v>
@@ -33439,7 +33442,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q155">
         <v>2.2</v>
@@ -33517,7 +33520,7 @@
         <v>1</v>
       </c>
       <c r="AP155">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ155">
         <v>0.58</v>
@@ -33645,7 +33648,7 @@
         <v>207</v>
       </c>
       <c r="P156" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33851,7 +33854,7 @@
         <v>109</v>
       </c>
       <c r="P157" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q157">
         <v>3.2</v>
@@ -34469,7 +34472,7 @@
         <v>209</v>
       </c>
       <c r="P160" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q160">
         <v>2.1</v>
@@ -34881,7 +34884,7 @@
         <v>211</v>
       </c>
       <c r="P162" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q162">
         <v>2.5</v>
@@ -35911,7 +35914,7 @@
         <v>215</v>
       </c>
       <c r="P167" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -36323,7 +36326,7 @@
         <v>217</v>
       </c>
       <c r="P169" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q169">
         <v>3</v>
@@ -36529,7 +36532,7 @@
         <v>218</v>
       </c>
       <c r="P170" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36735,7 +36738,7 @@
         <v>109</v>
       </c>
       <c r="P171" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q171">
         <v>2.25</v>
@@ -36941,7 +36944,7 @@
         <v>219</v>
       </c>
       <c r="P172" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q172">
         <v>2.4</v>
@@ -37353,7 +37356,7 @@
         <v>221</v>
       </c>
       <c r="P174" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q174">
         <v>2.5</v>
@@ -37559,7 +37562,7 @@
         <v>163</v>
       </c>
       <c r="P175" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -37765,7 +37768,7 @@
         <v>113</v>
       </c>
       <c r="P176" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q176">
         <v>2.4</v>
@@ -37971,7 +37974,7 @@
         <v>222</v>
       </c>
       <c r="P177" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -38177,7 +38180,7 @@
         <v>109</v>
       </c>
       <c r="P178" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q178">
         <v>2.38</v>
@@ -38589,7 +38592,7 @@
         <v>224</v>
       </c>
       <c r="P180" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -39001,7 +39004,7 @@
         <v>225</v>
       </c>
       <c r="P182" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q182">
         <v>3.75</v>
@@ -39207,7 +39210,7 @@
         <v>226</v>
       </c>
       <c r="P183" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q183">
         <v>2.5</v>
@@ -39413,7 +39416,7 @@
         <v>227</v>
       </c>
       <c r="P184" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q184">
         <v>2.05</v>
@@ -39825,7 +39828,7 @@
         <v>228</v>
       </c>
       <c r="P186" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q186">
         <v>2.4</v>
@@ -40237,7 +40240,7 @@
         <v>230</v>
       </c>
       <c r="P188" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40443,7 +40446,7 @@
         <v>176</v>
       </c>
       <c r="P189" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -41267,7 +41270,7 @@
         <v>233</v>
       </c>
       <c r="P193" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41473,7 +41476,7 @@
         <v>234</v>
       </c>
       <c r="P194" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41885,7 +41888,7 @@
         <v>198</v>
       </c>
       <c r="P196" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q196">
         <v>2.63</v>
@@ -41963,7 +41966,7 @@
         <v>1.71</v>
       </c>
       <c r="AP196">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ196">
         <v>1.83</v>
@@ -42172,7 +42175,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ197">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR197">
         <v>1.53</v>
@@ -42297,7 +42300,7 @@
         <v>103</v>
       </c>
       <c r="P198" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q198">
         <v>2.63</v>
@@ -43327,7 +43330,7 @@
         <v>109</v>
       </c>
       <c r="P203" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q203">
         <v>2.63</v>
@@ -43739,7 +43742,7 @@
         <v>237</v>
       </c>
       <c r="P205" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -44151,7 +44154,7 @@
         <v>109</v>
       </c>
       <c r="P207" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q207">
         <v>2.25</v>
@@ -44975,7 +44978,7 @@
         <v>240</v>
       </c>
       <c r="P211" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q211">
         <v>3.2</v>
@@ -45181,7 +45184,7 @@
         <v>109</v>
       </c>
       <c r="P212" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45387,7 +45390,7 @@
         <v>241</v>
       </c>
       <c r="P213" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q213">
         <v>4</v>
@@ -45799,7 +45802,7 @@
         <v>242</v>
       </c>
       <c r="P215" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -46005,7 +46008,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q216">
         <v>3.4</v>
@@ -46211,7 +46214,7 @@
         <v>243</v>
       </c>
       <c r="P217" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q217">
         <v>2.75</v>
@@ -46623,7 +46626,7 @@
         <v>244</v>
       </c>
       <c r="P219" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q219">
         <v>3.1</v>
@@ -47035,7 +47038,7 @@
         <v>246</v>
       </c>
       <c r="P221" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q221">
         <v>2.6</v>
@@ -47241,7 +47244,7 @@
         <v>247</v>
       </c>
       <c r="P222" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q222">
         <v>2.5</v>
@@ -47447,7 +47450,7 @@
         <v>248</v>
       </c>
       <c r="P223" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47653,7 +47656,7 @@
         <v>249</v>
       </c>
       <c r="P224" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47859,7 +47862,7 @@
         <v>250</v>
       </c>
       <c r="P225" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -48065,7 +48068,7 @@
         <v>251</v>
       </c>
       <c r="P226" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q226">
         <v>2.75</v>
@@ -48271,7 +48274,7 @@
         <v>252</v>
       </c>
       <c r="P227" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q227">
         <v>1.83</v>
@@ -48477,7 +48480,7 @@
         <v>253</v>
       </c>
       <c r="P228" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48683,7 +48686,7 @@
         <v>109</v>
       </c>
       <c r="P229" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q229">
         <v>2.5</v>
@@ -48889,7 +48892,7 @@
         <v>254</v>
       </c>
       <c r="P230" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q230">
         <v>3.25</v>
@@ -48970,7 +48973,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ230">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR230">
         <v>1.42</v>
@@ -49095,7 +49098,7 @@
         <v>119</v>
       </c>
       <c r="P231" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q231">
         <v>2.4</v>
@@ -49173,7 +49176,7 @@
         <v>1.17</v>
       </c>
       <c r="AP231">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ231">
         <v>1.9</v>
@@ -49713,7 +49716,7 @@
         <v>109</v>
       </c>
       <c r="P234" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q234">
         <v>2.5</v>
@@ -50331,7 +50334,7 @@
         <v>258</v>
       </c>
       <c r="P237" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q237">
         <v>2.75</v>
@@ -50537,7 +50540,7 @@
         <v>259</v>
       </c>
       <c r="P238" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q238">
         <v>2.6</v>
@@ -50743,7 +50746,7 @@
         <v>109</v>
       </c>
       <c r="P239" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -50949,7 +50952,7 @@
         <v>140</v>
       </c>
       <c r="P240" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -51361,7 +51364,7 @@
         <v>109</v>
       </c>
       <c r="P242" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q242">
         <v>3.1</v>
@@ -51773,7 +51776,7 @@
         <v>161</v>
       </c>
       <c r="P244" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q244">
         <v>2.1</v>
@@ -52060,7 +52063,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ245">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR245">
         <v>1.17</v>
@@ -52185,7 +52188,7 @@
         <v>156</v>
       </c>
       <c r="P246" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q246">
         <v>2.5</v>
@@ -52803,7 +52806,7 @@
         <v>176</v>
       </c>
       <c r="P249" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q249">
         <v>2.5</v>
@@ -53009,7 +53012,7 @@
         <v>264</v>
       </c>
       <c r="P250" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q250">
         <v>3.2</v>
@@ -53215,7 +53218,7 @@
         <v>109</v>
       </c>
       <c r="P251" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q251">
         <v>2.75</v>
@@ -53421,7 +53424,7 @@
         <v>265</v>
       </c>
       <c r="P252" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q252">
         <v>2.25</v>
@@ -54451,7 +54454,7 @@
         <v>270</v>
       </c>
       <c r="P257" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q257">
         <v>2.63</v>
@@ -54657,7 +54660,7 @@
         <v>271</v>
       </c>
       <c r="P258" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q258">
         <v>2.3</v>
@@ -54735,7 +54738,7 @@
         <v>2.14</v>
       </c>
       <c r="AP258">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ258">
         <v>1.88</v>
@@ -54863,7 +54866,7 @@
         <v>109</v>
       </c>
       <c r="P259" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q259">
         <v>3.1</v>
@@ -55275,7 +55278,7 @@
         <v>273</v>
       </c>
       <c r="P261" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -55481,7 +55484,7 @@
         <v>274</v>
       </c>
       <c r="P262" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q262">
         <v>2.5</v>
@@ -55687,7 +55690,7 @@
         <v>234</v>
       </c>
       <c r="P263" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q263">
         <v>2.25</v>
@@ -55893,7 +55896,7 @@
         <v>109</v>
       </c>
       <c r="P264" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q264">
         <v>2.75</v>
@@ -56305,7 +56308,7 @@
         <v>109</v>
       </c>
       <c r="P266" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q266">
         <v>3.4</v>
@@ -56717,7 +56720,7 @@
         <v>277</v>
       </c>
       <c r="P268" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q268">
         <v>2.2</v>
@@ -56795,7 +56798,7 @@
         <v>0.25</v>
       </c>
       <c r="AP268">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ268">
         <v>0.22</v>
@@ -56923,7 +56926,7 @@
         <v>278</v>
       </c>
       <c r="P269" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57129,7 +57132,7 @@
         <v>279</v>
       </c>
       <c r="P270" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q270">
         <v>3.35</v>
@@ -57541,7 +57544,7 @@
         <v>281</v>
       </c>
       <c r="P272" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q272">
         <v>2.38</v>
@@ -57747,7 +57750,7 @@
         <v>282</v>
       </c>
       <c r="P273" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q273">
         <v>3.4</v>
@@ -57953,7 +57956,7 @@
         <v>283</v>
       </c>
       <c r="P274" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q274">
         <v>3</v>
@@ -58240,7 +58243,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ275">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AR275">
         <v>1.64</v>
@@ -58365,7 +58368,7 @@
         <v>284</v>
       </c>
       <c r="P276" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q276">
         <v>2.63</v>
@@ -58571,7 +58574,7 @@
         <v>285</v>
       </c>
       <c r="P277" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -58983,7 +58986,7 @@
         <v>287</v>
       </c>
       <c r="P279" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q279">
         <v>2.63</v>
@@ -59395,7 +59398,7 @@
         <v>289</v>
       </c>
       <c r="P281" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q281">
         <v>2.25</v>
@@ -59601,7 +59604,7 @@
         <v>290</v>
       </c>
       <c r="P282" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q282">
         <v>2.88</v>
@@ -60219,7 +60222,7 @@
         <v>292</v>
       </c>
       <c r="P285" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q285">
         <v>2.5</v>
@@ -60425,7 +60428,7 @@
         <v>293</v>
       </c>
       <c r="P286" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -60837,7 +60840,7 @@
         <v>295</v>
       </c>
       <c r="P288" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q288">
         <v>2.5</v>
@@ -61406,6 +61409,212 @@
       </c>
       <c r="BP290">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="291" spans="1:68">
+      <c r="A291" s="1">
+        <v>290</v>
+      </c>
+      <c r="B291">
+        <v>7781370</v>
+      </c>
+      <c r="C291" t="s">
+        <v>68</v>
+      </c>
+      <c r="D291" t="s">
+        <v>69</v>
+      </c>
+      <c r="E291" s="2">
+        <v>45837.79166666666</v>
+      </c>
+      <c r="F291">
+        <v>0</v>
+      </c>
+      <c r="G291" t="s">
+        <v>74</v>
+      </c>
+      <c r="H291" t="s">
+        <v>89</v>
+      </c>
+      <c r="I291">
+        <v>1</v>
+      </c>
+      <c r="J291">
+        <v>0</v>
+      </c>
+      <c r="K291">
+        <v>1</v>
+      </c>
+      <c r="L291">
+        <v>1</v>
+      </c>
+      <c r="M291">
+        <v>0</v>
+      </c>
+      <c r="N291">
+        <v>1</v>
+      </c>
+      <c r="O291" t="s">
+        <v>297</v>
+      </c>
+      <c r="P291" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q291">
+        <v>2.5</v>
+      </c>
+      <c r="R291">
+        <v>2.38</v>
+      </c>
+      <c r="S291">
+        <v>3.75</v>
+      </c>
+      <c r="T291">
+        <v>1.3</v>
+      </c>
+      <c r="U291">
+        <v>3.4</v>
+      </c>
+      <c r="V291">
+        <v>2.5</v>
+      </c>
+      <c r="W291">
+        <v>1.5</v>
+      </c>
+      <c r="X291">
+        <v>6</v>
+      </c>
+      <c r="Y291">
+        <v>1.13</v>
+      </c>
+      <c r="Z291">
+        <v>1.87</v>
+      </c>
+      <c r="AA291">
+        <v>3.3</v>
+      </c>
+      <c r="AB291">
+        <v>3.53</v>
+      </c>
+      <c r="AC291">
+        <v>1.04</v>
+      </c>
+      <c r="AD291">
+        <v>10</v>
+      </c>
+      <c r="AE291">
+        <v>1.22</v>
+      </c>
+      <c r="AF291">
+        <v>4.2</v>
+      </c>
+      <c r="AG291">
+        <v>1.65</v>
+      </c>
+      <c r="AH291">
+        <v>2.1</v>
+      </c>
+      <c r="AI291">
+        <v>1.57</v>
+      </c>
+      <c r="AJ291">
+        <v>2.25</v>
+      </c>
+      <c r="AK291">
+        <v>1.25</v>
+      </c>
+      <c r="AL291">
+        <v>1.22</v>
+      </c>
+      <c r="AM291">
+        <v>1.85</v>
+      </c>
+      <c r="AN291">
+        <v>1.91</v>
+      </c>
+      <c r="AO291">
+        <v>2.11</v>
+      </c>
+      <c r="AP291">
+        <v>2</v>
+      </c>
+      <c r="AQ291">
+        <v>1.9</v>
+      </c>
+      <c r="AR291">
+        <v>1.88</v>
+      </c>
+      <c r="AS291">
+        <v>1.61</v>
+      </c>
+      <c r="AT291">
+        <v>3.49</v>
+      </c>
+      <c r="AU291">
+        <v>4</v>
+      </c>
+      <c r="AV291">
+        <v>2</v>
+      </c>
+      <c r="AW291">
+        <v>6</v>
+      </c>
+      <c r="AX291">
+        <v>6</v>
+      </c>
+      <c r="AY291">
+        <v>10</v>
+      </c>
+      <c r="AZ291">
+        <v>8</v>
+      </c>
+      <c r="BA291">
+        <v>2</v>
+      </c>
+      <c r="BB291">
+        <v>3</v>
+      </c>
+      <c r="BC291">
+        <v>5</v>
+      </c>
+      <c r="BD291">
+        <v>1.56</v>
+      </c>
+      <c r="BE291">
+        <v>6.75</v>
+      </c>
+      <c r="BF291">
+        <v>2.65</v>
+      </c>
+      <c r="BG291">
+        <v>1.32</v>
+      </c>
+      <c r="BH291">
+        <v>3.05</v>
+      </c>
+      <c r="BI291">
+        <v>1.56</v>
+      </c>
+      <c r="BJ291">
+        <v>2.23</v>
+      </c>
+      <c r="BK291">
+        <v>1.92</v>
+      </c>
+      <c r="BL291">
+        <v>1.77</v>
+      </c>
+      <c r="BM291">
+        <v>2.43</v>
+      </c>
+      <c r="BN291">
+        <v>1.48</v>
+      </c>
+      <c r="BO291">
+        <v>3.15</v>
+      </c>
+      <c r="BP291">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="431">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1668,7 +1668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP291"/>
+  <dimension ref="A1:BP292"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2002,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ2">
         <v>1.6</v>
@@ -4683,7 +4683,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ15">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -7152,7 +7152,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ27">
         <v>0.78</v>
@@ -11684,7 +11684,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ49">
         <v>1</v>
@@ -12717,7 +12717,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ54">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR54">
         <v>1.95</v>
@@ -17455,7 +17455,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ77">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR77">
         <v>0.9</v>
@@ -25692,7 +25692,7 @@
         <v>1.5</v>
       </c>
       <c r="AP117">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ117">
         <v>1.4</v>
@@ -28785,7 +28785,7 @@
         <v>1</v>
       </c>
       <c r="AQ132">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR132">
         <v>1.77</v>
@@ -31875,7 +31875,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ147">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR147">
         <v>1.85</v>
@@ -32284,7 +32284,7 @@
         <v>1</v>
       </c>
       <c r="AP149">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ149">
         <v>0.5</v>
@@ -34756,7 +34756,7 @@
         <v>0.75</v>
       </c>
       <c r="AP161">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ161">
         <v>1.11</v>
@@ -40936,7 +40936,7 @@
         <v>1.14</v>
       </c>
       <c r="AP191">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ191">
         <v>0.9</v>
@@ -43205,7 +43205,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ202">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR202">
         <v>1.61</v>
@@ -46707,7 +46707,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ219">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR219">
         <v>1.44</v>
@@ -53914,7 +53914,7 @@
         <v>0.89</v>
       </c>
       <c r="AP254">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ254">
         <v>0.8</v>
@@ -54741,7 +54741,7 @@
         <v>2</v>
       </c>
       <c r="AQ258">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR258">
         <v>1.85</v>
@@ -61615,6 +61615,212 @@
       </c>
       <c r="BP291">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="292" spans="1:68">
+      <c r="A292" s="1">
+        <v>291</v>
+      </c>
+      <c r="B292">
+        <v>7781367</v>
+      </c>
+      <c r="C292" t="s">
+        <v>68</v>
+      </c>
+      <c r="D292" t="s">
+        <v>69</v>
+      </c>
+      <c r="E292" s="2">
+        <v>45837.9375</v>
+      </c>
+      <c r="F292">
+        <v>0</v>
+      </c>
+      <c r="G292" t="s">
+        <v>70</v>
+      </c>
+      <c r="H292" t="s">
+        <v>95</v>
+      </c>
+      <c r="I292">
+        <v>0</v>
+      </c>
+      <c r="J292">
+        <v>1</v>
+      </c>
+      <c r="K292">
+        <v>1</v>
+      </c>
+      <c r="L292">
+        <v>0</v>
+      </c>
+      <c r="M292">
+        <v>1</v>
+      </c>
+      <c r="N292">
+        <v>1</v>
+      </c>
+      <c r="O292" t="s">
+        <v>109</v>
+      </c>
+      <c r="P292" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q292">
+        <v>0</v>
+      </c>
+      <c r="R292">
+        <v>0</v>
+      </c>
+      <c r="S292">
+        <v>0</v>
+      </c>
+      <c r="T292">
+        <v>0</v>
+      </c>
+      <c r="U292">
+        <v>0</v>
+      </c>
+      <c r="V292">
+        <v>0</v>
+      </c>
+      <c r="W292">
+        <v>0</v>
+      </c>
+      <c r="X292">
+        <v>0</v>
+      </c>
+      <c r="Y292">
+        <v>0</v>
+      </c>
+      <c r="Z292">
+        <v>1.92</v>
+      </c>
+      <c r="AA292">
+        <v>3.3</v>
+      </c>
+      <c r="AB292">
+        <v>3.39</v>
+      </c>
+      <c r="AC292">
+        <v>0</v>
+      </c>
+      <c r="AD292">
+        <v>0</v>
+      </c>
+      <c r="AE292">
+        <v>0</v>
+      </c>
+      <c r="AF292">
+        <v>0</v>
+      </c>
+      <c r="AG292">
+        <v>1.9</v>
+      </c>
+      <c r="AH292">
+        <v>1.8</v>
+      </c>
+      <c r="AI292">
+        <v>0</v>
+      </c>
+      <c r="AJ292">
+        <v>0</v>
+      </c>
+      <c r="AK292">
+        <v>0</v>
+      </c>
+      <c r="AL292">
+        <v>0</v>
+      </c>
+      <c r="AM292">
+        <v>0</v>
+      </c>
+      <c r="AN292">
+        <v>2.38</v>
+      </c>
+      <c r="AO292">
+        <v>1.88</v>
+      </c>
+      <c r="AP292">
+        <v>2.11</v>
+      </c>
+      <c r="AQ292">
+        <v>2</v>
+      </c>
+      <c r="AR292">
+        <v>1.84</v>
+      </c>
+      <c r="AS292">
+        <v>1.57</v>
+      </c>
+      <c r="AT292">
+        <v>3.41</v>
+      </c>
+      <c r="AU292">
+        <v>4</v>
+      </c>
+      <c r="AV292">
+        <v>2</v>
+      </c>
+      <c r="AW292">
+        <v>7</v>
+      </c>
+      <c r="AX292">
+        <v>2</v>
+      </c>
+      <c r="AY292">
+        <v>11</v>
+      </c>
+      <c r="AZ292">
+        <v>4</v>
+      </c>
+      <c r="BA292">
+        <v>4</v>
+      </c>
+      <c r="BB292">
+        <v>7</v>
+      </c>
+      <c r="BC292">
+        <v>11</v>
+      </c>
+      <c r="BD292">
+        <v>0</v>
+      </c>
+      <c r="BE292">
+        <v>0</v>
+      </c>
+      <c r="BF292">
+        <v>0</v>
+      </c>
+      <c r="BG292">
+        <v>0</v>
+      </c>
+      <c r="BH292">
+        <v>0</v>
+      </c>
+      <c r="BI292">
+        <v>0</v>
+      </c>
+      <c r="BJ292">
+        <v>0</v>
+      </c>
+      <c r="BK292">
+        <v>0</v>
+      </c>
+      <c r="BL292">
+        <v>0</v>
+      </c>
+      <c r="BM292">
+        <v>0</v>
+      </c>
+      <c r="BN292">
+        <v>0</v>
+      </c>
+      <c r="BO292">
+        <v>0</v>
+      </c>
+      <c r="BP292">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -61667,31 +61667,31 @@
         <v>203</v>
       </c>
       <c r="Q292">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R292">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S292">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T292">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="U292">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V292">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="W292">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X292">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y292">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z292">
         <v>1.92</v>
@@ -61721,10 +61721,10 @@
         <v>1.8</v>
       </c>
       <c r="AI292">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AJ292">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK292">
         <v>0</v>
@@ -61757,22 +61757,22 @@
         <v>3.41</v>
       </c>
       <c r="AU292">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV292">
         <v>2</v>
       </c>
       <c r="AW292">
+        <v>10</v>
+      </c>
+      <c r="AX292">
+        <v>5</v>
+      </c>
+      <c r="AY292">
+        <v>15</v>
+      </c>
+      <c r="AZ292">
         <v>7</v>
-      </c>
-      <c r="AX292">
-        <v>2</v>
-      </c>
-      <c r="AY292">
-        <v>11</v>
-      </c>
-      <c r="AZ292">
-        <v>4</v>
       </c>
       <c r="BA292">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="432">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -910,6 +910,9 @@
     <t>['4502']</t>
   </si>
   <si>
+    <t>['20', '49', '74']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -1668,7 +1671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP292"/>
+  <dimension ref="A1:BP293"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2130,7 +2133,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -2336,7 +2339,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2748,7 +2751,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2954,7 +2957,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3035,7 +3038,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ7">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3160,7 +3163,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -3572,7 +3575,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -4396,7 +4399,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -4602,7 +4605,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4808,7 +4811,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -5838,7 +5841,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -5919,7 +5922,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ21">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR21">
         <v>2.07</v>
@@ -6250,7 +6253,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6456,7 +6459,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6868,7 +6871,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -7898,7 +7901,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -8310,7 +8313,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -8803,7 +8806,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ35">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR35">
         <v>1.23</v>
@@ -9134,7 +9137,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9418,7 +9421,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ38">
         <v>1.6</v>
@@ -9752,7 +9755,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -10164,7 +10167,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -10988,7 +10991,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -11194,7 +11197,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -11400,7 +11403,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -12224,7 +12227,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12302,7 +12305,7 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ52">
         <v>1.6</v>
@@ -12430,7 +12433,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12842,7 +12845,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -13460,7 +13463,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13666,7 +13669,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -14078,7 +14081,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14284,7 +14287,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -14490,7 +14493,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14696,7 +14699,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -15189,7 +15192,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ66">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR66">
         <v>1.35</v>
@@ -15726,7 +15729,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -16138,7 +16141,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16344,7 +16347,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16756,7 +16759,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -17168,7 +17171,7 @@
         <v>153</v>
       </c>
       <c r="P76" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q76">
         <v>3.6</v>
@@ -17992,7 +17995,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18198,7 +18201,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18404,7 +18407,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -19022,7 +19025,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -19228,7 +19231,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -19434,7 +19437,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -20052,7 +20055,7 @@
         <v>164</v>
       </c>
       <c r="P90" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
@@ -21288,7 +21291,7 @@
         <v>168</v>
       </c>
       <c r="P96" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -22730,7 +22733,7 @@
         <v>122</v>
       </c>
       <c r="P103" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q103">
         <v>2.75</v>
@@ -22808,7 +22811,7 @@
         <v>1.33</v>
       </c>
       <c r="AP103">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ103">
         <v>1.6</v>
@@ -22936,7 +22939,7 @@
         <v>173</v>
       </c>
       <c r="P104" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q104">
         <v>2.75</v>
@@ -23142,7 +23145,7 @@
         <v>174</v>
       </c>
       <c r="P105" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q105">
         <v>1.91</v>
@@ -23223,7 +23226,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ105">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR105">
         <v>1.1</v>
@@ -24378,7 +24381,7 @@
         <v>109</v>
       </c>
       <c r="P111" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q111">
         <v>2.88</v>
@@ -24662,7 +24665,7 @@
         <v>2</v>
       </c>
       <c r="AP112">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ112">
         <v>1.9</v>
@@ -24996,7 +24999,7 @@
         <v>177</v>
       </c>
       <c r="P114" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25202,7 +25205,7 @@
         <v>178</v>
       </c>
       <c r="P115" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -25614,7 +25617,7 @@
         <v>179</v>
       </c>
       <c r="P117" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25820,7 +25823,7 @@
         <v>180</v>
       </c>
       <c r="P118" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -26232,7 +26235,7 @@
         <v>181</v>
       </c>
       <c r="P120" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -26644,7 +26647,7 @@
         <v>109</v>
       </c>
       <c r="P122" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q122">
         <v>2.75</v>
@@ -27056,7 +27059,7 @@
         <v>129</v>
       </c>
       <c r="P124" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q124">
         <v>2.5</v>
@@ -28086,7 +28089,7 @@
         <v>187</v>
       </c>
       <c r="P129" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28292,7 +28295,7 @@
         <v>188</v>
       </c>
       <c r="P130" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q130">
         <v>2.4</v>
@@ -28991,7 +28994,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ133">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR133">
         <v>1.25</v>
@@ -29116,7 +29119,7 @@
         <v>189</v>
       </c>
       <c r="P134" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q134">
         <v>3</v>
@@ -29322,7 +29325,7 @@
         <v>190</v>
       </c>
       <c r="P135" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -30558,7 +30561,7 @@
         <v>109</v>
       </c>
       <c r="P141" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q141">
         <v>2.38</v>
@@ -30970,7 +30973,7 @@
         <v>174</v>
       </c>
       <c r="P143" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -31382,7 +31385,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q145">
         <v>2.4</v>
@@ -31588,7 +31591,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31794,7 +31797,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q147">
         <v>2.6</v>
@@ -32000,7 +32003,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q148">
         <v>2.05</v>
@@ -32206,7 +32209,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -32412,7 +32415,7 @@
         <v>202</v>
       </c>
       <c r="P150" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q150">
         <v>2.4</v>
@@ -32824,7 +32827,7 @@
         <v>109</v>
       </c>
       <c r="P152" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q152">
         <v>2.88</v>
@@ -33030,7 +33033,7 @@
         <v>204</v>
       </c>
       <c r="P153" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -33236,7 +33239,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q154">
         <v>3.1</v>
@@ -33442,7 +33445,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q155">
         <v>2.2</v>
@@ -33648,7 +33651,7 @@
         <v>207</v>
       </c>
       <c r="P156" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33854,7 +33857,7 @@
         <v>109</v>
       </c>
       <c r="P157" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q157">
         <v>3.2</v>
@@ -34472,7 +34475,7 @@
         <v>209</v>
       </c>
       <c r="P160" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q160">
         <v>2.1</v>
@@ -34884,7 +34887,7 @@
         <v>211</v>
       </c>
       <c r="P162" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q162">
         <v>2.5</v>
@@ -35374,7 +35377,7 @@
         <v>1.8</v>
       </c>
       <c r="AP164">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ164">
         <v>1.83</v>
@@ -35914,7 +35917,7 @@
         <v>215</v>
       </c>
       <c r="P167" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -36326,7 +36329,7 @@
         <v>217</v>
       </c>
       <c r="P169" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q169">
         <v>3</v>
@@ -36532,7 +36535,7 @@
         <v>218</v>
       </c>
       <c r="P170" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36738,7 +36741,7 @@
         <v>109</v>
       </c>
       <c r="P171" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q171">
         <v>2.25</v>
@@ -36816,7 +36819,7 @@
         <v>0.25</v>
       </c>
       <c r="AP171">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ171">
         <v>0.73</v>
@@ -36944,7 +36947,7 @@
         <v>219</v>
       </c>
       <c r="P172" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q172">
         <v>2.4</v>
@@ -37356,7 +37359,7 @@
         <v>221</v>
       </c>
       <c r="P174" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q174">
         <v>2.5</v>
@@ -37562,7 +37565,7 @@
         <v>163</v>
       </c>
       <c r="P175" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -37768,7 +37771,7 @@
         <v>113</v>
       </c>
       <c r="P176" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q176">
         <v>2.4</v>
@@ -37974,7 +37977,7 @@
         <v>222</v>
       </c>
       <c r="P177" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -38180,7 +38183,7 @@
         <v>109</v>
       </c>
       <c r="P178" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q178">
         <v>2.38</v>
@@ -38592,7 +38595,7 @@
         <v>224</v>
       </c>
       <c r="P180" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -39004,7 +39007,7 @@
         <v>225</v>
       </c>
       <c r="P182" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q182">
         <v>3.75</v>
@@ -39210,7 +39213,7 @@
         <v>226</v>
       </c>
       <c r="P183" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q183">
         <v>2.5</v>
@@ -39416,7 +39419,7 @@
         <v>227</v>
       </c>
       <c r="P184" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q184">
         <v>2.05</v>
@@ -39828,7 +39831,7 @@
         <v>228</v>
       </c>
       <c r="P186" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q186">
         <v>2.4</v>
@@ -40240,7 +40243,7 @@
         <v>230</v>
       </c>
       <c r="P188" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40446,7 +40449,7 @@
         <v>176</v>
       </c>
       <c r="P189" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -41270,7 +41273,7 @@
         <v>233</v>
       </c>
       <c r="P193" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41476,7 +41479,7 @@
         <v>234</v>
       </c>
       <c r="P194" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41557,7 +41560,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ194">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR194">
         <v>1.58</v>
@@ -41760,7 +41763,7 @@
         <v>0.33</v>
       </c>
       <c r="AP195">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ195">
         <v>0.6</v>
@@ -41888,7 +41891,7 @@
         <v>198</v>
       </c>
       <c r="P196" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q196">
         <v>2.63</v>
@@ -42300,7 +42303,7 @@
         <v>103</v>
       </c>
       <c r="P198" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q198">
         <v>2.63</v>
@@ -43330,7 +43333,7 @@
         <v>109</v>
       </c>
       <c r="P203" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q203">
         <v>2.63</v>
@@ -43742,7 +43745,7 @@
         <v>237</v>
       </c>
       <c r="P205" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -44154,7 +44157,7 @@
         <v>109</v>
       </c>
       <c r="P207" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q207">
         <v>2.25</v>
@@ -44978,7 +44981,7 @@
         <v>240</v>
       </c>
       <c r="P211" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q211">
         <v>3.2</v>
@@ -45184,7 +45187,7 @@
         <v>109</v>
       </c>
       <c r="P212" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45390,7 +45393,7 @@
         <v>241</v>
       </c>
       <c r="P213" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q213">
         <v>4</v>
@@ -45802,7 +45805,7 @@
         <v>242</v>
       </c>
       <c r="P215" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -46008,7 +46011,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q216">
         <v>3.4</v>
@@ -46214,7 +46217,7 @@
         <v>243</v>
       </c>
       <c r="P217" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q217">
         <v>2.75</v>
@@ -46626,7 +46629,7 @@
         <v>244</v>
       </c>
       <c r="P219" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q219">
         <v>3.1</v>
@@ -47038,7 +47041,7 @@
         <v>246</v>
       </c>
       <c r="P221" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q221">
         <v>2.6</v>
@@ -47244,7 +47247,7 @@
         <v>247</v>
       </c>
       <c r="P222" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q222">
         <v>2.5</v>
@@ -47322,7 +47325,7 @@
         <v>1.71</v>
       </c>
       <c r="AP222">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ222">
         <v>1.8</v>
@@ -47450,7 +47453,7 @@
         <v>248</v>
       </c>
       <c r="P223" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47656,7 +47659,7 @@
         <v>249</v>
       </c>
       <c r="P224" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47862,7 +47865,7 @@
         <v>250</v>
       </c>
       <c r="P225" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -48068,7 +48071,7 @@
         <v>251</v>
       </c>
       <c r="P226" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q226">
         <v>2.75</v>
@@ -48274,7 +48277,7 @@
         <v>252</v>
       </c>
       <c r="P227" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q227">
         <v>1.83</v>
@@ -48480,7 +48483,7 @@
         <v>253</v>
       </c>
       <c r="P228" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48686,7 +48689,7 @@
         <v>109</v>
       </c>
       <c r="P229" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q229">
         <v>2.5</v>
@@ -48764,7 +48767,7 @@
         <v>1</v>
       </c>
       <c r="AP229">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ229">
         <v>1.11</v>
@@ -48892,7 +48895,7 @@
         <v>254</v>
       </c>
       <c r="P230" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q230">
         <v>3.25</v>
@@ -49098,7 +49101,7 @@
         <v>119</v>
       </c>
       <c r="P231" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q231">
         <v>2.4</v>
@@ -49716,7 +49719,7 @@
         <v>109</v>
       </c>
       <c r="P234" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q234">
         <v>2.5</v>
@@ -50334,7 +50337,7 @@
         <v>258</v>
       </c>
       <c r="P237" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q237">
         <v>2.75</v>
@@ -50540,7 +50543,7 @@
         <v>259</v>
       </c>
       <c r="P238" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q238">
         <v>2.6</v>
@@ -50746,7 +50749,7 @@
         <v>109</v>
       </c>
       <c r="P239" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -50952,7 +50955,7 @@
         <v>140</v>
       </c>
       <c r="P240" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -51364,7 +51367,7 @@
         <v>109</v>
       </c>
       <c r="P242" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q242">
         <v>3.1</v>
@@ -51776,7 +51779,7 @@
         <v>161</v>
       </c>
       <c r="P244" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q244">
         <v>2.1</v>
@@ -52188,7 +52191,7 @@
         <v>156</v>
       </c>
       <c r="P246" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q246">
         <v>2.5</v>
@@ -52806,7 +52809,7 @@
         <v>176</v>
       </c>
       <c r="P249" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q249">
         <v>2.5</v>
@@ -53012,7 +53015,7 @@
         <v>264</v>
       </c>
       <c r="P250" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q250">
         <v>3.2</v>
@@ -53218,7 +53221,7 @@
         <v>109</v>
       </c>
       <c r="P251" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q251">
         <v>2.75</v>
@@ -53424,7 +53427,7 @@
         <v>265</v>
       </c>
       <c r="P252" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q252">
         <v>2.25</v>
@@ -54120,7 +54123,7 @@
         <v>0.29</v>
       </c>
       <c r="AP255">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ255">
         <v>0.22</v>
@@ -54454,7 +54457,7 @@
         <v>270</v>
       </c>
       <c r="P257" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q257">
         <v>2.63</v>
@@ -54660,7 +54663,7 @@
         <v>271</v>
       </c>
       <c r="P258" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q258">
         <v>2.3</v>
@@ -54866,7 +54869,7 @@
         <v>109</v>
       </c>
       <c r="P259" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q259">
         <v>3.1</v>
@@ -55278,7 +55281,7 @@
         <v>273</v>
       </c>
       <c r="P261" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -55484,7 +55487,7 @@
         <v>274</v>
       </c>
       <c r="P262" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q262">
         <v>2.5</v>
@@ -55690,7 +55693,7 @@
         <v>234</v>
       </c>
       <c r="P263" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q263">
         <v>2.25</v>
@@ -55896,7 +55899,7 @@
         <v>109</v>
       </c>
       <c r="P264" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q264">
         <v>2.75</v>
@@ -56308,7 +56311,7 @@
         <v>109</v>
       </c>
       <c r="P266" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q266">
         <v>3.4</v>
@@ -56720,7 +56723,7 @@
         <v>277</v>
       </c>
       <c r="P268" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q268">
         <v>2.2</v>
@@ -56926,7 +56929,7 @@
         <v>278</v>
       </c>
       <c r="P269" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57132,7 +57135,7 @@
         <v>279</v>
       </c>
       <c r="P270" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q270">
         <v>3.35</v>
@@ -57544,7 +57547,7 @@
         <v>281</v>
       </c>
       <c r="P272" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q272">
         <v>2.38</v>
@@ -57750,7 +57753,7 @@
         <v>282</v>
       </c>
       <c r="P273" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q273">
         <v>3.4</v>
@@ -57956,7 +57959,7 @@
         <v>283</v>
       </c>
       <c r="P274" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q274">
         <v>3</v>
@@ -58368,7 +58371,7 @@
         <v>284</v>
       </c>
       <c r="P276" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q276">
         <v>2.63</v>
@@ -58574,7 +58577,7 @@
         <v>285</v>
       </c>
       <c r="P277" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -58986,7 +58989,7 @@
         <v>287</v>
       </c>
       <c r="P279" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q279">
         <v>2.63</v>
@@ -59398,7 +59401,7 @@
         <v>289</v>
       </c>
       <c r="P281" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q281">
         <v>2.25</v>
@@ -59604,7 +59607,7 @@
         <v>290</v>
       </c>
       <c r="P282" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q282">
         <v>2.88</v>
@@ -60222,7 +60225,7 @@
         <v>292</v>
       </c>
       <c r="P285" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q285">
         <v>2.5</v>
@@ -60428,7 +60431,7 @@
         <v>293</v>
       </c>
       <c r="P286" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -60840,7 +60843,7 @@
         <v>295</v>
       </c>
       <c r="P288" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q288">
         <v>2.5</v>
@@ -61821,6 +61824,212 @@
       </c>
       <c r="BP292">
         <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:68">
+      <c r="A293" s="1">
+        <v>292</v>
+      </c>
+      <c r="B293">
+        <v>7781371</v>
+      </c>
+      <c r="C293" t="s">
+        <v>68</v>
+      </c>
+      <c r="D293" t="s">
+        <v>69</v>
+      </c>
+      <c r="E293" s="2">
+        <v>45841.85416666666</v>
+      </c>
+      <c r="F293">
+        <v>0</v>
+      </c>
+      <c r="G293" t="s">
+        <v>96</v>
+      </c>
+      <c r="H293" t="s">
+        <v>98</v>
+      </c>
+      <c r="I293">
+        <v>1</v>
+      </c>
+      <c r="J293">
+        <v>0</v>
+      </c>
+      <c r="K293">
+        <v>1</v>
+      </c>
+      <c r="L293">
+        <v>3</v>
+      </c>
+      <c r="M293">
+        <v>0</v>
+      </c>
+      <c r="N293">
+        <v>3</v>
+      </c>
+      <c r="O293" t="s">
+        <v>298</v>
+      </c>
+      <c r="P293" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q293">
+        <v>2.07</v>
+      </c>
+      <c r="R293">
+        <v>2.47</v>
+      </c>
+      <c r="S293">
+        <v>5.86</v>
+      </c>
+      <c r="T293">
+        <v>1.3</v>
+      </c>
+      <c r="U293">
+        <v>3.2</v>
+      </c>
+      <c r="V293">
+        <v>2.62</v>
+      </c>
+      <c r="W293">
+        <v>1.49</v>
+      </c>
+      <c r="X293">
+        <v>5.5</v>
+      </c>
+      <c r="Y293">
+        <v>1.11</v>
+      </c>
+      <c r="Z293">
+        <v>1.58</v>
+      </c>
+      <c r="AA293">
+        <v>3.73</v>
+      </c>
+      <c r="AB293">
+        <v>4.6</v>
+      </c>
+      <c r="AC293">
+        <v>1.02</v>
+      </c>
+      <c r="AD293">
+        <v>10</v>
+      </c>
+      <c r="AE293">
+        <v>1.22</v>
+      </c>
+      <c r="AF293">
+        <v>3.8</v>
+      </c>
+      <c r="AG293">
+        <v>1.66</v>
+      </c>
+      <c r="AH293">
+        <v>2.08</v>
+      </c>
+      <c r="AI293">
+        <v>1.8</v>
+      </c>
+      <c r="AJ293">
+        <v>1.91</v>
+      </c>
+      <c r="AK293">
+        <v>1.17</v>
+      </c>
+      <c r="AL293">
+        <v>1.22</v>
+      </c>
+      <c r="AM293">
+        <v>2.4</v>
+      </c>
+      <c r="AN293">
+        <v>2.1</v>
+      </c>
+      <c r="AO293">
+        <v>1.14</v>
+      </c>
+      <c r="AP293">
+        <v>2.18</v>
+      </c>
+      <c r="AQ293">
+        <v>1</v>
+      </c>
+      <c r="AR293">
+        <v>1.78</v>
+      </c>
+      <c r="AS293">
+        <v>1.17</v>
+      </c>
+      <c r="AT293">
+        <v>2.95</v>
+      </c>
+      <c r="AU293">
+        <v>7</v>
+      </c>
+      <c r="AV293">
+        <v>5</v>
+      </c>
+      <c r="AW293">
+        <v>5</v>
+      </c>
+      <c r="AX293">
+        <v>9</v>
+      </c>
+      <c r="AY293">
+        <v>12</v>
+      </c>
+      <c r="AZ293">
+        <v>14</v>
+      </c>
+      <c r="BA293">
+        <v>5</v>
+      </c>
+      <c r="BB293">
+        <v>6</v>
+      </c>
+      <c r="BC293">
+        <v>11</v>
+      </c>
+      <c r="BD293">
+        <v>1.45</v>
+      </c>
+      <c r="BE293">
+        <v>7</v>
+      </c>
+      <c r="BF293">
+        <v>3.05</v>
+      </c>
+      <c r="BG293">
+        <v>1.22</v>
+      </c>
+      <c r="BH293">
+        <v>3.7</v>
+      </c>
+      <c r="BI293">
+        <v>1.4</v>
+      </c>
+      <c r="BJ293">
+        <v>2.7</v>
+      </c>
+      <c r="BK293">
+        <v>1.65</v>
+      </c>
+      <c r="BL293">
+        <v>2.08</v>
+      </c>
+      <c r="BM293">
+        <v>2</v>
+      </c>
+      <c r="BN293">
+        <v>1.71</v>
+      </c>
+      <c r="BO293">
+        <v>2.55</v>
+      </c>
+      <c r="BP293">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="435">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -913,6 +913,9 @@
     <t>['20', '49', '74']</t>
   </si>
   <si>
+    <t>['2', '60', '77']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -1311,6 +1314,12 @@
   <si>
     <t>['4501']</t>
   </si>
+  <si>
+    <t>['35', '58']</t>
+  </si>
+  <si>
+    <t>['4', '53']</t>
+  </si>
 </sst>
 </file>
 
@@ -1671,7 +1680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP293"/>
+  <dimension ref="A1:BP296"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2008,7 +2017,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ2">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2133,7 +2142,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -2339,7 +2348,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2751,7 +2760,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2957,7 +2966,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3163,7 +3172,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -3450,7 +3459,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ9">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3575,7 +3584,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -4399,7 +4408,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -4605,7 +4614,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4686,7 +4695,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ15">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4811,7 +4820,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4889,7 +4898,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AQ16">
         <v>1.8</v>
@@ -5841,7 +5850,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -6253,7 +6262,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6459,7 +6468,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6871,7 +6880,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -6949,7 +6958,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ26">
         <v>1.6</v>
@@ -7901,7 +7910,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -8313,7 +8322,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -9012,7 +9021,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ36">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR36">
         <v>1.23</v>
@@ -9137,7 +9146,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9755,7 +9764,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9833,7 +9842,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ40">
         <v>1.8</v>
@@ -10167,7 +10176,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -10660,7 +10669,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ44">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR44">
         <v>1.88</v>
@@ -10991,7 +11000,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -11069,7 +11078,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AQ46">
         <v>0.5</v>
@@ -11197,7 +11206,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -11403,7 +11412,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -12227,7 +12236,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12433,7 +12442,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12514,7 +12523,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ53">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR53">
         <v>1.56</v>
@@ -12717,10 +12726,10 @@
         <v>3</v>
       </c>
       <c r="AP54">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ54">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR54">
         <v>1.95</v>
@@ -12845,7 +12854,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -13463,7 +13472,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13669,7 +13678,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -14081,7 +14090,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14287,7 +14296,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -14493,7 +14502,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14699,7 +14708,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -15729,7 +15738,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -16141,7 +16150,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16219,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ71">
         <v>1.22</v>
@@ -16347,7 +16356,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16759,7 +16768,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -17171,7 +17180,7 @@
         <v>153</v>
       </c>
       <c r="P76" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q76">
         <v>3.6</v>
@@ -17458,7 +17467,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ77">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR77">
         <v>0.9</v>
@@ -17661,7 +17670,7 @@
         <v>0.5</v>
       </c>
       <c r="AP78">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ78">
         <v>0.58</v>
@@ -17995,7 +18004,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18201,7 +18210,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18407,7 +18416,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -18691,10 +18700,10 @@
         <v>0</v>
       </c>
       <c r="AP83">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ83">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR83">
         <v>1.35</v>
@@ -19025,7 +19034,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -19231,7 +19240,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -19309,7 +19318,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AQ86">
         <v>1.6</v>
@@ -19437,7 +19446,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -20055,7 +20064,7 @@
         <v>164</v>
       </c>
       <c r="P90" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
@@ -21291,7 +21300,7 @@
         <v>168</v>
       </c>
       <c r="P96" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -22733,7 +22742,7 @@
         <v>122</v>
       </c>
       <c r="P103" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q103">
         <v>2.75</v>
@@ -22814,7 +22823,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ103">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR103">
         <v>1.61</v>
@@ -22939,7 +22948,7 @@
         <v>173</v>
       </c>
       <c r="P104" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q104">
         <v>2.75</v>
@@ -23145,7 +23154,7 @@
         <v>174</v>
       </c>
       <c r="P105" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q105">
         <v>1.91</v>
@@ -23432,7 +23441,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ106">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR106">
         <v>1.03</v>
@@ -24381,7 +24390,7 @@
         <v>109</v>
       </c>
       <c r="P111" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q111">
         <v>2.88</v>
@@ -24871,7 +24880,7 @@
         <v>0.25</v>
       </c>
       <c r="AP113">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ113">
         <v>0.9</v>
@@ -24999,7 +25008,7 @@
         <v>177</v>
       </c>
       <c r="P114" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25205,7 +25214,7 @@
         <v>178</v>
       </c>
       <c r="P115" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -25283,7 +25292,7 @@
         <v>2</v>
       </c>
       <c r="AP115">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ115">
         <v>1.8</v>
@@ -25489,7 +25498,7 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AQ116">
         <v>1.11</v>
@@ -25617,7 +25626,7 @@
         <v>179</v>
       </c>
       <c r="P117" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25823,7 +25832,7 @@
         <v>180</v>
       </c>
       <c r="P118" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -26235,7 +26244,7 @@
         <v>181</v>
       </c>
       <c r="P120" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -26647,7 +26656,7 @@
         <v>109</v>
       </c>
       <c r="P122" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q122">
         <v>2.75</v>
@@ -27059,7 +27068,7 @@
         <v>129</v>
       </c>
       <c r="P124" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q124">
         <v>2.5</v>
@@ -28089,7 +28098,7 @@
         <v>187</v>
       </c>
       <c r="P129" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28295,7 +28304,7 @@
         <v>188</v>
       </c>
       <c r="P130" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q130">
         <v>2.4</v>
@@ -28788,7 +28797,7 @@
         <v>1</v>
       </c>
       <c r="AQ132">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR132">
         <v>1.77</v>
@@ -29119,7 +29128,7 @@
         <v>189</v>
       </c>
       <c r="P134" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q134">
         <v>3</v>
@@ -29325,7 +29334,7 @@
         <v>190</v>
       </c>
       <c r="P135" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -29406,7 +29415,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ135">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR135">
         <v>2.04</v>
@@ -29612,7 +29621,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ136">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR136">
         <v>1.75</v>
@@ -30561,7 +30570,7 @@
         <v>109</v>
       </c>
       <c r="P141" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q141">
         <v>2.38</v>
@@ -30973,7 +30982,7 @@
         <v>174</v>
       </c>
       <c r="P143" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -31385,7 +31394,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q145">
         <v>2.4</v>
@@ -31591,7 +31600,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31669,7 +31678,7 @@
         <v>0.8</v>
       </c>
       <c r="AP146">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ146">
         <v>0.9</v>
@@ -31797,7 +31806,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q147">
         <v>2.6</v>
@@ -31878,7 +31887,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ147">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR147">
         <v>1.85</v>
@@ -32003,7 +32012,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q148">
         <v>2.05</v>
@@ -32209,7 +32218,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -32415,7 +32424,7 @@
         <v>202</v>
       </c>
       <c r="P150" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q150">
         <v>2.4</v>
@@ -32493,7 +32502,7 @@
         <v>1.75</v>
       </c>
       <c r="AP150">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AQ150">
         <v>1.22</v>
@@ -32827,7 +32836,7 @@
         <v>109</v>
       </c>
       <c r="P152" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q152">
         <v>2.88</v>
@@ -33033,7 +33042,7 @@
         <v>204</v>
       </c>
       <c r="P153" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -33239,7 +33248,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q154">
         <v>3.1</v>
@@ -33445,7 +33454,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q155">
         <v>2.2</v>
@@ -33651,7 +33660,7 @@
         <v>207</v>
       </c>
       <c r="P156" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33857,7 +33866,7 @@
         <v>109</v>
       </c>
       <c r="P157" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q157">
         <v>3.2</v>
@@ -33938,7 +33947,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ157">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR157">
         <v>1.56</v>
@@ -34475,7 +34484,7 @@
         <v>209</v>
       </c>
       <c r="P160" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q160">
         <v>2.1</v>
@@ -34887,7 +34896,7 @@
         <v>211</v>
       </c>
       <c r="P162" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q162">
         <v>2.5</v>
@@ -35917,7 +35926,7 @@
         <v>215</v>
       </c>
       <c r="P167" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -36329,7 +36338,7 @@
         <v>217</v>
       </c>
       <c r="P169" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q169">
         <v>3</v>
@@ -36535,7 +36544,7 @@
         <v>218</v>
       </c>
       <c r="P170" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36741,7 +36750,7 @@
         <v>109</v>
       </c>
       <c r="P171" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q171">
         <v>2.25</v>
@@ -36947,7 +36956,7 @@
         <v>219</v>
       </c>
       <c r="P172" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q172">
         <v>2.4</v>
@@ -37359,7 +37368,7 @@
         <v>221</v>
       </c>
       <c r="P174" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q174">
         <v>2.5</v>
@@ -37437,7 +37446,7 @@
         <v>1</v>
       </c>
       <c r="AP174">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ174">
         <v>0.82</v>
@@ -37565,7 +37574,7 @@
         <v>163</v>
       </c>
       <c r="P175" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -37771,7 +37780,7 @@
         <v>113</v>
       </c>
       <c r="P176" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q176">
         <v>2.4</v>
@@ -37977,7 +37986,7 @@
         <v>222</v>
       </c>
       <c r="P177" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -38183,7 +38192,7 @@
         <v>109</v>
       </c>
       <c r="P178" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q178">
         <v>2.38</v>
@@ -38261,7 +38270,7 @@
         <v>0.75</v>
       </c>
       <c r="AP178">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ178">
         <v>1.4</v>
@@ -38470,7 +38479,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ179">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR179">
         <v>1.28</v>
@@ -38595,7 +38604,7 @@
         <v>224</v>
       </c>
       <c r="P180" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -39007,7 +39016,7 @@
         <v>225</v>
       </c>
       <c r="P182" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q182">
         <v>3.75</v>
@@ -39213,7 +39222,7 @@
         <v>226</v>
       </c>
       <c r="P183" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q183">
         <v>2.5</v>
@@ -39419,7 +39428,7 @@
         <v>227</v>
       </c>
       <c r="P184" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q184">
         <v>2.05</v>
@@ -39831,7 +39840,7 @@
         <v>228</v>
       </c>
       <c r="P186" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q186">
         <v>2.4</v>
@@ -40118,7 +40127,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ187">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR187">
         <v>1.64</v>
@@ -40243,7 +40252,7 @@
         <v>230</v>
       </c>
       <c r="P188" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40324,7 +40333,7 @@
         <v>1</v>
       </c>
       <c r="AQ188">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR188">
         <v>1.67</v>
@@ -40449,7 +40458,7 @@
         <v>176</v>
       </c>
       <c r="P189" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -41273,7 +41282,7 @@
         <v>233</v>
       </c>
       <c r="P193" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41479,7 +41488,7 @@
         <v>234</v>
       </c>
       <c r="P194" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41891,7 +41900,7 @@
         <v>198</v>
       </c>
       <c r="P196" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q196">
         <v>2.63</v>
@@ -42303,7 +42312,7 @@
         <v>103</v>
       </c>
       <c r="P198" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q198">
         <v>2.63</v>
@@ -43208,7 +43217,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ202">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR202">
         <v>1.61</v>
@@ -43333,7 +43342,7 @@
         <v>109</v>
       </c>
       <c r="P203" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q203">
         <v>2.63</v>
@@ -43411,7 +43420,7 @@
         <v>0.6</v>
       </c>
       <c r="AP203">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ203">
         <v>1.11</v>
@@ -43617,7 +43626,7 @@
         <v>1</v>
       </c>
       <c r="AP204">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ204">
         <v>0.82</v>
@@ -43745,7 +43754,7 @@
         <v>237</v>
       </c>
       <c r="P205" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -44032,7 +44041,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ206">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR206">
         <v>1.84</v>
@@ -44157,7 +44166,7 @@
         <v>109</v>
       </c>
       <c r="P207" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q207">
         <v>2.25</v>
@@ -44441,7 +44450,7 @@
         <v>0.83</v>
       </c>
       <c r="AP208">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AQ208">
         <v>0.88</v>
@@ -44981,7 +44990,7 @@
         <v>240</v>
       </c>
       <c r="P211" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q211">
         <v>3.2</v>
@@ -45187,7 +45196,7 @@
         <v>109</v>
       </c>
       <c r="P212" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45393,7 +45402,7 @@
         <v>241</v>
       </c>
       <c r="P213" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q213">
         <v>4</v>
@@ -45805,7 +45814,7 @@
         <v>242</v>
       </c>
       <c r="P215" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -46011,7 +46020,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q216">
         <v>3.4</v>
@@ -46217,7 +46226,7 @@
         <v>243</v>
       </c>
       <c r="P217" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q217">
         <v>2.75</v>
@@ -46629,7 +46638,7 @@
         <v>244</v>
       </c>
       <c r="P219" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q219">
         <v>3.1</v>
@@ -46710,7 +46719,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ219">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR219">
         <v>1.44</v>
@@ -46913,7 +46922,7 @@
         <v>0.71</v>
       </c>
       <c r="AP220">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ220">
         <v>0.5</v>
@@ -47041,7 +47050,7 @@
         <v>246</v>
       </c>
       <c r="P221" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q221">
         <v>2.6</v>
@@ -47247,7 +47256,7 @@
         <v>247</v>
       </c>
       <c r="P222" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q222">
         <v>2.5</v>
@@ -47453,7 +47462,7 @@
         <v>248</v>
       </c>
       <c r="P223" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47659,7 +47668,7 @@
         <v>249</v>
       </c>
       <c r="P224" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47865,7 +47874,7 @@
         <v>250</v>
       </c>
       <c r="P225" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -48071,7 +48080,7 @@
         <v>251</v>
       </c>
       <c r="P226" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q226">
         <v>2.75</v>
@@ -48277,7 +48286,7 @@
         <v>252</v>
       </c>
       <c r="P227" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q227">
         <v>1.83</v>
@@ -48483,7 +48492,7 @@
         <v>253</v>
       </c>
       <c r="P228" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48689,7 +48698,7 @@
         <v>109</v>
       </c>
       <c r="P229" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q229">
         <v>2.5</v>
@@ -48895,7 +48904,7 @@
         <v>254</v>
       </c>
       <c r="P230" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q230">
         <v>3.25</v>
@@ -49101,7 +49110,7 @@
         <v>119</v>
       </c>
       <c r="P231" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q231">
         <v>2.4</v>
@@ -49719,7 +49728,7 @@
         <v>109</v>
       </c>
       <c r="P234" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q234">
         <v>2.5</v>
@@ -49797,7 +49806,7 @@
         <v>1.17</v>
       </c>
       <c r="AP234">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AQ234">
         <v>1.4</v>
@@ -50212,7 +50221,7 @@
         <v>2</v>
       </c>
       <c r="AQ236">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR236">
         <v>1.96</v>
@@ -50337,7 +50346,7 @@
         <v>258</v>
       </c>
       <c r="P237" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q237">
         <v>2.75</v>
@@ -50543,7 +50552,7 @@
         <v>259</v>
       </c>
       <c r="P238" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q238">
         <v>2.6</v>
@@ -50749,7 +50758,7 @@
         <v>109</v>
       </c>
       <c r="P239" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -50955,7 +50964,7 @@
         <v>140</v>
       </c>
       <c r="P240" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -51367,7 +51376,7 @@
         <v>109</v>
       </c>
       <c r="P242" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q242">
         <v>3.1</v>
@@ -51779,7 +51788,7 @@
         <v>161</v>
       </c>
       <c r="P244" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q244">
         <v>2.1</v>
@@ -52063,7 +52072,7 @@
         <v>2.14</v>
       </c>
       <c r="AP245">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ245">
         <v>1.9</v>
@@ -52191,7 +52200,7 @@
         <v>156</v>
       </c>
       <c r="P246" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q246">
         <v>2.5</v>
@@ -52272,7 +52281,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ246">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR246">
         <v>1.72</v>
@@ -52475,7 +52484,7 @@
         <v>0.89</v>
       </c>
       <c r="AP247">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AQ247">
         <v>0.82</v>
@@ -52809,7 +52818,7 @@
         <v>176</v>
       </c>
       <c r="P249" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q249">
         <v>2.5</v>
@@ -52890,7 +52899,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ249">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR249">
         <v>1.98</v>
@@ -53015,7 +53024,7 @@
         <v>264</v>
       </c>
       <c r="P250" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q250">
         <v>3.2</v>
@@ -53221,7 +53230,7 @@
         <v>109</v>
       </c>
       <c r="P251" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q251">
         <v>2.75</v>
@@ -53299,7 +53308,7 @@
         <v>0.88</v>
       </c>
       <c r="AP251">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ251">
         <v>1</v>
@@ -53427,7 +53436,7 @@
         <v>265</v>
       </c>
       <c r="P252" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q252">
         <v>2.25</v>
@@ -53920,7 +53929,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ254">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AR254">
         <v>1.77</v>
@@ -54457,7 +54466,7 @@
         <v>270</v>
       </c>
       <c r="P257" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q257">
         <v>2.63</v>
@@ -54663,7 +54672,7 @@
         <v>271</v>
       </c>
       <c r="P258" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q258">
         <v>2.3</v>
@@ -54744,7 +54753,7 @@
         <v>2</v>
       </c>
       <c r="AQ258">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR258">
         <v>1.85</v>
@@ -54869,7 +54878,7 @@
         <v>109</v>
       </c>
       <c r="P259" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q259">
         <v>3.1</v>
@@ -55281,7 +55290,7 @@
         <v>273</v>
       </c>
       <c r="P261" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -55487,7 +55496,7 @@
         <v>274</v>
       </c>
       <c r="P262" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q262">
         <v>2.5</v>
@@ -55693,7 +55702,7 @@
         <v>234</v>
       </c>
       <c r="P263" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q263">
         <v>2.25</v>
@@ -55899,7 +55908,7 @@
         <v>109</v>
       </c>
       <c r="P264" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q264">
         <v>2.75</v>
@@ -56311,7 +56320,7 @@
         <v>109</v>
       </c>
       <c r="P266" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q266">
         <v>3.4</v>
@@ -56389,7 +56398,7 @@
         <v>1.25</v>
       </c>
       <c r="AP266">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ266">
         <v>1.6</v>
@@ -56723,7 +56732,7 @@
         <v>277</v>
       </c>
       <c r="P268" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q268">
         <v>2.2</v>
@@ -56929,7 +56938,7 @@
         <v>278</v>
       </c>
       <c r="P269" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57135,7 +57144,7 @@
         <v>279</v>
       </c>
       <c r="P270" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q270">
         <v>3.35</v>
@@ -57547,7 +57556,7 @@
         <v>281</v>
       </c>
       <c r="P272" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q272">
         <v>2.38</v>
@@ -57753,7 +57762,7 @@
         <v>282</v>
       </c>
       <c r="P273" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q273">
         <v>3.4</v>
@@ -57959,7 +57968,7 @@
         <v>283</v>
       </c>
       <c r="P274" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q274">
         <v>3</v>
@@ -58371,7 +58380,7 @@
         <v>284</v>
       </c>
       <c r="P276" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q276">
         <v>2.63</v>
@@ -58449,7 +58458,7 @@
         <v>1.22</v>
       </c>
       <c r="AP276">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ276">
         <v>1.4</v>
@@ -58577,7 +58586,7 @@
         <v>285</v>
       </c>
       <c r="P277" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -58861,7 +58870,7 @@
         <v>0.3</v>
       </c>
       <c r="AP278">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ278">
         <v>0.33</v>
@@ -58989,7 +58998,7 @@
         <v>287</v>
       </c>
       <c r="P279" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q279">
         <v>2.63</v>
@@ -59401,7 +59410,7 @@
         <v>289</v>
       </c>
       <c r="P281" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q281">
         <v>2.25</v>
@@ -59607,7 +59616,7 @@
         <v>290</v>
       </c>
       <c r="P282" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q282">
         <v>2.88</v>
@@ -59688,7 +59697,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ282">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR282">
         <v>1.63</v>
@@ -60225,7 +60234,7 @@
         <v>292</v>
       </c>
       <c r="P285" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q285">
         <v>2.5</v>
@@ -60431,7 +60440,7 @@
         <v>293</v>
       </c>
       <c r="P286" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -60509,7 +60518,7 @@
         <v>1.67</v>
       </c>
       <c r="AP286">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ286">
         <v>1.8</v>
@@ -60843,7 +60852,7 @@
         <v>295</v>
       </c>
       <c r="P288" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q288">
         <v>2.5</v>
@@ -61748,7 +61757,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ292">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR292">
         <v>1.84</v>
@@ -61864,16 +61873,16 @@
         <v>3</v>
       </c>
       <c r="M293">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N293">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O293" t="s">
         <v>298</v>
       </c>
       <c r="P293" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="Q293">
         <v>2.07</v>
@@ -61969,19 +61978,19 @@
         <v>7</v>
       </c>
       <c r="AV293">
+        <v>3</v>
+      </c>
+      <c r="AW293">
+        <v>3</v>
+      </c>
+      <c r="AX293">
         <v>5</v>
       </c>
-      <c r="AW293">
-        <v>5</v>
-      </c>
-      <c r="AX293">
-        <v>9</v>
-      </c>
       <c r="AY293">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ293">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="BA293">
         <v>5</v>
@@ -62030,6 +62039,624 @@
       </c>
       <c r="BP293">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="294" spans="1:68">
+      <c r="A294" s="1">
+        <v>293</v>
+      </c>
+      <c r="B294">
+        <v>7781372</v>
+      </c>
+      <c r="C294" t="s">
+        <v>68</v>
+      </c>
+      <c r="D294" t="s">
+        <v>69</v>
+      </c>
+      <c r="E294" s="2">
+        <v>45842.90625</v>
+      </c>
+      <c r="F294">
+        <v>0</v>
+      </c>
+      <c r="G294" t="s">
+        <v>97</v>
+      </c>
+      <c r="H294" t="s">
+        <v>92</v>
+      </c>
+      <c r="I294">
+        <v>0</v>
+      </c>
+      <c r="J294">
+        <v>1</v>
+      </c>
+      <c r="K294">
+        <v>1</v>
+      </c>
+      <c r="L294">
+        <v>1</v>
+      </c>
+      <c r="M294">
+        <v>2</v>
+      </c>
+      <c r="N294">
+        <v>3</v>
+      </c>
+      <c r="O294" t="s">
+        <v>112</v>
+      </c>
+      <c r="P294" t="s">
+        <v>433</v>
+      </c>
+      <c r="Q294">
+        <v>3.1</v>
+      </c>
+      <c r="R294">
+        <v>2.38</v>
+      </c>
+      <c r="S294">
+        <v>3</v>
+      </c>
+      <c r="T294">
+        <v>1.3</v>
+      </c>
+      <c r="U294">
+        <v>3.4</v>
+      </c>
+      <c r="V294">
+        <v>2.38</v>
+      </c>
+      <c r="W294">
+        <v>1.53</v>
+      </c>
+      <c r="X294">
+        <v>6</v>
+      </c>
+      <c r="Y294">
+        <v>1.13</v>
+      </c>
+      <c r="Z294">
+        <v>2.52</v>
+      </c>
+      <c r="AA294">
+        <v>3.21</v>
+      </c>
+      <c r="AB294">
+        <v>2.43</v>
+      </c>
+      <c r="AC294">
+        <v>1.03</v>
+      </c>
+      <c r="AD294">
+        <v>12</v>
+      </c>
+      <c r="AE294">
+        <v>1.19</v>
+      </c>
+      <c r="AF294">
+        <v>4.61</v>
+      </c>
+      <c r="AG294">
+        <v>1.58</v>
+      </c>
+      <c r="AH294">
+        <v>2.22</v>
+      </c>
+      <c r="AI294">
+        <v>1.53</v>
+      </c>
+      <c r="AJ294">
+        <v>2.38</v>
+      </c>
+      <c r="AK294">
+        <v>1.52</v>
+      </c>
+      <c r="AL294">
+        <v>1.27</v>
+      </c>
+      <c r="AM294">
+        <v>1.47</v>
+      </c>
+      <c r="AN294">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AO294">
+        <v>1.6</v>
+      </c>
+      <c r="AP294">
+        <v>0.5</v>
+      </c>
+      <c r="AQ294">
+        <v>1.73</v>
+      </c>
+      <c r="AR294">
+        <v>1.24</v>
+      </c>
+      <c r="AS294">
+        <v>1.4</v>
+      </c>
+      <c r="AT294">
+        <v>2.64</v>
+      </c>
+      <c r="AU294">
+        <v>4</v>
+      </c>
+      <c r="AV294">
+        <v>5</v>
+      </c>
+      <c r="AW294">
+        <v>4</v>
+      </c>
+      <c r="AX294">
+        <v>5</v>
+      </c>
+      <c r="AY294">
+        <v>8</v>
+      </c>
+      <c r="AZ294">
+        <v>10</v>
+      </c>
+      <c r="BA294">
+        <v>4</v>
+      </c>
+      <c r="BB294">
+        <v>8</v>
+      </c>
+      <c r="BC294">
+        <v>12</v>
+      </c>
+      <c r="BD294">
+        <v>1.98</v>
+      </c>
+      <c r="BE294">
+        <v>6.25</v>
+      </c>
+      <c r="BF294">
+        <v>2</v>
+      </c>
+      <c r="BG294">
+        <v>1.3</v>
+      </c>
+      <c r="BH294">
+        <v>3.15</v>
+      </c>
+      <c r="BI294">
+        <v>1.53</v>
+      </c>
+      <c r="BJ294">
+        <v>2.32</v>
+      </c>
+      <c r="BK294">
+        <v>1.86</v>
+      </c>
+      <c r="BL294">
+        <v>1.82</v>
+      </c>
+      <c r="BM294">
+        <v>2.33</v>
+      </c>
+      <c r="BN294">
+        <v>1.52</v>
+      </c>
+      <c r="BO294">
+        <v>3</v>
+      </c>
+      <c r="BP294">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="295" spans="1:68">
+      <c r="A295" s="1">
+        <v>294</v>
+      </c>
+      <c r="B295">
+        <v>7781373</v>
+      </c>
+      <c r="C295" t="s">
+        <v>68</v>
+      </c>
+      <c r="D295" t="s">
+        <v>69</v>
+      </c>
+      <c r="E295" s="2">
+        <v>45842.9375</v>
+      </c>
+      <c r="F295">
+        <v>0</v>
+      </c>
+      <c r="G295" t="s">
+        <v>93</v>
+      </c>
+      <c r="H295" t="s">
+        <v>91</v>
+      </c>
+      <c r="I295">
+        <v>0</v>
+      </c>
+      <c r="J295">
+        <v>1</v>
+      </c>
+      <c r="K295">
+        <v>1</v>
+      </c>
+      <c r="L295">
+        <v>1</v>
+      </c>
+      <c r="M295">
+        <v>2</v>
+      </c>
+      <c r="N295">
+        <v>3</v>
+      </c>
+      <c r="O295" t="s">
+        <v>122</v>
+      </c>
+      <c r="P295" t="s">
+        <v>434</v>
+      </c>
+      <c r="Q295">
+        <v>2.4</v>
+      </c>
+      <c r="R295">
+        <v>2.4</v>
+      </c>
+      <c r="S295">
+        <v>4</v>
+      </c>
+      <c r="T295">
+        <v>1.29</v>
+      </c>
+      <c r="U295">
+        <v>3.5</v>
+      </c>
+      <c r="V295">
+        <v>2.25</v>
+      </c>
+      <c r="W295">
+        <v>1.57</v>
+      </c>
+      <c r="X295">
+        <v>5.5</v>
+      </c>
+      <c r="Y295">
+        <v>1.14</v>
+      </c>
+      <c r="Z295">
+        <v>1.82</v>
+      </c>
+      <c r="AA295">
+        <v>3.69</v>
+      </c>
+      <c r="AB295">
+        <v>3.34</v>
+      </c>
+      <c r="AC295">
+        <v>1.02</v>
+      </c>
+      <c r="AD295">
+        <v>13.5</v>
+      </c>
+      <c r="AE295">
+        <v>1.17</v>
+      </c>
+      <c r="AF295">
+        <v>5.1</v>
+      </c>
+      <c r="AG295">
+        <v>1.52</v>
+      </c>
+      <c r="AH295">
+        <v>2.35</v>
+      </c>
+      <c r="AI295">
+        <v>1.53</v>
+      </c>
+      <c r="AJ295">
+        <v>2.38</v>
+      </c>
+      <c r="AK295">
+        <v>1.29</v>
+      </c>
+      <c r="AL295">
+        <v>1.24</v>
+      </c>
+      <c r="AM295">
+        <v>1.87</v>
+      </c>
+      <c r="AN295">
+        <v>1.55</v>
+      </c>
+      <c r="AO295">
+        <v>0.8</v>
+      </c>
+      <c r="AP295">
+        <v>1.42</v>
+      </c>
+      <c r="AQ295">
+        <v>1</v>
+      </c>
+      <c r="AR295">
+        <v>1.5</v>
+      </c>
+      <c r="AS295">
+        <v>1.29</v>
+      </c>
+      <c r="AT295">
+        <v>2.79</v>
+      </c>
+      <c r="AU295">
+        <v>4</v>
+      </c>
+      <c r="AV295">
+        <v>3</v>
+      </c>
+      <c r="AW295">
+        <v>3</v>
+      </c>
+      <c r="AX295">
+        <v>3</v>
+      </c>
+      <c r="AY295">
+        <v>7</v>
+      </c>
+      <c r="AZ295">
+        <v>6</v>
+      </c>
+      <c r="BA295">
+        <v>10</v>
+      </c>
+      <c r="BB295">
+        <v>2</v>
+      </c>
+      <c r="BC295">
+        <v>12</v>
+      </c>
+      <c r="BD295">
+        <v>1.68</v>
+      </c>
+      <c r="BE295">
+        <v>6.5</v>
+      </c>
+      <c r="BF295">
+        <v>2.43</v>
+      </c>
+      <c r="BG295">
+        <v>1.28</v>
+      </c>
+      <c r="BH295">
+        <v>3.2</v>
+      </c>
+      <c r="BI295">
+        <v>1.49</v>
+      </c>
+      <c r="BJ295">
+        <v>2.4</v>
+      </c>
+      <c r="BK295">
+        <v>1.79</v>
+      </c>
+      <c r="BL295">
+        <v>1.9</v>
+      </c>
+      <c r="BM295">
+        <v>2.23</v>
+      </c>
+      <c r="BN295">
+        <v>1.56</v>
+      </c>
+      <c r="BO295">
+        <v>2.9</v>
+      </c>
+      <c r="BP295">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="296" spans="1:68">
+      <c r="A296" s="1">
+        <v>295</v>
+      </c>
+      <c r="B296">
+        <v>7781374</v>
+      </c>
+      <c r="C296" t="s">
+        <v>68</v>
+      </c>
+      <c r="D296" t="s">
+        <v>69</v>
+      </c>
+      <c r="E296" s="2">
+        <v>45842.97916666666</v>
+      </c>
+      <c r="F296">
+        <v>0</v>
+      </c>
+      <c r="G296" t="s">
+        <v>84</v>
+      </c>
+      <c r="H296" t="s">
+        <v>95</v>
+      </c>
+      <c r="I296">
+        <v>1</v>
+      </c>
+      <c r="J296">
+        <v>0</v>
+      </c>
+      <c r="K296">
+        <v>1</v>
+      </c>
+      <c r="L296">
+        <v>3</v>
+      </c>
+      <c r="M296">
+        <v>0</v>
+      </c>
+      <c r="N296">
+        <v>3</v>
+      </c>
+      <c r="O296" t="s">
+        <v>299</v>
+      </c>
+      <c r="P296" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q296">
+        <v>3.1</v>
+      </c>
+      <c r="R296">
+        <v>2.3</v>
+      </c>
+      <c r="S296">
+        <v>3</v>
+      </c>
+      <c r="T296">
+        <v>1.3</v>
+      </c>
+      <c r="U296">
+        <v>3.4</v>
+      </c>
+      <c r="V296">
+        <v>2.5</v>
+      </c>
+      <c r="W296">
+        <v>1.5</v>
+      </c>
+      <c r="X296">
+        <v>6</v>
+      </c>
+      <c r="Y296">
+        <v>1.13</v>
+      </c>
+      <c r="Z296">
+        <v>2.44</v>
+      </c>
+      <c r="AA296">
+        <v>3.27</v>
+      </c>
+      <c r="AB296">
+        <v>2.47</v>
+      </c>
+      <c r="AC296">
+        <v>1.03</v>
+      </c>
+      <c r="AD296">
+        <v>11</v>
+      </c>
+      <c r="AE296">
+        <v>1.21</v>
+      </c>
+      <c r="AF296">
+        <v>4</v>
+      </c>
+      <c r="AG296">
+        <v>1.66</v>
+      </c>
+      <c r="AH296">
+        <v>2.08</v>
+      </c>
+      <c r="AI296">
+        <v>1.53</v>
+      </c>
+      <c r="AJ296">
+        <v>2.38</v>
+      </c>
+      <c r="AK296">
+        <v>1.47</v>
+      </c>
+      <c r="AL296">
+        <v>1.28</v>
+      </c>
+      <c r="AM296">
+        <v>1.49</v>
+      </c>
+      <c r="AN296">
+        <v>0.63</v>
+      </c>
+      <c r="AO296">
+        <v>2</v>
+      </c>
+      <c r="AP296">
+        <v>0.89</v>
+      </c>
+      <c r="AQ296">
+        <v>1.8</v>
+      </c>
+      <c r="AR296">
+        <v>1.45</v>
+      </c>
+      <c r="AS296">
+        <v>1.49</v>
+      </c>
+      <c r="AT296">
+        <v>2.94</v>
+      </c>
+      <c r="AU296">
+        <v>6</v>
+      </c>
+      <c r="AV296">
+        <v>2</v>
+      </c>
+      <c r="AW296">
+        <v>2</v>
+      </c>
+      <c r="AX296">
+        <v>2</v>
+      </c>
+      <c r="AY296">
+        <v>8</v>
+      </c>
+      <c r="AZ296">
+        <v>4</v>
+      </c>
+      <c r="BA296">
+        <v>6</v>
+      </c>
+      <c r="BB296">
+        <v>7</v>
+      </c>
+      <c r="BC296">
+        <v>13</v>
+      </c>
+      <c r="BD296">
+        <v>1.89</v>
+      </c>
+      <c r="BE296">
+        <v>6.75</v>
+      </c>
+      <c r="BF296">
+        <v>2.08</v>
+      </c>
+      <c r="BG296">
+        <v>1.21</v>
+      </c>
+      <c r="BH296">
+        <v>3.8</v>
+      </c>
+      <c r="BI296">
+        <v>1.38</v>
+      </c>
+      <c r="BJ296">
+        <v>2.75</v>
+      </c>
+      <c r="BK296">
+        <v>1.63</v>
+      </c>
+      <c r="BL296">
+        <v>2.12</v>
+      </c>
+      <c r="BM296">
+        <v>1.98</v>
+      </c>
+      <c r="BN296">
+        <v>1.72</v>
+      </c>
+      <c r="BO296">
+        <v>2.48</v>
+      </c>
+      <c r="BP296">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="437">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -808,16 +808,19 @@
     <t>['60', '9002']</t>
   </si>
   <si>
+    <t>['55', '83']</t>
+  </si>
+  <si>
     <t>['60']</t>
   </si>
   <si>
-    <t>['55', '9001']</t>
+    <t>['55', '90+1']</t>
   </si>
   <si>
     <t>['40', '70', '88']</t>
   </si>
   <si>
-    <t>['4501', '59', '9003']</t>
+    <t>['45+1', '59', '90+3']</t>
   </si>
   <si>
     <t>['44', '55', '57', '59']</t>
@@ -826,19 +829,19 @@
     <t>['71']</t>
   </si>
   <si>
-    <t>['35', '47', '9005']</t>
+    <t>['35', '47', '90+5']</t>
   </si>
   <si>
     <t>['2', '23']</t>
   </si>
   <si>
-    <t>['4502', '9008']</t>
+    <t>['45+2', '90+8']</t>
   </si>
   <si>
-    <t>['38']</t>
+    <t>['8', '38']</t>
   </si>
   <si>
-    <t>['8', '9001']</t>
+    <t>['8', '90+1']</t>
   </si>
   <si>
     <t>['6', '51']</t>
@@ -862,16 +865,16 @@
     <t>['60', '63', '70']</t>
   </si>
   <si>
-    <t>['40', '4503']</t>
+    <t>['40', '45+3']</t>
   </si>
   <si>
-    <t>['9003', '9006']</t>
+    <t>['90+3', '90+6']</t>
   </si>
   <si>
     <t>['30', '68']</t>
   </si>
   <si>
-    <t>['43', '66', '9006']</t>
+    <t>['43', '66', '90+6']</t>
   </si>
   <si>
     <t>['24', '28']</t>
@@ -880,10 +883,10 @@
     <t>['87']</t>
   </si>
   <si>
-    <t>['11', '56']</t>
+    <t>['11', '56', '90+4']</t>
   </si>
   <si>
-    <t>['86', '9003']</t>
+    <t>['58', '86', '90+3']</t>
   </si>
   <si>
     <t>['11', '90']</t>
@@ -904,10 +907,10 @@
     <t>['59']</t>
   </si>
   <si>
-    <t>['4502', '54']</t>
+    <t>['45+2', '54']</t>
   </si>
   <si>
-    <t>['4502']</t>
+    <t>['45+2']</t>
   </si>
   <si>
     <t>['20', '49', '74']</t>
@@ -1016,9 +1019,6 @@
   </si>
   <si>
     <t>['1', '62', '90+4']</t>
-  </si>
-  <si>
-    <t>['45+2']</t>
   </si>
   <si>
     <t>['16', '65']</t>
@@ -1261,13 +1261,19 @@
     <t>['51', '54', '58']</t>
   </si>
   <si>
-    <t>['8', '23', '30', '44', '56', '65', '9001']</t>
+    <t>['8', '23', '30', '44', '56', '65', '90+1']</t>
+  </si>
+  <si>
+    <t>['6', '66']</t>
+  </si>
+  <si>
+    <t>['90+3']</t>
   </si>
   <si>
     <t>['41', '51', '87']</t>
   </si>
   <si>
-    <t>['11', '66', '75', '9002']</t>
+    <t>['11', '66', '75', '90+2']</t>
   </si>
   <si>
     <t>['11', '59', '69', '82']</t>
@@ -1279,25 +1285,28 @@
     <t>['56', '75']</t>
   </si>
   <si>
+    <t>['23']</t>
+  </si>
+  <si>
     <t>['45', '65', '83']</t>
   </si>
   <si>
-    <t>['4502', '51', '58']</t>
+    <t>['45+2', '51', '58']</t>
   </si>
   <si>
-    <t>['9004']</t>
+    <t>['90+4']</t>
   </si>
   <si>
     <t>['7', '9', '22', '82']</t>
   </si>
   <si>
-    <t>['50', '57', '76', '9009']</t>
+    <t>['50', '57', '76', '90+9']</t>
   </si>
   <si>
     <t>['35', '37', '44', '47', '90']</t>
   </si>
   <si>
-    <t>['4504', '74']</t>
+    <t>['45+4', '74']</t>
   </si>
   <si>
     <t>['29', '40', '55']</t>
@@ -1309,10 +1318,7 @@
     <t>['56', '59']</t>
   </si>
   <si>
-    <t>['26', '77', '9006']</t>
-  </si>
-  <si>
-    <t>['4501']</t>
+    <t>['26', '77', '90+6']</t>
   </si>
   <si>
     <t>['35', '58']</t>
@@ -2142,7 +2148,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -2348,7 +2354,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2760,7 +2766,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2966,7 +2972,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3172,7 +3178,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -3584,7 +3590,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -4077,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="AQ12">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4408,7 +4414,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -4614,7 +4620,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4820,7 +4826,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -5438,7 +5444,7 @@
         <v>109</v>
       </c>
       <c r="P19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -5516,7 +5522,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ19">
         <v>1.5</v>
@@ -5850,7 +5856,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -6262,7 +6268,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6468,7 +6474,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6880,7 +6886,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -7910,7 +7916,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -8322,7 +8328,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -9146,7 +9152,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9224,7 +9230,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ37">
         <v>1.9</v>
@@ -9639,7 +9645,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ39">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AR39">
         <v>1.5</v>
@@ -9764,7 +9770,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -10176,7 +10182,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -11000,7 +11006,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -11206,7 +11212,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -11412,7 +11418,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -12236,7 +12242,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12442,7 +12448,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12854,7 +12860,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -13472,7 +13478,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13553,7 +13559,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ58">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AR58">
         <v>1.87</v>
@@ -13678,7 +13684,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -14090,7 +14096,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14296,7 +14302,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -14502,7 +14508,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14708,7 +14714,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -15738,7 +15744,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -16150,7 +16156,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16356,7 +16362,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16768,7 +16774,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -17180,7 +17186,7 @@
         <v>153</v>
       </c>
       <c r="P76" t="s">
-        <v>334</v>
+        <v>298</v>
       </c>
       <c r="Q76">
         <v>3.6</v>
@@ -17258,7 +17264,7 @@
         <v>0.5</v>
       </c>
       <c r="AP76">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ76">
         <v>0.6</v>
@@ -20682,7 +20688,7 @@
         <v>131</v>
       </c>
       <c r="P93" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q93">
         <v>2.2</v>
@@ -22411,7 +22417,7 @@
         <v>2</v>
       </c>
       <c r="AQ101">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AR101">
         <v>1.75</v>
@@ -22948,7 +22954,7 @@
         <v>173</v>
       </c>
       <c r="P104" t="s">
-        <v>334</v>
+        <v>298</v>
       </c>
       <c r="Q104">
         <v>2.75</v>
@@ -23154,7 +23160,7 @@
         <v>174</v>
       </c>
       <c r="P105" t="s">
-        <v>334</v>
+        <v>298</v>
       </c>
       <c r="Q105">
         <v>1.91</v>
@@ -24184,7 +24190,7 @@
         <v>175</v>
       </c>
       <c r="P110" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -27764,7 +27770,7 @@
         <v>0.5</v>
       </c>
       <c r="AP127">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ127">
         <v>0.78</v>
@@ -28385,7 +28391,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ130">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AR130">
         <v>1.45</v>
@@ -30570,7 +30576,7 @@
         <v>109</v>
       </c>
       <c r="P141" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q141">
         <v>2.38</v>
@@ -32630,7 +32636,7 @@
         <v>203</v>
       </c>
       <c r="P151" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q151">
         <v>2.63</v>
@@ -33741,7 +33747,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ156">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AR156">
         <v>1.51</v>
@@ -41157,7 +41163,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ192">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AR192">
         <v>1.75</v>
@@ -42106,7 +42112,7 @@
         <v>109</v>
       </c>
       <c r="P197" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q197">
         <v>2.75</v>
@@ -42596,7 +42602,7 @@
         <v>1.2</v>
       </c>
       <c r="AP199">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ199">
         <v>1.4</v>
@@ -50015,7 +50021,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ235">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AR235">
         <v>1.24</v>
@@ -52806,16 +52812,16 @@
         <v>0</v>
       </c>
       <c r="L249">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M249">
         <v>3</v>
       </c>
       <c r="N249">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O249" t="s">
-        <v>176</v>
+        <v>264</v>
       </c>
       <c r="P249" t="s">
         <v>414</v>
@@ -53021,7 +53027,7 @@
         <v>8</v>
       </c>
       <c r="O250" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P250" t="s">
         <v>415</v>
@@ -53221,16 +53227,16 @@
         <v>0</v>
       </c>
       <c r="M251">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N251">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O251" t="s">
         <v>109</v>
       </c>
       <c r="P251" t="s">
-        <v>384</v>
+        <v>416</v>
       </c>
       <c r="Q251">
         <v>2.75</v>
@@ -53433,7 +53439,7 @@
         <v>3</v>
       </c>
       <c r="O252" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P252" t="s">
         <v>337</v>
@@ -53639,7 +53645,7 @@
         <v>3</v>
       </c>
       <c r="O253" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P253" t="s">
         <v>109</v>
@@ -53845,7 +53851,7 @@
         <v>4</v>
       </c>
       <c r="O254" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P254" t="s">
         <v>161</v>
@@ -54051,7 +54057,7 @@
         <v>4</v>
       </c>
       <c r="O255" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P255" t="s">
         <v>109</v>
@@ -54257,10 +54263,10 @@
         <v>2</v>
       </c>
       <c r="O256" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P256" t="s">
-        <v>256</v>
+        <v>417</v>
       </c>
       <c r="Q256">
         <v>2.25</v>
@@ -54463,10 +54469,10 @@
         <v>6</v>
       </c>
       <c r="O257" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P257" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Q257">
         <v>2.63</v>
@@ -54669,7 +54675,7 @@
         <v>3</v>
       </c>
       <c r="O258" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P258" t="s">
         <v>384</v>
@@ -54878,7 +54884,7 @@
         <v>109</v>
       </c>
       <c r="P259" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q259">
         <v>3.1</v>
@@ -54956,7 +54962,7 @@
         <v>1.44</v>
       </c>
       <c r="AP259">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ259">
         <v>1.83</v>
@@ -55081,7 +55087,7 @@
         <v>3</v>
       </c>
       <c r="O260" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P260" t="s">
         <v>100</v>
@@ -55269,28 +55275,28 @@
         <v>94</v>
       </c>
       <c r="I261">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J261">
         <v>1</v>
       </c>
       <c r="K261">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L261">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M261">
         <v>4</v>
       </c>
       <c r="N261">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O261" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P261" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -55493,10 +55499,10 @@
         <v>6</v>
       </c>
       <c r="O262" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P262" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="Q262">
         <v>2.5</v>
@@ -55702,7 +55708,7 @@
         <v>234</v>
       </c>
       <c r="P263" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="Q263">
         <v>2.25</v>
@@ -55908,7 +55914,7 @@
         <v>109</v>
       </c>
       <c r="P264" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Q264">
         <v>2.75</v>
@@ -56096,25 +56102,25 @@
         <v>1</v>
       </c>
       <c r="J265">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K265">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L265">
         <v>2</v>
       </c>
       <c r="M265">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N265">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O265" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P265" t="s">
-        <v>109</v>
+        <v>423</v>
       </c>
       <c r="Q265">
         <v>2.88</v>
@@ -56523,7 +56529,7 @@
         <v>2</v>
       </c>
       <c r="O267" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P267" t="s">
         <v>109</v>
@@ -56729,7 +56735,7 @@
         <v>4</v>
       </c>
       <c r="O268" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P268" t="s">
         <v>379</v>
@@ -56935,10 +56941,10 @@
         <v>4</v>
       </c>
       <c r="O269" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P269" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57141,10 +57147,10 @@
         <v>5</v>
       </c>
       <c r="O270" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P270" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="Q270">
         <v>3.35</v>
@@ -57222,7 +57228,7 @@
         <v>1.63</v>
       </c>
       <c r="AP270">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ270">
         <v>1.9</v>
@@ -57347,7 +57353,7 @@
         <v>2</v>
       </c>
       <c r="O271" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P271" t="s">
         <v>203</v>
@@ -57553,10 +57559,10 @@
         <v>4</v>
       </c>
       <c r="O272" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P272" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="Q272">
         <v>2.38</v>
@@ -57759,10 +57765,10 @@
         <v>6</v>
       </c>
       <c r="O273" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P273" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="Q273">
         <v>3.4</v>
@@ -57965,7 +57971,7 @@
         <v>3</v>
       </c>
       <c r="O274" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P274" t="s">
         <v>377</v>
@@ -58377,10 +58383,10 @@
         <v>6</v>
       </c>
       <c r="O276" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P276" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="Q276">
         <v>2.63</v>
@@ -58583,10 +58589,10 @@
         <v>8</v>
       </c>
       <c r="O277" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P277" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -58789,7 +58795,7 @@
         <v>2</v>
       </c>
       <c r="O278" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P278" t="s">
         <v>109</v>
@@ -58995,10 +59001,10 @@
         <v>3</v>
       </c>
       <c r="O279" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P279" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="Q279">
         <v>2.63</v>
@@ -59192,16 +59198,16 @@
         <v>1</v>
       </c>
       <c r="L280">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M280">
         <v>0</v>
       </c>
       <c r="N280">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O280" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P280" t="s">
         <v>109</v>
@@ -59398,19 +59404,19 @@
         <v>2</v>
       </c>
       <c r="L281">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M281">
         <v>3</v>
       </c>
       <c r="N281">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O281" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P281" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="Q281">
         <v>2.25</v>
@@ -59488,10 +59494,10 @@
         <v>1</v>
       </c>
       <c r="AP281">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ281">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="AR281">
         <v>1.36</v>
@@ -59613,10 +59619,10 @@
         <v>4</v>
       </c>
       <c r="O282" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P282" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="Q282">
         <v>2.88</v>
@@ -59819,7 +59825,7 @@
         <v>1</v>
       </c>
       <c r="O283" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P283" t="s">
         <v>109</v>
@@ -60231,10 +60237,10 @@
         <v>5</v>
       </c>
       <c r="O285" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P285" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="Q285">
         <v>2.5</v>
@@ -60437,10 +60443,10 @@
         <v>5</v>
       </c>
       <c r="O286" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P286" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -60643,7 +60649,7 @@
         <v>1</v>
       </c>
       <c r="O287" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P287" t="s">
         <v>109</v>
@@ -60849,10 +60855,10 @@
         <v>2</v>
       </c>
       <c r="O288" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P288" t="s">
-        <v>432</v>
+        <v>141</v>
       </c>
       <c r="Q288">
         <v>2.5</v>
@@ -61261,7 +61267,7 @@
         <v>2</v>
       </c>
       <c r="O290" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P290" t="s">
         <v>109</v>
@@ -61467,7 +61473,7 @@
         <v>1</v>
       </c>
       <c r="O291" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P291" t="s">
         <v>109</v>
@@ -61879,7 +61885,7 @@
         <v>4</v>
       </c>
       <c r="O293" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P293" t="s">
         <v>103</v>
@@ -61978,19 +61984,19 @@
         <v>7</v>
       </c>
       <c r="AV293">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW293">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX293">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY293">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ293">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BA293">
         <v>5</v>
@@ -62088,7 +62094,7 @@
         <v>112</v>
       </c>
       <c r="P294" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="Q294">
         <v>3.1</v>
@@ -62294,7 +62300,7 @@
         <v>122</v>
       </c>
       <c r="P295" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="Q295">
         <v>2.4</v>
@@ -62497,7 +62503,7 @@
         <v>3</v>
       </c>
       <c r="O296" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P296" t="s">
         <v>109</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="449">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -919,6 +919,27 @@
     <t>['2', '60', '77']</t>
   </si>
   <si>
+    <t>['40', '65']</t>
+  </si>
+  <si>
+    <t>['2']</t>
+  </si>
+  <si>
+    <t>['19', '50']</t>
+  </si>
+  <si>
+    <t>['90+11']</t>
+  </si>
+  <si>
+    <t>['6', '43', '64']</t>
+  </si>
+  <si>
+    <t>['20', '72']</t>
+  </si>
+  <si>
+    <t>['25', '54', '67']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -1326,6 +1347,21 @@
   <si>
     <t>['4', '53']</t>
   </si>
+  <si>
+    <t>['69', '80']</t>
+  </si>
+  <si>
+    <t>['33', '40', '60', '62']</t>
+  </si>
+  <si>
+    <t>['51', '80']</t>
+  </si>
+  <si>
+    <t>['35']</t>
+  </si>
+  <si>
+    <t>['36', '45+2', '87', '90+10']</t>
+  </si>
 </sst>
 </file>
 
@@ -1686,7 +1722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP296"/>
+  <dimension ref="A1:BP305"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2148,7 +2184,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -2354,7 +2390,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2638,10 +2674,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ5">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2766,7 +2802,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2847,7 +2883,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2972,7 +3008,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3050,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ7">
         <v>1</v>
@@ -3178,7 +3214,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -3259,7 +3295,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ8">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3590,7 +3626,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -3874,10 +3910,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ11">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4286,7 +4322,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ13">
         <v>0.82</v>
@@ -4414,7 +4450,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -4620,7 +4656,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4698,7 +4734,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ15">
         <v>1.8</v>
@@ -4826,7 +4862,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -5110,10 +5146,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ17">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5316,7 +5352,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ18">
         <v>0.9</v>
@@ -5856,7 +5892,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -6268,7 +6304,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6474,7 +6510,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6886,7 +6922,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -7376,7 +7412,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ28">
         <v>1</v>
@@ -7582,10 +7618,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ29">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -7916,7 +7952,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -7997,7 +8033,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ31">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR31">
         <v>1.39</v>
@@ -8203,7 +8239,7 @@
         <v>2</v>
       </c>
       <c r="AQ32">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR32">
         <v>1.83</v>
@@ -8328,7 +8364,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -8615,7 +8651,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ34">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR34">
         <v>1.85</v>
@@ -8818,7 +8854,7 @@
         <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -9024,7 +9060,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ36">
         <v>1</v>
@@ -9152,7 +9188,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9233,7 +9269,7 @@
         <v>1</v>
       </c>
       <c r="AQ37">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR37">
         <v>0.85</v>
@@ -9439,7 +9475,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ38">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR38">
         <v>0</v>
@@ -9770,7 +9806,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9851,7 +9887,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ40">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR40">
         <v>0</v>
@@ -10054,7 +10090,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ41">
         <v>1.22</v>
@@ -10182,7 +10218,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -10260,7 +10296,7 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ42">
         <v>1.8</v>
@@ -10672,7 +10708,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ44">
         <v>1.73</v>
@@ -11006,7 +11042,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -11087,7 +11123,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ46">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR46">
         <v>0.92</v>
@@ -11212,7 +11248,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -11293,7 +11329,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ47">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR47">
         <v>0</v>
@@ -11418,7 +11454,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11499,7 +11535,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ48">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR48">
         <v>1.51</v>
@@ -11908,7 +11944,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ50">
         <v>1.83</v>
@@ -12114,7 +12150,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ51">
         <v>0.73</v>
@@ -12242,7 +12278,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12323,7 +12359,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ52">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR52">
         <v>1.84</v>
@@ -12448,7 +12484,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12860,7 +12896,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -13350,7 +13386,7 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ57">
         <v>1.5</v>
@@ -13478,7 +13514,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13556,7 +13592,7 @@
         <v>2</v>
       </c>
       <c r="AP58">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ58">
         <v>1</v>
@@ -13684,7 +13720,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13968,7 +14004,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ60">
         <v>0.33</v>
@@ -14096,7 +14132,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14177,7 +14213,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ61">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR61">
         <v>1.66</v>
@@ -14302,7 +14338,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -14380,10 +14416,10 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ62">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR62">
         <v>1.6</v>
@@ -14508,7 +14544,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14714,7 +14750,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -14792,7 +14828,7 @@
         <v>3</v>
       </c>
       <c r="AP64">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ64">
         <v>1.4</v>
@@ -15619,7 +15655,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ68">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR68">
         <v>1.48</v>
@@ -15744,7 +15780,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -16028,7 +16064,7 @@
         <v>0.25</v>
       </c>
       <c r="AP70">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ70">
         <v>0.73</v>
@@ -16156,7 +16192,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16362,7 +16398,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16440,7 +16476,7 @@
         <v>2</v>
       </c>
       <c r="AP72">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ72">
         <v>1.6</v>
@@ -16649,7 +16685,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ73">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR73">
         <v>2.23</v>
@@ -16774,7 +16810,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16855,7 +16891,7 @@
         <v>2</v>
       </c>
       <c r="AQ74">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR74">
         <v>1.88</v>
@@ -17267,7 +17303,7 @@
         <v>1</v>
       </c>
       <c r="AQ76">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR76">
         <v>0.97</v>
@@ -17885,7 +17921,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ79">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR79">
         <v>1.15</v>
@@ -18010,7 +18046,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18088,7 +18124,7 @@
         <v>2</v>
       </c>
       <c r="AP80">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ80">
         <v>1.5</v>
@@ -18216,7 +18252,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18422,7 +18458,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -19040,7 +19076,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -19118,7 +19154,7 @@
         <v>0</v>
       </c>
       <c r="AP85">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ85">
         <v>1.83</v>
@@ -19246,7 +19282,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -19327,7 +19363,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ86">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR86">
         <v>1.7</v>
@@ -19452,7 +19488,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -19530,7 +19566,7 @@
         <v>1.5</v>
       </c>
       <c r="AP87">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ87">
         <v>0.88</v>
@@ -19736,7 +19772,7 @@
         <v>0</v>
       </c>
       <c r="AP88">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ88">
         <v>0.9</v>
@@ -20070,7 +20106,7 @@
         <v>164</v>
       </c>
       <c r="P90" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
@@ -20148,10 +20184,10 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ90">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR90">
         <v>1.08</v>
@@ -20354,7 +20390,7 @@
         <v>1.5</v>
       </c>
       <c r="AP91">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ91">
         <v>1.9</v>
@@ -20560,7 +20596,7 @@
         <v>0.67</v>
       </c>
       <c r="AP92">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ92">
         <v>0.33</v>
@@ -20975,7 +21011,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ94">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR94">
         <v>1.73</v>
@@ -21178,10 +21214,10 @@
         <v>0.5</v>
       </c>
       <c r="AP95">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ95">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR95">
         <v>1.75</v>
@@ -21306,7 +21342,7 @@
         <v>168</v>
       </c>
       <c r="P96" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21593,7 +21629,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ97">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR97">
         <v>1.49</v>
@@ -22005,7 +22041,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ99">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR99">
         <v>1.7</v>
@@ -22620,7 +22656,7 @@
         <v>0.33</v>
       </c>
       <c r="AP102">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ102">
         <v>0.9</v>
@@ -22748,7 +22784,7 @@
         <v>122</v>
       </c>
       <c r="P103" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="Q103">
         <v>2.75</v>
@@ -23032,7 +23068,7 @@
         <v>0.5</v>
       </c>
       <c r="AP104">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ104">
         <v>0.89</v>
@@ -23653,7 +23689,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ107">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR107">
         <v>1.66</v>
@@ -23859,7 +23895,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ108">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR108">
         <v>1.87</v>
@@ -24062,7 +24098,7 @@
         <v>0.33</v>
       </c>
       <c r="AP109">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AQ109">
         <v>0.58</v>
@@ -24396,7 +24432,7 @@
         <v>109</v>
       </c>
       <c r="P111" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="Q111">
         <v>2.88</v>
@@ -24474,7 +24510,7 @@
         <v>1</v>
       </c>
       <c r="AP111">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ111">
         <v>1.83</v>
@@ -24683,7 +24719,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ112">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR112">
         <v>1.95</v>
@@ -25014,7 +25050,7 @@
         <v>177</v>
       </c>
       <c r="P114" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25092,7 +25128,7 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ114">
         <v>0.82</v>
@@ -25220,7 +25256,7 @@
         <v>178</v>
       </c>
       <c r="P115" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -25507,7 +25543,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ116">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR116">
         <v>1.62</v>
@@ -25632,7 +25668,7 @@
         <v>179</v>
       </c>
       <c r="P117" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25838,7 +25874,7 @@
         <v>180</v>
       </c>
       <c r="P118" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -26125,7 +26161,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ119">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR119">
         <v>0.98</v>
@@ -26250,7 +26286,7 @@
         <v>181</v>
       </c>
       <c r="P120" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -26662,7 +26698,7 @@
         <v>109</v>
       </c>
       <c r="P122" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="Q122">
         <v>2.75</v>
@@ -26743,7 +26779,7 @@
         <v>2</v>
       </c>
       <c r="AQ122">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR122">
         <v>1.93</v>
@@ -27074,7 +27110,7 @@
         <v>129</v>
       </c>
       <c r="P124" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="Q124">
         <v>2.5</v>
@@ -27361,7 +27397,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ125">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR125">
         <v>1.84</v>
@@ -27564,10 +27600,10 @@
         <v>1.25</v>
       </c>
       <c r="AP126">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AQ126">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR126">
         <v>1.94</v>
@@ -27976,7 +28012,7 @@
         <v>1.5</v>
       </c>
       <c r="AP128">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ128">
         <v>1.8</v>
@@ -28104,7 +28140,7 @@
         <v>187</v>
       </c>
       <c r="P129" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28310,7 +28346,7 @@
         <v>188</v>
       </c>
       <c r="P130" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="Q130">
         <v>2.4</v>
@@ -29006,7 +29042,7 @@
         <v>0.4</v>
       </c>
       <c r="AP133">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ133">
         <v>1</v>
@@ -29134,7 +29170,7 @@
         <v>189</v>
       </c>
       <c r="P134" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="Q134">
         <v>3</v>
@@ -29212,7 +29248,7 @@
         <v>0.75</v>
       </c>
       <c r="AP134">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ134">
         <v>0.88</v>
@@ -29340,7 +29376,7 @@
         <v>190</v>
       </c>
       <c r="P135" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -29418,7 +29454,7 @@
         <v>0</v>
       </c>
       <c r="AP135">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ135">
         <v>1</v>
@@ -29624,7 +29660,7 @@
         <v>0.75</v>
       </c>
       <c r="AP136">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ136">
         <v>1</v>
@@ -30451,7 +30487,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ140">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR140">
         <v>1.89</v>
@@ -30576,7 +30612,7 @@
         <v>109</v>
       </c>
       <c r="P141" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="Q141">
         <v>2.38</v>
@@ -30654,10 +30690,10 @@
         <v>1</v>
       </c>
       <c r="AP141">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ141">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR141">
         <v>1.68</v>
@@ -30988,7 +31024,7 @@
         <v>174</v>
       </c>
       <c r="P143" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -31066,7 +31102,7 @@
         <v>0.75</v>
       </c>
       <c r="AP143">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ143">
         <v>0.82</v>
@@ -31400,7 +31436,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="Q145">
         <v>2.4</v>
@@ -31478,10 +31514,10 @@
         <v>1.8</v>
       </c>
       <c r="AP145">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ145">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR145">
         <v>1.94</v>
@@ -31606,7 +31642,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31812,7 +31848,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="Q147">
         <v>2.6</v>
@@ -32018,7 +32054,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="Q148">
         <v>2.05</v>
@@ -32224,7 +32260,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -32305,7 +32341,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ149">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR149">
         <v>1.48</v>
@@ -32430,7 +32466,7 @@
         <v>202</v>
       </c>
       <c r="P150" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="Q150">
         <v>2.4</v>
@@ -32842,7 +32878,7 @@
         <v>109</v>
       </c>
       <c r="P152" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="Q152">
         <v>2.88</v>
@@ -32923,7 +32959,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ152">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR152">
         <v>1.12</v>
@@ -33048,7 +33084,7 @@
         <v>204</v>
       </c>
       <c r="P153" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -33129,7 +33165,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ153">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR153">
         <v>1.52</v>
@@ -33254,7 +33290,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="Q154">
         <v>3.1</v>
@@ -33332,10 +33368,10 @@
         <v>1.5</v>
       </c>
       <c r="AP154">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AQ154">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR154">
         <v>2.06</v>
@@ -33460,7 +33496,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="Q155">
         <v>2.2</v>
@@ -33666,7 +33702,7 @@
         <v>207</v>
       </c>
       <c r="P156" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -33744,7 +33780,7 @@
         <v>1.6</v>
       </c>
       <c r="AP156">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ156">
         <v>1</v>
@@ -33872,7 +33908,7 @@
         <v>109</v>
       </c>
       <c r="P157" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="Q157">
         <v>3.2</v>
@@ -34159,7 +34195,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ158">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR158">
         <v>1.51</v>
@@ -34362,7 +34398,7 @@
         <v>2</v>
       </c>
       <c r="AP159">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ159">
         <v>1.6</v>
@@ -34490,7 +34526,7 @@
         <v>209</v>
       </c>
       <c r="P160" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="Q160">
         <v>2.1</v>
@@ -34777,7 +34813,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ161">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR161">
         <v>1.68</v>
@@ -34902,7 +34938,7 @@
         <v>211</v>
       </c>
       <c r="P162" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="Q162">
         <v>2.5</v>
@@ -34980,7 +35016,7 @@
         <v>2</v>
       </c>
       <c r="AP162">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ162">
         <v>1.22</v>
@@ -35189,7 +35225,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ163">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR163">
         <v>1.87</v>
@@ -35807,7 +35843,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ166">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR166">
         <v>1.6</v>
@@ -35932,7 +35968,7 @@
         <v>215</v>
       </c>
       <c r="P167" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -36013,7 +36049,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ167">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR167">
         <v>1.76</v>
@@ -36344,7 +36380,7 @@
         <v>217</v>
       </c>
       <c r="P169" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="Q169">
         <v>3</v>
@@ -36550,7 +36586,7 @@
         <v>218</v>
       </c>
       <c r="P170" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36631,7 +36667,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ170">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR170">
         <v>1.89</v>
@@ -36756,7 +36792,7 @@
         <v>109</v>
       </c>
       <c r="P171" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="Q171">
         <v>2.25</v>
@@ -36962,7 +36998,7 @@
         <v>219</v>
       </c>
       <c r="P172" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="Q172">
         <v>2.4</v>
@@ -37040,7 +37076,7 @@
         <v>1.2</v>
       </c>
       <c r="AP172">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ172">
         <v>1</v>
@@ -37374,7 +37410,7 @@
         <v>221</v>
       </c>
       <c r="P174" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="Q174">
         <v>2.5</v>
@@ -37580,7 +37616,7 @@
         <v>163</v>
       </c>
       <c r="P175" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -37786,7 +37822,7 @@
         <v>113</v>
       </c>
       <c r="P176" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="Q176">
         <v>2.4</v>
@@ -37864,7 +37900,7 @@
         <v>0.8</v>
       </c>
       <c r="AP176">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ176">
         <v>0.58</v>
@@ -37992,7 +38028,7 @@
         <v>222</v>
       </c>
       <c r="P177" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -38198,7 +38234,7 @@
         <v>109</v>
       </c>
       <c r="P178" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="Q178">
         <v>2.38</v>
@@ -38482,7 +38518,7 @@
         <v>0.6</v>
       </c>
       <c r="AP179">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ179">
         <v>1</v>
@@ -38610,7 +38646,7 @@
         <v>224</v>
       </c>
       <c r="P180" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38894,7 +38930,7 @@
         <v>0.83</v>
       </c>
       <c r="AP181">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ181">
         <v>0.78</v>
@@ -39022,7 +39058,7 @@
         <v>225</v>
       </c>
       <c r="P182" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="Q182">
         <v>3.75</v>
@@ -39100,7 +39136,7 @@
         <v>2.2</v>
       </c>
       <c r="AP182">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AQ182">
         <v>1.5</v>
@@ -39228,7 +39264,7 @@
         <v>226</v>
       </c>
       <c r="P183" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="Q183">
         <v>2.5</v>
@@ -39434,7 +39470,7 @@
         <v>227</v>
       </c>
       <c r="P184" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="Q184">
         <v>2.05</v>
@@ -39846,7 +39882,7 @@
         <v>228</v>
       </c>
       <c r="P186" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="Q186">
         <v>2.4</v>
@@ -39924,10 +39960,10 @@
         <v>0.4</v>
       </c>
       <c r="AP186">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ186">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR186">
         <v>1.92</v>
@@ -40258,7 +40294,7 @@
         <v>230</v>
       </c>
       <c r="P188" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40464,7 +40500,7 @@
         <v>176</v>
       </c>
       <c r="P189" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40545,7 +40581,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ189">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR189">
         <v>1.57</v>
@@ -40748,7 +40784,7 @@
         <v>1.67</v>
       </c>
       <c r="AP190">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ190">
         <v>1.22</v>
@@ -41160,7 +41196,7 @@
         <v>1.33</v>
       </c>
       <c r="AP192">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ192">
         <v>1</v>
@@ -41288,7 +41324,7 @@
         <v>233</v>
       </c>
       <c r="P193" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41366,10 +41402,10 @@
         <v>2</v>
       </c>
       <c r="AP193">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ193">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR193">
         <v>2.11</v>
@@ -41494,7 +41530,7 @@
         <v>234</v>
       </c>
       <c r="P194" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41572,7 +41608,7 @@
         <v>0.83</v>
       </c>
       <c r="AP194">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AQ194">
         <v>1</v>
@@ -41781,7 +41817,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ195">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR195">
         <v>1.77</v>
@@ -41906,7 +41942,7 @@
         <v>198</v>
       </c>
       <c r="P196" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="Q196">
         <v>2.63</v>
@@ -42193,7 +42229,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ197">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR197">
         <v>1.53</v>
@@ -42318,7 +42354,7 @@
         <v>103</v>
       </c>
       <c r="P198" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="Q198">
         <v>2.63</v>
@@ -42396,10 +42432,10 @@
         <v>1.5</v>
       </c>
       <c r="AP198">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ198">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR198">
         <v>1.72</v>
@@ -42811,7 +42847,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ200">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR200">
         <v>1.69</v>
@@ -43014,7 +43050,7 @@
         <v>0.67</v>
       </c>
       <c r="AP201">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ201">
         <v>0.89</v>
@@ -43348,7 +43384,7 @@
         <v>109</v>
       </c>
       <c r="P203" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="Q203">
         <v>2.63</v>
@@ -43429,7 +43465,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ203">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR203">
         <v>1.04</v>
@@ -43760,7 +43796,7 @@
         <v>237</v>
       </c>
       <c r="P205" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -43838,7 +43874,7 @@
         <v>1</v>
       </c>
       <c r="AP205">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ205">
         <v>0.9</v>
@@ -44044,7 +44080,7 @@
         <v>0.57</v>
       </c>
       <c r="AP206">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ206">
         <v>1</v>
@@ -44172,7 +44208,7 @@
         <v>109</v>
       </c>
       <c r="P207" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="Q207">
         <v>2.25</v>
@@ -44253,7 +44289,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ207">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR207">
         <v>1.4</v>
@@ -44868,7 +44904,7 @@
         <v>0.25</v>
       </c>
       <c r="AP210">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ210">
         <v>0.33</v>
@@ -44996,7 +45032,7 @@
         <v>240</v>
       </c>
       <c r="P211" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="Q211">
         <v>3.2</v>
@@ -45074,7 +45110,7 @@
         <v>2</v>
       </c>
       <c r="AP211">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ211">
         <v>1.5</v>
@@ -45202,7 +45238,7 @@
         <v>109</v>
       </c>
       <c r="P212" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45280,10 +45316,10 @@
         <v>0.29</v>
       </c>
       <c r="AP212">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ212">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR212">
         <v>1.33</v>
@@ -45408,7 +45444,7 @@
         <v>241</v>
       </c>
       <c r="P213" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="Q213">
         <v>4</v>
@@ -45486,7 +45522,7 @@
         <v>0.86</v>
       </c>
       <c r="AP213">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AQ213">
         <v>0.88</v>
@@ -45820,7 +45856,7 @@
         <v>242</v>
       </c>
       <c r="P215" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -45901,7 +45937,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ215">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AR215">
         <v>1.85</v>
@@ -46026,7 +46062,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="Q216">
         <v>3.4</v>
@@ -46232,7 +46268,7 @@
         <v>243</v>
       </c>
       <c r="P217" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="Q217">
         <v>2.75</v>
@@ -46313,7 +46349,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ217">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR217">
         <v>1.58</v>
@@ -46644,7 +46680,7 @@
         <v>244</v>
       </c>
       <c r="P219" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="Q219">
         <v>3.1</v>
@@ -46722,7 +46758,7 @@
         <v>2</v>
       </c>
       <c r="AP219">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ219">
         <v>1.8</v>
@@ -46931,7 +46967,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ220">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR220">
         <v>1.69</v>
@@ -47056,7 +47092,7 @@
         <v>246</v>
       </c>
       <c r="P221" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="Q221">
         <v>2.6</v>
@@ -47134,10 +47170,10 @@
         <v>1</v>
       </c>
       <c r="AP221">
+        <v>1.27</v>
+      </c>
+      <c r="AQ221">
         <v>1.3</v>
-      </c>
-      <c r="AQ221">
-        <v>1.11</v>
       </c>
       <c r="AR221">
         <v>2.04</v>
@@ -47262,7 +47298,7 @@
         <v>247</v>
       </c>
       <c r="P222" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="Q222">
         <v>2.5</v>
@@ -47343,7 +47379,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ222">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR222">
         <v>1.71</v>
@@ -47468,7 +47504,7 @@
         <v>248</v>
       </c>
       <c r="P223" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47674,7 +47710,7 @@
         <v>249</v>
       </c>
       <c r="P224" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47755,7 +47791,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ224">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR224">
         <v>1.56</v>
@@ -47880,7 +47916,7 @@
         <v>250</v>
       </c>
       <c r="P225" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -47958,7 +47994,7 @@
         <v>1.5</v>
       </c>
       <c r="AP225">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ225">
         <v>1.6</v>
@@ -48086,7 +48122,7 @@
         <v>251</v>
       </c>
       <c r="P226" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="Q226">
         <v>2.75</v>
@@ -48164,10 +48200,10 @@
         <v>1.5</v>
       </c>
       <c r="AP226">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ226">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR226">
         <v>1.23</v>
@@ -48292,7 +48328,7 @@
         <v>252</v>
       </c>
       <c r="P227" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="Q227">
         <v>1.83</v>
@@ -48498,7 +48534,7 @@
         <v>253</v>
       </c>
       <c r="P228" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48704,7 +48740,7 @@
         <v>109</v>
       </c>
       <c r="P229" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="Q229">
         <v>2.5</v>
@@ -48785,7 +48821,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ229">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR229">
         <v>1.83</v>
@@ -48910,7 +48946,7 @@
         <v>254</v>
       </c>
       <c r="P230" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="Q230">
         <v>3.25</v>
@@ -48991,7 +49027,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ230">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR230">
         <v>1.42</v>
@@ -49116,7 +49152,7 @@
         <v>119</v>
       </c>
       <c r="P231" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="Q231">
         <v>2.4</v>
@@ -49734,7 +49770,7 @@
         <v>109</v>
       </c>
       <c r="P234" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="Q234">
         <v>2.5</v>
@@ -50018,7 +50054,7 @@
         <v>1.14</v>
       </c>
       <c r="AP235">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ235">
         <v>1</v>
@@ -50352,7 +50388,7 @@
         <v>258</v>
       </c>
       <c r="P237" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="Q237">
         <v>2.75</v>
@@ -50558,7 +50594,7 @@
         <v>259</v>
       </c>
       <c r="P238" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="Q238">
         <v>2.6</v>
@@ -50636,7 +50672,7 @@
         <v>0.86</v>
       </c>
       <c r="AP238">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ238">
         <v>0.78</v>
@@ -50764,7 +50800,7 @@
         <v>109</v>
       </c>
       <c r="P239" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -50970,7 +51006,7 @@
         <v>140</v>
       </c>
       <c r="P240" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -51048,7 +51084,7 @@
         <v>0.71</v>
       </c>
       <c r="AP240">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ240">
         <v>0.89</v>
@@ -51382,7 +51418,7 @@
         <v>109</v>
       </c>
       <c r="P242" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="Q242">
         <v>3.1</v>
@@ -51460,10 +51496,10 @@
         <v>1.44</v>
       </c>
       <c r="AP242">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AQ242">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR242">
         <v>1.55</v>
@@ -51669,7 +51705,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ243">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR243">
         <v>1.63</v>
@@ -51794,7 +51830,7 @@
         <v>161</v>
       </c>
       <c r="P244" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="Q244">
         <v>2.1</v>
@@ -51875,7 +51911,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ244">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR244">
         <v>1.92</v>
@@ -52081,7 +52117,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ245">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR245">
         <v>1.17</v>
@@ -52206,7 +52242,7 @@
         <v>156</v>
       </c>
       <c r="P246" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="Q246">
         <v>2.5</v>
@@ -52696,7 +52732,7 @@
         <v>1</v>
       </c>
       <c r="AP248">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ248">
         <v>1</v>
@@ -52824,7 +52860,7 @@
         <v>264</v>
       </c>
       <c r="P249" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="Q249">
         <v>2.5</v>
@@ -53030,7 +53066,7 @@
         <v>265</v>
       </c>
       <c r="P250" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="Q250">
         <v>3.2</v>
@@ -53108,10 +53144,10 @@
         <v>1.67</v>
       </c>
       <c r="AP250">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ250">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR250">
         <v>1.23</v>
@@ -53236,7 +53272,7 @@
         <v>109</v>
       </c>
       <c r="P251" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="Q251">
         <v>2.75</v>
@@ -53442,7 +53478,7 @@
         <v>266</v>
       </c>
       <c r="P252" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="Q252">
         <v>2.25</v>
@@ -53520,10 +53556,10 @@
         <v>0.63</v>
       </c>
       <c r="AP252">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ252">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR252">
         <v>1.24</v>
@@ -54141,7 +54177,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ255">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR255">
         <v>1.83</v>
@@ -54266,7 +54302,7 @@
         <v>270</v>
       </c>
       <c r="P256" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="Q256">
         <v>2.25</v>
@@ -54344,7 +54380,7 @@
         <v>1.25</v>
       </c>
       <c r="AP256">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ256">
         <v>1.4</v>
@@ -54472,7 +54508,7 @@
         <v>271</v>
       </c>
       <c r="P257" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="Q257">
         <v>2.63</v>
@@ -54678,7 +54714,7 @@
         <v>272</v>
       </c>
       <c r="P258" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="Q258">
         <v>2.3</v>
@@ -54884,7 +54920,7 @@
         <v>109</v>
       </c>
       <c r="P259" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="Q259">
         <v>3.1</v>
@@ -55296,7 +55332,7 @@
         <v>274</v>
       </c>
       <c r="P261" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -55502,7 +55538,7 @@
         <v>275</v>
       </c>
       <c r="P262" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="Q262">
         <v>2.5</v>
@@ -55708,7 +55744,7 @@
         <v>234</v>
       </c>
       <c r="P263" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="Q263">
         <v>2.25</v>
@@ -55914,7 +55950,7 @@
         <v>109</v>
       </c>
       <c r="P264" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="Q264">
         <v>2.75</v>
@@ -56120,7 +56156,7 @@
         <v>276</v>
       </c>
       <c r="P265" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="Q265">
         <v>2.88</v>
@@ -56201,7 +56237,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ265">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR265">
         <v>1.67</v>
@@ -56326,7 +56362,7 @@
         <v>109</v>
       </c>
       <c r="P266" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="Q266">
         <v>3.4</v>
@@ -56407,7 +56443,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ266">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR266">
         <v>1.57</v>
@@ -56610,7 +56646,7 @@
         <v>1</v>
       </c>
       <c r="AP267">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ267">
         <v>0.89</v>
@@ -56738,7 +56774,7 @@
         <v>278</v>
       </c>
       <c r="P268" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="Q268">
         <v>2.2</v>
@@ -56819,7 +56855,7 @@
         <v>2</v>
       </c>
       <c r="AQ268">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AR268">
         <v>1.84</v>
@@ -56944,7 +56980,7 @@
         <v>279</v>
       </c>
       <c r="P269" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57022,7 +57058,7 @@
         <v>1.6</v>
       </c>
       <c r="AP269">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AQ269">
         <v>1.83</v>
@@ -57150,7 +57186,7 @@
         <v>280</v>
       </c>
       <c r="P270" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="Q270">
         <v>3.35</v>
@@ -57437,7 +57473,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ271">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AR271">
         <v>1.42</v>
@@ -57562,7 +57598,7 @@
         <v>282</v>
       </c>
       <c r="P272" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="Q272">
         <v>2.38</v>
@@ -57643,7 +57679,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ272">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR272">
         <v>1.82</v>
@@ -57768,7 +57804,7 @@
         <v>283</v>
       </c>
       <c r="P273" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="Q273">
         <v>3.4</v>
@@ -57849,7 +57885,7 @@
         <v>1</v>
       </c>
       <c r="AQ273">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR273">
         <v>1.67</v>
@@ -57974,7 +58010,7 @@
         <v>284</v>
       </c>
       <c r="P274" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="Q274">
         <v>3</v>
@@ -58261,7 +58297,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ275">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR275">
         <v>1.64</v>
@@ -58386,7 +58422,7 @@
         <v>285</v>
       </c>
       <c r="P276" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="Q276">
         <v>2.63</v>
@@ -58592,7 +58628,7 @@
         <v>286</v>
       </c>
       <c r="P277" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -59004,7 +59040,7 @@
         <v>288</v>
       </c>
       <c r="P279" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="Q279">
         <v>2.63</v>
@@ -59416,7 +59452,7 @@
         <v>290</v>
       </c>
       <c r="P281" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="Q281">
         <v>2.25</v>
@@ -59622,7 +59658,7 @@
         <v>291</v>
       </c>
       <c r="P282" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="Q282">
         <v>2.88</v>
@@ -59906,7 +59942,7 @@
         <v>0.88</v>
       </c>
       <c r="AP283">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AQ283">
         <v>0.78</v>
@@ -60112,7 +60148,7 @@
         <v>1.78</v>
       </c>
       <c r="AP284">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ284">
         <v>1.9</v>
@@ -60240,7 +60276,7 @@
         <v>293</v>
       </c>
       <c r="P285" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="Q285">
         <v>2.5</v>
@@ -60446,7 +60482,7 @@
         <v>294</v>
       </c>
       <c r="P286" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -60733,7 +60769,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ287">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR287">
         <v>1.67</v>
@@ -61142,7 +61178,7 @@
         <v>0.27</v>
       </c>
       <c r="AP289">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ289">
         <v>0.33</v>
@@ -61557,7 +61593,7 @@
         <v>2</v>
       </c>
       <c r="AQ291">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR291">
         <v>1.88</v>
@@ -62094,7 +62130,7 @@
         <v>112</v>
       </c>
       <c r="P294" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="Q294">
         <v>3.1</v>
@@ -62300,7 +62336,7 @@
         <v>122</v>
       </c>
       <c r="P295" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="Q295">
         <v>2.4</v>
@@ -62663,6 +62699,1860 @@
       </c>
       <c r="BP296">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="297" spans="1:68">
+      <c r="A297" s="1">
+        <v>296</v>
+      </c>
+      <c r="B297">
+        <v>7781375</v>
+      </c>
+      <c r="C297" t="s">
+        <v>68</v>
+      </c>
+      <c r="D297" t="s">
+        <v>69</v>
+      </c>
+      <c r="E297" s="2">
+        <v>45843.84375</v>
+      </c>
+      <c r="F297">
+        <v>0</v>
+      </c>
+      <c r="G297" t="s">
+        <v>85</v>
+      </c>
+      <c r="H297" t="s">
+        <v>76</v>
+      </c>
+      <c r="I297">
+        <v>1</v>
+      </c>
+      <c r="J297">
+        <v>0</v>
+      </c>
+      <c r="K297">
+        <v>1</v>
+      </c>
+      <c r="L297">
+        <v>2</v>
+      </c>
+      <c r="M297">
+        <v>2</v>
+      </c>
+      <c r="N297">
+        <v>4</v>
+      </c>
+      <c r="O297" t="s">
+        <v>301</v>
+      </c>
+      <c r="P297" t="s">
+        <v>444</v>
+      </c>
+      <c r="Q297">
+        <v>0</v>
+      </c>
+      <c r="R297">
+        <v>0</v>
+      </c>
+      <c r="S297">
+        <v>0</v>
+      </c>
+      <c r="T297">
+        <v>0</v>
+      </c>
+      <c r="U297">
+        <v>0</v>
+      </c>
+      <c r="V297">
+        <v>0</v>
+      </c>
+      <c r="W297">
+        <v>0</v>
+      </c>
+      <c r="X297">
+        <v>0</v>
+      </c>
+      <c r="Y297">
+        <v>0</v>
+      </c>
+      <c r="Z297">
+        <v>2.44</v>
+      </c>
+      <c r="AA297">
+        <v>3.47</v>
+      </c>
+      <c r="AB297">
+        <v>2.37</v>
+      </c>
+      <c r="AC297">
+        <v>0</v>
+      </c>
+      <c r="AD297">
+        <v>0</v>
+      </c>
+      <c r="AE297">
+        <v>0</v>
+      </c>
+      <c r="AF297">
+        <v>0</v>
+      </c>
+      <c r="AG297">
+        <v>1.57</v>
+      </c>
+      <c r="AH297">
+        <v>2.25</v>
+      </c>
+      <c r="AI297">
+        <v>0</v>
+      </c>
+      <c r="AJ297">
+        <v>0</v>
+      </c>
+      <c r="AK297">
+        <v>0</v>
+      </c>
+      <c r="AL297">
+        <v>0</v>
+      </c>
+      <c r="AM297">
+        <v>0</v>
+      </c>
+      <c r="AN297">
+        <v>2.25</v>
+      </c>
+      <c r="AO297">
+        <v>1.6</v>
+      </c>
+      <c r="AP297">
+        <v>2.11</v>
+      </c>
+      <c r="AQ297">
+        <v>1.55</v>
+      </c>
+      <c r="AR297">
+        <v>1.73</v>
+      </c>
+      <c r="AS297">
+        <v>1.56</v>
+      </c>
+      <c r="AT297">
+        <v>3.29</v>
+      </c>
+      <c r="AU297">
+        <v>6</v>
+      </c>
+      <c r="AV297">
+        <v>7</v>
+      </c>
+      <c r="AW297">
+        <v>5</v>
+      </c>
+      <c r="AX297">
+        <v>5</v>
+      </c>
+      <c r="AY297">
+        <v>11</v>
+      </c>
+      <c r="AZ297">
+        <v>12</v>
+      </c>
+      <c r="BA297">
+        <v>2</v>
+      </c>
+      <c r="BB297">
+        <v>6</v>
+      </c>
+      <c r="BC297">
+        <v>8</v>
+      </c>
+      <c r="BD297">
+        <v>0</v>
+      </c>
+      <c r="BE297">
+        <v>0</v>
+      </c>
+      <c r="BF297">
+        <v>0</v>
+      </c>
+      <c r="BG297">
+        <v>0</v>
+      </c>
+      <c r="BH297">
+        <v>0</v>
+      </c>
+      <c r="BI297">
+        <v>0</v>
+      </c>
+      <c r="BJ297">
+        <v>0</v>
+      </c>
+      <c r="BK297">
+        <v>0</v>
+      </c>
+      <c r="BL297">
+        <v>0</v>
+      </c>
+      <c r="BM297">
+        <v>0</v>
+      </c>
+      <c r="BN297">
+        <v>0</v>
+      </c>
+      <c r="BO297">
+        <v>0</v>
+      </c>
+      <c r="BP297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:68">
+      <c r="A298" s="1">
+        <v>297</v>
+      </c>
+      <c r="B298">
+        <v>7781377</v>
+      </c>
+      <c r="C298" t="s">
+        <v>68</v>
+      </c>
+      <c r="D298" t="s">
+        <v>69</v>
+      </c>
+      <c r="E298" s="2">
+        <v>45843.85416666666</v>
+      </c>
+      <c r="F298">
+        <v>0</v>
+      </c>
+      <c r="G298" t="s">
+        <v>75</v>
+      </c>
+      <c r="H298" t="s">
+        <v>72</v>
+      </c>
+      <c r="I298">
+        <v>0</v>
+      </c>
+      <c r="J298">
+        <v>0</v>
+      </c>
+      <c r="K298">
+        <v>0</v>
+      </c>
+      <c r="L298">
+        <v>0</v>
+      </c>
+      <c r="M298">
+        <v>0</v>
+      </c>
+      <c r="N298">
+        <v>0</v>
+      </c>
+      <c r="O298" t="s">
+        <v>109</v>
+      </c>
+      <c r="P298" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q298">
+        <v>3.1</v>
+      </c>
+      <c r="R298">
+        <v>2.3</v>
+      </c>
+      <c r="S298">
+        <v>3.1</v>
+      </c>
+      <c r="T298">
+        <v>1.33</v>
+      </c>
+      <c r="U298">
+        <v>3.25</v>
+      </c>
+      <c r="V298">
+        <v>2.5</v>
+      </c>
+      <c r="W298">
+        <v>1.5</v>
+      </c>
+      <c r="X298">
+        <v>6</v>
+      </c>
+      <c r="Y298">
+        <v>1.13</v>
+      </c>
+      <c r="Z298">
+        <v>2.48</v>
+      </c>
+      <c r="AA298">
+        <v>3.38</v>
+      </c>
+      <c r="AB298">
+        <v>2.38</v>
+      </c>
+      <c r="AC298">
+        <v>1.04</v>
+      </c>
+      <c r="AD298">
+        <v>10</v>
+      </c>
+      <c r="AE298">
+        <v>1.22</v>
+      </c>
+      <c r="AF298">
+        <v>4.2</v>
+      </c>
+      <c r="AG298">
+        <v>1.62</v>
+      </c>
+      <c r="AH298">
+        <v>2.15</v>
+      </c>
+      <c r="AI298">
+        <v>1.57</v>
+      </c>
+      <c r="AJ298">
+        <v>2.25</v>
+      </c>
+      <c r="AK298">
+        <v>1.52</v>
+      </c>
+      <c r="AL298">
+        <v>1.27</v>
+      </c>
+      <c r="AM298">
+        <v>1.47</v>
+      </c>
+      <c r="AN298">
+        <v>0.91</v>
+      </c>
+      <c r="AO298">
+        <v>0.22</v>
+      </c>
+      <c r="AP298">
+        <v>0.92</v>
+      </c>
+      <c r="AQ298">
+        <v>0.3</v>
+      </c>
+      <c r="AR298">
+        <v>1.23</v>
+      </c>
+      <c r="AS298">
+        <v>1.29</v>
+      </c>
+      <c r="AT298">
+        <v>2.52</v>
+      </c>
+      <c r="AU298">
+        <v>2</v>
+      </c>
+      <c r="AV298">
+        <v>2</v>
+      </c>
+      <c r="AW298">
+        <v>7</v>
+      </c>
+      <c r="AX298">
+        <v>4</v>
+      </c>
+      <c r="AY298">
+        <v>9</v>
+      </c>
+      <c r="AZ298">
+        <v>6</v>
+      </c>
+      <c r="BA298">
+        <v>3</v>
+      </c>
+      <c r="BB298">
+        <v>0</v>
+      </c>
+      <c r="BC298">
+        <v>3</v>
+      </c>
+      <c r="BD298">
+        <v>1.74</v>
+      </c>
+      <c r="BE298">
+        <v>6.25</v>
+      </c>
+      <c r="BF298">
+        <v>2.33</v>
+      </c>
+      <c r="BG298">
+        <v>1.35</v>
+      </c>
+      <c r="BH298">
+        <v>2.9</v>
+      </c>
+      <c r="BI298">
+        <v>1.58</v>
+      </c>
+      <c r="BJ298">
+        <v>2.17</v>
+      </c>
+      <c r="BK298">
+        <v>1.96</v>
+      </c>
+      <c r="BL298">
+        <v>1.74</v>
+      </c>
+      <c r="BM298">
+        <v>2.48</v>
+      </c>
+      <c r="BN298">
+        <v>1.47</v>
+      </c>
+      <c r="BO298">
+        <v>3.2</v>
+      </c>
+      <c r="BP298">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="299" spans="1:68">
+      <c r="A299" s="1">
+        <v>298</v>
+      </c>
+      <c r="B299">
+        <v>7781378</v>
+      </c>
+      <c r="C299" t="s">
+        <v>68</v>
+      </c>
+      <c r="D299" t="s">
+        <v>69</v>
+      </c>
+      <c r="E299" s="2">
+        <v>45843.85416666666</v>
+      </c>
+      <c r="F299">
+        <v>0</v>
+      </c>
+      <c r="G299" t="s">
+        <v>99</v>
+      </c>
+      <c r="H299" t="s">
+        <v>71</v>
+      </c>
+      <c r="I299">
+        <v>1</v>
+      </c>
+      <c r="J299">
+        <v>2</v>
+      </c>
+      <c r="K299">
+        <v>3</v>
+      </c>
+      <c r="L299">
+        <v>1</v>
+      </c>
+      <c r="M299">
+        <v>4</v>
+      </c>
+      <c r="N299">
+        <v>5</v>
+      </c>
+      <c r="O299" t="s">
+        <v>302</v>
+      </c>
+      <c r="P299" t="s">
+        <v>445</v>
+      </c>
+      <c r="Q299">
+        <v>3.2</v>
+      </c>
+      <c r="R299">
+        <v>2.4</v>
+      </c>
+      <c r="S299">
+        <v>2.75</v>
+      </c>
+      <c r="T299">
+        <v>1.25</v>
+      </c>
+      <c r="U299">
+        <v>3.75</v>
+      </c>
+      <c r="V299">
+        <v>2.2</v>
+      </c>
+      <c r="W299">
+        <v>1.62</v>
+      </c>
+      <c r="X299">
+        <v>5</v>
+      </c>
+      <c r="Y299">
+        <v>1.17</v>
+      </c>
+      <c r="Z299">
+        <v>2.7</v>
+      </c>
+      <c r="AA299">
+        <v>3.66</v>
+      </c>
+      <c r="AB299">
+        <v>2.1</v>
+      </c>
+      <c r="AC299">
+        <v>1.01</v>
+      </c>
+      <c r="AD299">
+        <v>17</v>
+      </c>
+      <c r="AE299">
+        <v>1.18</v>
+      </c>
+      <c r="AF299">
+        <v>4.75</v>
+      </c>
+      <c r="AG299">
+        <v>1.53</v>
+      </c>
+      <c r="AH299">
+        <v>2.3</v>
+      </c>
+      <c r="AI299">
+        <v>1.5</v>
+      </c>
+      <c r="AJ299">
+        <v>2.5</v>
+      </c>
+      <c r="AK299">
+        <v>1.63</v>
+      </c>
+      <c r="AL299">
+        <v>1.25</v>
+      </c>
+      <c r="AM299">
+        <v>1.4</v>
+      </c>
+      <c r="AN299">
+        <v>0.67</v>
+      </c>
+      <c r="AO299">
+        <v>1.71</v>
+      </c>
+      <c r="AP299">
+        <v>0.6</v>
+      </c>
+      <c r="AQ299">
+        <v>1.88</v>
+      </c>
+      <c r="AR299">
+        <v>1.55</v>
+      </c>
+      <c r="AS299">
+        <v>1.32</v>
+      </c>
+      <c r="AT299">
+        <v>2.87</v>
+      </c>
+      <c r="AU299">
+        <v>10</v>
+      </c>
+      <c r="AV299">
+        <v>14</v>
+      </c>
+      <c r="AW299">
+        <v>3</v>
+      </c>
+      <c r="AX299">
+        <v>3</v>
+      </c>
+      <c r="AY299">
+        <v>13</v>
+      </c>
+      <c r="AZ299">
+        <v>17</v>
+      </c>
+      <c r="BA299">
+        <v>6</v>
+      </c>
+      <c r="BB299">
+        <v>2</v>
+      </c>
+      <c r="BC299">
+        <v>8</v>
+      </c>
+      <c r="BD299">
+        <v>1.9</v>
+      </c>
+      <c r="BE299">
+        <v>6.4</v>
+      </c>
+      <c r="BF299">
+        <v>2.08</v>
+      </c>
+      <c r="BG299">
+        <v>1.28</v>
+      </c>
+      <c r="BH299">
+        <v>3.3</v>
+      </c>
+      <c r="BI299">
+        <v>1.49</v>
+      </c>
+      <c r="BJ299">
+        <v>2.4</v>
+      </c>
+      <c r="BK299">
+        <v>1.8</v>
+      </c>
+      <c r="BL299">
+        <v>1.88</v>
+      </c>
+      <c r="BM299">
+        <v>2.25</v>
+      </c>
+      <c r="BN299">
+        <v>1.55</v>
+      </c>
+      <c r="BO299">
+        <v>2.9</v>
+      </c>
+      <c r="BP299">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="300" spans="1:68">
+      <c r="A300" s="1">
+        <v>299</v>
+      </c>
+      <c r="B300">
+        <v>7781376</v>
+      </c>
+      <c r="C300" t="s">
+        <v>68</v>
+      </c>
+      <c r="D300" t="s">
+        <v>69</v>
+      </c>
+      <c r="E300" s="2">
+        <v>45843.85416666666</v>
+      </c>
+      <c r="F300">
+        <v>0</v>
+      </c>
+      <c r="G300" t="s">
+        <v>73</v>
+      </c>
+      <c r="H300" t="s">
+        <v>90</v>
+      </c>
+      <c r="I300">
+        <v>1</v>
+      </c>
+      <c r="J300">
+        <v>0</v>
+      </c>
+      <c r="K300">
+        <v>1</v>
+      </c>
+      <c r="L300">
+        <v>2</v>
+      </c>
+      <c r="M300">
+        <v>1</v>
+      </c>
+      <c r="N300">
+        <v>3</v>
+      </c>
+      <c r="O300" t="s">
+        <v>303</v>
+      </c>
+      <c r="P300" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q300">
+        <v>2.3</v>
+      </c>
+      <c r="R300">
+        <v>2.5</v>
+      </c>
+      <c r="S300">
+        <v>4</v>
+      </c>
+      <c r="T300">
+        <v>1.25</v>
+      </c>
+      <c r="U300">
+        <v>3.75</v>
+      </c>
+      <c r="V300">
+        <v>2.1</v>
+      </c>
+      <c r="W300">
+        <v>1.67</v>
+      </c>
+      <c r="X300">
+        <v>5</v>
+      </c>
+      <c r="Y300">
+        <v>1.17</v>
+      </c>
+      <c r="Z300">
+        <v>1.65</v>
+      </c>
+      <c r="AA300">
+        <v>4.1</v>
+      </c>
+      <c r="AB300">
+        <v>3.73</v>
+      </c>
+      <c r="AC300">
+        <v>1.01</v>
+      </c>
+      <c r="AD300">
+        <v>17</v>
+      </c>
+      <c r="AE300">
+        <v>1.17</v>
+      </c>
+      <c r="AF300">
+        <v>5</v>
+      </c>
+      <c r="AG300">
+        <v>1.6</v>
+      </c>
+      <c r="AH300">
+        <v>2.34</v>
+      </c>
+      <c r="AI300">
+        <v>1.5</v>
+      </c>
+      <c r="AJ300">
+        <v>2.5</v>
+      </c>
+      <c r="AK300">
+        <v>1.27</v>
+      </c>
+      <c r="AL300">
+        <v>1.22</v>
+      </c>
+      <c r="AM300">
+        <v>1.95</v>
+      </c>
+      <c r="AN300">
+        <v>2.13</v>
+      </c>
+      <c r="AO300">
+        <v>1.8</v>
+      </c>
+      <c r="AP300">
+        <v>2.22</v>
+      </c>
+      <c r="AQ300">
+        <v>1.64</v>
+      </c>
+      <c r="AR300">
+        <v>1.88</v>
+      </c>
+      <c r="AS300">
+        <v>1.61</v>
+      </c>
+      <c r="AT300">
+        <v>3.49</v>
+      </c>
+      <c r="AU300">
+        <v>4</v>
+      </c>
+      <c r="AV300">
+        <v>4</v>
+      </c>
+      <c r="AW300">
+        <v>7</v>
+      </c>
+      <c r="AX300">
+        <v>8</v>
+      </c>
+      <c r="AY300">
+        <v>11</v>
+      </c>
+      <c r="AZ300">
+        <v>12</v>
+      </c>
+      <c r="BA300">
+        <v>1</v>
+      </c>
+      <c r="BB300">
+        <v>10</v>
+      </c>
+      <c r="BC300">
+        <v>11</v>
+      </c>
+      <c r="BD300">
+        <v>1.53</v>
+      </c>
+      <c r="BE300">
+        <v>6.75</v>
+      </c>
+      <c r="BF300">
+        <v>2.8</v>
+      </c>
+      <c r="BG300">
+        <v>1.27</v>
+      </c>
+      <c r="BH300">
+        <v>3.3</v>
+      </c>
+      <c r="BI300">
+        <v>1.48</v>
+      </c>
+      <c r="BJ300">
+        <v>2.45</v>
+      </c>
+      <c r="BK300">
+        <v>1.76</v>
+      </c>
+      <c r="BL300">
+        <v>1.94</v>
+      </c>
+      <c r="BM300">
+        <v>2.18</v>
+      </c>
+      <c r="BN300">
+        <v>1.58</v>
+      </c>
+      <c r="BO300">
+        <v>2.8</v>
+      </c>
+      <c r="BP300">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="301" spans="1:68">
+      <c r="A301" s="1">
+        <v>300</v>
+      </c>
+      <c r="B301">
+        <v>7781380</v>
+      </c>
+      <c r="C301" t="s">
+        <v>68</v>
+      </c>
+      <c r="D301" t="s">
+        <v>69</v>
+      </c>
+      <c r="E301" s="2">
+        <v>45843.89583333334</v>
+      </c>
+      <c r="F301">
+        <v>0</v>
+      </c>
+      <c r="G301" t="s">
+        <v>79</v>
+      </c>
+      <c r="H301" t="s">
+        <v>89</v>
+      </c>
+      <c r="I301">
+        <v>0</v>
+      </c>
+      <c r="J301">
+        <v>0</v>
+      </c>
+      <c r="K301">
+        <v>0</v>
+      </c>
+      <c r="L301">
+        <v>1</v>
+      </c>
+      <c r="M301">
+        <v>0</v>
+      </c>
+      <c r="N301">
+        <v>1</v>
+      </c>
+      <c r="O301" t="s">
+        <v>304</v>
+      </c>
+      <c r="P301" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q301">
+        <v>2.35</v>
+      </c>
+      <c r="R301">
+        <v>2.3</v>
+      </c>
+      <c r="S301">
+        <v>3.8</v>
+      </c>
+      <c r="T301">
+        <v>1.3</v>
+      </c>
+      <c r="U301">
+        <v>3.25</v>
+      </c>
+      <c r="V301">
+        <v>2.4</v>
+      </c>
+      <c r="W301">
+        <v>1.5</v>
+      </c>
+      <c r="X301">
+        <v>5.75</v>
+      </c>
+      <c r="Y301">
+        <v>1.12</v>
+      </c>
+      <c r="Z301">
+        <v>1.78</v>
+      </c>
+      <c r="AA301">
+        <v>3.62</v>
+      </c>
+      <c r="AB301">
+        <v>3.57</v>
+      </c>
+      <c r="AC301">
+        <v>1.03</v>
+      </c>
+      <c r="AD301">
+        <v>12</v>
+      </c>
+      <c r="AE301">
+        <v>1.2</v>
+      </c>
+      <c r="AF301">
+        <v>4.1</v>
+      </c>
+      <c r="AG301">
+        <v>1.79</v>
+      </c>
+      <c r="AH301">
+        <v>1.91</v>
+      </c>
+      <c r="AI301">
+        <v>1.62</v>
+      </c>
+      <c r="AJ301">
+        <v>2.15</v>
+      </c>
+      <c r="AK301">
+        <v>1.27</v>
+      </c>
+      <c r="AL301">
+        <v>1.24</v>
+      </c>
+      <c r="AM301">
+        <v>1.88</v>
+      </c>
+      <c r="AN301">
+        <v>2.1</v>
+      </c>
+      <c r="AO301">
+        <v>1.9</v>
+      </c>
+      <c r="AP301">
+        <v>2.18</v>
+      </c>
+      <c r="AQ301">
+        <v>1.73</v>
+      </c>
+      <c r="AR301">
+        <v>1.87</v>
+      </c>
+      <c r="AS301">
+        <v>1.52</v>
+      </c>
+      <c r="AT301">
+        <v>3.39</v>
+      </c>
+      <c r="AU301">
+        <v>5</v>
+      </c>
+      <c r="AV301">
+        <v>4</v>
+      </c>
+      <c r="AW301">
+        <v>6</v>
+      </c>
+      <c r="AX301">
+        <v>7</v>
+      </c>
+      <c r="AY301">
+        <v>11</v>
+      </c>
+      <c r="AZ301">
+        <v>11</v>
+      </c>
+      <c r="BA301">
+        <v>4</v>
+      </c>
+      <c r="BB301">
+        <v>3</v>
+      </c>
+      <c r="BC301">
+        <v>7</v>
+      </c>
+      <c r="BD301">
+        <v>1.68</v>
+      </c>
+      <c r="BE301">
+        <v>6.5</v>
+      </c>
+      <c r="BF301">
+        <v>2.4</v>
+      </c>
+      <c r="BG301">
+        <v>1.3</v>
+      </c>
+      <c r="BH301">
+        <v>3.15</v>
+      </c>
+      <c r="BI301">
+        <v>1.52</v>
+      </c>
+      <c r="BJ301">
+        <v>2.33</v>
+      </c>
+      <c r="BK301">
+        <v>1.84</v>
+      </c>
+      <c r="BL301">
+        <v>1.84</v>
+      </c>
+      <c r="BM301">
+        <v>2.32</v>
+      </c>
+      <c r="BN301">
+        <v>1.53</v>
+      </c>
+      <c r="BO301">
+        <v>2.95</v>
+      </c>
+      <c r="BP301">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="302" spans="1:68">
+      <c r="A302" s="1">
+        <v>301</v>
+      </c>
+      <c r="B302">
+        <v>7781381</v>
+      </c>
+      <c r="C302" t="s">
+        <v>68</v>
+      </c>
+      <c r="D302" t="s">
+        <v>69</v>
+      </c>
+      <c r="E302" s="2">
+        <v>45843.9375</v>
+      </c>
+      <c r="F302">
+        <v>0</v>
+      </c>
+      <c r="G302" t="s">
+        <v>86</v>
+      </c>
+      <c r="H302" t="s">
+        <v>80</v>
+      </c>
+      <c r="I302">
+        <v>2</v>
+      </c>
+      <c r="J302">
+        <v>0</v>
+      </c>
+      <c r="K302">
+        <v>2</v>
+      </c>
+      <c r="L302">
+        <v>3</v>
+      </c>
+      <c r="M302">
+        <v>2</v>
+      </c>
+      <c r="N302">
+        <v>5</v>
+      </c>
+      <c r="O302" t="s">
+        <v>305</v>
+      </c>
+      <c r="P302" t="s">
+        <v>446</v>
+      </c>
+      <c r="Q302">
+        <v>2.2</v>
+      </c>
+      <c r="R302">
+        <v>2.5</v>
+      </c>
+      <c r="S302">
+        <v>4.5</v>
+      </c>
+      <c r="T302">
+        <v>1.29</v>
+      </c>
+      <c r="U302">
+        <v>3.5</v>
+      </c>
+      <c r="V302">
+        <v>2.25</v>
+      </c>
+      <c r="W302">
+        <v>1.57</v>
+      </c>
+      <c r="X302">
+        <v>5.5</v>
+      </c>
+      <c r="Y302">
+        <v>1.14</v>
+      </c>
+      <c r="Z302">
+        <v>1.69</v>
+      </c>
+      <c r="AA302">
+        <v>3.85</v>
+      </c>
+      <c r="AB302">
+        <v>3.75</v>
+      </c>
+      <c r="AC302">
+        <v>1.03</v>
+      </c>
+      <c r="AD302">
+        <v>11</v>
+      </c>
+      <c r="AE302">
+        <v>1.18</v>
+      </c>
+      <c r="AF302">
+        <v>4.75</v>
+      </c>
+      <c r="AG302">
+        <v>1.52</v>
+      </c>
+      <c r="AH302">
+        <v>2.37</v>
+      </c>
+      <c r="AI302">
+        <v>1.57</v>
+      </c>
+      <c r="AJ302">
+        <v>2.25</v>
+      </c>
+      <c r="AK302">
+        <v>1.24</v>
+      </c>
+      <c r="AL302">
+        <v>1.22</v>
+      </c>
+      <c r="AM302">
+        <v>2</v>
+      </c>
+      <c r="AN302">
+        <v>1.25</v>
+      </c>
+      <c r="AO302">
+        <v>0.5</v>
+      </c>
+      <c r="AP302">
+        <v>1.44</v>
+      </c>
+      <c r="AQ302">
+        <v>0.45</v>
+      </c>
+      <c r="AR302">
+        <v>1.55</v>
+      </c>
+      <c r="AS302">
+        <v>1.13</v>
+      </c>
+      <c r="AT302">
+        <v>2.68</v>
+      </c>
+      <c r="AU302">
+        <v>9</v>
+      </c>
+      <c r="AV302">
+        <v>6</v>
+      </c>
+      <c r="AW302">
+        <v>7</v>
+      </c>
+      <c r="AX302">
+        <v>9</v>
+      </c>
+      <c r="AY302">
+        <v>16</v>
+      </c>
+      <c r="AZ302">
+        <v>15</v>
+      </c>
+      <c r="BA302">
+        <v>5</v>
+      </c>
+      <c r="BB302">
+        <v>10</v>
+      </c>
+      <c r="BC302">
+        <v>15</v>
+      </c>
+      <c r="BD302">
+        <v>1.41</v>
+      </c>
+      <c r="BE302">
+        <v>7</v>
+      </c>
+      <c r="BF302">
+        <v>3.2</v>
+      </c>
+      <c r="BG302">
+        <v>1.21</v>
+      </c>
+      <c r="BH302">
+        <v>3.8</v>
+      </c>
+      <c r="BI302">
+        <v>1.38</v>
+      </c>
+      <c r="BJ302">
+        <v>2.7</v>
+      </c>
+      <c r="BK302">
+        <v>1.63</v>
+      </c>
+      <c r="BL302">
+        <v>2.1</v>
+      </c>
+      <c r="BM302">
+        <v>1.98</v>
+      </c>
+      <c r="BN302">
+        <v>1.72</v>
+      </c>
+      <c r="BO302">
+        <v>2.48</v>
+      </c>
+      <c r="BP302">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="303" spans="1:68">
+      <c r="A303" s="1">
+        <v>302</v>
+      </c>
+      <c r="B303">
+        <v>7781382</v>
+      </c>
+      <c r="C303" t="s">
+        <v>68</v>
+      </c>
+      <c r="D303" t="s">
+        <v>69</v>
+      </c>
+      <c r="E303" s="2">
+        <v>45843.97916666666</v>
+      </c>
+      <c r="F303">
+        <v>0</v>
+      </c>
+      <c r="G303" t="s">
+        <v>83</v>
+      </c>
+      <c r="H303" t="s">
+        <v>87</v>
+      </c>
+      <c r="I303">
+        <v>1</v>
+      </c>
+      <c r="J303">
+        <v>1</v>
+      </c>
+      <c r="K303">
+        <v>2</v>
+      </c>
+      <c r="L303">
+        <v>2</v>
+      </c>
+      <c r="M303">
+        <v>1</v>
+      </c>
+      <c r="N303">
+        <v>3</v>
+      </c>
+      <c r="O303" t="s">
+        <v>306</v>
+      </c>
+      <c r="P303" t="s">
+        <v>447</v>
+      </c>
+      <c r="Q303">
+        <v>2.5</v>
+      </c>
+      <c r="R303">
+        <v>2.38</v>
+      </c>
+      <c r="S303">
+        <v>4</v>
+      </c>
+      <c r="T303">
+        <v>1.29</v>
+      </c>
+      <c r="U303">
+        <v>3.5</v>
+      </c>
+      <c r="V303">
+        <v>2.38</v>
+      </c>
+      <c r="W303">
+        <v>1.53</v>
+      </c>
+      <c r="X303">
+        <v>5.5</v>
+      </c>
+      <c r="Y303">
+        <v>1.14</v>
+      </c>
+      <c r="Z303">
+        <v>1.87</v>
+      </c>
+      <c r="AA303">
+        <v>3.56</v>
+      </c>
+      <c r="AB303">
+        <v>3.28</v>
+      </c>
+      <c r="AC303">
+        <v>1.04</v>
+      </c>
+      <c r="AD303">
+        <v>10</v>
+      </c>
+      <c r="AE303">
+        <v>1.2</v>
+      </c>
+      <c r="AF303">
+        <v>4.33</v>
+      </c>
+      <c r="AG303">
+        <v>1.56</v>
+      </c>
+      <c r="AH303">
+        <v>2.27</v>
+      </c>
+      <c r="AI303">
+        <v>1.57</v>
+      </c>
+      <c r="AJ303">
+        <v>2.25</v>
+      </c>
+      <c r="AK303">
+        <v>1.3</v>
+      </c>
+      <c r="AL303">
+        <v>1.25</v>
+      </c>
+      <c r="AM303">
+        <v>1.82</v>
+      </c>
+      <c r="AN303">
+        <v>1.9</v>
+      </c>
+      <c r="AO303">
+        <v>1.6</v>
+      </c>
+      <c r="AP303">
+        <v>2</v>
+      </c>
+      <c r="AQ303">
+        <v>1.45</v>
+      </c>
+      <c r="AR303">
+        <v>1.33</v>
+      </c>
+      <c r="AS303">
+        <v>1.44</v>
+      </c>
+      <c r="AT303">
+        <v>2.77</v>
+      </c>
+      <c r="AU303">
+        <v>6</v>
+      </c>
+      <c r="AV303">
+        <v>5</v>
+      </c>
+      <c r="AW303">
+        <v>9</v>
+      </c>
+      <c r="AX303">
+        <v>11</v>
+      </c>
+      <c r="AY303">
+        <v>15</v>
+      </c>
+      <c r="AZ303">
+        <v>16</v>
+      </c>
+      <c r="BA303">
+        <v>5</v>
+      </c>
+      <c r="BB303">
+        <v>8</v>
+      </c>
+      <c r="BC303">
+        <v>13</v>
+      </c>
+      <c r="BD303">
+        <v>1.76</v>
+      </c>
+      <c r="BE303">
+        <v>6.5</v>
+      </c>
+      <c r="BF303">
+        <v>2.25</v>
+      </c>
+      <c r="BG303">
+        <v>1.26</v>
+      </c>
+      <c r="BH303">
+        <v>3.4</v>
+      </c>
+      <c r="BI303">
+        <v>1.47</v>
+      </c>
+      <c r="BJ303">
+        <v>2.48</v>
+      </c>
+      <c r="BK303">
+        <v>1.76</v>
+      </c>
+      <c r="BL303">
+        <v>1.93</v>
+      </c>
+      <c r="BM303">
+        <v>2.18</v>
+      </c>
+      <c r="BN303">
+        <v>1.58</v>
+      </c>
+      <c r="BO303">
+        <v>2.8</v>
+      </c>
+      <c r="BP303">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="304" spans="1:68">
+      <c r="A304" s="1">
+        <v>303</v>
+      </c>
+      <c r="B304">
+        <v>7781383</v>
+      </c>
+      <c r="C304" t="s">
+        <v>68</v>
+      </c>
+      <c r="D304" t="s">
+        <v>69</v>
+      </c>
+      <c r="E304" s="2">
+        <v>45843.97916666666</v>
+      </c>
+      <c r="F304">
+        <v>0</v>
+      </c>
+      <c r="G304" t="s">
+        <v>94</v>
+      </c>
+      <c r="H304" t="s">
+        <v>78</v>
+      </c>
+      <c r="I304">
+        <v>1</v>
+      </c>
+      <c r="J304">
+        <v>2</v>
+      </c>
+      <c r="K304">
+        <v>3</v>
+      </c>
+      <c r="L304">
+        <v>3</v>
+      </c>
+      <c r="M304">
+        <v>4</v>
+      </c>
+      <c r="N304">
+        <v>7</v>
+      </c>
+      <c r="O304" t="s">
+        <v>307</v>
+      </c>
+      <c r="P304" t="s">
+        <v>448</v>
+      </c>
+      <c r="Q304">
+        <v>0</v>
+      </c>
+      <c r="R304">
+        <v>0</v>
+      </c>
+      <c r="S304">
+        <v>0</v>
+      </c>
+      <c r="T304">
+        <v>0</v>
+      </c>
+      <c r="U304">
+        <v>0</v>
+      </c>
+      <c r="V304">
+        <v>0</v>
+      </c>
+      <c r="W304">
+        <v>0</v>
+      </c>
+      <c r="X304">
+        <v>0</v>
+      </c>
+      <c r="Y304">
+        <v>0</v>
+      </c>
+      <c r="Z304">
+        <v>1.67</v>
+      </c>
+      <c r="AA304">
+        <v>3.68</v>
+      </c>
+      <c r="AB304">
+        <v>3.98</v>
+      </c>
+      <c r="AC304">
+        <v>0</v>
+      </c>
+      <c r="AD304">
+        <v>0</v>
+      </c>
+      <c r="AE304">
+        <v>0</v>
+      </c>
+      <c r="AF304">
+        <v>0</v>
+      </c>
+      <c r="AG304">
+        <v>1.53</v>
+      </c>
+      <c r="AH304">
+        <v>2.33</v>
+      </c>
+      <c r="AI304">
+        <v>0</v>
+      </c>
+      <c r="AJ304">
+        <v>0</v>
+      </c>
+      <c r="AK304">
+        <v>0</v>
+      </c>
+      <c r="AL304">
+        <v>0</v>
+      </c>
+      <c r="AM304">
+        <v>0</v>
+      </c>
+      <c r="AN304">
+        <v>2.1</v>
+      </c>
+      <c r="AO304">
+        <v>1.11</v>
+      </c>
+      <c r="AP304">
+        <v>1.91</v>
+      </c>
+      <c r="AQ304">
+        <v>1.3</v>
+      </c>
+      <c r="AR304">
+        <v>1.82</v>
+      </c>
+      <c r="AS304">
+        <v>1.14</v>
+      </c>
+      <c r="AT304">
+        <v>2.96</v>
+      </c>
+      <c r="AU304">
+        <v>8</v>
+      </c>
+      <c r="AV304">
+        <v>6</v>
+      </c>
+      <c r="AW304">
+        <v>4</v>
+      </c>
+      <c r="AX304">
+        <v>1</v>
+      </c>
+      <c r="AY304">
+        <v>12</v>
+      </c>
+      <c r="AZ304">
+        <v>7</v>
+      </c>
+      <c r="BA304">
+        <v>5</v>
+      </c>
+      <c r="BB304">
+        <v>2</v>
+      </c>
+      <c r="BC304">
+        <v>7</v>
+      </c>
+      <c r="BD304">
+        <v>0</v>
+      </c>
+      <c r="BE304">
+        <v>0</v>
+      </c>
+      <c r="BF304">
+        <v>0</v>
+      </c>
+      <c r="BG304">
+        <v>0</v>
+      </c>
+      <c r="BH304">
+        <v>0</v>
+      </c>
+      <c r="BI304">
+        <v>0</v>
+      </c>
+      <c r="BJ304">
+        <v>0</v>
+      </c>
+      <c r="BK304">
+        <v>0</v>
+      </c>
+      <c r="BL304">
+        <v>0</v>
+      </c>
+      <c r="BM304">
+        <v>0</v>
+      </c>
+      <c r="BN304">
+        <v>0</v>
+      </c>
+      <c r="BO304">
+        <v>0</v>
+      </c>
+      <c r="BP304">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:68">
+      <c r="A305" s="1">
+        <v>304</v>
+      </c>
+      <c r="B305">
+        <v>7781384</v>
+      </c>
+      <c r="C305" t="s">
+        <v>68</v>
+      </c>
+      <c r="D305" t="s">
+        <v>69</v>
+      </c>
+      <c r="E305" s="2">
+        <v>45843.97916666666</v>
+      </c>
+      <c r="F305">
+        <v>0</v>
+      </c>
+      <c r="G305" t="s">
+        <v>81</v>
+      </c>
+      <c r="H305" t="s">
+        <v>88</v>
+      </c>
+      <c r="I305">
+        <v>0</v>
+      </c>
+      <c r="J305">
+        <v>1</v>
+      </c>
+      <c r="K305">
+        <v>1</v>
+      </c>
+      <c r="L305">
+        <v>1</v>
+      </c>
+      <c r="M305">
+        <v>1</v>
+      </c>
+      <c r="N305">
+        <v>2</v>
+      </c>
+      <c r="O305" t="s">
+        <v>255</v>
+      </c>
+      <c r="P305" t="s">
+        <v>403</v>
+      </c>
+      <c r="Q305">
+        <v>2.5</v>
+      </c>
+      <c r="R305">
+        <v>2.4</v>
+      </c>
+      <c r="S305">
+        <v>3.6</v>
+      </c>
+      <c r="T305">
+        <v>1.25</v>
+      </c>
+      <c r="U305">
+        <v>3.75</v>
+      </c>
+      <c r="V305">
+        <v>2.25</v>
+      </c>
+      <c r="W305">
+        <v>1.57</v>
+      </c>
+      <c r="X305">
+        <v>5.5</v>
+      </c>
+      <c r="Y305">
+        <v>1.14</v>
+      </c>
+      <c r="Z305">
+        <v>1.89</v>
+      </c>
+      <c r="AA305">
+        <v>3.67</v>
+      </c>
+      <c r="AB305">
+        <v>3.13</v>
+      </c>
+      <c r="AC305">
+        <v>1.01</v>
+      </c>
+      <c r="AD305">
+        <v>17</v>
+      </c>
+      <c r="AE305">
+        <v>1.18</v>
+      </c>
+      <c r="AF305">
+        <v>4.75</v>
+      </c>
+      <c r="AG305">
+        <v>1.67</v>
+      </c>
+      <c r="AH305">
+        <v>2.1</v>
+      </c>
+      <c r="AI305">
+        <v>1.5</v>
+      </c>
+      <c r="AJ305">
+        <v>2.5</v>
+      </c>
+      <c r="AK305">
+        <v>1.32</v>
+      </c>
+      <c r="AL305">
+        <v>1.24</v>
+      </c>
+      <c r="AM305">
+        <v>1.78</v>
+      </c>
+      <c r="AN305">
+        <v>1.3</v>
+      </c>
+      <c r="AO305">
+        <v>0.6</v>
+      </c>
+      <c r="AP305">
+        <v>1.27</v>
+      </c>
+      <c r="AQ305">
+        <v>0.64</v>
+      </c>
+      <c r="AR305">
+        <v>1.96</v>
+      </c>
+      <c r="AS305">
+        <v>1.15</v>
+      </c>
+      <c r="AT305">
+        <v>3.11</v>
+      </c>
+      <c r="AU305">
+        <v>5</v>
+      </c>
+      <c r="AV305">
+        <v>6</v>
+      </c>
+      <c r="AW305">
+        <v>13</v>
+      </c>
+      <c r="AX305">
+        <v>7</v>
+      </c>
+      <c r="AY305">
+        <v>18</v>
+      </c>
+      <c r="AZ305">
+        <v>13</v>
+      </c>
+      <c r="BA305">
+        <v>9</v>
+      </c>
+      <c r="BB305">
+        <v>7</v>
+      </c>
+      <c r="BC305">
+        <v>16</v>
+      </c>
+      <c r="BD305">
+        <v>1.79</v>
+      </c>
+      <c r="BE305">
+        <v>6.4</v>
+      </c>
+      <c r="BF305">
+        <v>2.23</v>
+      </c>
+      <c r="BG305">
+        <v>1.27</v>
+      </c>
+      <c r="BH305">
+        <v>3.3</v>
+      </c>
+      <c r="BI305">
+        <v>1.48</v>
+      </c>
+      <c r="BJ305">
+        <v>2.43</v>
+      </c>
+      <c r="BK305">
+        <v>1.77</v>
+      </c>
+      <c r="BL305">
+        <v>1.92</v>
+      </c>
+      <c r="BM305">
+        <v>2.23</v>
+      </c>
+      <c r="BN305">
+        <v>1.57</v>
+      </c>
+      <c r="BO305">
+        <v>2.8</v>
+      </c>
+      <c r="BP305">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="449">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -940,6 +940,9 @@
     <t>['25', '54', '67']</t>
   </si>
   <si>
+    <t>['43']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -1121,9 +1124,6 @@
   </si>
   <si>
     <t>['11', '27']</t>
-  </si>
-  <si>
-    <t>['43']</t>
   </si>
   <si>
     <t>['2', '84']</t>
@@ -1722,7 +1722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP305"/>
+  <dimension ref="A1:BP306"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2184,7 +2184,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -2390,7 +2390,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2802,7 +2802,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -3008,7 +3008,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3214,7 +3214,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -3626,7 +3626,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -4450,7 +4450,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -4528,7 +4528,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ14">
         <v>0.58</v>
@@ -4656,7 +4656,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4862,7 +4862,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -5561,7 +5561,7 @@
         <v>1</v>
       </c>
       <c r="AQ19">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -6304,7 +6304,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6510,7 +6510,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6922,7 +6922,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -7952,7 +7952,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -8364,7 +8364,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -8442,7 +8442,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ33">
         <v>0.88</v>
@@ -9188,7 +9188,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9806,7 +9806,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -10218,7 +10218,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -11042,7 +11042,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -11248,7 +11248,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -11454,7 +11454,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -12278,7 +12278,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12484,7 +12484,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12896,7 +12896,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -13389,7 +13389,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ57">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR57">
         <v>1.55</v>
@@ -13514,7 +13514,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13720,7 +13720,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -14132,7 +14132,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14338,7 +14338,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -14544,7 +14544,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14750,7 +14750,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -15780,7 +15780,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -16192,7 +16192,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16398,7 +16398,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16682,7 +16682,7 @@
         <v>1</v>
       </c>
       <c r="AP73">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ73">
         <v>1.3</v>
@@ -16810,7 +16810,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -18046,7 +18046,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18127,7 +18127,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ80">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR80">
         <v>1.6</v>
@@ -18252,7 +18252,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18458,7 +18458,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -19076,7 +19076,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -19282,7 +19282,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -19488,7 +19488,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -20106,7 +20106,7 @@
         <v>164</v>
       </c>
       <c r="P90" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
@@ -21342,7 +21342,7 @@
         <v>168</v>
       </c>
       <c r="P96" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -22784,7 +22784,7 @@
         <v>122</v>
       </c>
       <c r="P103" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q103">
         <v>2.75</v>
@@ -24432,7 +24432,7 @@
         <v>109</v>
       </c>
       <c r="P111" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q111">
         <v>2.88</v>
@@ -25050,7 +25050,7 @@
         <v>177</v>
       </c>
       <c r="P114" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25256,7 +25256,7 @@
         <v>178</v>
       </c>
       <c r="P115" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -25668,7 +25668,7 @@
         <v>179</v>
       </c>
       <c r="P117" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25874,7 +25874,7 @@
         <v>180</v>
       </c>
       <c r="P118" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -26286,7 +26286,7 @@
         <v>181</v>
       </c>
       <c r="P120" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -26367,7 +26367,7 @@
         <v>1</v>
       </c>
       <c r="AQ120">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR120">
         <v>1.84</v>
@@ -26698,7 +26698,7 @@
         <v>109</v>
       </c>
       <c r="P122" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q122">
         <v>2.75</v>
@@ -26982,7 +26982,7 @@
         <v>1</v>
       </c>
       <c r="AP123">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ123">
         <v>1.9</v>
@@ -27110,7 +27110,7 @@
         <v>129</v>
       </c>
       <c r="P124" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q124">
         <v>2.5</v>
@@ -28140,7 +28140,7 @@
         <v>187</v>
       </c>
       <c r="P129" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28346,7 +28346,7 @@
         <v>188</v>
       </c>
       <c r="P130" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q130">
         <v>2.4</v>
@@ -29170,7 +29170,7 @@
         <v>189</v>
       </c>
       <c r="P134" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q134">
         <v>3</v>
@@ -29376,7 +29376,7 @@
         <v>190</v>
       </c>
       <c r="P135" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -30612,7 +30612,7 @@
         <v>109</v>
       </c>
       <c r="P141" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q141">
         <v>2.38</v>
@@ -31024,7 +31024,7 @@
         <v>174</v>
       </c>
       <c r="P143" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -31436,7 +31436,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q145">
         <v>2.4</v>
@@ -31642,7 +31642,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31848,7 +31848,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q147">
         <v>2.6</v>
@@ -32054,7 +32054,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q148">
         <v>2.05</v>
@@ -32260,7 +32260,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -32466,7 +32466,7 @@
         <v>202</v>
       </c>
       <c r="P150" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q150">
         <v>2.4</v>
@@ -32878,7 +32878,7 @@
         <v>109</v>
       </c>
       <c r="P152" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q152">
         <v>2.88</v>
@@ -33084,7 +33084,7 @@
         <v>204</v>
       </c>
       <c r="P153" t="s">
-        <v>369</v>
+        <v>308</v>
       </c>
       <c r="Q153">
         <v>2.1</v>
@@ -33702,7 +33702,7 @@
         <v>207</v>
       </c>
       <c r="P156" t="s">
-        <v>369</v>
+        <v>308</v>
       </c>
       <c r="Q156">
         <v>2.5</v>
@@ -35222,7 +35222,7 @@
         <v>1</v>
       </c>
       <c r="AP163">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ163">
         <v>0.45</v>
@@ -36461,7 +36461,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ169">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR169">
         <v>1.68</v>
@@ -39139,7 +39139,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ182">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR182">
         <v>1.89</v>
@@ -43796,7 +43796,7 @@
         <v>237</v>
       </c>
       <c r="P205" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -44698,7 +44698,7 @@
         <v>1.71</v>
       </c>
       <c r="AP209">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ209">
         <v>1.6</v>
@@ -45113,7 +45113,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ211">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR211">
         <v>1.68</v>
@@ -49436,7 +49436,7 @@
         <v>1.5</v>
       </c>
       <c r="AP232">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ232">
         <v>1.8</v>
@@ -51293,7 +51293,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ241">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR241">
         <v>1.5</v>
@@ -52938,7 +52938,7 @@
         <v>1.5</v>
       </c>
       <c r="AP249">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ249">
         <v>1.73</v>
@@ -53478,7 +53478,7 @@
         <v>266</v>
       </c>
       <c r="P252" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q252">
         <v>2.25</v>
@@ -54920,7 +54920,7 @@
         <v>109</v>
       </c>
       <c r="P259" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q259">
         <v>3.1</v>
@@ -61384,7 +61384,7 @@
         <v>1.11</v>
       </c>
       <c r="AP290">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ290">
         <v>1</v>
@@ -64553,6 +64553,212 @@
       </c>
       <c r="BP305">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="306" spans="1:68">
+      <c r="A306" s="1">
+        <v>305</v>
+      </c>
+      <c r="B306">
+        <v>7781385</v>
+      </c>
+      <c r="C306" t="s">
+        <v>68</v>
+      </c>
+      <c r="D306" t="s">
+        <v>69</v>
+      </c>
+      <c r="E306" s="2">
+        <v>45844.75</v>
+      </c>
+      <c r="F306">
+        <v>0</v>
+      </c>
+      <c r="G306" t="s">
+        <v>82</v>
+      </c>
+      <c r="H306" t="s">
+        <v>74</v>
+      </c>
+      <c r="I306">
+        <v>1</v>
+      </c>
+      <c r="J306">
+        <v>1</v>
+      </c>
+      <c r="K306">
+        <v>2</v>
+      </c>
+      <c r="L306">
+        <v>1</v>
+      </c>
+      <c r="M306">
+        <v>1</v>
+      </c>
+      <c r="N306">
+        <v>2</v>
+      </c>
+      <c r="O306" t="s">
+        <v>308</v>
+      </c>
+      <c r="P306" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q306">
+        <v>2.5</v>
+      </c>
+      <c r="R306">
+        <v>2.3</v>
+      </c>
+      <c r="S306">
+        <v>4</v>
+      </c>
+      <c r="T306">
+        <v>1.3</v>
+      </c>
+      <c r="U306">
+        <v>3.4</v>
+      </c>
+      <c r="V306">
+        <v>2.5</v>
+      </c>
+      <c r="W306">
+        <v>1.5</v>
+      </c>
+      <c r="X306">
+        <v>6</v>
+      </c>
+      <c r="Y306">
+        <v>1.13</v>
+      </c>
+      <c r="Z306">
+        <v>1.86</v>
+      </c>
+      <c r="AA306">
+        <v>3.41</v>
+      </c>
+      <c r="AB306">
+        <v>3.47</v>
+      </c>
+      <c r="AC306">
+        <v>1.01</v>
+      </c>
+      <c r="AD306">
+        <v>11</v>
+      </c>
+      <c r="AE306">
+        <v>1.18</v>
+      </c>
+      <c r="AF306">
+        <v>4.05</v>
+      </c>
+      <c r="AG306">
+        <v>1.54</v>
+      </c>
+      <c r="AH306">
+        <v>2.3</v>
+      </c>
+      <c r="AI306">
+        <v>1.62</v>
+      </c>
+      <c r="AJ306">
+        <v>2.2</v>
+      </c>
+      <c r="AK306">
+        <v>1.3</v>
+      </c>
+      <c r="AL306">
+        <v>1.26</v>
+      </c>
+      <c r="AM306">
+        <v>1.77</v>
+      </c>
+      <c r="AN306">
+        <v>2.22</v>
+      </c>
+      <c r="AO306">
+        <v>1.5</v>
+      </c>
+      <c r="AP306">
+        <v>2.1</v>
+      </c>
+      <c r="AQ306">
+        <v>1.44</v>
+      </c>
+      <c r="AR306">
+        <v>1.96</v>
+      </c>
+      <c r="AS306">
+        <v>1.44</v>
+      </c>
+      <c r="AT306">
+        <v>3.4</v>
+      </c>
+      <c r="AU306">
+        <v>3</v>
+      </c>
+      <c r="AV306">
+        <v>4</v>
+      </c>
+      <c r="AW306">
+        <v>7</v>
+      </c>
+      <c r="AX306">
+        <v>6</v>
+      </c>
+      <c r="AY306">
+        <v>10</v>
+      </c>
+      <c r="AZ306">
+        <v>10</v>
+      </c>
+      <c r="BA306">
+        <v>2</v>
+      </c>
+      <c r="BB306">
+        <v>1</v>
+      </c>
+      <c r="BC306">
+        <v>3</v>
+      </c>
+      <c r="BD306">
+        <v>1.67</v>
+      </c>
+      <c r="BE306">
+        <v>6.4</v>
+      </c>
+      <c r="BF306">
+        <v>2.48</v>
+      </c>
+      <c r="BG306">
+        <v>1.32</v>
+      </c>
+      <c r="BH306">
+        <v>3.05</v>
+      </c>
+      <c r="BI306">
+        <v>1.54</v>
+      </c>
+      <c r="BJ306">
+        <v>2.28</v>
+      </c>
+      <c r="BK306">
+        <v>1.88</v>
+      </c>
+      <c r="BL306">
+        <v>1.8</v>
+      </c>
+      <c r="BM306">
+        <v>2.4</v>
+      </c>
+      <c r="BN306">
+        <v>1.49</v>
+      </c>
+      <c r="BO306">
+        <v>3.05</v>
+      </c>
+      <c r="BP306">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -62751,31 +62751,31 @@
         <v>444</v>
       </c>
       <c r="Q297">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R297">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S297">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T297">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U297">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V297">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="W297">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X297">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y297">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z297">
         <v>2.44</v>
@@ -62787,16 +62787,16 @@
         <v>2.37</v>
       </c>
       <c r="AC297">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AD297">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE297">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF297">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="AG297">
         <v>1.57</v>
@@ -62805,19 +62805,19 @@
         <v>2.25</v>
       </c>
       <c r="AI297">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ297">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK297">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL297">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AM297">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AN297">
         <v>2.25</v>
@@ -62841,22 +62841,22 @@
         <v>3.29</v>
       </c>
       <c r="AU297">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV297">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW297">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX297">
         <v>5</v>
       </c>
       <c r="AY297">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AZ297">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA297">
         <v>2</v>
@@ -62868,43 +62868,43 @@
         <v>8</v>
       </c>
       <c r="BD297">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BE297">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BF297">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BG297">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BH297">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BI297">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BJ297">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BK297">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BL297">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BM297">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BN297">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BO297">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BP297">
-        <v>0</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="298" spans="1:68">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="451">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -943,6 +943,9 @@
     <t>['43']</t>
   </si>
   <si>
+    <t>['42', '48', '59']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -1362,6 +1365,9 @@
   <si>
     <t>['36', '45+2', '87', '90+10']</t>
   </si>
+  <si>
+    <t>['27', '38']</t>
+  </si>
 </sst>
 </file>
 
@@ -1722,7 +1728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP306"/>
+  <dimension ref="A1:BP308"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2056,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ2">
         <v>1.73</v>
@@ -2184,7 +2190,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -2390,7 +2396,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2802,7 +2808,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -3008,7 +3014,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3214,7 +3220,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -3626,7 +3632,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -4119,7 +4125,7 @@
         <v>1</v>
       </c>
       <c r="AQ12">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4450,7 +4456,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -4656,7 +4662,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4862,7 +4868,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -5558,7 +5564,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ19">
         <v>1.44</v>
@@ -5892,7 +5898,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -6304,7 +6310,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6510,7 +6516,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6922,7 +6928,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -7206,7 +7212,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ27">
         <v>0.78</v>
@@ -7952,7 +7958,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -8033,7 +8039,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ31">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR31">
         <v>1.39</v>
@@ -8364,7 +8370,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -9188,7 +9194,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9266,7 +9272,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ37">
         <v>1.73</v>
@@ -9681,7 +9687,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ39">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR39">
         <v>1.5</v>
@@ -9806,7 +9812,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -10218,7 +10224,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -11042,7 +11048,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -11248,7 +11254,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -11454,7 +11460,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11738,7 +11744,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ49">
         <v>1</v>
@@ -12278,7 +12284,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12484,7 +12490,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12896,7 +12902,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -13514,7 +13520,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13595,7 +13601,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ58">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR58">
         <v>1.87</v>
@@ -13720,7 +13726,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -14132,7 +14138,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14213,7 +14219,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ61">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR61">
         <v>1.66</v>
@@ -14338,7 +14344,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -14544,7 +14550,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14750,7 +14756,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -15780,7 +15786,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -16192,7 +16198,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16398,7 +16404,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16810,7 +16816,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -17300,7 +17306,7 @@
         <v>0.5</v>
       </c>
       <c r="AP76">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ76">
         <v>0.64</v>
@@ -18046,7 +18052,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18252,7 +18258,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18458,7 +18464,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -19076,7 +19082,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -19282,7 +19288,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -19488,7 +19494,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -20106,7 +20112,7 @@
         <v>164</v>
       </c>
       <c r="P90" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
@@ -21342,7 +21348,7 @@
         <v>168</v>
       </c>
       <c r="P96" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -22453,7 +22459,7 @@
         <v>2</v>
       </c>
       <c r="AQ101">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR101">
         <v>1.75</v>
@@ -22784,7 +22790,7 @@
         <v>122</v>
       </c>
       <c r="P103" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q103">
         <v>2.75</v>
@@ -24432,7 +24438,7 @@
         <v>109</v>
       </c>
       <c r="P111" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q111">
         <v>2.88</v>
@@ -25050,7 +25056,7 @@
         <v>177</v>
       </c>
       <c r="P114" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25256,7 +25262,7 @@
         <v>178</v>
       </c>
       <c r="P115" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -25668,7 +25674,7 @@
         <v>179</v>
       </c>
       <c r="P117" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25746,7 +25752,7 @@
         <v>1.5</v>
       </c>
       <c r="AP117">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ117">
         <v>1.4</v>
@@ -25874,7 +25880,7 @@
         <v>180</v>
       </c>
       <c r="P118" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -26161,7 +26167,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ119">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR119">
         <v>0.98</v>
@@ -26286,7 +26292,7 @@
         <v>181</v>
       </c>
       <c r="P120" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -26698,7 +26704,7 @@
         <v>109</v>
       </c>
       <c r="P122" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q122">
         <v>2.75</v>
@@ -26779,7 +26785,7 @@
         <v>2</v>
       </c>
       <c r="AQ122">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR122">
         <v>1.93</v>
@@ -27110,7 +27116,7 @@
         <v>129</v>
       </c>
       <c r="P124" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q124">
         <v>2.5</v>
@@ -27806,7 +27812,7 @@
         <v>0.5</v>
       </c>
       <c r="AP127">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ127">
         <v>0.78</v>
@@ -28140,7 +28146,7 @@
         <v>187</v>
       </c>
       <c r="P129" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28346,7 +28352,7 @@
         <v>188</v>
       </c>
       <c r="P130" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q130">
         <v>2.4</v>
@@ -28427,7 +28433,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ130">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR130">
         <v>1.45</v>
@@ -29170,7 +29176,7 @@
         <v>189</v>
       </c>
       <c r="P134" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q134">
         <v>3</v>
@@ -29376,7 +29382,7 @@
         <v>190</v>
       </c>
       <c r="P135" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -30612,7 +30618,7 @@
         <v>109</v>
       </c>
       <c r="P141" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q141">
         <v>2.38</v>
@@ -31024,7 +31030,7 @@
         <v>174</v>
       </c>
       <c r="P143" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -31436,7 +31442,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q145">
         <v>2.4</v>
@@ -31642,7 +31648,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31848,7 +31854,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q147">
         <v>2.6</v>
@@ -32054,7 +32060,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q148">
         <v>2.05</v>
@@ -32260,7 +32266,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -32338,7 +32344,7 @@
         <v>1</v>
       </c>
       <c r="AP149">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ149">
         <v>0.45</v>
@@ -32466,7 +32472,7 @@
         <v>202</v>
       </c>
       <c r="P150" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q150">
         <v>2.4</v>
@@ -32878,7 +32884,7 @@
         <v>109</v>
       </c>
       <c r="P152" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q152">
         <v>2.88</v>
@@ -33290,7 +33296,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q154">
         <v>3.1</v>
@@ -33496,7 +33502,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q155">
         <v>2.2</v>
@@ -33783,7 +33789,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ156">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR156">
         <v>1.51</v>
@@ -33908,7 +33914,7 @@
         <v>109</v>
       </c>
       <c r="P157" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q157">
         <v>3.2</v>
@@ -34526,7 +34532,7 @@
         <v>209</v>
       </c>
       <c r="P160" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q160">
         <v>2.1</v>
@@ -34810,7 +34816,7 @@
         <v>0.75</v>
       </c>
       <c r="AP161">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ161">
         <v>1.3</v>
@@ -34938,7 +34944,7 @@
         <v>211</v>
       </c>
       <c r="P162" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q162">
         <v>2.5</v>
@@ -35968,7 +35974,7 @@
         <v>215</v>
       </c>
       <c r="P167" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -36049,7 +36055,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ167">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR167">
         <v>1.76</v>
@@ -36380,7 +36386,7 @@
         <v>217</v>
       </c>
       <c r="P169" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q169">
         <v>3</v>
@@ -36586,7 +36592,7 @@
         <v>218</v>
       </c>
       <c r="P170" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36792,7 +36798,7 @@
         <v>109</v>
       </c>
       <c r="P171" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q171">
         <v>2.25</v>
@@ -36998,7 +37004,7 @@
         <v>219</v>
       </c>
       <c r="P172" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q172">
         <v>2.4</v>
@@ -37410,7 +37416,7 @@
         <v>221</v>
       </c>
       <c r="P174" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q174">
         <v>2.5</v>
@@ -37616,7 +37622,7 @@
         <v>163</v>
       </c>
       <c r="P175" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -37822,7 +37828,7 @@
         <v>113</v>
       </c>
       <c r="P176" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q176">
         <v>2.4</v>
@@ -38028,7 +38034,7 @@
         <v>222</v>
       </c>
       <c r="P177" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -38234,7 +38240,7 @@
         <v>109</v>
       </c>
       <c r="P178" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q178">
         <v>2.38</v>
@@ -38646,7 +38652,7 @@
         <v>224</v>
       </c>
       <c r="P180" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -39058,7 +39064,7 @@
         <v>225</v>
       </c>
       <c r="P182" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q182">
         <v>3.75</v>
@@ -39264,7 +39270,7 @@
         <v>226</v>
       </c>
       <c r="P183" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q183">
         <v>2.5</v>
@@ -39470,7 +39476,7 @@
         <v>227</v>
       </c>
       <c r="P184" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q184">
         <v>2.05</v>
@@ -39882,7 +39888,7 @@
         <v>228</v>
       </c>
       <c r="P186" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q186">
         <v>2.4</v>
@@ -40294,7 +40300,7 @@
         <v>230</v>
       </c>
       <c r="P188" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40500,7 +40506,7 @@
         <v>176</v>
       </c>
       <c r="P189" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40990,7 +40996,7 @@
         <v>1.14</v>
       </c>
       <c r="AP191">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ191">
         <v>0.9</v>
@@ -41199,7 +41205,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ192">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR192">
         <v>1.75</v>
@@ -41324,7 +41330,7 @@
         <v>233</v>
       </c>
       <c r="P193" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41405,7 +41411,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ193">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR193">
         <v>2.11</v>
@@ -41530,7 +41536,7 @@
         <v>234</v>
       </c>
       <c r="P194" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41942,7 +41948,7 @@
         <v>198</v>
       </c>
       <c r="P196" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q196">
         <v>2.63</v>
@@ -42354,7 +42360,7 @@
         <v>103</v>
       </c>
       <c r="P198" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q198">
         <v>2.63</v>
@@ -42638,7 +42644,7 @@
         <v>1.2</v>
       </c>
       <c r="AP199">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ199">
         <v>1.4</v>
@@ -43384,7 +43390,7 @@
         <v>109</v>
       </c>
       <c r="P203" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q203">
         <v>2.63</v>
@@ -43796,7 +43802,7 @@
         <v>237</v>
       </c>
       <c r="P205" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -44208,7 +44214,7 @@
         <v>109</v>
       </c>
       <c r="P207" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q207">
         <v>2.25</v>
@@ -45032,7 +45038,7 @@
         <v>240</v>
       </c>
       <c r="P211" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q211">
         <v>3.2</v>
@@ -45238,7 +45244,7 @@
         <v>109</v>
       </c>
       <c r="P212" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45444,7 +45450,7 @@
         <v>241</v>
       </c>
       <c r="P213" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q213">
         <v>4</v>
@@ -45856,7 +45862,7 @@
         <v>242</v>
       </c>
       <c r="P215" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -45937,7 +45943,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ215">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR215">
         <v>1.85</v>
@@ -46062,7 +46068,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q216">
         <v>3.4</v>
@@ -46268,7 +46274,7 @@
         <v>243</v>
       </c>
       <c r="P217" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q217">
         <v>2.75</v>
@@ -46680,7 +46686,7 @@
         <v>244</v>
       </c>
       <c r="P219" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q219">
         <v>3.1</v>
@@ -47092,7 +47098,7 @@
         <v>246</v>
       </c>
       <c r="P221" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q221">
         <v>2.6</v>
@@ -47298,7 +47304,7 @@
         <v>247</v>
       </c>
       <c r="P222" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q222">
         <v>2.5</v>
@@ -47504,7 +47510,7 @@
         <v>248</v>
       </c>
       <c r="P223" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47710,7 +47716,7 @@
         <v>249</v>
       </c>
       <c r="P224" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47916,7 +47922,7 @@
         <v>250</v>
       </c>
       <c r="P225" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -48122,7 +48128,7 @@
         <v>251</v>
       </c>
       <c r="P226" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q226">
         <v>2.75</v>
@@ -48328,7 +48334,7 @@
         <v>252</v>
       </c>
       <c r="P227" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q227">
         <v>1.83</v>
@@ -48534,7 +48540,7 @@
         <v>253</v>
       </c>
       <c r="P228" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48740,7 +48746,7 @@
         <v>109</v>
       </c>
       <c r="P229" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q229">
         <v>2.5</v>
@@ -48946,7 +48952,7 @@
         <v>254</v>
       </c>
       <c r="P230" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q230">
         <v>3.25</v>
@@ -49152,7 +49158,7 @@
         <v>119</v>
       </c>
       <c r="P231" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q231">
         <v>2.4</v>
@@ -49770,7 +49776,7 @@
         <v>109</v>
       </c>
       <c r="P234" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q234">
         <v>2.5</v>
@@ -50057,7 +50063,7 @@
         <v>2</v>
       </c>
       <c r="AQ235">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR235">
         <v>1.24</v>
@@ -50388,7 +50394,7 @@
         <v>258</v>
       </c>
       <c r="P237" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q237">
         <v>2.75</v>
@@ -50594,7 +50600,7 @@
         <v>259</v>
       </c>
       <c r="P238" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q238">
         <v>2.6</v>
@@ -50800,7 +50806,7 @@
         <v>109</v>
       </c>
       <c r="P239" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -51006,7 +51012,7 @@
         <v>140</v>
       </c>
       <c r="P240" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -51418,7 +51424,7 @@
         <v>109</v>
       </c>
       <c r="P242" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q242">
         <v>3.1</v>
@@ -51830,7 +51836,7 @@
         <v>161</v>
       </c>
       <c r="P244" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q244">
         <v>2.1</v>
@@ -52242,7 +52248,7 @@
         <v>156</v>
       </c>
       <c r="P246" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q246">
         <v>2.5</v>
@@ -52860,7 +52866,7 @@
         <v>264</v>
       </c>
       <c r="P249" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q249">
         <v>2.5</v>
@@ -53066,7 +53072,7 @@
         <v>265</v>
       </c>
       <c r="P250" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q250">
         <v>3.2</v>
@@ -53272,7 +53278,7 @@
         <v>109</v>
       </c>
       <c r="P251" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q251">
         <v>2.75</v>
@@ -53478,7 +53484,7 @@
         <v>266</v>
       </c>
       <c r="P252" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q252">
         <v>2.25</v>
@@ -53968,7 +53974,7 @@
         <v>0.89</v>
       </c>
       <c r="AP254">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ254">
         <v>1</v>
@@ -54302,7 +54308,7 @@
         <v>270</v>
       </c>
       <c r="P256" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q256">
         <v>2.25</v>
@@ -54508,7 +54514,7 @@
         <v>271</v>
       </c>
       <c r="P257" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q257">
         <v>2.63</v>
@@ -54714,7 +54720,7 @@
         <v>272</v>
       </c>
       <c r="P258" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q258">
         <v>2.3</v>
@@ -54920,7 +54926,7 @@
         <v>109</v>
       </c>
       <c r="P259" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q259">
         <v>3.1</v>
@@ -54998,7 +55004,7 @@
         <v>1.44</v>
       </c>
       <c r="AP259">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ259">
         <v>1.83</v>
@@ -55332,7 +55338,7 @@
         <v>274</v>
       </c>
       <c r="P261" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -55538,7 +55544,7 @@
         <v>275</v>
       </c>
       <c r="P262" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q262">
         <v>2.5</v>
@@ -55744,7 +55750,7 @@
         <v>234</v>
       </c>
       <c r="P263" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q263">
         <v>2.25</v>
@@ -55950,7 +55956,7 @@
         <v>109</v>
       </c>
       <c r="P264" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q264">
         <v>2.75</v>
@@ -56156,7 +56162,7 @@
         <v>276</v>
       </c>
       <c r="P265" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q265">
         <v>2.88</v>
@@ -56362,7 +56368,7 @@
         <v>109</v>
       </c>
       <c r="P266" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q266">
         <v>3.4</v>
@@ -56774,7 +56780,7 @@
         <v>278</v>
       </c>
       <c r="P268" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q268">
         <v>2.2</v>
@@ -56980,7 +56986,7 @@
         <v>279</v>
       </c>
       <c r="P269" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57186,7 +57192,7 @@
         <v>280</v>
       </c>
       <c r="P270" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q270">
         <v>3.35</v>
@@ -57264,7 +57270,7 @@
         <v>1.63</v>
       </c>
       <c r="AP270">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ270">
         <v>1.9</v>
@@ -57598,7 +57604,7 @@
         <v>282</v>
       </c>
       <c r="P272" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q272">
         <v>2.38</v>
@@ -57804,7 +57810,7 @@
         <v>283</v>
       </c>
       <c r="P273" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q273">
         <v>3.4</v>
@@ -58010,7 +58016,7 @@
         <v>284</v>
       </c>
       <c r="P274" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q274">
         <v>3</v>
@@ -58422,7 +58428,7 @@
         <v>285</v>
       </c>
       <c r="P276" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q276">
         <v>2.63</v>
@@ -58628,7 +58634,7 @@
         <v>286</v>
       </c>
       <c r="P277" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -59040,7 +59046,7 @@
         <v>288</v>
       </c>
       <c r="P279" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q279">
         <v>2.63</v>
@@ -59452,7 +59458,7 @@
         <v>290</v>
       </c>
       <c r="P281" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q281">
         <v>2.25</v>
@@ -59530,10 +59536,10 @@
         <v>1</v>
       </c>
       <c r="AP281">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ281">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR281">
         <v>1.36</v>
@@ -59658,7 +59664,7 @@
         <v>291</v>
       </c>
       <c r="P282" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q282">
         <v>2.88</v>
@@ -60276,7 +60282,7 @@
         <v>293</v>
       </c>
       <c r="P285" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q285">
         <v>2.5</v>
@@ -60482,7 +60488,7 @@
         <v>294</v>
       </c>
       <c r="P286" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -61796,7 +61802,7 @@
         <v>1.88</v>
       </c>
       <c r="AP292">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ292">
         <v>1.8</v>
@@ -62130,7 +62136,7 @@
         <v>112</v>
       </c>
       <c r="P294" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q294">
         <v>3.1</v>
@@ -62336,7 +62342,7 @@
         <v>122</v>
       </c>
       <c r="P295" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q295">
         <v>2.4</v>
@@ -62748,7 +62754,7 @@
         <v>301</v>
       </c>
       <c r="P297" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q297">
         <v>3.4</v>
@@ -63160,7 +63166,7 @@
         <v>302</v>
       </c>
       <c r="P299" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Q299">
         <v>3.2</v>
@@ -63241,7 +63247,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ299">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR299">
         <v>1.55</v>
@@ -63778,7 +63784,7 @@
         <v>305</v>
       </c>
       <c r="P302" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Q302">
         <v>2.2</v>
@@ -63984,7 +63990,7 @@
         <v>306</v>
       </c>
       <c r="P303" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q303">
         <v>2.5</v>
@@ -64190,7 +64196,7 @@
         <v>307</v>
       </c>
       <c r="P304" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Q304">
         <v>0</v>
@@ -64396,7 +64402,7 @@
         <v>255</v>
       </c>
       <c r="P305" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q305">
         <v>2.5</v>
@@ -64759,6 +64765,418 @@
       </c>
       <c r="BP306">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="307" spans="1:68">
+      <c r="A307" s="1">
+        <v>306</v>
+      </c>
+      <c r="B307">
+        <v>7781386</v>
+      </c>
+      <c r="C307" t="s">
+        <v>68</v>
+      </c>
+      <c r="D307" t="s">
+        <v>69</v>
+      </c>
+      <c r="E307" s="2">
+        <v>45847.85416666666</v>
+      </c>
+      <c r="F307">
+        <v>0</v>
+      </c>
+      <c r="G307" t="s">
+        <v>87</v>
+      </c>
+      <c r="H307" t="s">
+        <v>71</v>
+      </c>
+      <c r="I307">
+        <v>0</v>
+      </c>
+      <c r="J307">
+        <v>2</v>
+      </c>
+      <c r="K307">
+        <v>2</v>
+      </c>
+      <c r="L307">
+        <v>1</v>
+      </c>
+      <c r="M307">
+        <v>2</v>
+      </c>
+      <c r="N307">
+        <v>3</v>
+      </c>
+      <c r="O307" t="s">
+        <v>199</v>
+      </c>
+      <c r="P307" t="s">
+        <v>450</v>
+      </c>
+      <c r="Q307">
+        <v>3.26</v>
+      </c>
+      <c r="R307">
+        <v>2.35</v>
+      </c>
+      <c r="S307">
+        <v>2.77</v>
+      </c>
+      <c r="T307">
+        <v>1.24</v>
+      </c>
+      <c r="U307">
+        <v>3.34</v>
+      </c>
+      <c r="V307">
+        <v>2.17</v>
+      </c>
+      <c r="W307">
+        <v>1.61</v>
+      </c>
+      <c r="X307">
+        <v>4.6</v>
+      </c>
+      <c r="Y307">
+        <v>1.13</v>
+      </c>
+      <c r="Z307">
+        <v>2.39</v>
+      </c>
+      <c r="AA307">
+        <v>3.47</v>
+      </c>
+      <c r="AB307">
+        <v>2.42</v>
+      </c>
+      <c r="AC307">
+        <v>1.01</v>
+      </c>
+      <c r="AD307">
+        <v>17</v>
+      </c>
+      <c r="AE307">
+        <v>1.12</v>
+      </c>
+      <c r="AF307">
+        <v>4.65</v>
+      </c>
+      <c r="AG307">
+        <v>1.49</v>
+      </c>
+      <c r="AH307">
+        <v>2.51</v>
+      </c>
+      <c r="AI307">
+        <v>1.45</v>
+      </c>
+      <c r="AJ307">
+        <v>2.55</v>
+      </c>
+      <c r="AK307">
+        <v>1.6</v>
+      </c>
+      <c r="AL307">
+        <v>1.28</v>
+      </c>
+      <c r="AM307">
+        <v>1.44</v>
+      </c>
+      <c r="AN307">
+        <v>1</v>
+      </c>
+      <c r="AO307">
+        <v>1.88</v>
+      </c>
+      <c r="AP307">
+        <v>0.89</v>
+      </c>
+      <c r="AQ307">
+        <v>2</v>
+      </c>
+      <c r="AR307">
+        <v>1.51</v>
+      </c>
+      <c r="AS307">
+        <v>1.45</v>
+      </c>
+      <c r="AT307">
+        <v>2.96</v>
+      </c>
+      <c r="AU307">
+        <v>7</v>
+      </c>
+      <c r="AV307">
+        <v>3</v>
+      </c>
+      <c r="AW307">
+        <v>8</v>
+      </c>
+      <c r="AX307">
+        <v>11</v>
+      </c>
+      <c r="AY307">
+        <v>15</v>
+      </c>
+      <c r="AZ307">
+        <v>14</v>
+      </c>
+      <c r="BA307">
+        <v>5</v>
+      </c>
+      <c r="BB307">
+        <v>3</v>
+      </c>
+      <c r="BC307">
+        <v>8</v>
+      </c>
+      <c r="BD307">
+        <v>2.02</v>
+      </c>
+      <c r="BE307">
+        <v>6.75</v>
+      </c>
+      <c r="BF307">
+        <v>1.95</v>
+      </c>
+      <c r="BG307">
+        <v>1.23</v>
+      </c>
+      <c r="BH307">
+        <v>3.65</v>
+      </c>
+      <c r="BI307">
+        <v>1.41</v>
+      </c>
+      <c r="BJ307">
+        <v>2.65</v>
+      </c>
+      <c r="BK307">
+        <v>1.68</v>
+      </c>
+      <c r="BL307">
+        <v>2.04</v>
+      </c>
+      <c r="BM307">
+        <v>2.06</v>
+      </c>
+      <c r="BN307">
+        <v>1.66</v>
+      </c>
+      <c r="BO307">
+        <v>2.6</v>
+      </c>
+      <c r="BP307">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="308" spans="1:68">
+      <c r="A308" s="1">
+        <v>307</v>
+      </c>
+      <c r="B308">
+        <v>7781323</v>
+      </c>
+      <c r="C308" t="s">
+        <v>68</v>
+      </c>
+      <c r="D308" t="s">
+        <v>69</v>
+      </c>
+      <c r="E308" s="2">
+        <v>45847.97569444445</v>
+      </c>
+      <c r="F308">
+        <v>0</v>
+      </c>
+      <c r="G308" t="s">
+        <v>70</v>
+      </c>
+      <c r="H308" t="s">
+        <v>93</v>
+      </c>
+      <c r="I308">
+        <v>1</v>
+      </c>
+      <c r="J308">
+        <v>0</v>
+      </c>
+      <c r="K308">
+        <v>1</v>
+      </c>
+      <c r="L308">
+        <v>3</v>
+      </c>
+      <c r="M308">
+        <v>0</v>
+      </c>
+      <c r="N308">
+        <v>3</v>
+      </c>
+      <c r="O308" t="s">
+        <v>309</v>
+      </c>
+      <c r="P308" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q308">
+        <v>2.4</v>
+      </c>
+      <c r="R308">
+        <v>2.38</v>
+      </c>
+      <c r="S308">
+        <v>4</v>
+      </c>
+      <c r="T308">
+        <v>1.3</v>
+      </c>
+      <c r="U308">
+        <v>3.4</v>
+      </c>
+      <c r="V308">
+        <v>2.5</v>
+      </c>
+      <c r="W308">
+        <v>1.5</v>
+      </c>
+      <c r="X308">
+        <v>6</v>
+      </c>
+      <c r="Y308">
+        <v>1.13</v>
+      </c>
+      <c r="Z308">
+        <v>1.29</v>
+      </c>
+      <c r="AA308">
+        <v>4.8</v>
+      </c>
+      <c r="AB308">
+        <v>7.3</v>
+      </c>
+      <c r="AC308">
+        <v>1.04</v>
+      </c>
+      <c r="AD308">
+        <v>10</v>
+      </c>
+      <c r="AE308">
+        <v>1.14</v>
+      </c>
+      <c r="AF308">
+        <v>4.4</v>
+      </c>
+      <c r="AG308">
+        <v>1.42</v>
+      </c>
+      <c r="AH308">
+        <v>2.74</v>
+      </c>
+      <c r="AI308">
+        <v>1.62</v>
+      </c>
+      <c r="AJ308">
+        <v>2.2</v>
+      </c>
+      <c r="AK308">
+        <v>1.08</v>
+      </c>
+      <c r="AL308">
+        <v>1.17</v>
+      </c>
+      <c r="AM308">
+        <v>3.08</v>
+      </c>
+      <c r="AN308">
+        <v>2.11</v>
+      </c>
+      <c r="AO308">
+        <v>1</v>
+      </c>
+      <c r="AP308">
+        <v>2.2</v>
+      </c>
+      <c r="AQ308">
+        <v>0.9</v>
+      </c>
+      <c r="AR308">
+        <v>1.83</v>
+      </c>
+      <c r="AS308">
+        <v>0.99</v>
+      </c>
+      <c r="AT308">
+        <v>2.82</v>
+      </c>
+      <c r="AU308">
+        <v>6</v>
+      </c>
+      <c r="AV308">
+        <v>3</v>
+      </c>
+      <c r="AW308">
+        <v>6</v>
+      </c>
+      <c r="AX308">
+        <v>1</v>
+      </c>
+      <c r="AY308">
+        <v>12</v>
+      </c>
+      <c r="AZ308">
+        <v>4</v>
+      </c>
+      <c r="BA308">
+        <v>2</v>
+      </c>
+      <c r="BB308">
+        <v>0</v>
+      </c>
+      <c r="BC308">
+        <v>2</v>
+      </c>
+      <c r="BD308">
+        <v>1.32</v>
+      </c>
+      <c r="BE308">
+        <v>7</v>
+      </c>
+      <c r="BF308">
+        <v>3.8</v>
+      </c>
+      <c r="BG308">
+        <v>1.26</v>
+      </c>
+      <c r="BH308">
+        <v>3.4</v>
+      </c>
+      <c r="BI308">
+        <v>1.47</v>
+      </c>
+      <c r="BJ308">
+        <v>2.48</v>
+      </c>
+      <c r="BK308">
+        <v>1.76</v>
+      </c>
+      <c r="BL308">
+        <v>1.94</v>
+      </c>
+      <c r="BM308">
+        <v>2.18</v>
+      </c>
+      <c r="BN308">
+        <v>1.58</v>
+      </c>
+      <c r="BO308">
+        <v>2.8</v>
+      </c>
+      <c r="BP308">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="464">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -946,6 +946,42 @@
     <t>['42', '48', '59']</t>
   </si>
   <si>
+    <t>['9', '24']</t>
+  </si>
+  <si>
+    <t>['48']</t>
+  </si>
+  <si>
+    <t>['28']</t>
+  </si>
+  <si>
+    <t>['17', '62']</t>
+  </si>
+  <si>
+    <t>['67', '90+6']</t>
+  </si>
+  <si>
+    <t>['2', '42', '45+5', '90+5']</t>
+  </si>
+  <si>
+    <t>['1', '5']</t>
+  </si>
+  <si>
+    <t>['14', '81']</t>
+  </si>
+  <si>
+    <t>['12', '30', '59']</t>
+  </si>
+  <si>
+    <t>['42']</t>
+  </si>
+  <si>
+    <t>['23', '53']</t>
+  </si>
+  <si>
+    <t>['31', '45']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -1072,9 +1108,6 @@
     <t>['1', '29']</t>
   </si>
   <si>
-    <t>['28']</t>
-  </si>
-  <si>
     <t>['49', '89']</t>
   </si>
   <si>
@@ -1139,12 +1172,6 @@
   </si>
   <si>
     <t>['90+6']</t>
-  </si>
-  <si>
-    <t>['42']</t>
-  </si>
-  <si>
-    <t>['48']</t>
   </si>
   <si>
     <t>['61', '90+3']</t>
@@ -1367,6 +1394,18 @@
   </si>
   <si>
     <t>['27', '38']</t>
+  </si>
+  <si>
+    <t>['83']</t>
+  </si>
+  <si>
+    <t>['8', '45+3']</t>
+  </si>
+  <si>
+    <t>['15', '27', '45+8']</t>
+  </si>
+  <si>
+    <t>['42', '45+3', '59', '90+3']</t>
   </si>
 </sst>
 </file>
@@ -1728,7 +1767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP308"/>
+  <dimension ref="A1:BP322"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2062,7 +2101,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ2">
         <v>1.73</v>
@@ -2190,7 +2229,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -2268,10 +2307,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2396,7 +2435,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2477,7 +2516,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ4">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2680,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ5">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2808,7 +2847,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -3014,7 +3053,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3220,7 +3259,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -3298,7 +3337,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ8">
         <v>1.73</v>
@@ -3504,7 +3543,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -3632,7 +3671,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -3713,7 +3752,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ10">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3919,7 +3958,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ11">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4456,7 +4495,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -4662,7 +4701,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4743,7 +4782,7 @@
         <v>2</v>
       </c>
       <c r="AQ15">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4868,7 +4907,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4946,10 +4985,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ16">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5152,10 +5191,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ17">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5358,10 +5397,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ18">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5567,7 +5606,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ19">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5773,7 +5812,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ20">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5898,7 +5937,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -5976,7 +6015,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ21">
         <v>1</v>
@@ -6182,7 +6221,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ22">
         <v>1.83</v>
@@ -6310,7 +6349,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6388,10 +6427,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ23">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6516,7 +6555,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6594,10 +6633,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ24">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -6800,10 +6839,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ25">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6928,7 +6967,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -7006,10 +7045,10 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ26">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR26">
         <v>0</v>
@@ -7212,10 +7251,10 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ27">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR27">
         <v>1.64</v>
@@ -7958,7 +7997,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -8245,7 +8284,7 @@
         <v>2</v>
       </c>
       <c r="AQ32">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR32">
         <v>1.83</v>
@@ -8370,7 +8409,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -8657,7 +8696,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ34">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR34">
         <v>1.85</v>
@@ -8860,7 +8899,7 @@
         <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -9194,7 +9233,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9684,7 +9723,7 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ39">
         <v>0.9</v>
@@ -9812,7 +9851,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -10224,7 +10263,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -10302,10 +10341,10 @@
         <v>3</v>
       </c>
       <c r="AP42">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ42">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR42">
         <v>1.41</v>
@@ -10511,7 +10550,7 @@
         <v>2</v>
       </c>
       <c r="AQ43">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR43">
         <v>1.87</v>
@@ -10920,7 +10959,7 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ45">
         <v>0.58</v>
@@ -11048,7 +11087,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -11126,7 +11165,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ46">
         <v>0.45</v>
@@ -11254,7 +11293,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -11332,7 +11371,7 @@
         <v>1.5</v>
       </c>
       <c r="AP47">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ47">
         <v>1.64</v>
@@ -11460,7 +11499,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11744,7 +11783,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ49">
         <v>1</v>
@@ -11950,7 +11989,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ50">
         <v>1.83</v>
@@ -12159,7 +12198,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ51">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR51">
         <v>1.36</v>
@@ -12284,7 +12323,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12365,7 +12404,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ52">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR52">
         <v>1.84</v>
@@ -12490,7 +12529,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12568,7 +12607,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ53">
         <v>1.73</v>
@@ -12777,7 +12816,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ54">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR54">
         <v>1.95</v>
@@ -12902,7 +12941,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -13189,7 +13228,7 @@
         <v>1</v>
       </c>
       <c r="AQ56">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR56">
         <v>2.14</v>
@@ -13395,7 +13434,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ57">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR57">
         <v>1.55</v>
@@ -13520,7 +13559,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13726,7 +13765,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13804,10 +13843,10 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ59">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR59">
         <v>1.65</v>
@@ -14138,7 +14177,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14344,7 +14383,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -14422,10 +14461,10 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ62">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR62">
         <v>1.6</v>
@@ -14550,7 +14589,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14628,7 +14667,7 @@
         <v>0.5</v>
       </c>
       <c r="AP63">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ63">
         <v>0.33</v>
@@ -14756,7 +14795,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -14834,10 +14873,10 @@
         <v>3</v>
       </c>
       <c r="AP64">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ64">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR64">
         <v>1.62</v>
@@ -15043,7 +15082,7 @@
         <v>2</v>
       </c>
       <c r="AQ65">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR65">
         <v>1.71</v>
@@ -15452,10 +15491,10 @@
         <v>1</v>
       </c>
       <c r="AP67">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ67">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR67">
         <v>1.65</v>
@@ -15658,7 +15697,7 @@
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ68">
         <v>0.45</v>
@@ -15786,7 +15825,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15864,7 +15903,7 @@
         <v>0</v>
       </c>
       <c r="AP69">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ69">
         <v>0.88</v>
@@ -16073,7 +16112,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ70">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR70">
         <v>1.96</v>
@@ -16198,7 +16237,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16276,7 +16315,7 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ71">
         <v>1.22</v>
@@ -16404,7 +16443,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16482,10 +16521,10 @@
         <v>2</v>
       </c>
       <c r="AP72">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ72">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR72">
         <v>1.41</v>
@@ -16691,7 +16730,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ73">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR73">
         <v>2.23</v>
@@ -16816,7 +16855,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -17100,10 +17139,10 @@
         <v>3</v>
       </c>
       <c r="AP75">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ75">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR75">
         <v>1.74</v>
@@ -17309,7 +17348,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ76">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR76">
         <v>0.97</v>
@@ -17512,10 +17551,10 @@
         <v>3</v>
       </c>
       <c r="AP77">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ77">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR77">
         <v>0.9</v>
@@ -17718,7 +17757,7 @@
         <v>0.5</v>
       </c>
       <c r="AP78">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ78">
         <v>0.58</v>
@@ -17924,7 +17963,7 @@
         <v>3</v>
       </c>
       <c r="AP79">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ79">
         <v>1.73</v>
@@ -18052,7 +18091,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18133,7 +18172,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ80">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR80">
         <v>1.6</v>
@@ -18258,7 +18297,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18339,7 +18378,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ81">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR81">
         <v>1.62</v>
@@ -18464,7 +18503,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -18542,10 +18581,10 @@
         <v>0.2</v>
       </c>
       <c r="AP82">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ82">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR82">
         <v>1.1</v>
@@ -18954,7 +18993,7 @@
         <v>1.5</v>
       </c>
       <c r="AP84">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ84">
         <v>0.82</v>
@@ -19082,7 +19121,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -19288,7 +19327,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -19366,7 +19405,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ86">
         <v>1.55</v>
@@ -19494,7 +19533,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -19781,7 +19820,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ88">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR88">
         <v>2.16</v>
@@ -20112,7 +20151,7 @@
         <v>164</v>
       </c>
       <c r="P90" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
@@ -20193,7 +20232,7 @@
         <v>2</v>
       </c>
       <c r="AQ90">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR90">
         <v>1.08</v>
@@ -20396,10 +20435,10 @@
         <v>1.5</v>
       </c>
       <c r="AP91">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ91">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR91">
         <v>1.64</v>
@@ -20602,7 +20641,7 @@
         <v>0.67</v>
       </c>
       <c r="AP92">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ92">
         <v>0.33</v>
@@ -20811,7 +20850,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ93">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR93">
         <v>1.68</v>
@@ -21014,7 +21053,7 @@
         <v>1.33</v>
       </c>
       <c r="AP94">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ94">
         <v>1.55</v>
@@ -21220,10 +21259,10 @@
         <v>0.5</v>
       </c>
       <c r="AP95">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ95">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR95">
         <v>1.75</v>
@@ -21348,7 +21387,7 @@
         <v>168</v>
       </c>
       <c r="P96" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21429,7 +21468,7 @@
         <v>2</v>
       </c>
       <c r="AQ96">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR96">
         <v>2.09</v>
@@ -21838,7 +21877,7 @@
         <v>1.5</v>
       </c>
       <c r="AP98">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ98">
         <v>1.22</v>
@@ -22044,7 +22083,7 @@
         <v>1.33</v>
       </c>
       <c r="AP99">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ99">
         <v>0.45</v>
@@ -22665,7 +22704,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ102">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR102">
         <v>2.01</v>
@@ -22790,7 +22829,7 @@
         <v>122</v>
       </c>
       <c r="P103" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="Q103">
         <v>2.75</v>
@@ -23077,7 +23116,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ104">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR104">
         <v>1.95</v>
@@ -23280,7 +23319,7 @@
         <v>0.25</v>
       </c>
       <c r="AP105">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ105">
         <v>1</v>
@@ -23486,7 +23525,7 @@
         <v>1.75</v>
       </c>
       <c r="AP106">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ106">
         <v>1.73</v>
@@ -23695,7 +23734,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ107">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR107">
         <v>1.66</v>
@@ -23898,10 +23937,10 @@
         <v>0.33</v>
       </c>
       <c r="AP108">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ108">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR108">
         <v>1.87</v>
@@ -24438,7 +24477,7 @@
         <v>109</v>
       </c>
       <c r="P111" t="s">
-        <v>352</v>
+        <v>312</v>
       </c>
       <c r="Q111">
         <v>2.88</v>
@@ -24931,7 +24970,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ113">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR113">
         <v>1.19</v>
@@ -25056,7 +25095,7 @@
         <v>177</v>
       </c>
       <c r="P114" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25262,7 +25301,7 @@
         <v>178</v>
       </c>
       <c r="P115" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -25340,10 +25379,10 @@
         <v>2</v>
       </c>
       <c r="AP115">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ115">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR115">
         <v>1.76</v>
@@ -25546,10 +25585,10 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ116">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR116">
         <v>1.62</v>
@@ -25674,7 +25713,7 @@
         <v>179</v>
       </c>
       <c r="P117" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25752,10 +25791,10 @@
         <v>1.5</v>
       </c>
       <c r="AP117">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ117">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR117">
         <v>1.48</v>
@@ -25880,7 +25919,7 @@
         <v>180</v>
       </c>
       <c r="P118" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -25958,7 +25997,7 @@
         <v>1.33</v>
       </c>
       <c r="AP118">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ118">
         <v>1.22</v>
@@ -26164,7 +26203,7 @@
         <v>3</v>
       </c>
       <c r="AP119">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ119">
         <v>2</v>
@@ -26292,7 +26331,7 @@
         <v>181</v>
       </c>
       <c r="P120" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -26373,7 +26412,7 @@
         <v>1</v>
       </c>
       <c r="AQ120">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR120">
         <v>1.84</v>
@@ -26576,7 +26615,7 @@
         <v>0.5</v>
       </c>
       <c r="AP121">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ121">
         <v>0.33</v>
@@ -26704,7 +26743,7 @@
         <v>109</v>
       </c>
       <c r="P122" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="Q122">
         <v>2.75</v>
@@ -26991,7 +27030,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ123">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR123">
         <v>1.96</v>
@@ -27116,7 +27155,7 @@
         <v>129</v>
       </c>
       <c r="P124" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="Q124">
         <v>2.5</v>
@@ -27197,7 +27236,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ124">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR124">
         <v>1.48</v>
@@ -27400,10 +27439,10 @@
         <v>0.5</v>
       </c>
       <c r="AP125">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ125">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR125">
         <v>1.84</v>
@@ -27815,7 +27854,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ127">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR127">
         <v>1.21</v>
@@ -28018,10 +28057,10 @@
         <v>1.5</v>
       </c>
       <c r="AP128">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ128">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR128">
         <v>1.53</v>
@@ -28146,7 +28185,7 @@
         <v>187</v>
       </c>
       <c r="P129" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28224,7 +28263,7 @@
         <v>1.5</v>
       </c>
       <c r="AP129">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ129">
         <v>1.83</v>
@@ -28352,7 +28391,7 @@
         <v>188</v>
       </c>
       <c r="P130" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="Q130">
         <v>2.4</v>
@@ -28636,10 +28675,10 @@
         <v>2</v>
       </c>
       <c r="AP131">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ131">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR131">
         <v>1.86</v>
@@ -28845,7 +28884,7 @@
         <v>1</v>
       </c>
       <c r="AQ132">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR132">
         <v>1.77</v>
@@ -29048,7 +29087,7 @@
         <v>0.4</v>
       </c>
       <c r="AP133">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ133">
         <v>1</v>
@@ -29176,7 +29215,7 @@
         <v>189</v>
       </c>
       <c r="P134" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="Q134">
         <v>3</v>
@@ -29382,7 +29421,7 @@
         <v>190</v>
       </c>
       <c r="P135" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -29666,7 +29705,7 @@
         <v>0.75</v>
       </c>
       <c r="AP136">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ136">
         <v>1</v>
@@ -29872,10 +29911,10 @@
         <v>0.4</v>
       </c>
       <c r="AP137">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ137">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR137">
         <v>1.09</v>
@@ -30078,10 +30117,10 @@
         <v>1</v>
       </c>
       <c r="AP138">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ138">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR138">
         <v>1.73</v>
@@ -30287,7 +30326,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ139">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR139">
         <v>1.51</v>
@@ -30490,10 +30529,10 @@
         <v>0.33</v>
       </c>
       <c r="AP140">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ140">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR140">
         <v>1.89</v>
@@ -30618,7 +30657,7 @@
         <v>109</v>
       </c>
       <c r="P141" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="Q141">
         <v>2.38</v>
@@ -30696,10 +30735,10 @@
         <v>1</v>
       </c>
       <c r="AP141">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ141">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR141">
         <v>1.68</v>
@@ -30905,7 +30944,7 @@
         <v>2</v>
       </c>
       <c r="AQ142">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR142">
         <v>1.65</v>
@@ -31030,7 +31069,7 @@
         <v>174</v>
       </c>
       <c r="P143" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -31442,7 +31481,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="Q145">
         <v>2.4</v>
@@ -31648,7 +31687,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31726,10 +31765,10 @@
         <v>0.8</v>
       </c>
       <c r="AP146">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ146">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR146">
         <v>1.83</v>
@@ -31854,7 +31893,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="Q147">
         <v>2.6</v>
@@ -31932,10 +31971,10 @@
         <v>2</v>
       </c>
       <c r="AP147">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ147">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR147">
         <v>1.85</v>
@@ -32060,7 +32099,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="Q148">
         <v>2.05</v>
@@ -32138,10 +32177,10 @@
         <v>1.8</v>
       </c>
       <c r="AP148">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ148">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR148">
         <v>1.55</v>
@@ -32266,7 +32305,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -32344,7 +32383,7 @@
         <v>1</v>
       </c>
       <c r="AP149">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ149">
         <v>0.45</v>
@@ -32472,7 +32511,7 @@
         <v>202</v>
       </c>
       <c r="P150" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="Q150">
         <v>2.4</v>
@@ -32550,7 +32589,7 @@
         <v>1.75</v>
       </c>
       <c r="AP150">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ150">
         <v>1.22</v>
@@ -32759,7 +32798,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ151">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR151">
         <v>1.66</v>
@@ -32884,7 +32923,7 @@
         <v>109</v>
       </c>
       <c r="P152" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="Q152">
         <v>2.88</v>
@@ -32962,10 +33001,10 @@
         <v>1.4</v>
       </c>
       <c r="AP152">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ152">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR152">
         <v>1.12</v>
@@ -33168,10 +33207,10 @@
         <v>0.5</v>
       </c>
       <c r="AP153">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ153">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR153">
         <v>1.52</v>
@@ -33296,7 +33335,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="Q154">
         <v>3.1</v>
@@ -33502,7 +33541,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="Q155">
         <v>2.2</v>
@@ -33914,7 +33953,7 @@
         <v>109</v>
       </c>
       <c r="P157" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="Q157">
         <v>3.2</v>
@@ -33992,7 +34031,7 @@
         <v>1.6</v>
       </c>
       <c r="AP157">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ157">
         <v>1.73</v>
@@ -34198,7 +34237,7 @@
         <v>1.2</v>
       </c>
       <c r="AP158">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ158">
         <v>1.55</v>
@@ -34407,7 +34446,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ159">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR159">
         <v>1.77</v>
@@ -34532,7 +34571,7 @@
         <v>209</v>
       </c>
       <c r="P160" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="Q160">
         <v>2.1</v>
@@ -34816,10 +34855,10 @@
         <v>0.75</v>
       </c>
       <c r="AP161">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ161">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR161">
         <v>1.68</v>
@@ -34944,7 +34983,7 @@
         <v>211</v>
       </c>
       <c r="P162" t="s">
-        <v>375</v>
+        <v>319</v>
       </c>
       <c r="Q162">
         <v>2.5</v>
@@ -35640,7 +35679,7 @@
         <v>0.4</v>
       </c>
       <c r="AP165">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ165">
         <v>0.33</v>
@@ -35846,10 +35885,10 @@
         <v>0.25</v>
       </c>
       <c r="AP166">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ166">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR166">
         <v>1.6</v>
@@ -35974,7 +36013,7 @@
         <v>215</v>
       </c>
       <c r="P167" t="s">
-        <v>376</v>
+        <v>311</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -36052,7 +36091,7 @@
         <v>2.5</v>
       </c>
       <c r="AP167">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ167">
         <v>2</v>
@@ -36258,10 +36297,10 @@
         <v>0.8</v>
       </c>
       <c r="AP168">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ168">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR168">
         <v>1.25</v>
@@ -36386,7 +36425,7 @@
         <v>217</v>
       </c>
       <c r="P169" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="Q169">
         <v>3</v>
@@ -36464,10 +36503,10 @@
         <v>2.5</v>
       </c>
       <c r="AP169">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ169">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR169">
         <v>1.68</v>
@@ -36592,7 +36631,7 @@
         <v>218</v>
       </c>
       <c r="P170" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36670,10 +36709,10 @@
         <v>1.67</v>
       </c>
       <c r="AP170">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ170">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR170">
         <v>1.89</v>
@@ -36798,7 +36837,7 @@
         <v>109</v>
       </c>
       <c r="P171" t="s">
-        <v>376</v>
+        <v>311</v>
       </c>
       <c r="Q171">
         <v>2.25</v>
@@ -36879,7 +36918,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ171">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR171">
         <v>1.87</v>
@@ -37004,7 +37043,7 @@
         <v>219</v>
       </c>
       <c r="P172" t="s">
-        <v>376</v>
+        <v>311</v>
       </c>
       <c r="Q172">
         <v>2.4</v>
@@ -37082,7 +37121,7 @@
         <v>1.2</v>
       </c>
       <c r="AP172">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ172">
         <v>1</v>
@@ -37416,7 +37455,7 @@
         <v>221</v>
       </c>
       <c r="P174" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="Q174">
         <v>2.5</v>
@@ -37622,7 +37661,7 @@
         <v>163</v>
       </c>
       <c r="P175" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -37703,7 +37742,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ175">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR175">
         <v>1.61</v>
@@ -37828,7 +37867,7 @@
         <v>113</v>
       </c>
       <c r="P176" t="s">
-        <v>376</v>
+        <v>311</v>
       </c>
       <c r="Q176">
         <v>2.4</v>
@@ -38034,7 +38073,7 @@
         <v>222</v>
       </c>
       <c r="P177" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -38115,7 +38154,7 @@
         <v>1</v>
       </c>
       <c r="AQ177">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR177">
         <v>1.66</v>
@@ -38240,7 +38279,7 @@
         <v>109</v>
       </c>
       <c r="P178" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="Q178">
         <v>2.38</v>
@@ -38318,10 +38357,10 @@
         <v>0.75</v>
       </c>
       <c r="AP178">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ178">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR178">
         <v>1.84</v>
@@ -38652,7 +38691,7 @@
         <v>224</v>
       </c>
       <c r="P180" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38939,7 +38978,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ181">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR181">
         <v>1.42</v>
@@ -39064,7 +39103,7 @@
         <v>225</v>
       </c>
       <c r="P182" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="Q182">
         <v>3.75</v>
@@ -39145,7 +39184,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ182">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR182">
         <v>1.89</v>
@@ -39270,7 +39309,7 @@
         <v>226</v>
       </c>
       <c r="P183" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="Q183">
         <v>2.5</v>
@@ -39348,7 +39387,7 @@
         <v>0.67</v>
       </c>
       <c r="AP183">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ183">
         <v>0.58</v>
@@ -39476,7 +39515,7 @@
         <v>227</v>
       </c>
       <c r="P184" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="Q184">
         <v>2.05</v>
@@ -39554,7 +39593,7 @@
         <v>0.29</v>
       </c>
       <c r="AP184">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ184">
         <v>0.33</v>
@@ -39760,7 +39799,7 @@
         <v>1.5</v>
       </c>
       <c r="AP185">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ185">
         <v>1.83</v>
@@ -39888,7 +39927,7 @@
         <v>228</v>
       </c>
       <c r="P186" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="Q186">
         <v>2.4</v>
@@ -39969,7 +40008,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ186">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR186">
         <v>1.92</v>
@@ -40300,7 +40339,7 @@
         <v>230</v>
       </c>
       <c r="P188" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40506,7 +40545,7 @@
         <v>176</v>
       </c>
       <c r="P189" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40584,10 +40623,10 @@
         <v>0.2</v>
       </c>
       <c r="AP189">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ189">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR189">
         <v>1.57</v>
@@ -40790,7 +40829,7 @@
         <v>1.67</v>
       </c>
       <c r="AP190">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ190">
         <v>1.22</v>
@@ -40996,10 +41035,10 @@
         <v>1.14</v>
       </c>
       <c r="AP191">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ191">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR191">
         <v>1.76</v>
@@ -41330,7 +41369,7 @@
         <v>233</v>
       </c>
       <c r="P193" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41536,7 +41575,7 @@
         <v>234</v>
       </c>
       <c r="P194" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41823,7 +41862,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ195">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR195">
         <v>1.77</v>
@@ -41948,7 +41987,7 @@
         <v>198</v>
       </c>
       <c r="P196" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="Q196">
         <v>2.63</v>
@@ -42360,7 +42399,7 @@
         <v>103</v>
       </c>
       <c r="P198" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="Q198">
         <v>2.63</v>
@@ -42438,7 +42477,7 @@
         <v>1.5</v>
       </c>
       <c r="AP198">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ198">
         <v>1.64</v>
@@ -42647,7 +42686,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ199">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR199">
         <v>1.32</v>
@@ -42850,7 +42889,7 @@
         <v>0.83</v>
       </c>
       <c r="AP200">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ200">
         <v>0.45</v>
@@ -43059,7 +43098,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ201">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR201">
         <v>1.89</v>
@@ -43262,10 +43301,10 @@
         <v>2.2</v>
       </c>
       <c r="AP202">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ202">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR202">
         <v>1.61</v>
@@ -43390,7 +43429,7 @@
         <v>109</v>
       </c>
       <c r="P203" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="Q203">
         <v>2.63</v>
@@ -43471,7 +43510,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ203">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR203">
         <v>1.04</v>
@@ -43674,7 +43713,7 @@
         <v>1</v>
       </c>
       <c r="AP204">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ204">
         <v>0.82</v>
@@ -43802,7 +43841,7 @@
         <v>237</v>
       </c>
       <c r="P205" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -43883,7 +43922,7 @@
         <v>2</v>
       </c>
       <c r="AQ205">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR205">
         <v>1.3</v>
@@ -44214,7 +44253,7 @@
         <v>109</v>
       </c>
       <c r="P207" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="Q207">
         <v>2.25</v>
@@ -44292,7 +44331,7 @@
         <v>1.17</v>
       </c>
       <c r="AP207">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ207">
         <v>1.55</v>
@@ -44498,7 +44537,7 @@
         <v>0.83</v>
       </c>
       <c r="AP208">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ208">
         <v>0.88</v>
@@ -44707,7 +44746,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ209">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR209">
         <v>2.06</v>
@@ -45038,7 +45077,7 @@
         <v>240</v>
       </c>
       <c r="P211" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="Q211">
         <v>3.2</v>
@@ -45116,10 +45155,10 @@
         <v>2</v>
       </c>
       <c r="AP211">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ211">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR211">
         <v>1.68</v>
@@ -45244,7 +45283,7 @@
         <v>109</v>
       </c>
       <c r="P212" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45325,7 +45364,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ212">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR212">
         <v>1.33</v>
@@ -45450,7 +45489,7 @@
         <v>241</v>
       </c>
       <c r="P213" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="Q213">
         <v>4</v>
@@ -45734,7 +45773,7 @@
         <v>1.57</v>
       </c>
       <c r="AP214">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ214">
         <v>1.22</v>
@@ -45862,7 +45901,7 @@
         <v>242</v>
       </c>
       <c r="P215" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -45940,7 +45979,7 @@
         <v>1.83</v>
       </c>
       <c r="AP215">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ215">
         <v>2</v>
@@ -46068,7 +46107,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="Q216">
         <v>3.4</v>
@@ -46146,10 +46185,10 @@
         <v>0.8</v>
       </c>
       <c r="AP216">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ216">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR216">
         <v>1.44</v>
@@ -46274,7 +46313,7 @@
         <v>243</v>
       </c>
       <c r="P217" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="Q217">
         <v>2.75</v>
@@ -46352,10 +46391,10 @@
         <v>1.57</v>
       </c>
       <c r="AP217">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ217">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR217">
         <v>1.58</v>
@@ -46558,7 +46597,7 @@
         <v>1</v>
       </c>
       <c r="AP218">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ218">
         <v>1</v>
@@ -46686,7 +46725,7 @@
         <v>244</v>
       </c>
       <c r="P219" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="Q219">
         <v>3.1</v>
@@ -46764,10 +46803,10 @@
         <v>2</v>
       </c>
       <c r="AP219">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ219">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR219">
         <v>1.44</v>
@@ -46970,7 +47009,7 @@
         <v>0.71</v>
       </c>
       <c r="AP220">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ220">
         <v>0.45</v>
@@ -47098,7 +47137,7 @@
         <v>246</v>
       </c>
       <c r="P221" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="Q221">
         <v>2.6</v>
@@ -47179,7 +47218,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ221">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR221">
         <v>2.04</v>
@@ -47304,7 +47343,7 @@
         <v>247</v>
       </c>
       <c r="P222" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="Q222">
         <v>2.5</v>
@@ -47510,7 +47549,7 @@
         <v>248</v>
       </c>
       <c r="P223" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47716,7 +47755,7 @@
         <v>249</v>
       </c>
       <c r="P224" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47922,7 +47961,7 @@
         <v>250</v>
       </c>
       <c r="P225" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -48000,10 +48039,10 @@
         <v>1.5</v>
       </c>
       <c r="AP225">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ225">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR225">
         <v>1.88</v>
@@ -48128,7 +48167,7 @@
         <v>251</v>
       </c>
       <c r="P226" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="Q226">
         <v>2.75</v>
@@ -48209,7 +48248,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ226">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR226">
         <v>1.23</v>
@@ -48334,7 +48373,7 @@
         <v>252</v>
       </c>
       <c r="P227" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="Q227">
         <v>1.83</v>
@@ -48412,10 +48451,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP227">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ227">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR227">
         <v>1.5</v>
@@ -48540,7 +48579,7 @@
         <v>253</v>
       </c>
       <c r="P228" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48746,7 +48785,7 @@
         <v>109</v>
       </c>
       <c r="P229" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="Q229">
         <v>2.5</v>
@@ -48827,7 +48866,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ229">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR229">
         <v>1.83</v>
@@ -48952,7 +48991,7 @@
         <v>254</v>
       </c>
       <c r="P230" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="Q230">
         <v>3.25</v>
@@ -49030,7 +49069,7 @@
         <v>2</v>
       </c>
       <c r="AP230">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ230">
         <v>1.73</v>
@@ -49158,7 +49197,7 @@
         <v>119</v>
       </c>
       <c r="P231" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="Q231">
         <v>2.4</v>
@@ -49239,7 +49278,7 @@
         <v>2</v>
       </c>
       <c r="AQ231">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR231">
         <v>1.85</v>
@@ -49445,7 +49484,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ232">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR232">
         <v>1.98</v>
@@ -49648,7 +49687,7 @@
         <v>0.88</v>
       </c>
       <c r="AP233">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ233">
         <v>0.82</v>
@@ -49776,7 +49815,7 @@
         <v>109</v>
       </c>
       <c r="P234" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="Q234">
         <v>2.5</v>
@@ -49854,10 +49893,10 @@
         <v>1.17</v>
       </c>
       <c r="AP234">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ234">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR234">
         <v>1.45</v>
@@ -50394,7 +50433,7 @@
         <v>258</v>
       </c>
       <c r="P237" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="Q237">
         <v>2.75</v>
@@ -50475,7 +50514,7 @@
         <v>1</v>
       </c>
       <c r="AQ237">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR237">
         <v>1.68</v>
@@ -50600,7 +50639,7 @@
         <v>259</v>
       </c>
       <c r="P238" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="Q238">
         <v>2.6</v>
@@ -50681,7 +50720,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ238">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR238">
         <v>1.87</v>
@@ -50806,7 +50845,7 @@
         <v>109</v>
       </c>
       <c r="P239" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -50884,7 +50923,7 @@
         <v>0.5</v>
       </c>
       <c r="AP239">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ239">
         <v>0.58</v>
@@ -51012,7 +51051,7 @@
         <v>140</v>
       </c>
       <c r="P240" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -51090,10 +51129,10 @@
         <v>0.71</v>
       </c>
       <c r="AP240">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ240">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR240">
         <v>1.88</v>
@@ -51296,10 +51335,10 @@
         <v>1.71</v>
       </c>
       <c r="AP241">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ241">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR241">
         <v>1.5</v>
@@ -51424,7 +51463,7 @@
         <v>109</v>
       </c>
       <c r="P242" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="Q242">
         <v>3.1</v>
@@ -51505,7 +51544,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ242">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR242">
         <v>1.55</v>
@@ -51711,7 +51750,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ243">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR243">
         <v>1.63</v>
@@ -51836,7 +51875,7 @@
         <v>161</v>
       </c>
       <c r="P244" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="Q244">
         <v>2.1</v>
@@ -51914,7 +51953,7 @@
         <v>1.5</v>
       </c>
       <c r="AP244">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ244">
         <v>1.64</v>
@@ -52248,7 +52287,7 @@
         <v>156</v>
       </c>
       <c r="P246" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="Q246">
         <v>2.5</v>
@@ -52532,7 +52571,7 @@
         <v>0.89</v>
       </c>
       <c r="AP247">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ247">
         <v>0.82</v>
@@ -52866,7 +52905,7 @@
         <v>264</v>
       </c>
       <c r="P249" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="Q249">
         <v>2.5</v>
@@ -53072,7 +53111,7 @@
         <v>265</v>
       </c>
       <c r="P250" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="Q250">
         <v>3.2</v>
@@ -53278,7 +53317,7 @@
         <v>109</v>
       </c>
       <c r="P251" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="Q251">
         <v>2.75</v>
@@ -53356,7 +53395,7 @@
         <v>0.88</v>
       </c>
       <c r="AP251">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ251">
         <v>1</v>
@@ -53484,7 +53523,7 @@
         <v>266</v>
       </c>
       <c r="P252" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="Q252">
         <v>2.25</v>
@@ -53771,7 +53810,7 @@
         <v>2</v>
       </c>
       <c r="AQ253">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR253">
         <v>1.96</v>
@@ -53974,7 +54013,7 @@
         <v>0.89</v>
       </c>
       <c r="AP254">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ254">
         <v>1</v>
@@ -54183,7 +54222,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ255">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR255">
         <v>1.83</v>
@@ -54308,7 +54347,7 @@
         <v>270</v>
       </c>
       <c r="P256" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="Q256">
         <v>2.25</v>
@@ -54389,7 +54428,7 @@
         <v>2</v>
       </c>
       <c r="AQ256">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR256">
         <v>1.24</v>
@@ -54514,7 +54553,7 @@
         <v>271</v>
       </c>
       <c r="P257" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="Q257">
         <v>2.63</v>
@@ -54720,7 +54759,7 @@
         <v>272</v>
       </c>
       <c r="P258" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="Q258">
         <v>2.3</v>
@@ -54801,7 +54840,7 @@
         <v>2</v>
       </c>
       <c r="AQ258">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR258">
         <v>1.85</v>
@@ -54926,7 +54965,7 @@
         <v>109</v>
       </c>
       <c r="P259" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="Q259">
         <v>3.1</v>
@@ -55210,7 +55249,7 @@
         <v>0.78</v>
       </c>
       <c r="AP260">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ260">
         <v>0.58</v>
@@ -55338,7 +55377,7 @@
         <v>274</v>
       </c>
       <c r="P261" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -55416,10 +55455,10 @@
         <v>1.29</v>
       </c>
       <c r="AP261">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ261">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR261">
         <v>1.82</v>
@@ -55544,7 +55583,7 @@
         <v>275</v>
       </c>
       <c r="P262" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="Q262">
         <v>2.5</v>
@@ -55622,10 +55661,10 @@
         <v>1.44</v>
       </c>
       <c r="AP262">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ262">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR262">
         <v>1.61</v>
@@ -55750,7 +55789,7 @@
         <v>234</v>
       </c>
       <c r="P263" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="Q263">
         <v>2.25</v>
@@ -55831,7 +55870,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ263">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR263">
         <v>1.72</v>
@@ -55956,7 +55995,7 @@
         <v>109</v>
       </c>
       <c r="P264" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="Q264">
         <v>2.75</v>
@@ -56034,10 +56073,10 @@
         <v>1.43</v>
       </c>
       <c r="AP264">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ264">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR264">
         <v>1.64</v>
@@ -56162,7 +56201,7 @@
         <v>276</v>
       </c>
       <c r="P265" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="Q265">
         <v>2.88</v>
@@ -56240,10 +56279,10 @@
         <v>0.63</v>
       </c>
       <c r="AP265">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ265">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR265">
         <v>1.67</v>
@@ -56368,7 +56407,7 @@
         <v>109</v>
       </c>
       <c r="P266" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="Q266">
         <v>3.4</v>
@@ -56446,7 +56485,7 @@
         <v>1.25</v>
       </c>
       <c r="AP266">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ266">
         <v>1.55</v>
@@ -56652,10 +56691,10 @@
         <v>1</v>
       </c>
       <c r="AP267">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ267">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR267">
         <v>1.45</v>
@@ -56780,7 +56819,7 @@
         <v>278</v>
       </c>
       <c r="P268" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="Q268">
         <v>2.2</v>
@@ -56861,7 +56900,7 @@
         <v>2</v>
       </c>
       <c r="AQ268">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR268">
         <v>1.84</v>
@@ -56986,7 +57025,7 @@
         <v>279</v>
       </c>
       <c r="P269" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57192,7 +57231,7 @@
         <v>280</v>
       </c>
       <c r="P270" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="Q270">
         <v>3.35</v>
@@ -57273,7 +57312,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ270">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR270">
         <v>1.36</v>
@@ -57476,10 +57515,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP271">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ271">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR271">
         <v>1.42</v>
@@ -57604,7 +57643,7 @@
         <v>282</v>
       </c>
       <c r="P272" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="Q272">
         <v>2.38</v>
@@ -57682,10 +57721,10 @@
         <v>1.25</v>
       </c>
       <c r="AP272">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ272">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR272">
         <v>1.82</v>
@@ -57810,7 +57849,7 @@
         <v>283</v>
       </c>
       <c r="P273" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="Q273">
         <v>3.4</v>
@@ -58016,7 +58055,7 @@
         <v>284</v>
       </c>
       <c r="P274" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="Q274">
         <v>3</v>
@@ -58094,7 +58133,7 @@
         <v>0.7</v>
       </c>
       <c r="AP274">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ274">
         <v>0.58</v>
@@ -58300,7 +58339,7 @@
         <v>2</v>
       </c>
       <c r="AP275">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ275">
         <v>1.73</v>
@@ -58428,7 +58467,7 @@
         <v>285</v>
       </c>
       <c r="P276" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="Q276">
         <v>2.63</v>
@@ -58509,7 +58548,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ276">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR276">
         <v>1.17</v>
@@ -58634,7 +58673,7 @@
         <v>286</v>
       </c>
       <c r="P277" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -58715,7 +58754,7 @@
         <v>2</v>
       </c>
       <c r="AQ277">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR277">
         <v>1.94</v>
@@ -58918,7 +58957,7 @@
         <v>0.3</v>
       </c>
       <c r="AP278">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ278">
         <v>0.33</v>
@@ -59046,7 +59085,7 @@
         <v>288</v>
       </c>
       <c r="P279" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="Q279">
         <v>2.63</v>
@@ -59124,7 +59163,7 @@
         <v>1.73</v>
       </c>
       <c r="AP279">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ279">
         <v>1.83</v>
@@ -59330,7 +59369,7 @@
         <v>1.38</v>
       </c>
       <c r="AP280">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AQ280">
         <v>1.22</v>
@@ -59458,7 +59497,7 @@
         <v>290</v>
       </c>
       <c r="P281" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="Q281">
         <v>2.25</v>
@@ -59664,7 +59703,7 @@
         <v>291</v>
       </c>
       <c r="P282" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="Q282">
         <v>2.88</v>
@@ -59951,7 +59990,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ283">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR283">
         <v>1.54</v>
@@ -60157,7 +60196,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ284">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AR284">
         <v>1.23</v>
@@ -60282,7 +60321,7 @@
         <v>293</v>
       </c>
       <c r="P285" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="Q285">
         <v>2.5</v>
@@ -60360,7 +60399,7 @@
         <v>0.64</v>
       </c>
       <c r="AP285">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ285">
         <v>0.58</v>
@@ -60488,7 +60527,7 @@
         <v>294</v>
       </c>
       <c r="P286" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -60569,7 +60608,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ286">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR286">
         <v>1.24</v>
@@ -60978,7 +61017,7 @@
         <v>0.8</v>
       </c>
       <c r="AP288">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ288">
         <v>0.82</v>
@@ -61802,10 +61841,10 @@
         <v>1.88</v>
       </c>
       <c r="AP292">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ292">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR292">
         <v>1.84</v>
@@ -62136,7 +62175,7 @@
         <v>112</v>
       </c>
       <c r="P294" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="Q294">
         <v>3.1</v>
@@ -62342,7 +62381,7 @@
         <v>122</v>
       </c>
       <c r="P295" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="Q295">
         <v>2.4</v>
@@ -62420,7 +62459,7 @@
         <v>0.8</v>
       </c>
       <c r="AP295">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ295">
         <v>1</v>
@@ -62626,10 +62665,10 @@
         <v>2</v>
       </c>
       <c r="AP296">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ296">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AR296">
         <v>1.45</v>
@@ -62754,7 +62793,7 @@
         <v>301</v>
       </c>
       <c r="P297" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="Q297">
         <v>3.4</v>
@@ -62832,7 +62871,7 @@
         <v>1.6</v>
       </c>
       <c r="AP297">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ297">
         <v>1.55</v>
@@ -63041,7 +63080,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ298">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AR298">
         <v>1.23</v>
@@ -63166,7 +63205,7 @@
         <v>302</v>
       </c>
       <c r="P299" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="Q299">
         <v>3.2</v>
@@ -63450,7 +63489,7 @@
         <v>1.8</v>
       </c>
       <c r="AP300">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AQ300">
         <v>1.64</v>
@@ -63784,7 +63823,7 @@
         <v>305</v>
       </c>
       <c r="P302" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="Q302">
         <v>2.2</v>
@@ -63862,7 +63901,7 @@
         <v>0.5</v>
       </c>
       <c r="AP302">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ302">
         <v>0.45</v>
@@ -63948,7 +63987,7 @@
         <v>302</v>
       </c>
       <c r="B303">
-        <v>7781382</v>
+        <v>7781384</v>
       </c>
       <c r="C303" t="s">
         <v>68</v>
@@ -63963,55 +64002,55 @@
         <v>0</v>
       </c>
       <c r="G303" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H303" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I303">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J303">
         <v>1</v>
       </c>
       <c r="K303">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L303">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M303">
         <v>1</v>
       </c>
       <c r="N303">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O303" t="s">
-        <v>306</v>
+        <v>255</v>
       </c>
       <c r="P303" t="s">
-        <v>448</v>
+        <v>413</v>
       </c>
       <c r="Q303">
         <v>2.5</v>
       </c>
       <c r="R303">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S303">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="T303">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="U303">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="V303">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="W303">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="X303">
         <v>5.5</v>
@@ -64020,133 +64059,133 @@
         <v>1.14</v>
       </c>
       <c r="Z303">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AA303">
-        <v>3.56</v>
+        <v>3.67</v>
       </c>
       <c r="AB303">
-        <v>3.28</v>
+        <v>3.13</v>
       </c>
       <c r="AC303">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AD303">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AE303">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF303">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AG303">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AH303">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="AI303">
+        <v>1.5</v>
+      </c>
+      <c r="AJ303">
+        <v>2.5</v>
+      </c>
+      <c r="AK303">
+        <v>1.32</v>
+      </c>
+      <c r="AL303">
+        <v>1.24</v>
+      </c>
+      <c r="AM303">
+        <v>1.78</v>
+      </c>
+      <c r="AN303">
+        <v>1.3</v>
+      </c>
+      <c r="AO303">
+        <v>0.6</v>
+      </c>
+      <c r="AP303">
+        <v>1.27</v>
+      </c>
+      <c r="AQ303">
+        <v>0.58</v>
+      </c>
+      <c r="AR303">
+        <v>1.96</v>
+      </c>
+      <c r="AS303">
+        <v>1.15</v>
+      </c>
+      <c r="AT303">
+        <v>3.11</v>
+      </c>
+      <c r="AU303">
+        <v>5</v>
+      </c>
+      <c r="AV303">
+        <v>6</v>
+      </c>
+      <c r="AW303">
+        <v>13</v>
+      </c>
+      <c r="AX303">
+        <v>7</v>
+      </c>
+      <c r="AY303">
+        <v>18</v>
+      </c>
+      <c r="AZ303">
+        <v>13</v>
+      </c>
+      <c r="BA303">
+        <v>9</v>
+      </c>
+      <c r="BB303">
+        <v>7</v>
+      </c>
+      <c r="BC303">
+        <v>16</v>
+      </c>
+      <c r="BD303">
+        <v>1.79</v>
+      </c>
+      <c r="BE303">
+        <v>6.4</v>
+      </c>
+      <c r="BF303">
+        <v>2.23</v>
+      </c>
+      <c r="BG303">
+        <v>1.27</v>
+      </c>
+      <c r="BH303">
+        <v>3.3</v>
+      </c>
+      <c r="BI303">
+        <v>1.48</v>
+      </c>
+      <c r="BJ303">
+        <v>2.43</v>
+      </c>
+      <c r="BK303">
+        <v>1.77</v>
+      </c>
+      <c r="BL303">
+        <v>1.92</v>
+      </c>
+      <c r="BM303">
+        <v>2.23</v>
+      </c>
+      <c r="BN303">
         <v>1.57</v>
-      </c>
-      <c r="AJ303">
-        <v>2.25</v>
-      </c>
-      <c r="AK303">
-        <v>1.3</v>
-      </c>
-      <c r="AL303">
-        <v>1.25</v>
-      </c>
-      <c r="AM303">
-        <v>1.82</v>
-      </c>
-      <c r="AN303">
-        <v>1.9</v>
-      </c>
-      <c r="AO303">
-        <v>1.6</v>
-      </c>
-      <c r="AP303">
-        <v>2</v>
-      </c>
-      <c r="AQ303">
-        <v>1.45</v>
-      </c>
-      <c r="AR303">
-        <v>1.33</v>
-      </c>
-      <c r="AS303">
-        <v>1.44</v>
-      </c>
-      <c r="AT303">
-        <v>2.77</v>
-      </c>
-      <c r="AU303">
-        <v>6</v>
-      </c>
-      <c r="AV303">
-        <v>5</v>
-      </c>
-      <c r="AW303">
-        <v>9</v>
-      </c>
-      <c r="AX303">
-        <v>11</v>
-      </c>
-      <c r="AY303">
-        <v>15</v>
-      </c>
-      <c r="AZ303">
-        <v>16</v>
-      </c>
-      <c r="BA303">
-        <v>5</v>
-      </c>
-      <c r="BB303">
-        <v>8</v>
-      </c>
-      <c r="BC303">
-        <v>13</v>
-      </c>
-      <c r="BD303">
-        <v>1.76</v>
-      </c>
-      <c r="BE303">
-        <v>6.5</v>
-      </c>
-      <c r="BF303">
-        <v>2.25</v>
-      </c>
-      <c r="BG303">
-        <v>1.26</v>
-      </c>
-      <c r="BH303">
-        <v>3.4</v>
-      </c>
-      <c r="BI303">
-        <v>1.47</v>
-      </c>
-      <c r="BJ303">
-        <v>2.48</v>
-      </c>
-      <c r="BK303">
-        <v>1.76</v>
-      </c>
-      <c r="BL303">
-        <v>1.93</v>
-      </c>
-      <c r="BM303">
-        <v>2.18</v>
-      </c>
-      <c r="BN303">
-        <v>1.58</v>
       </c>
       <c r="BO303">
         <v>2.8</v>
       </c>
       <c r="BP303">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="304" spans="1:68">
@@ -64154,7 +64193,7 @@
         <v>303</v>
       </c>
       <c r="B304">
-        <v>7781383</v>
+        <v>7781382</v>
       </c>
       <c r="C304" t="s">
         <v>68</v>
@@ -64169,190 +64208,190 @@
         <v>0</v>
       </c>
       <c r="G304" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H304" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I304">
         <v>1</v>
       </c>
       <c r="J304">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K304">
+        <v>2</v>
+      </c>
+      <c r="L304">
+        <v>2</v>
+      </c>
+      <c r="M304">
+        <v>1</v>
+      </c>
+      <c r="N304">
         <v>3</v>
       </c>
-      <c r="L304">
-        <v>3</v>
-      </c>
-      <c r="M304">
+      <c r="O304" t="s">
+        <v>306</v>
+      </c>
+      <c r="P304" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q304">
+        <v>2.5</v>
+      </c>
+      <c r="R304">
+        <v>2.38</v>
+      </c>
+      <c r="S304">
         <v>4</v>
       </c>
-      <c r="N304">
-        <v>7</v>
-      </c>
-      <c r="O304" t="s">
-        <v>307</v>
-      </c>
-      <c r="P304" t="s">
-        <v>449</v>
-      </c>
-      <c r="Q304">
-        <v>0</v>
-      </c>
-      <c r="R304">
-        <v>0</v>
-      </c>
-      <c r="S304">
-        <v>0</v>
-      </c>
       <c r="T304">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="U304">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V304">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="W304">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X304">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Y304">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z304">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AA304">
-        <v>3.68</v>
+        <v>3.56</v>
       </c>
       <c r="AB304">
-        <v>3.98</v>
+        <v>3.28</v>
       </c>
       <c r="AC304">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AD304">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE304">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF304">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AG304">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AH304">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="AI304">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ304">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AK304">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL304">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AM304">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AN304">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AO304">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="AP304">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ304">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AR304">
-        <v>1.82</v>
+        <v>1.33</v>
       </c>
       <c r="AS304">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AT304">
-        <v>2.96</v>
+        <v>2.77</v>
       </c>
       <c r="AU304">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV304">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW304">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AX304">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AY304">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AZ304">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="BA304">
         <v>5</v>
       </c>
       <c r="BB304">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BC304">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BD304">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BE304">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BF304">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BG304">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BH304">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BI304">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BJ304">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BK304">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BL304">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BM304">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BN304">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BO304">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BP304">
-        <v>0</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="305" spans="1:68">
@@ -64360,7 +64399,7 @@
         <v>304</v>
       </c>
       <c r="B305">
-        <v>7781384</v>
+        <v>7781383</v>
       </c>
       <c r="C305" t="s">
         <v>68</v>
@@ -64375,190 +64414,190 @@
         <v>0</v>
       </c>
       <c r="G305" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H305" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="I305">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J305">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K305">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L305">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M305">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N305">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O305" t="s">
-        <v>255</v>
+        <v>307</v>
       </c>
       <c r="P305" t="s">
-        <v>404</v>
+        <v>458</v>
       </c>
       <c r="Q305">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R305">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S305">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T305">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U305">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V305">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="W305">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="X305">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Y305">
+        <v>0</v>
+      </c>
+      <c r="Z305">
+        <v>1.67</v>
+      </c>
+      <c r="AA305">
+        <v>3.68</v>
+      </c>
+      <c r="AB305">
+        <v>3.98</v>
+      </c>
+      <c r="AC305">
+        <v>0</v>
+      </c>
+      <c r="AD305">
+        <v>0</v>
+      </c>
+      <c r="AE305">
+        <v>0</v>
+      </c>
+      <c r="AF305">
+        <v>0</v>
+      </c>
+      <c r="AG305">
+        <v>1.53</v>
+      </c>
+      <c r="AH305">
+        <v>2.33</v>
+      </c>
+      <c r="AI305">
+        <v>0</v>
+      </c>
+      <c r="AJ305">
+        <v>0</v>
+      </c>
+      <c r="AK305">
+        <v>0</v>
+      </c>
+      <c r="AL305">
+        <v>0</v>
+      </c>
+      <c r="AM305">
+        <v>0</v>
+      </c>
+      <c r="AN305">
+        <v>2.1</v>
+      </c>
+      <c r="AO305">
+        <v>1.11</v>
+      </c>
+      <c r="AP305">
+        <v>1.91</v>
+      </c>
+      <c r="AQ305">
+        <v>1.18</v>
+      </c>
+      <c r="AR305">
+        <v>1.82</v>
+      </c>
+      <c r="AS305">
         <v>1.14</v>
       </c>
-      <c r="Z305">
-        <v>1.89</v>
-      </c>
-      <c r="AA305">
-        <v>3.67</v>
-      </c>
-      <c r="AB305">
-        <v>3.13</v>
-      </c>
-      <c r="AC305">
-        <v>1.01</v>
-      </c>
-      <c r="AD305">
-        <v>17</v>
-      </c>
-      <c r="AE305">
-        <v>1.18</v>
-      </c>
-      <c r="AF305">
-        <v>4.75</v>
-      </c>
-      <c r="AG305">
-        <v>1.67</v>
-      </c>
-      <c r="AH305">
-        <v>2.1</v>
-      </c>
-      <c r="AI305">
-        <v>1.5</v>
-      </c>
-      <c r="AJ305">
-        <v>2.5</v>
-      </c>
-      <c r="AK305">
-        <v>1.32</v>
-      </c>
-      <c r="AL305">
-        <v>1.24</v>
-      </c>
-      <c r="AM305">
-        <v>1.78</v>
-      </c>
-      <c r="AN305">
-        <v>1.3</v>
-      </c>
-      <c r="AO305">
-        <v>0.6</v>
-      </c>
-      <c r="AP305">
-        <v>1.27</v>
-      </c>
-      <c r="AQ305">
-        <v>0.64</v>
-      </c>
-      <c r="AR305">
-        <v>1.96</v>
-      </c>
-      <c r="AS305">
-        <v>1.15</v>
-      </c>
       <c r="AT305">
-        <v>3.11</v>
+        <v>2.96</v>
       </c>
       <c r="AU305">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AV305">
         <v>6</v>
       </c>
       <c r="AW305">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AX305">
+        <v>1</v>
+      </c>
+      <c r="AY305">
+        <v>12</v>
+      </c>
+      <c r="AZ305">
         <v>7</v>
       </c>
-      <c r="AY305">
-        <v>18</v>
-      </c>
-      <c r="AZ305">
-        <v>13</v>
-      </c>
       <c r="BA305">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BB305">
+        <v>2</v>
+      </c>
+      <c r="BC305">
         <v>7</v>
       </c>
-      <c r="BC305">
-        <v>16</v>
-      </c>
       <c r="BD305">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BE305">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BF305">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BG305">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BH305">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BI305">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="BJ305">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BK305">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BL305">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BM305">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BN305">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BO305">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BP305">
-        <v>1.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="306" spans="1:68">
@@ -64689,7 +64728,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ306">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR306">
         <v>1.96</v>
@@ -64814,7 +64853,7 @@
         <v>199</v>
       </c>
       <c r="P307" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="Q307">
         <v>3.26</v>
@@ -65098,7 +65137,7 @@
         <v>1</v>
       </c>
       <c r="AP308">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ308">
         <v>0.9</v>
@@ -65177,6 +65216,2890 @@
       </c>
       <c r="BP308">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="309" spans="1:68">
+      <c r="A309" s="1">
+        <v>308</v>
+      </c>
+      <c r="B309">
+        <v>7781391</v>
+      </c>
+      <c r="C309" t="s">
+        <v>68</v>
+      </c>
+      <c r="D309" t="s">
+        <v>69</v>
+      </c>
+      <c r="E309" s="2">
+        <v>45850.85416666666</v>
+      </c>
+      <c r="F309">
+        <v>0</v>
+      </c>
+      <c r="G309" t="s">
+        <v>89</v>
+      </c>
+      <c r="H309" t="s">
+        <v>88</v>
+      </c>
+      <c r="I309">
+        <v>2</v>
+      </c>
+      <c r="J309">
+        <v>0</v>
+      </c>
+      <c r="K309">
+        <v>2</v>
+      </c>
+      <c r="L309">
+        <v>2</v>
+      </c>
+      <c r="M309">
+        <v>0</v>
+      </c>
+      <c r="N309">
+        <v>2</v>
+      </c>
+      <c r="O309" t="s">
+        <v>310</v>
+      </c>
+      <c r="P309" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q309">
+        <v>2.41</v>
+      </c>
+      <c r="R309">
+        <v>2.21</v>
+      </c>
+      <c r="S309">
+        <v>4.45</v>
+      </c>
+      <c r="T309">
+        <v>1.33</v>
+      </c>
+      <c r="U309">
+        <v>2.93</v>
+      </c>
+      <c r="V309">
+        <v>2.51</v>
+      </c>
+      <c r="W309">
+        <v>1.44</v>
+      </c>
+      <c r="X309">
+        <v>5.75</v>
+      </c>
+      <c r="Y309">
+        <v>1.07</v>
+      </c>
+      <c r="Z309">
+        <v>1.78</v>
+      </c>
+      <c r="AA309">
+        <v>3.45</v>
+      </c>
+      <c r="AB309">
+        <v>3.73</v>
+      </c>
+      <c r="AC309">
+        <v>1</v>
+      </c>
+      <c r="AD309">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE309">
+        <v>1.22</v>
+      </c>
+      <c r="AF309">
+        <v>3.64</v>
+      </c>
+      <c r="AG309">
+        <v>1.76</v>
+      </c>
+      <c r="AH309">
+        <v>1.94</v>
+      </c>
+      <c r="AI309">
+        <v>1.69</v>
+      </c>
+      <c r="AJ309">
+        <v>2.04</v>
+      </c>
+      <c r="AK309">
+        <v>1.25</v>
+      </c>
+      <c r="AL309">
+        <v>1.28</v>
+      </c>
+      <c r="AM309">
+        <v>1.91</v>
+      </c>
+      <c r="AN309">
+        <v>2.1</v>
+      </c>
+      <c r="AO309">
+        <v>0.64</v>
+      </c>
+      <c r="AP309">
+        <v>2.18</v>
+      </c>
+      <c r="AQ309">
+        <v>0.58</v>
+      </c>
+      <c r="AR309">
+        <v>1.89</v>
+      </c>
+      <c r="AS309">
+        <v>1.2</v>
+      </c>
+      <c r="AT309">
+        <v>3.09</v>
+      </c>
+      <c r="AU309">
+        <v>5</v>
+      </c>
+      <c r="AV309">
+        <v>2</v>
+      </c>
+      <c r="AW309">
+        <v>14</v>
+      </c>
+      <c r="AX309">
+        <v>7</v>
+      </c>
+      <c r="AY309">
+        <v>19</v>
+      </c>
+      <c r="AZ309">
+        <v>9</v>
+      </c>
+      <c r="BA309">
+        <v>8</v>
+      </c>
+      <c r="BB309">
+        <v>5</v>
+      </c>
+      <c r="BC309">
+        <v>13</v>
+      </c>
+      <c r="BD309">
+        <v>1.5</v>
+      </c>
+      <c r="BE309">
+        <v>6.75</v>
+      </c>
+      <c r="BF309">
+        <v>2.8</v>
+      </c>
+      <c r="BG309">
+        <v>1.33</v>
+      </c>
+      <c r="BH309">
+        <v>2.95</v>
+      </c>
+      <c r="BI309">
+        <v>1.57</v>
+      </c>
+      <c r="BJ309">
+        <v>2.23</v>
+      </c>
+      <c r="BK309">
+        <v>1.92</v>
+      </c>
+      <c r="BL309">
+        <v>1.77</v>
+      </c>
+      <c r="BM309">
+        <v>2.43</v>
+      </c>
+      <c r="BN309">
+        <v>1.48</v>
+      </c>
+      <c r="BO309">
+        <v>3.15</v>
+      </c>
+      <c r="BP309">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="310" spans="1:68">
+      <c r="A310" s="1">
+        <v>309</v>
+      </c>
+      <c r="B310">
+        <v>7781392</v>
+      </c>
+      <c r="C310" t="s">
+        <v>68</v>
+      </c>
+      <c r="D310" t="s">
+        <v>69</v>
+      </c>
+      <c r="E310" s="2">
+        <v>45850.85416666666</v>
+      </c>
+      <c r="F310">
+        <v>0</v>
+      </c>
+      <c r="G310" t="s">
+        <v>98</v>
+      </c>
+      <c r="H310" t="s">
+        <v>72</v>
+      </c>
+      <c r="I310">
+        <v>0</v>
+      </c>
+      <c r="J310">
+        <v>0</v>
+      </c>
+      <c r="K310">
+        <v>0</v>
+      </c>
+      <c r="L310">
+        <v>1</v>
+      </c>
+      <c r="M310">
+        <v>1</v>
+      </c>
+      <c r="N310">
+        <v>2</v>
+      </c>
+      <c r="O310" t="s">
+        <v>311</v>
+      </c>
+      <c r="P310" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q310">
+        <v>3.04</v>
+      </c>
+      <c r="R310">
+        <v>2.23</v>
+      </c>
+      <c r="S310">
+        <v>3.18</v>
+      </c>
+      <c r="T310">
+        <v>1.28</v>
+      </c>
+      <c r="U310">
+        <v>3.18</v>
+      </c>
+      <c r="V310">
+        <v>2.48</v>
+      </c>
+      <c r="W310">
+        <v>1.45</v>
+      </c>
+      <c r="X310">
+        <v>6</v>
+      </c>
+      <c r="Y310">
+        <v>1.06</v>
+      </c>
+      <c r="Z310">
+        <v>2.46</v>
+      </c>
+      <c r="AA310">
+        <v>3.33</v>
+      </c>
+      <c r="AB310">
+        <v>2.42</v>
+      </c>
+      <c r="AC310">
+        <v>1.05</v>
+      </c>
+      <c r="AD310">
+        <v>9.5</v>
+      </c>
+      <c r="AE310">
+        <v>1.19</v>
+      </c>
+      <c r="AF310">
+        <v>3.94</v>
+      </c>
+      <c r="AG310">
+        <v>1.75</v>
+      </c>
+      <c r="AH310">
+        <v>1.95</v>
+      </c>
+      <c r="AI310">
+        <v>1.59</v>
+      </c>
+      <c r="AJ310">
+        <v>2.21</v>
+      </c>
+      <c r="AK310">
+        <v>1.48</v>
+      </c>
+      <c r="AL310">
+        <v>1.29</v>
+      </c>
+      <c r="AM310">
+        <v>1.53</v>
+      </c>
+      <c r="AN310">
+        <v>0.75</v>
+      </c>
+      <c r="AO310">
+        <v>0.3</v>
+      </c>
+      <c r="AP310">
+        <v>0.77</v>
+      </c>
+      <c r="AQ310">
+        <v>0.36</v>
+      </c>
+      <c r="AR310">
+        <v>1.34</v>
+      </c>
+      <c r="AS310">
+        <v>1.25</v>
+      </c>
+      <c r="AT310">
+        <v>2.59</v>
+      </c>
+      <c r="AU310">
+        <v>6</v>
+      </c>
+      <c r="AV310">
+        <v>5</v>
+      </c>
+      <c r="AW310">
+        <v>8</v>
+      </c>
+      <c r="AX310">
+        <v>6</v>
+      </c>
+      <c r="AY310">
+        <v>14</v>
+      </c>
+      <c r="AZ310">
+        <v>11</v>
+      </c>
+      <c r="BA310">
+        <v>3</v>
+      </c>
+      <c r="BB310">
+        <v>3</v>
+      </c>
+      <c r="BC310">
+        <v>6</v>
+      </c>
+      <c r="BD310">
+        <v>1.84</v>
+      </c>
+      <c r="BE310">
+        <v>6.4</v>
+      </c>
+      <c r="BF310">
+        <v>2.15</v>
+      </c>
+      <c r="BG310">
+        <v>1.27</v>
+      </c>
+      <c r="BH310">
+        <v>3.3</v>
+      </c>
+      <c r="BI310">
+        <v>1.47</v>
+      </c>
+      <c r="BJ310">
+        <v>2.48</v>
+      </c>
+      <c r="BK310">
+        <v>1.76</v>
+      </c>
+      <c r="BL310">
+        <v>1.94</v>
+      </c>
+      <c r="BM310">
+        <v>2.18</v>
+      </c>
+      <c r="BN310">
+        <v>1.58</v>
+      </c>
+      <c r="BO310">
+        <v>2.8</v>
+      </c>
+      <c r="BP310">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="311" spans="1:68">
+      <c r="A311" s="1">
+        <v>310</v>
+      </c>
+      <c r="B311">
+        <v>7781390</v>
+      </c>
+      <c r="C311" t="s">
+        <v>68</v>
+      </c>
+      <c r="D311" t="s">
+        <v>69</v>
+      </c>
+      <c r="E311" s="2">
+        <v>45850.85416666666</v>
+      </c>
+      <c r="F311">
+        <v>0</v>
+      </c>
+      <c r="G311" t="s">
+        <v>76</v>
+      </c>
+      <c r="H311" t="s">
+        <v>99</v>
+      </c>
+      <c r="I311">
+        <v>1</v>
+      </c>
+      <c r="J311">
+        <v>0</v>
+      </c>
+      <c r="K311">
+        <v>1</v>
+      </c>
+      <c r="L311">
+        <v>1</v>
+      </c>
+      <c r="M311">
+        <v>1</v>
+      </c>
+      <c r="N311">
+        <v>2</v>
+      </c>
+      <c r="O311" t="s">
+        <v>312</v>
+      </c>
+      <c r="P311" t="s">
+        <v>460</v>
+      </c>
+      <c r="Q311">
+        <v>1.83</v>
+      </c>
+      <c r="R311">
+        <v>2.58</v>
+      </c>
+      <c r="S311">
+        <v>6.25</v>
+      </c>
+      <c r="T311">
+        <v>1.23</v>
+      </c>
+      <c r="U311">
+        <v>3.42</v>
+      </c>
+      <c r="V311">
+        <v>2.21</v>
+      </c>
+      <c r="W311">
+        <v>1.59</v>
+      </c>
+      <c r="X311">
+        <v>4.7</v>
+      </c>
+      <c r="Y311">
+        <v>1.12</v>
+      </c>
+      <c r="Z311">
+        <v>1.39</v>
+      </c>
+      <c r="AA311">
+        <v>4.33</v>
+      </c>
+      <c r="AB311">
+        <v>5.8</v>
+      </c>
+      <c r="AC311">
+        <v>1.03</v>
+      </c>
+      <c r="AD311">
+        <v>11</v>
+      </c>
+      <c r="AE311">
+        <v>1.14</v>
+      </c>
+      <c r="AF311">
+        <v>4.6</v>
+      </c>
+      <c r="AG311">
+        <v>1.56</v>
+      </c>
+      <c r="AH311">
+        <v>2.27</v>
+      </c>
+      <c r="AI311">
+        <v>1.75</v>
+      </c>
+      <c r="AJ311">
+        <v>1.96</v>
+      </c>
+      <c r="AK311">
+        <v>1.09</v>
+      </c>
+      <c r="AL311">
+        <v>1.17</v>
+      </c>
+      <c r="AM311">
+        <v>2.94</v>
+      </c>
+      <c r="AN311">
+        <v>1.7</v>
+      </c>
+      <c r="AO311">
+        <v>0.73</v>
+      </c>
+      <c r="AP311">
+        <v>1.64</v>
+      </c>
+      <c r="AQ311">
+        <v>0.75</v>
+      </c>
+      <c r="AR311">
+        <v>1.9</v>
+      </c>
+      <c r="AS311">
+        <v>1.35</v>
+      </c>
+      <c r="AT311">
+        <v>3.25</v>
+      </c>
+      <c r="AU311">
+        <v>5</v>
+      </c>
+      <c r="AV311">
+        <v>3</v>
+      </c>
+      <c r="AW311">
+        <v>7</v>
+      </c>
+      <c r="AX311">
+        <v>3</v>
+      </c>
+      <c r="AY311">
+        <v>12</v>
+      </c>
+      <c r="AZ311">
+        <v>6</v>
+      </c>
+      <c r="BA311">
+        <v>3</v>
+      </c>
+      <c r="BB311">
+        <v>2</v>
+      </c>
+      <c r="BC311">
+        <v>5</v>
+      </c>
+      <c r="BD311">
+        <v>1.4</v>
+      </c>
+      <c r="BE311">
+        <v>7</v>
+      </c>
+      <c r="BF311">
+        <v>3.3</v>
+      </c>
+      <c r="BG311">
+        <v>1.3</v>
+      </c>
+      <c r="BH311">
+        <v>3.1</v>
+      </c>
+      <c r="BI311">
+        <v>1.52</v>
+      </c>
+      <c r="BJ311">
+        <v>2.33</v>
+      </c>
+      <c r="BK311">
+        <v>1.84</v>
+      </c>
+      <c r="BL311">
+        <v>1.84</v>
+      </c>
+      <c r="BM311">
+        <v>2.3</v>
+      </c>
+      <c r="BN311">
+        <v>1.53</v>
+      </c>
+      <c r="BO311">
+        <v>2.95</v>
+      </c>
+      <c r="BP311">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="312" spans="1:68">
+      <c r="A312" s="1">
+        <v>311</v>
+      </c>
+      <c r="B312">
+        <v>7781389</v>
+      </c>
+      <c r="C312" t="s">
+        <v>68</v>
+      </c>
+      <c r="D312" t="s">
+        <v>69</v>
+      </c>
+      <c r="E312" s="2">
+        <v>45850.86458333334</v>
+      </c>
+      <c r="F312">
+        <v>0</v>
+      </c>
+      <c r="G312" t="s">
+        <v>71</v>
+      </c>
+      <c r="H312" t="s">
+        <v>79</v>
+      </c>
+      <c r="I312">
+        <v>1</v>
+      </c>
+      <c r="J312">
+        <v>0</v>
+      </c>
+      <c r="K312">
+        <v>1</v>
+      </c>
+      <c r="L312">
+        <v>2</v>
+      </c>
+      <c r="M312">
+        <v>1</v>
+      </c>
+      <c r="N312">
+        <v>3</v>
+      </c>
+      <c r="O312" t="s">
+        <v>313</v>
+      </c>
+      <c r="P312" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q312">
+        <v>2.4</v>
+      </c>
+      <c r="R312">
+        <v>2.38</v>
+      </c>
+      <c r="S312">
+        <v>3.55</v>
+      </c>
+      <c r="T312">
+        <v>1.22</v>
+      </c>
+      <c r="U312">
+        <v>3.75</v>
+      </c>
+      <c r="V312">
+        <v>2</v>
+      </c>
+      <c r="W312">
+        <v>1.73</v>
+      </c>
+      <c r="X312">
+        <v>4</v>
+      </c>
+      <c r="Y312">
+        <v>1.2</v>
+      </c>
+      <c r="Z312">
+        <v>1.92</v>
+      </c>
+      <c r="AA312">
+        <v>3.75</v>
+      </c>
+      <c r="AB312">
+        <v>3.02</v>
+      </c>
+      <c r="AC312">
+        <v>1.01</v>
+      </c>
+      <c r="AD312">
+        <v>17</v>
+      </c>
+      <c r="AE312">
+        <v>1.12</v>
+      </c>
+      <c r="AF312">
+        <v>5.75</v>
+      </c>
+      <c r="AG312">
+        <v>1.42</v>
+      </c>
+      <c r="AH312">
+        <v>2.74</v>
+      </c>
+      <c r="AI312">
+        <v>1.36</v>
+      </c>
+      <c r="AJ312">
+        <v>2.9</v>
+      </c>
+      <c r="AK312">
+        <v>1.33</v>
+      </c>
+      <c r="AL312">
+        <v>1.2</v>
+      </c>
+      <c r="AM312">
+        <v>1.77</v>
+      </c>
+      <c r="AN312">
+        <v>1.89</v>
+      </c>
+      <c r="AO312">
+        <v>1.9</v>
+      </c>
+      <c r="AP312">
+        <v>2</v>
+      </c>
+      <c r="AQ312">
+        <v>1.73</v>
+      </c>
+      <c r="AR312">
+        <v>1.5</v>
+      </c>
+      <c r="AS312">
+        <v>1.6</v>
+      </c>
+      <c r="AT312">
+        <v>3.1</v>
+      </c>
+      <c r="AU312">
+        <v>6</v>
+      </c>
+      <c r="AV312">
+        <v>3</v>
+      </c>
+      <c r="AW312">
+        <v>3</v>
+      </c>
+      <c r="AX312">
+        <v>2</v>
+      </c>
+      <c r="AY312">
+        <v>9</v>
+      </c>
+      <c r="AZ312">
+        <v>5</v>
+      </c>
+      <c r="BA312">
+        <v>0</v>
+      </c>
+      <c r="BB312">
+        <v>4</v>
+      </c>
+      <c r="BC312">
+        <v>4</v>
+      </c>
+      <c r="BD312">
+        <v>1.65</v>
+      </c>
+      <c r="BE312">
+        <v>6.75</v>
+      </c>
+      <c r="BF312">
+        <v>2.48</v>
+      </c>
+      <c r="BG312">
+        <v>1.24</v>
+      </c>
+      <c r="BH312">
+        <v>3.55</v>
+      </c>
+      <c r="BI312">
+        <v>1.44</v>
+      </c>
+      <c r="BJ312">
+        <v>2.55</v>
+      </c>
+      <c r="BK312">
+        <v>1.72</v>
+      </c>
+      <c r="BL312">
+        <v>1.98</v>
+      </c>
+      <c r="BM312">
+        <v>2.1</v>
+      </c>
+      <c r="BN312">
+        <v>1.64</v>
+      </c>
+      <c r="BO312">
+        <v>2.65</v>
+      </c>
+      <c r="BP312">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="313" spans="1:68">
+      <c r="A313" s="1">
+        <v>312</v>
+      </c>
+      <c r="B313">
+        <v>7781393</v>
+      </c>
+      <c r="C313" t="s">
+        <v>68</v>
+      </c>
+      <c r="D313" t="s">
+        <v>69</v>
+      </c>
+      <c r="E313" s="2">
+        <v>45850.89583333334</v>
+      </c>
+      <c r="F313">
+        <v>0</v>
+      </c>
+      <c r="G313" t="s">
+        <v>77</v>
+      </c>
+      <c r="H313" t="s">
+        <v>87</v>
+      </c>
+      <c r="I313">
+        <v>0</v>
+      </c>
+      <c r="J313">
+        <v>0</v>
+      </c>
+      <c r="K313">
+        <v>0</v>
+      </c>
+      <c r="L313">
+        <v>0</v>
+      </c>
+      <c r="M313">
+        <v>0</v>
+      </c>
+      <c r="N313">
+        <v>0</v>
+      </c>
+      <c r="O313" t="s">
+        <v>109</v>
+      </c>
+      <c r="P313" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q313">
+        <v>2.75</v>
+      </c>
+      <c r="R313">
+        <v>2.2</v>
+      </c>
+      <c r="S313">
+        <v>3.75</v>
+      </c>
+      <c r="T313">
+        <v>1.36</v>
+      </c>
+      <c r="U313">
+        <v>3</v>
+      </c>
+      <c r="V313">
+        <v>2.75</v>
+      </c>
+      <c r="W313">
+        <v>1.4</v>
+      </c>
+      <c r="X313">
+        <v>7</v>
+      </c>
+      <c r="Y313">
+        <v>1.1</v>
+      </c>
+      <c r="Z313">
+        <v>2.06</v>
+      </c>
+      <c r="AA313">
+        <v>3.4</v>
+      </c>
+      <c r="AB313">
+        <v>2.94</v>
+      </c>
+      <c r="AC313">
+        <v>1.05</v>
+      </c>
+      <c r="AD313">
+        <v>9.5</v>
+      </c>
+      <c r="AE313">
+        <v>1.28</v>
+      </c>
+      <c r="AF313">
+        <v>3.55</v>
+      </c>
+      <c r="AG313">
+        <v>1.85</v>
+      </c>
+      <c r="AH313">
+        <v>1.85</v>
+      </c>
+      <c r="AI313">
+        <v>1.75</v>
+      </c>
+      <c r="AJ313">
+        <v>2</v>
+      </c>
+      <c r="AK313">
+        <v>1.35</v>
+      </c>
+      <c r="AL313">
+        <v>1.28</v>
+      </c>
+      <c r="AM313">
+        <v>1.66</v>
+      </c>
+      <c r="AN313">
+        <v>1.6</v>
+      </c>
+      <c r="AO313">
+        <v>1.45</v>
+      </c>
+      <c r="AP313">
+        <v>1.55</v>
+      </c>
+      <c r="AQ313">
+        <v>1.42</v>
+      </c>
+      <c r="AR313">
+        <v>1.62</v>
+      </c>
+      <c r="AS313">
+        <v>1.49</v>
+      </c>
+      <c r="AT313">
+        <v>3.11</v>
+      </c>
+      <c r="AU313">
+        <v>5</v>
+      </c>
+      <c r="AV313">
+        <v>9</v>
+      </c>
+      <c r="AW313">
+        <v>14</v>
+      </c>
+      <c r="AX313">
+        <v>4</v>
+      </c>
+      <c r="AY313">
+        <v>19</v>
+      </c>
+      <c r="AZ313">
+        <v>13</v>
+      </c>
+      <c r="BA313">
+        <v>7</v>
+      </c>
+      <c r="BB313">
+        <v>7</v>
+      </c>
+      <c r="BC313">
+        <v>14</v>
+      </c>
+      <c r="BD313">
+        <v>1.76</v>
+      </c>
+      <c r="BE313">
+        <v>6.75</v>
+      </c>
+      <c r="BF313">
+        <v>2.25</v>
+      </c>
+      <c r="BG313">
+        <v>1.25</v>
+      </c>
+      <c r="BH313">
+        <v>3.4</v>
+      </c>
+      <c r="BI313">
+        <v>1.44</v>
+      </c>
+      <c r="BJ313">
+        <v>2.55</v>
+      </c>
+      <c r="BK313">
+        <v>1.72</v>
+      </c>
+      <c r="BL313">
+        <v>1.98</v>
+      </c>
+      <c r="BM313">
+        <v>2.12</v>
+      </c>
+      <c r="BN313">
+        <v>1.63</v>
+      </c>
+      <c r="BO313">
+        <v>2.7</v>
+      </c>
+      <c r="BP313">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="314" spans="1:68">
+      <c r="A314" s="1">
+        <v>313</v>
+      </c>
+      <c r="B314">
+        <v>7781394</v>
+      </c>
+      <c r="C314" t="s">
+        <v>68</v>
+      </c>
+      <c r="D314" t="s">
+        <v>69</v>
+      </c>
+      <c r="E314" s="2">
+        <v>45850.89583333334</v>
+      </c>
+      <c r="F314">
+        <v>0</v>
+      </c>
+      <c r="G314" t="s">
+        <v>90</v>
+      </c>
+      <c r="H314" t="s">
+        <v>94</v>
+      </c>
+      <c r="I314">
+        <v>0</v>
+      </c>
+      <c r="J314">
+        <v>2</v>
+      </c>
+      <c r="K314">
+        <v>2</v>
+      </c>
+      <c r="L314">
+        <v>1</v>
+      </c>
+      <c r="M314">
+        <v>2</v>
+      </c>
+      <c r="N314">
+        <v>3</v>
+      </c>
+      <c r="O314" t="s">
+        <v>288</v>
+      </c>
+      <c r="P314" t="s">
+        <v>461</v>
+      </c>
+      <c r="Q314">
+        <v>0</v>
+      </c>
+      <c r="R314">
+        <v>0</v>
+      </c>
+      <c r="S314">
+        <v>0</v>
+      </c>
+      <c r="T314">
+        <v>0</v>
+      </c>
+      <c r="U314">
+        <v>0</v>
+      </c>
+      <c r="V314">
+        <v>0</v>
+      </c>
+      <c r="W314">
+        <v>0</v>
+      </c>
+      <c r="X314">
+        <v>0</v>
+      </c>
+      <c r="Y314">
+        <v>0</v>
+      </c>
+      <c r="Z314">
+        <v>2.34</v>
+      </c>
+      <c r="AA314">
+        <v>3.45</v>
+      </c>
+      <c r="AB314">
+        <v>2.48</v>
+      </c>
+      <c r="AC314">
+        <v>0</v>
+      </c>
+      <c r="AD314">
+        <v>0</v>
+      </c>
+      <c r="AE314">
+        <v>0</v>
+      </c>
+      <c r="AF314">
+        <v>0</v>
+      </c>
+      <c r="AG314">
+        <v>1.4</v>
+      </c>
+      <c r="AH314">
+        <v>2.82</v>
+      </c>
+      <c r="AI314">
+        <v>0</v>
+      </c>
+      <c r="AJ314">
+        <v>0</v>
+      </c>
+      <c r="AK314">
+        <v>0</v>
+      </c>
+      <c r="AL314">
+        <v>0</v>
+      </c>
+      <c r="AM314">
+        <v>0</v>
+      </c>
+      <c r="AN314">
+        <v>1.11</v>
+      </c>
+      <c r="AO314">
+        <v>1.8</v>
+      </c>
+      <c r="AP314">
+        <v>1</v>
+      </c>
+      <c r="AQ314">
+        <v>1.91</v>
+      </c>
+      <c r="AR314">
+        <v>1.55</v>
+      </c>
+      <c r="AS314">
+        <v>1.67</v>
+      </c>
+      <c r="AT314">
+        <v>3.22</v>
+      </c>
+      <c r="AU314">
+        <v>2</v>
+      </c>
+      <c r="AV314">
+        <v>5</v>
+      </c>
+      <c r="AW314">
+        <v>5</v>
+      </c>
+      <c r="AX314">
+        <v>2</v>
+      </c>
+      <c r="AY314">
+        <v>7</v>
+      </c>
+      <c r="AZ314">
+        <v>7</v>
+      </c>
+      <c r="BA314">
+        <v>4</v>
+      </c>
+      <c r="BB314">
+        <v>0</v>
+      </c>
+      <c r="BC314">
+        <v>4</v>
+      </c>
+      <c r="BD314">
+        <v>0</v>
+      </c>
+      <c r="BE314">
+        <v>0</v>
+      </c>
+      <c r="BF314">
+        <v>0</v>
+      </c>
+      <c r="BG314">
+        <v>0</v>
+      </c>
+      <c r="BH314">
+        <v>0</v>
+      </c>
+      <c r="BI314">
+        <v>0</v>
+      </c>
+      <c r="BJ314">
+        <v>0</v>
+      </c>
+      <c r="BK314">
+        <v>0</v>
+      </c>
+      <c r="BL314">
+        <v>0</v>
+      </c>
+      <c r="BM314">
+        <v>0</v>
+      </c>
+      <c r="BN314">
+        <v>0</v>
+      </c>
+      <c r="BO314">
+        <v>0</v>
+      </c>
+      <c r="BP314">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:68">
+      <c r="A315" s="1">
+        <v>314</v>
+      </c>
+      <c r="B315">
+        <v>7781395</v>
+      </c>
+      <c r="C315" t="s">
+        <v>68</v>
+      </c>
+      <c r="D315" t="s">
+        <v>69</v>
+      </c>
+      <c r="E315" s="2">
+        <v>45850.89583333334</v>
+      </c>
+      <c r="F315">
+        <v>0</v>
+      </c>
+      <c r="G315" t="s">
+        <v>91</v>
+      </c>
+      <c r="H315" t="s">
+        <v>82</v>
+      </c>
+      <c r="I315">
+        <v>0</v>
+      </c>
+      <c r="J315">
+        <v>3</v>
+      </c>
+      <c r="K315">
+        <v>3</v>
+      </c>
+      <c r="L315">
+        <v>2</v>
+      </c>
+      <c r="M315">
+        <v>3</v>
+      </c>
+      <c r="N315">
+        <v>5</v>
+      </c>
+      <c r="O315" t="s">
+        <v>314</v>
+      </c>
+      <c r="P315" t="s">
+        <v>462</v>
+      </c>
+      <c r="Q315">
+        <v>3.5</v>
+      </c>
+      <c r="R315">
+        <v>2.38</v>
+      </c>
+      <c r="S315">
+        <v>2.63</v>
+      </c>
+      <c r="T315">
+        <v>1.29</v>
+      </c>
+      <c r="U315">
+        <v>3.5</v>
+      </c>
+      <c r="V315">
+        <v>2.38</v>
+      </c>
+      <c r="W315">
+        <v>1.53</v>
+      </c>
+      <c r="X315">
+        <v>5.5</v>
+      </c>
+      <c r="Y315">
+        <v>1.14</v>
+      </c>
+      <c r="Z315">
+        <v>2.86</v>
+      </c>
+      <c r="AA315">
+        <v>3.58</v>
+      </c>
+      <c r="AB315">
+        <v>2.04</v>
+      </c>
+      <c r="AC315">
+        <v>1.04</v>
+      </c>
+      <c r="AD315">
+        <v>10</v>
+      </c>
+      <c r="AE315">
+        <v>1.2</v>
+      </c>
+      <c r="AF315">
+        <v>4.5</v>
+      </c>
+      <c r="AG315">
+        <v>1.67</v>
+      </c>
+      <c r="AH315">
+        <v>2.07</v>
+      </c>
+      <c r="AI315">
+        <v>1.53</v>
+      </c>
+      <c r="AJ315">
+        <v>2.38</v>
+      </c>
+      <c r="AK315">
+        <v>1.66</v>
+      </c>
+      <c r="AL315">
+        <v>1.26</v>
+      </c>
+      <c r="AM315">
+        <v>1.37</v>
+      </c>
+      <c r="AN315">
+        <v>1.2</v>
+      </c>
+      <c r="AO315">
+        <v>0.9</v>
+      </c>
+      <c r="AP315">
+        <v>1.09</v>
+      </c>
+      <c r="AQ315">
+        <v>1.09</v>
+      </c>
+      <c r="AR315">
+        <v>1.65</v>
+      </c>
+      <c r="AS315">
+        <v>1.52</v>
+      </c>
+      <c r="AT315">
+        <v>3.17</v>
+      </c>
+      <c r="AU315">
+        <v>10</v>
+      </c>
+      <c r="AV315">
+        <v>7</v>
+      </c>
+      <c r="AW315">
+        <v>11</v>
+      </c>
+      <c r="AX315">
+        <v>6</v>
+      </c>
+      <c r="AY315">
+        <v>21</v>
+      </c>
+      <c r="AZ315">
+        <v>13</v>
+      </c>
+      <c r="BA315">
+        <v>7</v>
+      </c>
+      <c r="BB315">
+        <v>4</v>
+      </c>
+      <c r="BC315">
+        <v>11</v>
+      </c>
+      <c r="BD315">
+        <v>2.05</v>
+      </c>
+      <c r="BE315">
+        <v>6.75</v>
+      </c>
+      <c r="BF315">
+        <v>1.92</v>
+      </c>
+      <c r="BG315">
+        <v>1.23</v>
+      </c>
+      <c r="BH315">
+        <v>3.65</v>
+      </c>
+      <c r="BI315">
+        <v>1.41</v>
+      </c>
+      <c r="BJ315">
+        <v>2.65</v>
+      </c>
+      <c r="BK315">
+        <v>1.66</v>
+      </c>
+      <c r="BL315">
+        <v>2.06</v>
+      </c>
+      <c r="BM315">
+        <v>2.04</v>
+      </c>
+      <c r="BN315">
+        <v>1.68</v>
+      </c>
+      <c r="BO315">
+        <v>2.55</v>
+      </c>
+      <c r="BP315">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="316" spans="1:68">
+      <c r="A316" s="1">
+        <v>315</v>
+      </c>
+      <c r="B316">
+        <v>7781396</v>
+      </c>
+      <c r="C316" t="s">
+        <v>68</v>
+      </c>
+      <c r="D316" t="s">
+        <v>69</v>
+      </c>
+      <c r="E316" s="2">
+        <v>45850.89583333334</v>
+      </c>
+      <c r="F316">
+        <v>0</v>
+      </c>
+      <c r="G316" t="s">
+        <v>92</v>
+      </c>
+      <c r="H316" t="s">
+        <v>81</v>
+      </c>
+      <c r="I316">
+        <v>3</v>
+      </c>
+      <c r="J316">
+        <v>0</v>
+      </c>
+      <c r="K316">
+        <v>3</v>
+      </c>
+      <c r="L316">
+        <v>4</v>
+      </c>
+      <c r="M316">
+        <v>1</v>
+      </c>
+      <c r="N316">
+        <v>5</v>
+      </c>
+      <c r="O316" t="s">
+        <v>315</v>
+      </c>
+      <c r="P316" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q316">
+        <v>2.38</v>
+      </c>
+      <c r="R316">
+        <v>2.5</v>
+      </c>
+      <c r="S316">
+        <v>3.75</v>
+      </c>
+      <c r="T316">
+        <v>1.25</v>
+      </c>
+      <c r="U316">
+        <v>3.75</v>
+      </c>
+      <c r="V316">
+        <v>2.1</v>
+      </c>
+      <c r="W316">
+        <v>1.67</v>
+      </c>
+      <c r="X316">
+        <v>5</v>
+      </c>
+      <c r="Y316">
+        <v>1.17</v>
+      </c>
+      <c r="Z316">
+        <v>1.77</v>
+      </c>
+      <c r="AA316">
+        <v>3.77</v>
+      </c>
+      <c r="AB316">
+        <v>3.45</v>
+      </c>
+      <c r="AC316">
+        <v>1.01</v>
+      </c>
+      <c r="AD316">
+        <v>17</v>
+      </c>
+      <c r="AE316">
+        <v>1.17</v>
+      </c>
+      <c r="AF316">
+        <v>5</v>
+      </c>
+      <c r="AG316">
+        <v>1.45</v>
+      </c>
+      <c r="AH316">
+        <v>2.63</v>
+      </c>
+      <c r="AI316">
+        <v>1.5</v>
+      </c>
+      <c r="AJ316">
+        <v>2.5</v>
+      </c>
+      <c r="AK316">
+        <v>1.27</v>
+      </c>
+      <c r="AL316">
+        <v>1.24</v>
+      </c>
+      <c r="AM316">
+        <v>1.88</v>
+      </c>
+      <c r="AN316">
+        <v>1.8</v>
+      </c>
+      <c r="AO316">
+        <v>1.4</v>
+      </c>
+      <c r="AP316">
+        <v>1.91</v>
+      </c>
+      <c r="AQ316">
+        <v>1.27</v>
+      </c>
+      <c r="AR316">
+        <v>1.76</v>
+      </c>
+      <c r="AS316">
+        <v>1.92</v>
+      </c>
+      <c r="AT316">
+        <v>3.68</v>
+      </c>
+      <c r="AU316">
+        <v>7</v>
+      </c>
+      <c r="AV316">
+        <v>5</v>
+      </c>
+      <c r="AW316">
+        <v>4</v>
+      </c>
+      <c r="AX316">
+        <v>6</v>
+      </c>
+      <c r="AY316">
+        <v>11</v>
+      </c>
+      <c r="AZ316">
+        <v>11</v>
+      </c>
+      <c r="BA316">
+        <v>5</v>
+      </c>
+      <c r="BB316">
+        <v>8</v>
+      </c>
+      <c r="BC316">
+        <v>13</v>
+      </c>
+      <c r="BD316">
+        <v>1.56</v>
+      </c>
+      <c r="BE316">
+        <v>6.75</v>
+      </c>
+      <c r="BF316">
+        <v>2.65</v>
+      </c>
+      <c r="BG316">
+        <v>1.23</v>
+      </c>
+      <c r="BH316">
+        <v>3.65</v>
+      </c>
+      <c r="BI316">
+        <v>1.41</v>
+      </c>
+      <c r="BJ316">
+        <v>2.65</v>
+      </c>
+      <c r="BK316">
+        <v>1.67</v>
+      </c>
+      <c r="BL316">
+        <v>2.05</v>
+      </c>
+      <c r="BM316">
+        <v>2.05</v>
+      </c>
+      <c r="BN316">
+        <v>1.67</v>
+      </c>
+      <c r="BO316">
+        <v>2.55</v>
+      </c>
+      <c r="BP316">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="317" spans="1:68">
+      <c r="A317" s="1">
+        <v>316</v>
+      </c>
+      <c r="B317">
+        <v>7781388</v>
+      </c>
+      <c r="C317" t="s">
+        <v>68</v>
+      </c>
+      <c r="D317" t="s">
+        <v>69</v>
+      </c>
+      <c r="E317" s="2">
+        <v>45850.9</v>
+      </c>
+      <c r="F317">
+        <v>0</v>
+      </c>
+      <c r="G317" t="s">
+        <v>73</v>
+      </c>
+      <c r="H317" t="s">
+        <v>74</v>
+      </c>
+      <c r="I317">
+        <v>2</v>
+      </c>
+      <c r="J317">
+        <v>2</v>
+      </c>
+      <c r="K317">
+        <v>4</v>
+      </c>
+      <c r="L317">
+        <v>2</v>
+      </c>
+      <c r="M317">
+        <v>4</v>
+      </c>
+      <c r="N317">
+        <v>6</v>
+      </c>
+      <c r="O317" t="s">
+        <v>316</v>
+      </c>
+      <c r="P317" t="s">
+        <v>463</v>
+      </c>
+      <c r="Q317">
+        <v>2.63</v>
+      </c>
+      <c r="R317">
+        <v>2.5</v>
+      </c>
+      <c r="S317">
+        <v>3.4</v>
+      </c>
+      <c r="T317">
+        <v>1.25</v>
+      </c>
+      <c r="U317">
+        <v>3.75</v>
+      </c>
+      <c r="V317">
+        <v>2.2</v>
+      </c>
+      <c r="W317">
+        <v>1.62</v>
+      </c>
+      <c r="X317">
+        <v>5</v>
+      </c>
+      <c r="Y317">
+        <v>1.17</v>
+      </c>
+      <c r="Z317">
+        <v>2.02</v>
+      </c>
+      <c r="AA317">
+        <v>3.69</v>
+      </c>
+      <c r="AB317">
+        <v>2.84</v>
+      </c>
+      <c r="AC317">
+        <v>1.03</v>
+      </c>
+      <c r="AD317">
+        <v>11</v>
+      </c>
+      <c r="AE317">
+        <v>1.17</v>
+      </c>
+      <c r="AF317">
+        <v>5</v>
+      </c>
+      <c r="AG317">
+        <v>1.55</v>
+      </c>
+      <c r="AH317">
+        <v>2.3</v>
+      </c>
+      <c r="AI317">
+        <v>1.5</v>
+      </c>
+      <c r="AJ317">
+        <v>2.5</v>
+      </c>
+      <c r="AK317">
+        <v>1.36</v>
+      </c>
+      <c r="AL317">
+        <v>1.22</v>
+      </c>
+      <c r="AM317">
+        <v>1.67</v>
+      </c>
+      <c r="AN317">
+        <v>2.22</v>
+      </c>
+      <c r="AO317">
+        <v>1.44</v>
+      </c>
+      <c r="AP317">
+        <v>2</v>
+      </c>
+      <c r="AQ317">
+        <v>1.6</v>
+      </c>
+      <c r="AR317">
+        <v>1.77</v>
+      </c>
+      <c r="AS317">
+        <v>1.42</v>
+      </c>
+      <c r="AT317">
+        <v>3.19</v>
+      </c>
+      <c r="AU317">
+        <v>5</v>
+      </c>
+      <c r="AV317">
+        <v>6</v>
+      </c>
+      <c r="AW317">
+        <v>9</v>
+      </c>
+      <c r="AX317">
+        <v>7</v>
+      </c>
+      <c r="AY317">
+        <v>14</v>
+      </c>
+      <c r="AZ317">
+        <v>13</v>
+      </c>
+      <c r="BA317">
+        <v>5</v>
+      </c>
+      <c r="BB317">
+        <v>4</v>
+      </c>
+      <c r="BC317">
+        <v>9</v>
+      </c>
+      <c r="BD317">
+        <v>1.76</v>
+      </c>
+      <c r="BE317">
+        <v>6.4</v>
+      </c>
+      <c r="BF317">
+        <v>2.3</v>
+      </c>
+      <c r="BG317">
+        <v>1.35</v>
+      </c>
+      <c r="BH317">
+        <v>2.9</v>
+      </c>
+      <c r="BI317">
+        <v>1.7</v>
+      </c>
+      <c r="BJ317">
+        <v>2.05</v>
+      </c>
+      <c r="BK317">
+        <v>1.96</v>
+      </c>
+      <c r="BL317">
+        <v>1.73</v>
+      </c>
+      <c r="BM317">
+        <v>2.5</v>
+      </c>
+      <c r="BN317">
+        <v>1.46</v>
+      </c>
+      <c r="BO317">
+        <v>3.3</v>
+      </c>
+      <c r="BP317">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="318" spans="1:68">
+      <c r="A318" s="1">
+        <v>317</v>
+      </c>
+      <c r="B318">
+        <v>7781387</v>
+      </c>
+      <c r="C318" t="s">
+        <v>68</v>
+      </c>
+      <c r="D318" t="s">
+        <v>69</v>
+      </c>
+      <c r="E318" s="2">
+        <v>45850.91527777778</v>
+      </c>
+      <c r="F318">
+        <v>0</v>
+      </c>
+      <c r="G318" t="s">
+        <v>85</v>
+      </c>
+      <c r="H318" t="s">
+        <v>96</v>
+      </c>
+      <c r="I318">
+        <v>1</v>
+      </c>
+      <c r="J318">
+        <v>0</v>
+      </c>
+      <c r="K318">
+        <v>1</v>
+      </c>
+      <c r="L318">
+        <v>2</v>
+      </c>
+      <c r="M318">
+        <v>0</v>
+      </c>
+      <c r="N318">
+        <v>2</v>
+      </c>
+      <c r="O318" t="s">
+        <v>317</v>
+      </c>
+      <c r="P318" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q318">
+        <v>2.4</v>
+      </c>
+      <c r="R318">
+        <v>2.3</v>
+      </c>
+      <c r="S318">
+        <v>3.7</v>
+      </c>
+      <c r="T318">
+        <v>1.28</v>
+      </c>
+      <c r="U318">
+        <v>3.4</v>
+      </c>
+      <c r="V318">
+        <v>2.2</v>
+      </c>
+      <c r="W318">
+        <v>1.6</v>
+      </c>
+      <c r="X318">
+        <v>4.75</v>
+      </c>
+      <c r="Y318">
+        <v>1.15</v>
+      </c>
+      <c r="Z318">
+        <v>1.9</v>
+      </c>
+      <c r="AA318">
+        <v>3.45</v>
+      </c>
+      <c r="AB318">
+        <v>3.31</v>
+      </c>
+      <c r="AC318">
+        <v>1.04</v>
+      </c>
+      <c r="AD318">
+        <v>10</v>
+      </c>
+      <c r="AE318">
+        <v>1.18</v>
+      </c>
+      <c r="AF318">
+        <v>4.75</v>
+      </c>
+      <c r="AG318">
+        <v>1.48</v>
+      </c>
+      <c r="AH318">
+        <v>2.54</v>
+      </c>
+      <c r="AI318">
+        <v>1.48</v>
+      </c>
+      <c r="AJ318">
+        <v>2.5</v>
+      </c>
+      <c r="AK318">
+        <v>1.3</v>
+      </c>
+      <c r="AL318">
+        <v>1.22</v>
+      </c>
+      <c r="AM318">
+        <v>1.77</v>
+      </c>
+      <c r="AN318">
+        <v>2.11</v>
+      </c>
+      <c r="AO318">
+        <v>0.78</v>
+      </c>
+      <c r="AP318">
+        <v>2.2</v>
+      </c>
+      <c r="AQ318">
+        <v>0.7</v>
+      </c>
+      <c r="AR318">
+        <v>1.64</v>
+      </c>
+      <c r="AS318">
+        <v>1.25</v>
+      </c>
+      <c r="AT318">
+        <v>2.89</v>
+      </c>
+      <c r="AU318">
+        <v>4</v>
+      </c>
+      <c r="AV318">
+        <v>3</v>
+      </c>
+      <c r="AW318">
+        <v>4</v>
+      </c>
+      <c r="AX318">
+        <v>14</v>
+      </c>
+      <c r="AY318">
+        <v>8</v>
+      </c>
+      <c r="AZ318">
+        <v>17</v>
+      </c>
+      <c r="BA318">
+        <v>3</v>
+      </c>
+      <c r="BB318">
+        <v>2</v>
+      </c>
+      <c r="BC318">
+        <v>5</v>
+      </c>
+      <c r="BD318">
+        <v>1.74</v>
+      </c>
+      <c r="BE318">
+        <v>6.5</v>
+      </c>
+      <c r="BF318">
+        <v>2.33</v>
+      </c>
+      <c r="BG318">
+        <v>1.23</v>
+      </c>
+      <c r="BH318">
+        <v>3.65</v>
+      </c>
+      <c r="BI318">
+        <v>1.41</v>
+      </c>
+      <c r="BJ318">
+        <v>2.65</v>
+      </c>
+      <c r="BK318">
+        <v>1.66</v>
+      </c>
+      <c r="BL318">
+        <v>2.07</v>
+      </c>
+      <c r="BM318">
+        <v>2.02</v>
+      </c>
+      <c r="BN318">
+        <v>1.68</v>
+      </c>
+      <c r="BO318">
+        <v>2.55</v>
+      </c>
+      <c r="BP318">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="319" spans="1:68">
+      <c r="A319" s="1">
+        <v>318</v>
+      </c>
+      <c r="B319">
+        <v>7781397</v>
+      </c>
+      <c r="C319" t="s">
+        <v>68</v>
+      </c>
+      <c r="D319" t="s">
+        <v>69</v>
+      </c>
+      <c r="E319" s="2">
+        <v>45850.9375</v>
+      </c>
+      <c r="F319">
+        <v>0</v>
+      </c>
+      <c r="G319" t="s">
+        <v>93</v>
+      </c>
+      <c r="H319" t="s">
+        <v>95</v>
+      </c>
+      <c r="I319">
+        <v>2</v>
+      </c>
+      <c r="J319">
+        <v>0</v>
+      </c>
+      <c r="K319">
+        <v>2</v>
+      </c>
+      <c r="L319">
+        <v>3</v>
+      </c>
+      <c r="M319">
+        <v>0</v>
+      </c>
+      <c r="N319">
+        <v>3</v>
+      </c>
+      <c r="O319" t="s">
+        <v>318</v>
+      </c>
+      <c r="P319" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q319">
+        <v>2.88</v>
+      </c>
+      <c r="R319">
+        <v>2.38</v>
+      </c>
+      <c r="S319">
+        <v>3.25</v>
+      </c>
+      <c r="T319">
+        <v>1.29</v>
+      </c>
+      <c r="U319">
+        <v>3.5</v>
+      </c>
+      <c r="V319">
+        <v>2.38</v>
+      </c>
+      <c r="W319">
+        <v>1.53</v>
+      </c>
+      <c r="X319">
+        <v>5.5</v>
+      </c>
+      <c r="Y319">
+        <v>1.14</v>
+      </c>
+      <c r="Z319">
+        <v>2.2</v>
+      </c>
+      <c r="AA319">
+        <v>3.31</v>
+      </c>
+      <c r="AB319">
+        <v>2.75</v>
+      </c>
+      <c r="AC319">
+        <v>1.04</v>
+      </c>
+      <c r="AD319">
+        <v>10</v>
+      </c>
+      <c r="AE319">
+        <v>1.2</v>
+      </c>
+      <c r="AF319">
+        <v>4.33</v>
+      </c>
+      <c r="AG319">
+        <v>1.6</v>
+      </c>
+      <c r="AH319">
+        <v>2.2</v>
+      </c>
+      <c r="AI319">
+        <v>1.53</v>
+      </c>
+      <c r="AJ319">
+        <v>2.38</v>
+      </c>
+      <c r="AK319">
+        <v>1.39</v>
+      </c>
+      <c r="AL319">
+        <v>1.29</v>
+      </c>
+      <c r="AM319">
+        <v>1.58</v>
+      </c>
+      <c r="AN319">
+        <v>1.42</v>
+      </c>
+      <c r="AO319">
+        <v>1.8</v>
+      </c>
+      <c r="AP319">
+        <v>1.54</v>
+      </c>
+      <c r="AQ319">
+        <v>1.64</v>
+      </c>
+      <c r="AR319">
+        <v>1.45</v>
+      </c>
+      <c r="AS319">
+        <v>1.41</v>
+      </c>
+      <c r="AT319">
+        <v>2.86</v>
+      </c>
+      <c r="AU319">
+        <v>5</v>
+      </c>
+      <c r="AV319">
+        <v>3</v>
+      </c>
+      <c r="AW319">
+        <v>10</v>
+      </c>
+      <c r="AX319">
+        <v>12</v>
+      </c>
+      <c r="AY319">
+        <v>15</v>
+      </c>
+      <c r="AZ319">
+        <v>15</v>
+      </c>
+      <c r="BA319">
+        <v>7</v>
+      </c>
+      <c r="BB319">
+        <v>10</v>
+      </c>
+      <c r="BC319">
+        <v>17</v>
+      </c>
+      <c r="BD319">
+        <v>1.88</v>
+      </c>
+      <c r="BE319">
+        <v>6.4</v>
+      </c>
+      <c r="BF319">
+        <v>2.12</v>
+      </c>
+      <c r="BG319">
+        <v>1.25</v>
+      </c>
+      <c r="BH319">
+        <v>3.45</v>
+      </c>
+      <c r="BI319">
+        <v>1.44</v>
+      </c>
+      <c r="BJ319">
+        <v>2.55</v>
+      </c>
+      <c r="BK319">
+        <v>1.83</v>
+      </c>
+      <c r="BL319">
+        <v>1.85</v>
+      </c>
+      <c r="BM319">
+        <v>2.14</v>
+      </c>
+      <c r="BN319">
+        <v>1.62</v>
+      </c>
+      <c r="BO319">
+        <v>2.7</v>
+      </c>
+      <c r="BP319">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="320" spans="1:68">
+      <c r="A320" s="1">
+        <v>319</v>
+      </c>
+      <c r="B320">
+        <v>7781398</v>
+      </c>
+      <c r="C320" t="s">
+        <v>68</v>
+      </c>
+      <c r="D320" t="s">
+        <v>69</v>
+      </c>
+      <c r="E320" s="2">
+        <v>45850.9375</v>
+      </c>
+      <c r="F320">
+        <v>0</v>
+      </c>
+      <c r="G320" t="s">
+        <v>86</v>
+      </c>
+      <c r="H320" t="s">
+        <v>78</v>
+      </c>
+      <c r="I320">
+        <v>1</v>
+      </c>
+      <c r="J320">
+        <v>0</v>
+      </c>
+      <c r="K320">
+        <v>1</v>
+      </c>
+      <c r="L320">
+        <v>1</v>
+      </c>
+      <c r="M320">
+        <v>0</v>
+      </c>
+      <c r="N320">
+        <v>1</v>
+      </c>
+      <c r="O320" t="s">
+        <v>319</v>
+      </c>
+      <c r="P320" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q320">
+        <v>2.6</v>
+      </c>
+      <c r="R320">
+        <v>2.25</v>
+      </c>
+      <c r="S320">
+        <v>4</v>
+      </c>
+      <c r="T320">
+        <v>1.33</v>
+      </c>
+      <c r="U320">
+        <v>3.25</v>
+      </c>
+      <c r="V320">
+        <v>2.63</v>
+      </c>
+      <c r="W320">
+        <v>1.44</v>
+      </c>
+      <c r="X320">
+        <v>6.5</v>
+      </c>
+      <c r="Y320">
+        <v>1.11</v>
+      </c>
+      <c r="Z320">
+        <v>1.92</v>
+      </c>
+      <c r="AA320">
+        <v>3.41</v>
+      </c>
+      <c r="AB320">
+        <v>3.26</v>
+      </c>
+      <c r="AC320">
+        <v>1.05</v>
+      </c>
+      <c r="AD320">
+        <v>9.5</v>
+      </c>
+      <c r="AE320">
+        <v>1.25</v>
+      </c>
+      <c r="AF320">
+        <v>3.9</v>
+      </c>
+      <c r="AG320">
+        <v>1.7</v>
+      </c>
+      <c r="AH320">
+        <v>2.02</v>
+      </c>
+      <c r="AI320">
+        <v>1.67</v>
+      </c>
+      <c r="AJ320">
+        <v>2.1</v>
+      </c>
+      <c r="AK320">
+        <v>1.3</v>
+      </c>
+      <c r="AL320">
+        <v>1.27</v>
+      </c>
+      <c r="AM320">
+        <v>1.75</v>
+      </c>
+      <c r="AN320">
+        <v>1.44</v>
+      </c>
+      <c r="AO320">
+        <v>1.3</v>
+      </c>
+      <c r="AP320">
+        <v>1.6</v>
+      </c>
+      <c r="AQ320">
+        <v>1.18</v>
+      </c>
+      <c r="AR320">
+        <v>1.61</v>
+      </c>
+      <c r="AS320">
+        <v>1.14</v>
+      </c>
+      <c r="AT320">
+        <v>2.75</v>
+      </c>
+      <c r="AU320">
+        <v>6</v>
+      </c>
+      <c r="AV320">
+        <v>4</v>
+      </c>
+      <c r="AW320">
+        <v>7</v>
+      </c>
+      <c r="AX320">
+        <v>12</v>
+      </c>
+      <c r="AY320">
+        <v>13</v>
+      </c>
+      <c r="AZ320">
+        <v>16</v>
+      </c>
+      <c r="BA320">
+        <v>5</v>
+      </c>
+      <c r="BB320">
+        <v>4</v>
+      </c>
+      <c r="BC320">
+        <v>9</v>
+      </c>
+      <c r="BD320">
+        <v>1.58</v>
+      </c>
+      <c r="BE320">
+        <v>6.75</v>
+      </c>
+      <c r="BF320">
+        <v>2.6</v>
+      </c>
+      <c r="BG320">
+        <v>1.25</v>
+      </c>
+      <c r="BH320">
+        <v>3.45</v>
+      </c>
+      <c r="BI320">
+        <v>1.44</v>
+      </c>
+      <c r="BJ320">
+        <v>2.55</v>
+      </c>
+      <c r="BK320">
+        <v>1.7</v>
+      </c>
+      <c r="BL320">
+        <v>2.05</v>
+      </c>
+      <c r="BM320">
+        <v>2.15</v>
+      </c>
+      <c r="BN320">
+        <v>1.61</v>
+      </c>
+      <c r="BO320">
+        <v>2.7</v>
+      </c>
+      <c r="BP320">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="321" spans="1:68">
+      <c r="A321" s="1">
+        <v>320</v>
+      </c>
+      <c r="B321">
+        <v>7781399</v>
+      </c>
+      <c r="C321" t="s">
+        <v>68</v>
+      </c>
+      <c r="D321" t="s">
+        <v>69</v>
+      </c>
+      <c r="E321" s="2">
+        <v>45850.97916666666</v>
+      </c>
+      <c r="F321">
+        <v>0</v>
+      </c>
+      <c r="G321" t="s">
+        <v>84</v>
+      </c>
+      <c r="H321" t="s">
+        <v>75</v>
+      </c>
+      <c r="I321">
+        <v>1</v>
+      </c>
+      <c r="J321">
+        <v>0</v>
+      </c>
+      <c r="K321">
+        <v>1</v>
+      </c>
+      <c r="L321">
+        <v>2</v>
+      </c>
+      <c r="M321">
+        <v>1</v>
+      </c>
+      <c r="N321">
+        <v>3</v>
+      </c>
+      <c r="O321" t="s">
+        <v>320</v>
+      </c>
+      <c r="P321" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q321">
+        <v>2.2</v>
+      </c>
+      <c r="R321">
+        <v>2.38</v>
+      </c>
+      <c r="S321">
+        <v>5</v>
+      </c>
+      <c r="T321">
+        <v>1.33</v>
+      </c>
+      <c r="U321">
+        <v>3.25</v>
+      </c>
+      <c r="V321">
+        <v>2.5</v>
+      </c>
+      <c r="W321">
+        <v>1.5</v>
+      </c>
+      <c r="X321">
+        <v>6.5</v>
+      </c>
+      <c r="Y321">
+        <v>1.11</v>
+      </c>
+      <c r="Z321">
+        <v>1.62</v>
+      </c>
+      <c r="AA321">
+        <v>3.66</v>
+      </c>
+      <c r="AB321">
+        <v>4.33</v>
+      </c>
+      <c r="AC321">
+        <v>1.05</v>
+      </c>
+      <c r="AD321">
+        <v>9.5</v>
+      </c>
+      <c r="AE321">
+        <v>1.25</v>
+      </c>
+      <c r="AF321">
+        <v>3.8</v>
+      </c>
+      <c r="AG321">
+        <v>1.57</v>
+      </c>
+      <c r="AH321">
+        <v>2.25</v>
+      </c>
+      <c r="AI321">
+        <v>1.75</v>
+      </c>
+      <c r="AJ321">
+        <v>2</v>
+      </c>
+      <c r="AK321">
+        <v>1.18</v>
+      </c>
+      <c r="AL321">
+        <v>1.24</v>
+      </c>
+      <c r="AM321">
+        <v>2.15</v>
+      </c>
+      <c r="AN321">
+        <v>0.89</v>
+      </c>
+      <c r="AO321">
+        <v>0.89</v>
+      </c>
+      <c r="AP321">
+        <v>1.1</v>
+      </c>
+      <c r="AQ321">
+        <v>0.8</v>
+      </c>
+      <c r="AR321">
+        <v>1.42</v>
+      </c>
+      <c r="AS321">
+        <v>1.55</v>
+      </c>
+      <c r="AT321">
+        <v>2.97</v>
+      </c>
+      <c r="AU321">
+        <v>6</v>
+      </c>
+      <c r="AV321">
+        <v>4</v>
+      </c>
+      <c r="AW321">
+        <v>5</v>
+      </c>
+      <c r="AX321">
+        <v>5</v>
+      </c>
+      <c r="AY321">
+        <v>11</v>
+      </c>
+      <c r="AZ321">
+        <v>9</v>
+      </c>
+      <c r="BA321">
+        <v>2</v>
+      </c>
+      <c r="BB321">
+        <v>5</v>
+      </c>
+      <c r="BC321">
+        <v>7</v>
+      </c>
+      <c r="BD321">
+        <v>1.54</v>
+      </c>
+      <c r="BE321">
+        <v>6.75</v>
+      </c>
+      <c r="BF321">
+        <v>2.75</v>
+      </c>
+      <c r="BG321">
+        <v>1.3</v>
+      </c>
+      <c r="BH321">
+        <v>3.05</v>
+      </c>
+      <c r="BI321">
+        <v>1.53</v>
+      </c>
+      <c r="BJ321">
+        <v>2.32</v>
+      </c>
+      <c r="BK321">
+        <v>1.85</v>
+      </c>
+      <c r="BL321">
+        <v>1.85</v>
+      </c>
+      <c r="BM321">
+        <v>2.32</v>
+      </c>
+      <c r="BN321">
+        <v>1.53</v>
+      </c>
+      <c r="BO321">
+        <v>3.05</v>
+      </c>
+      <c r="BP321">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="322" spans="1:68">
+      <c r="A322" s="1">
+        <v>321</v>
+      </c>
+      <c r="B322">
+        <v>7781400</v>
+      </c>
+      <c r="C322" t="s">
+        <v>68</v>
+      </c>
+      <c r="D322" t="s">
+        <v>69</v>
+      </c>
+      <c r="E322" s="2">
+        <v>45850.97916666666</v>
+      </c>
+      <c r="F322">
+        <v>0</v>
+      </c>
+      <c r="G322" t="s">
+        <v>70</v>
+      </c>
+      <c r="H322" t="s">
+        <v>97</v>
+      </c>
+      <c r="I322">
+        <v>2</v>
+      </c>
+      <c r="J322">
+        <v>0</v>
+      </c>
+      <c r="K322">
+        <v>2</v>
+      </c>
+      <c r="L322">
+        <v>2</v>
+      </c>
+      <c r="M322">
+        <v>0</v>
+      </c>
+      <c r="N322">
+        <v>2</v>
+      </c>
+      <c r="O322" t="s">
+        <v>321</v>
+      </c>
+      <c r="P322" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q322">
+        <v>1.91</v>
+      </c>
+      <c r="R322">
+        <v>2.63</v>
+      </c>
+      <c r="S322">
+        <v>6</v>
+      </c>
+      <c r="T322">
+        <v>1.25</v>
+      </c>
+      <c r="U322">
+        <v>3.75</v>
+      </c>
+      <c r="V322">
+        <v>2.1</v>
+      </c>
+      <c r="W322">
+        <v>1.67</v>
+      </c>
+      <c r="X322">
+        <v>4.5</v>
+      </c>
+      <c r="Y322">
+        <v>1.18</v>
+      </c>
+      <c r="Z322">
+        <v>1.4</v>
+      </c>
+      <c r="AA322">
+        <v>4.2</v>
+      </c>
+      <c r="AB322">
+        <v>6</v>
+      </c>
+      <c r="AC322">
+        <v>1.01</v>
+      </c>
+      <c r="AD322">
+        <v>17</v>
+      </c>
+      <c r="AE322">
+        <v>1.15</v>
+      </c>
+      <c r="AF322">
+        <v>5.25</v>
+      </c>
+      <c r="AG322">
+        <v>1.44</v>
+      </c>
+      <c r="AH322">
+        <v>2.67</v>
+      </c>
+      <c r="AI322">
+        <v>1.67</v>
+      </c>
+      <c r="AJ322">
+        <v>2.1</v>
+      </c>
+      <c r="AK322">
+        <v>1.12</v>
+      </c>
+      <c r="AL322">
+        <v>1.18</v>
+      </c>
+      <c r="AM322">
+        <v>2.7</v>
+      </c>
+      <c r="AN322">
+        <v>2.2</v>
+      </c>
+      <c r="AO322">
+        <v>1.6</v>
+      </c>
+      <c r="AP322">
+        <v>2.27</v>
+      </c>
+      <c r="AQ322">
+        <v>1.45</v>
+      </c>
+      <c r="AR322">
+        <v>1.83</v>
+      </c>
+      <c r="AS322">
+        <v>1.37</v>
+      </c>
+      <c r="AT322">
+        <v>3.2</v>
+      </c>
+      <c r="AU322">
+        <v>10</v>
+      </c>
+      <c r="AV322">
+        <v>2</v>
+      </c>
+      <c r="AW322">
+        <v>7</v>
+      </c>
+      <c r="AX322">
+        <v>9</v>
+      </c>
+      <c r="AY322">
+        <v>17</v>
+      </c>
+      <c r="AZ322">
+        <v>11</v>
+      </c>
+      <c r="BA322">
+        <v>8</v>
+      </c>
+      <c r="BB322">
+        <v>3</v>
+      </c>
+      <c r="BC322">
+        <v>11</v>
+      </c>
+      <c r="BD322">
+        <v>1.34</v>
+      </c>
+      <c r="BE322">
+        <v>7.5</v>
+      </c>
+      <c r="BF322">
+        <v>3.55</v>
+      </c>
+      <c r="BG322">
+        <v>1.26</v>
+      </c>
+      <c r="BH322">
+        <v>3.4</v>
+      </c>
+      <c r="BI322">
+        <v>1.46</v>
+      </c>
+      <c r="BJ322">
+        <v>2.5</v>
+      </c>
+      <c r="BK322">
+        <v>1.73</v>
+      </c>
+      <c r="BL322">
+        <v>1.96</v>
+      </c>
+      <c r="BM322">
+        <v>2.17</v>
+      </c>
+      <c r="BN322">
+        <v>1.6</v>
+      </c>
+      <c r="BO322">
+        <v>2.7</v>
+      </c>
+      <c r="BP322">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="465">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -982,6 +982,9 @@
     <t>['31', '45']</t>
   </si>
   <si>
+    <t>['54', '67']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -1767,7 +1770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP322"/>
+  <dimension ref="A1:BP323"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2229,7 +2232,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -2435,7 +2438,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2847,7 +2850,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -3053,7 +3056,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3259,7 +3262,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -3671,7 +3674,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -4161,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ12">
         <v>0.9</v>
@@ -4495,7 +4498,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -4701,7 +4704,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4907,7 +4910,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -5937,7 +5940,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -6349,7 +6352,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6555,7 +6558,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6967,7 +6970,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -7997,7 +8000,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -8409,7 +8412,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -9233,7 +9236,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9851,7 +9854,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -10138,7 +10141,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ41">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR41">
         <v>1.65</v>
@@ -10263,7 +10266,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -11087,7 +11090,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -11293,7 +11296,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -11499,7 +11502,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -12323,7 +12326,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12529,7 +12532,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12941,7 +12944,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -13225,7 +13228,7 @@
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ56">
         <v>1.09</v>
@@ -13559,7 +13562,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13765,7 +13768,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -14177,7 +14180,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14383,7 +14386,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -14589,7 +14592,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14795,7 +14798,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -15825,7 +15828,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -16237,7 +16240,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16318,7 +16321,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ71">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR71">
         <v>1.88</v>
@@ -16443,7 +16446,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16855,7 +16858,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -18091,7 +18094,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18297,7 +18300,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18503,7 +18506,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -19121,7 +19124,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -19327,7 +19330,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -19533,7 +19536,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -20023,7 +20026,7 @@
         <v>1.5</v>
       </c>
       <c r="AP89">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ89">
         <v>1</v>
@@ -20151,7 +20154,7 @@
         <v>164</v>
       </c>
       <c r="P90" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
@@ -21387,7 +21390,7 @@
         <v>168</v>
       </c>
       <c r="P96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21880,7 +21883,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ98">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR98">
         <v>1.57</v>
@@ -22829,7 +22832,7 @@
         <v>122</v>
       </c>
       <c r="P103" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q103">
         <v>2.75</v>
@@ -25095,7 +25098,7 @@
         <v>177</v>
       </c>
       <c r="P114" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25301,7 +25304,7 @@
         <v>178</v>
       </c>
       <c r="P115" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -25713,7 +25716,7 @@
         <v>179</v>
       </c>
       <c r="P117" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25919,7 +25922,7 @@
         <v>180</v>
       </c>
       <c r="P118" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -26000,7 +26003,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ118">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR118">
         <v>1.68</v>
@@ -26331,7 +26334,7 @@
         <v>181</v>
       </c>
       <c r="P120" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -26409,7 +26412,7 @@
         <v>2.33</v>
       </c>
       <c r="AP120">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ120">
         <v>1.6</v>
@@ -26743,7 +26746,7 @@
         <v>109</v>
       </c>
       <c r="P122" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q122">
         <v>2.75</v>
@@ -27155,7 +27158,7 @@
         <v>129</v>
       </c>
       <c r="P124" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q124">
         <v>2.5</v>
@@ -28185,7 +28188,7 @@
         <v>187</v>
       </c>
       <c r="P129" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28391,7 +28394,7 @@
         <v>188</v>
       </c>
       <c r="P130" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q130">
         <v>2.4</v>
@@ -28881,7 +28884,7 @@
         <v>2.33</v>
       </c>
       <c r="AP132">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ132">
         <v>1.64</v>
@@ -29215,7 +29218,7 @@
         <v>189</v>
       </c>
       <c r="P134" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q134">
         <v>3</v>
@@ -29421,7 +29424,7 @@
         <v>190</v>
       </c>
       <c r="P135" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -30657,7 +30660,7 @@
         <v>109</v>
       </c>
       <c r="P141" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q141">
         <v>2.38</v>
@@ -31069,7 +31072,7 @@
         <v>174</v>
       </c>
       <c r="P143" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -31481,7 +31484,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q145">
         <v>2.4</v>
@@ -31687,7 +31690,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31893,7 +31896,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q147">
         <v>2.6</v>
@@ -32099,7 +32102,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q148">
         <v>2.05</v>
@@ -32305,7 +32308,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -32511,7 +32514,7 @@
         <v>202</v>
       </c>
       <c r="P150" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q150">
         <v>2.4</v>
@@ -32592,7 +32595,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ150">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR150">
         <v>1.41</v>
@@ -32923,7 +32926,7 @@
         <v>109</v>
       </c>
       <c r="P152" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q152">
         <v>2.88</v>
@@ -33335,7 +33338,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q154">
         <v>3.1</v>
@@ -33541,7 +33544,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q155">
         <v>2.2</v>
@@ -33953,7 +33956,7 @@
         <v>109</v>
       </c>
       <c r="P157" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q157">
         <v>3.2</v>
@@ -34571,7 +34574,7 @@
         <v>209</v>
       </c>
       <c r="P160" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q160">
         <v>2.1</v>
@@ -35064,7 +35067,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ162">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR162">
         <v>2.1</v>
@@ -36425,7 +36428,7 @@
         <v>217</v>
       </c>
       <c r="P169" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q169">
         <v>3</v>
@@ -36631,7 +36634,7 @@
         <v>218</v>
       </c>
       <c r="P170" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -37455,7 +37458,7 @@
         <v>221</v>
       </c>
       <c r="P174" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q174">
         <v>2.5</v>
@@ -37661,7 +37664,7 @@
         <v>163</v>
       </c>
       <c r="P175" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -38073,7 +38076,7 @@
         <v>222</v>
       </c>
       <c r="P177" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -38151,7 +38154,7 @@
         <v>1.2</v>
       </c>
       <c r="AP177">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ177">
         <v>1.91</v>
@@ -38279,7 +38282,7 @@
         <v>109</v>
       </c>
       <c r="P178" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q178">
         <v>2.38</v>
@@ -38691,7 +38694,7 @@
         <v>224</v>
       </c>
       <c r="P180" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -39103,7 +39106,7 @@
         <v>225</v>
       </c>
       <c r="P182" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q182">
         <v>3.75</v>
@@ -39309,7 +39312,7 @@
         <v>226</v>
       </c>
       <c r="P183" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q183">
         <v>2.5</v>
@@ -39515,7 +39518,7 @@
         <v>227</v>
       </c>
       <c r="P184" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q184">
         <v>2.05</v>
@@ -39927,7 +39930,7 @@
         <v>228</v>
       </c>
       <c r="P186" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q186">
         <v>2.4</v>
@@ -40339,7 +40342,7 @@
         <v>230</v>
       </c>
       <c r="P188" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40417,7 +40420,7 @@
         <v>0.5</v>
       </c>
       <c r="AP188">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ188">
         <v>1</v>
@@ -40545,7 +40548,7 @@
         <v>176</v>
       </c>
       <c r="P189" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -40832,7 +40835,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ190">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR190">
         <v>1.5</v>
@@ -41369,7 +41372,7 @@
         <v>233</v>
       </c>
       <c r="P193" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41575,7 +41578,7 @@
         <v>234</v>
       </c>
       <c r="P194" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41987,7 +41990,7 @@
         <v>198</v>
       </c>
       <c r="P196" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q196">
         <v>2.63</v>
@@ -42399,7 +42402,7 @@
         <v>103</v>
       </c>
       <c r="P198" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q198">
         <v>2.63</v>
@@ -43429,7 +43432,7 @@
         <v>109</v>
       </c>
       <c r="P203" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q203">
         <v>2.63</v>
@@ -43841,7 +43844,7 @@
         <v>237</v>
       </c>
       <c r="P205" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -44253,7 +44256,7 @@
         <v>109</v>
       </c>
       <c r="P207" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q207">
         <v>2.25</v>
@@ -45077,7 +45080,7 @@
         <v>240</v>
       </c>
       <c r="P211" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q211">
         <v>3.2</v>
@@ -45283,7 +45286,7 @@
         <v>109</v>
       </c>
       <c r="P212" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45489,7 +45492,7 @@
         <v>241</v>
       </c>
       <c r="P213" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q213">
         <v>4</v>
@@ -45776,7 +45779,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ214">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR214">
         <v>1.93</v>
@@ -45901,7 +45904,7 @@
         <v>242</v>
       </c>
       <c r="P215" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -46107,7 +46110,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q216">
         <v>3.4</v>
@@ -46313,7 +46316,7 @@
         <v>243</v>
       </c>
       <c r="P217" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q217">
         <v>2.75</v>
@@ -46725,7 +46728,7 @@
         <v>244</v>
       </c>
       <c r="P219" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q219">
         <v>3.1</v>
@@ -47137,7 +47140,7 @@
         <v>246</v>
       </c>
       <c r="P221" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q221">
         <v>2.6</v>
@@ -47343,7 +47346,7 @@
         <v>247</v>
       </c>
       <c r="P222" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q222">
         <v>2.5</v>
@@ -47549,7 +47552,7 @@
         <v>248</v>
       </c>
       <c r="P223" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47755,7 +47758,7 @@
         <v>249</v>
       </c>
       <c r="P224" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47961,7 +47964,7 @@
         <v>250</v>
       </c>
       <c r="P225" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -48167,7 +48170,7 @@
         <v>251</v>
       </c>
       <c r="P226" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q226">
         <v>2.75</v>
@@ -48373,7 +48376,7 @@
         <v>252</v>
       </c>
       <c r="P227" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q227">
         <v>1.83</v>
@@ -48579,7 +48582,7 @@
         <v>253</v>
       </c>
       <c r="P228" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48785,7 +48788,7 @@
         <v>109</v>
       </c>
       <c r="P229" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q229">
         <v>2.5</v>
@@ -48991,7 +48994,7 @@
         <v>254</v>
       </c>
       <c r="P230" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q230">
         <v>3.25</v>
@@ -49197,7 +49200,7 @@
         <v>119</v>
       </c>
       <c r="P231" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q231">
         <v>2.4</v>
@@ -49815,7 +49818,7 @@
         <v>109</v>
       </c>
       <c r="P234" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q234">
         <v>2.5</v>
@@ -50433,7 +50436,7 @@
         <v>258</v>
       </c>
       <c r="P237" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q237">
         <v>2.75</v>
@@ -50511,7 +50514,7 @@
         <v>1.43</v>
       </c>
       <c r="AP237">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ237">
         <v>1.27</v>
@@ -50639,7 +50642,7 @@
         <v>259</v>
       </c>
       <c r="P238" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q238">
         <v>2.6</v>
@@ -50845,7 +50848,7 @@
         <v>109</v>
       </c>
       <c r="P239" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -51051,7 +51054,7 @@
         <v>140</v>
       </c>
       <c r="P240" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -51463,7 +51466,7 @@
         <v>109</v>
       </c>
       <c r="P242" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q242">
         <v>3.1</v>
@@ -51875,7 +51878,7 @@
         <v>161</v>
       </c>
       <c r="P244" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q244">
         <v>2.1</v>
@@ -52287,7 +52290,7 @@
         <v>156</v>
       </c>
       <c r="P246" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q246">
         <v>2.5</v>
@@ -52905,7 +52908,7 @@
         <v>264</v>
       </c>
       <c r="P249" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q249">
         <v>2.5</v>
@@ -53111,7 +53114,7 @@
         <v>265</v>
       </c>
       <c r="P250" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q250">
         <v>3.2</v>
@@ -53317,7 +53320,7 @@
         <v>109</v>
       </c>
       <c r="P251" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q251">
         <v>2.75</v>
@@ -53523,7 +53526,7 @@
         <v>266</v>
       </c>
       <c r="P252" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q252">
         <v>2.25</v>
@@ -54347,7 +54350,7 @@
         <v>270</v>
       </c>
       <c r="P256" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q256">
         <v>2.25</v>
@@ -54553,7 +54556,7 @@
         <v>271</v>
       </c>
       <c r="P257" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q257">
         <v>2.63</v>
@@ -54631,7 +54634,7 @@
         <v>0.22</v>
       </c>
       <c r="AP257">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ257">
         <v>0.33</v>
@@ -54759,7 +54762,7 @@
         <v>272</v>
       </c>
       <c r="P258" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q258">
         <v>2.3</v>
@@ -54965,7 +54968,7 @@
         <v>109</v>
       </c>
       <c r="P259" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q259">
         <v>3.1</v>
@@ -55377,7 +55380,7 @@
         <v>274</v>
       </c>
       <c r="P261" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -55583,7 +55586,7 @@
         <v>275</v>
       </c>
       <c r="P262" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q262">
         <v>2.5</v>
@@ -55789,7 +55792,7 @@
         <v>234</v>
       </c>
       <c r="P263" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q263">
         <v>2.25</v>
@@ -55995,7 +55998,7 @@
         <v>109</v>
       </c>
       <c r="P264" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q264">
         <v>2.75</v>
@@ -56201,7 +56204,7 @@
         <v>276</v>
       </c>
       <c r="P265" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q265">
         <v>2.88</v>
@@ -56407,7 +56410,7 @@
         <v>109</v>
       </c>
       <c r="P266" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q266">
         <v>3.4</v>
@@ -56819,7 +56822,7 @@
         <v>278</v>
       </c>
       <c r="P268" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q268">
         <v>2.2</v>
@@ -57025,7 +57028,7 @@
         <v>279</v>
       </c>
       <c r="P269" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57231,7 +57234,7 @@
         <v>280</v>
       </c>
       <c r="P270" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q270">
         <v>3.35</v>
@@ -57643,7 +57646,7 @@
         <v>282</v>
       </c>
       <c r="P272" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q272">
         <v>2.38</v>
@@ -57849,7 +57852,7 @@
         <v>283</v>
       </c>
       <c r="P273" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q273">
         <v>3.4</v>
@@ -57927,7 +57930,7 @@
         <v>1.44</v>
       </c>
       <c r="AP273">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ273">
         <v>1.55</v>
@@ -58055,7 +58058,7 @@
         <v>284</v>
       </c>
       <c r="P274" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q274">
         <v>3</v>
@@ -58467,7 +58470,7 @@
         <v>285</v>
       </c>
       <c r="P276" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Q276">
         <v>2.63</v>
@@ -58673,7 +58676,7 @@
         <v>286</v>
       </c>
       <c r="P277" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -59085,7 +59088,7 @@
         <v>288</v>
       </c>
       <c r="P279" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q279">
         <v>2.63</v>
@@ -59372,7 +59375,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ280">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR280">
         <v>1.3</v>
@@ -59497,7 +59500,7 @@
         <v>290</v>
       </c>
       <c r="P281" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Q281">
         <v>2.25</v>
@@ -59703,7 +59706,7 @@
         <v>291</v>
       </c>
       <c r="P282" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q282">
         <v>2.88</v>
@@ -60321,7 +60324,7 @@
         <v>293</v>
       </c>
       <c r="P285" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q285">
         <v>2.5</v>
@@ -60527,7 +60530,7 @@
         <v>294</v>
       </c>
       <c r="P286" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -62175,7 +62178,7 @@
         <v>112</v>
       </c>
       <c r="P294" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Q294">
         <v>3.1</v>
@@ -62381,7 +62384,7 @@
         <v>122</v>
       </c>
       <c r="P295" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q295">
         <v>2.4</v>
@@ -62793,7 +62796,7 @@
         <v>301</v>
       </c>
       <c r="P297" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q297">
         <v>3.4</v>
@@ -63205,7 +63208,7 @@
         <v>302</v>
       </c>
       <c r="P299" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q299">
         <v>3.2</v>
@@ -63823,7 +63826,7 @@
         <v>305</v>
       </c>
       <c r="P302" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q302">
         <v>2.2</v>
@@ -64029,7 +64032,7 @@
         <v>255</v>
       </c>
       <c r="P303" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q303">
         <v>2.5</v>
@@ -64235,7 +64238,7 @@
         <v>306</v>
       </c>
       <c r="P304" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Q304">
         <v>2.5</v>
@@ -64441,7 +64444,7 @@
         <v>307</v>
       </c>
       <c r="P305" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -64853,7 +64856,7 @@
         <v>199</v>
       </c>
       <c r="P307" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Q307">
         <v>3.26</v>
@@ -65677,7 +65680,7 @@
         <v>312</v>
       </c>
       <c r="P311" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Q311">
         <v>1.83</v>
@@ -66295,7 +66298,7 @@
         <v>288</v>
       </c>
       <c r="P314" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Q314">
         <v>0</v>
@@ -66501,7 +66504,7 @@
         <v>314</v>
       </c>
       <c r="P315" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Q315">
         <v>3.5</v>
@@ -66913,7 +66916,7 @@
         <v>316</v>
       </c>
       <c r="P317" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Q317">
         <v>2.63</v>
@@ -67737,7 +67740,7 @@
         <v>320</v>
       </c>
       <c r="P321" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q321">
         <v>2.2</v>
@@ -68100,6 +68103,212 @@
       </c>
       <c r="BP322">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="323" spans="1:68">
+      <c r="A323" s="1">
+        <v>322</v>
+      </c>
+      <c r="B323">
+        <v>7781401</v>
+      </c>
+      <c r="C323" t="s">
+        <v>68</v>
+      </c>
+      <c r="D323" t="s">
+        <v>69</v>
+      </c>
+      <c r="E323" s="2">
+        <v>45851.83333333334</v>
+      </c>
+      <c r="F323">
+        <v>0</v>
+      </c>
+      <c r="G323" t="s">
+        <v>80</v>
+      </c>
+      <c r="H323" t="s">
+        <v>83</v>
+      </c>
+      <c r="I323">
+        <v>0</v>
+      </c>
+      <c r="J323">
+        <v>1</v>
+      </c>
+      <c r="K323">
+        <v>1</v>
+      </c>
+      <c r="L323">
+        <v>2</v>
+      </c>
+      <c r="M323">
+        <v>1</v>
+      </c>
+      <c r="N323">
+        <v>3</v>
+      </c>
+      <c r="O323" t="s">
+        <v>322</v>
+      </c>
+      <c r="P323" t="s">
+        <v>414</v>
+      </c>
+      <c r="Q323">
+        <v>2.63</v>
+      </c>
+      <c r="R323">
+        <v>2.4</v>
+      </c>
+      <c r="S323">
+        <v>3.4</v>
+      </c>
+      <c r="T323">
+        <v>1.25</v>
+      </c>
+      <c r="U323">
+        <v>3.75</v>
+      </c>
+      <c r="V323">
+        <v>2.2</v>
+      </c>
+      <c r="W323">
+        <v>1.62</v>
+      </c>
+      <c r="X323">
+        <v>5</v>
+      </c>
+      <c r="Y323">
+        <v>1.17</v>
+      </c>
+      <c r="Z323">
+        <v>2.06</v>
+      </c>
+      <c r="AA323">
+        <v>3.53</v>
+      </c>
+      <c r="AB323">
+        <v>2.85</v>
+      </c>
+      <c r="AC323">
+        <v>1.02</v>
+      </c>
+      <c r="AD323">
+        <v>13.5</v>
+      </c>
+      <c r="AE323">
+        <v>1.15</v>
+      </c>
+      <c r="AF323">
+        <v>5.36</v>
+      </c>
+      <c r="AG323">
+        <v>1.61</v>
+      </c>
+      <c r="AH323">
+        <v>2.15</v>
+      </c>
+      <c r="AI323">
+        <v>1.5</v>
+      </c>
+      <c r="AJ323">
+        <v>2.5</v>
+      </c>
+      <c r="AK323">
+        <v>1.39</v>
+      </c>
+      <c r="AL323">
+        <v>1.26</v>
+      </c>
+      <c r="AM323">
+        <v>1.63</v>
+      </c>
+      <c r="AN323">
+        <v>1</v>
+      </c>
+      <c r="AO323">
+        <v>1.22</v>
+      </c>
+      <c r="AP323">
+        <v>1.18</v>
+      </c>
+      <c r="AQ323">
+        <v>1.1</v>
+      </c>
+      <c r="AR323">
+        <v>1.73</v>
+      </c>
+      <c r="AS323">
+        <v>1.42</v>
+      </c>
+      <c r="AT323">
+        <v>3.15</v>
+      </c>
+      <c r="AU323">
+        <v>8</v>
+      </c>
+      <c r="AV323">
+        <v>4</v>
+      </c>
+      <c r="AW323">
+        <v>11</v>
+      </c>
+      <c r="AX323">
+        <v>7</v>
+      </c>
+      <c r="AY323">
+        <v>19</v>
+      </c>
+      <c r="AZ323">
+        <v>11</v>
+      </c>
+      <c r="BA323">
+        <v>4</v>
+      </c>
+      <c r="BB323">
+        <v>3</v>
+      </c>
+      <c r="BC323">
+        <v>7</v>
+      </c>
+      <c r="BD323">
+        <v>1.71</v>
+      </c>
+      <c r="BE323">
+        <v>6.5</v>
+      </c>
+      <c r="BF323">
+        <v>2.38</v>
+      </c>
+      <c r="BG323">
+        <v>1.25</v>
+      </c>
+      <c r="BH323">
+        <v>3.45</v>
+      </c>
+      <c r="BI323">
+        <v>1.44</v>
+      </c>
+      <c r="BJ323">
+        <v>2.55</v>
+      </c>
+      <c r="BK323">
+        <v>1.83</v>
+      </c>
+      <c r="BL323">
+        <v>1.85</v>
+      </c>
+      <c r="BM323">
+        <v>2.1</v>
+      </c>
+      <c r="BN323">
+        <v>1.64</v>
+      </c>
+      <c r="BO323">
+        <v>2.65</v>
+      </c>
+      <c r="BP323">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="480">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -985,6 +985,33 @@
     <t>['54', '67']</t>
   </si>
   <si>
+    <t>['37', '50']</t>
+  </si>
+  <si>
+    <t>['56', '70', '72', '83', '88']</t>
+  </si>
+  <si>
+    <t>['16', '50', '70']</t>
+  </si>
+  <si>
+    <t>['44', '48']</t>
+  </si>
+  <si>
+    <t>['56', '90+4']</t>
+  </si>
+  <si>
+    <t>['2', '30', '82']</t>
+  </si>
+  <si>
+    <t>['16', '43', '47']</t>
+  </si>
+  <si>
+    <t>['21', '86']</t>
+  </si>
+  <si>
+    <t>['90+3']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -1321,9 +1348,6 @@
     <t>['6', '66']</t>
   </si>
   <si>
-    <t>['90+3']</t>
-  </si>
-  <si>
     <t>['41', '51', '87']</t>
   </si>
   <si>
@@ -1409,6 +1433,27 @@
   </si>
   <si>
     <t>['42', '45+3', '59', '90+3']</t>
+  </si>
+  <si>
+    <t>['5', '30', '90+3']</t>
+  </si>
+  <si>
+    <t>['2', '79']</t>
+  </si>
+  <si>
+    <t>['87', '90+1']</t>
+  </si>
+  <si>
+    <t>['4', '42', '56']</t>
+  </si>
+  <si>
+    <t>['50', '53', '75']</t>
+  </si>
+  <si>
+    <t>['45+3', '85']</t>
+  </si>
+  <si>
+    <t>['40', '63']</t>
   </si>
 </sst>
 </file>
@@ -1770,7 +1815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP323"/>
+  <dimension ref="A1:BP337"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2232,7 +2277,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -2313,7 +2358,7 @@
         <v>2</v>
       </c>
       <c r="AQ3">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2438,7 +2483,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2516,10 +2561,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ4">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2722,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ5">
         <v>0.58</v>
@@ -2850,7 +2895,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2931,7 +2976,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3056,7 +3101,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3137,7 +3182,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3262,7 +3307,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -3340,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ8">
         <v>1.73</v>
@@ -3674,7 +3719,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -3752,10 +3797,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ10">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3958,10 +4003,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ11">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4167,7 +4212,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ12">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4370,10 +4415,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ13">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4498,7 +4543,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -4576,7 +4621,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ14">
         <v>0.58</v>
@@ -4704,7 +4749,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4782,10 +4827,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ15">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4910,7 +4955,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4988,7 +5033,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ16">
         <v>1.91</v>
@@ -5194,7 +5239,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ17">
         <v>0.36</v>
@@ -5609,7 +5654,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ19">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5812,7 +5857,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ20">
         <v>1.73</v>
@@ -5940,7 +5985,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -6018,10 +6063,10 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ21">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR21">
         <v>2.07</v>
@@ -6224,7 +6269,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ22">
         <v>1.83</v>
@@ -6352,7 +6397,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6433,7 +6478,7 @@
         <v>1</v>
       </c>
       <c r="AQ23">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6558,7 +6603,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -6842,10 +6887,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ25">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6970,7 +7015,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -7051,7 +7096,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ26">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR26">
         <v>0</v>
@@ -7257,7 +7302,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ27">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR27">
         <v>1.64</v>
@@ -7460,10 +7505,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ28">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR28">
         <v>0.72</v>
@@ -7666,7 +7711,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ29">
         <v>0.45</v>
@@ -8000,7 +8045,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -8078,10 +8123,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ31">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR31">
         <v>1.39</v>
@@ -8412,7 +8457,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -8490,10 +8535,10 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ33">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR33">
         <v>2.47</v>
@@ -8696,7 +8741,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ34">
         <v>0.58</v>
@@ -8902,10 +8947,10 @@
         <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR35">
         <v>1.23</v>
@@ -9236,7 +9281,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9729,7 +9774,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ39">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR39">
         <v>1.5</v>
@@ -9854,7 +9899,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -9935,7 +9980,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ40">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR40">
         <v>0</v>
@@ -10138,7 +10183,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ41">
         <v>1.1</v>
@@ -10266,7 +10311,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -10553,7 +10598,7 @@
         <v>2</v>
       </c>
       <c r="AQ43">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR43">
         <v>1.87</v>
@@ -10756,7 +10801,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ44">
         <v>1.73</v>
@@ -11090,7 +11135,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -11168,7 +11213,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ46">
         <v>0.45</v>
@@ -11296,7 +11341,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -11377,7 +11422,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ47">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR47">
         <v>0</v>
@@ -11502,7 +11547,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -11580,7 +11625,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ48">
         <v>1.55</v>
@@ -11789,7 +11834,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ49">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR49">
         <v>1.41</v>
@@ -11992,7 +12037,7 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ50">
         <v>1.83</v>
@@ -12201,7 +12246,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ51">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR51">
         <v>1.36</v>
@@ -12326,7 +12371,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12407,7 +12452,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ52">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR52">
         <v>1.84</v>
@@ -12532,7 +12577,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12819,7 +12864,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ54">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR54">
         <v>1.95</v>
@@ -12944,7 +12989,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -13022,10 +13067,10 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ55">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR55">
         <v>1.22</v>
@@ -13434,10 +13479,10 @@
         <v>3</v>
       </c>
       <c r="AP57">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ57">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR57">
         <v>1.55</v>
@@ -13562,7 +13607,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13640,10 +13685,10 @@
         <v>2</v>
       </c>
       <c r="AP58">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ58">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR58">
         <v>1.87</v>
@@ -13768,7 +13813,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -13846,7 +13891,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ59">
         <v>1.73</v>
@@ -14052,7 +14097,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ60">
         <v>0.33</v>
@@ -14180,7 +14225,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14258,10 +14303,10 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ61">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR61">
         <v>1.66</v>
@@ -14386,7 +14431,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -14464,7 +14509,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ62">
         <v>0.36</v>
@@ -14592,7 +14637,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14670,7 +14715,7 @@
         <v>0.5</v>
       </c>
       <c r="AP63">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ63">
         <v>0.33</v>
@@ -14798,7 +14843,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -14876,7 +14921,7 @@
         <v>3</v>
       </c>
       <c r="AP64">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ64">
         <v>1.27</v>
@@ -15085,7 +15130,7 @@
         <v>2</v>
       </c>
       <c r="AQ65">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR65">
         <v>1.71</v>
@@ -15288,10 +15333,10 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ66">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR66">
         <v>1.35</v>
@@ -15494,10 +15539,10 @@
         <v>1</v>
       </c>
       <c r="AP67">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ67">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR67">
         <v>1.65</v>
@@ -15700,7 +15745,7 @@
         <v>2</v>
       </c>
       <c r="AP68">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ68">
         <v>0.45</v>
@@ -15828,7 +15873,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -15909,7 +15954,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ69">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR69">
         <v>1.7</v>
@@ -16112,10 +16157,10 @@
         <v>0.25</v>
       </c>
       <c r="AP70">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ70">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR70">
         <v>1.96</v>
@@ -16240,7 +16285,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16446,7 +16491,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16527,7 +16572,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ72">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR72">
         <v>1.41</v>
@@ -16730,7 +16775,7 @@
         <v>1</v>
       </c>
       <c r="AP73">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ73">
         <v>1.18</v>
@@ -16858,7 +16903,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16939,7 +16984,7 @@
         <v>2</v>
       </c>
       <c r="AQ74">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR74">
         <v>1.88</v>
@@ -17557,7 +17602,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ77">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR77">
         <v>0.9</v>
@@ -18094,7 +18139,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18175,7 +18220,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ80">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR80">
         <v>1.6</v>
@@ -18300,7 +18345,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18378,10 +18423,10 @@
         <v>0.67</v>
       </c>
       <c r="AP81">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ81">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR81">
         <v>1.62</v>
@@ -18506,7 +18551,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -18587,7 +18632,7 @@
         <v>1</v>
       </c>
       <c r="AQ82">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR82">
         <v>1.1</v>
@@ -18996,10 +19041,10 @@
         <v>1.5</v>
       </c>
       <c r="AP84">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ84">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR84">
         <v>1.92</v>
@@ -19124,7 +19169,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -19202,7 +19247,7 @@
         <v>0</v>
       </c>
       <c r="AP85">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ85">
         <v>1.83</v>
@@ -19330,7 +19375,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -19408,7 +19453,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ86">
         <v>1.55</v>
@@ -19536,7 +19581,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -19614,10 +19659,10 @@
         <v>1.5</v>
       </c>
       <c r="AP87">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ87">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR87">
         <v>1.99</v>
@@ -19820,7 +19865,7 @@
         <v>0</v>
       </c>
       <c r="AP88">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ88">
         <v>1.09</v>
@@ -20029,7 +20074,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ89">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR89">
         <v>1.83</v>
@@ -20154,7 +20199,7 @@
         <v>164</v>
       </c>
       <c r="P90" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
@@ -20232,7 +20277,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ90">
         <v>1.18</v>
@@ -20438,7 +20483,7 @@
         <v>1.5</v>
       </c>
       <c r="AP91">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ91">
         <v>1.73</v>
@@ -20850,10 +20895,10 @@
         <v>2.33</v>
       </c>
       <c r="AP93">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ93">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR93">
         <v>1.68</v>
@@ -21056,7 +21101,7 @@
         <v>1.33</v>
       </c>
       <c r="AP94">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ94">
         <v>1.55</v>
@@ -21262,10 +21307,10 @@
         <v>0.5</v>
       </c>
       <c r="AP95">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ95">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR95">
         <v>1.75</v>
@@ -21390,7 +21435,7 @@
         <v>168</v>
       </c>
       <c r="P96" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21471,7 +21516,7 @@
         <v>2</v>
       </c>
       <c r="AQ96">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR96">
         <v>2.09</v>
@@ -21674,10 +21719,10 @@
         <v>2.25</v>
       </c>
       <c r="AP97">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ97">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR97">
         <v>1.49</v>
@@ -22292,10 +22337,10 @@
         <v>1</v>
       </c>
       <c r="AP100">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ100">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR100">
         <v>1.45</v>
@@ -22501,7 +22546,7 @@
         <v>2</v>
       </c>
       <c r="AQ101">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR101">
         <v>1.75</v>
@@ -22704,7 +22749,7 @@
         <v>0.33</v>
       </c>
       <c r="AP102">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ102">
         <v>1.09</v>
@@ -22832,7 +22877,7 @@
         <v>122</v>
       </c>
       <c r="P103" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="Q103">
         <v>2.75</v>
@@ -23116,10 +23161,10 @@
         <v>0.5</v>
       </c>
       <c r="AP104">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ104">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR104">
         <v>1.95</v>
@@ -23325,7 +23370,7 @@
         <v>2</v>
       </c>
       <c r="AQ105">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR105">
         <v>1.1</v>
@@ -23734,10 +23779,10 @@
         <v>0.33</v>
       </c>
       <c r="AP107">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ107">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR107">
         <v>1.66</v>
@@ -23940,7 +23985,7 @@
         <v>0.33</v>
       </c>
       <c r="AP108">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ108">
         <v>0.58</v>
@@ -24355,7 +24400,7 @@
         <v>2</v>
       </c>
       <c r="AQ110">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR110">
         <v>1.84</v>
@@ -25098,7 +25143,7 @@
         <v>177</v>
       </c>
       <c r="P114" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25176,10 +25221,10 @@
         <v>1</v>
       </c>
       <c r="AP114">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ114">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR114">
         <v>1.81</v>
@@ -25304,7 +25349,7 @@
         <v>178</v>
       </c>
       <c r="P115" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -25588,7 +25633,7 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ116">
         <v>1.18</v>
@@ -25716,7 +25761,7 @@
         <v>179</v>
       </c>
       <c r="P117" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25922,7 +25967,7 @@
         <v>180</v>
       </c>
       <c r="P118" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -26209,7 +26254,7 @@
         <v>1</v>
       </c>
       <c r="AQ119">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR119">
         <v>0.98</v>
@@ -26334,7 +26379,7 @@
         <v>181</v>
       </c>
       <c r="P120" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -26415,7 +26460,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ120">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR120">
         <v>1.84</v>
@@ -26746,7 +26791,7 @@
         <v>109</v>
       </c>
       <c r="P122" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="Q122">
         <v>2.75</v>
@@ -26827,7 +26872,7 @@
         <v>2</v>
       </c>
       <c r="AQ122">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR122">
         <v>1.93</v>
@@ -27030,7 +27075,7 @@
         <v>1</v>
       </c>
       <c r="AP123">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ123">
         <v>1.73</v>
@@ -27158,7 +27203,7 @@
         <v>129</v>
       </c>
       <c r="P124" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="Q124">
         <v>2.5</v>
@@ -27236,10 +27281,10 @@
         <v>0.33</v>
       </c>
       <c r="AP124">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ124">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR124">
         <v>1.48</v>
@@ -27442,7 +27487,7 @@
         <v>0.5</v>
       </c>
       <c r="AP125">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ125">
         <v>0.36</v>
@@ -27857,7 +27902,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ127">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR127">
         <v>1.21</v>
@@ -28060,7 +28105,7 @@
         <v>1.5</v>
       </c>
       <c r="AP128">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ128">
         <v>1.91</v>
@@ -28188,7 +28233,7 @@
         <v>187</v>
       </c>
       <c r="P129" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28394,7 +28439,7 @@
         <v>188</v>
       </c>
       <c r="P130" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="Q130">
         <v>2.4</v>
@@ -28472,10 +28517,10 @@
         <v>1.75</v>
       </c>
       <c r="AP130">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ130">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR130">
         <v>1.45</v>
@@ -28678,10 +28723,10 @@
         <v>2</v>
       </c>
       <c r="AP131">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ131">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR131">
         <v>1.86</v>
@@ -28887,7 +28932,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ132">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR132">
         <v>1.77</v>
@@ -29093,7 +29138,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ133">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR133">
         <v>1.25</v>
@@ -29218,7 +29263,7 @@
         <v>189</v>
       </c>
       <c r="P134" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="Q134">
         <v>3</v>
@@ -29296,10 +29341,10 @@
         <v>0.75</v>
       </c>
       <c r="AP134">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ134">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR134">
         <v>1.31</v>
@@ -29424,7 +29469,7 @@
         <v>190</v>
       </c>
       <c r="P135" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -29502,7 +29547,7 @@
         <v>0</v>
       </c>
       <c r="AP135">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ135">
         <v>1</v>
@@ -29708,7 +29753,7 @@
         <v>0.75</v>
       </c>
       <c r="AP136">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ136">
         <v>1</v>
@@ -29917,7 +29962,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ137">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR137">
         <v>1.09</v>
@@ -30120,10 +30165,10 @@
         <v>1</v>
       </c>
       <c r="AP138">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ138">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR138">
         <v>1.73</v>
@@ -30326,10 +30371,10 @@
         <v>0.29</v>
       </c>
       <c r="AP139">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ139">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR139">
         <v>1.51</v>
@@ -30532,7 +30577,7 @@
         <v>0.33</v>
       </c>
       <c r="AP140">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ140">
         <v>0.36</v>
@@ -30660,7 +30705,7 @@
         <v>109</v>
       </c>
       <c r="P141" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="Q141">
         <v>2.38</v>
@@ -30738,10 +30783,10 @@
         <v>1</v>
       </c>
       <c r="AP141">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ141">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR141">
         <v>1.68</v>
@@ -31072,7 +31117,7 @@
         <v>174</v>
       </c>
       <c r="P143" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -31150,10 +31195,10 @@
         <v>0.75</v>
       </c>
       <c r="AP143">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ143">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR143">
         <v>1.8</v>
@@ -31356,10 +31401,10 @@
         <v>1.5</v>
       </c>
       <c r="AP144">
+        <v>1.08</v>
+      </c>
+      <c r="AQ144">
         <v>1.18</v>
-      </c>
-      <c r="AQ144">
-        <v>1</v>
       </c>
       <c r="AR144">
         <v>1.61</v>
@@ -31484,7 +31529,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="Q145">
         <v>2.4</v>
@@ -31562,10 +31607,10 @@
         <v>1.8</v>
       </c>
       <c r="AP145">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ145">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR145">
         <v>1.94</v>
@@ -31690,7 +31735,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31896,7 +31941,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="Q147">
         <v>2.6</v>
@@ -31974,10 +32019,10 @@
         <v>2</v>
       </c>
       <c r="AP147">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ147">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR147">
         <v>1.85</v>
@@ -32102,7 +32147,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="Q148">
         <v>2.05</v>
@@ -32183,7 +32228,7 @@
         <v>2</v>
       </c>
       <c r="AQ148">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR148">
         <v>1.55</v>
@@ -32308,7 +32353,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -32514,7 +32559,7 @@
         <v>202</v>
       </c>
       <c r="P150" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="Q150">
         <v>2.4</v>
@@ -32592,7 +32637,7 @@
         <v>1.75</v>
       </c>
       <c r="AP150">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ150">
         <v>1.1</v>
@@ -32798,7 +32843,7 @@
         <v>0.75</v>
       </c>
       <c r="AP151">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ151">
         <v>1.73</v>
@@ -32926,7 +32971,7 @@
         <v>109</v>
       </c>
       <c r="P152" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="Q152">
         <v>2.88</v>
@@ -33007,7 +33052,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ152">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR152">
         <v>1.12</v>
@@ -33338,7 +33383,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="Q154">
         <v>3.1</v>
@@ -33544,7 +33589,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="Q155">
         <v>2.2</v>
@@ -33831,7 +33876,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ156">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR156">
         <v>1.51</v>
@@ -33956,7 +34001,7 @@
         <v>109</v>
       </c>
       <c r="P157" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="Q157">
         <v>3.2</v>
@@ -34446,10 +34491,10 @@
         <v>2</v>
       </c>
       <c r="AP159">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ159">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR159">
         <v>1.77</v>
@@ -34574,7 +34619,7 @@
         <v>209</v>
       </c>
       <c r="P160" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="Q160">
         <v>2.1</v>
@@ -34655,7 +34700,7 @@
         <v>2</v>
       </c>
       <c r="AQ160">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR160">
         <v>1.99</v>
@@ -35064,7 +35109,7 @@
         <v>2</v>
       </c>
       <c r="AP162">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ162">
         <v>1.1</v>
@@ -35270,7 +35315,7 @@
         <v>1</v>
       </c>
       <c r="AP163">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ163">
         <v>0.45</v>
@@ -36094,10 +36139,10 @@
         <v>2.5</v>
       </c>
       <c r="AP167">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ167">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR167">
         <v>1.76</v>
@@ -36303,7 +36348,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ168">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR168">
         <v>1.25</v>
@@ -36428,7 +36473,7 @@
         <v>217</v>
       </c>
       <c r="P169" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="Q169">
         <v>3</v>
@@ -36506,10 +36551,10 @@
         <v>2.5</v>
       </c>
       <c r="AP169">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ169">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR169">
         <v>1.68</v>
@@ -36634,7 +36679,7 @@
         <v>218</v>
       </c>
       <c r="P170" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -36712,10 +36757,10 @@
         <v>1.67</v>
       </c>
       <c r="AP170">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ170">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR170">
         <v>1.89</v>
@@ -36921,7 +36966,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ171">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR171">
         <v>1.87</v>
@@ -37124,10 +37169,10 @@
         <v>1.2</v>
       </c>
       <c r="AP172">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ172">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR172">
         <v>1.8</v>
@@ -37330,7 +37375,7 @@
         <v>0.33</v>
       </c>
       <c r="AP173">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ173">
         <v>0.33</v>
@@ -37458,7 +37503,7 @@
         <v>221</v>
       </c>
       <c r="P174" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="Q174">
         <v>2.5</v>
@@ -37539,7 +37584,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ174">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR174">
         <v>1.03</v>
@@ -37664,7 +37709,7 @@
         <v>163</v>
       </c>
       <c r="P175" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -37742,7 +37787,7 @@
         <v>0.83</v>
       </c>
       <c r="AP175">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ175">
         <v>1.09</v>
@@ -37948,7 +37993,7 @@
         <v>0.8</v>
       </c>
       <c r="AP176">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ176">
         <v>0.58</v>
@@ -38076,7 +38121,7 @@
         <v>222</v>
       </c>
       <c r="P177" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -38282,7 +38327,7 @@
         <v>109</v>
       </c>
       <c r="P178" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="Q178">
         <v>2.38</v>
@@ -38566,7 +38611,7 @@
         <v>0.6</v>
       </c>
       <c r="AP179">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ179">
         <v>1</v>
@@ -38694,7 +38739,7 @@
         <v>224</v>
       </c>
       <c r="P180" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -38775,7 +38820,7 @@
         <v>2</v>
       </c>
       <c r="AQ180">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR180">
         <v>2.03</v>
@@ -38981,7 +39026,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ181">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR181">
         <v>1.42</v>
@@ -39106,7 +39151,7 @@
         <v>225</v>
       </c>
       <c r="P182" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="Q182">
         <v>3.75</v>
@@ -39187,7 +39232,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ182">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR182">
         <v>1.89</v>
@@ -39312,7 +39357,7 @@
         <v>226</v>
       </c>
       <c r="P183" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="Q183">
         <v>2.5</v>
@@ -39390,7 +39435,7 @@
         <v>0.67</v>
       </c>
       <c r="AP183">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ183">
         <v>0.58</v>
@@ -39518,7 +39563,7 @@
         <v>227</v>
       </c>
       <c r="P184" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="Q184">
         <v>2.05</v>
@@ -39596,7 +39641,7 @@
         <v>0.29</v>
       </c>
       <c r="AP184">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ184">
         <v>0.33</v>
@@ -39930,7 +39975,7 @@
         <v>228</v>
       </c>
       <c r="P186" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="Q186">
         <v>2.4</v>
@@ -40008,7 +40053,7 @@
         <v>0.4</v>
       </c>
       <c r="AP186">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ186">
         <v>0.58</v>
@@ -40214,7 +40259,7 @@
         <v>1.83</v>
       </c>
       <c r="AP187">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ187">
         <v>1.73</v>
@@ -40342,7 +40387,7 @@
         <v>230</v>
       </c>
       <c r="P188" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40548,7 +40593,7 @@
         <v>176</v>
       </c>
       <c r="P189" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -41244,10 +41289,10 @@
         <v>1.33</v>
       </c>
       <c r="AP192">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ192">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR192">
         <v>1.75</v>
@@ -41372,7 +41417,7 @@
         <v>233</v>
       </c>
       <c r="P193" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41450,10 +41495,10 @@
         <v>2</v>
       </c>
       <c r="AP193">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ193">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR193">
         <v>2.11</v>
@@ -41578,7 +41623,7 @@
         <v>234</v>
       </c>
       <c r="P194" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -41659,7 +41704,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ194">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR194">
         <v>1.58</v>
@@ -41990,7 +42035,7 @@
         <v>198</v>
       </c>
       <c r="P196" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="Q196">
         <v>2.63</v>
@@ -42274,7 +42319,7 @@
         <v>1.8</v>
       </c>
       <c r="AP197">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ197">
         <v>1.73</v>
@@ -42402,7 +42447,7 @@
         <v>103</v>
       </c>
       <c r="P198" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="Q198">
         <v>2.63</v>
@@ -42480,10 +42525,10 @@
         <v>1.5</v>
       </c>
       <c r="AP198">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ198">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR198">
         <v>1.72</v>
@@ -42892,7 +42937,7 @@
         <v>0.83</v>
       </c>
       <c r="AP200">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ200">
         <v>0.45</v>
@@ -43098,10 +43143,10 @@
         <v>0.67</v>
       </c>
       <c r="AP201">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ201">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR201">
         <v>1.89</v>
@@ -43307,7 +43352,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ202">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR202">
         <v>1.61</v>
@@ -43432,7 +43477,7 @@
         <v>109</v>
       </c>
       <c r="P203" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="Q203">
         <v>2.63</v>
@@ -43719,7 +43764,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ204">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR204">
         <v>1.79</v>
@@ -43844,7 +43889,7 @@
         <v>237</v>
       </c>
       <c r="P205" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -43922,7 +43967,7 @@
         <v>1</v>
       </c>
       <c r="AP205">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ205">
         <v>1.09</v>
@@ -44128,7 +44173,7 @@
         <v>0.57</v>
       </c>
       <c r="AP206">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ206">
         <v>1</v>
@@ -44256,7 +44301,7 @@
         <v>109</v>
       </c>
       <c r="P207" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="Q207">
         <v>2.25</v>
@@ -44540,10 +44585,10 @@
         <v>0.83</v>
       </c>
       <c r="AP208">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ208">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR208">
         <v>1.53</v>
@@ -44746,10 +44791,10 @@
         <v>1.71</v>
       </c>
       <c r="AP209">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ209">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR209">
         <v>2.06</v>
@@ -44952,7 +44997,7 @@
         <v>0.25</v>
       </c>
       <c r="AP210">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ210">
         <v>0.33</v>
@@ -45080,7 +45125,7 @@
         <v>240</v>
       </c>
       <c r="P211" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="Q211">
         <v>3.2</v>
@@ -45158,10 +45203,10 @@
         <v>2</v>
       </c>
       <c r="AP211">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ211">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR211">
         <v>1.68</v>
@@ -45286,7 +45331,7 @@
         <v>109</v>
       </c>
       <c r="P212" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45492,7 +45537,7 @@
         <v>241</v>
       </c>
       <c r="P213" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="Q213">
         <v>4</v>
@@ -45573,7 +45618,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ213">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR213">
         <v>1.55</v>
@@ -45776,7 +45821,7 @@
         <v>1.57</v>
       </c>
       <c r="AP214">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ214">
         <v>1.1</v>
@@ -45904,7 +45949,7 @@
         <v>242</v>
       </c>
       <c r="P215" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -45982,10 +46027,10 @@
         <v>1.83</v>
       </c>
       <c r="AP215">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ215">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR215">
         <v>1.85</v>
@@ -46110,7 +46155,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="Q216">
         <v>3.4</v>
@@ -46316,7 +46361,7 @@
         <v>243</v>
       </c>
       <c r="P217" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="Q217">
         <v>2.75</v>
@@ -46397,7 +46442,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ217">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR217">
         <v>1.58</v>
@@ -46600,10 +46645,10 @@
         <v>1</v>
       </c>
       <c r="AP218">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ218">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR218">
         <v>1.82</v>
@@ -46728,7 +46773,7 @@
         <v>244</v>
       </c>
       <c r="P219" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="Q219">
         <v>3.1</v>
@@ -46809,7 +46854,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ219">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR219">
         <v>1.44</v>
@@ -47140,7 +47185,7 @@
         <v>246</v>
       </c>
       <c r="P221" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="Q221">
         <v>2.6</v>
@@ -47218,7 +47263,7 @@
         <v>1</v>
       </c>
       <c r="AP221">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ221">
         <v>1.18</v>
@@ -47346,7 +47391,7 @@
         <v>247</v>
       </c>
       <c r="P222" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="Q222">
         <v>2.5</v>
@@ -47427,7 +47472,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ222">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR222">
         <v>1.71</v>
@@ -47552,7 +47597,7 @@
         <v>248</v>
       </c>
       <c r="P223" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47630,7 +47675,7 @@
         <v>1.63</v>
       </c>
       <c r="AP223">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ223">
         <v>1.83</v>
@@ -47758,7 +47803,7 @@
         <v>249</v>
       </c>
       <c r="P224" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47836,7 +47881,7 @@
         <v>1.43</v>
       </c>
       <c r="AP224">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ224">
         <v>1.55</v>
@@ -47964,7 +48009,7 @@
         <v>250</v>
       </c>
       <c r="P225" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -48042,10 +48087,10 @@
         <v>1.5</v>
       </c>
       <c r="AP225">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ225">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR225">
         <v>1.88</v>
@@ -48170,7 +48215,7 @@
         <v>251</v>
       </c>
       <c r="P226" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="Q226">
         <v>2.75</v>
@@ -48251,7 +48296,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ226">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR226">
         <v>1.23</v>
@@ -48376,7 +48421,7 @@
         <v>252</v>
       </c>
       <c r="P227" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="Q227">
         <v>1.83</v>
@@ -48457,7 +48502,7 @@
         <v>2</v>
       </c>
       <c r="AQ227">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR227">
         <v>1.5</v>
@@ -48582,7 +48627,7 @@
         <v>253</v>
       </c>
       <c r="P228" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48660,7 +48705,7 @@
         <v>0.57</v>
       </c>
       <c r="AP228">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ228">
         <v>0.58</v>
@@ -48788,7 +48833,7 @@
         <v>109</v>
       </c>
       <c r="P229" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="Q229">
         <v>2.5</v>
@@ -48994,7 +49039,7 @@
         <v>254</v>
       </c>
       <c r="P230" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="Q230">
         <v>3.25</v>
@@ -49200,7 +49245,7 @@
         <v>119</v>
       </c>
       <c r="P231" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="Q231">
         <v>2.4</v>
@@ -49484,7 +49529,7 @@
         <v>1.5</v>
       </c>
       <c r="AP232">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ232">
         <v>1.91</v>
@@ -49693,7 +49738,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ233">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR233">
         <v>1.67</v>
@@ -49818,7 +49863,7 @@
         <v>109</v>
       </c>
       <c r="P234" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="Q234">
         <v>2.5</v>
@@ -49896,7 +49941,7 @@
         <v>1.17</v>
       </c>
       <c r="AP234">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ234">
         <v>1.27</v>
@@ -50102,10 +50147,10 @@
         <v>1.14</v>
       </c>
       <c r="AP235">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ235">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR235">
         <v>1.24</v>
@@ -50436,7 +50481,7 @@
         <v>258</v>
       </c>
       <c r="P237" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="Q237">
         <v>2.75</v>
@@ -50642,7 +50687,7 @@
         <v>259</v>
       </c>
       <c r="P238" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="Q238">
         <v>2.6</v>
@@ -50720,10 +50765,10 @@
         <v>0.86</v>
       </c>
       <c r="AP238">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ238">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR238">
         <v>1.87</v>
@@ -50848,7 +50893,7 @@
         <v>109</v>
       </c>
       <c r="P239" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -51054,7 +51099,7 @@
         <v>140</v>
       </c>
       <c r="P240" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -51132,10 +51177,10 @@
         <v>0.71</v>
       </c>
       <c r="AP240">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ240">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR240">
         <v>1.88</v>
@@ -51341,7 +51386,7 @@
         <v>2</v>
       </c>
       <c r="AQ241">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR241">
         <v>1.5</v>
@@ -51466,7 +51511,7 @@
         <v>109</v>
       </c>
       <c r="P242" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="Q242">
         <v>3.1</v>
@@ -51547,7 +51592,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ242">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR242">
         <v>1.55</v>
@@ -51750,7 +51795,7 @@
         <v>0.33</v>
       </c>
       <c r="AP243">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ243">
         <v>0.36</v>
@@ -51878,7 +51923,7 @@
         <v>161</v>
       </c>
       <c r="P244" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="Q244">
         <v>2.1</v>
@@ -51956,10 +52001,10 @@
         <v>1.5</v>
       </c>
       <c r="AP244">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ244">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR244">
         <v>1.92</v>
@@ -52290,7 +52335,7 @@
         <v>156</v>
       </c>
       <c r="P246" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="Q246">
         <v>2.5</v>
@@ -52368,7 +52413,7 @@
         <v>0.63</v>
       </c>
       <c r="AP246">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ246">
         <v>1</v>
@@ -52574,10 +52619,10 @@
         <v>0.89</v>
       </c>
       <c r="AP247">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ247">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR247">
         <v>1.45</v>
@@ -52780,10 +52825,10 @@
         <v>1</v>
       </c>
       <c r="AP248">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ248">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR248">
         <v>1.82</v>
@@ -52908,7 +52953,7 @@
         <v>264</v>
       </c>
       <c r="P249" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="Q249">
         <v>2.5</v>
@@ -52986,7 +53031,7 @@
         <v>1.5</v>
       </c>
       <c r="AP249">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ249">
         <v>1.73</v>
@@ -53114,7 +53159,7 @@
         <v>265</v>
       </c>
       <c r="P250" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="Q250">
         <v>3.2</v>
@@ -53195,7 +53240,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ250">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR250">
         <v>1.23</v>
@@ -53320,7 +53365,7 @@
         <v>109</v>
       </c>
       <c r="P251" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="Q251">
         <v>2.75</v>
@@ -53401,7 +53446,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ251">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR251">
         <v>1.67</v>
@@ -53526,7 +53571,7 @@
         <v>266</v>
       </c>
       <c r="P252" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="Q252">
         <v>2.25</v>
@@ -53604,7 +53649,7 @@
         <v>0.63</v>
       </c>
       <c r="AP252">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ252">
         <v>0.45</v>
@@ -54350,7 +54395,7 @@
         <v>270</v>
       </c>
       <c r="P256" t="s">
-        <v>435</v>
+        <v>331</v>
       </c>
       <c r="Q256">
         <v>2.25</v>
@@ -54428,7 +54473,7 @@
         <v>1.25</v>
       </c>
       <c r="AP256">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ256">
         <v>1.27</v>
@@ -54556,7 +54601,7 @@
         <v>271</v>
       </c>
       <c r="P257" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="Q257">
         <v>2.63</v>
@@ -54762,7 +54807,7 @@
         <v>272</v>
       </c>
       <c r="P258" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="Q258">
         <v>2.3</v>
@@ -54843,7 +54888,7 @@
         <v>2</v>
       </c>
       <c r="AQ258">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR258">
         <v>1.85</v>
@@ -54968,7 +55013,7 @@
         <v>109</v>
       </c>
       <c r="P259" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="Q259">
         <v>3.1</v>
@@ -55252,7 +55297,7 @@
         <v>0.78</v>
       </c>
       <c r="AP260">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ260">
         <v>0.58</v>
@@ -55380,7 +55425,7 @@
         <v>274</v>
       </c>
       <c r="P261" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -55458,7 +55503,7 @@
         <v>1.29</v>
       </c>
       <c r="AP261">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ261">
         <v>1.91</v>
@@ -55586,7 +55631,7 @@
         <v>275</v>
       </c>
       <c r="P262" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="Q262">
         <v>2.5</v>
@@ -55667,7 +55712,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ262">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR262">
         <v>1.61</v>
@@ -55792,7 +55837,7 @@
         <v>234</v>
       </c>
       <c r="P263" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="Q263">
         <v>2.25</v>
@@ -55870,10 +55915,10 @@
         <v>0.5</v>
       </c>
       <c r="AP263">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ263">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR263">
         <v>1.72</v>
@@ -55998,7 +56043,7 @@
         <v>109</v>
       </c>
       <c r="P264" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="Q264">
         <v>2.75</v>
@@ -56204,7 +56249,7 @@
         <v>276</v>
       </c>
       <c r="P265" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="Q265">
         <v>2.88</v>
@@ -56410,7 +56455,7 @@
         <v>109</v>
       </c>
       <c r="P266" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="Q266">
         <v>3.4</v>
@@ -56697,7 +56742,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ267">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR267">
         <v>1.45</v>
@@ -56822,7 +56867,7 @@
         <v>278</v>
       </c>
       <c r="P268" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="Q268">
         <v>2.2</v>
@@ -57028,7 +57073,7 @@
         <v>279</v>
       </c>
       <c r="P269" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57234,7 +57279,7 @@
         <v>280</v>
       </c>
       <c r="P270" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="Q270">
         <v>3.35</v>
@@ -57646,7 +57691,7 @@
         <v>282</v>
       </c>
       <c r="P272" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="Q272">
         <v>2.38</v>
@@ -57724,7 +57769,7 @@
         <v>1.25</v>
       </c>
       <c r="AP272">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ272">
         <v>1.18</v>
@@ -57852,7 +57897,7 @@
         <v>283</v>
       </c>
       <c r="P273" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="Q273">
         <v>3.4</v>
@@ -58058,7 +58103,7 @@
         <v>284</v>
       </c>
       <c r="P274" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="Q274">
         <v>3</v>
@@ -58470,7 +58515,7 @@
         <v>285</v>
       </c>
       <c r="P276" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="Q276">
         <v>2.63</v>
@@ -58676,7 +58721,7 @@
         <v>286</v>
       </c>
       <c r="P277" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -59088,7 +59133,7 @@
         <v>288</v>
       </c>
       <c r="P279" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="Q279">
         <v>2.63</v>
@@ -59166,7 +59211,7 @@
         <v>1.73</v>
       </c>
       <c r="AP279">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ279">
         <v>1.83</v>
@@ -59500,7 +59545,7 @@
         <v>290</v>
       </c>
       <c r="P281" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="Q281">
         <v>2.25</v>
@@ -59581,7 +59626,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ281">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR281">
         <v>1.36</v>
@@ -59706,7 +59751,7 @@
         <v>291</v>
       </c>
       <c r="P282" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="Q282">
         <v>2.88</v>
@@ -59784,7 +59829,7 @@
         <v>1.67</v>
       </c>
       <c r="AP282">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AQ282">
         <v>1.73</v>
@@ -59993,7 +60038,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ283">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR283">
         <v>1.54</v>
@@ -60324,7 +60369,7 @@
         <v>293</v>
       </c>
       <c r="P285" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="Q285">
         <v>2.5</v>
@@ -60530,7 +60575,7 @@
         <v>294</v>
       </c>
       <c r="P286" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -60814,7 +60859,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP287">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ287">
         <v>0.45</v>
@@ -61023,7 +61068,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ288">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR288">
         <v>1.64</v>
@@ -61226,7 +61271,7 @@
         <v>0.27</v>
       </c>
       <c r="AP289">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ289">
         <v>0.33</v>
@@ -61432,10 +61477,10 @@
         <v>1.11</v>
       </c>
       <c r="AP290">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ290">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR290">
         <v>1.98</v>
@@ -61847,7 +61892,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ292">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR292">
         <v>1.84</v>
@@ -62053,7 +62098,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ293">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR293">
         <v>1.78</v>
@@ -62178,7 +62223,7 @@
         <v>112</v>
       </c>
       <c r="P294" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="Q294">
         <v>3.1</v>
@@ -62384,7 +62429,7 @@
         <v>122</v>
       </c>
       <c r="P295" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="Q295">
         <v>2.4</v>
@@ -62668,10 +62713,10 @@
         <v>2</v>
       </c>
       <c r="AP296">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ296">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR296">
         <v>1.45</v>
@@ -62796,7 +62841,7 @@
         <v>301</v>
       </c>
       <c r="P297" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="Q297">
         <v>3.4</v>
@@ -62874,7 +62919,7 @@
         <v>1.6</v>
       </c>
       <c r="AP297">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ297">
         <v>1.55</v>
@@ -63208,7 +63253,7 @@
         <v>302</v>
       </c>
       <c r="P299" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="Q299">
         <v>3.2</v>
@@ -63289,7 +63334,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ299">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR299">
         <v>1.55</v>
@@ -63492,10 +63537,10 @@
         <v>1.8</v>
       </c>
       <c r="AP300">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ300">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AR300">
         <v>1.88</v>
@@ -63698,7 +63743,7 @@
         <v>1.9</v>
       </c>
       <c r="AP301">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ301">
         <v>1.73</v>
@@ -63826,7 +63871,7 @@
         <v>305</v>
       </c>
       <c r="P302" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="Q302">
         <v>2.2</v>
@@ -64032,7 +64077,7 @@
         <v>255</v>
       </c>
       <c r="P303" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="Q303">
         <v>2.5</v>
@@ -64110,7 +64155,7 @@
         <v>0.6</v>
       </c>
       <c r="AP303">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ303">
         <v>0.58</v>
@@ -64238,7 +64283,7 @@
         <v>306</v>
       </c>
       <c r="P304" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="Q304">
         <v>2.5</v>
@@ -64316,10 +64361,10 @@
         <v>1.6</v>
       </c>
       <c r="AP304">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ304">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR304">
         <v>1.33</v>
@@ -64444,7 +64489,7 @@
         <v>307</v>
       </c>
       <c r="P305" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -64522,7 +64567,7 @@
         <v>1.11</v>
       </c>
       <c r="AP305">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ305">
         <v>1.18</v>
@@ -64728,10 +64773,10 @@
         <v>1.5</v>
       </c>
       <c r="AP306">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ306">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR306">
         <v>1.96</v>
@@ -64856,7 +64901,7 @@
         <v>199</v>
       </c>
       <c r="P307" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="Q307">
         <v>3.26</v>
@@ -64937,7 +64982,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ307">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR307">
         <v>1.51</v>
@@ -65143,7 +65188,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ308">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR308">
         <v>1.83</v>
@@ -65346,7 +65391,7 @@
         <v>0.64</v>
       </c>
       <c r="AP309">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ309">
         <v>0.58</v>
@@ -65680,7 +65725,7 @@
         <v>312</v>
       </c>
       <c r="P311" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="Q311">
         <v>1.83</v>
@@ -65758,10 +65803,10 @@
         <v>0.73</v>
       </c>
       <c r="AP311">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ311">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR311">
         <v>1.9</v>
@@ -66173,7 +66218,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ313">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR313">
         <v>1.62</v>
@@ -66298,7 +66343,7 @@
         <v>288</v>
       </c>
       <c r="P314" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="Q314">
         <v>0</v>
@@ -66504,7 +66549,7 @@
         <v>314</v>
       </c>
       <c r="P315" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="Q315">
         <v>3.5</v>
@@ -66788,7 +66833,7 @@
         <v>1.4</v>
       </c>
       <c r="AP316">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ316">
         <v>1.27</v>
@@ -66916,7 +66961,7 @@
         <v>316</v>
       </c>
       <c r="P317" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="Q317">
         <v>2.63</v>
@@ -66994,10 +67039,10 @@
         <v>1.44</v>
       </c>
       <c r="AP317">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ317">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR317">
         <v>1.77</v>
@@ -67200,10 +67245,10 @@
         <v>0.78</v>
       </c>
       <c r="AP318">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ318">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="AR318">
         <v>1.64</v>
@@ -67409,7 +67454,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ319">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR319">
         <v>1.45</v>
@@ -67740,7 +67785,7 @@
         <v>320</v>
       </c>
       <c r="P321" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="Q321">
         <v>2.2</v>
@@ -67818,10 +67863,10 @@
         <v>0.89</v>
       </c>
       <c r="AP321">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ321">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR321">
         <v>1.42</v>
@@ -68027,7 +68072,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ322">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR322">
         <v>1.83</v>
@@ -68152,7 +68197,7 @@
         <v>322</v>
       </c>
       <c r="P323" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="Q323">
         <v>2.63</v>
@@ -68309,6 +68354,2890 @@
       </c>
       <c r="BP323">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="324" spans="1:68">
+      <c r="A324" s="1">
+        <v>323</v>
+      </c>
+      <c r="B324">
+        <v>7781407</v>
+      </c>
+      <c r="C324" t="s">
+        <v>68</v>
+      </c>
+      <c r="D324" t="s">
+        <v>69</v>
+      </c>
+      <c r="E324" s="2">
+        <v>45854.85416666666</v>
+      </c>
+      <c r="F324">
+        <v>0</v>
+      </c>
+      <c r="G324" t="s">
+        <v>89</v>
+      </c>
+      <c r="H324" t="s">
+        <v>99</v>
+      </c>
+      <c r="I324">
+        <v>1</v>
+      </c>
+      <c r="J324">
+        <v>1</v>
+      </c>
+      <c r="K324">
+        <v>2</v>
+      </c>
+      <c r="L324">
+        <v>2</v>
+      </c>
+      <c r="M324">
+        <v>1</v>
+      </c>
+      <c r="N324">
+        <v>3</v>
+      </c>
+      <c r="O324" t="s">
+        <v>323</v>
+      </c>
+      <c r="P324" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q324">
+        <v>2</v>
+      </c>
+      <c r="R324">
+        <v>2.37</v>
+      </c>
+      <c r="S324">
+        <v>5</v>
+      </c>
+      <c r="T324">
+        <v>1.28</v>
+      </c>
+      <c r="U324">
+        <v>3.4</v>
+      </c>
+      <c r="V324">
+        <v>2.25</v>
+      </c>
+      <c r="W324">
+        <v>1.57</v>
+      </c>
+      <c r="X324">
+        <v>5</v>
+      </c>
+      <c r="Y324">
+        <v>1.14</v>
+      </c>
+      <c r="Z324">
+        <v>1.38</v>
+      </c>
+      <c r="AA324">
+        <v>4.3</v>
+      </c>
+      <c r="AB324">
+        <v>6</v>
+      </c>
+      <c r="AC324">
+        <v>1.04</v>
+      </c>
+      <c r="AD324">
+        <v>10</v>
+      </c>
+      <c r="AE324">
+        <v>1.2</v>
+      </c>
+      <c r="AF324">
+        <v>4.33</v>
+      </c>
+      <c r="AG324">
+        <v>1.52</v>
+      </c>
+      <c r="AH324">
+        <v>2.35</v>
+      </c>
+      <c r="AI324">
+        <v>1.7</v>
+      </c>
+      <c r="AJ324">
+        <v>2</v>
+      </c>
+      <c r="AK324">
+        <v>1.14</v>
+      </c>
+      <c r="AL324">
+        <v>1.21</v>
+      </c>
+      <c r="AM324">
+        <v>2.4</v>
+      </c>
+      <c r="AN324">
+        <v>2.18</v>
+      </c>
+      <c r="AO324">
+        <v>0.75</v>
+      </c>
+      <c r="AP324">
+        <v>2.25</v>
+      </c>
+      <c r="AQ324">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR324">
+        <v>1.89</v>
+      </c>
+      <c r="AS324">
+        <v>1.31</v>
+      </c>
+      <c r="AT324">
+        <v>3.2</v>
+      </c>
+      <c r="AU324">
+        <v>7</v>
+      </c>
+      <c r="AV324">
+        <v>5</v>
+      </c>
+      <c r="AW324">
+        <v>10</v>
+      </c>
+      <c r="AX324">
+        <v>7</v>
+      </c>
+      <c r="AY324">
+        <v>17</v>
+      </c>
+      <c r="AZ324">
+        <v>12</v>
+      </c>
+      <c r="BA324">
+        <v>9</v>
+      </c>
+      <c r="BB324">
+        <v>4</v>
+      </c>
+      <c r="BC324">
+        <v>13</v>
+      </c>
+      <c r="BD324">
+        <v>1.44</v>
+      </c>
+      <c r="BE324">
+        <v>7</v>
+      </c>
+      <c r="BF324">
+        <v>3.15</v>
+      </c>
+      <c r="BG324">
+        <v>1.28</v>
+      </c>
+      <c r="BH324">
+        <v>3.2</v>
+      </c>
+      <c r="BI324">
+        <v>1.49</v>
+      </c>
+      <c r="BJ324">
+        <v>2.4</v>
+      </c>
+      <c r="BK324">
+        <v>1.81</v>
+      </c>
+      <c r="BL324">
+        <v>1.88</v>
+      </c>
+      <c r="BM324">
+        <v>2.25</v>
+      </c>
+      <c r="BN324">
+        <v>1.55</v>
+      </c>
+      <c r="BO324">
+        <v>2.9</v>
+      </c>
+      <c r="BP324">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="325" spans="1:68">
+      <c r="A325" s="1">
+        <v>324</v>
+      </c>
+      <c r="B325">
+        <v>7781405</v>
+      </c>
+      <c r="C325" t="s">
+        <v>68</v>
+      </c>
+      <c r="D325" t="s">
+        <v>69</v>
+      </c>
+      <c r="E325" s="2">
+        <v>45854.85416666666</v>
+      </c>
+      <c r="F325">
+        <v>0</v>
+      </c>
+      <c r="G325" t="s">
+        <v>88</v>
+      </c>
+      <c r="H325" t="s">
+        <v>87</v>
+      </c>
+      <c r="I325">
+        <v>0</v>
+      </c>
+      <c r="J325">
+        <v>2</v>
+      </c>
+      <c r="K325">
+        <v>2</v>
+      </c>
+      <c r="L325">
+        <v>5</v>
+      </c>
+      <c r="M325">
+        <v>3</v>
+      </c>
+      <c r="N325">
+        <v>8</v>
+      </c>
+      <c r="O325" t="s">
+        <v>324</v>
+      </c>
+      <c r="P325" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q325">
+        <v>2.3</v>
+      </c>
+      <c r="R325">
+        <v>2.2</v>
+      </c>
+      <c r="S325">
+        <v>4.2</v>
+      </c>
+      <c r="T325">
+        <v>1.33</v>
+      </c>
+      <c r="U325">
+        <v>3</v>
+      </c>
+      <c r="V325">
+        <v>2.5</v>
+      </c>
+      <c r="W325">
+        <v>1.46</v>
+      </c>
+      <c r="X325">
+        <v>6</v>
+      </c>
+      <c r="Y325">
+        <v>1.11</v>
+      </c>
+      <c r="Z325">
+        <v>1.74</v>
+      </c>
+      <c r="AA325">
+        <v>3.5</v>
+      </c>
+      <c r="AB325">
+        <v>3.87</v>
+      </c>
+      <c r="AC325">
+        <v>1.05</v>
+      </c>
+      <c r="AD325">
+        <v>9.5</v>
+      </c>
+      <c r="AE325">
+        <v>1.25</v>
+      </c>
+      <c r="AF325">
+        <v>3.8</v>
+      </c>
+      <c r="AG325">
+        <v>1.67</v>
+      </c>
+      <c r="AH325">
+        <v>2.07</v>
+      </c>
+      <c r="AI325">
+        <v>1.7</v>
+      </c>
+      <c r="AJ325">
+        <v>2</v>
+      </c>
+      <c r="AK325">
+        <v>1.23</v>
+      </c>
+      <c r="AL325">
+        <v>1.26</v>
+      </c>
+      <c r="AM325">
+        <v>1.95</v>
+      </c>
+      <c r="AN325">
+        <v>2.3</v>
+      </c>
+      <c r="AO325">
+        <v>1.42</v>
+      </c>
+      <c r="AP325">
+        <v>2.36</v>
+      </c>
+      <c r="AQ325">
+        <v>1.31</v>
+      </c>
+      <c r="AR325">
+        <v>1.74</v>
+      </c>
+      <c r="AS325">
+        <v>1.51</v>
+      </c>
+      <c r="AT325">
+        <v>3.25</v>
+      </c>
+      <c r="AU325">
+        <v>7</v>
+      </c>
+      <c r="AV325">
+        <v>9</v>
+      </c>
+      <c r="AW325">
+        <v>12</v>
+      </c>
+      <c r="AX325">
+        <v>7</v>
+      </c>
+      <c r="AY325">
+        <v>19</v>
+      </c>
+      <c r="AZ325">
+        <v>16</v>
+      </c>
+      <c r="BA325">
+        <v>3</v>
+      </c>
+      <c r="BB325">
+        <v>4</v>
+      </c>
+      <c r="BC325">
+        <v>7</v>
+      </c>
+      <c r="BD325">
+        <v>1.54</v>
+      </c>
+      <c r="BE325">
+        <v>6.75</v>
+      </c>
+      <c r="BF325">
+        <v>2.7</v>
+      </c>
+      <c r="BG325">
+        <v>1.3</v>
+      </c>
+      <c r="BH325">
+        <v>3.05</v>
+      </c>
+      <c r="BI325">
+        <v>1.52</v>
+      </c>
+      <c r="BJ325">
+        <v>2.32</v>
+      </c>
+      <c r="BK325">
+        <v>1.86</v>
+      </c>
+      <c r="BL325">
+        <v>1.82</v>
+      </c>
+      <c r="BM325">
+        <v>2.33</v>
+      </c>
+      <c r="BN325">
+        <v>1.5</v>
+      </c>
+      <c r="BO325">
+        <v>3.05</v>
+      </c>
+      <c r="BP325">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="326" spans="1:68">
+      <c r="A326" s="1">
+        <v>325</v>
+      </c>
+      <c r="B326">
+        <v>7781404</v>
+      </c>
+      <c r="C326" t="s">
+        <v>68</v>
+      </c>
+      <c r="D326" t="s">
+        <v>69</v>
+      </c>
+      <c r="E326" s="2">
+        <v>45854.85416666666</v>
+      </c>
+      <c r="F326">
+        <v>0</v>
+      </c>
+      <c r="G326" t="s">
+        <v>73</v>
+      </c>
+      <c r="H326" t="s">
+        <v>71</v>
+      </c>
+      <c r="I326">
+        <v>1</v>
+      </c>
+      <c r="J326">
+        <v>0</v>
+      </c>
+      <c r="K326">
+        <v>1</v>
+      </c>
+      <c r="L326">
+        <v>3</v>
+      </c>
+      <c r="M326">
+        <v>0</v>
+      </c>
+      <c r="N326">
+        <v>3</v>
+      </c>
+      <c r="O326" t="s">
+        <v>325</v>
+      </c>
+      <c r="P326" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q326">
+        <v>2.7</v>
+      </c>
+      <c r="R326">
+        <v>2.25</v>
+      </c>
+      <c r="S326">
+        <v>3.2</v>
+      </c>
+      <c r="T326">
+        <v>1.27</v>
+      </c>
+      <c r="U326">
+        <v>3.4</v>
+      </c>
+      <c r="V326">
+        <v>2.2</v>
+      </c>
+      <c r="W326">
+        <v>1.6</v>
+      </c>
+      <c r="X326">
+        <v>4.8</v>
+      </c>
+      <c r="Y326">
+        <v>1.15</v>
+      </c>
+      <c r="Z326">
+        <v>2.06</v>
+      </c>
+      <c r="AA326">
+        <v>3.6</v>
+      </c>
+      <c r="AB326">
+        <v>2.82</v>
+      </c>
+      <c r="AC326">
+        <v>1.04</v>
+      </c>
+      <c r="AD326">
+        <v>10</v>
+      </c>
+      <c r="AE326">
+        <v>1.18</v>
+      </c>
+      <c r="AF326">
+        <v>4.75</v>
+      </c>
+      <c r="AG326">
+        <v>1.37</v>
+      </c>
+      <c r="AH326">
+        <v>2.94</v>
+      </c>
+      <c r="AI326">
+        <v>1.47</v>
+      </c>
+      <c r="AJ326">
+        <v>2.45</v>
+      </c>
+      <c r="AK326">
+        <v>1.4</v>
+      </c>
+      <c r="AL326">
+        <v>1.27</v>
+      </c>
+      <c r="AM326">
+        <v>1.61</v>
+      </c>
+      <c r="AN326">
+        <v>2</v>
+      </c>
+      <c r="AO326">
+        <v>2</v>
+      </c>
+      <c r="AP326">
+        <v>2.09</v>
+      </c>
+      <c r="AQ326">
+        <v>1.8</v>
+      </c>
+      <c r="AR326">
+        <v>1.74</v>
+      </c>
+      <c r="AS326">
+        <v>1.44</v>
+      </c>
+      <c r="AT326">
+        <v>3.18</v>
+      </c>
+      <c r="AU326">
+        <v>6</v>
+      </c>
+      <c r="AV326">
+        <v>2</v>
+      </c>
+      <c r="AW326">
+        <v>4</v>
+      </c>
+      <c r="AX326">
+        <v>8</v>
+      </c>
+      <c r="AY326">
+        <v>10</v>
+      </c>
+      <c r="AZ326">
+        <v>10</v>
+      </c>
+      <c r="BA326">
+        <v>1</v>
+      </c>
+      <c r="BB326">
+        <v>4</v>
+      </c>
+      <c r="BC326">
+        <v>5</v>
+      </c>
+      <c r="BD326">
+        <v>1.78</v>
+      </c>
+      <c r="BE326">
+        <v>6.4</v>
+      </c>
+      <c r="BF326">
+        <v>2.23</v>
+      </c>
+      <c r="BG326">
+        <v>1.33</v>
+      </c>
+      <c r="BH326">
+        <v>2.95</v>
+      </c>
+      <c r="BI326">
+        <v>1.55</v>
+      </c>
+      <c r="BJ326">
+        <v>2.25</v>
+      </c>
+      <c r="BK326">
+        <v>1.91</v>
+      </c>
+      <c r="BL326">
+        <v>1.78</v>
+      </c>
+      <c r="BM326">
+        <v>2.4</v>
+      </c>
+      <c r="BN326">
+        <v>1.49</v>
+      </c>
+      <c r="BO326">
+        <v>3.15</v>
+      </c>
+      <c r="BP326">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="327" spans="1:68">
+      <c r="A327" s="1">
+        <v>326</v>
+      </c>
+      <c r="B327">
+        <v>7781403</v>
+      </c>
+      <c r="C327" t="s">
+        <v>68</v>
+      </c>
+      <c r="D327" t="s">
+        <v>69</v>
+      </c>
+      <c r="E327" s="2">
+        <v>45854.85416666666</v>
+      </c>
+      <c r="F327">
+        <v>0</v>
+      </c>
+      <c r="G327" t="s">
+        <v>85</v>
+      </c>
+      <c r="H327" t="s">
+        <v>75</v>
+      </c>
+      <c r="I327">
+        <v>1</v>
+      </c>
+      <c r="J327">
+        <v>0</v>
+      </c>
+      <c r="K327">
+        <v>1</v>
+      </c>
+      <c r="L327">
+        <v>2</v>
+      </c>
+      <c r="M327">
+        <v>1</v>
+      </c>
+      <c r="N327">
+        <v>3</v>
+      </c>
+      <c r="O327" t="s">
+        <v>326</v>
+      </c>
+      <c r="P327" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q327">
+        <v>2.15</v>
+      </c>
+      <c r="R327">
+        <v>2.35</v>
+      </c>
+      <c r="S327">
+        <v>4.33</v>
+      </c>
+      <c r="T327">
+        <v>1.27</v>
+      </c>
+      <c r="U327">
+        <v>3.4</v>
+      </c>
+      <c r="V327">
+        <v>2.25</v>
+      </c>
+      <c r="W327">
+        <v>1.57</v>
+      </c>
+      <c r="X327">
+        <v>5</v>
+      </c>
+      <c r="Y327">
+        <v>1.14</v>
+      </c>
+      <c r="Z327">
+        <v>1.61</v>
+      </c>
+      <c r="AA327">
+        <v>3.81</v>
+      </c>
+      <c r="AB327">
+        <v>4.2</v>
+      </c>
+      <c r="AC327">
+        <v>1.04</v>
+      </c>
+      <c r="AD327">
+        <v>10</v>
+      </c>
+      <c r="AE327">
+        <v>1.2</v>
+      </c>
+      <c r="AF327">
+        <v>4.5</v>
+      </c>
+      <c r="AG327">
+        <v>1.57</v>
+      </c>
+      <c r="AH327">
+        <v>2.25</v>
+      </c>
+      <c r="AI327">
+        <v>1.61</v>
+      </c>
+      <c r="AJ327">
+        <v>2.15</v>
+      </c>
+      <c r="AK327">
+        <v>1.2</v>
+      </c>
+      <c r="AL327">
+        <v>1.23</v>
+      </c>
+      <c r="AM327">
+        <v>2.1</v>
+      </c>
+      <c r="AN327">
+        <v>2.2</v>
+      </c>
+      <c r="AO327">
+        <v>0.8</v>
+      </c>
+      <c r="AP327">
+        <v>2.27</v>
+      </c>
+      <c r="AQ327">
+        <v>0.73</v>
+      </c>
+      <c r="AR327">
+        <v>1.57</v>
+      </c>
+      <c r="AS327">
+        <v>1.51</v>
+      </c>
+      <c r="AT327">
+        <v>3.08</v>
+      </c>
+      <c r="AU327">
+        <v>9</v>
+      </c>
+      <c r="AV327">
+        <v>2</v>
+      </c>
+      <c r="AW327">
+        <v>9</v>
+      </c>
+      <c r="AX327">
+        <v>10</v>
+      </c>
+      <c r="AY327">
+        <v>18</v>
+      </c>
+      <c r="AZ327">
+        <v>12</v>
+      </c>
+      <c r="BA327">
+        <v>9</v>
+      </c>
+      <c r="BB327">
+        <v>4</v>
+      </c>
+      <c r="BC327">
+        <v>13</v>
+      </c>
+      <c r="BD327">
+        <v>1.68</v>
+      </c>
+      <c r="BE327">
+        <v>6.5</v>
+      </c>
+      <c r="BF327">
+        <v>2.43</v>
+      </c>
+      <c r="BG327">
+        <v>1.34</v>
+      </c>
+      <c r="BH327">
+        <v>2.9</v>
+      </c>
+      <c r="BI327">
+        <v>1.58</v>
+      </c>
+      <c r="BJ327">
+        <v>2.18</v>
+      </c>
+      <c r="BK327">
+        <v>1.95</v>
+      </c>
+      <c r="BL327">
+        <v>1.74</v>
+      </c>
+      <c r="BM327">
+        <v>2.45</v>
+      </c>
+      <c r="BN327">
+        <v>1.48</v>
+      </c>
+      <c r="BO327">
+        <v>3.15</v>
+      </c>
+      <c r="BP327">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="328" spans="1:68">
+      <c r="A328" s="1">
+        <v>327</v>
+      </c>
+      <c r="B328">
+        <v>7781402</v>
+      </c>
+      <c r="C328" t="s">
+        <v>68</v>
+      </c>
+      <c r="D328" t="s">
+        <v>69</v>
+      </c>
+      <c r="E328" s="2">
+        <v>45854.85416666666</v>
+      </c>
+      <c r="F328">
+        <v>0</v>
+      </c>
+      <c r="G328" t="s">
+        <v>72</v>
+      </c>
+      <c r="H328" t="s">
+        <v>90</v>
+      </c>
+      <c r="I328">
+        <v>0</v>
+      </c>
+      <c r="J328">
+        <v>1</v>
+      </c>
+      <c r="K328">
+        <v>1</v>
+      </c>
+      <c r="L328">
+        <v>2</v>
+      </c>
+      <c r="M328">
+        <v>2</v>
+      </c>
+      <c r="N328">
+        <v>4</v>
+      </c>
+      <c r="O328" t="s">
+        <v>327</v>
+      </c>
+      <c r="P328" t="s">
+        <v>474</v>
+      </c>
+      <c r="Q328">
+        <v>2.55</v>
+      </c>
+      <c r="R328">
+        <v>2.3</v>
+      </c>
+      <c r="S328">
+        <v>3.4</v>
+      </c>
+      <c r="T328">
+        <v>1.27</v>
+      </c>
+      <c r="U328">
+        <v>3.4</v>
+      </c>
+      <c r="V328">
+        <v>2.2</v>
+      </c>
+      <c r="W328">
+        <v>1.58</v>
+      </c>
+      <c r="X328">
+        <v>5</v>
+      </c>
+      <c r="Y328">
+        <v>1.15</v>
+      </c>
+      <c r="Z328">
+        <v>2</v>
+      </c>
+      <c r="AA328">
+        <v>3.63</v>
+      </c>
+      <c r="AB328">
+        <v>2.91</v>
+      </c>
+      <c r="AC328">
+        <v>1.04</v>
+      </c>
+      <c r="AD328">
+        <v>10</v>
+      </c>
+      <c r="AE328">
+        <v>1.18</v>
+      </c>
+      <c r="AF328">
+        <v>4.75</v>
+      </c>
+      <c r="AG328">
+        <v>1.59</v>
+      </c>
+      <c r="AH328">
+        <v>2.36</v>
+      </c>
+      <c r="AI328">
+        <v>1.49</v>
+      </c>
+      <c r="AJ328">
+        <v>2.4</v>
+      </c>
+      <c r="AK328">
+        <v>1.35</v>
+      </c>
+      <c r="AL328">
+        <v>1.26</v>
+      </c>
+      <c r="AM328">
+        <v>1.68</v>
+      </c>
+      <c r="AN328">
+        <v>1.5</v>
+      </c>
+      <c r="AO328">
+        <v>1.64</v>
+      </c>
+      <c r="AP328">
+        <v>1.45</v>
+      </c>
+      <c r="AQ328">
+        <v>1.58</v>
+      </c>
+      <c r="AR328">
+        <v>1.56</v>
+      </c>
+      <c r="AS328">
+        <v>1.6</v>
+      </c>
+      <c r="AT328">
+        <v>3.16</v>
+      </c>
+      <c r="AU328">
+        <v>5</v>
+      </c>
+      <c r="AV328">
+        <v>10</v>
+      </c>
+      <c r="AW328">
+        <v>7</v>
+      </c>
+      <c r="AX328">
+        <v>5</v>
+      </c>
+      <c r="AY328">
+        <v>12</v>
+      </c>
+      <c r="AZ328">
+        <v>15</v>
+      </c>
+      <c r="BA328">
+        <v>3</v>
+      </c>
+      <c r="BB328">
+        <v>4</v>
+      </c>
+      <c r="BC328">
+        <v>7</v>
+      </c>
+      <c r="BD328">
+        <v>1.67</v>
+      </c>
+      <c r="BE328">
+        <v>6.4</v>
+      </c>
+      <c r="BF328">
+        <v>2.45</v>
+      </c>
+      <c r="BG328">
+        <v>1.26</v>
+      </c>
+      <c r="BH328">
+        <v>3.4</v>
+      </c>
+      <c r="BI328">
+        <v>1.46</v>
+      </c>
+      <c r="BJ328">
+        <v>2.48</v>
+      </c>
+      <c r="BK328">
+        <v>1.74</v>
+      </c>
+      <c r="BL328">
+        <v>1.96</v>
+      </c>
+      <c r="BM328">
+        <v>2.17</v>
+      </c>
+      <c r="BN328">
+        <v>1.6</v>
+      </c>
+      <c r="BO328">
+        <v>2.75</v>
+      </c>
+      <c r="BP328">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="329" spans="1:68">
+      <c r="A329" s="1">
+        <v>328</v>
+      </c>
+      <c r="B329">
+        <v>7781406</v>
+      </c>
+      <c r="C329" t="s">
+        <v>68</v>
+      </c>
+      <c r="D329" t="s">
+        <v>69</v>
+      </c>
+      <c r="E329" s="2">
+        <v>45854.88541666666</v>
+      </c>
+      <c r="F329">
+        <v>0</v>
+      </c>
+      <c r="G329" t="s">
+        <v>76</v>
+      </c>
+      <c r="H329" t="s">
+        <v>96</v>
+      </c>
+      <c r="I329">
+        <v>1</v>
+      </c>
+      <c r="J329">
+        <v>0</v>
+      </c>
+      <c r="K329">
+        <v>1</v>
+      </c>
+      <c r="L329">
+        <v>1</v>
+      </c>
+      <c r="M329">
+        <v>2</v>
+      </c>
+      <c r="N329">
+        <v>3</v>
+      </c>
+      <c r="O329" t="s">
+        <v>237</v>
+      </c>
+      <c r="P329" t="s">
+        <v>475</v>
+      </c>
+      <c r="Q329">
+        <v>2.15</v>
+      </c>
+      <c r="R329">
+        <v>2.3</v>
+      </c>
+      <c r="S329">
+        <v>4.5</v>
+      </c>
+      <c r="T329">
+        <v>1.27</v>
+      </c>
+      <c r="U329">
+        <v>3.4</v>
+      </c>
+      <c r="V329">
+        <v>2.15</v>
+      </c>
+      <c r="W329">
+        <v>1.6</v>
+      </c>
+      <c r="X329">
+        <v>4.8</v>
+      </c>
+      <c r="Y329">
+        <v>1.15</v>
+      </c>
+      <c r="Z329">
+        <v>1.73</v>
+      </c>
+      <c r="AA329">
+        <v>3.55</v>
+      </c>
+      <c r="AB329">
+        <v>3.83</v>
+      </c>
+      <c r="AC329">
+        <v>1.04</v>
+      </c>
+      <c r="AD329">
+        <v>10</v>
+      </c>
+      <c r="AE329">
+        <v>1.18</v>
+      </c>
+      <c r="AF329">
+        <v>4.75</v>
+      </c>
+      <c r="AG329">
+        <v>1.56</v>
+      </c>
+      <c r="AH329">
+        <v>2.27</v>
+      </c>
+      <c r="AI329">
+        <v>1.57</v>
+      </c>
+      <c r="AJ329">
+        <v>2.25</v>
+      </c>
+      <c r="AK329">
+        <v>1.18</v>
+      </c>
+      <c r="AL329">
+        <v>1.24</v>
+      </c>
+      <c r="AM329">
+        <v>2.15</v>
+      </c>
+      <c r="AN329">
+        <v>1.64</v>
+      </c>
+      <c r="AO329">
+        <v>0.7</v>
+      </c>
+      <c r="AP329">
+        <v>1.5</v>
+      </c>
+      <c r="AQ329">
+        <v>0.91</v>
+      </c>
+      <c r="AR329">
+        <v>1.85</v>
+      </c>
+      <c r="AS329">
+        <v>1.32</v>
+      </c>
+      <c r="AT329">
+        <v>3.17</v>
+      </c>
+      <c r="AU329">
+        <v>9</v>
+      </c>
+      <c r="AV329">
+        <v>5</v>
+      </c>
+      <c r="AW329">
+        <v>16</v>
+      </c>
+      <c r="AX329">
+        <v>7</v>
+      </c>
+      <c r="AY329">
+        <v>25</v>
+      </c>
+      <c r="AZ329">
+        <v>12</v>
+      </c>
+      <c r="BA329">
+        <v>9</v>
+      </c>
+      <c r="BB329">
+        <v>4</v>
+      </c>
+      <c r="BC329">
+        <v>13</v>
+      </c>
+      <c r="BD329">
+        <v>1.48</v>
+      </c>
+      <c r="BE329">
+        <v>7</v>
+      </c>
+      <c r="BF329">
+        <v>2.9</v>
+      </c>
+      <c r="BG329">
+        <v>1.2</v>
+      </c>
+      <c r="BH329">
+        <v>3.9</v>
+      </c>
+      <c r="BI329">
+        <v>1.37</v>
+      </c>
+      <c r="BJ329">
+        <v>2.8</v>
+      </c>
+      <c r="BK329">
+        <v>1.58</v>
+      </c>
+      <c r="BL329">
+        <v>2.17</v>
+      </c>
+      <c r="BM329">
+        <v>1.95</v>
+      </c>
+      <c r="BN329">
+        <v>1.75</v>
+      </c>
+      <c r="BO329">
+        <v>2.43</v>
+      </c>
+      <c r="BP329">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="330" spans="1:68">
+      <c r="A330" s="1">
+        <v>329</v>
+      </c>
+      <c r="B330">
+        <v>7781408</v>
+      </c>
+      <c r="C330" t="s">
+        <v>68</v>
+      </c>
+      <c r="D330" t="s">
+        <v>69</v>
+      </c>
+      <c r="E330" s="2">
+        <v>45854.89583333334</v>
+      </c>
+      <c r="F330">
+        <v>0</v>
+      </c>
+      <c r="G330" t="s">
+        <v>78</v>
+      </c>
+      <c r="H330" t="s">
+        <v>95</v>
+      </c>
+      <c r="I330">
+        <v>0</v>
+      </c>
+      <c r="J330">
+        <v>2</v>
+      </c>
+      <c r="K330">
+        <v>2</v>
+      </c>
+      <c r="L330">
+        <v>0</v>
+      </c>
+      <c r="M330">
+        <v>3</v>
+      </c>
+      <c r="N330">
+        <v>3</v>
+      </c>
+      <c r="O330" t="s">
+        <v>109</v>
+      </c>
+      <c r="P330" t="s">
+        <v>476</v>
+      </c>
+      <c r="Q330">
+        <v>2.8</v>
+      </c>
+      <c r="R330">
+        <v>2.1</v>
+      </c>
+      <c r="S330">
+        <v>3.5</v>
+      </c>
+      <c r="T330">
+        <v>1.36</v>
+      </c>
+      <c r="U330">
+        <v>2.87</v>
+      </c>
+      <c r="V330">
+        <v>2.6</v>
+      </c>
+      <c r="W330">
+        <v>1.43</v>
+      </c>
+      <c r="X330">
+        <v>6.5</v>
+      </c>
+      <c r="Y330">
+        <v>1.1</v>
+      </c>
+      <c r="Z330">
+        <v>2.16</v>
+      </c>
+      <c r="AA330">
+        <v>3.21</v>
+      </c>
+      <c r="AB330">
+        <v>2.9</v>
+      </c>
+      <c r="AC330">
+        <v>1.05</v>
+      </c>
+      <c r="AD330">
+        <v>9.5</v>
+      </c>
+      <c r="AE330">
+        <v>1.27</v>
+      </c>
+      <c r="AF330">
+        <v>3.4</v>
+      </c>
+      <c r="AG330">
+        <v>1.82</v>
+      </c>
+      <c r="AH330">
+        <v>1.88</v>
+      </c>
+      <c r="AI330">
+        <v>1.68</v>
+      </c>
+      <c r="AJ330">
+        <v>2.05</v>
+      </c>
+      <c r="AK330">
+        <v>1.36</v>
+      </c>
+      <c r="AL330">
+        <v>1.3</v>
+      </c>
+      <c r="AM330">
+        <v>1.61</v>
+      </c>
+      <c r="AN330">
+        <v>1.18</v>
+      </c>
+      <c r="AO330">
+        <v>1.64</v>
+      </c>
+      <c r="AP330">
+        <v>1.08</v>
+      </c>
+      <c r="AQ330">
+        <v>1.75</v>
+      </c>
+      <c r="AR330">
+        <v>1.69</v>
+      </c>
+      <c r="AS330">
+        <v>1.42</v>
+      </c>
+      <c r="AT330">
+        <v>3.11</v>
+      </c>
+      <c r="AU330">
+        <v>4</v>
+      </c>
+      <c r="AV330">
+        <v>7</v>
+      </c>
+      <c r="AW330">
+        <v>8</v>
+      </c>
+      <c r="AX330">
+        <v>5</v>
+      </c>
+      <c r="AY330">
+        <v>12</v>
+      </c>
+      <c r="AZ330">
+        <v>12</v>
+      </c>
+      <c r="BA330">
+        <v>6</v>
+      </c>
+      <c r="BB330">
+        <v>1</v>
+      </c>
+      <c r="BC330">
+        <v>7</v>
+      </c>
+      <c r="BD330">
+        <v>1.78</v>
+      </c>
+      <c r="BE330">
+        <v>6.75</v>
+      </c>
+      <c r="BF330">
+        <v>2.23</v>
+      </c>
+      <c r="BG330">
+        <v>1.21</v>
+      </c>
+      <c r="BH330">
+        <v>3.8</v>
+      </c>
+      <c r="BI330">
+        <v>1.4</v>
+      </c>
+      <c r="BJ330">
+        <v>2.7</v>
+      </c>
+      <c r="BK330">
+        <v>1.65</v>
+      </c>
+      <c r="BL330">
+        <v>2.08</v>
+      </c>
+      <c r="BM330">
+        <v>2</v>
+      </c>
+      <c r="BN330">
+        <v>1.7</v>
+      </c>
+      <c r="BO330">
+        <v>2.55</v>
+      </c>
+      <c r="BP330">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="331" spans="1:68">
+      <c r="A331" s="1">
+        <v>330</v>
+      </c>
+      <c r="B331">
+        <v>7781409</v>
+      </c>
+      <c r="C331" t="s">
+        <v>68</v>
+      </c>
+      <c r="D331" t="s">
+        <v>69</v>
+      </c>
+      <c r="E331" s="2">
+        <v>45854.89583333334</v>
+      </c>
+      <c r="F331">
+        <v>0</v>
+      </c>
+      <c r="G331" t="s">
+        <v>92</v>
+      </c>
+      <c r="H331" t="s">
+        <v>70</v>
+      </c>
+      <c r="I331">
+        <v>0</v>
+      </c>
+      <c r="J331">
+        <v>1</v>
+      </c>
+      <c r="K331">
+        <v>1</v>
+      </c>
+      <c r="L331">
+        <v>0</v>
+      </c>
+      <c r="M331">
+        <v>1</v>
+      </c>
+      <c r="N331">
+        <v>1</v>
+      </c>
+      <c r="O331" t="s">
+        <v>109</v>
+      </c>
+      <c r="P331" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q331">
+        <v>3.1</v>
+      </c>
+      <c r="R331">
+        <v>2.15</v>
+      </c>
+      <c r="S331">
+        <v>2.95</v>
+      </c>
+      <c r="T331">
+        <v>1.33</v>
+      </c>
+      <c r="U331">
+        <v>3</v>
+      </c>
+      <c r="V331">
+        <v>2.5</v>
+      </c>
+      <c r="W331">
+        <v>1.46</v>
+      </c>
+      <c r="X331">
+        <v>6</v>
+      </c>
+      <c r="Y331">
+        <v>1.11</v>
+      </c>
+      <c r="Z331">
+        <v>2.53</v>
+      </c>
+      <c r="AA331">
+        <v>3.3</v>
+      </c>
+      <c r="AB331">
+        <v>2.37</v>
+      </c>
+      <c r="AC331">
+        <v>1.05</v>
+      </c>
+      <c r="AD331">
+        <v>9.5</v>
+      </c>
+      <c r="AE331">
+        <v>1.25</v>
+      </c>
+      <c r="AF331">
+        <v>3.75</v>
+      </c>
+      <c r="AG331">
+        <v>1.77</v>
+      </c>
+      <c r="AH331">
+        <v>1.93</v>
+      </c>
+      <c r="AI331">
+        <v>1.63</v>
+      </c>
+      <c r="AJ331">
+        <v>2.1</v>
+      </c>
+      <c r="AK331">
+        <v>1.51</v>
+      </c>
+      <c r="AL331">
+        <v>1.29</v>
+      </c>
+      <c r="AM331">
+        <v>1.46</v>
+      </c>
+      <c r="AN331">
+        <v>1.91</v>
+      </c>
+      <c r="AO331">
+        <v>0.88</v>
+      </c>
+      <c r="AP331">
+        <v>1.75</v>
+      </c>
+      <c r="AQ331">
+        <v>1.11</v>
+      </c>
+      <c r="AR331">
+        <v>1.72</v>
+      </c>
+      <c r="AS331">
+        <v>1.55</v>
+      </c>
+      <c r="AT331">
+        <v>3.27</v>
+      </c>
+      <c r="AU331">
+        <v>3</v>
+      </c>
+      <c r="AV331">
+        <v>7</v>
+      </c>
+      <c r="AW331">
+        <v>8</v>
+      </c>
+      <c r="AX331">
+        <v>2</v>
+      </c>
+      <c r="AY331">
+        <v>11</v>
+      </c>
+      <c r="AZ331">
+        <v>9</v>
+      </c>
+      <c r="BA331">
+        <v>10</v>
+      </c>
+      <c r="BB331">
+        <v>3</v>
+      </c>
+      <c r="BC331">
+        <v>13</v>
+      </c>
+      <c r="BD331">
+        <v>2.07</v>
+      </c>
+      <c r="BE331">
+        <v>6.4</v>
+      </c>
+      <c r="BF331">
+        <v>1.94</v>
+      </c>
+      <c r="BG331">
+        <v>1.29</v>
+      </c>
+      <c r="BH331">
+        <v>3.2</v>
+      </c>
+      <c r="BI331">
+        <v>1.5</v>
+      </c>
+      <c r="BJ331">
+        <v>2.38</v>
+      </c>
+      <c r="BK331">
+        <v>1.81</v>
+      </c>
+      <c r="BL331">
+        <v>1.88</v>
+      </c>
+      <c r="BM331">
+        <v>2.28</v>
+      </c>
+      <c r="BN331">
+        <v>1.54</v>
+      </c>
+      <c r="BO331">
+        <v>2.9</v>
+      </c>
+      <c r="BP331">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="332" spans="1:68">
+      <c r="A332" s="1">
+        <v>331</v>
+      </c>
+      <c r="B332">
+        <v>7781410</v>
+      </c>
+      <c r="C332" t="s">
+        <v>68</v>
+      </c>
+      <c r="D332" t="s">
+        <v>69</v>
+      </c>
+      <c r="E332" s="2">
+        <v>45854.89583333334</v>
+      </c>
+      <c r="F332">
+        <v>0</v>
+      </c>
+      <c r="G332" t="s">
+        <v>79</v>
+      </c>
+      <c r="H332" t="s">
+        <v>74</v>
+      </c>
+      <c r="I332">
+        <v>2</v>
+      </c>
+      <c r="J332">
+        <v>0</v>
+      </c>
+      <c r="K332">
+        <v>2</v>
+      </c>
+      <c r="L332">
+        <v>3</v>
+      </c>
+      <c r="M332">
+        <v>0</v>
+      </c>
+      <c r="N332">
+        <v>3</v>
+      </c>
+      <c r="O332" t="s">
+        <v>328</v>
+      </c>
+      <c r="P332" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q332">
+        <v>2.55</v>
+      </c>
+      <c r="R332">
+        <v>2.25</v>
+      </c>
+      <c r="S332">
+        <v>3.5</v>
+      </c>
+      <c r="T332">
+        <v>1.3</v>
+      </c>
+      <c r="U332">
+        <v>3.2</v>
+      </c>
+      <c r="V332">
+        <v>2.35</v>
+      </c>
+      <c r="W332">
+        <v>1.52</v>
+      </c>
+      <c r="X332">
+        <v>5.5</v>
+      </c>
+      <c r="Y332">
+        <v>1.13</v>
+      </c>
+      <c r="Z332">
+        <v>1.98</v>
+      </c>
+      <c r="AA332">
+        <v>3.39</v>
+      </c>
+      <c r="AB332">
+        <v>3.12</v>
+      </c>
+      <c r="AC332">
+        <v>1.03</v>
+      </c>
+      <c r="AD332">
+        <v>11.5</v>
+      </c>
+      <c r="AE332">
+        <v>1.2</v>
+      </c>
+      <c r="AF332">
+        <v>4.1</v>
+      </c>
+      <c r="AG332">
+        <v>1.54</v>
+      </c>
+      <c r="AH332">
+        <v>2.3</v>
+      </c>
+      <c r="AI332">
+        <v>1.57</v>
+      </c>
+      <c r="AJ332">
+        <v>2.2</v>
+      </c>
+      <c r="AK332">
+        <v>1.32</v>
+      </c>
+      <c r="AL332">
+        <v>1.27</v>
+      </c>
+      <c r="AM332">
+        <v>1.72</v>
+      </c>
+      <c r="AN332">
+        <v>2.18</v>
+      </c>
+      <c r="AO332">
+        <v>1.6</v>
+      </c>
+      <c r="AP332">
+        <v>2.25</v>
+      </c>
+      <c r="AQ332">
+        <v>1.45</v>
+      </c>
+      <c r="AR332">
+        <v>1.87</v>
+      </c>
+      <c r="AS332">
+        <v>1.43</v>
+      </c>
+      <c r="AT332">
+        <v>3.3</v>
+      </c>
+      <c r="AU332">
+        <v>5</v>
+      </c>
+      <c r="AV332">
+        <v>5</v>
+      </c>
+      <c r="AW332">
+        <v>4</v>
+      </c>
+      <c r="AX332">
+        <v>10</v>
+      </c>
+      <c r="AY332">
+        <v>9</v>
+      </c>
+      <c r="AZ332">
+        <v>15</v>
+      </c>
+      <c r="BA332">
+        <v>1</v>
+      </c>
+      <c r="BB332">
+        <v>5</v>
+      </c>
+      <c r="BC332">
+        <v>6</v>
+      </c>
+      <c r="BD332">
+        <v>1.74</v>
+      </c>
+      <c r="BE332">
+        <v>6.4</v>
+      </c>
+      <c r="BF332">
+        <v>2.33</v>
+      </c>
+      <c r="BG332">
+        <v>1.35</v>
+      </c>
+      <c r="BH332">
+        <v>2.9</v>
+      </c>
+      <c r="BI332">
+        <v>1.6</v>
+      </c>
+      <c r="BJ332">
+        <v>2.17</v>
+      </c>
+      <c r="BK332">
+        <v>1.96</v>
+      </c>
+      <c r="BL332">
+        <v>1.73</v>
+      </c>
+      <c r="BM332">
+        <v>2.48</v>
+      </c>
+      <c r="BN332">
+        <v>1.47</v>
+      </c>
+      <c r="BO332">
+        <v>3.2</v>
+      </c>
+      <c r="BP332">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="333" spans="1:68">
+      <c r="A333" s="1">
+        <v>332</v>
+      </c>
+      <c r="B333">
+        <v>7781411</v>
+      </c>
+      <c r="C333" t="s">
+        <v>68</v>
+      </c>
+      <c r="D333" t="s">
+        <v>69</v>
+      </c>
+      <c r="E333" s="2">
+        <v>45854.95833333334</v>
+      </c>
+      <c r="F333">
+        <v>0</v>
+      </c>
+      <c r="G333" t="s">
+        <v>82</v>
+      </c>
+      <c r="H333" t="s">
+        <v>93</v>
+      </c>
+      <c r="I333">
+        <v>2</v>
+      </c>
+      <c r="J333">
+        <v>0</v>
+      </c>
+      <c r="K333">
+        <v>2</v>
+      </c>
+      <c r="L333">
+        <v>3</v>
+      </c>
+      <c r="M333">
+        <v>3</v>
+      </c>
+      <c r="N333">
+        <v>6</v>
+      </c>
+      <c r="O333" t="s">
+        <v>329</v>
+      </c>
+      <c r="P333" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q333">
+        <v>1.95</v>
+      </c>
+      <c r="R333">
+        <v>2.25</v>
+      </c>
+      <c r="S333">
+        <v>6</v>
+      </c>
+      <c r="T333">
+        <v>1.36</v>
+      </c>
+      <c r="U333">
+        <v>2.9</v>
+      </c>
+      <c r="V333">
+        <v>2.6</v>
+      </c>
+      <c r="W333">
+        <v>1.43</v>
+      </c>
+      <c r="X333">
+        <v>6.5</v>
+      </c>
+      <c r="Y333">
+        <v>1.1</v>
+      </c>
+      <c r="Z333">
+        <v>1.44</v>
+      </c>
+      <c r="AA333">
+        <v>4.1</v>
+      </c>
+      <c r="AB333">
+        <v>5.6</v>
+      </c>
+      <c r="AC333">
+        <v>1.05</v>
+      </c>
+      <c r="AD333">
+        <v>9.5</v>
+      </c>
+      <c r="AE333">
+        <v>1.3</v>
+      </c>
+      <c r="AF333">
+        <v>3.45</v>
+      </c>
+      <c r="AG333">
+        <v>1.76</v>
+      </c>
+      <c r="AH333">
+        <v>1.94</v>
+      </c>
+      <c r="AI333">
+        <v>2.05</v>
+      </c>
+      <c r="AJ333">
+        <v>1.68</v>
+      </c>
+      <c r="AK333">
+        <v>1.11</v>
+      </c>
+      <c r="AL333">
+        <v>1.22</v>
+      </c>
+      <c r="AM333">
+        <v>2.6</v>
+      </c>
+      <c r="AN333">
+        <v>2.1</v>
+      </c>
+      <c r="AO333">
+        <v>0.9</v>
+      </c>
+      <c r="AP333">
+        <v>2</v>
+      </c>
+      <c r="AQ333">
+        <v>0.91</v>
+      </c>
+      <c r="AR333">
+        <v>1.85</v>
+      </c>
+      <c r="AS333">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AT333">
+        <v>2.79</v>
+      </c>
+      <c r="AU333">
+        <v>5</v>
+      </c>
+      <c r="AV333">
+        <v>4</v>
+      </c>
+      <c r="AW333">
+        <v>1</v>
+      </c>
+      <c r="AX333">
+        <v>2</v>
+      </c>
+      <c r="AY333">
+        <v>6</v>
+      </c>
+      <c r="AZ333">
+        <v>6</v>
+      </c>
+      <c r="BA333">
+        <v>3</v>
+      </c>
+      <c r="BB333">
+        <v>7</v>
+      </c>
+      <c r="BC333">
+        <v>10</v>
+      </c>
+      <c r="BD333">
+        <v>1.3</v>
+      </c>
+      <c r="BE333">
+        <v>7.5</v>
+      </c>
+      <c r="BF333">
+        <v>3.9</v>
+      </c>
+      <c r="BG333">
+        <v>1.29</v>
+      </c>
+      <c r="BH333">
+        <v>3.2</v>
+      </c>
+      <c r="BI333">
+        <v>1.5</v>
+      </c>
+      <c r="BJ333">
+        <v>2.4</v>
+      </c>
+      <c r="BK333">
+        <v>1.8</v>
+      </c>
+      <c r="BL333">
+        <v>1.89</v>
+      </c>
+      <c r="BM333">
+        <v>2.23</v>
+      </c>
+      <c r="BN333">
+        <v>1.56</v>
+      </c>
+      <c r="BO333">
+        <v>2.9</v>
+      </c>
+      <c r="BP333">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="334" spans="1:68">
+      <c r="A334" s="1">
+        <v>333</v>
+      </c>
+      <c r="B334">
+        <v>7781415</v>
+      </c>
+      <c r="C334" t="s">
+        <v>68</v>
+      </c>
+      <c r="D334" t="s">
+        <v>69</v>
+      </c>
+      <c r="E334" s="2">
+        <v>45854.97916666666</v>
+      </c>
+      <c r="F334">
+        <v>0</v>
+      </c>
+      <c r="G334" t="s">
+        <v>81</v>
+      </c>
+      <c r="H334" t="s">
+        <v>97</v>
+      </c>
+      <c r="I334">
+        <v>1</v>
+      </c>
+      <c r="J334">
+        <v>1</v>
+      </c>
+      <c r="K334">
+        <v>2</v>
+      </c>
+      <c r="L334">
+        <v>2</v>
+      </c>
+      <c r="M334">
+        <v>2</v>
+      </c>
+      <c r="N334">
+        <v>4</v>
+      </c>
+      <c r="O334" t="s">
+        <v>330</v>
+      </c>
+      <c r="P334" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q334">
+        <v>2.05</v>
+      </c>
+      <c r="R334">
+        <v>2.55</v>
+      </c>
+      <c r="S334">
+        <v>4.2</v>
+      </c>
+      <c r="T334">
+        <v>1.2</v>
+      </c>
+      <c r="U334">
+        <v>4.1</v>
+      </c>
+      <c r="V334">
+        <v>1.93</v>
+      </c>
+      <c r="W334">
+        <v>1.77</v>
+      </c>
+      <c r="X334">
+        <v>4</v>
+      </c>
+      <c r="Y334">
+        <v>1.21</v>
+      </c>
+      <c r="Z334">
+        <v>1.59</v>
+      </c>
+      <c r="AA334">
+        <v>3.95</v>
+      </c>
+      <c r="AB334">
+        <v>4.2</v>
+      </c>
+      <c r="AC334">
+        <v>1.01</v>
+      </c>
+      <c r="AD334">
+        <v>23</v>
+      </c>
+      <c r="AE334">
+        <v>1.11</v>
+      </c>
+      <c r="AF334">
+        <v>6.25</v>
+      </c>
+      <c r="AG334">
+        <v>1.34</v>
+      </c>
+      <c r="AH334">
+        <v>3.09</v>
+      </c>
+      <c r="AI334">
+        <v>1.44</v>
+      </c>
+      <c r="AJ334">
+        <v>2.55</v>
+      </c>
+      <c r="AK334">
+        <v>1.2</v>
+      </c>
+      <c r="AL334">
+        <v>1.2</v>
+      </c>
+      <c r="AM334">
+        <v>2.2</v>
+      </c>
+      <c r="AN334">
+        <v>1.27</v>
+      </c>
+      <c r="AO334">
+        <v>1.45</v>
+      </c>
+      <c r="AP334">
+        <v>1.25</v>
+      </c>
+      <c r="AQ334">
+        <v>1.42</v>
+      </c>
+      <c r="AR334">
+        <v>1.96</v>
+      </c>
+      <c r="AS334">
+        <v>1.35</v>
+      </c>
+      <c r="AT334">
+        <v>3.31</v>
+      </c>
+      <c r="AU334">
+        <v>3</v>
+      </c>
+      <c r="AV334">
+        <v>4</v>
+      </c>
+      <c r="AW334">
+        <v>0</v>
+      </c>
+      <c r="AX334">
+        <v>2</v>
+      </c>
+      <c r="AY334">
+        <v>3</v>
+      </c>
+      <c r="AZ334">
+        <v>6</v>
+      </c>
+      <c r="BA334">
+        <v>4</v>
+      </c>
+      <c r="BB334">
+        <v>4</v>
+      </c>
+      <c r="BC334">
+        <v>8</v>
+      </c>
+      <c r="BD334">
+        <v>1.49</v>
+      </c>
+      <c r="BE334">
+        <v>6.75</v>
+      </c>
+      <c r="BF334">
+        <v>2.9</v>
+      </c>
+      <c r="BG334">
+        <v>1.23</v>
+      </c>
+      <c r="BH334">
+        <v>3.65</v>
+      </c>
+      <c r="BI334">
+        <v>1.41</v>
+      </c>
+      <c r="BJ334">
+        <v>2.65</v>
+      </c>
+      <c r="BK334">
+        <v>1.67</v>
+      </c>
+      <c r="BL334">
+        <v>2.05</v>
+      </c>
+      <c r="BM334">
+        <v>2.05</v>
+      </c>
+      <c r="BN334">
+        <v>1.67</v>
+      </c>
+      <c r="BO334">
+        <v>2.55</v>
+      </c>
+      <c r="BP334">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="335" spans="1:68">
+      <c r="A335" s="1">
+        <v>334</v>
+      </c>
+      <c r="B335">
+        <v>7781414</v>
+      </c>
+      <c r="C335" t="s">
+        <v>68</v>
+      </c>
+      <c r="D335" t="s">
+        <v>69</v>
+      </c>
+      <c r="E335" s="2">
+        <v>45854.97916666666</v>
+      </c>
+      <c r="F335">
+        <v>0</v>
+      </c>
+      <c r="G335" t="s">
+        <v>94</v>
+      </c>
+      <c r="H335" t="s">
+        <v>98</v>
+      </c>
+      <c r="I335">
+        <v>0</v>
+      </c>
+      <c r="J335">
+        <v>1</v>
+      </c>
+      <c r="K335">
+        <v>1</v>
+      </c>
+      <c r="L335">
+        <v>0</v>
+      </c>
+      <c r="M335">
+        <v>1</v>
+      </c>
+      <c r="N335">
+        <v>1</v>
+      </c>
+      <c r="O335" t="s">
+        <v>109</v>
+      </c>
+      <c r="P335" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q335">
+        <v>0</v>
+      </c>
+      <c r="R335">
+        <v>0</v>
+      </c>
+      <c r="S335">
+        <v>0</v>
+      </c>
+      <c r="T335">
+        <v>0</v>
+      </c>
+      <c r="U335">
+        <v>0</v>
+      </c>
+      <c r="V335">
+        <v>0</v>
+      </c>
+      <c r="W335">
+        <v>0</v>
+      </c>
+      <c r="X335">
+        <v>0</v>
+      </c>
+      <c r="Y335">
+        <v>0</v>
+      </c>
+      <c r="Z335">
+        <v>1.29</v>
+      </c>
+      <c r="AA335">
+        <v>4.8</v>
+      </c>
+      <c r="AB335">
+        <v>7.3</v>
+      </c>
+      <c r="AC335">
+        <v>0</v>
+      </c>
+      <c r="AD335">
+        <v>0</v>
+      </c>
+      <c r="AE335">
+        <v>0</v>
+      </c>
+      <c r="AF335">
+        <v>0</v>
+      </c>
+      <c r="AG335">
+        <v>1.57</v>
+      </c>
+      <c r="AH335">
+        <v>2.4</v>
+      </c>
+      <c r="AI335">
+        <v>0</v>
+      </c>
+      <c r="AJ335">
+        <v>0</v>
+      </c>
+      <c r="AK335">
+        <v>0</v>
+      </c>
+      <c r="AL335">
+        <v>0</v>
+      </c>
+      <c r="AM335">
+        <v>0</v>
+      </c>
+      <c r="AN335">
+        <v>1.91</v>
+      </c>
+      <c r="AO335">
+        <v>1</v>
+      </c>
+      <c r="AP335">
+        <v>1.75</v>
+      </c>
+      <c r="AQ335">
+        <v>1.22</v>
+      </c>
+      <c r="AR335">
+        <v>1.82</v>
+      </c>
+      <c r="AS335">
+        <v>1.23</v>
+      </c>
+      <c r="AT335">
+        <v>3.05</v>
+      </c>
+      <c r="AU335">
+        <v>2</v>
+      </c>
+      <c r="AV335">
+        <v>3</v>
+      </c>
+      <c r="AW335">
+        <v>1</v>
+      </c>
+      <c r="AX335">
+        <v>1</v>
+      </c>
+      <c r="AY335">
+        <v>3</v>
+      </c>
+      <c r="AZ335">
+        <v>4</v>
+      </c>
+      <c r="BA335">
+        <v>4</v>
+      </c>
+      <c r="BB335">
+        <v>1</v>
+      </c>
+      <c r="BC335">
+        <v>5</v>
+      </c>
+      <c r="BD335">
+        <v>0</v>
+      </c>
+      <c r="BE335">
+        <v>0</v>
+      </c>
+      <c r="BF335">
+        <v>0</v>
+      </c>
+      <c r="BG335">
+        <v>0</v>
+      </c>
+      <c r="BH335">
+        <v>0</v>
+      </c>
+      <c r="BI335">
+        <v>0</v>
+      </c>
+      <c r="BJ335">
+        <v>0</v>
+      </c>
+      <c r="BK335">
+        <v>0</v>
+      </c>
+      <c r="BL335">
+        <v>0</v>
+      </c>
+      <c r="BM335">
+        <v>0</v>
+      </c>
+      <c r="BN335">
+        <v>0</v>
+      </c>
+      <c r="BO335">
+        <v>0</v>
+      </c>
+      <c r="BP335">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:68">
+      <c r="A336" s="1">
+        <v>335</v>
+      </c>
+      <c r="B336">
+        <v>7781413</v>
+      </c>
+      <c r="C336" t="s">
+        <v>68</v>
+      </c>
+      <c r="D336" t="s">
+        <v>69</v>
+      </c>
+      <c r="E336" s="2">
+        <v>45854.97916666666</v>
+      </c>
+      <c r="F336">
+        <v>0</v>
+      </c>
+      <c r="G336" t="s">
+        <v>83</v>
+      </c>
+      <c r="H336" t="s">
+        <v>86</v>
+      </c>
+      <c r="I336">
+        <v>0</v>
+      </c>
+      <c r="J336">
+        <v>0</v>
+      </c>
+      <c r="K336">
+        <v>0</v>
+      </c>
+      <c r="L336">
+        <v>0</v>
+      </c>
+      <c r="M336">
+        <v>1</v>
+      </c>
+      <c r="N336">
+        <v>1</v>
+      </c>
+      <c r="O336" t="s">
+        <v>109</v>
+      </c>
+      <c r="P336" t="s">
+        <v>469</v>
+      </c>
+      <c r="Q336">
+        <v>2.63</v>
+      </c>
+      <c r="R336">
+        <v>2.3</v>
+      </c>
+      <c r="S336">
+        <v>3.75</v>
+      </c>
+      <c r="T336">
+        <v>1.3</v>
+      </c>
+      <c r="U336">
+        <v>3.4</v>
+      </c>
+      <c r="V336">
+        <v>2.5</v>
+      </c>
+      <c r="W336">
+        <v>1.5</v>
+      </c>
+      <c r="X336">
+        <v>6</v>
+      </c>
+      <c r="Y336">
+        <v>1.13</v>
+      </c>
+      <c r="Z336">
+        <v>1.99</v>
+      </c>
+      <c r="AA336">
+        <v>3.25</v>
+      </c>
+      <c r="AB336">
+        <v>3.25</v>
+      </c>
+      <c r="AC336">
+        <v>1.05</v>
+      </c>
+      <c r="AD336">
+        <v>9.5</v>
+      </c>
+      <c r="AE336">
+        <v>1.22</v>
+      </c>
+      <c r="AF336">
+        <v>4.2</v>
+      </c>
+      <c r="AG336">
+        <v>1.54</v>
+      </c>
+      <c r="AH336">
+        <v>2.3</v>
+      </c>
+      <c r="AI336">
+        <v>1.57</v>
+      </c>
+      <c r="AJ336">
+        <v>2.25</v>
+      </c>
+      <c r="AK336">
+        <v>1.3</v>
+      </c>
+      <c r="AL336">
+        <v>1.3</v>
+      </c>
+      <c r="AM336">
+        <v>1.71</v>
+      </c>
+      <c r="AN336">
+        <v>2</v>
+      </c>
+      <c r="AO336">
+        <v>0.82</v>
+      </c>
+      <c r="AP336">
+        <v>1.83</v>
+      </c>
+      <c r="AQ336">
+        <v>1</v>
+      </c>
+      <c r="AR336">
+        <v>1.39</v>
+      </c>
+      <c r="AS336">
+        <v>1.65</v>
+      </c>
+      <c r="AT336">
+        <v>3.04</v>
+      </c>
+      <c r="AU336">
+        <v>0</v>
+      </c>
+      <c r="AV336">
+        <v>2</v>
+      </c>
+      <c r="AW336">
+        <v>5</v>
+      </c>
+      <c r="AX336">
+        <v>2</v>
+      </c>
+      <c r="AY336">
+        <v>5</v>
+      </c>
+      <c r="AZ336">
+        <v>4</v>
+      </c>
+      <c r="BA336">
+        <v>9</v>
+      </c>
+      <c r="BB336">
+        <v>2</v>
+      </c>
+      <c r="BC336">
+        <v>11</v>
+      </c>
+      <c r="BD336">
+        <v>2.04</v>
+      </c>
+      <c r="BE336">
+        <v>6.65</v>
+      </c>
+      <c r="BF336">
+        <v>2.21</v>
+      </c>
+      <c r="BG336">
+        <v>1.18</v>
+      </c>
+      <c r="BH336">
+        <v>3.84</v>
+      </c>
+      <c r="BI336">
+        <v>1.38</v>
+      </c>
+      <c r="BJ336">
+        <v>2.71</v>
+      </c>
+      <c r="BK336">
+        <v>1.77</v>
+      </c>
+      <c r="BL336">
+        <v>1.91</v>
+      </c>
+      <c r="BM336">
+        <v>2.12</v>
+      </c>
+      <c r="BN336">
+        <v>1.61</v>
+      </c>
+      <c r="BO336">
+        <v>2.8</v>
+      </c>
+      <c r="BP336">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="337" spans="1:68">
+      <c r="A337" s="1">
+        <v>336</v>
+      </c>
+      <c r="B337">
+        <v>7781412</v>
+      </c>
+      <c r="C337" t="s">
+        <v>68</v>
+      </c>
+      <c r="D337" t="s">
+        <v>69</v>
+      </c>
+      <c r="E337" s="2">
+        <v>45854.97916666666</v>
+      </c>
+      <c r="F337">
+        <v>0</v>
+      </c>
+      <c r="G337" t="s">
+        <v>84</v>
+      </c>
+      <c r="H337" t="s">
+        <v>77</v>
+      </c>
+      <c r="I337">
+        <v>0</v>
+      </c>
+      <c r="J337">
+        <v>1</v>
+      </c>
+      <c r="K337">
+        <v>1</v>
+      </c>
+      <c r="L337">
+        <v>1</v>
+      </c>
+      <c r="M337">
+        <v>2</v>
+      </c>
+      <c r="N337">
+        <v>3</v>
+      </c>
+      <c r="O337" t="s">
+        <v>331</v>
+      </c>
+      <c r="P337" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q337">
+        <v>2.5</v>
+      </c>
+      <c r="R337">
+        <v>2.2</v>
+      </c>
+      <c r="S337">
+        <v>3.7</v>
+      </c>
+      <c r="T337">
+        <v>1.33</v>
+      </c>
+      <c r="U337">
+        <v>3.1</v>
+      </c>
+      <c r="V337">
+        <v>2.45</v>
+      </c>
+      <c r="W337">
+        <v>1.47</v>
+      </c>
+      <c r="X337">
+        <v>6</v>
+      </c>
+      <c r="Y337">
+        <v>1.11</v>
+      </c>
+      <c r="Z337">
+        <v>1.94</v>
+      </c>
+      <c r="AA337">
+        <v>3.41</v>
+      </c>
+      <c r="AB337">
+        <v>3.2</v>
+      </c>
+      <c r="AC337">
+        <v>1.05</v>
+      </c>
+      <c r="AD337">
+        <v>9.5</v>
+      </c>
+      <c r="AE337">
+        <v>1.25</v>
+      </c>
+      <c r="AF337">
+        <v>3.8</v>
+      </c>
+      <c r="AG337">
+        <v>1.72</v>
+      </c>
+      <c r="AH337">
+        <v>2</v>
+      </c>
+      <c r="AI337">
+        <v>1.65</v>
+      </c>
+      <c r="AJ337">
+        <v>2.1</v>
+      </c>
+      <c r="AK337">
+        <v>1.3</v>
+      </c>
+      <c r="AL337">
+        <v>1.27</v>
+      </c>
+      <c r="AM337">
+        <v>1.75</v>
+      </c>
+      <c r="AN337">
+        <v>1.1</v>
+      </c>
+      <c r="AO337">
+        <v>1</v>
+      </c>
+      <c r="AP337">
+        <v>1</v>
+      </c>
+      <c r="AQ337">
+        <v>1.18</v>
+      </c>
+      <c r="AR337">
+        <v>1.43</v>
+      </c>
+      <c r="AS337">
+        <v>1.2</v>
+      </c>
+      <c r="AT337">
+        <v>2.63</v>
+      </c>
+      <c r="AU337">
+        <v>2</v>
+      </c>
+      <c r="AV337">
+        <v>4</v>
+      </c>
+      <c r="AW337">
+        <v>2</v>
+      </c>
+      <c r="AX337">
+        <v>1</v>
+      </c>
+      <c r="AY337">
+        <v>4</v>
+      </c>
+      <c r="AZ337">
+        <v>5</v>
+      </c>
+      <c r="BA337">
+        <v>8</v>
+      </c>
+      <c r="BB337">
+        <v>2</v>
+      </c>
+      <c r="BC337">
+        <v>10</v>
+      </c>
+      <c r="BD337">
+        <v>1.68</v>
+      </c>
+      <c r="BE337">
+        <v>6.4</v>
+      </c>
+      <c r="BF337">
+        <v>2.43</v>
+      </c>
+      <c r="BG337">
+        <v>1.24</v>
+      </c>
+      <c r="BH337">
+        <v>3.55</v>
+      </c>
+      <c r="BI337">
+        <v>1.44</v>
+      </c>
+      <c r="BJ337">
+        <v>2.55</v>
+      </c>
+      <c r="BK337">
+        <v>1.71</v>
+      </c>
+      <c r="BL337">
+        <v>2</v>
+      </c>
+      <c r="BM337">
+        <v>2.1</v>
+      </c>
+      <c r="BN337">
+        <v>1.63</v>
+      </c>
+      <c r="BO337">
+        <v>2.65</v>
+      </c>
+      <c r="BP337">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="481">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1012,6 +1012,9 @@
     <t>['90+3']</t>
   </si>
   <si>
+    <t>['31', '78']</t>
+  </si>
+  <si>
     <t>['26', '55']</t>
   </si>
   <si>
@@ -1815,7 +1818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP337"/>
+  <dimension ref="A1:BP338"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2277,7 +2280,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -2483,7 +2486,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2895,7 +2898,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -2973,7 +2976,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ6">
         <v>1.58</v>
@@ -3101,7 +3104,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3307,7 +3310,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -3719,7 +3722,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -4543,7 +4546,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -4749,7 +4752,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4955,7 +4958,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -5985,7 +5988,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -6397,7 +6400,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6478,7 +6481,7 @@
         <v>1</v>
       </c>
       <c r="AQ23">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6603,7 +6606,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -7015,7 +7018,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -8045,7 +8048,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -8329,7 +8332,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ32">
         <v>1.18</v>
@@ -8457,7 +8460,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -9281,7 +9284,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9899,7 +9902,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -10311,7 +10314,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -11135,7 +11138,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -11341,7 +11344,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -11547,7 +11550,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -12371,7 +12374,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12577,7 +12580,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12989,7 +12992,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -13607,7 +13610,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13813,7 +13816,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -14225,7 +14228,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14431,7 +14434,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -14637,7 +14640,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14843,7 +14846,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -15127,7 +15130,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ65">
         <v>0.91</v>
@@ -15542,7 +15545,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ67">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR67">
         <v>1.65</v>
@@ -15873,7 +15876,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -16285,7 +16288,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16491,7 +16494,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16903,7 +16906,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -18139,7 +18142,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18345,7 +18348,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18551,7 +18554,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -19169,7 +19172,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -19375,7 +19378,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -19581,7 +19584,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -20199,7 +20202,7 @@
         <v>164</v>
       </c>
       <c r="P90" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
@@ -21435,7 +21438,7 @@
         <v>168</v>
       </c>
       <c r="P96" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -21513,7 +21516,7 @@
         <v>0.33</v>
       </c>
       <c r="AP96">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ96">
         <v>0.6899999999999999</v>
@@ -22877,7 +22880,7 @@
         <v>122</v>
       </c>
       <c r="P103" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q103">
         <v>2.75</v>
@@ -23164,7 +23167,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ104">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR104">
         <v>1.95</v>
@@ -25143,7 +25146,7 @@
         <v>177</v>
       </c>
       <c r="P114" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25349,7 +25352,7 @@
         <v>178</v>
       </c>
       <c r="P115" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -25761,7 +25764,7 @@
         <v>179</v>
       </c>
       <c r="P117" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25967,7 +25970,7 @@
         <v>180</v>
       </c>
       <c r="P118" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -26379,7 +26382,7 @@
         <v>181</v>
       </c>
       <c r="P120" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -26791,7 +26794,7 @@
         <v>109</v>
       </c>
       <c r="P122" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q122">
         <v>2.75</v>
@@ -26869,7 +26872,7 @@
         <v>2.33</v>
       </c>
       <c r="AP122">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ122">
         <v>1.8</v>
@@ -27203,7 +27206,7 @@
         <v>129</v>
       </c>
       <c r="P124" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q124">
         <v>2.5</v>
@@ -27284,7 +27287,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ124">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR124">
         <v>1.48</v>
@@ -28233,7 +28236,7 @@
         <v>187</v>
       </c>
       <c r="P129" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28439,7 +28442,7 @@
         <v>188</v>
       </c>
       <c r="P130" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q130">
         <v>2.4</v>
@@ -29263,7 +29266,7 @@
         <v>189</v>
       </c>
       <c r="P134" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q134">
         <v>3</v>
@@ -29469,7 +29472,7 @@
         <v>190</v>
       </c>
       <c r="P135" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -30168,7 +30171,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ138">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR138">
         <v>1.73</v>
@@ -30705,7 +30708,7 @@
         <v>109</v>
       </c>
       <c r="P141" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q141">
         <v>2.38</v>
@@ -30989,7 +30992,7 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ142">
         <v>1.27</v>
@@ -31117,7 +31120,7 @@
         <v>174</v>
       </c>
       <c r="P143" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -31529,7 +31532,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q145">
         <v>2.4</v>
@@ -31735,7 +31738,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31941,7 +31944,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q147">
         <v>2.6</v>
@@ -32147,7 +32150,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q148">
         <v>2.05</v>
@@ -32353,7 +32356,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -32559,7 +32562,7 @@
         <v>202</v>
       </c>
       <c r="P150" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q150">
         <v>2.4</v>
@@ -32971,7 +32974,7 @@
         <v>109</v>
       </c>
       <c r="P152" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q152">
         <v>2.88</v>
@@ -33383,7 +33386,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q154">
         <v>3.1</v>
@@ -33589,7 +33592,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q155">
         <v>2.2</v>
@@ -33667,7 +33670,7 @@
         <v>1</v>
       </c>
       <c r="AP155">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ155">
         <v>0.58</v>
@@ -34001,7 +34004,7 @@
         <v>109</v>
       </c>
       <c r="P157" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q157">
         <v>3.2</v>
@@ -34619,7 +34622,7 @@
         <v>209</v>
       </c>
       <c r="P160" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q160">
         <v>2.1</v>
@@ -36348,7 +36351,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ168">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR168">
         <v>1.25</v>
@@ -36473,7 +36476,7 @@
         <v>217</v>
       </c>
       <c r="P169" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q169">
         <v>3</v>
@@ -36679,7 +36682,7 @@
         <v>218</v>
       </c>
       <c r="P170" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -37503,7 +37506,7 @@
         <v>221</v>
       </c>
       <c r="P174" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q174">
         <v>2.5</v>
@@ -37709,7 +37712,7 @@
         <v>163</v>
       </c>
       <c r="P175" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -38121,7 +38124,7 @@
         <v>222</v>
       </c>
       <c r="P177" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -38327,7 +38330,7 @@
         <v>109</v>
       </c>
       <c r="P178" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q178">
         <v>2.38</v>
@@ -38739,7 +38742,7 @@
         <v>224</v>
       </c>
       <c r="P180" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -39151,7 +39154,7 @@
         <v>225</v>
       </c>
       <c r="P182" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q182">
         <v>3.75</v>
@@ -39357,7 +39360,7 @@
         <v>226</v>
       </c>
       <c r="P183" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q183">
         <v>2.5</v>
@@ -39563,7 +39566,7 @@
         <v>227</v>
       </c>
       <c r="P184" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q184">
         <v>2.05</v>
@@ -39975,7 +39978,7 @@
         <v>228</v>
       </c>
       <c r="P186" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q186">
         <v>2.4</v>
@@ -40387,7 +40390,7 @@
         <v>230</v>
       </c>
       <c r="P188" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40593,7 +40596,7 @@
         <v>176</v>
       </c>
       <c r="P189" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -41417,7 +41420,7 @@
         <v>233</v>
       </c>
       <c r="P193" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41623,7 +41626,7 @@
         <v>234</v>
       </c>
       <c r="P194" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -42035,7 +42038,7 @@
         <v>198</v>
       </c>
       <c r="P196" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q196">
         <v>2.63</v>
@@ -42113,7 +42116,7 @@
         <v>1.71</v>
       </c>
       <c r="AP196">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ196">
         <v>1.83</v>
@@ -42447,7 +42450,7 @@
         <v>103</v>
       </c>
       <c r="P198" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q198">
         <v>2.63</v>
@@ -43146,7 +43149,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ201">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR201">
         <v>1.89</v>
@@ -43477,7 +43480,7 @@
         <v>109</v>
       </c>
       <c r="P203" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q203">
         <v>2.63</v>
@@ -43889,7 +43892,7 @@
         <v>237</v>
       </c>
       <c r="P205" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -44301,7 +44304,7 @@
         <v>109</v>
       </c>
       <c r="P207" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q207">
         <v>2.25</v>
@@ -45125,7 +45128,7 @@
         <v>240</v>
       </c>
       <c r="P211" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q211">
         <v>3.2</v>
@@ -45331,7 +45334,7 @@
         <v>109</v>
       </c>
       <c r="P212" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45537,7 +45540,7 @@
         <v>241</v>
       </c>
       <c r="P213" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q213">
         <v>4</v>
@@ -45949,7 +45952,7 @@
         <v>242</v>
       </c>
       <c r="P215" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -46155,7 +46158,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q216">
         <v>3.4</v>
@@ -46361,7 +46364,7 @@
         <v>243</v>
       </c>
       <c r="P217" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q217">
         <v>2.75</v>
@@ -46773,7 +46776,7 @@
         <v>244</v>
       </c>
       <c r="P219" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q219">
         <v>3.1</v>
@@ -47185,7 +47188,7 @@
         <v>246</v>
       </c>
       <c r="P221" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q221">
         <v>2.6</v>
@@ -47391,7 +47394,7 @@
         <v>247</v>
       </c>
       <c r="P222" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q222">
         <v>2.5</v>
@@ -47597,7 +47600,7 @@
         <v>248</v>
       </c>
       <c r="P223" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47803,7 +47806,7 @@
         <v>249</v>
       </c>
       <c r="P224" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -48009,7 +48012,7 @@
         <v>250</v>
       </c>
       <c r="P225" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -48215,7 +48218,7 @@
         <v>251</v>
       </c>
       <c r="P226" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q226">
         <v>2.75</v>
@@ -48421,7 +48424,7 @@
         <v>252</v>
       </c>
       <c r="P227" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q227">
         <v>1.83</v>
@@ -48627,7 +48630,7 @@
         <v>253</v>
       </c>
       <c r="P228" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48833,7 +48836,7 @@
         <v>109</v>
       </c>
       <c r="P229" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q229">
         <v>2.5</v>
@@ -49039,7 +49042,7 @@
         <v>254</v>
       </c>
       <c r="P230" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q230">
         <v>3.25</v>
@@ -49245,7 +49248,7 @@
         <v>119</v>
       </c>
       <c r="P231" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q231">
         <v>2.4</v>
@@ -49323,7 +49326,7 @@
         <v>1.17</v>
       </c>
       <c r="AP231">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ231">
         <v>1.73</v>
@@ -49863,7 +49866,7 @@
         <v>109</v>
       </c>
       <c r="P234" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q234">
         <v>2.5</v>
@@ -50481,7 +50484,7 @@
         <v>258</v>
       </c>
       <c r="P237" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q237">
         <v>2.75</v>
@@ -50687,7 +50690,7 @@
         <v>259</v>
       </c>
       <c r="P238" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q238">
         <v>2.6</v>
@@ -50893,7 +50896,7 @@
         <v>109</v>
       </c>
       <c r="P239" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -51099,7 +51102,7 @@
         <v>140</v>
       </c>
       <c r="P240" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -51180,7 +51183,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ240">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR240">
         <v>1.88</v>
@@ -51511,7 +51514,7 @@
         <v>109</v>
       </c>
       <c r="P242" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q242">
         <v>3.1</v>
@@ -51923,7 +51926,7 @@
         <v>161</v>
       </c>
       <c r="P244" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q244">
         <v>2.1</v>
@@ -52335,7 +52338,7 @@
         <v>156</v>
       </c>
       <c r="P246" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q246">
         <v>2.5</v>
@@ -52953,7 +52956,7 @@
         <v>264</v>
       </c>
       <c r="P249" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q249">
         <v>2.5</v>
@@ -53159,7 +53162,7 @@
         <v>265</v>
       </c>
       <c r="P250" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q250">
         <v>3.2</v>
@@ -53365,7 +53368,7 @@
         <v>109</v>
       </c>
       <c r="P251" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q251">
         <v>2.75</v>
@@ -53571,7 +53574,7 @@
         <v>266</v>
       </c>
       <c r="P252" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q252">
         <v>2.25</v>
@@ -54601,7 +54604,7 @@
         <v>271</v>
       </c>
       <c r="P257" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q257">
         <v>2.63</v>
@@ -54807,7 +54810,7 @@
         <v>272</v>
       </c>
       <c r="P258" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q258">
         <v>2.3</v>
@@ -54885,7 +54888,7 @@
         <v>2.14</v>
       </c>
       <c r="AP258">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ258">
         <v>1.75</v>
@@ -55013,7 +55016,7 @@
         <v>109</v>
       </c>
       <c r="P259" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q259">
         <v>3.1</v>
@@ -55425,7 +55428,7 @@
         <v>274</v>
       </c>
       <c r="P261" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -55631,7 +55634,7 @@
         <v>275</v>
       </c>
       <c r="P262" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Q262">
         <v>2.5</v>
@@ -55837,7 +55840,7 @@
         <v>234</v>
       </c>
       <c r="P263" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q263">
         <v>2.25</v>
@@ -56043,7 +56046,7 @@
         <v>109</v>
       </c>
       <c r="P264" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Q264">
         <v>2.75</v>
@@ -56249,7 +56252,7 @@
         <v>276</v>
       </c>
       <c r="P265" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q265">
         <v>2.88</v>
@@ -56455,7 +56458,7 @@
         <v>109</v>
       </c>
       <c r="P266" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q266">
         <v>3.4</v>
@@ -56742,7 +56745,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ267">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR267">
         <v>1.45</v>
@@ -56867,7 +56870,7 @@
         <v>278</v>
       </c>
       <c r="P268" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q268">
         <v>2.2</v>
@@ -56945,7 +56948,7 @@
         <v>0.25</v>
       </c>
       <c r="AP268">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ268">
         <v>0.36</v>
@@ -57073,7 +57076,7 @@
         <v>279</v>
       </c>
       <c r="P269" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57279,7 +57282,7 @@
         <v>280</v>
       </c>
       <c r="P270" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q270">
         <v>3.35</v>
@@ -57691,7 +57694,7 @@
         <v>282</v>
       </c>
       <c r="P272" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Q272">
         <v>2.38</v>
@@ -57897,7 +57900,7 @@
         <v>283</v>
       </c>
       <c r="P273" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q273">
         <v>3.4</v>
@@ -58103,7 +58106,7 @@
         <v>284</v>
       </c>
       <c r="P274" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q274">
         <v>3</v>
@@ -58515,7 +58518,7 @@
         <v>285</v>
       </c>
       <c r="P276" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q276">
         <v>2.63</v>
@@ -58721,7 +58724,7 @@
         <v>286</v>
       </c>
       <c r="P277" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -59133,7 +59136,7 @@
         <v>288</v>
       </c>
       <c r="P279" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q279">
         <v>2.63</v>
@@ -59545,7 +59548,7 @@
         <v>290</v>
       </c>
       <c r="P281" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Q281">
         <v>2.25</v>
@@ -59751,7 +59754,7 @@
         <v>291</v>
       </c>
       <c r="P282" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Q282">
         <v>2.88</v>
@@ -60369,7 +60372,7 @@
         <v>293</v>
       </c>
       <c r="P285" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Q285">
         <v>2.5</v>
@@ -60575,7 +60578,7 @@
         <v>294</v>
       </c>
       <c r="P286" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -61683,7 +61686,7 @@
         <v>2.11</v>
       </c>
       <c r="AP291">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ291">
         <v>1.73</v>
@@ -62223,7 +62226,7 @@
         <v>112</v>
       </c>
       <c r="P294" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Q294">
         <v>3.1</v>
@@ -62429,7 +62432,7 @@
         <v>122</v>
       </c>
       <c r="P295" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Q295">
         <v>2.4</v>
@@ -62841,7 +62844,7 @@
         <v>301</v>
       </c>
       <c r="P297" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Q297">
         <v>3.4</v>
@@ -63253,7 +63256,7 @@
         <v>302</v>
       </c>
       <c r="P299" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Q299">
         <v>3.2</v>
@@ -63871,7 +63874,7 @@
         <v>305</v>
       </c>
       <c r="P302" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Q302">
         <v>2.2</v>
@@ -64077,7 +64080,7 @@
         <v>255</v>
       </c>
       <c r="P303" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q303">
         <v>2.5</v>
@@ -64283,7 +64286,7 @@
         <v>306</v>
       </c>
       <c r="P304" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Q304">
         <v>2.5</v>
@@ -64489,7 +64492,7 @@
         <v>307</v>
       </c>
       <c r="P305" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -64901,7 +64904,7 @@
         <v>199</v>
       </c>
       <c r="P307" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Q307">
         <v>3.26</v>
@@ -65725,7 +65728,7 @@
         <v>312</v>
       </c>
       <c r="P311" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="Q311">
         <v>1.83</v>
@@ -66343,7 +66346,7 @@
         <v>288</v>
       </c>
       <c r="P314" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="Q314">
         <v>0</v>
@@ -66549,7 +66552,7 @@
         <v>314</v>
       </c>
       <c r="P315" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Q315">
         <v>3.5</v>
@@ -66961,7 +66964,7 @@
         <v>316</v>
       </c>
       <c r="P317" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Q317">
         <v>2.63</v>
@@ -67785,7 +67788,7 @@
         <v>320</v>
       </c>
       <c r="P321" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q321">
         <v>2.2</v>
@@ -67866,7 +67869,7 @@
         <v>1</v>
       </c>
       <c r="AQ321">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR321">
         <v>1.42</v>
@@ -68197,7 +68200,7 @@
         <v>322</v>
       </c>
       <c r="P323" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q323">
         <v>2.63</v>
@@ -68609,7 +68612,7 @@
         <v>324</v>
       </c>
       <c r="P325" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Q325">
         <v>2.3</v>
@@ -69102,7 +69105,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ327">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR327">
         <v>1.57</v>
@@ -69227,7 +69230,7 @@
         <v>327</v>
       </c>
       <c r="P328" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Q328">
         <v>2.55</v>
@@ -69433,7 +69436,7 @@
         <v>237</v>
       </c>
       <c r="P329" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Q329">
         <v>2.15</v>
@@ -69639,7 +69642,7 @@
         <v>109</v>
       </c>
       <c r="P330" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="Q330">
         <v>2.8</v>
@@ -70257,7 +70260,7 @@
         <v>329</v>
       </c>
       <c r="P333" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="Q333">
         <v>1.95</v>
@@ -70463,7 +70466,7 @@
         <v>330</v>
       </c>
       <c r="P334" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Q334">
         <v>2.05</v>
@@ -70875,7 +70878,7 @@
         <v>109</v>
       </c>
       <c r="P336" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="Q336">
         <v>2.63</v>
@@ -71081,7 +71084,7 @@
         <v>331</v>
       </c>
       <c r="P337" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Q337">
         <v>2.5</v>
@@ -71238,6 +71241,212 @@
       </c>
       <c r="BP337">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="338" spans="1:68">
+      <c r="A338" s="1">
+        <v>337</v>
+      </c>
+      <c r="B338">
+        <v>7781417</v>
+      </c>
+      <c r="C338" t="s">
+        <v>68</v>
+      </c>
+      <c r="D338" t="s">
+        <v>69</v>
+      </c>
+      <c r="E338" s="2">
+        <v>45857.88541666666</v>
+      </c>
+      <c r="F338">
+        <v>0</v>
+      </c>
+      <c r="G338" t="s">
+        <v>74</v>
+      </c>
+      <c r="H338" t="s">
+        <v>75</v>
+      </c>
+      <c r="I338">
+        <v>1</v>
+      </c>
+      <c r="J338">
+        <v>0</v>
+      </c>
+      <c r="K338">
+        <v>1</v>
+      </c>
+      <c r="L338">
+        <v>2</v>
+      </c>
+      <c r="M338">
+        <v>1</v>
+      </c>
+      <c r="N338">
+        <v>3</v>
+      </c>
+      <c r="O338" t="s">
+        <v>332</v>
+      </c>
+      <c r="P338" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q338">
+        <v>1.95</v>
+      </c>
+      <c r="R338">
+        <v>2.63</v>
+      </c>
+      <c r="S338">
+        <v>5.5</v>
+      </c>
+      <c r="T338">
+        <v>1.25</v>
+      </c>
+      <c r="U338">
+        <v>3.75</v>
+      </c>
+      <c r="V338">
+        <v>2.1</v>
+      </c>
+      <c r="W338">
+        <v>1.67</v>
+      </c>
+      <c r="X338">
+        <v>4.5</v>
+      </c>
+      <c r="Y338">
+        <v>1.18</v>
+      </c>
+      <c r="Z338">
+        <v>1.45</v>
+      </c>
+      <c r="AA338">
+        <v>3.8</v>
+      </c>
+      <c r="AB338">
+        <v>6</v>
+      </c>
+      <c r="AC338">
+        <v>1.01</v>
+      </c>
+      <c r="AD338">
+        <v>17</v>
+      </c>
+      <c r="AE338">
+        <v>1.17</v>
+      </c>
+      <c r="AF338">
+        <v>5</v>
+      </c>
+      <c r="AG338">
+        <v>1.45</v>
+      </c>
+      <c r="AH338">
+        <v>2.63</v>
+      </c>
+      <c r="AI338">
+        <v>1.57</v>
+      </c>
+      <c r="AJ338">
+        <v>2.25</v>
+      </c>
+      <c r="AK338">
+        <v>1.14</v>
+      </c>
+      <c r="AL338">
+        <v>1.2</v>
+      </c>
+      <c r="AM338">
+        <v>2.5</v>
+      </c>
+      <c r="AN338">
+        <v>2</v>
+      </c>
+      <c r="AO338">
+        <v>0.73</v>
+      </c>
+      <c r="AP338">
+        <v>2.08</v>
+      </c>
+      <c r="AQ338">
+        <v>0.67</v>
+      </c>
+      <c r="AR338">
+        <v>1.81</v>
+      </c>
+      <c r="AS338">
+        <v>1.46</v>
+      </c>
+      <c r="AT338">
+        <v>3.27</v>
+      </c>
+      <c r="AU338">
+        <v>5</v>
+      </c>
+      <c r="AV338">
+        <v>2</v>
+      </c>
+      <c r="AW338">
+        <v>14</v>
+      </c>
+      <c r="AX338">
+        <v>5</v>
+      </c>
+      <c r="AY338">
+        <v>19</v>
+      </c>
+      <c r="AZ338">
+        <v>7</v>
+      </c>
+      <c r="BA338">
+        <v>7</v>
+      </c>
+      <c r="BB338">
+        <v>0</v>
+      </c>
+      <c r="BC338">
+        <v>7</v>
+      </c>
+      <c r="BD338">
+        <v>1.46</v>
+      </c>
+      <c r="BE338">
+        <v>6.75</v>
+      </c>
+      <c r="BF338">
+        <v>3.05</v>
+      </c>
+      <c r="BG338">
+        <v>1.34</v>
+      </c>
+      <c r="BH338">
+        <v>2.9</v>
+      </c>
+      <c r="BI338">
+        <v>1.58</v>
+      </c>
+      <c r="BJ338">
+        <v>2.2</v>
+      </c>
+      <c r="BK338">
+        <v>1.95</v>
+      </c>
+      <c r="BL338">
+        <v>1.74</v>
+      </c>
+      <c r="BM338">
+        <v>2.48</v>
+      </c>
+      <c r="BN338">
+        <v>1.47</v>
+      </c>
+      <c r="BO338">
+        <v>3.2</v>
+      </c>
+      <c r="BP338">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/USA MLS_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="483">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1012,6 +1012,9 @@
     <t>['90+3']</t>
   </si>
   <si>
+    <t>['19', '86']</t>
+  </si>
+  <si>
     <t>['31', '78']</t>
   </si>
   <si>
@@ -1458,6 +1461,9 @@
   <si>
     <t>['40', '63']</t>
   </si>
+  <si>
+    <t>['46', '59', '77']</t>
+  </si>
 </sst>
 </file>
 
@@ -1818,7 +1824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP338"/>
+  <dimension ref="A1:BP339"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2280,7 +2286,7 @@
         <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q3">
         <v>2.25</v>
@@ -2486,7 +2492,7 @@
         <v>102</v>
       </c>
       <c r="P4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -2564,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4">
         <v>0.6899999999999999</v>
@@ -2898,7 +2904,7 @@
         <v>104</v>
       </c>
       <c r="P6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
@@ -3104,7 +3110,7 @@
         <v>105</v>
       </c>
       <c r="P7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q7">
         <v>2.38</v>
@@ -3310,7 +3316,7 @@
         <v>106</v>
       </c>
       <c r="P8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q8">
         <v>2.25</v>
@@ -3722,7 +3728,7 @@
         <v>108</v>
       </c>
       <c r="P10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
@@ -4546,7 +4552,7 @@
         <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q14">
         <v>2.38</v>
@@ -4627,7 +4633,7 @@
         <v>2</v>
       </c>
       <c r="AQ14">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4752,7 +4758,7 @@
         <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q15">
         <v>2.4</v>
@@ -4958,7 +4964,7 @@
         <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -5988,7 +5994,7 @@
         <v>115</v>
       </c>
       <c r="P21" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -6400,7 +6406,7 @@
         <v>117</v>
       </c>
       <c r="P23" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -6606,7 +6612,7 @@
         <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q24">
         <v>2.63</v>
@@ -7018,7 +7024,7 @@
         <v>120</v>
       </c>
       <c r="P26" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q26">
         <v>2.75</v>
@@ -8048,7 +8054,7 @@
         <v>124</v>
       </c>
       <c r="P31" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -8460,7 +8466,7 @@
         <v>125</v>
       </c>
       <c r="P33" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -8744,7 +8750,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ34">
         <v>0.58</v>
@@ -9284,7 +9290,7 @@
         <v>109</v>
       </c>
       <c r="P37" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q37">
         <v>3.1</v>
@@ -9902,7 +9908,7 @@
         <v>129</v>
       </c>
       <c r="P40" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q40">
         <v>2.38</v>
@@ -10314,7 +10320,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -11013,7 +11019,7 @@
         <v>2</v>
       </c>
       <c r="AQ45">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR45">
         <v>1.62</v>
@@ -11138,7 +11144,7 @@
         <v>109</v>
       </c>
       <c r="P46" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q46">
         <v>2.2</v>
@@ -11344,7 +11350,7 @@
         <v>134</v>
       </c>
       <c r="P47" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q47">
         <v>2.63</v>
@@ -11550,7 +11556,7 @@
         <v>135</v>
       </c>
       <c r="P48" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q48">
         <v>2.88</v>
@@ -12374,7 +12380,7 @@
         <v>137</v>
       </c>
       <c r="P52" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q52">
         <v>2.3</v>
@@ -12580,7 +12586,7 @@
         <v>138</v>
       </c>
       <c r="P53" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q53">
         <v>3</v>
@@ -12992,7 +12998,7 @@
         <v>139</v>
       </c>
       <c r="P55" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q55">
         <v>2.38</v>
@@ -13610,7 +13616,7 @@
         <v>141</v>
       </c>
       <c r="P58" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q58">
         <v>2.6</v>
@@ -13816,7 +13822,7 @@
         <v>142</v>
       </c>
       <c r="P59" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q59">
         <v>2.38</v>
@@ -14228,7 +14234,7 @@
         <v>134</v>
       </c>
       <c r="P61" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14306,7 +14312,7 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ61">
         <v>1.8</v>
@@ -14434,7 +14440,7 @@
         <v>144</v>
       </c>
       <c r="P62" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q62">
         <v>2.38</v>
@@ -14640,7 +14646,7 @@
         <v>145</v>
       </c>
       <c r="P63" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q63">
         <v>2.5</v>
@@ -14846,7 +14852,7 @@
         <v>146</v>
       </c>
       <c r="P64" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -15876,7 +15882,7 @@
         <v>109</v>
       </c>
       <c r="P69" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -16288,7 +16294,7 @@
         <v>109</v>
       </c>
       <c r="P71" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q71">
         <v>2.38</v>
@@ -16494,7 +16500,7 @@
         <v>109</v>
       </c>
       <c r="P72" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q72">
         <v>2.6</v>
@@ -16906,7 +16912,7 @@
         <v>151</v>
       </c>
       <c r="P74" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -17811,7 +17817,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ78">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR78">
         <v>1.49</v>
@@ -18142,7 +18148,7 @@
         <v>156</v>
       </c>
       <c r="P80" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q80">
         <v>3</v>
@@ -18348,7 +18354,7 @@
         <v>157</v>
       </c>
       <c r="P81" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q81">
         <v>2.5</v>
@@ -18426,7 +18432,7 @@
         <v>0.67</v>
       </c>
       <c r="AP81">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ81">
         <v>0.91</v>
@@ -18554,7 +18560,7 @@
         <v>158</v>
       </c>
       <c r="P82" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -19172,7 +19178,7 @@
         <v>161</v>
       </c>
       <c r="P85" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q85">
         <v>2.88</v>
@@ -19378,7 +19384,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -19584,7 +19590,7 @@
         <v>162</v>
       </c>
       <c r="P87" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -20202,7 +20208,7 @@
         <v>164</v>
       </c>
       <c r="P90" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
@@ -20898,7 +20904,7 @@
         <v>2.33</v>
       </c>
       <c r="AP93">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ93">
         <v>1.42</v>
@@ -21438,7 +21444,7 @@
         <v>168</v>
       </c>
       <c r="P96" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q96">
         <v>1.95</v>
@@ -22880,7 +22886,7 @@
         <v>122</v>
       </c>
       <c r="P103" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q103">
         <v>2.75</v>
@@ -23782,7 +23788,7 @@
         <v>0.33</v>
       </c>
       <c r="AP107">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ107">
         <v>1.31</v>
@@ -24197,7 +24203,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ109">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR109">
         <v>0</v>
@@ -25146,7 +25152,7 @@
         <v>177</v>
       </c>
       <c r="P114" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q114">
         <v>2.4</v>
@@ -25352,7 +25358,7 @@
         <v>178</v>
       </c>
       <c r="P115" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -25764,7 +25770,7 @@
         <v>179</v>
       </c>
       <c r="P117" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -25970,7 +25976,7 @@
         <v>180</v>
       </c>
       <c r="P118" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q118">
         <v>2.75</v>
@@ -26382,7 +26388,7 @@
         <v>181</v>
       </c>
       <c r="P120" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q120">
         <v>3.1</v>
@@ -26794,7 +26800,7 @@
         <v>109</v>
       </c>
       <c r="P122" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q122">
         <v>2.75</v>
@@ -27206,7 +27212,7 @@
         <v>129</v>
       </c>
       <c r="P124" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q124">
         <v>2.5</v>
@@ -28236,7 +28242,7 @@
         <v>187</v>
       </c>
       <c r="P129" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -28442,7 +28448,7 @@
         <v>188</v>
       </c>
       <c r="P130" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q130">
         <v>2.4</v>
@@ -29266,7 +29272,7 @@
         <v>189</v>
       </c>
       <c r="P134" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q134">
         <v>3</v>
@@ -29472,7 +29478,7 @@
         <v>190</v>
       </c>
       <c r="P135" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -30708,7 +30714,7 @@
         <v>109</v>
       </c>
       <c r="P141" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q141">
         <v>2.38</v>
@@ -31120,7 +31126,7 @@
         <v>174</v>
       </c>
       <c r="P143" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -31532,7 +31538,7 @@
         <v>197</v>
       </c>
       <c r="P145" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q145">
         <v>2.4</v>
@@ -31738,7 +31744,7 @@
         <v>198</v>
       </c>
       <c r="P146" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q146">
         <v>3.25</v>
@@ -31944,7 +31950,7 @@
         <v>199</v>
       </c>
       <c r="P147" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q147">
         <v>2.6</v>
@@ -32150,7 +32156,7 @@
         <v>200</v>
       </c>
       <c r="P148" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q148">
         <v>2.05</v>
@@ -32356,7 +32362,7 @@
         <v>201</v>
       </c>
       <c r="P149" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -32562,7 +32568,7 @@
         <v>202</v>
       </c>
       <c r="P150" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q150">
         <v>2.4</v>
@@ -32846,7 +32852,7 @@
         <v>0.75</v>
       </c>
       <c r="AP151">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ151">
         <v>1.73</v>
@@ -32974,7 +32980,7 @@
         <v>109</v>
       </c>
       <c r="P152" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q152">
         <v>2.88</v>
@@ -33386,7 +33392,7 @@
         <v>205</v>
       </c>
       <c r="P154" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q154">
         <v>3.1</v>
@@ -33592,7 +33598,7 @@
         <v>206</v>
       </c>
       <c r="P155" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q155">
         <v>2.2</v>
@@ -33673,7 +33679,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ155">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR155">
         <v>1.65</v>
@@ -34004,7 +34010,7 @@
         <v>109</v>
       </c>
       <c r="P157" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q157">
         <v>3.2</v>
@@ -34622,7 +34628,7 @@
         <v>209</v>
       </c>
       <c r="P160" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q160">
         <v>2.1</v>
@@ -36476,7 +36482,7 @@
         <v>217</v>
       </c>
       <c r="P169" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q169">
         <v>3</v>
@@ -36682,7 +36688,7 @@
         <v>218</v>
       </c>
       <c r="P170" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -37506,7 +37512,7 @@
         <v>221</v>
       </c>
       <c r="P174" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q174">
         <v>2.5</v>
@@ -37712,7 +37718,7 @@
         <v>163</v>
       </c>
       <c r="P175" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -37999,7 +38005,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ176">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR176">
         <v>1.93</v>
@@ -38124,7 +38130,7 @@
         <v>222</v>
       </c>
       <c r="P177" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -38330,7 +38336,7 @@
         <v>109</v>
       </c>
       <c r="P178" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q178">
         <v>2.38</v>
@@ -38742,7 +38748,7 @@
         <v>224</v>
       </c>
       <c r="P180" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q180">
         <v>2.5</v>
@@ -39154,7 +39160,7 @@
         <v>225</v>
       </c>
       <c r="P182" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q182">
         <v>3.75</v>
@@ -39360,7 +39366,7 @@
         <v>226</v>
       </c>
       <c r="P183" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q183">
         <v>2.5</v>
@@ -39441,7 +39447,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ183">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR183">
         <v>1.98</v>
@@ -39566,7 +39572,7 @@
         <v>227</v>
       </c>
       <c r="P184" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q184">
         <v>2.05</v>
@@ -39978,7 +39984,7 @@
         <v>228</v>
       </c>
       <c r="P186" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q186">
         <v>2.4</v>
@@ -40390,7 +40396,7 @@
         <v>230</v>
       </c>
       <c r="P188" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q188">
         <v>3</v>
@@ -40596,7 +40602,7 @@
         <v>176</v>
       </c>
       <c r="P189" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q189">
         <v>3</v>
@@ -41420,7 +41426,7 @@
         <v>233</v>
       </c>
       <c r="P193" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q193">
         <v>3</v>
@@ -41626,7 +41632,7 @@
         <v>234</v>
       </c>
       <c r="P194" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q194">
         <v>2.75</v>
@@ -42038,7 +42044,7 @@
         <v>198</v>
       </c>
       <c r="P196" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q196">
         <v>2.63</v>
@@ -42322,7 +42328,7 @@
         <v>1.8</v>
       </c>
       <c r="AP197">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ197">
         <v>1.73</v>
@@ -42450,7 +42456,7 @@
         <v>103</v>
       </c>
       <c r="P198" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q198">
         <v>2.63</v>
@@ -43480,7 +43486,7 @@
         <v>109</v>
       </c>
       <c r="P203" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q203">
         <v>2.63</v>
@@ -43892,7 +43898,7 @@
         <v>237</v>
       </c>
       <c r="P205" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q205">
         <v>3</v>
@@ -44304,7 +44310,7 @@
         <v>109</v>
       </c>
       <c r="P207" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q207">
         <v>2.25</v>
@@ -45128,7 +45134,7 @@
         <v>240</v>
       </c>
       <c r="P211" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q211">
         <v>3.2</v>
@@ -45334,7 +45340,7 @@
         <v>109</v>
       </c>
       <c r="P212" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q212">
         <v>3.1</v>
@@ -45540,7 +45546,7 @@
         <v>241</v>
       </c>
       <c r="P213" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q213">
         <v>4</v>
@@ -45952,7 +45958,7 @@
         <v>242</v>
       </c>
       <c r="P215" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q215">
         <v>2.75</v>
@@ -46158,7 +46164,7 @@
         <v>222</v>
       </c>
       <c r="P216" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q216">
         <v>3.4</v>
@@ -46364,7 +46370,7 @@
         <v>243</v>
       </c>
       <c r="P217" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q217">
         <v>2.75</v>
@@ -46776,7 +46782,7 @@
         <v>244</v>
       </c>
       <c r="P219" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q219">
         <v>3.1</v>
@@ -47188,7 +47194,7 @@
         <v>246</v>
       </c>
       <c r="P221" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q221">
         <v>2.6</v>
@@ -47394,7 +47400,7 @@
         <v>247</v>
       </c>
       <c r="P222" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q222">
         <v>2.5</v>
@@ -47600,7 +47606,7 @@
         <v>248</v>
       </c>
       <c r="P223" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q223">
         <v>3</v>
@@ -47678,7 +47684,7 @@
         <v>1.63</v>
       </c>
       <c r="AP223">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ223">
         <v>1.83</v>
@@ -47806,7 +47812,7 @@
         <v>249</v>
       </c>
       <c r="P224" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q224">
         <v>3</v>
@@ -47884,7 +47890,7 @@
         <v>1.43</v>
       </c>
       <c r="AP224">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ224">
         <v>1.55</v>
@@ -48012,7 +48018,7 @@
         <v>250</v>
       </c>
       <c r="P225" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q225">
         <v>2.2</v>
@@ -48218,7 +48224,7 @@
         <v>251</v>
       </c>
       <c r="P226" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q226">
         <v>2.75</v>
@@ -48424,7 +48430,7 @@
         <v>252</v>
       </c>
       <c r="P227" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q227">
         <v>1.83</v>
@@ -48630,7 +48636,7 @@
         <v>253</v>
       </c>
       <c r="P228" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q228">
         <v>2.5</v>
@@ -48711,7 +48717,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ228">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR228">
         <v>1.63</v>
@@ -48836,7 +48842,7 @@
         <v>109</v>
       </c>
       <c r="P229" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q229">
         <v>2.5</v>
@@ -49042,7 +49048,7 @@
         <v>254</v>
       </c>
       <c r="P230" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q230">
         <v>3.25</v>
@@ -49248,7 +49254,7 @@
         <v>119</v>
       </c>
       <c r="P231" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q231">
         <v>2.4</v>
@@ -49866,7 +49872,7 @@
         <v>109</v>
       </c>
       <c r="P234" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q234">
         <v>2.5</v>
@@ -50484,7 +50490,7 @@
         <v>258</v>
       </c>
       <c r="P237" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q237">
         <v>2.75</v>
@@ -50690,7 +50696,7 @@
         <v>259</v>
       </c>
       <c r="P238" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q238">
         <v>2.6</v>
@@ -50896,7 +50902,7 @@
         <v>109</v>
       </c>
       <c r="P239" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q239">
         <v>3.1</v>
@@ -50977,7 +50983,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ239">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR239">
         <v>1.42</v>
@@ -51102,7 +51108,7 @@
         <v>140</v>
       </c>
       <c r="P240" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -51514,7 +51520,7 @@
         <v>109</v>
       </c>
       <c r="P242" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q242">
         <v>3.1</v>
@@ -51926,7 +51932,7 @@
         <v>161</v>
       </c>
       <c r="P244" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q244">
         <v>2.1</v>
@@ -52338,7 +52344,7 @@
         <v>156</v>
       </c>
       <c r="P246" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q246">
         <v>2.5</v>
@@ -52956,7 +52962,7 @@
         <v>264</v>
       </c>
       <c r="P249" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q249">
         <v>2.5</v>
@@ -53162,7 +53168,7 @@
         <v>265</v>
       </c>
       <c r="P250" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q250">
         <v>3.2</v>
@@ -53368,7 +53374,7 @@
         <v>109</v>
       </c>
       <c r="P251" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q251">
         <v>2.75</v>
@@ -53574,7 +53580,7 @@
         <v>266</v>
       </c>
       <c r="P252" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q252">
         <v>2.25</v>
@@ -54604,7 +54610,7 @@
         <v>271</v>
       </c>
       <c r="P257" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Q257">
         <v>2.63</v>
@@ -54810,7 +54816,7 @@
         <v>272</v>
       </c>
       <c r="P258" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q258">
         <v>2.3</v>
@@ -55016,7 +55022,7 @@
         <v>109</v>
       </c>
       <c r="P259" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q259">
         <v>3.1</v>
@@ -55303,7 +55309,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ260">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR260">
         <v>1.87</v>
@@ -55428,7 +55434,7 @@
         <v>274</v>
       </c>
       <c r="P261" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -55634,7 +55640,7 @@
         <v>275</v>
       </c>
       <c r="P262" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q262">
         <v>2.5</v>
@@ -55840,7 +55846,7 @@
         <v>234</v>
       </c>
       <c r="P263" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Q263">
         <v>2.25</v>
@@ -56046,7 +56052,7 @@
         <v>109</v>
       </c>
       <c r="P264" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q264">
         <v>2.75</v>
@@ -56252,7 +56258,7 @@
         <v>276</v>
       </c>
       <c r="P265" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q265">
         <v>2.88</v>
@@ -56458,7 +56464,7 @@
         <v>109</v>
       </c>
       <c r="P266" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q266">
         <v>3.4</v>
@@ -56870,7 +56876,7 @@
         <v>278</v>
       </c>
       <c r="P268" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q268">
         <v>2.2</v>
@@ -57076,7 +57082,7 @@
         <v>279</v>
       </c>
       <c r="P269" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57282,7 +57288,7 @@
         <v>280</v>
       </c>
       <c r="P270" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Q270">
         <v>3.35</v>
@@ -57694,7 +57700,7 @@
         <v>282</v>
       </c>
       <c r="P272" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q272">
         <v>2.38</v>
@@ -57900,7 +57906,7 @@
         <v>283</v>
       </c>
       <c r="P273" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q273">
         <v>3.4</v>
@@ -58106,7 +58112,7 @@
         <v>284</v>
       </c>
       <c r="P274" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q274">
         <v>3</v>
@@ -58187,7 +58193,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ274">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR274">
         <v>1.59</v>
@@ -58518,7 +58524,7 @@
         <v>285</v>
       </c>
       <c r="P276" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q276">
         <v>2.63</v>
@@ -58724,7 +58730,7 @@
         <v>286</v>
       </c>
       <c r="P277" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -59136,7 +59142,7 @@
         <v>288</v>
       </c>
       <c r="P279" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Q279">
         <v>2.63</v>
@@ -59548,7 +59554,7 @@
         <v>290</v>
       </c>
       <c r="P281" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Q281">
         <v>2.25</v>
@@ -59754,7 +59760,7 @@
         <v>291</v>
       </c>
       <c r="P282" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Q282">
         <v>2.88</v>
@@ -60372,7 +60378,7 @@
         <v>293</v>
       </c>
       <c r="P285" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Q285">
         <v>2.5</v>
@@ -60453,7 +60459,7 @@
         <v>1</v>
       </c>
       <c r="AQ285">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR285">
         <v>1.56</v>
@@ -60578,7 +60584,7 @@
         <v>294</v>
       </c>
       <c r="P286" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -62226,7 +62232,7 @@
         <v>112</v>
       </c>
       <c r="P294" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Q294">
         <v>3.1</v>
@@ -62432,7 +62438,7 @@
         <v>122</v>
       </c>
       <c r="P295" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Q295">
         <v>2.4</v>
@@ -62844,7 +62850,7 @@
         <v>301</v>
       </c>
       <c r="P297" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Q297">
         <v>3.4</v>
@@ -63256,7 +63262,7 @@
         <v>302</v>
       </c>
       <c r="P299" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Q299">
         <v>3.2</v>
@@ -63874,7 +63880,7 @@
         <v>305</v>
       </c>
       <c r="P302" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Q302">
         <v>2.2</v>
@@ -64080,7 +64086,7 @@
         <v>255</v>
       </c>
       <c r="P303" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q303">
         <v>2.5</v>
@@ -64286,7 +64292,7 @@
         <v>306</v>
       </c>
       <c r="P304" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Q304">
         <v>2.5</v>
@@ -64492,7 +64498,7 @@
         <v>307</v>
       </c>
       <c r="P305" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -64904,7 +64910,7 @@
         <v>199</v>
       </c>
       <c r="P307" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="Q307">
         <v>3.26</v>
@@ -65728,7 +65734,7 @@
         <v>312</v>
       </c>
       <c r="P311" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="Q311">
         <v>1.83</v>
@@ -66346,7 +66352,7 @@
         <v>288</v>
       </c>
       <c r="P314" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Q314">
         <v>0</v>
@@ -66552,7 +66558,7 @@
         <v>314</v>
       </c>
       <c r="P315" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Q315">
         <v>3.5</v>
@@ -66964,7 +66970,7 @@
         <v>316</v>
       </c>
       <c r="P317" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Q317">
         <v>2.63</v>
@@ -67788,7 +67794,7 @@
         <v>320</v>
       </c>
       <c r="P321" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q321">
         <v>2.2</v>
@@ -68200,7 +68206,7 @@
         <v>322</v>
       </c>
       <c r="P323" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q323">
         <v>2.63</v>
@@ -68612,7 +68618,7 @@
         <v>324</v>
       </c>
       <c r="P325" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Q325">
         <v>2.3</v>
@@ -69230,7 +69236,7 @@
         <v>327</v>
       </c>
       <c r="P328" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Q328">
         <v>2.55</v>
@@ -69308,7 +69314,7 @@
         <v>1.64</v>
       </c>
       <c r="AP328">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ328">
         <v>1.58</v>
@@ -69436,7 +69442,7 @@
         <v>237</v>
       </c>
       <c r="P329" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="Q329">
         <v>2.15</v>
@@ -69642,7 +69648,7 @@
         <v>109</v>
       </c>
       <c r="P330" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="Q330">
         <v>2.8</v>
@@ -70260,7 +70266,7 @@
         <v>329</v>
       </c>
       <c r="P333" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Q333">
         <v>1.95</v>
@@ -70466,7 +70472,7 @@
         <v>330</v>
       </c>
       <c r="P334" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Q334">
         <v>2.05</v>
@@ -70878,7 +70884,7 @@
         <v>109</v>
       </c>
       <c r="P336" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="Q336">
         <v>2.63</v>
@@ -71084,7 +71090,7 @@
         <v>331</v>
       </c>
       <c r="P337" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="Q337">
         <v>2.5</v>
@@ -71248,7 +71254,7 @@
         <v>337</v>
       </c>
       <c r="B338">
-        <v>7781417</v>
+        <v>7781416</v>
       </c>
       <c r="C338" t="s">
         <v>68</v>
@@ -71257,16 +71263,16 @@
         <v>69</v>
       </c>
       <c r="E338" s="2">
-        <v>45857.88541666666</v>
+        <v>45857.85416666666</v>
       </c>
       <c r="F338">
         <v>0</v>
       </c>
       <c r="G338" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H338" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I338">
         <v>1</v>
@@ -71281,31 +71287,31 @@
         <v>2</v>
       </c>
       <c r="M338">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N338">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O338" t="s">
         <v>332</v>
       </c>
       <c r="P338" t="s">
-        <v>311</v>
+        <v>482</v>
       </c>
       <c r="Q338">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="R338">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S338">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="T338">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="U338">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="V338">
         <v>2.1</v>
@@ -71320,13 +71326,13 @@
         <v>1.18</v>
       </c>
       <c r="Z338">
-        <v>1.45</v>
+        <v>2.11</v>
       </c>
       <c r="AA338">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="AB338">
-        <v>6</v>
+        <v>3.08</v>
       </c>
       <c r="AC338">
         <v>1.01</v>
@@ -71347,55 +71353,55 @@
         <v>2.63</v>
       </c>
       <c r="AI338">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AJ338">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AK338">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="AL338">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AM338">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="AN338">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="AO338">
-        <v>0.73</v>
+        <v>0.58</v>
       </c>
       <c r="AP338">
-        <v>2.08</v>
+        <v>1.33</v>
       </c>
       <c r="AQ338">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="AR338">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="AS338">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="AT338">
-        <v>3.27</v>
+        <v>2.76</v>
       </c>
       <c r="AU338">
+        <v>7</v>
+      </c>
+      <c r="AV338">
         <v>5</v>
       </c>
-      <c r="AV338">
-        <v>2</v>
-      </c>
       <c r="AW338">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AX338">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY338">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ338">
         <v>7</v>
@@ -71404,48 +71410,254 @@
         <v>7</v>
       </c>
       <c r="BB338">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BC338">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD338">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="BE338">
         <v>6.75</v>
       </c>
       <c r="BF338">
+        <v>2.55</v>
+      </c>
+      <c r="BG338">
+        <v>1.24</v>
+      </c>
+      <c r="BH338">
+        <v>3.55</v>
+      </c>
+      <c r="BI338">
+        <v>1.43</v>
+      </c>
+      <c r="BJ338">
+        <v>2.6</v>
+      </c>
+      <c r="BK338">
+        <v>1.7</v>
+      </c>
+      <c r="BL338">
+        <v>2.02</v>
+      </c>
+      <c r="BM338">
+        <v>2.08</v>
+      </c>
+      <c r="BN338">
+        <v>1.65</v>
+      </c>
+      <c r="BO338">
+        <v>2.65</v>
+      </c>
+      <c r="BP338">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="339" spans="1:68">
+      <c r="A339" s="1">
+        <v>338</v>
+      </c>
+      <c r="B339">
+        <v>7781417</v>
+      </c>
+      <c r="C339" t="s">
+        <v>68</v>
+      </c>
+      <c r="D339" t="s">
+        <v>69</v>
+      </c>
+      <c r="E339" s="2">
+        <v>45857.88541666666</v>
+      </c>
+      <c r="F339">
+        <v>0</v>
+      </c>
+      <c r="G339" t="s">
+        <v>74</v>
+      </c>
+      <c r="H339" t="s">
+        <v>75</v>
+      </c>
+      <c r="I339">
+        <v>1</v>
+      </c>
+      <c r="J339">
+        <v>0</v>
+      </c>
+      <c r="K339">
+        <v>1</v>
+      </c>
+      <c r="L339">
+        <v>2</v>
+      </c>
+      <c r="M339">
+        <v>1</v>
+      </c>
+      <c r="N339">
+        <v>3</v>
+      </c>
+      <c r="O339" t="s">
+        <v>333</v>
+      </c>
+      <c r="P339" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q339">
+        <v>1.95</v>
+      </c>
+      <c r="R339">
+        <v>2.63</v>
+      </c>
+      <c r="S339">
+        <v>5.5</v>
+      </c>
+      <c r="T339">
+        <v>1.25</v>
+      </c>
+      <c r="U339">
+        <v>3.75</v>
+      </c>
+      <c r="V339">
+        <v>2.1</v>
+      </c>
+      <c r="W339">
+        <v>1.67</v>
+      </c>
+      <c r="X339">
+        <v>4.5</v>
+      </c>
+      <c r="Y339">
+        <v>1.18</v>
+      </c>
+      <c r="Z339">
+        <v>1.45</v>
+      </c>
+      <c r="AA339">
+        <v>3.8</v>
+      </c>
+      <c r="AB339">
+        <v>6</v>
+      </c>
+      <c r="AC339">
+        <v>1.01</v>
+      </c>
+      <c r="AD339">
+        <v>17</v>
+      </c>
+      <c r="AE339">
+        <v>1.17</v>
+      </c>
+      <c r="AF339">
+        <v>5</v>
+      </c>
+      <c r="AG339">
+        <v>1.45</v>
+      </c>
+      <c r="AH339">
+        <v>2.63</v>
+      </c>
+      <c r="AI339">
+        <v>1.57</v>
+      </c>
+      <c r="AJ339">
+        <v>2.25</v>
+      </c>
+      <c r="AK339">
+        <v>1.14</v>
+      </c>
+      <c r="AL339">
+        <v>1.2</v>
+      </c>
+      <c r="AM339">
+        <v>2.5</v>
+      </c>
+      <c r="AN339">
+        <v>2</v>
+      </c>
+      <c r="AO339">
+        <v>0.73</v>
+      </c>
+      <c r="AP339">
+        <v>2.08</v>
+      </c>
+      <c r="AQ339">
+        <v>0.67</v>
+      </c>
+      <c r="AR339">
+        <v>1.81</v>
+      </c>
+      <c r="AS339">
+        <v>1.46</v>
+      </c>
+      <c r="AT339">
+        <v>3.27</v>
+      </c>
+      <c r="AU339">
+        <v>5</v>
+      </c>
+      <c r="AV339">
+        <v>2</v>
+      </c>
+      <c r="AW339">
+        <v>14</v>
+      </c>
+      <c r="AX339">
+        <v>5</v>
+      </c>
+      <c r="AY339">
+        <v>19</v>
+      </c>
+      <c r="AZ339">
+        <v>7</v>
+      </c>
+      <c r="BA339">
+        <v>7</v>
+      </c>
+      <c r="BB339">
+        <v>0</v>
+      </c>
+      <c r="BC339">
+        <v>7</v>
+      </c>
+      <c r="BD339">
+        <v>1.46</v>
+      </c>
+      <c r="BE339">
+        <v>6.75</v>
+      </c>
+      <c r="BF339">
         <v>3.05</v>
       </c>
-      <c r="BG338">
+      <c r="BG339">
         <v>1.34</v>
       </c>
-      <c r="BH338">
+      <c r="BH339">
         <v>2.9</v>
       </c>
-      <c r="BI338">
+      <c r="BI339">
         <v>1.58</v>
       </c>
-      <c r="BJ338">
+      <c r="BJ339">
         <v>2.2</v>
       </c>
-      <c r="BK338">
+      <c r="BK339">
         <v>1.95</v>
       </c>
-      <c r="BL338">
+      <c r="BL339">
         <v>1.74</v>
       </c>
-      <c r="BM338">
+      <c r="BM339">
         <v>2.48</v>
       </c>
-      <c r="BN338">
+      <c r="BN339">
         <v>1.47</v>
       </c>
-      <c r="BO338">
+      <c r="BO339">
         <v>3.2</v>
       </c>
-      <c r="BP338">
+      <c r="BP339">
         <v>1.28</v>
       </c>
     </row>
